--- a/LubanConfig/DataTables/Datas/#ArtifactParam.xlsx
+++ b/LubanConfig/DataTables/Datas/#ArtifactParam.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\monster-ball\LubanConfig\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A45E50E6-447E-454C-9DB8-CD08A0BB8A14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0EDA055-20B1-43C6-8853-BD063FE19742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,10 +22,36 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
+    <author>Hannya T</author>
     <author/>
   </authors>
   <commentList>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{768C14FC-6E31-47AF-A906-3057EBFEC3E3}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Hannya T:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Internal ID, can just follow the index format by making it i++
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -40,7 +66,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="D1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -50,12 +76,12 @@
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">String
-The displayed name for the artifact
+The displayed name for the artifact in artifact selection page
 </t>
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="E1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -64,13 +90,19 @@
             <rFont val="Arial"/>
             <scheme val="minor"/>
           </rPr>
-          <t>Int
-Purchase price of the artifact, in points</t>
+          <t xml:space="preserve">String
+Ball ID if the artifact is </t>
         </r>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
-      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">a </t>
+        </r>
         <r>
           <rPr>
             <sz val="10"/>
@@ -78,12 +110,11 @@
             <rFont val="Arial"/>
             <scheme val="minor"/>
           </rPr>
-          <t>String
-Ball ID if the artifact is ball specific upgrade</t>
+          <t>ball specific upgrade</t>
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="F1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
@@ -97,7 +128,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="G1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
@@ -111,7 +142,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{A2122591-74C1-4294-AD07-432D4CD2F7B4}">
+    <comment ref="I1" authorId="1" shapeId="0" xr:uid="{A2122591-74C1-4294-AD07-432D4CD2F7B4}">
       <text>
         <r>
           <rPr>
@@ -125,7 +156,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{A90D4D9A-BBFE-4379-8D00-4A158030AE29}">
+    <comment ref="K1" authorId="1" shapeId="0" xr:uid="{A90D4D9A-BBFE-4379-8D00-4A158030AE29}">
       <text>
         <r>
           <rPr>
@@ -139,7 +170,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
+    <comment ref="M1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
       <text>
         <r>
           <rPr>
@@ -158,7 +189,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="38">
   <si>
     <t>##var</t>
   </si>
@@ -167,9 +198,6 @@
   </si>
   <si>
     <t>ArtifactName</t>
-  </si>
-  <si>
-    <t>ArtifactPrice</t>
   </si>
   <si>
     <t>BallRelation</t>
@@ -185,9 +213,6 @@
   </si>
   <si>
     <t>string</t>
-  </si>
-  <si>
-    <t>int</t>
   </si>
   <si>
     <t>#group</t>
@@ -305,7 +330,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -338,6 +363,19 @@
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -596,8 +634,9 @@
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="17.33203125" customWidth="1"/>
-    <col min="5" max="6" width="18.6640625" customWidth="1"/>
-    <col min="7" max="7" width="50" customWidth="1"/>
+    <col min="5" max="5" width="18.6640625" customWidth="1"/>
+    <col min="6" max="6" width="71.88671875" customWidth="1"/>
+    <col min="7" max="7" width="20.109375" customWidth="1"/>
     <col min="8" max="8" width="15.21875" customWidth="1"/>
     <col min="10" max="10" width="14.33203125" customWidth="1"/>
   </cols>
@@ -607,7 +646,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -621,29 +660,26 @@
       <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
+      <c r="G1" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>16</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="L1" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>6</v>
+      <c r="M1" s="1" t="s">
+        <v>5</v>
       </c>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
@@ -663,46 +699,43 @@
     </row>
     <row r="2" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="D2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>8</v>
+      <c r="G2" s="2" t="s">
+        <v>15</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>19</v>
+      <c r="I2" s="2" t="s">
+        <v>15</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K2" s="3" t="s">
-        <v>19</v>
+      <c r="K2" s="2" t="s">
+        <v>15</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>17</v>
+      <c r="M2" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
@@ -722,7 +755,7 @@
     </row>
     <row r="3" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -736,7 +769,6 @@
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="1"/>
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
       <c r="Q3" s="1"/>
@@ -755,7 +787,7 @@
     </row>
     <row r="4" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -769,7 +801,6 @@
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
       <c r="O4" s="1"/>
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
@@ -792,32 +823,29 @@
         <v>0</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="1">
-        <v>100000</v>
+      <c r="G5" s="2" t="s">
+        <v>18</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I5" s="1">
+      <c r="H5" s="1">
         <v>4</v>
       </c>
+      <c r="I5" s="1"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="2" t="s">
-        <v>26</v>
+      <c r="M5" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="O5" s="1"/>
       <c r="P5" s="1"/>
@@ -841,30 +869,27 @@
         <v>1</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="1"/>
+      <c r="F6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" s="1">
-        <v>50000</v>
-      </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="I6" s="1">
+      <c r="H6" s="1">
         <v>200</v>
       </c>
+      <c r="I6" s="1"/>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="2" t="s">
-        <v>27</v>
+      <c r="M6" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
@@ -888,34 +913,31 @@
         <v>2</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="1"/>
+      <c r="F7" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="H7" s="1">
+        <v>50</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="J7" s="1">
         <v>30</v>
       </c>
-      <c r="E7" s="1">
-        <v>75000</v>
-      </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I7" s="1">
-        <v>50</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K7" s="1">
-        <v>30</v>
-      </c>
+      <c r="K7" s="1"/>
       <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="2" t="s">
-        <v>30</v>
+      <c r="M7" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
@@ -939,30 +961,27 @@
         <v>3</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
-      <c r="E8" s="1">
-        <v>40000</v>
-      </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H8" s="2" t="s">
+      <c r="E8" s="1"/>
+      <c r="F8" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="I8" s="1">
+      <c r="G8" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H8" s="1">
         <v>100</v>
       </c>
+      <c r="I8" s="1"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1" t="s">
-        <v>34</v>
+      <c r="M8" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
@@ -986,32 +1005,29 @@
         <v>4</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
-      <c r="E9" s="1">
-        <v>100000</v>
+      <c r="E9" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>37</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
-      <c r="H9" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="I9" s="1">
+      <c r="H9" s="1">
         <v>30</v>
       </c>
+      <c r="I9" s="1"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1" t="s">
-        <v>36</v>
+      <c r="M9" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
@@ -1043,7 +1059,6 @@
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>

--- a/LubanConfig/DataTables/Datas/#ArtifactParam.xlsx
+++ b/LubanConfig/DataTables/Datas/#ArtifactParam.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\601\monster-ball\LubanConfig\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADB73DEB-06D6-4CB6-AABA-0C4D36B99329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A7D1785-4DBF-484B-9B9A-508140F72185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -59,6 +59,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">String
@@ -74,6 +75,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">String
@@ -89,6 +91,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">String
@@ -109,6 +112,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>ball specific upgrade</t>
@@ -122,6 +126,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>String
@@ -136,6 +141,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>[string, int]
@@ -150,6 +156,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>[string, int]
@@ -164,6 +171,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>[string, int]
@@ -178,6 +186,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Artifact's ingame Icon
@@ -238,9 +247,6 @@
   </si>
   <si>
     <t>ID</t>
-  </si>
-  <si>
-    <t>ArtifactName</t>
   </si>
   <si>
     <t>BallRelation</t>
@@ -352,12 +358,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>FireTrailDuration</t>
-  </si>
-  <si>
-    <t>FireTrailSize</t>
-  </si>
-  <si>
     <t>Increase the duration of the fire trail left by the fireball by 30%</t>
   </si>
   <si>
@@ -367,13 +367,7 @@
     <t>FireCoal</t>
   </si>
   <si>
-    <t>FireTrailUptime</t>
-  </si>
-  <si>
     <t>Increase fireball's firetrail uptime by 30% when triggered.</t>
-  </si>
-  <si>
-    <t>SplitCount</t>
   </si>
   <si>
     <t>Splitball</t>
@@ -383,9 +377,6 @@
   </si>
   <si>
     <t>BallAttack</t>
-  </si>
-  <si>
-    <t>SplitSize</t>
   </si>
   <si>
     <t>Increase splitball's size by 30%.</t>
@@ -403,16 +394,10 @@
     <t>Reduce stenball's speed by 30%.</t>
   </si>
   <si>
-    <t>IceSize</t>
-  </si>
-  <si>
     <t>Iceball</t>
   </si>
   <si>
     <t>Increase the size of the ice zone left by the iceball by 30%.</t>
-  </si>
-  <si>
-    <t>IceAtk</t>
   </si>
   <si>
     <t>Increase iceball's attack by 30%, but increase skill requirment by 50%.</t>
@@ -424,13 +409,7 @@
     <t>Increase lightningball's zapping detection zone size by 30%, but make lightningball 40% more expensive to purchase.</t>
   </si>
   <si>
-    <t>LightningFrequency</t>
-  </si>
-  <si>
     <t>Increase lightningball's zapping frequency by 40%, but reduce its attack by 50%.</t>
-  </si>
-  <si>
-    <t>LightingReq</t>
   </si>
   <si>
     <t>Reduce lightningball's skill requirement by 30%, but reduce its speed by 30%.</t>
@@ -543,6 +522,46 @@
     <t>StenSpeed</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>Artifacts.ID</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FireTrailDuration</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ArtifactName</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FireTrailSize</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FireTrailUptime</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SplitSize</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>IceSize</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>IceAtk</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LightningFrequency</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LightingReq</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -559,6 +578,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -886,40 +906,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="G1" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="L1" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="M1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
@@ -939,43 +959,43 @@
     </row>
     <row r="2" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>7</v>
-      </c>
       <c r="E2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
@@ -995,7 +1015,7 @@
     </row>
     <row r="3" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -1027,7 +1047,7 @@
     </row>
     <row r="4" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1063,19 +1083,19 @@
         <v>0</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>33</v>
+        <v>79</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="H5" s="1">
         <v>1.3</v>
@@ -1085,7 +1105,7 @@
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
       <c r="M5" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O5" s="1"/>
       <c r="P5" s="1"/>
@@ -1109,19 +1129,19 @@
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="H6" s="5">
         <v>1.3</v>
@@ -1129,7 +1149,7 @@
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
@@ -1153,19 +1173,19 @@
         <v>2</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>38</v>
+        <v>82</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="H7" s="5">
         <v>1.3</v>
@@ -1194,25 +1214,25 @@
         <v>3</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="H8" s="1">
         <v>1.5</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="J8" s="5">
         <v>0.7</v>
@@ -1241,19 +1261,19 @@
         <v>4</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="H9" s="1">
         <v>1.3</v>
@@ -1282,19 +1302,19 @@
         <v>5</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="F10" s="2" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H10" s="1">
         <v>0.7</v>
@@ -1304,7 +1324,7 @@
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
@@ -1327,20 +1347,20 @@
       <c r="B11" s="1">
         <v>6</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>87</v>
+      <c r="C11" s="1" t="s">
+        <v>77</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="H11" s="1">
         <v>1.3</v>
@@ -1373,19 +1393,19 @@
         <v>7</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="H12" s="1">
         <v>1.3</v>
@@ -1418,25 +1438,25 @@
         <v>8</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="H13" s="1">
         <v>1.3</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="J13" s="5">
         <v>1.5</v>
@@ -1463,26 +1483,26 @@
       <c r="B14" s="1">
         <v>9</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>64</v>
+      <c r="C14" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="H14" s="1">
         <v>1.3</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="J14" s="5">
         <v>1.4</v>
@@ -1510,25 +1530,25 @@
         <v>10</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>57</v>
+        <v>86</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="H15" s="1">
         <v>0.6</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="J15" s="5">
         <v>0.5</v>
@@ -1556,25 +1576,25 @@
         <v>11</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>59</v>
+        <v>87</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="H16" s="1">
         <v>0.7</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="J16" s="5">
         <v>0.7</v>
@@ -1601,17 +1621,29 @@
       <c r="B17" s="1">
         <v>12</v>
       </c>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
+      <c r="C17" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
+      <c r="F17" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H17" s="1">
+        <v>200</v>
+      </c>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
+      <c r="M17" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
       <c r="P17" s="1"/>
@@ -1635,27 +1667,31 @@
         <v>13</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E18" s="1"/>
-      <c r="F18" s="2" t="s">
-        <v>22</v>
+      <c r="F18" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H18" s="1">
-        <v>200</v>
+        <v>50</v>
       </c>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
+      <c r="I18" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J18" s="1">
+        <v>30</v>
+      </c>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
       <c r="M18" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
@@ -1679,32 +1715,28 @@
       <c r="B19" s="1">
         <v>14</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>24</v>
+      <c r="C19" s="1" t="s">
+        <v>27</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>24</v>
+      <c r="D19" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="E19" s="1"/>
-      <c r="F19" s="4" t="s">
-        <v>25</v>
+      <c r="F19" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H19" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
-      <c r="I19" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="J19" s="1">
-        <v>30</v>
-      </c>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
-      <c r="M19" s="2" t="s">
-        <v>24</v>
+      <c r="M19" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
@@ -1725,32 +1757,7 @@
     </row>
     <row r="20" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1"/>
-      <c r="B20" s="1">
-        <v>15</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E20" s="1"/>
-      <c r="F20" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H20" s="1">
-        <v>100</v>
-      </c>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
-      <c r="M20" s="1" t="s">
-        <v>28</v>
-      </c>
+      <c r="B20" s="1"/>
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
       <c r="P20" s="1"/>

--- a/LubanConfig/DataTables/Datas/#ArtifactParam.xlsx
+++ b/LubanConfig/DataTables/Datas/#ArtifactParam.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\601\monster-ball\LubanConfig\DataTables\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\monster-ball\LubanConfig\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A7D1785-4DBF-484B-9B9A-508140F72185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7C2736F-42ED-444C-ADB1-E8D23982F7B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ArtifactParam" sheetId="1" r:id="rId1"/>
@@ -241,7 +241,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="96">
   <si>
     <t>##var</t>
   </si>
@@ -309,9 +309,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Pheonixfeather</t>
-  </si>
-  <si>
     <t>Invester</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -347,9 +344,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Splitfire</t>
-  </si>
-  <si>
     <t>Splitball</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -362,9 +356,6 @@
   </si>
   <si>
     <t>Increase the size of the fire trail left by the fireball by 30%</t>
-  </si>
-  <si>
-    <t>FireCoal</t>
   </si>
   <si>
     <t>Increase fireball's firetrail uptime by 30% when triggered.</t>
@@ -562,12 +553,55 @@
     <t>LightingReq</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>EverlastingCoal</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PheonixFeather</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ExtraFuel</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HologramProjector</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SplitFire</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>EmailNotification</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>EyeOfFrost</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LightningRod</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>StormCaller</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BountifulSupply</t>
+  </si>
+  <si>
+    <t>BottledThunder</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -631,12 +665,18 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -651,7 +691,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -671,9 +711,15 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -890,18 +936,19 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AC1001"/>
-  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="17.28515625" customWidth="1"/>
-    <col min="5" max="5" width="18.7109375" customWidth="1"/>
-    <col min="6" max="6" width="71.85546875" customWidth="1"/>
-    <col min="7" max="7" width="20.140625" customWidth="1"/>
-    <col min="8" max="8" width="15.28515625" customWidth="1"/>
-    <col min="10" max="10" width="14.28515625" customWidth="1"/>
+    <col min="4" max="4" width="17.33203125" customWidth="1"/>
+    <col min="5" max="5" width="18.6640625" customWidth="1"/>
+    <col min="6" max="6" width="71.88671875" customWidth="1"/>
+    <col min="7" max="7" width="20.109375" customWidth="1"/>
+    <col min="8" max="8" width="15.33203125" customWidth="1"/>
+    <col min="10" max="10" width="14.33203125" customWidth="1"/>
+    <col min="13" max="13" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:29" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -912,7 +959,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>2</v>
@@ -957,7 +1004,7 @@
       <c r="AB1" s="1"/>
       <c r="AC1" s="1"/>
     </row>
-    <row r="2" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:29" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -965,7 +1012,7 @@
         <v>13</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>6</v>
@@ -980,19 +1027,19 @@
         <v>11</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>11</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>11</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="M2" s="2" t="s">
         <v>11</v>
@@ -1013,7 +1060,7 @@
       <c r="AB2" s="1"/>
       <c r="AC2" s="1"/>
     </row>
-    <row r="3" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:29" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -1045,7 +1092,7 @@
       <c r="AB3" s="1"/>
       <c r="AC3" s="1"/>
     </row>
-    <row r="4" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:29" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -1077,25 +1124,25 @@
       <c r="AB4" s="1"/>
       <c r="AC4" s="1"/>
     </row>
-    <row r="5" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" ht="15.75" customHeight="1">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>0</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>9</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="H5" s="1">
         <v>1.3</v>
@@ -1104,8 +1151,8 @@
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
-      <c r="M5" s="2" t="s">
-        <v>19</v>
+      <c r="M5" s="7" t="s">
+        <v>86</v>
       </c>
       <c r="O5" s="1"/>
       <c r="P5" s="1"/>
@@ -1123,33 +1170,33 @@
       <c r="AB5" s="1"/>
       <c r="AC5" s="1"/>
     </row>
-    <row r="6" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" ht="15.75" customHeight="1">
       <c r="A6" s="1"/>
       <c r="B6" s="1">
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>9</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="H6" s="5">
         <v>1.3</v>
       </c>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
-      <c r="M6" s="2" t="s">
-        <v>34</v>
+      <c r="M6" s="7" t="s">
+        <v>85</v>
       </c>
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
@@ -1167,31 +1214,34 @@
       <c r="AB6" s="1"/>
       <c r="AC6" s="1"/>
     </row>
-    <row r="7" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" ht="30" customHeight="1">
       <c r="A7" s="1"/>
       <c r="B7" s="1">
         <v>2</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>9</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="H7" s="5">
         <v>1.3</v>
       </c>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
+      <c r="M7" s="7" t="s">
+        <v>87</v>
+      </c>
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
@@ -1208,37 +1258,40 @@
       <c r="AB7" s="1"/>
       <c r="AC7" s="1"/>
     </row>
-    <row r="8" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" ht="15.75" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="1">
         <v>3</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="H8" s="1">
         <v>1.5</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="J8" s="5">
         <v>0.7</v>
       </c>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
+      <c r="M8" s="7" t="s">
+        <v>88</v>
+      </c>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
@@ -1255,31 +1308,34 @@
       <c r="AB8" s="1"/>
       <c r="AC8" s="1"/>
     </row>
-    <row r="9" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" ht="15.75" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="1">
         <v>4</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="G9" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="H9" s="1">
         <v>1.3</v>
       </c>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
+      <c r="M9" s="7" t="s">
+        <v>94</v>
+      </c>
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
@@ -1296,25 +1352,25 @@
       <c r="AB9" s="1"/>
       <c r="AC9" s="1"/>
     </row>
-    <row r="10" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" ht="15.75" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="1">
         <v>5</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H10" s="1">
         <v>0.7</v>
@@ -1323,8 +1379,8 @@
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
-      <c r="M10" s="1" t="s">
-        <v>29</v>
+      <c r="M10" s="7" t="s">
+        <v>89</v>
       </c>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
@@ -1342,25 +1398,25 @@
       <c r="AB10" s="1"/>
       <c r="AC10" s="1"/>
     </row>
-    <row r="11" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" ht="15.75" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="1">
         <v>6</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H11" s="1">
         <v>1.3</v>
@@ -1369,7 +1425,9 @@
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
+      <c r="M11" s="7" t="s">
+        <v>90</v>
+      </c>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
@@ -1387,25 +1445,25 @@
       <c r="AB11" s="1"/>
       <c r="AC11" s="1"/>
     </row>
-    <row r="12" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:29" ht="15.75" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="1">
         <v>7</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H12" s="1">
         <v>1.3</v>
@@ -1414,7 +1472,9 @@
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
+      <c r="M12" s="7" t="s">
+        <v>91</v>
+      </c>
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
@@ -1432,34 +1492,37 @@
       <c r="AB12" s="1"/>
       <c r="AC12" s="1"/>
     </row>
-    <row r="13" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:29" ht="15.75" customHeight="1">
       <c r="A13" s="1"/>
       <c r="B13" s="1">
         <v>8</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H13" s="1">
         <v>1.3</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="J13" s="5">
         <v>1.5</v>
+      </c>
+      <c r="M13" s="8" t="s">
+        <v>70</v>
       </c>
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
@@ -1478,34 +1541,37 @@
       <c r="AB13" s="1"/>
       <c r="AC13" s="1"/>
     </row>
-    <row r="14" spans="1:29" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:29" ht="28.5" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="1">
         <v>9</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H14" s="1">
         <v>1.3</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="J14" s="5">
         <v>1.4</v>
+      </c>
+      <c r="M14" s="7" t="s">
+        <v>92</v>
       </c>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
@@ -1524,34 +1590,37 @@
       <c r="AB14" s="1"/>
       <c r="AC14" s="1"/>
     </row>
-    <row r="15" spans="1:29" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:29" ht="32.25" customHeight="1">
       <c r="A15" s="1"/>
       <c r="B15" s="1">
         <v>10</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="H15" s="1">
         <v>0.6</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="J15" s="5">
         <v>0.5</v>
+      </c>
+      <c r="M15" s="7" t="s">
+        <v>93</v>
       </c>
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
@@ -1570,34 +1639,37 @@
       <c r="AB15" s="1"/>
       <c r="AC15" s="1"/>
     </row>
-    <row r="16" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:29" ht="15.75" customHeight="1">
       <c r="A16" s="1"/>
       <c r="B16" s="1">
         <v>11</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="H16" s="1">
         <v>0.7</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="J16" s="5">
         <v>0.7</v>
+      </c>
+      <c r="M16" s="7" t="s">
+        <v>95</v>
       </c>
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
@@ -1616,23 +1688,23 @@
       <c r="AB16" s="1"/>
       <c r="AC16" s="1"/>
     </row>
-    <row r="17" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:29" ht="15.75" customHeight="1">
       <c r="A17" s="1"/>
       <c r="B17" s="1">
         <v>12</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H17" s="1">
         <v>200</v>
@@ -1641,8 +1713,8 @@
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
-      <c r="M17" s="2" t="s">
-        <v>20</v>
+      <c r="M17" s="8" t="s">
+        <v>19</v>
       </c>
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
@@ -1661,37 +1733,37 @@
       <c r="AB17" s="1"/>
       <c r="AC17" s="1"/>
     </row>
-    <row r="18" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:29" ht="15.75" customHeight="1">
       <c r="A18" s="1"/>
       <c r="B18" s="1">
         <v>13</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H18" s="1">
         <v>50</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J18" s="1">
         <v>30</v>
       </c>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
-      <c r="M18" s="2" t="s">
-        <v>23</v>
+      <c r="M18" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
@@ -1710,23 +1782,23 @@
       <c r="AB18" s="1"/>
       <c r="AC18" s="1"/>
     </row>
-    <row r="19" spans="1:29" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:29" ht="35.25" customHeight="1">
       <c r="A19" s="1"/>
       <c r="B19" s="1">
         <v>14</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H19" s="1">
         <v>100</v>
@@ -1735,8 +1807,8 @@
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
-      <c r="M19" s="1" t="s">
-        <v>27</v>
+      <c r="M19" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
@@ -1755,7 +1827,7 @@
       <c r="AB19" s="1"/>
       <c r="AC19" s="1"/>
     </row>
-    <row r="20" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:29" ht="15.75" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="N20" s="1"/>
@@ -1775,7 +1847,7 @@
       <c r="AB20" s="1"/>
       <c r="AC20" s="1"/>
     </row>
-    <row r="21" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:29" ht="15.75" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="N21" s="1"/>
@@ -1795,7 +1867,7 @@
       <c r="AB21" s="1"/>
       <c r="AC21" s="1"/>
     </row>
-    <row r="22" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:29" ht="15.75" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -1826,7 +1898,7 @@
       <c r="AB22" s="1"/>
       <c r="AC22" s="1"/>
     </row>
-    <row r="23" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:29" ht="15.75" customHeight="1">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -1857,7 +1929,7 @@
       <c r="AB23" s="1"/>
       <c r="AC23" s="1"/>
     </row>
-    <row r="24" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:29" ht="15.75" customHeight="1">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -1888,7 +1960,7 @@
       <c r="AB24" s="1"/>
       <c r="AC24" s="1"/>
     </row>
-    <row r="25" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:29" ht="15.75" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -1919,7 +1991,7 @@
       <c r="AB25" s="1"/>
       <c r="AC25" s="1"/>
     </row>
-    <row r="26" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:29" ht="15.75" customHeight="1">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -1950,7 +2022,7 @@
       <c r="AB26" s="1"/>
       <c r="AC26" s="1"/>
     </row>
-    <row r="27" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:29" ht="15.75" customHeight="1">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -1981,7 +2053,7 @@
       <c r="AB27" s="1"/>
       <c r="AC27" s="1"/>
     </row>
-    <row r="28" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:29" ht="15.75" customHeight="1">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -2012,7 +2084,7 @@
       <c r="AB28" s="1"/>
       <c r="AC28" s="1"/>
     </row>
-    <row r="29" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:29" ht="15.75" customHeight="1">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -2043,7 +2115,7 @@
       <c r="AB29" s="1"/>
       <c r="AC29" s="1"/>
     </row>
-    <row r="30" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:29" ht="15.75" customHeight="1">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -2074,7 +2146,7 @@
       <c r="AB30" s="1"/>
       <c r="AC30" s="1"/>
     </row>
-    <row r="31" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:29" ht="15.75" customHeight="1">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -2105,7 +2177,7 @@
       <c r="AB31" s="1"/>
       <c r="AC31" s="1"/>
     </row>
-    <row r="32" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:29" ht="15.75" customHeight="1">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -2136,7 +2208,7 @@
       <c r="AB32" s="1"/>
       <c r="AC32" s="1"/>
     </row>
-    <row r="33" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:29" ht="15.75" customHeight="1">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -2167,7 +2239,7 @@
       <c r="AB33" s="1"/>
       <c r="AC33" s="1"/>
     </row>
-    <row r="34" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:29" ht="15.75" customHeight="1">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -2198,7 +2270,7 @@
       <c r="AB34" s="1"/>
       <c r="AC34" s="1"/>
     </row>
-    <row r="35" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:29" ht="15.75" customHeight="1">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -2229,7 +2301,7 @@
       <c r="AB35" s="1"/>
       <c r="AC35" s="1"/>
     </row>
-    <row r="36" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:29" ht="15.75" customHeight="1">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -2260,7 +2332,7 @@
       <c r="AB36" s="1"/>
       <c r="AC36" s="1"/>
     </row>
-    <row r="37" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:29" ht="15.75" customHeight="1">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -2291,7 +2363,7 @@
       <c r="AB37" s="1"/>
       <c r="AC37" s="1"/>
     </row>
-    <row r="38" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:29" ht="15.75" customHeight="1">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -2322,7 +2394,7 @@
       <c r="AB38" s="1"/>
       <c r="AC38" s="1"/>
     </row>
-    <row r="39" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:29" ht="15.75" customHeight="1">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -2353,7 +2425,7 @@
       <c r="AB39" s="1"/>
       <c r="AC39" s="1"/>
     </row>
-    <row r="40" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:29" ht="15.75" customHeight="1">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -2384,7 +2456,7 @@
       <c r="AB40" s="1"/>
       <c r="AC40" s="1"/>
     </row>
-    <row r="41" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:29" ht="15.75" customHeight="1">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -2415,7 +2487,7 @@
       <c r="AB41" s="1"/>
       <c r="AC41" s="1"/>
     </row>
-    <row r="42" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:29" ht="15.75" customHeight="1">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -2446,7 +2518,7 @@
       <c r="AB42" s="1"/>
       <c r="AC42" s="1"/>
     </row>
-    <row r="43" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:29" ht="15.75" customHeight="1">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -2477,7 +2549,7 @@
       <c r="AB43" s="1"/>
       <c r="AC43" s="1"/>
     </row>
-    <row r="44" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:29" ht="15.75" customHeight="1">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -2508,7 +2580,7 @@
       <c r="AB44" s="1"/>
       <c r="AC44" s="1"/>
     </row>
-    <row r="45" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:29" ht="15.75" customHeight="1">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -2539,7 +2611,7 @@
       <c r="AB45" s="1"/>
       <c r="AC45" s="1"/>
     </row>
-    <row r="46" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:29" ht="15.75" customHeight="1">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -2570,7 +2642,7 @@
       <c r="AB46" s="1"/>
       <c r="AC46" s="1"/>
     </row>
-    <row r="47" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:29" ht="15.75" customHeight="1">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -2601,7 +2673,7 @@
       <c r="AB47" s="1"/>
       <c r="AC47" s="1"/>
     </row>
-    <row r="48" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:29" ht="15.75" customHeight="1">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -2632,7 +2704,7 @@
       <c r="AB48" s="1"/>
       <c r="AC48" s="1"/>
     </row>
-    <row r="49" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:29" ht="15.75" customHeight="1">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -2663,7 +2735,7 @@
       <c r="AB49" s="1"/>
       <c r="AC49" s="1"/>
     </row>
-    <row r="50" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:29" ht="15.75" customHeight="1">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -2694,7 +2766,7 @@
       <c r="AB50" s="1"/>
       <c r="AC50" s="1"/>
     </row>
-    <row r="51" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:29" ht="15.75" customHeight="1">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -2725,7 +2797,7 @@
       <c r="AB51" s="1"/>
       <c r="AC51" s="1"/>
     </row>
-    <row r="52" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:29" ht="15.75" customHeight="1">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -2756,7 +2828,7 @@
       <c r="AB52" s="1"/>
       <c r="AC52" s="1"/>
     </row>
-    <row r="53" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:29" ht="15.75" customHeight="1">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -2787,7 +2859,7 @@
       <c r="AB53" s="1"/>
       <c r="AC53" s="1"/>
     </row>
-    <row r="54" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:29" ht="15.75" customHeight="1">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -2818,7 +2890,7 @@
       <c r="AB54" s="1"/>
       <c r="AC54" s="1"/>
     </row>
-    <row r="55" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:29" ht="15.75" customHeight="1">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -2849,7 +2921,7 @@
       <c r="AB55" s="1"/>
       <c r="AC55" s="1"/>
     </row>
-    <row r="56" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:29" ht="15.75" customHeight="1">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -2880,7 +2952,7 @@
       <c r="AB56" s="1"/>
       <c r="AC56" s="1"/>
     </row>
-    <row r="57" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:29" ht="15.75" customHeight="1">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -2911,7 +2983,7 @@
       <c r="AB57" s="1"/>
       <c r="AC57" s="1"/>
     </row>
-    <row r="58" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:29" ht="15.75" customHeight="1">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -2942,7 +3014,7 @@
       <c r="AB58" s="1"/>
       <c r="AC58" s="1"/>
     </row>
-    <row r="59" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:29" ht="15.75" customHeight="1">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -2973,7 +3045,7 @@
       <c r="AB59" s="1"/>
       <c r="AC59" s="1"/>
     </row>
-    <row r="60" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:29" ht="15.75" customHeight="1">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -3004,7 +3076,7 @@
       <c r="AB60" s="1"/>
       <c r="AC60" s="1"/>
     </row>
-    <row r="61" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:29" ht="15.75" customHeight="1">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -3035,7 +3107,7 @@
       <c r="AB61" s="1"/>
       <c r="AC61" s="1"/>
     </row>
-    <row r="62" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:29" ht="15.75" customHeight="1">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -3066,7 +3138,7 @@
       <c r="AB62" s="1"/>
       <c r="AC62" s="1"/>
     </row>
-    <row r="63" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:29" ht="15.75" customHeight="1">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -3097,7 +3169,7 @@
       <c r="AB63" s="1"/>
       <c r="AC63" s="1"/>
     </row>
-    <row r="64" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:29" ht="13.2">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -3128,7 +3200,7 @@
       <c r="AB64" s="1"/>
       <c r="AC64" s="1"/>
     </row>
-    <row r="65" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:29" ht="13.2">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -3159,7 +3231,7 @@
       <c r="AB65" s="1"/>
       <c r="AC65" s="1"/>
     </row>
-    <row r="66" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:29" ht="13.2">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -3190,7 +3262,7 @@
       <c r="AB66" s="1"/>
       <c r="AC66" s="1"/>
     </row>
-    <row r="67" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:29" ht="13.2">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -3221,7 +3293,7 @@
       <c r="AB67" s="1"/>
       <c r="AC67" s="1"/>
     </row>
-    <row r="68" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:29" ht="13.2">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -3252,7 +3324,7 @@
       <c r="AB68" s="1"/>
       <c r="AC68" s="1"/>
     </row>
-    <row r="69" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:29" ht="13.2">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -3283,7 +3355,7 @@
       <c r="AB69" s="1"/>
       <c r="AC69" s="1"/>
     </row>
-    <row r="70" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:29" ht="13.2">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -3314,7 +3386,7 @@
       <c r="AB70" s="1"/>
       <c r="AC70" s="1"/>
     </row>
-    <row r="71" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:29" ht="13.2">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -3345,7 +3417,7 @@
       <c r="AB71" s="1"/>
       <c r="AC71" s="1"/>
     </row>
-    <row r="72" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:29" ht="13.2">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -3376,7 +3448,7 @@
       <c r="AB72" s="1"/>
       <c r="AC72" s="1"/>
     </row>
-    <row r="73" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:29" ht="13.2">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -3407,7 +3479,7 @@
       <c r="AB73" s="1"/>
       <c r="AC73" s="1"/>
     </row>
-    <row r="74" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:29" ht="13.2">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -3438,7 +3510,7 @@
       <c r="AB74" s="1"/>
       <c r="AC74" s="1"/>
     </row>
-    <row r="75" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:29" ht="13.2">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -3469,7 +3541,7 @@
       <c r="AB75" s="1"/>
       <c r="AC75" s="1"/>
     </row>
-    <row r="76" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:29" ht="13.2">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -3500,7 +3572,7 @@
       <c r="AB76" s="1"/>
       <c r="AC76" s="1"/>
     </row>
-    <row r="77" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:29" ht="13.2">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -3531,7 +3603,7 @@
       <c r="AB77" s="1"/>
       <c r="AC77" s="1"/>
     </row>
-    <row r="78" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:29" ht="13.2">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -3562,7 +3634,7 @@
       <c r="AB78" s="1"/>
       <c r="AC78" s="1"/>
     </row>
-    <row r="79" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:29" ht="13.2">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -3593,7 +3665,7 @@
       <c r="AB79" s="1"/>
       <c r="AC79" s="1"/>
     </row>
-    <row r="80" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:29" ht="13.2">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -3624,7 +3696,7 @@
       <c r="AB80" s="1"/>
       <c r="AC80" s="1"/>
     </row>
-    <row r="81" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:29" ht="13.2">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -3655,7 +3727,7 @@
       <c r="AB81" s="1"/>
       <c r="AC81" s="1"/>
     </row>
-    <row r="82" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:29" ht="13.2">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -3686,7 +3758,7 @@
       <c r="AB82" s="1"/>
       <c r="AC82" s="1"/>
     </row>
-    <row r="83" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:29" ht="13.2">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -3717,7 +3789,7 @@
       <c r="AB83" s="1"/>
       <c r="AC83" s="1"/>
     </row>
-    <row r="84" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:29" ht="13.2">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -3748,7 +3820,7 @@
       <c r="AB84" s="1"/>
       <c r="AC84" s="1"/>
     </row>
-    <row r="85" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:29" ht="13.2">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -3779,7 +3851,7 @@
       <c r="AB85" s="1"/>
       <c r="AC85" s="1"/>
     </row>
-    <row r="86" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:29" ht="13.2">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -3810,7 +3882,7 @@
       <c r="AB86" s="1"/>
       <c r="AC86" s="1"/>
     </row>
-    <row r="87" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:29" ht="13.2">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -3841,7 +3913,7 @@
       <c r="AB87" s="1"/>
       <c r="AC87" s="1"/>
     </row>
-    <row r="88" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:29" ht="13.2">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -3872,7 +3944,7 @@
       <c r="AB88" s="1"/>
       <c r="AC88" s="1"/>
     </row>
-    <row r="89" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:29" ht="13.2">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -3903,7 +3975,7 @@
       <c r="AB89" s="1"/>
       <c r="AC89" s="1"/>
     </row>
-    <row r="90" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:29" ht="13.2">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -3934,7 +4006,7 @@
       <c r="AB90" s="1"/>
       <c r="AC90" s="1"/>
     </row>
-    <row r="91" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:29" ht="13.2">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -3965,7 +4037,7 @@
       <c r="AB91" s="1"/>
       <c r="AC91" s="1"/>
     </row>
-    <row r="92" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:29" ht="13.2">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -3996,7 +4068,7 @@
       <c r="AB92" s="1"/>
       <c r="AC92" s="1"/>
     </row>
-    <row r="93" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:29" ht="13.2">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -4027,7 +4099,7 @@
       <c r="AB93" s="1"/>
       <c r="AC93" s="1"/>
     </row>
-    <row r="94" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:29" ht="13.2">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -4058,7 +4130,7 @@
       <c r="AB94" s="1"/>
       <c r="AC94" s="1"/>
     </row>
-    <row r="95" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:29" ht="13.2">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -4089,7 +4161,7 @@
       <c r="AB95" s="1"/>
       <c r="AC95" s="1"/>
     </row>
-    <row r="96" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:29" ht="13.2">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -4120,7 +4192,7 @@
       <c r="AB96" s="1"/>
       <c r="AC96" s="1"/>
     </row>
-    <row r="97" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:29" ht="13.2">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -4151,7 +4223,7 @@
       <c r="AB97" s="1"/>
       <c r="AC97" s="1"/>
     </row>
-    <row r="98" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:29" ht="13.2">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -4182,7 +4254,7 @@
       <c r="AB98" s="1"/>
       <c r="AC98" s="1"/>
     </row>
-    <row r="99" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:29" ht="13.2">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -4213,7 +4285,7 @@
       <c r="AB99" s="1"/>
       <c r="AC99" s="1"/>
     </row>
-    <row r="100" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:29" ht="13.2">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -4244,7 +4316,7 @@
       <c r="AB100" s="1"/>
       <c r="AC100" s="1"/>
     </row>
-    <row r="101" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:29" ht="13.2">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -4275,7 +4347,7 @@
       <c r="AB101" s="1"/>
       <c r="AC101" s="1"/>
     </row>
-    <row r="102" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:29" ht="13.2">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -4306,7 +4378,7 @@
       <c r="AB102" s="1"/>
       <c r="AC102" s="1"/>
     </row>
-    <row r="103" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:29" ht="13.2">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -4337,7 +4409,7 @@
       <c r="AB103" s="1"/>
       <c r="AC103" s="1"/>
     </row>
-    <row r="104" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:29" ht="13.2">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -4368,7 +4440,7 @@
       <c r="AB104" s="1"/>
       <c r="AC104" s="1"/>
     </row>
-    <row r="105" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:29" ht="13.2">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -4399,7 +4471,7 @@
       <c r="AB105" s="1"/>
       <c r="AC105" s="1"/>
     </row>
-    <row r="106" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:29" ht="13.2">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -4430,7 +4502,7 @@
       <c r="AB106" s="1"/>
       <c r="AC106" s="1"/>
     </row>
-    <row r="107" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:29" ht="13.2">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -4461,7 +4533,7 @@
       <c r="AB107" s="1"/>
       <c r="AC107" s="1"/>
     </row>
-    <row r="108" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:29" ht="13.2">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -4492,7 +4564,7 @@
       <c r="AB108" s="1"/>
       <c r="AC108" s="1"/>
     </row>
-    <row r="109" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:29" ht="13.2">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -4523,7 +4595,7 @@
       <c r="AB109" s="1"/>
       <c r="AC109" s="1"/>
     </row>
-    <row r="110" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:29" ht="13.2">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -4554,7 +4626,7 @@
       <c r="AB110" s="1"/>
       <c r="AC110" s="1"/>
     </row>
-    <row r="111" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:29" ht="13.2">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -4585,7 +4657,7 @@
       <c r="AB111" s="1"/>
       <c r="AC111" s="1"/>
     </row>
-    <row r="112" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:29" ht="13.2">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -4616,7 +4688,7 @@
       <c r="AB112" s="1"/>
       <c r="AC112" s="1"/>
     </row>
-    <row r="113" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:29" ht="13.2">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -4647,7 +4719,7 @@
       <c r="AB113" s="1"/>
       <c r="AC113" s="1"/>
     </row>
-    <row r="114" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:29" ht="13.2">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -4678,7 +4750,7 @@
       <c r="AB114" s="1"/>
       <c r="AC114" s="1"/>
     </row>
-    <row r="115" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:29" ht="13.2">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -4709,7 +4781,7 @@
       <c r="AB115" s="1"/>
       <c r="AC115" s="1"/>
     </row>
-    <row r="116" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:29" ht="13.2">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -4740,7 +4812,7 @@
       <c r="AB116" s="1"/>
       <c r="AC116" s="1"/>
     </row>
-    <row r="117" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:29" ht="13.2">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -4771,7 +4843,7 @@
       <c r="AB117" s="1"/>
       <c r="AC117" s="1"/>
     </row>
-    <row r="118" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:29" ht="13.2">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -4802,7 +4874,7 @@
       <c r="AB118" s="1"/>
       <c r="AC118" s="1"/>
     </row>
-    <row r="119" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:29" ht="13.2">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -4833,7 +4905,7 @@
       <c r="AB119" s="1"/>
       <c r="AC119" s="1"/>
     </row>
-    <row r="120" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:29" ht="13.2">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -4864,7 +4936,7 @@
       <c r="AB120" s="1"/>
       <c r="AC120" s="1"/>
     </row>
-    <row r="121" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:29" ht="13.2">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -4895,7 +4967,7 @@
       <c r="AB121" s="1"/>
       <c r="AC121" s="1"/>
     </row>
-    <row r="122" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:29" ht="13.2">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -4926,7 +4998,7 @@
       <c r="AB122" s="1"/>
       <c r="AC122" s="1"/>
     </row>
-    <row r="123" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:29" ht="13.2">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -4957,7 +5029,7 @@
       <c r="AB123" s="1"/>
       <c r="AC123" s="1"/>
     </row>
-    <row r="124" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:29" ht="13.2">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -4988,7 +5060,7 @@
       <c r="AB124" s="1"/>
       <c r="AC124" s="1"/>
     </row>
-    <row r="125" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:29" ht="13.2">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -5019,7 +5091,7 @@
       <c r="AB125" s="1"/>
       <c r="AC125" s="1"/>
     </row>
-    <row r="126" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:29" ht="13.2">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -5050,7 +5122,7 @@
       <c r="AB126" s="1"/>
       <c r="AC126" s="1"/>
     </row>
-    <row r="127" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:29" ht="13.2">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -5081,7 +5153,7 @@
       <c r="AB127" s="1"/>
       <c r="AC127" s="1"/>
     </row>
-    <row r="128" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:29" ht="13.2">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -5112,7 +5184,7 @@
       <c r="AB128" s="1"/>
       <c r="AC128" s="1"/>
     </row>
-    <row r="129" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:29" ht="13.2">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -5143,7 +5215,7 @@
       <c r="AB129" s="1"/>
       <c r="AC129" s="1"/>
     </row>
-    <row r="130" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:29" ht="13.2">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -5174,7 +5246,7 @@
       <c r="AB130" s="1"/>
       <c r="AC130" s="1"/>
     </row>
-    <row r="131" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:29" ht="13.2">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -5205,7 +5277,7 @@
       <c r="AB131" s="1"/>
       <c r="AC131" s="1"/>
     </row>
-    <row r="132" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:29" ht="13.2">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -5236,7 +5308,7 @@
       <c r="AB132" s="1"/>
       <c r="AC132" s="1"/>
     </row>
-    <row r="133" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:29" ht="13.2">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -5267,7 +5339,7 @@
       <c r="AB133" s="1"/>
       <c r="AC133" s="1"/>
     </row>
-    <row r="134" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:29" ht="13.2">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -5298,7 +5370,7 @@
       <c r="AB134" s="1"/>
       <c r="AC134" s="1"/>
     </row>
-    <row r="135" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:29" ht="13.2">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -5329,7 +5401,7 @@
       <c r="AB135" s="1"/>
       <c r="AC135" s="1"/>
     </row>
-    <row r="136" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:29" ht="13.2">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -5360,7 +5432,7 @@
       <c r="AB136" s="1"/>
       <c r="AC136" s="1"/>
     </row>
-    <row r="137" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:29" ht="13.2">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -5391,7 +5463,7 @@
       <c r="AB137" s="1"/>
       <c r="AC137" s="1"/>
     </row>
-    <row r="138" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:29" ht="13.2">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -5422,7 +5494,7 @@
       <c r="AB138" s="1"/>
       <c r="AC138" s="1"/>
     </row>
-    <row r="139" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:29" ht="13.2">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -5453,7 +5525,7 @@
       <c r="AB139" s="1"/>
       <c r="AC139" s="1"/>
     </row>
-    <row r="140" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:29" ht="13.2">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -5484,7 +5556,7 @@
       <c r="AB140" s="1"/>
       <c r="AC140" s="1"/>
     </row>
-    <row r="141" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:29" ht="13.2">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -5515,7 +5587,7 @@
       <c r="AB141" s="1"/>
       <c r="AC141" s="1"/>
     </row>
-    <row r="142" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:29" ht="13.2">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -5546,7 +5618,7 @@
       <c r="AB142" s="1"/>
       <c r="AC142" s="1"/>
     </row>
-    <row r="143" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:29" ht="13.2">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -5577,7 +5649,7 @@
       <c r="AB143" s="1"/>
       <c r="AC143" s="1"/>
     </row>
-    <row r="144" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:29" ht="13.2">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -5608,7 +5680,7 @@
       <c r="AB144" s="1"/>
       <c r="AC144" s="1"/>
     </row>
-    <row r="145" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:29" ht="13.2">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -5639,7 +5711,7 @@
       <c r="AB145" s="1"/>
       <c r="AC145" s="1"/>
     </row>
-    <row r="146" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:29" ht="13.2">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -5670,7 +5742,7 @@
       <c r="AB146" s="1"/>
       <c r="AC146" s="1"/>
     </row>
-    <row r="147" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:29" ht="13.2">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -5701,7 +5773,7 @@
       <c r="AB147" s="1"/>
       <c r="AC147" s="1"/>
     </row>
-    <row r="148" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:29" ht="13.2">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -5732,7 +5804,7 @@
       <c r="AB148" s="1"/>
       <c r="AC148" s="1"/>
     </row>
-    <row r="149" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:29" ht="13.2">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -5763,7 +5835,7 @@
       <c r="AB149" s="1"/>
       <c r="AC149" s="1"/>
     </row>
-    <row r="150" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:29" ht="13.2">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -5794,7 +5866,7 @@
       <c r="AB150" s="1"/>
       <c r="AC150" s="1"/>
     </row>
-    <row r="151" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:29" ht="13.2">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -5825,7 +5897,7 @@
       <c r="AB151" s="1"/>
       <c r="AC151" s="1"/>
     </row>
-    <row r="152" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:29" ht="13.2">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -5856,7 +5928,7 @@
       <c r="AB152" s="1"/>
       <c r="AC152" s="1"/>
     </row>
-    <row r="153" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:29" ht="13.2">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -5887,7 +5959,7 @@
       <c r="AB153" s="1"/>
       <c r="AC153" s="1"/>
     </row>
-    <row r="154" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:29" ht="13.2">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -5918,7 +5990,7 @@
       <c r="AB154" s="1"/>
       <c r="AC154" s="1"/>
     </row>
-    <row r="155" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:29" ht="13.2">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -5949,7 +6021,7 @@
       <c r="AB155" s="1"/>
       <c r="AC155" s="1"/>
     </row>
-    <row r="156" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:29" ht="13.2">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -5980,7 +6052,7 @@
       <c r="AB156" s="1"/>
       <c r="AC156" s="1"/>
     </row>
-    <row r="157" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:29" ht="13.2">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -6011,7 +6083,7 @@
       <c r="AB157" s="1"/>
       <c r="AC157" s="1"/>
     </row>
-    <row r="158" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:29" ht="13.2">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -6042,7 +6114,7 @@
       <c r="AB158" s="1"/>
       <c r="AC158" s="1"/>
     </row>
-    <row r="159" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:29" ht="13.2">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -6073,7 +6145,7 @@
       <c r="AB159" s="1"/>
       <c r="AC159" s="1"/>
     </row>
-    <row r="160" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:29" ht="13.2">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -6104,7 +6176,7 @@
       <c r="AB160" s="1"/>
       <c r="AC160" s="1"/>
     </row>
-    <row r="161" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:29" ht="13.2">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -6135,7 +6207,7 @@
       <c r="AB161" s="1"/>
       <c r="AC161" s="1"/>
     </row>
-    <row r="162" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:29" ht="13.2">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -6166,7 +6238,7 @@
       <c r="AB162" s="1"/>
       <c r="AC162" s="1"/>
     </row>
-    <row r="163" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:29" ht="13.2">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -6197,7 +6269,7 @@
       <c r="AB163" s="1"/>
       <c r="AC163" s="1"/>
     </row>
-    <row r="164" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:29" ht="13.2">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -6228,7 +6300,7 @@
       <c r="AB164" s="1"/>
       <c r="AC164" s="1"/>
     </row>
-    <row r="165" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:29" ht="13.2">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -6259,7 +6331,7 @@
       <c r="AB165" s="1"/>
       <c r="AC165" s="1"/>
     </row>
-    <row r="166" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:29" ht="13.2">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -6290,7 +6362,7 @@
       <c r="AB166" s="1"/>
       <c r="AC166" s="1"/>
     </row>
-    <row r="167" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:29" ht="13.2">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -6321,7 +6393,7 @@
       <c r="AB167" s="1"/>
       <c r="AC167" s="1"/>
     </row>
-    <row r="168" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:29" ht="13.2">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -6352,7 +6424,7 @@
       <c r="AB168" s="1"/>
       <c r="AC168" s="1"/>
     </row>
-    <row r="169" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:29" ht="13.2">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -6383,7 +6455,7 @@
       <c r="AB169" s="1"/>
       <c r="AC169" s="1"/>
     </row>
-    <row r="170" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:29" ht="13.2">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -6414,7 +6486,7 @@
       <c r="AB170" s="1"/>
       <c r="AC170" s="1"/>
     </row>
-    <row r="171" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:29" ht="13.2">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -6445,7 +6517,7 @@
       <c r="AB171" s="1"/>
       <c r="AC171" s="1"/>
     </row>
-    <row r="172" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:29" ht="13.2">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -6476,7 +6548,7 @@
       <c r="AB172" s="1"/>
       <c r="AC172" s="1"/>
     </row>
-    <row r="173" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:29" ht="13.2">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -6507,7 +6579,7 @@
       <c r="AB173" s="1"/>
       <c r="AC173" s="1"/>
     </row>
-    <row r="174" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:29" ht="13.2">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -6538,7 +6610,7 @@
       <c r="AB174" s="1"/>
       <c r="AC174" s="1"/>
     </row>
-    <row r="175" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:29" ht="13.2">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -6569,7 +6641,7 @@
       <c r="AB175" s="1"/>
       <c r="AC175" s="1"/>
     </row>
-    <row r="176" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:29" ht="13.2">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -6600,7 +6672,7 @@
       <c r="AB176" s="1"/>
       <c r="AC176" s="1"/>
     </row>
-    <row r="177" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:29" ht="13.2">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -6631,7 +6703,7 @@
       <c r="AB177" s="1"/>
       <c r="AC177" s="1"/>
     </row>
-    <row r="178" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:29" ht="13.2">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -6662,7 +6734,7 @@
       <c r="AB178" s="1"/>
       <c r="AC178" s="1"/>
     </row>
-    <row r="179" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:29" ht="13.2">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -6693,7 +6765,7 @@
       <c r="AB179" s="1"/>
       <c r="AC179" s="1"/>
     </row>
-    <row r="180" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:29" ht="13.2">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -6724,7 +6796,7 @@
       <c r="AB180" s="1"/>
       <c r="AC180" s="1"/>
     </row>
-    <row r="181" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:29" ht="13.2">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -6755,7 +6827,7 @@
       <c r="AB181" s="1"/>
       <c r="AC181" s="1"/>
     </row>
-    <row r="182" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:29" ht="13.2">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -6786,7 +6858,7 @@
       <c r="AB182" s="1"/>
       <c r="AC182" s="1"/>
     </row>
-    <row r="183" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:29" ht="13.2">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -6817,7 +6889,7 @@
       <c r="AB183" s="1"/>
       <c r="AC183" s="1"/>
     </row>
-    <row r="184" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:29" ht="13.2">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -6848,7 +6920,7 @@
       <c r="AB184" s="1"/>
       <c r="AC184" s="1"/>
     </row>
-    <row r="185" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:29" ht="13.2">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -6879,7 +6951,7 @@
       <c r="AB185" s="1"/>
       <c r="AC185" s="1"/>
     </row>
-    <row r="186" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:29" ht="13.2">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -6910,7 +6982,7 @@
       <c r="AB186" s="1"/>
       <c r="AC186" s="1"/>
     </row>
-    <row r="187" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:29" ht="13.2">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -6941,7 +7013,7 @@
       <c r="AB187" s="1"/>
       <c r="AC187" s="1"/>
     </row>
-    <row r="188" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:29" ht="13.2">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -6972,7 +7044,7 @@
       <c r="AB188" s="1"/>
       <c r="AC188" s="1"/>
     </row>
-    <row r="189" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:29" ht="13.2">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -7003,7 +7075,7 @@
       <c r="AB189" s="1"/>
       <c r="AC189" s="1"/>
     </row>
-    <row r="190" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:29" ht="13.2">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -7034,7 +7106,7 @@
       <c r="AB190" s="1"/>
       <c r="AC190" s="1"/>
     </row>
-    <row r="191" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:29" ht="13.2">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -7065,7 +7137,7 @@
       <c r="AB191" s="1"/>
       <c r="AC191" s="1"/>
     </row>
-    <row r="192" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:29" ht="13.2">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -7096,7 +7168,7 @@
       <c r="AB192" s="1"/>
       <c r="AC192" s="1"/>
     </row>
-    <row r="193" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:29" ht="13.2">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -7127,7 +7199,7 @@
       <c r="AB193" s="1"/>
       <c r="AC193" s="1"/>
     </row>
-    <row r="194" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:29" ht="13.2">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -7158,7 +7230,7 @@
       <c r="AB194" s="1"/>
       <c r="AC194" s="1"/>
     </row>
-    <row r="195" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:29" ht="13.2">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -7189,7 +7261,7 @@
       <c r="AB195" s="1"/>
       <c r="AC195" s="1"/>
     </row>
-    <row r="196" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:29" ht="13.2">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
@@ -7220,7 +7292,7 @@
       <c r="AB196" s="1"/>
       <c r="AC196" s="1"/>
     </row>
-    <row r="197" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:29" ht="13.2">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
@@ -7251,7 +7323,7 @@
       <c r="AB197" s="1"/>
       <c r="AC197" s="1"/>
     </row>
-    <row r="198" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:29" ht="13.2">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
@@ -7282,7 +7354,7 @@
       <c r="AB198" s="1"/>
       <c r="AC198" s="1"/>
     </row>
-    <row r="199" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:29" ht="13.2">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
@@ -7313,7 +7385,7 @@
       <c r="AB199" s="1"/>
       <c r="AC199" s="1"/>
     </row>
-    <row r="200" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:29" ht="13.2">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
@@ -7344,7 +7416,7 @@
       <c r="AB200" s="1"/>
       <c r="AC200" s="1"/>
     </row>
-    <row r="201" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:29" ht="13.2">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
@@ -7375,7 +7447,7 @@
       <c r="AB201" s="1"/>
       <c r="AC201" s="1"/>
     </row>
-    <row r="202" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:29" ht="13.2">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
@@ -7406,7 +7478,7 @@
       <c r="AB202" s="1"/>
       <c r="AC202" s="1"/>
     </row>
-    <row r="203" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:29" ht="13.2">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
@@ -7437,7 +7509,7 @@
       <c r="AB203" s="1"/>
       <c r="AC203" s="1"/>
     </row>
-    <row r="204" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:29" ht="13.2">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
@@ -7468,7 +7540,7 @@
       <c r="AB204" s="1"/>
       <c r="AC204" s="1"/>
     </row>
-    <row r="205" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:29" ht="13.2">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
@@ -7499,7 +7571,7 @@
       <c r="AB205" s="1"/>
       <c r="AC205" s="1"/>
     </row>
-    <row r="206" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:29" ht="13.2">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
@@ -7530,7 +7602,7 @@
       <c r="AB206" s="1"/>
       <c r="AC206" s="1"/>
     </row>
-    <row r="207" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:29" ht="13.2">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
@@ -7561,7 +7633,7 @@
       <c r="AB207" s="1"/>
       <c r="AC207" s="1"/>
     </row>
-    <row r="208" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:29" ht="13.2">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
@@ -7592,7 +7664,7 @@
       <c r="AB208" s="1"/>
       <c r="AC208" s="1"/>
     </row>
-    <row r="209" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:29" ht="13.2">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
@@ -7623,7 +7695,7 @@
       <c r="AB209" s="1"/>
       <c r="AC209" s="1"/>
     </row>
-    <row r="210" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:29" ht="13.2">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
@@ -7654,7 +7726,7 @@
       <c r="AB210" s="1"/>
       <c r="AC210" s="1"/>
     </row>
-    <row r="211" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:29" ht="13.2">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
@@ -7685,7 +7757,7 @@
       <c r="AB211" s="1"/>
       <c r="AC211" s="1"/>
     </row>
-    <row r="212" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:29" ht="13.2">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
@@ -7716,7 +7788,7 @@
       <c r="AB212" s="1"/>
       <c r="AC212" s="1"/>
     </row>
-    <row r="213" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:29" ht="13.2">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
@@ -7747,7 +7819,7 @@
       <c r="AB213" s="1"/>
       <c r="AC213" s="1"/>
     </row>
-    <row r="214" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:29" ht="13.2">
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
@@ -7778,7 +7850,7 @@
       <c r="AB214" s="1"/>
       <c r="AC214" s="1"/>
     </row>
-    <row r="215" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:29" ht="13.2">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
@@ -7809,7 +7881,7 @@
       <c r="AB215" s="1"/>
       <c r="AC215" s="1"/>
     </row>
-    <row r="216" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:29" ht="13.2">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
@@ -7840,7 +7912,7 @@
       <c r="AB216" s="1"/>
       <c r="AC216" s="1"/>
     </row>
-    <row r="217" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:29" ht="13.2">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
@@ -7871,7 +7943,7 @@
       <c r="AB217" s="1"/>
       <c r="AC217" s="1"/>
     </row>
-    <row r="218" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:29" ht="13.2">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
@@ -7902,7 +7974,7 @@
       <c r="AB218" s="1"/>
       <c r="AC218" s="1"/>
     </row>
-    <row r="219" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:29" ht="13.2">
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
@@ -7933,7 +8005,7 @@
       <c r="AB219" s="1"/>
       <c r="AC219" s="1"/>
     </row>
-    <row r="220" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:29" ht="13.2">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
@@ -7964,7 +8036,7 @@
       <c r="AB220" s="1"/>
       <c r="AC220" s="1"/>
     </row>
-    <row r="221" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:29" ht="13.2">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="C221" s="1"/>
@@ -7995,7 +8067,7 @@
       <c r="AB221" s="1"/>
       <c r="AC221" s="1"/>
     </row>
-    <row r="222" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:29" ht="13.2">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
       <c r="C222" s="1"/>
@@ -8026,7 +8098,7 @@
       <c r="AB222" s="1"/>
       <c r="AC222" s="1"/>
     </row>
-    <row r="223" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:29" ht="13.2">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="C223" s="1"/>
@@ -8057,7 +8129,7 @@
       <c r="AB223" s="1"/>
       <c r="AC223" s="1"/>
     </row>
-    <row r="224" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:29" ht="13.2">
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
       <c r="C224" s="1"/>
@@ -8088,7 +8160,7 @@
       <c r="AB224" s="1"/>
       <c r="AC224" s="1"/>
     </row>
-    <row r="225" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:29" ht="13.2">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
@@ -8119,7 +8191,7 @@
       <c r="AB225" s="1"/>
       <c r="AC225" s="1"/>
     </row>
-    <row r="226" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:29" ht="13.2">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
@@ -8150,7 +8222,7 @@
       <c r="AB226" s="1"/>
       <c r="AC226" s="1"/>
     </row>
-    <row r="227" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:29" ht="13.2">
       <c r="A227" s="1"/>
       <c r="B227" s="1"/>
       <c r="C227" s="1"/>
@@ -8181,7 +8253,7 @@
       <c r="AB227" s="1"/>
       <c r="AC227" s="1"/>
     </row>
-    <row r="228" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:29" ht="13.2">
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
@@ -8212,7 +8284,7 @@
       <c r="AB228" s="1"/>
       <c r="AC228" s="1"/>
     </row>
-    <row r="229" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:29" ht="13.2">
       <c r="A229" s="1"/>
       <c r="B229" s="1"/>
       <c r="C229" s="1"/>
@@ -8243,7 +8315,7 @@
       <c r="AB229" s="1"/>
       <c r="AC229" s="1"/>
     </row>
-    <row r="230" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:29" ht="13.2">
       <c r="A230" s="1"/>
       <c r="B230" s="1"/>
       <c r="C230" s="1"/>
@@ -8274,7 +8346,7 @@
       <c r="AB230" s="1"/>
       <c r="AC230" s="1"/>
     </row>
-    <row r="231" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:29" ht="13.2">
       <c r="A231" s="1"/>
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
@@ -8305,7 +8377,7 @@
       <c r="AB231" s="1"/>
       <c r="AC231" s="1"/>
     </row>
-    <row r="232" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:29" ht="13.2">
       <c r="A232" s="1"/>
       <c r="B232" s="1"/>
       <c r="C232" s="1"/>
@@ -8336,7 +8408,7 @@
       <c r="AB232" s="1"/>
       <c r="AC232" s="1"/>
     </row>
-    <row r="233" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:29" ht="13.2">
       <c r="A233" s="1"/>
       <c r="B233" s="1"/>
       <c r="C233" s="1"/>
@@ -8367,7 +8439,7 @@
       <c r="AB233" s="1"/>
       <c r="AC233" s="1"/>
     </row>
-    <row r="234" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:29" ht="13.2">
       <c r="A234" s="1"/>
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
@@ -8398,7 +8470,7 @@
       <c r="AB234" s="1"/>
       <c r="AC234" s="1"/>
     </row>
-    <row r="235" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:29" ht="13.2">
       <c r="A235" s="1"/>
       <c r="B235" s="1"/>
       <c r="C235" s="1"/>
@@ -8429,7 +8501,7 @@
       <c r="AB235" s="1"/>
       <c r="AC235" s="1"/>
     </row>
-    <row r="236" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:29" ht="13.2">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
@@ -8460,7 +8532,7 @@
       <c r="AB236" s="1"/>
       <c r="AC236" s="1"/>
     </row>
-    <row r="237" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:29" ht="13.2">
       <c r="A237" s="1"/>
       <c r="B237" s="1"/>
       <c r="C237" s="1"/>
@@ -8491,7 +8563,7 @@
       <c r="AB237" s="1"/>
       <c r="AC237" s="1"/>
     </row>
-    <row r="238" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:29" ht="13.2">
       <c r="A238" s="1"/>
       <c r="B238" s="1"/>
       <c r="C238" s="1"/>
@@ -8522,7 +8594,7 @@
       <c r="AB238" s="1"/>
       <c r="AC238" s="1"/>
     </row>
-    <row r="239" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:29" ht="13.2">
       <c r="A239" s="1"/>
       <c r="B239" s="1"/>
       <c r="C239" s="1"/>
@@ -8553,7 +8625,7 @@
       <c r="AB239" s="1"/>
       <c r="AC239" s="1"/>
     </row>
-    <row r="240" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:29" ht="13.2">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
@@ -8584,7 +8656,7 @@
       <c r="AB240" s="1"/>
       <c r="AC240" s="1"/>
     </row>
-    <row r="241" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:29" ht="13.2">
       <c r="A241" s="1"/>
       <c r="B241" s="1"/>
       <c r="C241" s="1"/>
@@ -8615,7 +8687,7 @@
       <c r="AB241" s="1"/>
       <c r="AC241" s="1"/>
     </row>
-    <row r="242" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:29" ht="13.2">
       <c r="A242" s="1"/>
       <c r="B242" s="1"/>
       <c r="C242" s="1"/>
@@ -8646,7 +8718,7 @@
       <c r="AB242" s="1"/>
       <c r="AC242" s="1"/>
     </row>
-    <row r="243" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:29" ht="13.2">
       <c r="A243" s="1"/>
       <c r="B243" s="1"/>
       <c r="C243" s="1"/>
@@ -8677,7 +8749,7 @@
       <c r="AB243" s="1"/>
       <c r="AC243" s="1"/>
     </row>
-    <row r="244" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:29" ht="13.2">
       <c r="A244" s="1"/>
       <c r="B244" s="1"/>
       <c r="C244" s="1"/>
@@ -8708,7 +8780,7 @@
       <c r="AB244" s="1"/>
       <c r="AC244" s="1"/>
     </row>
-    <row r="245" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:29" ht="13.2">
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="1"/>
@@ -8739,7 +8811,7 @@
       <c r="AB245" s="1"/>
       <c r="AC245" s="1"/>
     </row>
-    <row r="246" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:29" ht="13.2">
       <c r="A246" s="1"/>
       <c r="B246" s="1"/>
       <c r="C246" s="1"/>
@@ -8770,7 +8842,7 @@
       <c r="AB246" s="1"/>
       <c r="AC246" s="1"/>
     </row>
-    <row r="247" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:29" ht="13.2">
       <c r="A247" s="1"/>
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
@@ -8801,7 +8873,7 @@
       <c r="AB247" s="1"/>
       <c r="AC247" s="1"/>
     </row>
-    <row r="248" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:29" ht="13.2">
       <c r="A248" s="1"/>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
@@ -8832,7 +8904,7 @@
       <c r="AB248" s="1"/>
       <c r="AC248" s="1"/>
     </row>
-    <row r="249" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:29" ht="13.2">
       <c r="A249" s="1"/>
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
@@ -8863,7 +8935,7 @@
       <c r="AB249" s="1"/>
       <c r="AC249" s="1"/>
     </row>
-    <row r="250" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:29" ht="13.2">
       <c r="A250" s="1"/>
       <c r="B250" s="1"/>
       <c r="C250" s="1"/>
@@ -8894,7 +8966,7 @@
       <c r="AB250" s="1"/>
       <c r="AC250" s="1"/>
     </row>
-    <row r="251" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:29" ht="13.2">
       <c r="A251" s="1"/>
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
@@ -8925,7 +8997,7 @@
       <c r="AB251" s="1"/>
       <c r="AC251" s="1"/>
     </row>
-    <row r="252" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:29" ht="13.2">
       <c r="A252" s="1"/>
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
@@ -8956,7 +9028,7 @@
       <c r="AB252" s="1"/>
       <c r="AC252" s="1"/>
     </row>
-    <row r="253" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:29" ht="13.2">
       <c r="A253" s="1"/>
       <c r="B253" s="1"/>
       <c r="C253" s="1"/>
@@ -8987,7 +9059,7 @@
       <c r="AB253" s="1"/>
       <c r="AC253" s="1"/>
     </row>
-    <row r="254" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:29" ht="13.2">
       <c r="A254" s="1"/>
       <c r="B254" s="1"/>
       <c r="C254" s="1"/>
@@ -9018,7 +9090,7 @@
       <c r="AB254" s="1"/>
       <c r="AC254" s="1"/>
     </row>
-    <row r="255" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:29" ht="13.2">
       <c r="A255" s="1"/>
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
@@ -9049,7 +9121,7 @@
       <c r="AB255" s="1"/>
       <c r="AC255" s="1"/>
     </row>
-    <row r="256" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:29" ht="13.2">
       <c r="A256" s="1"/>
       <c r="B256" s="1"/>
       <c r="C256" s="1"/>
@@ -9080,7 +9152,7 @@
       <c r="AB256" s="1"/>
       <c r="AC256" s="1"/>
     </row>
-    <row r="257" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:29" ht="13.2">
       <c r="A257" s="1"/>
       <c r="B257" s="1"/>
       <c r="C257" s="1"/>
@@ -9111,7 +9183,7 @@
       <c r="AB257" s="1"/>
       <c r="AC257" s="1"/>
     </row>
-    <row r="258" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:29" ht="13.2">
       <c r="A258" s="1"/>
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
@@ -9142,7 +9214,7 @@
       <c r="AB258" s="1"/>
       <c r="AC258" s="1"/>
     </row>
-    <row r="259" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:29" ht="13.2">
       <c r="A259" s="1"/>
       <c r="B259" s="1"/>
       <c r="C259" s="1"/>
@@ -9173,7 +9245,7 @@
       <c r="AB259" s="1"/>
       <c r="AC259" s="1"/>
     </row>
-    <row r="260" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:29" ht="13.2">
       <c r="A260" s="1"/>
       <c r="B260" s="1"/>
       <c r="C260" s="1"/>
@@ -9204,7 +9276,7 @@
       <c r="AB260" s="1"/>
       <c r="AC260" s="1"/>
     </row>
-    <row r="261" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:29" ht="13.2">
       <c r="A261" s="1"/>
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
@@ -9235,7 +9307,7 @@
       <c r="AB261" s="1"/>
       <c r="AC261" s="1"/>
     </row>
-    <row r="262" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:29" ht="13.2">
       <c r="A262" s="1"/>
       <c r="B262" s="1"/>
       <c r="C262" s="1"/>
@@ -9266,7 +9338,7 @@
       <c r="AB262" s="1"/>
       <c r="AC262" s="1"/>
     </row>
-    <row r="263" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:29" ht="13.2">
       <c r="A263" s="1"/>
       <c r="B263" s="1"/>
       <c r="C263" s="1"/>
@@ -9297,7 +9369,7 @@
       <c r="AB263" s="1"/>
       <c r="AC263" s="1"/>
     </row>
-    <row r="264" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:29" ht="13.2">
       <c r="A264" s="1"/>
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
@@ -9328,7 +9400,7 @@
       <c r="AB264" s="1"/>
       <c r="AC264" s="1"/>
     </row>
-    <row r="265" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:29" ht="13.2">
       <c r="A265" s="1"/>
       <c r="B265" s="1"/>
       <c r="C265" s="1"/>
@@ -9359,7 +9431,7 @@
       <c r="AB265" s="1"/>
       <c r="AC265" s="1"/>
     </row>
-    <row r="266" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:29" ht="13.2">
       <c r="A266" s="1"/>
       <c r="B266" s="1"/>
       <c r="C266" s="1"/>
@@ -9390,7 +9462,7 @@
       <c r="AB266" s="1"/>
       <c r="AC266" s="1"/>
     </row>
-    <row r="267" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:29" ht="13.2">
       <c r="A267" s="1"/>
       <c r="B267" s="1"/>
       <c r="C267" s="1"/>
@@ -9421,7 +9493,7 @@
       <c r="AB267" s="1"/>
       <c r="AC267" s="1"/>
     </row>
-    <row r="268" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:29" ht="13.2">
       <c r="A268" s="1"/>
       <c r="B268" s="1"/>
       <c r="C268" s="1"/>
@@ -9452,7 +9524,7 @@
       <c r="AB268" s="1"/>
       <c r="AC268" s="1"/>
     </row>
-    <row r="269" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:29" ht="13.2">
       <c r="A269" s="1"/>
       <c r="B269" s="1"/>
       <c r="C269" s="1"/>
@@ -9483,7 +9555,7 @@
       <c r="AB269" s="1"/>
       <c r="AC269" s="1"/>
     </row>
-    <row r="270" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:29" ht="13.2">
       <c r="A270" s="1"/>
       <c r="B270" s="1"/>
       <c r="C270" s="1"/>
@@ -9514,7 +9586,7 @@
       <c r="AB270" s="1"/>
       <c r="AC270" s="1"/>
     </row>
-    <row r="271" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:29" ht="13.2">
       <c r="A271" s="1"/>
       <c r="B271" s="1"/>
       <c r="C271" s="1"/>
@@ -9545,7 +9617,7 @@
       <c r="AB271" s="1"/>
       <c r="AC271" s="1"/>
     </row>
-    <row r="272" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:29" ht="13.2">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
@@ -9576,7 +9648,7 @@
       <c r="AB272" s="1"/>
       <c r="AC272" s="1"/>
     </row>
-    <row r="273" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:29" ht="13.2">
       <c r="A273" s="1"/>
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
@@ -9607,7 +9679,7 @@
       <c r="AB273" s="1"/>
       <c r="AC273" s="1"/>
     </row>
-    <row r="274" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:29" ht="13.2">
       <c r="A274" s="1"/>
       <c r="B274" s="1"/>
       <c r="C274" s="1"/>
@@ -9638,7 +9710,7 @@
       <c r="AB274" s="1"/>
       <c r="AC274" s="1"/>
     </row>
-    <row r="275" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:29" ht="13.2">
       <c r="A275" s="1"/>
       <c r="B275" s="1"/>
       <c r="C275" s="1"/>
@@ -9669,7 +9741,7 @@
       <c r="AB275" s="1"/>
       <c r="AC275" s="1"/>
     </row>
-    <row r="276" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:29" ht="13.2">
       <c r="A276" s="1"/>
       <c r="B276" s="1"/>
       <c r="C276" s="1"/>
@@ -9700,7 +9772,7 @@
       <c r="AB276" s="1"/>
       <c r="AC276" s="1"/>
     </row>
-    <row r="277" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:29" ht="13.2">
       <c r="A277" s="1"/>
       <c r="B277" s="1"/>
       <c r="C277" s="1"/>
@@ -9731,7 +9803,7 @@
       <c r="AB277" s="1"/>
       <c r="AC277" s="1"/>
     </row>
-    <row r="278" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:29" ht="13.2">
       <c r="A278" s="1"/>
       <c r="B278" s="1"/>
       <c r="C278" s="1"/>
@@ -9762,7 +9834,7 @@
       <c r="AB278" s="1"/>
       <c r="AC278" s="1"/>
     </row>
-    <row r="279" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:29" ht="13.2">
       <c r="A279" s="1"/>
       <c r="B279" s="1"/>
       <c r="C279" s="1"/>
@@ -9793,7 +9865,7 @@
       <c r="AB279" s="1"/>
       <c r="AC279" s="1"/>
     </row>
-    <row r="280" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:29" ht="13.2">
       <c r="A280" s="1"/>
       <c r="B280" s="1"/>
       <c r="C280" s="1"/>
@@ -9824,7 +9896,7 @@
       <c r="AB280" s="1"/>
       <c r="AC280" s="1"/>
     </row>
-    <row r="281" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:29" ht="13.2">
       <c r="A281" s="1"/>
       <c r="B281" s="1"/>
       <c r="C281" s="1"/>
@@ -9855,7 +9927,7 @@
       <c r="AB281" s="1"/>
       <c r="AC281" s="1"/>
     </row>
-    <row r="282" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:29" ht="13.2">
       <c r="A282" s="1"/>
       <c r="B282" s="1"/>
       <c r="C282" s="1"/>
@@ -9886,7 +9958,7 @@
       <c r="AB282" s="1"/>
       <c r="AC282" s="1"/>
     </row>
-    <row r="283" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:29" ht="13.2">
       <c r="A283" s="1"/>
       <c r="B283" s="1"/>
       <c r="C283" s="1"/>
@@ -9917,7 +9989,7 @@
       <c r="AB283" s="1"/>
       <c r="AC283" s="1"/>
     </row>
-    <row r="284" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:29" ht="13.2">
       <c r="A284" s="1"/>
       <c r="B284" s="1"/>
       <c r="C284" s="1"/>
@@ -9948,7 +10020,7 @@
       <c r="AB284" s="1"/>
       <c r="AC284" s="1"/>
     </row>
-    <row r="285" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:29" ht="13.2">
       <c r="A285" s="1"/>
       <c r="B285" s="1"/>
       <c r="C285" s="1"/>
@@ -9979,7 +10051,7 @@
       <c r="AB285" s="1"/>
       <c r="AC285" s="1"/>
     </row>
-    <row r="286" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:29" ht="13.2">
       <c r="A286" s="1"/>
       <c r="B286" s="1"/>
       <c r="C286" s="1"/>
@@ -10010,7 +10082,7 @@
       <c r="AB286" s="1"/>
       <c r="AC286" s="1"/>
     </row>
-    <row r="287" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:29" ht="13.2">
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
@@ -10041,7 +10113,7 @@
       <c r="AB287" s="1"/>
       <c r="AC287" s="1"/>
     </row>
-    <row r="288" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:29" ht="13.2">
       <c r="A288" s="1"/>
       <c r="B288" s="1"/>
       <c r="C288" s="1"/>
@@ -10072,7 +10144,7 @@
       <c r="AB288" s="1"/>
       <c r="AC288" s="1"/>
     </row>
-    <row r="289" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:29" ht="13.2">
       <c r="A289" s="1"/>
       <c r="B289" s="1"/>
       <c r="C289" s="1"/>
@@ -10103,7 +10175,7 @@
       <c r="AB289" s="1"/>
       <c r="AC289" s="1"/>
     </row>
-    <row r="290" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:29" ht="13.2">
       <c r="A290" s="1"/>
       <c r="B290" s="1"/>
       <c r="C290" s="1"/>
@@ -10134,7 +10206,7 @@
       <c r="AB290" s="1"/>
       <c r="AC290" s="1"/>
     </row>
-    <row r="291" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:29" ht="13.2">
       <c r="A291" s="1"/>
       <c r="B291" s="1"/>
       <c r="C291" s="1"/>
@@ -10165,7 +10237,7 @@
       <c r="AB291" s="1"/>
       <c r="AC291" s="1"/>
     </row>
-    <row r="292" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:29" ht="13.2">
       <c r="A292" s="1"/>
       <c r="B292" s="1"/>
       <c r="C292" s="1"/>
@@ -10196,7 +10268,7 @@
       <c r="AB292" s="1"/>
       <c r="AC292" s="1"/>
     </row>
-    <row r="293" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:29" ht="13.2">
       <c r="A293" s="1"/>
       <c r="B293" s="1"/>
       <c r="C293" s="1"/>
@@ -10227,7 +10299,7 @@
       <c r="AB293" s="1"/>
       <c r="AC293" s="1"/>
     </row>
-    <row r="294" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:29" ht="13.2">
       <c r="A294" s="1"/>
       <c r="B294" s="1"/>
       <c r="C294" s="1"/>
@@ -10258,7 +10330,7 @@
       <c r="AB294" s="1"/>
       <c r="AC294" s="1"/>
     </row>
-    <row r="295" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:29" ht="13.2">
       <c r="A295" s="1"/>
       <c r="B295" s="1"/>
       <c r="C295" s="1"/>
@@ -10289,7 +10361,7 @@
       <c r="AB295" s="1"/>
       <c r="AC295" s="1"/>
     </row>
-    <row r="296" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:29" ht="13.2">
       <c r="A296" s="1"/>
       <c r="B296" s="1"/>
       <c r="C296" s="1"/>
@@ -10320,7 +10392,7 @@
       <c r="AB296" s="1"/>
       <c r="AC296" s="1"/>
     </row>
-    <row r="297" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:29" ht="13.2">
       <c r="A297" s="1"/>
       <c r="B297" s="1"/>
       <c r="C297" s="1"/>
@@ -10351,7 +10423,7 @@
       <c r="AB297" s="1"/>
       <c r="AC297" s="1"/>
     </row>
-    <row r="298" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:29" ht="13.2">
       <c r="A298" s="1"/>
       <c r="B298" s="1"/>
       <c r="C298" s="1"/>
@@ -10382,7 +10454,7 @@
       <c r="AB298" s="1"/>
       <c r="AC298" s="1"/>
     </row>
-    <row r="299" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:29" ht="13.2">
       <c r="A299" s="1"/>
       <c r="B299" s="1"/>
       <c r="C299" s="1"/>
@@ -10413,7 +10485,7 @@
       <c r="AB299" s="1"/>
       <c r="AC299" s="1"/>
     </row>
-    <row r="300" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:29" ht="13.2">
       <c r="A300" s="1"/>
       <c r="B300" s="1"/>
       <c r="C300" s="1"/>
@@ -10444,7 +10516,7 @@
       <c r="AB300" s="1"/>
       <c r="AC300" s="1"/>
     </row>
-    <row r="301" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:29" ht="13.2">
       <c r="A301" s="1"/>
       <c r="B301" s="1"/>
       <c r="C301" s="1"/>
@@ -10475,7 +10547,7 @@
       <c r="AB301" s="1"/>
       <c r="AC301" s="1"/>
     </row>
-    <row r="302" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:29" ht="13.2">
       <c r="A302" s="1"/>
       <c r="B302" s="1"/>
       <c r="C302" s="1"/>
@@ -10506,7 +10578,7 @@
       <c r="AB302" s="1"/>
       <c r="AC302" s="1"/>
     </row>
-    <row r="303" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:29" ht="13.2">
       <c r="A303" s="1"/>
       <c r="B303" s="1"/>
       <c r="C303" s="1"/>
@@ -10537,7 +10609,7 @@
       <c r="AB303" s="1"/>
       <c r="AC303" s="1"/>
     </row>
-    <row r="304" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:29" ht="13.2">
       <c r="A304" s="1"/>
       <c r="B304" s="1"/>
       <c r="C304" s="1"/>
@@ -10568,7 +10640,7 @@
       <c r="AB304" s="1"/>
       <c r="AC304" s="1"/>
     </row>
-    <row r="305" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:29" ht="13.2">
       <c r="A305" s="1"/>
       <c r="B305" s="1"/>
       <c r="C305" s="1"/>
@@ -10599,7 +10671,7 @@
       <c r="AB305" s="1"/>
       <c r="AC305" s="1"/>
     </row>
-    <row r="306" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:29" ht="13.2">
       <c r="A306" s="1"/>
       <c r="B306" s="1"/>
       <c r="C306" s="1"/>
@@ -10630,7 +10702,7 @@
       <c r="AB306" s="1"/>
       <c r="AC306" s="1"/>
     </row>
-    <row r="307" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:29" ht="13.2">
       <c r="A307" s="1"/>
       <c r="B307" s="1"/>
       <c r="C307" s="1"/>
@@ -10661,7 +10733,7 @@
       <c r="AB307" s="1"/>
       <c r="AC307" s="1"/>
     </row>
-    <row r="308" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:29" ht="13.2">
       <c r="A308" s="1"/>
       <c r="B308" s="1"/>
       <c r="C308" s="1"/>
@@ -10692,7 +10764,7 @@
       <c r="AB308" s="1"/>
       <c r="AC308" s="1"/>
     </row>
-    <row r="309" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:29" ht="13.2">
       <c r="A309" s="1"/>
       <c r="B309" s="1"/>
       <c r="C309" s="1"/>
@@ -10723,7 +10795,7 @@
       <c r="AB309" s="1"/>
       <c r="AC309" s="1"/>
     </row>
-    <row r="310" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:29" ht="13.2">
       <c r="A310" s="1"/>
       <c r="B310" s="1"/>
       <c r="C310" s="1"/>
@@ -10754,7 +10826,7 @@
       <c r="AB310" s="1"/>
       <c r="AC310" s="1"/>
     </row>
-    <row r="311" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:29" ht="13.2">
       <c r="A311" s="1"/>
       <c r="B311" s="1"/>
       <c r="C311" s="1"/>
@@ -10785,7 +10857,7 @@
       <c r="AB311" s="1"/>
       <c r="AC311" s="1"/>
     </row>
-    <row r="312" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:29" ht="13.2">
       <c r="A312" s="1"/>
       <c r="B312" s="1"/>
       <c r="C312" s="1"/>
@@ -10816,7 +10888,7 @@
       <c r="AB312" s="1"/>
       <c r="AC312" s="1"/>
     </row>
-    <row r="313" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:29" ht="13.2">
       <c r="A313" s="1"/>
       <c r="B313" s="1"/>
       <c r="C313" s="1"/>
@@ -10847,7 +10919,7 @@
       <c r="AB313" s="1"/>
       <c r="AC313" s="1"/>
     </row>
-    <row r="314" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:29" ht="13.2">
       <c r="A314" s="1"/>
       <c r="B314" s="1"/>
       <c r="C314" s="1"/>
@@ -10878,7 +10950,7 @@
       <c r="AB314" s="1"/>
       <c r="AC314" s="1"/>
     </row>
-    <row r="315" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:29" ht="13.2">
       <c r="A315" s="1"/>
       <c r="B315" s="1"/>
       <c r="C315" s="1"/>
@@ -10909,7 +10981,7 @@
       <c r="AB315" s="1"/>
       <c r="AC315" s="1"/>
     </row>
-    <row r="316" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:29" ht="13.2">
       <c r="A316" s="1"/>
       <c r="B316" s="1"/>
       <c r="C316" s="1"/>
@@ -10940,7 +11012,7 @@
       <c r="AB316" s="1"/>
       <c r="AC316" s="1"/>
     </row>
-    <row r="317" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:29" ht="13.2">
       <c r="A317" s="1"/>
       <c r="B317" s="1"/>
       <c r="C317" s="1"/>
@@ -10971,7 +11043,7 @@
       <c r="AB317" s="1"/>
       <c r="AC317" s="1"/>
     </row>
-    <row r="318" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:29" ht="13.2">
       <c r="A318" s="1"/>
       <c r="B318" s="1"/>
       <c r="C318" s="1"/>
@@ -11002,7 +11074,7 @@
       <c r="AB318" s="1"/>
       <c r="AC318" s="1"/>
     </row>
-    <row r="319" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:29" ht="13.2">
       <c r="A319" s="1"/>
       <c r="B319" s="1"/>
       <c r="C319" s="1"/>
@@ -11033,7 +11105,7 @@
       <c r="AB319" s="1"/>
       <c r="AC319" s="1"/>
     </row>
-    <row r="320" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:29" ht="13.2">
       <c r="A320" s="1"/>
       <c r="B320" s="1"/>
       <c r="C320" s="1"/>
@@ -11064,7 +11136,7 @@
       <c r="AB320" s="1"/>
       <c r="AC320" s="1"/>
     </row>
-    <row r="321" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:29" ht="13.2">
       <c r="A321" s="1"/>
       <c r="B321" s="1"/>
       <c r="C321" s="1"/>
@@ -11095,7 +11167,7 @@
       <c r="AB321" s="1"/>
       <c r="AC321" s="1"/>
     </row>
-    <row r="322" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:29" ht="13.2">
       <c r="A322" s="1"/>
       <c r="B322" s="1"/>
       <c r="C322" s="1"/>
@@ -11126,7 +11198,7 @@
       <c r="AB322" s="1"/>
       <c r="AC322" s="1"/>
     </row>
-    <row r="323" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:29" ht="13.2">
       <c r="A323" s="1"/>
       <c r="B323" s="1"/>
       <c r="C323" s="1"/>
@@ -11157,7 +11229,7 @@
       <c r="AB323" s="1"/>
       <c r="AC323" s="1"/>
     </row>
-    <row r="324" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:29" ht="13.2">
       <c r="A324" s="1"/>
       <c r="B324" s="1"/>
       <c r="C324" s="1"/>
@@ -11188,7 +11260,7 @@
       <c r="AB324" s="1"/>
       <c r="AC324" s="1"/>
     </row>
-    <row r="325" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:29" ht="13.2">
       <c r="A325" s="1"/>
       <c r="B325" s="1"/>
       <c r="C325" s="1"/>
@@ -11219,7 +11291,7 @@
       <c r="AB325" s="1"/>
       <c r="AC325" s="1"/>
     </row>
-    <row r="326" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:29" ht="13.2">
       <c r="A326" s="1"/>
       <c r="B326" s="1"/>
       <c r="C326" s="1"/>
@@ -11250,7 +11322,7 @@
       <c r="AB326" s="1"/>
       <c r="AC326" s="1"/>
     </row>
-    <row r="327" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:29" ht="13.2">
       <c r="A327" s="1"/>
       <c r="B327" s="1"/>
       <c r="C327" s="1"/>
@@ -11281,7 +11353,7 @@
       <c r="AB327" s="1"/>
       <c r="AC327" s="1"/>
     </row>
-    <row r="328" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:29" ht="13.2">
       <c r="A328" s="1"/>
       <c r="B328" s="1"/>
       <c r="C328" s="1"/>
@@ -11312,7 +11384,7 @@
       <c r="AB328" s="1"/>
       <c r="AC328" s="1"/>
     </row>
-    <row r="329" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:29" ht="13.2">
       <c r="A329" s="1"/>
       <c r="B329" s="1"/>
       <c r="C329" s="1"/>
@@ -11343,7 +11415,7 @@
       <c r="AB329" s="1"/>
       <c r="AC329" s="1"/>
     </row>
-    <row r="330" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:29" ht="13.2">
       <c r="A330" s="1"/>
       <c r="B330" s="1"/>
       <c r="C330" s="1"/>
@@ -11374,7 +11446,7 @@
       <c r="AB330" s="1"/>
       <c r="AC330" s="1"/>
     </row>
-    <row r="331" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:29" ht="13.2">
       <c r="A331" s="1"/>
       <c r="B331" s="1"/>
       <c r="C331" s="1"/>
@@ -11405,7 +11477,7 @@
       <c r="AB331" s="1"/>
       <c r="AC331" s="1"/>
     </row>
-    <row r="332" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:29" ht="13.2">
       <c r="A332" s="1"/>
       <c r="B332" s="1"/>
       <c r="C332" s="1"/>
@@ -11436,7 +11508,7 @@
       <c r="AB332" s="1"/>
       <c r="AC332" s="1"/>
     </row>
-    <row r="333" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:29" ht="13.2">
       <c r="A333" s="1"/>
       <c r="B333" s="1"/>
       <c r="C333" s="1"/>
@@ -11467,7 +11539,7 @@
       <c r="AB333" s="1"/>
       <c r="AC333" s="1"/>
     </row>
-    <row r="334" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:29" ht="13.2">
       <c r="A334" s="1"/>
       <c r="B334" s="1"/>
       <c r="C334" s="1"/>
@@ -11498,7 +11570,7 @@
       <c r="AB334" s="1"/>
       <c r="AC334" s="1"/>
     </row>
-    <row r="335" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:29" ht="13.2">
       <c r="A335" s="1"/>
       <c r="B335" s="1"/>
       <c r="C335" s="1"/>
@@ -11529,7 +11601,7 @@
       <c r="AB335" s="1"/>
       <c r="AC335" s="1"/>
     </row>
-    <row r="336" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:29" ht="13.2">
       <c r="A336" s="1"/>
       <c r="B336" s="1"/>
       <c r="C336" s="1"/>
@@ -11560,7 +11632,7 @@
       <c r="AB336" s="1"/>
       <c r="AC336" s="1"/>
     </row>
-    <row r="337" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:29" ht="13.2">
       <c r="A337" s="1"/>
       <c r="B337" s="1"/>
       <c r="C337" s="1"/>
@@ -11591,7 +11663,7 @@
       <c r="AB337" s="1"/>
       <c r="AC337" s="1"/>
     </row>
-    <row r="338" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:29" ht="13.2">
       <c r="A338" s="1"/>
       <c r="B338" s="1"/>
       <c r="C338" s="1"/>
@@ -11622,7 +11694,7 @@
       <c r="AB338" s="1"/>
       <c r="AC338" s="1"/>
     </row>
-    <row r="339" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:29" ht="13.2">
       <c r="A339" s="1"/>
       <c r="B339" s="1"/>
       <c r="C339" s="1"/>
@@ -11653,7 +11725,7 @@
       <c r="AB339" s="1"/>
       <c r="AC339" s="1"/>
     </row>
-    <row r="340" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:29" ht="13.2">
       <c r="A340" s="1"/>
       <c r="B340" s="1"/>
       <c r="C340" s="1"/>
@@ -11684,7 +11756,7 @@
       <c r="AB340" s="1"/>
       <c r="AC340" s="1"/>
     </row>
-    <row r="341" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:29" ht="13.2">
       <c r="A341" s="1"/>
       <c r="B341" s="1"/>
       <c r="C341" s="1"/>
@@ -11715,7 +11787,7 @@
       <c r="AB341" s="1"/>
       <c r="AC341" s="1"/>
     </row>
-    <row r="342" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:29" ht="13.2">
       <c r="A342" s="1"/>
       <c r="B342" s="1"/>
       <c r="C342" s="1"/>
@@ -11746,7 +11818,7 @@
       <c r="AB342" s="1"/>
       <c r="AC342" s="1"/>
     </row>
-    <row r="343" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:29" ht="13.2">
       <c r="A343" s="1"/>
       <c r="B343" s="1"/>
       <c r="C343" s="1"/>
@@ -11777,7 +11849,7 @@
       <c r="AB343" s="1"/>
       <c r="AC343" s="1"/>
     </row>
-    <row r="344" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:29" ht="13.2">
       <c r="A344" s="1"/>
       <c r="B344" s="1"/>
       <c r="C344" s="1"/>
@@ -11808,7 +11880,7 @@
       <c r="AB344" s="1"/>
       <c r="AC344" s="1"/>
     </row>
-    <row r="345" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:29" ht="13.2">
       <c r="A345" s="1"/>
       <c r="B345" s="1"/>
       <c r="C345" s="1"/>
@@ -11839,7 +11911,7 @@
       <c r="AB345" s="1"/>
       <c r="AC345" s="1"/>
     </row>
-    <row r="346" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:29" ht="13.2">
       <c r="A346" s="1"/>
       <c r="B346" s="1"/>
       <c r="C346" s="1"/>
@@ -11870,7 +11942,7 @@
       <c r="AB346" s="1"/>
       <c r="AC346" s="1"/>
     </row>
-    <row r="347" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:29" ht="13.2">
       <c r="A347" s="1"/>
       <c r="B347" s="1"/>
       <c r="C347" s="1"/>
@@ -11901,7 +11973,7 @@
       <c r="AB347" s="1"/>
       <c r="AC347" s="1"/>
     </row>
-    <row r="348" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:29" ht="13.2">
       <c r="A348" s="1"/>
       <c r="B348" s="1"/>
       <c r="C348" s="1"/>
@@ -11932,7 +12004,7 @@
       <c r="AB348" s="1"/>
       <c r="AC348" s="1"/>
     </row>
-    <row r="349" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:29" ht="13.2">
       <c r="A349" s="1"/>
       <c r="B349" s="1"/>
       <c r="C349" s="1"/>
@@ -11963,7 +12035,7 @@
       <c r="AB349" s="1"/>
       <c r="AC349" s="1"/>
     </row>
-    <row r="350" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:29" ht="13.2">
       <c r="A350" s="1"/>
       <c r="B350" s="1"/>
       <c r="C350" s="1"/>
@@ -11994,7 +12066,7 @@
       <c r="AB350" s="1"/>
       <c r="AC350" s="1"/>
     </row>
-    <row r="351" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:29" ht="13.2">
       <c r="A351" s="1"/>
       <c r="B351" s="1"/>
       <c r="C351" s="1"/>
@@ -12025,7 +12097,7 @@
       <c r="AB351" s="1"/>
       <c r="AC351" s="1"/>
     </row>
-    <row r="352" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:29" ht="13.2">
       <c r="A352" s="1"/>
       <c r="B352" s="1"/>
       <c r="C352" s="1"/>
@@ -12056,7 +12128,7 @@
       <c r="AB352" s="1"/>
       <c r="AC352" s="1"/>
     </row>
-    <row r="353" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:29" ht="13.2">
       <c r="A353" s="1"/>
       <c r="B353" s="1"/>
       <c r="C353" s="1"/>
@@ -12087,7 +12159,7 @@
       <c r="AB353" s="1"/>
       <c r="AC353" s="1"/>
     </row>
-    <row r="354" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:29" ht="13.2">
       <c r="A354" s="1"/>
       <c r="B354" s="1"/>
       <c r="C354" s="1"/>
@@ -12118,7 +12190,7 @@
       <c r="AB354" s="1"/>
       <c r="AC354" s="1"/>
     </row>
-    <row r="355" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:29" ht="13.2">
       <c r="A355" s="1"/>
       <c r="B355" s="1"/>
       <c r="C355" s="1"/>
@@ -12149,7 +12221,7 @@
       <c r="AB355" s="1"/>
       <c r="AC355" s="1"/>
     </row>
-    <row r="356" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:29" ht="13.2">
       <c r="A356" s="1"/>
       <c r="B356" s="1"/>
       <c r="C356" s="1"/>
@@ -12180,7 +12252,7 @@
       <c r="AB356" s="1"/>
       <c r="AC356" s="1"/>
     </row>
-    <row r="357" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:29" ht="13.2">
       <c r="A357" s="1"/>
       <c r="B357" s="1"/>
       <c r="C357" s="1"/>
@@ -12211,7 +12283,7 @@
       <c r="AB357" s="1"/>
       <c r="AC357" s="1"/>
     </row>
-    <row r="358" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:29" ht="13.2">
       <c r="A358" s="1"/>
       <c r="B358" s="1"/>
       <c r="C358" s="1"/>
@@ -12242,7 +12314,7 @@
       <c r="AB358" s="1"/>
       <c r="AC358" s="1"/>
     </row>
-    <row r="359" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:29" ht="13.2">
       <c r="A359" s="1"/>
       <c r="B359" s="1"/>
       <c r="C359" s="1"/>
@@ -12273,7 +12345,7 @@
       <c r="AB359" s="1"/>
       <c r="AC359" s="1"/>
     </row>
-    <row r="360" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:29" ht="13.2">
       <c r="A360" s="1"/>
       <c r="B360" s="1"/>
       <c r="C360" s="1"/>
@@ -12304,7 +12376,7 @@
       <c r="AB360" s="1"/>
       <c r="AC360" s="1"/>
     </row>
-    <row r="361" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:29" ht="13.2">
       <c r="A361" s="1"/>
       <c r="B361" s="1"/>
       <c r="C361" s="1"/>
@@ -12335,7 +12407,7 @@
       <c r="AB361" s="1"/>
       <c r="AC361" s="1"/>
     </row>
-    <row r="362" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:29" ht="13.2">
       <c r="A362" s="1"/>
       <c r="B362" s="1"/>
       <c r="C362" s="1"/>
@@ -12366,7 +12438,7 @@
       <c r="AB362" s="1"/>
       <c r="AC362" s="1"/>
     </row>
-    <row r="363" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:29" ht="13.2">
       <c r="A363" s="1"/>
       <c r="B363" s="1"/>
       <c r="C363" s="1"/>
@@ -12397,7 +12469,7 @@
       <c r="AB363" s="1"/>
       <c r="AC363" s="1"/>
     </row>
-    <row r="364" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:29" ht="13.2">
       <c r="A364" s="1"/>
       <c r="B364" s="1"/>
       <c r="C364" s="1"/>
@@ -12428,7 +12500,7 @@
       <c r="AB364" s="1"/>
       <c r="AC364" s="1"/>
     </row>
-    <row r="365" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:29" ht="13.2">
       <c r="A365" s="1"/>
       <c r="B365" s="1"/>
       <c r="C365" s="1"/>
@@ -12459,7 +12531,7 @@
       <c r="AB365" s="1"/>
       <c r="AC365" s="1"/>
     </row>
-    <row r="366" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:29" ht="13.2">
       <c r="A366" s="1"/>
       <c r="B366" s="1"/>
       <c r="C366" s="1"/>
@@ -12490,7 +12562,7 @@
       <c r="AB366" s="1"/>
       <c r="AC366" s="1"/>
     </row>
-    <row r="367" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:29" ht="13.2">
       <c r="A367" s="1"/>
       <c r="B367" s="1"/>
       <c r="C367" s="1"/>
@@ -12521,7 +12593,7 @@
       <c r="AB367" s="1"/>
       <c r="AC367" s="1"/>
     </row>
-    <row r="368" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:29" ht="13.2">
       <c r="A368" s="1"/>
       <c r="B368" s="1"/>
       <c r="C368" s="1"/>
@@ -12552,7 +12624,7 @@
       <c r="AB368" s="1"/>
       <c r="AC368" s="1"/>
     </row>
-    <row r="369" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:29" ht="13.2">
       <c r="A369" s="1"/>
       <c r="B369" s="1"/>
       <c r="C369" s="1"/>
@@ -12583,7 +12655,7 @@
       <c r="AB369" s="1"/>
       <c r="AC369" s="1"/>
     </row>
-    <row r="370" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:29" ht="13.2">
       <c r="A370" s="1"/>
       <c r="B370" s="1"/>
       <c r="C370" s="1"/>
@@ -12614,7 +12686,7 @@
       <c r="AB370" s="1"/>
       <c r="AC370" s="1"/>
     </row>
-    <row r="371" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:29" ht="13.2">
       <c r="A371" s="1"/>
       <c r="B371" s="1"/>
       <c r="C371" s="1"/>
@@ -12645,7 +12717,7 @@
       <c r="AB371" s="1"/>
       <c r="AC371" s="1"/>
     </row>
-    <row r="372" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:29" ht="13.2">
       <c r="A372" s="1"/>
       <c r="B372" s="1"/>
       <c r="C372" s="1"/>
@@ -12676,7 +12748,7 @@
       <c r="AB372" s="1"/>
       <c r="AC372" s="1"/>
     </row>
-    <row r="373" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:29" ht="13.2">
       <c r="A373" s="1"/>
       <c r="B373" s="1"/>
       <c r="C373" s="1"/>
@@ -12707,7 +12779,7 @@
       <c r="AB373" s="1"/>
       <c r="AC373" s="1"/>
     </row>
-    <row r="374" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:29" ht="13.2">
       <c r="A374" s="1"/>
       <c r="B374" s="1"/>
       <c r="C374" s="1"/>
@@ -12738,7 +12810,7 @@
       <c r="AB374" s="1"/>
       <c r="AC374" s="1"/>
     </row>
-    <row r="375" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:29" ht="13.2">
       <c r="A375" s="1"/>
       <c r="B375" s="1"/>
       <c r="C375" s="1"/>
@@ -12769,7 +12841,7 @@
       <c r="AB375" s="1"/>
       <c r="AC375" s="1"/>
     </row>
-    <row r="376" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:29" ht="13.2">
       <c r="A376" s="1"/>
       <c r="B376" s="1"/>
       <c r="C376" s="1"/>
@@ -12800,7 +12872,7 @@
       <c r="AB376" s="1"/>
       <c r="AC376" s="1"/>
     </row>
-    <row r="377" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:29" ht="13.2">
       <c r="A377" s="1"/>
       <c r="B377" s="1"/>
       <c r="C377" s="1"/>
@@ -12831,7 +12903,7 @@
       <c r="AB377" s="1"/>
       <c r="AC377" s="1"/>
     </row>
-    <row r="378" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:29" ht="13.2">
       <c r="A378" s="1"/>
       <c r="B378" s="1"/>
       <c r="C378" s="1"/>
@@ -12862,7 +12934,7 @@
       <c r="AB378" s="1"/>
       <c r="AC378" s="1"/>
     </row>
-    <row r="379" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:29" ht="13.2">
       <c r="A379" s="1"/>
       <c r="B379" s="1"/>
       <c r="C379" s="1"/>
@@ -12893,7 +12965,7 @@
       <c r="AB379" s="1"/>
       <c r="AC379" s="1"/>
     </row>
-    <row r="380" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:29" ht="13.2">
       <c r="A380" s="1"/>
       <c r="B380" s="1"/>
       <c r="C380" s="1"/>
@@ -12924,7 +12996,7 @@
       <c r="AB380" s="1"/>
       <c r="AC380" s="1"/>
     </row>
-    <row r="381" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:29" ht="13.2">
       <c r="A381" s="1"/>
       <c r="B381" s="1"/>
       <c r="C381" s="1"/>
@@ -12955,7 +13027,7 @@
       <c r="AB381" s="1"/>
       <c r="AC381" s="1"/>
     </row>
-    <row r="382" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:29" ht="13.2">
       <c r="A382" s="1"/>
       <c r="B382" s="1"/>
       <c r="C382" s="1"/>
@@ -12986,7 +13058,7 @@
       <c r="AB382" s="1"/>
       <c r="AC382" s="1"/>
     </row>
-    <row r="383" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:29" ht="13.2">
       <c r="A383" s="1"/>
       <c r="B383" s="1"/>
       <c r="C383" s="1"/>
@@ -13017,7 +13089,7 @@
       <c r="AB383" s="1"/>
       <c r="AC383" s="1"/>
     </row>
-    <row r="384" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:29" ht="13.2">
       <c r="A384" s="1"/>
       <c r="B384" s="1"/>
       <c r="C384" s="1"/>
@@ -13048,7 +13120,7 @@
       <c r="AB384" s="1"/>
       <c r="AC384" s="1"/>
     </row>
-    <row r="385" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:29" ht="13.2">
       <c r="A385" s="1"/>
       <c r="B385" s="1"/>
       <c r="C385" s="1"/>
@@ -13079,7 +13151,7 @@
       <c r="AB385" s="1"/>
       <c r="AC385" s="1"/>
     </row>
-    <row r="386" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:29" ht="13.2">
       <c r="A386" s="1"/>
       <c r="B386" s="1"/>
       <c r="C386" s="1"/>
@@ -13110,7 +13182,7 @@
       <c r="AB386" s="1"/>
       <c r="AC386" s="1"/>
     </row>
-    <row r="387" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:29" ht="13.2">
       <c r="A387" s="1"/>
       <c r="B387" s="1"/>
       <c r="C387" s="1"/>
@@ -13141,7 +13213,7 @@
       <c r="AB387" s="1"/>
       <c r="AC387" s="1"/>
     </row>
-    <row r="388" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:29" ht="13.2">
       <c r="A388" s="1"/>
       <c r="B388" s="1"/>
       <c r="C388" s="1"/>
@@ -13172,7 +13244,7 @@
       <c r="AB388" s="1"/>
       <c r="AC388" s="1"/>
     </row>
-    <row r="389" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:29" ht="13.2">
       <c r="A389" s="1"/>
       <c r="B389" s="1"/>
       <c r="C389" s="1"/>
@@ -13203,7 +13275,7 @@
       <c r="AB389" s="1"/>
       <c r="AC389" s="1"/>
     </row>
-    <row r="390" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:29" ht="13.2">
       <c r="A390" s="1"/>
       <c r="B390" s="1"/>
       <c r="C390" s="1"/>
@@ -13234,7 +13306,7 @@
       <c r="AB390" s="1"/>
       <c r="AC390" s="1"/>
     </row>
-    <row r="391" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:29" ht="13.2">
       <c r="A391" s="1"/>
       <c r="B391" s="1"/>
       <c r="C391" s="1"/>
@@ -13265,7 +13337,7 @@
       <c r="AB391" s="1"/>
       <c r="AC391" s="1"/>
     </row>
-    <row r="392" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:29" ht="13.2">
       <c r="A392" s="1"/>
       <c r="B392" s="1"/>
       <c r="C392" s="1"/>
@@ -13296,7 +13368,7 @@
       <c r="AB392" s="1"/>
       <c r="AC392" s="1"/>
     </row>
-    <row r="393" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:29" ht="13.2">
       <c r="A393" s="1"/>
       <c r="B393" s="1"/>
       <c r="C393" s="1"/>
@@ -13327,7 +13399,7 @@
       <c r="AB393" s="1"/>
       <c r="AC393" s="1"/>
     </row>
-    <row r="394" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:29" ht="13.2">
       <c r="A394" s="1"/>
       <c r="B394" s="1"/>
       <c r="C394" s="1"/>
@@ -13358,7 +13430,7 @@
       <c r="AB394" s="1"/>
       <c r="AC394" s="1"/>
     </row>
-    <row r="395" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:29" ht="13.2">
       <c r="A395" s="1"/>
       <c r="B395" s="1"/>
       <c r="C395" s="1"/>
@@ -13389,7 +13461,7 @@
       <c r="AB395" s="1"/>
       <c r="AC395" s="1"/>
     </row>
-    <row r="396" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:29" ht="13.2">
       <c r="A396" s="1"/>
       <c r="B396" s="1"/>
       <c r="C396" s="1"/>
@@ -13420,7 +13492,7 @@
       <c r="AB396" s="1"/>
       <c r="AC396" s="1"/>
     </row>
-    <row r="397" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:29" ht="13.2">
       <c r="A397" s="1"/>
       <c r="B397" s="1"/>
       <c r="C397" s="1"/>
@@ -13451,7 +13523,7 @@
       <c r="AB397" s="1"/>
       <c r="AC397" s="1"/>
     </row>
-    <row r="398" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:29" ht="13.2">
       <c r="A398" s="1"/>
       <c r="B398" s="1"/>
       <c r="C398" s="1"/>
@@ -13482,7 +13554,7 @@
       <c r="AB398" s="1"/>
       <c r="AC398" s="1"/>
     </row>
-    <row r="399" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:29" ht="13.2">
       <c r="A399" s="1"/>
       <c r="B399" s="1"/>
       <c r="C399" s="1"/>
@@ -13513,7 +13585,7 @@
       <c r="AB399" s="1"/>
       <c r="AC399" s="1"/>
     </row>
-    <row r="400" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:29" ht="13.2">
       <c r="A400" s="1"/>
       <c r="B400" s="1"/>
       <c r="C400" s="1"/>
@@ -13544,7 +13616,7 @@
       <c r="AB400" s="1"/>
       <c r="AC400" s="1"/>
     </row>
-    <row r="401" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:29" ht="13.2">
       <c r="A401" s="1"/>
       <c r="B401" s="1"/>
       <c r="C401" s="1"/>
@@ -13575,7 +13647,7 @@
       <c r="AB401" s="1"/>
       <c r="AC401" s="1"/>
     </row>
-    <row r="402" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:29" ht="13.2">
       <c r="A402" s="1"/>
       <c r="B402" s="1"/>
       <c r="C402" s="1"/>
@@ -13606,7 +13678,7 @@
       <c r="AB402" s="1"/>
       <c r="AC402" s="1"/>
     </row>
-    <row r="403" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:29" ht="13.2">
       <c r="A403" s="1"/>
       <c r="B403" s="1"/>
       <c r="C403" s="1"/>
@@ -13637,7 +13709,7 @@
       <c r="AB403" s="1"/>
       <c r="AC403" s="1"/>
     </row>
-    <row r="404" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:29" ht="13.2">
       <c r="A404" s="1"/>
       <c r="B404" s="1"/>
       <c r="C404" s="1"/>
@@ -13668,7 +13740,7 @@
       <c r="AB404" s="1"/>
       <c r="AC404" s="1"/>
     </row>
-    <row r="405" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:29" ht="13.2">
       <c r="A405" s="1"/>
       <c r="B405" s="1"/>
       <c r="C405" s="1"/>
@@ -13699,7 +13771,7 @@
       <c r="AB405" s="1"/>
       <c r="AC405" s="1"/>
     </row>
-    <row r="406" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:29" ht="13.2">
       <c r="A406" s="1"/>
       <c r="B406" s="1"/>
       <c r="C406" s="1"/>
@@ -13730,7 +13802,7 @@
       <c r="AB406" s="1"/>
       <c r="AC406" s="1"/>
     </row>
-    <row r="407" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:29" ht="13.2">
       <c r="A407" s="1"/>
       <c r="B407" s="1"/>
       <c r="C407" s="1"/>
@@ -13761,7 +13833,7 @@
       <c r="AB407" s="1"/>
       <c r="AC407" s="1"/>
     </row>
-    <row r="408" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:29" ht="13.2">
       <c r="A408" s="1"/>
       <c r="B408" s="1"/>
       <c r="C408" s="1"/>
@@ -13792,7 +13864,7 @@
       <c r="AB408" s="1"/>
       <c r="AC408" s="1"/>
     </row>
-    <row r="409" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:29" ht="13.2">
       <c r="A409" s="1"/>
       <c r="B409" s="1"/>
       <c r="C409" s="1"/>
@@ -13823,7 +13895,7 @@
       <c r="AB409" s="1"/>
       <c r="AC409" s="1"/>
     </row>
-    <row r="410" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:29" ht="13.2">
       <c r="A410" s="1"/>
       <c r="B410" s="1"/>
       <c r="C410" s="1"/>
@@ -13854,7 +13926,7 @@
       <c r="AB410" s="1"/>
       <c r="AC410" s="1"/>
     </row>
-    <row r="411" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:29" ht="13.2">
       <c r="A411" s="1"/>
       <c r="B411" s="1"/>
       <c r="C411" s="1"/>
@@ -13885,7 +13957,7 @@
       <c r="AB411" s="1"/>
       <c r="AC411" s="1"/>
     </row>
-    <row r="412" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:29" ht="13.2">
       <c r="A412" s="1"/>
       <c r="B412" s="1"/>
       <c r="C412" s="1"/>
@@ -13916,7 +13988,7 @@
       <c r="AB412" s="1"/>
       <c r="AC412" s="1"/>
     </row>
-    <row r="413" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:29" ht="13.2">
       <c r="A413" s="1"/>
       <c r="B413" s="1"/>
       <c r="C413" s="1"/>
@@ -13947,7 +14019,7 @@
       <c r="AB413" s="1"/>
       <c r="AC413" s="1"/>
     </row>
-    <row r="414" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:29" ht="13.2">
       <c r="A414" s="1"/>
       <c r="B414" s="1"/>
       <c r="C414" s="1"/>
@@ -13978,7 +14050,7 @@
       <c r="AB414" s="1"/>
       <c r="AC414" s="1"/>
     </row>
-    <row r="415" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:29" ht="13.2">
       <c r="A415" s="1"/>
       <c r="B415" s="1"/>
       <c r="C415" s="1"/>
@@ -14009,7 +14081,7 @@
       <c r="AB415" s="1"/>
       <c r="AC415" s="1"/>
     </row>
-    <row r="416" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:29" ht="13.2">
       <c r="A416" s="1"/>
       <c r="B416" s="1"/>
       <c r="C416" s="1"/>
@@ -14040,7 +14112,7 @@
       <c r="AB416" s="1"/>
       <c r="AC416" s="1"/>
     </row>
-    <row r="417" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:29" ht="13.2">
       <c r="A417" s="1"/>
       <c r="B417" s="1"/>
       <c r="C417" s="1"/>
@@ -14071,7 +14143,7 @@
       <c r="AB417" s="1"/>
       <c r="AC417" s="1"/>
     </row>
-    <row r="418" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:29" ht="13.2">
       <c r="A418" s="1"/>
       <c r="B418" s="1"/>
       <c r="C418" s="1"/>
@@ -14102,7 +14174,7 @@
       <c r="AB418" s="1"/>
       <c r="AC418" s="1"/>
     </row>
-    <row r="419" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:29" ht="13.2">
       <c r="A419" s="1"/>
       <c r="B419" s="1"/>
       <c r="C419" s="1"/>
@@ -14133,7 +14205,7 @@
       <c r="AB419" s="1"/>
       <c r="AC419" s="1"/>
     </row>
-    <row r="420" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:29" ht="13.2">
       <c r="A420" s="1"/>
       <c r="B420" s="1"/>
       <c r="C420" s="1"/>
@@ -14164,7 +14236,7 @@
       <c r="AB420" s="1"/>
       <c r="AC420" s="1"/>
     </row>
-    <row r="421" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:29" ht="13.2">
       <c r="A421" s="1"/>
       <c r="B421" s="1"/>
       <c r="C421" s="1"/>
@@ -14195,7 +14267,7 @@
       <c r="AB421" s="1"/>
       <c r="AC421" s="1"/>
     </row>
-    <row r="422" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:29" ht="13.2">
       <c r="A422" s="1"/>
       <c r="B422" s="1"/>
       <c r="C422" s="1"/>
@@ -14226,7 +14298,7 @@
       <c r="AB422" s="1"/>
       <c r="AC422" s="1"/>
     </row>
-    <row r="423" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:29" ht="13.2">
       <c r="A423" s="1"/>
       <c r="B423" s="1"/>
       <c r="C423" s="1"/>
@@ -14257,7 +14329,7 @@
       <c r="AB423" s="1"/>
       <c r="AC423" s="1"/>
     </row>
-    <row r="424" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:29" ht="13.2">
       <c r="A424" s="1"/>
       <c r="B424" s="1"/>
       <c r="C424" s="1"/>
@@ -14288,7 +14360,7 @@
       <c r="AB424" s="1"/>
       <c r="AC424" s="1"/>
     </row>
-    <row r="425" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:29" ht="13.2">
       <c r="A425" s="1"/>
       <c r="B425" s="1"/>
       <c r="C425" s="1"/>
@@ -14319,7 +14391,7 @@
       <c r="AB425" s="1"/>
       <c r="AC425" s="1"/>
     </row>
-    <row r="426" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:29" ht="13.2">
       <c r="A426" s="1"/>
       <c r="B426" s="1"/>
       <c r="C426" s="1"/>
@@ -14350,7 +14422,7 @@
       <c r="AB426" s="1"/>
       <c r="AC426" s="1"/>
     </row>
-    <row r="427" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:29" ht="13.2">
       <c r="A427" s="1"/>
       <c r="B427" s="1"/>
       <c r="C427" s="1"/>
@@ -14381,7 +14453,7 @@
       <c r="AB427" s="1"/>
       <c r="AC427" s="1"/>
     </row>
-    <row r="428" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:29" ht="13.2">
       <c r="A428" s="1"/>
       <c r="B428" s="1"/>
       <c r="C428" s="1"/>
@@ -14412,7 +14484,7 @@
       <c r="AB428" s="1"/>
       <c r="AC428" s="1"/>
     </row>
-    <row r="429" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:29" ht="13.2">
       <c r="A429" s="1"/>
       <c r="B429" s="1"/>
       <c r="C429" s="1"/>
@@ -14443,7 +14515,7 @@
       <c r="AB429" s="1"/>
       <c r="AC429" s="1"/>
     </row>
-    <row r="430" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:29" ht="13.2">
       <c r="A430" s="1"/>
       <c r="B430" s="1"/>
       <c r="C430" s="1"/>
@@ -14474,7 +14546,7 @@
       <c r="AB430" s="1"/>
       <c r="AC430" s="1"/>
     </row>
-    <row r="431" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:29" ht="13.2">
       <c r="A431" s="1"/>
       <c r="B431" s="1"/>
       <c r="C431" s="1"/>
@@ -14505,7 +14577,7 @@
       <c r="AB431" s="1"/>
       <c r="AC431" s="1"/>
     </row>
-    <row r="432" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:29" ht="13.2">
       <c r="A432" s="1"/>
       <c r="B432" s="1"/>
       <c r="C432" s="1"/>
@@ -14536,7 +14608,7 @@
       <c r="AB432" s="1"/>
       <c r="AC432" s="1"/>
     </row>
-    <row r="433" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:29" ht="13.2">
       <c r="A433" s="1"/>
       <c r="B433" s="1"/>
       <c r="C433" s="1"/>
@@ -14567,7 +14639,7 @@
       <c r="AB433" s="1"/>
       <c r="AC433" s="1"/>
     </row>
-    <row r="434" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:29" ht="13.2">
       <c r="A434" s="1"/>
       <c r="B434" s="1"/>
       <c r="C434" s="1"/>
@@ -14598,7 +14670,7 @@
       <c r="AB434" s="1"/>
       <c r="AC434" s="1"/>
     </row>
-    <row r="435" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:29" ht="13.2">
       <c r="A435" s="1"/>
       <c r="B435" s="1"/>
       <c r="C435" s="1"/>
@@ -14629,7 +14701,7 @@
       <c r="AB435" s="1"/>
       <c r="AC435" s="1"/>
     </row>
-    <row r="436" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:29" ht="13.2">
       <c r="A436" s="1"/>
       <c r="B436" s="1"/>
       <c r="C436" s="1"/>
@@ -14660,7 +14732,7 @@
       <c r="AB436" s="1"/>
       <c r="AC436" s="1"/>
     </row>
-    <row r="437" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:29" ht="13.2">
       <c r="A437" s="1"/>
       <c r="B437" s="1"/>
       <c r="C437" s="1"/>
@@ -14691,7 +14763,7 @@
       <c r="AB437" s="1"/>
       <c r="AC437" s="1"/>
     </row>
-    <row r="438" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:29" ht="13.2">
       <c r="A438" s="1"/>
       <c r="B438" s="1"/>
       <c r="C438" s="1"/>
@@ -14722,7 +14794,7 @@
       <c r="AB438" s="1"/>
       <c r="AC438" s="1"/>
     </row>
-    <row r="439" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:29" ht="13.2">
       <c r="A439" s="1"/>
       <c r="B439" s="1"/>
       <c r="C439" s="1"/>
@@ -14753,7 +14825,7 @@
       <c r="AB439" s="1"/>
       <c r="AC439" s="1"/>
     </row>
-    <row r="440" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:29" ht="13.2">
       <c r="A440" s="1"/>
       <c r="B440" s="1"/>
       <c r="C440" s="1"/>
@@ -14784,7 +14856,7 @@
       <c r="AB440" s="1"/>
       <c r="AC440" s="1"/>
     </row>
-    <row r="441" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:29" ht="13.2">
       <c r="A441" s="1"/>
       <c r="B441" s="1"/>
       <c r="C441" s="1"/>
@@ -14815,7 +14887,7 @@
       <c r="AB441" s="1"/>
       <c r="AC441" s="1"/>
     </row>
-    <row r="442" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:29" ht="13.2">
       <c r="A442" s="1"/>
       <c r="B442" s="1"/>
       <c r="C442" s="1"/>
@@ -14846,7 +14918,7 @@
       <c r="AB442" s="1"/>
       <c r="AC442" s="1"/>
     </row>
-    <row r="443" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:29" ht="13.2">
       <c r="A443" s="1"/>
       <c r="B443" s="1"/>
       <c r="C443" s="1"/>
@@ -14877,7 +14949,7 @@
       <c r="AB443" s="1"/>
       <c r="AC443" s="1"/>
     </row>
-    <row r="444" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:29" ht="13.2">
       <c r="A444" s="1"/>
       <c r="B444" s="1"/>
       <c r="C444" s="1"/>
@@ -14908,7 +14980,7 @@
       <c r="AB444" s="1"/>
       <c r="AC444" s="1"/>
     </row>
-    <row r="445" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:29" ht="13.2">
       <c r="A445" s="1"/>
       <c r="B445" s="1"/>
       <c r="C445" s="1"/>
@@ -14939,7 +15011,7 @@
       <c r="AB445" s="1"/>
       <c r="AC445" s="1"/>
     </row>
-    <row r="446" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:29" ht="13.2">
       <c r="A446" s="1"/>
       <c r="B446" s="1"/>
       <c r="C446" s="1"/>
@@ -14970,7 +15042,7 @@
       <c r="AB446" s="1"/>
       <c r="AC446" s="1"/>
     </row>
-    <row r="447" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:29" ht="13.2">
       <c r="A447" s="1"/>
       <c r="B447" s="1"/>
       <c r="C447" s="1"/>
@@ -15001,7 +15073,7 @@
       <c r="AB447" s="1"/>
       <c r="AC447" s="1"/>
     </row>
-    <row r="448" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:29" ht="13.2">
       <c r="A448" s="1"/>
       <c r="B448" s="1"/>
       <c r="C448" s="1"/>
@@ -15032,7 +15104,7 @@
       <c r="AB448" s="1"/>
       <c r="AC448" s="1"/>
     </row>
-    <row r="449" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:29" ht="13.2">
       <c r="A449" s="1"/>
       <c r="B449" s="1"/>
       <c r="C449" s="1"/>
@@ -15063,7 +15135,7 @@
       <c r="AB449" s="1"/>
       <c r="AC449" s="1"/>
     </row>
-    <row r="450" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:29" ht="13.2">
       <c r="A450" s="1"/>
       <c r="B450" s="1"/>
       <c r="C450" s="1"/>
@@ -15094,7 +15166,7 @@
       <c r="AB450" s="1"/>
       <c r="AC450" s="1"/>
     </row>
-    <row r="451" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:29" ht="13.2">
       <c r="A451" s="1"/>
       <c r="B451" s="1"/>
       <c r="C451" s="1"/>
@@ -15125,7 +15197,7 @@
       <c r="AB451" s="1"/>
       <c r="AC451" s="1"/>
     </row>
-    <row r="452" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:29" ht="13.2">
       <c r="A452" s="1"/>
       <c r="B452" s="1"/>
       <c r="C452" s="1"/>
@@ -15156,7 +15228,7 @@
       <c r="AB452" s="1"/>
       <c r="AC452" s="1"/>
     </row>
-    <row r="453" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:29" ht="13.2">
       <c r="A453" s="1"/>
       <c r="B453" s="1"/>
       <c r="C453" s="1"/>
@@ -15187,7 +15259,7 @@
       <c r="AB453" s="1"/>
       <c r="AC453" s="1"/>
     </row>
-    <row r="454" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:29" ht="13.2">
       <c r="A454" s="1"/>
       <c r="B454" s="1"/>
       <c r="C454" s="1"/>
@@ -15218,7 +15290,7 @@
       <c r="AB454" s="1"/>
       <c r="AC454" s="1"/>
     </row>
-    <row r="455" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:29" ht="13.2">
       <c r="A455" s="1"/>
       <c r="B455" s="1"/>
       <c r="C455" s="1"/>
@@ -15249,7 +15321,7 @@
       <c r="AB455" s="1"/>
       <c r="AC455" s="1"/>
     </row>
-    <row r="456" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:29" ht="13.2">
       <c r="A456" s="1"/>
       <c r="B456" s="1"/>
       <c r="C456" s="1"/>
@@ -15280,7 +15352,7 @@
       <c r="AB456" s="1"/>
       <c r="AC456" s="1"/>
     </row>
-    <row r="457" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:29" ht="13.2">
       <c r="A457" s="1"/>
       <c r="B457" s="1"/>
       <c r="C457" s="1"/>
@@ -15311,7 +15383,7 @@
       <c r="AB457" s="1"/>
       <c r="AC457" s="1"/>
     </row>
-    <row r="458" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:29" ht="13.2">
       <c r="A458" s="1"/>
       <c r="B458" s="1"/>
       <c r="C458" s="1"/>
@@ -15342,7 +15414,7 @@
       <c r="AB458" s="1"/>
       <c r="AC458" s="1"/>
     </row>
-    <row r="459" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:29" ht="13.2">
       <c r="A459" s="1"/>
       <c r="B459" s="1"/>
       <c r="C459" s="1"/>
@@ -15373,7 +15445,7 @@
       <c r="AB459" s="1"/>
       <c r="AC459" s="1"/>
     </row>
-    <row r="460" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:29" ht="13.2">
       <c r="A460" s="1"/>
       <c r="B460" s="1"/>
       <c r="C460" s="1"/>
@@ -15404,7 +15476,7 @@
       <c r="AB460" s="1"/>
       <c r="AC460" s="1"/>
     </row>
-    <row r="461" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:29" ht="13.2">
       <c r="A461" s="1"/>
       <c r="B461" s="1"/>
       <c r="C461" s="1"/>
@@ -15435,7 +15507,7 @@
       <c r="AB461" s="1"/>
       <c r="AC461" s="1"/>
     </row>
-    <row r="462" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:29" ht="13.2">
       <c r="A462" s="1"/>
       <c r="B462" s="1"/>
       <c r="C462" s="1"/>
@@ -15466,7 +15538,7 @@
       <c r="AB462" s="1"/>
       <c r="AC462" s="1"/>
     </row>
-    <row r="463" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:29" ht="13.2">
       <c r="A463" s="1"/>
       <c r="B463" s="1"/>
       <c r="C463" s="1"/>
@@ -15497,7 +15569,7 @@
       <c r="AB463" s="1"/>
       <c r="AC463" s="1"/>
     </row>
-    <row r="464" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:29" ht="13.2">
       <c r="A464" s="1"/>
       <c r="B464" s="1"/>
       <c r="C464" s="1"/>
@@ -15528,7 +15600,7 @@
       <c r="AB464" s="1"/>
       <c r="AC464" s="1"/>
     </row>
-    <row r="465" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:29" ht="13.2">
       <c r="A465" s="1"/>
       <c r="B465" s="1"/>
       <c r="C465" s="1"/>
@@ -15559,7 +15631,7 @@
       <c r="AB465" s="1"/>
       <c r="AC465" s="1"/>
     </row>
-    <row r="466" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:29" ht="13.2">
       <c r="A466" s="1"/>
       <c r="B466" s="1"/>
       <c r="C466" s="1"/>
@@ -15590,7 +15662,7 @@
       <c r="AB466" s="1"/>
       <c r="AC466" s="1"/>
     </row>
-    <row r="467" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:29" ht="13.2">
       <c r="A467" s="1"/>
       <c r="B467" s="1"/>
       <c r="C467" s="1"/>
@@ -15621,7 +15693,7 @@
       <c r="AB467" s="1"/>
       <c r="AC467" s="1"/>
     </row>
-    <row r="468" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:29" ht="13.2">
       <c r="A468" s="1"/>
       <c r="B468" s="1"/>
       <c r="C468" s="1"/>
@@ -15652,7 +15724,7 @@
       <c r="AB468" s="1"/>
       <c r="AC468" s="1"/>
     </row>
-    <row r="469" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:29" ht="13.2">
       <c r="A469" s="1"/>
       <c r="B469" s="1"/>
       <c r="C469" s="1"/>
@@ -15683,7 +15755,7 @@
       <c r="AB469" s="1"/>
       <c r="AC469" s="1"/>
     </row>
-    <row r="470" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:29" ht="13.2">
       <c r="A470" s="1"/>
       <c r="B470" s="1"/>
       <c r="C470" s="1"/>
@@ -15714,7 +15786,7 @@
       <c r="AB470" s="1"/>
       <c r="AC470" s="1"/>
     </row>
-    <row r="471" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:29" ht="13.2">
       <c r="A471" s="1"/>
       <c r="B471" s="1"/>
       <c r="C471" s="1"/>
@@ -15745,7 +15817,7 @@
       <c r="AB471" s="1"/>
       <c r="AC471" s="1"/>
     </row>
-    <row r="472" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:29" ht="13.2">
       <c r="A472" s="1"/>
       <c r="B472" s="1"/>
       <c r="C472" s="1"/>
@@ -15776,7 +15848,7 @@
       <c r="AB472" s="1"/>
       <c r="AC472" s="1"/>
     </row>
-    <row r="473" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:29" ht="13.2">
       <c r="A473" s="1"/>
       <c r="B473" s="1"/>
       <c r="C473" s="1"/>
@@ -15807,7 +15879,7 @@
       <c r="AB473" s="1"/>
       <c r="AC473" s="1"/>
     </row>
-    <row r="474" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:29" ht="13.2">
       <c r="A474" s="1"/>
       <c r="B474" s="1"/>
       <c r="C474" s="1"/>
@@ -15838,7 +15910,7 @@
       <c r="AB474" s="1"/>
       <c r="AC474" s="1"/>
     </row>
-    <row r="475" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:29" ht="13.2">
       <c r="A475" s="1"/>
       <c r="B475" s="1"/>
       <c r="C475" s="1"/>
@@ -15869,7 +15941,7 @@
       <c r="AB475" s="1"/>
       <c r="AC475" s="1"/>
     </row>
-    <row r="476" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:29" ht="13.2">
       <c r="A476" s="1"/>
       <c r="B476" s="1"/>
       <c r="C476" s="1"/>
@@ -15900,7 +15972,7 @@
       <c r="AB476" s="1"/>
       <c r="AC476" s="1"/>
     </row>
-    <row r="477" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:29" ht="13.2">
       <c r="A477" s="1"/>
       <c r="B477" s="1"/>
       <c r="C477" s="1"/>
@@ -15931,7 +16003,7 @@
       <c r="AB477" s="1"/>
       <c r="AC477" s="1"/>
     </row>
-    <row r="478" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:29" ht="13.2">
       <c r="A478" s="1"/>
       <c r="B478" s="1"/>
       <c r="C478" s="1"/>
@@ -15962,7 +16034,7 @@
       <c r="AB478" s="1"/>
       <c r="AC478" s="1"/>
     </row>
-    <row r="479" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:29" ht="13.2">
       <c r="A479" s="1"/>
       <c r="B479" s="1"/>
       <c r="C479" s="1"/>
@@ -15993,7 +16065,7 @@
       <c r="AB479" s="1"/>
       <c r="AC479" s="1"/>
     </row>
-    <row r="480" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:29" ht="13.2">
       <c r="A480" s="1"/>
       <c r="B480" s="1"/>
       <c r="C480" s="1"/>
@@ -16024,7 +16096,7 @@
       <c r="AB480" s="1"/>
       <c r="AC480" s="1"/>
     </row>
-    <row r="481" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:29" ht="13.2">
       <c r="A481" s="1"/>
       <c r="B481" s="1"/>
       <c r="C481" s="1"/>
@@ -16055,7 +16127,7 @@
       <c r="AB481" s="1"/>
       <c r="AC481" s="1"/>
     </row>
-    <row r="482" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:29" ht="13.2">
       <c r="A482" s="1"/>
       <c r="B482" s="1"/>
       <c r="C482" s="1"/>
@@ -16086,7 +16158,7 @@
       <c r="AB482" s="1"/>
       <c r="AC482" s="1"/>
     </row>
-    <row r="483" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:29" ht="13.2">
       <c r="A483" s="1"/>
       <c r="B483" s="1"/>
       <c r="C483" s="1"/>
@@ -16117,7 +16189,7 @@
       <c r="AB483" s="1"/>
       <c r="AC483" s="1"/>
     </row>
-    <row r="484" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:29" ht="13.2">
       <c r="A484" s="1"/>
       <c r="B484" s="1"/>
       <c r="C484" s="1"/>
@@ -16148,7 +16220,7 @@
       <c r="AB484" s="1"/>
       <c r="AC484" s="1"/>
     </row>
-    <row r="485" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:29" ht="13.2">
       <c r="A485" s="1"/>
       <c r="B485" s="1"/>
       <c r="C485" s="1"/>
@@ -16179,7 +16251,7 @@
       <c r="AB485" s="1"/>
       <c r="AC485" s="1"/>
     </row>
-    <row r="486" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:29" ht="13.2">
       <c r="A486" s="1"/>
       <c r="B486" s="1"/>
       <c r="C486" s="1"/>
@@ -16210,7 +16282,7 @@
       <c r="AB486" s="1"/>
       <c r="AC486" s="1"/>
     </row>
-    <row r="487" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:29" ht="13.2">
       <c r="A487" s="1"/>
       <c r="B487" s="1"/>
       <c r="C487" s="1"/>
@@ -16241,7 +16313,7 @@
       <c r="AB487" s="1"/>
       <c r="AC487" s="1"/>
     </row>
-    <row r="488" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:29" ht="13.2">
       <c r="A488" s="1"/>
       <c r="B488" s="1"/>
       <c r="C488" s="1"/>
@@ -16272,7 +16344,7 @@
       <c r="AB488" s="1"/>
       <c r="AC488" s="1"/>
     </row>
-    <row r="489" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:29" ht="13.2">
       <c r="A489" s="1"/>
       <c r="B489" s="1"/>
       <c r="C489" s="1"/>
@@ -16303,7 +16375,7 @@
       <c r="AB489" s="1"/>
       <c r="AC489" s="1"/>
     </row>
-    <row r="490" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:29" ht="13.2">
       <c r="A490" s="1"/>
       <c r="B490" s="1"/>
       <c r="C490" s="1"/>
@@ -16334,7 +16406,7 @@
       <c r="AB490" s="1"/>
       <c r="AC490" s="1"/>
     </row>
-    <row r="491" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:29" ht="13.2">
       <c r="A491" s="1"/>
       <c r="B491" s="1"/>
       <c r="C491" s="1"/>
@@ -16365,7 +16437,7 @@
       <c r="AB491" s="1"/>
       <c r="AC491" s="1"/>
     </row>
-    <row r="492" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:29" ht="13.2">
       <c r="A492" s="1"/>
       <c r="B492" s="1"/>
       <c r="C492" s="1"/>
@@ -16396,7 +16468,7 @@
       <c r="AB492" s="1"/>
       <c r="AC492" s="1"/>
     </row>
-    <row r="493" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:29" ht="13.2">
       <c r="A493" s="1"/>
       <c r="B493" s="1"/>
       <c r="C493" s="1"/>
@@ -16427,7 +16499,7 @@
       <c r="AB493" s="1"/>
       <c r="AC493" s="1"/>
     </row>
-    <row r="494" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:29" ht="13.2">
       <c r="A494" s="1"/>
       <c r="B494" s="1"/>
       <c r="C494" s="1"/>
@@ -16458,7 +16530,7 @@
       <c r="AB494" s="1"/>
       <c r="AC494" s="1"/>
     </row>
-    <row r="495" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:29" ht="13.2">
       <c r="A495" s="1"/>
       <c r="B495" s="1"/>
       <c r="C495" s="1"/>
@@ -16489,7 +16561,7 @@
       <c r="AB495" s="1"/>
       <c r="AC495" s="1"/>
     </row>
-    <row r="496" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:29" ht="13.2">
       <c r="A496" s="1"/>
       <c r="B496" s="1"/>
       <c r="C496" s="1"/>
@@ -16520,7 +16592,7 @@
       <c r="AB496" s="1"/>
       <c r="AC496" s="1"/>
     </row>
-    <row r="497" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:29" ht="13.2">
       <c r="A497" s="1"/>
       <c r="B497" s="1"/>
       <c r="C497" s="1"/>
@@ -16551,7 +16623,7 @@
       <c r="AB497" s="1"/>
       <c r="AC497" s="1"/>
     </row>
-    <row r="498" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:29" ht="13.2">
       <c r="A498" s="1"/>
       <c r="B498" s="1"/>
       <c r="C498" s="1"/>
@@ -16582,7 +16654,7 @@
       <c r="AB498" s="1"/>
       <c r="AC498" s="1"/>
     </row>
-    <row r="499" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:29" ht="13.2">
       <c r="A499" s="1"/>
       <c r="B499" s="1"/>
       <c r="C499" s="1"/>
@@ -16613,7 +16685,7 @@
       <c r="AB499" s="1"/>
       <c r="AC499" s="1"/>
     </row>
-    <row r="500" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:29" ht="13.2">
       <c r="A500" s="1"/>
       <c r="B500" s="1"/>
       <c r="C500" s="1"/>
@@ -16644,7 +16716,7 @@
       <c r="AB500" s="1"/>
       <c r="AC500" s="1"/>
     </row>
-    <row r="501" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:29" ht="13.2">
       <c r="A501" s="1"/>
       <c r="B501" s="1"/>
       <c r="C501" s="1"/>
@@ -16675,7 +16747,7 @@
       <c r="AB501" s="1"/>
       <c r="AC501" s="1"/>
     </row>
-    <row r="502" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:29" ht="13.2">
       <c r="A502" s="1"/>
       <c r="B502" s="1"/>
       <c r="C502" s="1"/>
@@ -16706,7 +16778,7 @@
       <c r="AB502" s="1"/>
       <c r="AC502" s="1"/>
     </row>
-    <row r="503" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:29" ht="13.2">
       <c r="A503" s="1"/>
       <c r="B503" s="1"/>
       <c r="C503" s="1"/>
@@ -16737,7 +16809,7 @@
       <c r="AB503" s="1"/>
       <c r="AC503" s="1"/>
     </row>
-    <row r="504" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:29" ht="13.2">
       <c r="A504" s="1"/>
       <c r="B504" s="1"/>
       <c r="C504" s="1"/>
@@ -16768,7 +16840,7 @@
       <c r="AB504" s="1"/>
       <c r="AC504" s="1"/>
     </row>
-    <row r="505" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:29" ht="13.2">
       <c r="A505" s="1"/>
       <c r="B505" s="1"/>
       <c r="C505" s="1"/>
@@ -16799,7 +16871,7 @@
       <c r="AB505" s="1"/>
       <c r="AC505" s="1"/>
     </row>
-    <row r="506" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:29" ht="13.2">
       <c r="A506" s="1"/>
       <c r="B506" s="1"/>
       <c r="C506" s="1"/>
@@ -16830,7 +16902,7 @@
       <c r="AB506" s="1"/>
       <c r="AC506" s="1"/>
     </row>
-    <row r="507" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:29" ht="13.2">
       <c r="A507" s="1"/>
       <c r="B507" s="1"/>
       <c r="C507" s="1"/>
@@ -16861,7 +16933,7 @@
       <c r="AB507" s="1"/>
       <c r="AC507" s="1"/>
     </row>
-    <row r="508" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:29" ht="13.2">
       <c r="A508" s="1"/>
       <c r="B508" s="1"/>
       <c r="C508" s="1"/>
@@ -16892,7 +16964,7 @@
       <c r="AB508" s="1"/>
       <c r="AC508" s="1"/>
     </row>
-    <row r="509" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:29" ht="13.2">
       <c r="A509" s="1"/>
       <c r="B509" s="1"/>
       <c r="C509" s="1"/>
@@ -16923,7 +16995,7 @@
       <c r="AB509" s="1"/>
       <c r="AC509" s="1"/>
     </row>
-    <row r="510" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:29" ht="13.2">
       <c r="A510" s="1"/>
       <c r="B510" s="1"/>
       <c r="C510" s="1"/>
@@ -16954,7 +17026,7 @@
       <c r="AB510" s="1"/>
       <c r="AC510" s="1"/>
     </row>
-    <row r="511" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:29" ht="13.2">
       <c r="A511" s="1"/>
       <c r="B511" s="1"/>
       <c r="C511" s="1"/>
@@ -16985,7 +17057,7 @@
       <c r="AB511" s="1"/>
       <c r="AC511" s="1"/>
     </row>
-    <row r="512" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:29" ht="13.2">
       <c r="A512" s="1"/>
       <c r="B512" s="1"/>
       <c r="C512" s="1"/>
@@ -17016,7 +17088,7 @@
       <c r="AB512" s="1"/>
       <c r="AC512" s="1"/>
     </row>
-    <row r="513" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:29" ht="13.2">
       <c r="A513" s="1"/>
       <c r="B513" s="1"/>
       <c r="C513" s="1"/>
@@ -17047,7 +17119,7 @@
       <c r="AB513" s="1"/>
       <c r="AC513" s="1"/>
     </row>
-    <row r="514" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:29" ht="13.2">
       <c r="A514" s="1"/>
       <c r="B514" s="1"/>
       <c r="C514" s="1"/>
@@ -17078,7 +17150,7 @@
       <c r="AB514" s="1"/>
       <c r="AC514" s="1"/>
     </row>
-    <row r="515" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:29" ht="13.2">
       <c r="A515" s="1"/>
       <c r="B515" s="1"/>
       <c r="C515" s="1"/>
@@ -17109,7 +17181,7 @@
       <c r="AB515" s="1"/>
       <c r="AC515" s="1"/>
     </row>
-    <row r="516" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:29" ht="13.2">
       <c r="A516" s="1"/>
       <c r="B516" s="1"/>
       <c r="C516" s="1"/>
@@ -17140,7 +17212,7 @@
       <c r="AB516" s="1"/>
       <c r="AC516" s="1"/>
     </row>
-    <row r="517" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:29" ht="13.2">
       <c r="A517" s="1"/>
       <c r="B517" s="1"/>
       <c r="C517" s="1"/>
@@ -17171,7 +17243,7 @@
       <c r="AB517" s="1"/>
       <c r="AC517" s="1"/>
     </row>
-    <row r="518" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:29" ht="13.2">
       <c r="A518" s="1"/>
       <c r="B518" s="1"/>
       <c r="C518" s="1"/>
@@ -17202,7 +17274,7 @@
       <c r="AB518" s="1"/>
       <c r="AC518" s="1"/>
     </row>
-    <row r="519" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:29" ht="13.2">
       <c r="A519" s="1"/>
       <c r="B519" s="1"/>
       <c r="C519" s="1"/>
@@ -17233,7 +17305,7 @@
       <c r="AB519" s="1"/>
       <c r="AC519" s="1"/>
     </row>
-    <row r="520" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:29" ht="13.2">
       <c r="A520" s="1"/>
       <c r="B520" s="1"/>
       <c r="C520" s="1"/>
@@ -17264,7 +17336,7 @@
       <c r="AB520" s="1"/>
       <c r="AC520" s="1"/>
     </row>
-    <row r="521" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:29" ht="13.2">
       <c r="A521" s="1"/>
       <c r="B521" s="1"/>
       <c r="C521" s="1"/>
@@ -17295,7 +17367,7 @@
       <c r="AB521" s="1"/>
       <c r="AC521" s="1"/>
     </row>
-    <row r="522" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:29" ht="13.2">
       <c r="A522" s="1"/>
       <c r="B522" s="1"/>
       <c r="C522" s="1"/>
@@ -17326,7 +17398,7 @@
       <c r="AB522" s="1"/>
       <c r="AC522" s="1"/>
     </row>
-    <row r="523" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:29" ht="13.2">
       <c r="A523" s="1"/>
       <c r="B523" s="1"/>
       <c r="C523" s="1"/>
@@ -17357,7 +17429,7 @@
       <c r="AB523" s="1"/>
       <c r="AC523" s="1"/>
     </row>
-    <row r="524" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:29" ht="13.2">
       <c r="A524" s="1"/>
       <c r="B524" s="1"/>
       <c r="C524" s="1"/>
@@ -17388,7 +17460,7 @@
       <c r="AB524" s="1"/>
       <c r="AC524" s="1"/>
     </row>
-    <row r="525" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:29" ht="13.2">
       <c r="A525" s="1"/>
       <c r="B525" s="1"/>
       <c r="C525" s="1"/>
@@ -17419,7 +17491,7 @@
       <c r="AB525" s="1"/>
       <c r="AC525" s="1"/>
     </row>
-    <row r="526" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:29" ht="13.2">
       <c r="A526" s="1"/>
       <c r="B526" s="1"/>
       <c r="C526" s="1"/>
@@ -17450,7 +17522,7 @@
       <c r="AB526" s="1"/>
       <c r="AC526" s="1"/>
     </row>
-    <row r="527" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:29" ht="13.2">
       <c r="A527" s="1"/>
       <c r="B527" s="1"/>
       <c r="C527" s="1"/>
@@ -17481,7 +17553,7 @@
       <c r="AB527" s="1"/>
       <c r="AC527" s="1"/>
     </row>
-    <row r="528" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:29" ht="13.2">
       <c r="A528" s="1"/>
       <c r="B528" s="1"/>
       <c r="C528" s="1"/>
@@ -17512,7 +17584,7 @@
       <c r="AB528" s="1"/>
       <c r="AC528" s="1"/>
     </row>
-    <row r="529" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:29" ht="13.2">
       <c r="A529" s="1"/>
       <c r="B529" s="1"/>
       <c r="C529" s="1"/>
@@ -17543,7 +17615,7 @@
       <c r="AB529" s="1"/>
       <c r="AC529" s="1"/>
     </row>
-    <row r="530" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:29" ht="13.2">
       <c r="A530" s="1"/>
       <c r="B530" s="1"/>
       <c r="C530" s="1"/>
@@ -17574,7 +17646,7 @@
       <c r="AB530" s="1"/>
       <c r="AC530" s="1"/>
     </row>
-    <row r="531" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:29" ht="13.2">
       <c r="A531" s="1"/>
       <c r="B531" s="1"/>
       <c r="C531" s="1"/>
@@ -17605,7 +17677,7 @@
       <c r="AB531" s="1"/>
       <c r="AC531" s="1"/>
     </row>
-    <row r="532" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:29" ht="13.2">
       <c r="A532" s="1"/>
       <c r="B532" s="1"/>
       <c r="C532" s="1"/>
@@ -17636,7 +17708,7 @@
       <c r="AB532" s="1"/>
       <c r="AC532" s="1"/>
     </row>
-    <row r="533" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:29" ht="13.2">
       <c r="A533" s="1"/>
       <c r="B533" s="1"/>
       <c r="C533" s="1"/>
@@ -17667,7 +17739,7 @@
       <c r="AB533" s="1"/>
       <c r="AC533" s="1"/>
     </row>
-    <row r="534" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:29" ht="13.2">
       <c r="A534" s="1"/>
       <c r="B534" s="1"/>
       <c r="C534" s="1"/>
@@ -17698,7 +17770,7 @@
       <c r="AB534" s="1"/>
       <c r="AC534" s="1"/>
     </row>
-    <row r="535" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:29" ht="13.2">
       <c r="A535" s="1"/>
       <c r="B535" s="1"/>
       <c r="C535" s="1"/>
@@ -17729,7 +17801,7 @@
       <c r="AB535" s="1"/>
       <c r="AC535" s="1"/>
     </row>
-    <row r="536" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:29" ht="13.2">
       <c r="A536" s="1"/>
       <c r="B536" s="1"/>
       <c r="C536" s="1"/>
@@ -17760,7 +17832,7 @@
       <c r="AB536" s="1"/>
       <c r="AC536" s="1"/>
     </row>
-    <row r="537" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:29" ht="13.2">
       <c r="A537" s="1"/>
       <c r="B537" s="1"/>
       <c r="C537" s="1"/>
@@ -17791,7 +17863,7 @@
       <c r="AB537" s="1"/>
       <c r="AC537" s="1"/>
     </row>
-    <row r="538" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:29" ht="13.2">
       <c r="A538" s="1"/>
       <c r="B538" s="1"/>
       <c r="C538" s="1"/>
@@ -17822,7 +17894,7 @@
       <c r="AB538" s="1"/>
       <c r="AC538" s="1"/>
     </row>
-    <row r="539" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:29" ht="13.2">
       <c r="A539" s="1"/>
       <c r="B539" s="1"/>
       <c r="C539" s="1"/>
@@ -17853,7 +17925,7 @@
       <c r="AB539" s="1"/>
       <c r="AC539" s="1"/>
     </row>
-    <row r="540" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:29" ht="13.2">
       <c r="A540" s="1"/>
       <c r="B540" s="1"/>
       <c r="C540" s="1"/>
@@ -17884,7 +17956,7 @@
       <c r="AB540" s="1"/>
       <c r="AC540" s="1"/>
     </row>
-    <row r="541" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:29" ht="13.2">
       <c r="A541" s="1"/>
       <c r="B541" s="1"/>
       <c r="C541" s="1"/>
@@ -17915,7 +17987,7 @@
       <c r="AB541" s="1"/>
       <c r="AC541" s="1"/>
     </row>
-    <row r="542" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:29" ht="13.2">
       <c r="A542" s="1"/>
       <c r="B542" s="1"/>
       <c r="C542" s="1"/>
@@ -17946,7 +18018,7 @@
       <c r="AB542" s="1"/>
       <c r="AC542" s="1"/>
     </row>
-    <row r="543" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:29" ht="13.2">
       <c r="A543" s="1"/>
       <c r="B543" s="1"/>
       <c r="C543" s="1"/>
@@ -17977,7 +18049,7 @@
       <c r="AB543" s="1"/>
       <c r="AC543" s="1"/>
     </row>
-    <row r="544" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:29" ht="13.2">
       <c r="A544" s="1"/>
       <c r="B544" s="1"/>
       <c r="C544" s="1"/>
@@ -18008,7 +18080,7 @@
       <c r="AB544" s="1"/>
       <c r="AC544" s="1"/>
     </row>
-    <row r="545" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:29" ht="13.2">
       <c r="A545" s="1"/>
       <c r="B545" s="1"/>
       <c r="C545" s="1"/>
@@ -18039,7 +18111,7 @@
       <c r="AB545" s="1"/>
       <c r="AC545" s="1"/>
     </row>
-    <row r="546" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:29" ht="13.2">
       <c r="A546" s="1"/>
       <c r="B546" s="1"/>
       <c r="C546" s="1"/>
@@ -18070,7 +18142,7 @@
       <c r="AB546" s="1"/>
       <c r="AC546" s="1"/>
     </row>
-    <row r="547" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:29" ht="13.2">
       <c r="A547" s="1"/>
       <c r="B547" s="1"/>
       <c r="C547" s="1"/>
@@ -18101,7 +18173,7 @@
       <c r="AB547" s="1"/>
       <c r="AC547" s="1"/>
     </row>
-    <row r="548" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:29" ht="13.2">
       <c r="A548" s="1"/>
       <c r="B548" s="1"/>
       <c r="C548" s="1"/>
@@ -18132,7 +18204,7 @@
       <c r="AB548" s="1"/>
       <c r="AC548" s="1"/>
     </row>
-    <row r="549" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:29" ht="13.2">
       <c r="A549" s="1"/>
       <c r="B549" s="1"/>
       <c r="C549" s="1"/>
@@ -18163,7 +18235,7 @@
       <c r="AB549" s="1"/>
       <c r="AC549" s="1"/>
     </row>
-    <row r="550" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:29" ht="13.2">
       <c r="A550" s="1"/>
       <c r="B550" s="1"/>
       <c r="C550" s="1"/>
@@ -18194,7 +18266,7 @@
       <c r="AB550" s="1"/>
       <c r="AC550" s="1"/>
     </row>
-    <row r="551" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:29" ht="13.2">
       <c r="A551" s="1"/>
       <c r="B551" s="1"/>
       <c r="C551" s="1"/>
@@ -18225,7 +18297,7 @@
       <c r="AB551" s="1"/>
       <c r="AC551" s="1"/>
     </row>
-    <row r="552" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:29" ht="13.2">
       <c r="A552" s="1"/>
       <c r="B552" s="1"/>
       <c r="C552" s="1"/>
@@ -18256,7 +18328,7 @@
       <c r="AB552" s="1"/>
       <c r="AC552" s="1"/>
     </row>
-    <row r="553" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:29" ht="13.2">
       <c r="A553" s="1"/>
       <c r="B553" s="1"/>
       <c r="C553" s="1"/>
@@ -18287,7 +18359,7 @@
       <c r="AB553" s="1"/>
       <c r="AC553" s="1"/>
     </row>
-    <row r="554" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:29" ht="13.2">
       <c r="A554" s="1"/>
       <c r="B554" s="1"/>
       <c r="C554" s="1"/>
@@ -18318,7 +18390,7 @@
       <c r="AB554" s="1"/>
       <c r="AC554" s="1"/>
     </row>
-    <row r="555" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:29" ht="13.2">
       <c r="A555" s="1"/>
       <c r="B555" s="1"/>
       <c r="C555" s="1"/>
@@ -18349,7 +18421,7 @@
       <c r="AB555" s="1"/>
       <c r="AC555" s="1"/>
     </row>
-    <row r="556" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:29" ht="13.2">
       <c r="A556" s="1"/>
       <c r="B556" s="1"/>
       <c r="C556" s="1"/>
@@ -18380,7 +18452,7 @@
       <c r="AB556" s="1"/>
       <c r="AC556" s="1"/>
     </row>
-    <row r="557" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:29" ht="13.2">
       <c r="A557" s="1"/>
       <c r="B557" s="1"/>
       <c r="C557" s="1"/>
@@ -18411,7 +18483,7 @@
       <c r="AB557" s="1"/>
       <c r="AC557" s="1"/>
     </row>
-    <row r="558" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:29" ht="13.2">
       <c r="A558" s="1"/>
       <c r="B558" s="1"/>
       <c r="C558" s="1"/>
@@ -18442,7 +18514,7 @@
       <c r="AB558" s="1"/>
       <c r="AC558" s="1"/>
     </row>
-    <row r="559" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:29" ht="13.2">
       <c r="A559" s="1"/>
       <c r="B559" s="1"/>
       <c r="C559" s="1"/>
@@ -18473,7 +18545,7 @@
       <c r="AB559" s="1"/>
       <c r="AC559" s="1"/>
     </row>
-    <row r="560" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:29" ht="13.2">
       <c r="A560" s="1"/>
       <c r="B560" s="1"/>
       <c r="C560" s="1"/>
@@ -18504,7 +18576,7 @@
       <c r="AB560" s="1"/>
       <c r="AC560" s="1"/>
     </row>
-    <row r="561" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:29" ht="13.2">
       <c r="A561" s="1"/>
       <c r="B561" s="1"/>
       <c r="C561" s="1"/>
@@ -18535,7 +18607,7 @@
       <c r="AB561" s="1"/>
       <c r="AC561" s="1"/>
     </row>
-    <row r="562" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:29" ht="13.2">
       <c r="A562" s="1"/>
       <c r="B562" s="1"/>
       <c r="C562" s="1"/>
@@ -18566,7 +18638,7 @@
       <c r="AB562" s="1"/>
       <c r="AC562" s="1"/>
     </row>
-    <row r="563" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:29" ht="13.2">
       <c r="A563" s="1"/>
       <c r="B563" s="1"/>
       <c r="C563" s="1"/>
@@ -18597,7 +18669,7 @@
       <c r="AB563" s="1"/>
       <c r="AC563" s="1"/>
     </row>
-    <row r="564" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:29" ht="13.2">
       <c r="A564" s="1"/>
       <c r="B564" s="1"/>
       <c r="C564" s="1"/>
@@ -18628,7 +18700,7 @@
       <c r="AB564" s="1"/>
       <c r="AC564" s="1"/>
     </row>
-    <row r="565" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:29" ht="13.2">
       <c r="A565" s="1"/>
       <c r="B565" s="1"/>
       <c r="C565" s="1"/>
@@ -18659,7 +18731,7 @@
       <c r="AB565" s="1"/>
       <c r="AC565" s="1"/>
     </row>
-    <row r="566" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:29" ht="13.2">
       <c r="A566" s="1"/>
       <c r="B566" s="1"/>
       <c r="C566" s="1"/>
@@ -18690,7 +18762,7 @@
       <c r="AB566" s="1"/>
       <c r="AC566" s="1"/>
     </row>
-    <row r="567" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:29" ht="13.2">
       <c r="A567" s="1"/>
       <c r="B567" s="1"/>
       <c r="C567" s="1"/>
@@ -18721,7 +18793,7 @@
       <c r="AB567" s="1"/>
       <c r="AC567" s="1"/>
     </row>
-    <row r="568" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:29" ht="13.2">
       <c r="A568" s="1"/>
       <c r="B568" s="1"/>
       <c r="C568" s="1"/>
@@ -18752,7 +18824,7 @@
       <c r="AB568" s="1"/>
       <c r="AC568" s="1"/>
     </row>
-    <row r="569" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:29" ht="13.2">
       <c r="A569" s="1"/>
       <c r="B569" s="1"/>
       <c r="C569" s="1"/>
@@ -18783,7 +18855,7 @@
       <c r="AB569" s="1"/>
       <c r="AC569" s="1"/>
     </row>
-    <row r="570" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:29" ht="13.2">
       <c r="A570" s="1"/>
       <c r="B570" s="1"/>
       <c r="C570" s="1"/>
@@ -18814,7 +18886,7 @@
       <c r="AB570" s="1"/>
       <c r="AC570" s="1"/>
     </row>
-    <row r="571" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:29" ht="13.2">
       <c r="A571" s="1"/>
       <c r="B571" s="1"/>
       <c r="C571" s="1"/>
@@ -18845,7 +18917,7 @@
       <c r="AB571" s="1"/>
       <c r="AC571" s="1"/>
     </row>
-    <row r="572" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:29" ht="13.2">
       <c r="A572" s="1"/>
       <c r="B572" s="1"/>
       <c r="C572" s="1"/>
@@ -18876,7 +18948,7 @@
       <c r="AB572" s="1"/>
       <c r="AC572" s="1"/>
     </row>
-    <row r="573" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:29" ht="13.2">
       <c r="A573" s="1"/>
       <c r="B573" s="1"/>
       <c r="C573" s="1"/>
@@ -18907,7 +18979,7 @@
       <c r="AB573" s="1"/>
       <c r="AC573" s="1"/>
     </row>
-    <row r="574" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:29" ht="13.2">
       <c r="A574" s="1"/>
       <c r="B574" s="1"/>
       <c r="C574" s="1"/>
@@ -18938,7 +19010,7 @@
       <c r="AB574" s="1"/>
       <c r="AC574" s="1"/>
     </row>
-    <row r="575" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:29" ht="13.2">
       <c r="A575" s="1"/>
       <c r="B575" s="1"/>
       <c r="C575" s="1"/>
@@ -18969,7 +19041,7 @@
       <c r="AB575" s="1"/>
       <c r="AC575" s="1"/>
     </row>
-    <row r="576" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:29" ht="13.2">
       <c r="A576" s="1"/>
       <c r="B576" s="1"/>
       <c r="C576" s="1"/>
@@ -19000,7 +19072,7 @@
       <c r="AB576" s="1"/>
       <c r="AC576" s="1"/>
     </row>
-    <row r="577" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:29" ht="13.2">
       <c r="A577" s="1"/>
       <c r="B577" s="1"/>
       <c r="C577" s="1"/>
@@ -19031,7 +19103,7 @@
       <c r="AB577" s="1"/>
       <c r="AC577" s="1"/>
     </row>
-    <row r="578" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:29" ht="13.2">
       <c r="A578" s="1"/>
       <c r="B578" s="1"/>
       <c r="C578" s="1"/>
@@ -19062,7 +19134,7 @@
       <c r="AB578" s="1"/>
       <c r="AC578" s="1"/>
     </row>
-    <row r="579" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:29" ht="13.2">
       <c r="A579" s="1"/>
       <c r="B579" s="1"/>
       <c r="C579" s="1"/>
@@ -19093,7 +19165,7 @@
       <c r="AB579" s="1"/>
       <c r="AC579" s="1"/>
     </row>
-    <row r="580" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:29" ht="13.2">
       <c r="A580" s="1"/>
       <c r="B580" s="1"/>
       <c r="C580" s="1"/>
@@ -19124,7 +19196,7 @@
       <c r="AB580" s="1"/>
       <c r="AC580" s="1"/>
     </row>
-    <row r="581" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:29" ht="13.2">
       <c r="A581" s="1"/>
       <c r="B581" s="1"/>
       <c r="C581" s="1"/>
@@ -19155,7 +19227,7 @@
       <c r="AB581" s="1"/>
       <c r="AC581" s="1"/>
     </row>
-    <row r="582" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:29" ht="13.2">
       <c r="A582" s="1"/>
       <c r="B582" s="1"/>
       <c r="C582" s="1"/>
@@ -19186,7 +19258,7 @@
       <c r="AB582" s="1"/>
       <c r="AC582" s="1"/>
     </row>
-    <row r="583" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:29" ht="13.2">
       <c r="A583" s="1"/>
       <c r="B583" s="1"/>
       <c r="C583" s="1"/>
@@ -19217,7 +19289,7 @@
       <c r="AB583" s="1"/>
       <c r="AC583" s="1"/>
     </row>
-    <row r="584" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:29" ht="13.2">
       <c r="A584" s="1"/>
       <c r="B584" s="1"/>
       <c r="C584" s="1"/>
@@ -19248,7 +19320,7 @@
       <c r="AB584" s="1"/>
       <c r="AC584" s="1"/>
     </row>
-    <row r="585" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:29" ht="13.2">
       <c r="A585" s="1"/>
       <c r="B585" s="1"/>
       <c r="C585" s="1"/>
@@ -19279,7 +19351,7 @@
       <c r="AB585" s="1"/>
       <c r="AC585" s="1"/>
     </row>
-    <row r="586" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:29" ht="13.2">
       <c r="A586" s="1"/>
       <c r="B586" s="1"/>
       <c r="C586" s="1"/>
@@ -19310,7 +19382,7 @@
       <c r="AB586" s="1"/>
       <c r="AC586" s="1"/>
     </row>
-    <row r="587" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:29" ht="13.2">
       <c r="A587" s="1"/>
       <c r="B587" s="1"/>
       <c r="C587" s="1"/>
@@ -19341,7 +19413,7 @@
       <c r="AB587" s="1"/>
       <c r="AC587" s="1"/>
     </row>
-    <row r="588" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:29" ht="13.2">
       <c r="A588" s="1"/>
       <c r="B588" s="1"/>
       <c r="C588" s="1"/>
@@ -19372,7 +19444,7 @@
       <c r="AB588" s="1"/>
       <c r="AC588" s="1"/>
     </row>
-    <row r="589" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:29" ht="13.2">
       <c r="A589" s="1"/>
       <c r="B589" s="1"/>
       <c r="C589" s="1"/>
@@ -19403,7 +19475,7 @@
       <c r="AB589" s="1"/>
       <c r="AC589" s="1"/>
     </row>
-    <row r="590" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:29" ht="13.2">
       <c r="A590" s="1"/>
       <c r="B590" s="1"/>
       <c r="C590" s="1"/>
@@ -19434,7 +19506,7 @@
       <c r="AB590" s="1"/>
       <c r="AC590" s="1"/>
     </row>
-    <row r="591" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:29" ht="13.2">
       <c r="A591" s="1"/>
       <c r="B591" s="1"/>
       <c r="C591" s="1"/>
@@ -19465,7 +19537,7 @@
       <c r="AB591" s="1"/>
       <c r="AC591" s="1"/>
     </row>
-    <row r="592" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:29" ht="13.2">
       <c r="A592" s="1"/>
       <c r="B592" s="1"/>
       <c r="C592" s="1"/>
@@ -19496,7 +19568,7 @@
       <c r="AB592" s="1"/>
       <c r="AC592" s="1"/>
     </row>
-    <row r="593" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:29" ht="13.2">
       <c r="A593" s="1"/>
       <c r="B593" s="1"/>
       <c r="C593" s="1"/>
@@ -19527,7 +19599,7 @@
       <c r="AB593" s="1"/>
       <c r="AC593" s="1"/>
     </row>
-    <row r="594" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:29" ht="13.2">
       <c r="A594" s="1"/>
       <c r="B594" s="1"/>
       <c r="C594" s="1"/>
@@ -19558,7 +19630,7 @@
       <c r="AB594" s="1"/>
       <c r="AC594" s="1"/>
     </row>
-    <row r="595" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:29" ht="13.2">
       <c r="A595" s="1"/>
       <c r="B595" s="1"/>
       <c r="C595" s="1"/>
@@ -19589,7 +19661,7 @@
       <c r="AB595" s="1"/>
       <c r="AC595" s="1"/>
     </row>
-    <row r="596" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:29" ht="13.2">
       <c r="A596" s="1"/>
       <c r="B596" s="1"/>
       <c r="C596" s="1"/>
@@ -19620,7 +19692,7 @@
       <c r="AB596" s="1"/>
       <c r="AC596" s="1"/>
     </row>
-    <row r="597" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:29" ht="13.2">
       <c r="A597" s="1"/>
       <c r="B597" s="1"/>
       <c r="C597" s="1"/>
@@ -19651,7 +19723,7 @@
       <c r="AB597" s="1"/>
       <c r="AC597" s="1"/>
     </row>
-    <row r="598" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:29" ht="13.2">
       <c r="A598" s="1"/>
       <c r="B598" s="1"/>
       <c r="C598" s="1"/>
@@ -19682,7 +19754,7 @@
       <c r="AB598" s="1"/>
       <c r="AC598" s="1"/>
     </row>
-    <row r="599" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:29" ht="13.2">
       <c r="A599" s="1"/>
       <c r="B599" s="1"/>
       <c r="C599" s="1"/>
@@ -19713,7 +19785,7 @@
       <c r="AB599" s="1"/>
       <c r="AC599" s="1"/>
     </row>
-    <row r="600" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:29" ht="13.2">
       <c r="A600" s="1"/>
       <c r="B600" s="1"/>
       <c r="C600" s="1"/>
@@ -19744,7 +19816,7 @@
       <c r="AB600" s="1"/>
       <c r="AC600" s="1"/>
     </row>
-    <row r="601" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:29" ht="13.2">
       <c r="A601" s="1"/>
       <c r="B601" s="1"/>
       <c r="C601" s="1"/>
@@ -19775,7 +19847,7 @@
       <c r="AB601" s="1"/>
       <c r="AC601" s="1"/>
     </row>
-    <row r="602" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:29" ht="13.2">
       <c r="A602" s="1"/>
       <c r="B602" s="1"/>
       <c r="C602" s="1"/>
@@ -19806,7 +19878,7 @@
       <c r="AB602" s="1"/>
       <c r="AC602" s="1"/>
     </row>
-    <row r="603" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:29" ht="13.2">
       <c r="A603" s="1"/>
       <c r="B603" s="1"/>
       <c r="C603" s="1"/>
@@ -19837,7 +19909,7 @@
       <c r="AB603" s="1"/>
       <c r="AC603" s="1"/>
     </row>
-    <row r="604" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:29" ht="13.2">
       <c r="A604" s="1"/>
       <c r="B604" s="1"/>
       <c r="C604" s="1"/>
@@ -19868,7 +19940,7 @@
       <c r="AB604" s="1"/>
       <c r="AC604" s="1"/>
     </row>
-    <row r="605" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:29" ht="13.2">
       <c r="A605" s="1"/>
       <c r="B605" s="1"/>
       <c r="C605" s="1"/>
@@ -19899,7 +19971,7 @@
       <c r="AB605" s="1"/>
       <c r="AC605" s="1"/>
     </row>
-    <row r="606" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:29" ht="13.2">
       <c r="A606" s="1"/>
       <c r="B606" s="1"/>
       <c r="C606" s="1"/>
@@ -19930,7 +20002,7 @@
       <c r="AB606" s="1"/>
       <c r="AC606" s="1"/>
     </row>
-    <row r="607" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:29" ht="13.2">
       <c r="A607" s="1"/>
       <c r="B607" s="1"/>
       <c r="C607" s="1"/>
@@ -19961,7 +20033,7 @@
       <c r="AB607" s="1"/>
       <c r="AC607" s="1"/>
     </row>
-    <row r="608" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:29" ht="13.2">
       <c r="A608" s="1"/>
       <c r="B608" s="1"/>
       <c r="C608" s="1"/>
@@ -19992,7 +20064,7 @@
       <c r="AB608" s="1"/>
       <c r="AC608" s="1"/>
     </row>
-    <row r="609" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:29" ht="13.2">
       <c r="A609" s="1"/>
       <c r="B609" s="1"/>
       <c r="C609" s="1"/>
@@ -20023,7 +20095,7 @@
       <c r="AB609" s="1"/>
       <c r="AC609" s="1"/>
     </row>
-    <row r="610" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:29" ht="13.2">
       <c r="A610" s="1"/>
       <c r="B610" s="1"/>
       <c r="C610" s="1"/>
@@ -20054,7 +20126,7 @@
       <c r="AB610" s="1"/>
       <c r="AC610" s="1"/>
     </row>
-    <row r="611" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:29" ht="13.2">
       <c r="A611" s="1"/>
       <c r="B611" s="1"/>
       <c r="C611" s="1"/>
@@ -20085,7 +20157,7 @@
       <c r="AB611" s="1"/>
       <c r="AC611" s="1"/>
     </row>
-    <row r="612" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:29" ht="13.2">
       <c r="A612" s="1"/>
       <c r="B612" s="1"/>
       <c r="C612" s="1"/>
@@ -20116,7 +20188,7 @@
       <c r="AB612" s="1"/>
       <c r="AC612" s="1"/>
     </row>
-    <row r="613" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:29" ht="13.2">
       <c r="A613" s="1"/>
       <c r="B613" s="1"/>
       <c r="C613" s="1"/>
@@ -20147,7 +20219,7 @@
       <c r="AB613" s="1"/>
       <c r="AC613" s="1"/>
     </row>
-    <row r="614" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:29" ht="13.2">
       <c r="A614" s="1"/>
       <c r="B614" s="1"/>
       <c r="C614" s="1"/>
@@ -20178,7 +20250,7 @@
       <c r="AB614" s="1"/>
       <c r="AC614" s="1"/>
     </row>
-    <row r="615" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:29" ht="13.2">
       <c r="A615" s="1"/>
       <c r="B615" s="1"/>
       <c r="C615" s="1"/>
@@ -20209,7 +20281,7 @@
       <c r="AB615" s="1"/>
       <c r="AC615" s="1"/>
     </row>
-    <row r="616" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:29" ht="13.2">
       <c r="A616" s="1"/>
       <c r="B616" s="1"/>
       <c r="C616" s="1"/>
@@ -20240,7 +20312,7 @@
       <c r="AB616" s="1"/>
       <c r="AC616" s="1"/>
     </row>
-    <row r="617" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:29" ht="13.2">
       <c r="A617" s="1"/>
       <c r="B617" s="1"/>
       <c r="C617" s="1"/>
@@ -20271,7 +20343,7 @@
       <c r="AB617" s="1"/>
       <c r="AC617" s="1"/>
     </row>
-    <row r="618" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:29" ht="13.2">
       <c r="A618" s="1"/>
       <c r="B618" s="1"/>
       <c r="C618" s="1"/>
@@ -20302,7 +20374,7 @@
       <c r="AB618" s="1"/>
       <c r="AC618" s="1"/>
     </row>
-    <row r="619" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:29" ht="13.2">
       <c r="A619" s="1"/>
       <c r="B619" s="1"/>
       <c r="C619" s="1"/>
@@ -20333,7 +20405,7 @@
       <c r="AB619" s="1"/>
       <c r="AC619" s="1"/>
     </row>
-    <row r="620" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:29" ht="13.2">
       <c r="A620" s="1"/>
       <c r="B620" s="1"/>
       <c r="C620" s="1"/>
@@ -20364,7 +20436,7 @@
       <c r="AB620" s="1"/>
       <c r="AC620" s="1"/>
     </row>
-    <row r="621" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:29" ht="13.2">
       <c r="A621" s="1"/>
       <c r="B621" s="1"/>
       <c r="C621" s="1"/>
@@ -20395,7 +20467,7 @@
       <c r="AB621" s="1"/>
       <c r="AC621" s="1"/>
     </row>
-    <row r="622" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:29" ht="13.2">
       <c r="A622" s="1"/>
       <c r="B622" s="1"/>
       <c r="C622" s="1"/>
@@ -20426,7 +20498,7 @@
       <c r="AB622" s="1"/>
       <c r="AC622" s="1"/>
     </row>
-    <row r="623" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:29" ht="13.2">
       <c r="A623" s="1"/>
       <c r="B623" s="1"/>
       <c r="C623" s="1"/>
@@ -20457,7 +20529,7 @@
       <c r="AB623" s="1"/>
       <c r="AC623" s="1"/>
     </row>
-    <row r="624" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:29" ht="13.2">
       <c r="A624" s="1"/>
       <c r="B624" s="1"/>
       <c r="C624" s="1"/>
@@ -20488,7 +20560,7 @@
       <c r="AB624" s="1"/>
       <c r="AC624" s="1"/>
     </row>
-    <row r="625" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:29" ht="13.2">
       <c r="A625" s="1"/>
       <c r="B625" s="1"/>
       <c r="C625" s="1"/>
@@ -20519,7 +20591,7 @@
       <c r="AB625" s="1"/>
       <c r="AC625" s="1"/>
     </row>
-    <row r="626" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:29" ht="13.2">
       <c r="A626" s="1"/>
       <c r="B626" s="1"/>
       <c r="C626" s="1"/>
@@ -20550,7 +20622,7 @@
       <c r="AB626" s="1"/>
       <c r="AC626" s="1"/>
     </row>
-    <row r="627" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:29" ht="13.2">
       <c r="A627" s="1"/>
       <c r="B627" s="1"/>
       <c r="C627" s="1"/>
@@ -20581,7 +20653,7 @@
       <c r="AB627" s="1"/>
       <c r="AC627" s="1"/>
     </row>
-    <row r="628" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:29" ht="13.2">
       <c r="A628" s="1"/>
       <c r="B628" s="1"/>
       <c r="C628" s="1"/>
@@ -20612,7 +20684,7 @@
       <c r="AB628" s="1"/>
       <c r="AC628" s="1"/>
     </row>
-    <row r="629" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:29" ht="13.2">
       <c r="A629" s="1"/>
       <c r="B629" s="1"/>
       <c r="C629" s="1"/>
@@ -20643,7 +20715,7 @@
       <c r="AB629" s="1"/>
       <c r="AC629" s="1"/>
     </row>
-    <row r="630" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:29" ht="13.2">
       <c r="A630" s="1"/>
       <c r="B630" s="1"/>
       <c r="C630" s="1"/>
@@ -20674,7 +20746,7 @@
       <c r="AB630" s="1"/>
       <c r="AC630" s="1"/>
     </row>
-    <row r="631" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:29" ht="13.2">
       <c r="A631" s="1"/>
       <c r="B631" s="1"/>
       <c r="C631" s="1"/>
@@ -20705,7 +20777,7 @@
       <c r="AB631" s="1"/>
       <c r="AC631" s="1"/>
     </row>
-    <row r="632" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:29" ht="13.2">
       <c r="A632" s="1"/>
       <c r="B632" s="1"/>
       <c r="C632" s="1"/>
@@ -20736,7 +20808,7 @@
       <c r="AB632" s="1"/>
       <c r="AC632" s="1"/>
     </row>
-    <row r="633" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:29" ht="13.2">
       <c r="A633" s="1"/>
       <c r="B633" s="1"/>
       <c r="C633" s="1"/>
@@ -20767,7 +20839,7 @@
       <c r="AB633" s="1"/>
       <c r="AC633" s="1"/>
     </row>
-    <row r="634" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:29" ht="13.2">
       <c r="A634" s="1"/>
       <c r="B634" s="1"/>
       <c r="C634" s="1"/>
@@ -20798,7 +20870,7 @@
       <c r="AB634" s="1"/>
       <c r="AC634" s="1"/>
     </row>
-    <row r="635" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:29" ht="13.2">
       <c r="A635" s="1"/>
       <c r="B635" s="1"/>
       <c r="C635" s="1"/>
@@ -20829,7 +20901,7 @@
       <c r="AB635" s="1"/>
       <c r="AC635" s="1"/>
     </row>
-    <row r="636" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:29" ht="13.2">
       <c r="A636" s="1"/>
       <c r="B636" s="1"/>
       <c r="C636" s="1"/>
@@ -20860,7 +20932,7 @@
       <c r="AB636" s="1"/>
       <c r="AC636" s="1"/>
     </row>
-    <row r="637" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:29" ht="13.2">
       <c r="A637" s="1"/>
       <c r="B637" s="1"/>
       <c r="C637" s="1"/>
@@ -20891,7 +20963,7 @@
       <c r="AB637" s="1"/>
       <c r="AC637" s="1"/>
     </row>
-    <row r="638" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:29" ht="13.2">
       <c r="A638" s="1"/>
       <c r="B638" s="1"/>
       <c r="C638" s="1"/>
@@ -20922,7 +20994,7 @@
       <c r="AB638" s="1"/>
       <c r="AC638" s="1"/>
     </row>
-    <row r="639" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:29" ht="13.2">
       <c r="A639" s="1"/>
       <c r="B639" s="1"/>
       <c r="C639" s="1"/>
@@ -20953,7 +21025,7 @@
       <c r="AB639" s="1"/>
       <c r="AC639" s="1"/>
     </row>
-    <row r="640" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:29" ht="13.2">
       <c r="A640" s="1"/>
       <c r="B640" s="1"/>
       <c r="C640" s="1"/>
@@ -20984,7 +21056,7 @@
       <c r="AB640" s="1"/>
       <c r="AC640" s="1"/>
     </row>
-    <row r="641" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:29" ht="13.2">
       <c r="A641" s="1"/>
       <c r="B641" s="1"/>
       <c r="C641" s="1"/>
@@ -21015,7 +21087,7 @@
       <c r="AB641" s="1"/>
       <c r="AC641" s="1"/>
     </row>
-    <row r="642" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:29" ht="13.2">
       <c r="A642" s="1"/>
       <c r="B642" s="1"/>
       <c r="C642" s="1"/>
@@ -21046,7 +21118,7 @@
       <c r="AB642" s="1"/>
       <c r="AC642" s="1"/>
     </row>
-    <row r="643" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:29" ht="13.2">
       <c r="A643" s="1"/>
       <c r="B643" s="1"/>
       <c r="C643" s="1"/>
@@ -21077,7 +21149,7 @@
       <c r="AB643" s="1"/>
       <c r="AC643" s="1"/>
     </row>
-    <row r="644" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:29" ht="13.2">
       <c r="A644" s="1"/>
       <c r="B644" s="1"/>
       <c r="C644" s="1"/>
@@ -21108,7 +21180,7 @@
       <c r="AB644" s="1"/>
       <c r="AC644" s="1"/>
     </row>
-    <row r="645" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:29" ht="13.2">
       <c r="A645" s="1"/>
       <c r="B645" s="1"/>
       <c r="C645" s="1"/>
@@ -21139,7 +21211,7 @@
       <c r="AB645" s="1"/>
       <c r="AC645" s="1"/>
     </row>
-    <row r="646" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:29" ht="13.2">
       <c r="A646" s="1"/>
       <c r="B646" s="1"/>
       <c r="C646" s="1"/>
@@ -21170,7 +21242,7 @@
       <c r="AB646" s="1"/>
       <c r="AC646" s="1"/>
     </row>
-    <row r="647" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:29" ht="13.2">
       <c r="A647" s="1"/>
       <c r="B647" s="1"/>
       <c r="C647" s="1"/>
@@ -21201,7 +21273,7 @@
       <c r="AB647" s="1"/>
       <c r="AC647" s="1"/>
     </row>
-    <row r="648" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:29" ht="13.2">
       <c r="A648" s="1"/>
       <c r="B648" s="1"/>
       <c r="C648" s="1"/>
@@ -21232,7 +21304,7 @@
       <c r="AB648" s="1"/>
       <c r="AC648" s="1"/>
     </row>
-    <row r="649" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:29" ht="13.2">
       <c r="A649" s="1"/>
       <c r="B649" s="1"/>
       <c r="C649" s="1"/>
@@ -21263,7 +21335,7 @@
       <c r="AB649" s="1"/>
       <c r="AC649" s="1"/>
     </row>
-    <row r="650" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:29" ht="13.2">
       <c r="A650" s="1"/>
       <c r="B650" s="1"/>
       <c r="C650" s="1"/>
@@ -21294,7 +21366,7 @@
       <c r="AB650" s="1"/>
       <c r="AC650" s="1"/>
     </row>
-    <row r="651" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:29" ht="13.2">
       <c r="A651" s="1"/>
       <c r="B651" s="1"/>
       <c r="C651" s="1"/>
@@ -21325,7 +21397,7 @@
       <c r="AB651" s="1"/>
       <c r="AC651" s="1"/>
     </row>
-    <row r="652" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:29" ht="13.2">
       <c r="A652" s="1"/>
       <c r="B652" s="1"/>
       <c r="C652" s="1"/>
@@ -21356,7 +21428,7 @@
       <c r="AB652" s="1"/>
       <c r="AC652" s="1"/>
     </row>
-    <row r="653" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:29" ht="13.2">
       <c r="A653" s="1"/>
       <c r="B653" s="1"/>
       <c r="C653" s="1"/>
@@ -21387,7 +21459,7 @@
       <c r="AB653" s="1"/>
       <c r="AC653" s="1"/>
     </row>
-    <row r="654" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:29" ht="13.2">
       <c r="A654" s="1"/>
       <c r="B654" s="1"/>
       <c r="C654" s="1"/>
@@ -21418,7 +21490,7 @@
       <c r="AB654" s="1"/>
       <c r="AC654" s="1"/>
     </row>
-    <row r="655" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:29" ht="13.2">
       <c r="A655" s="1"/>
       <c r="B655" s="1"/>
       <c r="C655" s="1"/>
@@ -21449,7 +21521,7 @@
       <c r="AB655" s="1"/>
       <c r="AC655" s="1"/>
     </row>
-    <row r="656" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:29" ht="13.2">
       <c r="A656" s="1"/>
       <c r="B656" s="1"/>
       <c r="C656" s="1"/>
@@ -21480,7 +21552,7 @@
       <c r="AB656" s="1"/>
       <c r="AC656" s="1"/>
     </row>
-    <row r="657" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:29" ht="13.2">
       <c r="A657" s="1"/>
       <c r="B657" s="1"/>
       <c r="C657" s="1"/>
@@ -21511,7 +21583,7 @@
       <c r="AB657" s="1"/>
       <c r="AC657" s="1"/>
     </row>
-    <row r="658" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:29" ht="13.2">
       <c r="A658" s="1"/>
       <c r="B658" s="1"/>
       <c r="C658" s="1"/>
@@ -21542,7 +21614,7 @@
       <c r="AB658" s="1"/>
       <c r="AC658" s="1"/>
     </row>
-    <row r="659" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:29" ht="13.2">
       <c r="A659" s="1"/>
       <c r="B659" s="1"/>
       <c r="C659" s="1"/>
@@ -21573,7 +21645,7 @@
       <c r="AB659" s="1"/>
       <c r="AC659" s="1"/>
     </row>
-    <row r="660" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:29" ht="13.2">
       <c r="A660" s="1"/>
       <c r="B660" s="1"/>
       <c r="C660" s="1"/>
@@ -21604,7 +21676,7 @@
       <c r="AB660" s="1"/>
       <c r="AC660" s="1"/>
     </row>
-    <row r="661" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:29" ht="13.2">
       <c r="A661" s="1"/>
       <c r="B661" s="1"/>
       <c r="C661" s="1"/>
@@ -21635,7 +21707,7 @@
       <c r="AB661" s="1"/>
       <c r="AC661" s="1"/>
     </row>
-    <row r="662" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:29" ht="13.2">
       <c r="A662" s="1"/>
       <c r="B662" s="1"/>
       <c r="C662" s="1"/>
@@ -21666,7 +21738,7 @@
       <c r="AB662" s="1"/>
       <c r="AC662" s="1"/>
     </row>
-    <row r="663" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:29" ht="13.2">
       <c r="A663" s="1"/>
       <c r="B663" s="1"/>
       <c r="C663" s="1"/>
@@ -21697,7 +21769,7 @@
       <c r="AB663" s="1"/>
       <c r="AC663" s="1"/>
     </row>
-    <row r="664" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:29" ht="13.2">
       <c r="A664" s="1"/>
       <c r="B664" s="1"/>
       <c r="C664" s="1"/>
@@ -21728,7 +21800,7 @@
       <c r="AB664" s="1"/>
       <c r="AC664" s="1"/>
     </row>
-    <row r="665" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:29" ht="13.2">
       <c r="A665" s="1"/>
       <c r="B665" s="1"/>
       <c r="C665" s="1"/>
@@ -21759,7 +21831,7 @@
       <c r="AB665" s="1"/>
       <c r="AC665" s="1"/>
     </row>
-    <row r="666" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:29" ht="13.2">
       <c r="A666" s="1"/>
       <c r="B666" s="1"/>
       <c r="C666" s="1"/>
@@ -21790,7 +21862,7 @@
       <c r="AB666" s="1"/>
       <c r="AC666" s="1"/>
     </row>
-    <row r="667" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:29" ht="13.2">
       <c r="A667" s="1"/>
       <c r="B667" s="1"/>
       <c r="C667" s="1"/>
@@ -21821,7 +21893,7 @@
       <c r="AB667" s="1"/>
       <c r="AC667" s="1"/>
     </row>
-    <row r="668" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:29" ht="13.2">
       <c r="A668" s="1"/>
       <c r="B668" s="1"/>
       <c r="C668" s="1"/>
@@ -21852,7 +21924,7 @@
       <c r="AB668" s="1"/>
       <c r="AC668" s="1"/>
     </row>
-    <row r="669" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:29" ht="13.2">
       <c r="A669" s="1"/>
       <c r="B669" s="1"/>
       <c r="C669" s="1"/>
@@ -21883,7 +21955,7 @@
       <c r="AB669" s="1"/>
       <c r="AC669" s="1"/>
     </row>
-    <row r="670" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:29" ht="13.2">
       <c r="A670" s="1"/>
       <c r="B670" s="1"/>
       <c r="C670" s="1"/>
@@ -21914,7 +21986,7 @@
       <c r="AB670" s="1"/>
       <c r="AC670" s="1"/>
     </row>
-    <row r="671" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:29" ht="13.2">
       <c r="A671" s="1"/>
       <c r="B671" s="1"/>
       <c r="C671" s="1"/>
@@ -21945,7 +22017,7 @@
       <c r="AB671" s="1"/>
       <c r="AC671" s="1"/>
     </row>
-    <row r="672" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:29" ht="13.2">
       <c r="A672" s="1"/>
       <c r="B672" s="1"/>
       <c r="C672" s="1"/>
@@ -21976,7 +22048,7 @@
       <c r="AB672" s="1"/>
       <c r="AC672" s="1"/>
     </row>
-    <row r="673" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:29" ht="13.2">
       <c r="A673" s="1"/>
       <c r="B673" s="1"/>
       <c r="C673" s="1"/>
@@ -22007,7 +22079,7 @@
       <c r="AB673" s="1"/>
       <c r="AC673" s="1"/>
     </row>
-    <row r="674" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:29" ht="13.2">
       <c r="A674" s="1"/>
       <c r="B674" s="1"/>
       <c r="C674" s="1"/>
@@ -22038,7 +22110,7 @@
       <c r="AB674" s="1"/>
       <c r="AC674" s="1"/>
     </row>
-    <row r="675" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:29" ht="13.2">
       <c r="A675" s="1"/>
       <c r="B675" s="1"/>
       <c r="C675" s="1"/>
@@ -22069,7 +22141,7 @@
       <c r="AB675" s="1"/>
       <c r="AC675" s="1"/>
     </row>
-    <row r="676" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:29" ht="13.2">
       <c r="A676" s="1"/>
       <c r="B676" s="1"/>
       <c r="C676" s="1"/>
@@ -22100,7 +22172,7 @@
       <c r="AB676" s="1"/>
       <c r="AC676" s="1"/>
     </row>
-    <row r="677" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:29" ht="13.2">
       <c r="A677" s="1"/>
       <c r="B677" s="1"/>
       <c r="C677" s="1"/>
@@ -22131,7 +22203,7 @@
       <c r="AB677" s="1"/>
       <c r="AC677" s="1"/>
     </row>
-    <row r="678" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:29" ht="13.2">
       <c r="A678" s="1"/>
       <c r="B678" s="1"/>
       <c r="C678" s="1"/>
@@ -22162,7 +22234,7 @@
       <c r="AB678" s="1"/>
       <c r="AC678" s="1"/>
     </row>
-    <row r="679" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:29" ht="13.2">
       <c r="A679" s="1"/>
       <c r="B679" s="1"/>
       <c r="C679" s="1"/>
@@ -22193,7 +22265,7 @@
       <c r="AB679" s="1"/>
       <c r="AC679" s="1"/>
     </row>
-    <row r="680" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:29" ht="13.2">
       <c r="A680" s="1"/>
       <c r="B680" s="1"/>
       <c r="C680" s="1"/>
@@ -22224,7 +22296,7 @@
       <c r="AB680" s="1"/>
       <c r="AC680" s="1"/>
     </row>
-    <row r="681" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:29" ht="13.2">
       <c r="A681" s="1"/>
       <c r="B681" s="1"/>
       <c r="C681" s="1"/>
@@ -22255,7 +22327,7 @@
       <c r="AB681" s="1"/>
       <c r="AC681" s="1"/>
     </row>
-    <row r="682" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:29" ht="13.2">
       <c r="A682" s="1"/>
       <c r="B682" s="1"/>
       <c r="C682" s="1"/>
@@ -22286,7 +22358,7 @@
       <c r="AB682" s="1"/>
       <c r="AC682" s="1"/>
     </row>
-    <row r="683" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="683" spans="1:29" ht="13.2">
       <c r="A683" s="1"/>
       <c r="B683" s="1"/>
       <c r="C683" s="1"/>
@@ -22317,7 +22389,7 @@
       <c r="AB683" s="1"/>
       <c r="AC683" s="1"/>
     </row>
-    <row r="684" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:29" ht="13.2">
       <c r="A684" s="1"/>
       <c r="B684" s="1"/>
       <c r="C684" s="1"/>
@@ -22348,7 +22420,7 @@
       <c r="AB684" s="1"/>
       <c r="AC684" s="1"/>
     </row>
-    <row r="685" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:29" ht="13.2">
       <c r="A685" s="1"/>
       <c r="B685" s="1"/>
       <c r="C685" s="1"/>
@@ -22379,7 +22451,7 @@
       <c r="AB685" s="1"/>
       <c r="AC685" s="1"/>
     </row>
-    <row r="686" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:29" ht="13.2">
       <c r="A686" s="1"/>
       <c r="B686" s="1"/>
       <c r="C686" s="1"/>
@@ -22410,7 +22482,7 @@
       <c r="AB686" s="1"/>
       <c r="AC686" s="1"/>
     </row>
-    <row r="687" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="687" spans="1:29" ht="13.2">
       <c r="A687" s="1"/>
       <c r="B687" s="1"/>
       <c r="C687" s="1"/>
@@ -22441,7 +22513,7 @@
       <c r="AB687" s="1"/>
       <c r="AC687" s="1"/>
     </row>
-    <row r="688" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="688" spans="1:29" ht="13.2">
       <c r="A688" s="1"/>
       <c r="B688" s="1"/>
       <c r="C688" s="1"/>
@@ -22472,7 +22544,7 @@
       <c r="AB688" s="1"/>
       <c r="AC688" s="1"/>
     </row>
-    <row r="689" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:29" ht="13.2">
       <c r="A689" s="1"/>
       <c r="B689" s="1"/>
       <c r="C689" s="1"/>
@@ -22503,7 +22575,7 @@
       <c r="AB689" s="1"/>
       <c r="AC689" s="1"/>
     </row>
-    <row r="690" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:29" ht="13.2">
       <c r="A690" s="1"/>
       <c r="B690" s="1"/>
       <c r="C690" s="1"/>
@@ -22534,7 +22606,7 @@
       <c r="AB690" s="1"/>
       <c r="AC690" s="1"/>
     </row>
-    <row r="691" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="691" spans="1:29" ht="13.2">
       <c r="A691" s="1"/>
       <c r="B691" s="1"/>
       <c r="C691" s="1"/>
@@ -22565,7 +22637,7 @@
       <c r="AB691" s="1"/>
       <c r="AC691" s="1"/>
     </row>
-    <row r="692" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="692" spans="1:29" ht="13.2">
       <c r="A692" s="1"/>
       <c r="B692" s="1"/>
       <c r="C692" s="1"/>
@@ -22596,7 +22668,7 @@
       <c r="AB692" s="1"/>
       <c r="AC692" s="1"/>
     </row>
-    <row r="693" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="693" spans="1:29" ht="13.2">
       <c r="A693" s="1"/>
       <c r="B693" s="1"/>
       <c r="C693" s="1"/>
@@ -22627,7 +22699,7 @@
       <c r="AB693" s="1"/>
       <c r="AC693" s="1"/>
     </row>
-    <row r="694" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="694" spans="1:29" ht="13.2">
       <c r="A694" s="1"/>
       <c r="B694" s="1"/>
       <c r="C694" s="1"/>
@@ -22658,7 +22730,7 @@
       <c r="AB694" s="1"/>
       <c r="AC694" s="1"/>
     </row>
-    <row r="695" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="695" spans="1:29" ht="13.2">
       <c r="A695" s="1"/>
       <c r="B695" s="1"/>
       <c r="C695" s="1"/>
@@ -22689,7 +22761,7 @@
       <c r="AB695" s="1"/>
       <c r="AC695" s="1"/>
     </row>
-    <row r="696" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="696" spans="1:29" ht="13.2">
       <c r="A696" s="1"/>
       <c r="B696" s="1"/>
       <c r="C696" s="1"/>
@@ -22720,7 +22792,7 @@
       <c r="AB696" s="1"/>
       <c r="AC696" s="1"/>
     </row>
-    <row r="697" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="697" spans="1:29" ht="13.2">
       <c r="A697" s="1"/>
       <c r="B697" s="1"/>
       <c r="C697" s="1"/>
@@ -22751,7 +22823,7 @@
       <c r="AB697" s="1"/>
       <c r="AC697" s="1"/>
     </row>
-    <row r="698" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="698" spans="1:29" ht="13.2">
       <c r="A698" s="1"/>
       <c r="B698" s="1"/>
       <c r="C698" s="1"/>
@@ -22782,7 +22854,7 @@
       <c r="AB698" s="1"/>
       <c r="AC698" s="1"/>
     </row>
-    <row r="699" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="699" spans="1:29" ht="13.2">
       <c r="A699" s="1"/>
       <c r="B699" s="1"/>
       <c r="C699" s="1"/>
@@ -22813,7 +22885,7 @@
       <c r="AB699" s="1"/>
       <c r="AC699" s="1"/>
     </row>
-    <row r="700" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="700" spans="1:29" ht="13.2">
       <c r="A700" s="1"/>
       <c r="B700" s="1"/>
       <c r="C700" s="1"/>
@@ -22844,7 +22916,7 @@
       <c r="AB700" s="1"/>
       <c r="AC700" s="1"/>
     </row>
-    <row r="701" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="701" spans="1:29" ht="13.2">
       <c r="A701" s="1"/>
       <c r="B701" s="1"/>
       <c r="C701" s="1"/>
@@ -22875,7 +22947,7 @@
       <c r="AB701" s="1"/>
       <c r="AC701" s="1"/>
     </row>
-    <row r="702" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="702" spans="1:29" ht="13.2">
       <c r="A702" s="1"/>
       <c r="B702" s="1"/>
       <c r="C702" s="1"/>
@@ -22906,7 +22978,7 @@
       <c r="AB702" s="1"/>
       <c r="AC702" s="1"/>
     </row>
-    <row r="703" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="703" spans="1:29" ht="13.2">
       <c r="A703" s="1"/>
       <c r="B703" s="1"/>
       <c r="C703" s="1"/>
@@ -22937,7 +23009,7 @@
       <c r="AB703" s="1"/>
       <c r="AC703" s="1"/>
     </row>
-    <row r="704" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="704" spans="1:29" ht="13.2">
       <c r="A704" s="1"/>
       <c r="B704" s="1"/>
       <c r="C704" s="1"/>
@@ -22968,7 +23040,7 @@
       <c r="AB704" s="1"/>
       <c r="AC704" s="1"/>
     </row>
-    <row r="705" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:29" ht="13.2">
       <c r="A705" s="1"/>
       <c r="B705" s="1"/>
       <c r="C705" s="1"/>
@@ -22999,7 +23071,7 @@
       <c r="AB705" s="1"/>
       <c r="AC705" s="1"/>
     </row>
-    <row r="706" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:29" ht="13.2">
       <c r="A706" s="1"/>
       <c r="B706" s="1"/>
       <c r="C706" s="1"/>
@@ -23030,7 +23102,7 @@
       <c r="AB706" s="1"/>
       <c r="AC706" s="1"/>
     </row>
-    <row r="707" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:29" ht="13.2">
       <c r="A707" s="1"/>
       <c r="B707" s="1"/>
       <c r="C707" s="1"/>
@@ -23061,7 +23133,7 @@
       <c r="AB707" s="1"/>
       <c r="AC707" s="1"/>
     </row>
-    <row r="708" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="708" spans="1:29" ht="13.2">
       <c r="A708" s="1"/>
       <c r="B708" s="1"/>
       <c r="C708" s="1"/>
@@ -23092,7 +23164,7 @@
       <c r="AB708" s="1"/>
       <c r="AC708" s="1"/>
     </row>
-    <row r="709" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="709" spans="1:29" ht="13.2">
       <c r="A709" s="1"/>
       <c r="B709" s="1"/>
       <c r="C709" s="1"/>
@@ -23123,7 +23195,7 @@
       <c r="AB709" s="1"/>
       <c r="AC709" s="1"/>
     </row>
-    <row r="710" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="710" spans="1:29" ht="13.2">
       <c r="A710" s="1"/>
       <c r="B710" s="1"/>
       <c r="C710" s="1"/>
@@ -23154,7 +23226,7 @@
       <c r="AB710" s="1"/>
       <c r="AC710" s="1"/>
     </row>
-    <row r="711" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="711" spans="1:29" ht="13.2">
       <c r="A711" s="1"/>
       <c r="B711" s="1"/>
       <c r="C711" s="1"/>
@@ -23185,7 +23257,7 @@
       <c r="AB711" s="1"/>
       <c r="AC711" s="1"/>
     </row>
-    <row r="712" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:29" ht="13.2">
       <c r="A712" s="1"/>
       <c r="B712" s="1"/>
       <c r="C712" s="1"/>
@@ -23216,7 +23288,7 @@
       <c r="AB712" s="1"/>
       <c r="AC712" s="1"/>
     </row>
-    <row r="713" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="713" spans="1:29" ht="13.2">
       <c r="A713" s="1"/>
       <c r="B713" s="1"/>
       <c r="C713" s="1"/>
@@ -23247,7 +23319,7 @@
       <c r="AB713" s="1"/>
       <c r="AC713" s="1"/>
     </row>
-    <row r="714" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="714" spans="1:29" ht="13.2">
       <c r="A714" s="1"/>
       <c r="B714" s="1"/>
       <c r="C714" s="1"/>
@@ -23278,7 +23350,7 @@
       <c r="AB714" s="1"/>
       <c r="AC714" s="1"/>
     </row>
-    <row r="715" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="715" spans="1:29" ht="13.2">
       <c r="A715" s="1"/>
       <c r="B715" s="1"/>
       <c r="C715" s="1"/>
@@ -23309,7 +23381,7 @@
       <c r="AB715" s="1"/>
       <c r="AC715" s="1"/>
     </row>
-    <row r="716" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="716" spans="1:29" ht="13.2">
       <c r="A716" s="1"/>
       <c r="B716" s="1"/>
       <c r="C716" s="1"/>
@@ -23340,7 +23412,7 @@
       <c r="AB716" s="1"/>
       <c r="AC716" s="1"/>
     </row>
-    <row r="717" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="717" spans="1:29" ht="13.2">
       <c r="A717" s="1"/>
       <c r="B717" s="1"/>
       <c r="C717" s="1"/>
@@ -23371,7 +23443,7 @@
       <c r="AB717" s="1"/>
       <c r="AC717" s="1"/>
     </row>
-    <row r="718" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="718" spans="1:29" ht="13.2">
       <c r="A718" s="1"/>
       <c r="B718" s="1"/>
       <c r="C718" s="1"/>
@@ -23402,7 +23474,7 @@
       <c r="AB718" s="1"/>
       <c r="AC718" s="1"/>
     </row>
-    <row r="719" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="719" spans="1:29" ht="13.2">
       <c r="A719" s="1"/>
       <c r="B719" s="1"/>
       <c r="C719" s="1"/>
@@ -23433,7 +23505,7 @@
       <c r="AB719" s="1"/>
       <c r="AC719" s="1"/>
     </row>
-    <row r="720" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="720" spans="1:29" ht="13.2">
       <c r="A720" s="1"/>
       <c r="B720" s="1"/>
       <c r="C720" s="1"/>
@@ -23464,7 +23536,7 @@
       <c r="AB720" s="1"/>
       <c r="AC720" s="1"/>
     </row>
-    <row r="721" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="721" spans="1:29" ht="13.2">
       <c r="A721" s="1"/>
       <c r="B721" s="1"/>
       <c r="C721" s="1"/>
@@ -23495,7 +23567,7 @@
       <c r="AB721" s="1"/>
       <c r="AC721" s="1"/>
     </row>
-    <row r="722" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="722" spans="1:29" ht="13.2">
       <c r="A722" s="1"/>
       <c r="B722" s="1"/>
       <c r="C722" s="1"/>
@@ -23526,7 +23598,7 @@
       <c r="AB722" s="1"/>
       <c r="AC722" s="1"/>
     </row>
-    <row r="723" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="723" spans="1:29" ht="13.2">
       <c r="A723" s="1"/>
       <c r="B723" s="1"/>
       <c r="C723" s="1"/>
@@ -23557,7 +23629,7 @@
       <c r="AB723" s="1"/>
       <c r="AC723" s="1"/>
     </row>
-    <row r="724" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="724" spans="1:29" ht="13.2">
       <c r="A724" s="1"/>
       <c r="B724" s="1"/>
       <c r="C724" s="1"/>
@@ -23588,7 +23660,7 @@
       <c r="AB724" s="1"/>
       <c r="AC724" s="1"/>
     </row>
-    <row r="725" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="725" spans="1:29" ht="13.2">
       <c r="A725" s="1"/>
       <c r="B725" s="1"/>
       <c r="C725" s="1"/>
@@ -23619,7 +23691,7 @@
       <c r="AB725" s="1"/>
       <c r="AC725" s="1"/>
     </row>
-    <row r="726" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="726" spans="1:29" ht="13.2">
       <c r="A726" s="1"/>
       <c r="B726" s="1"/>
       <c r="C726" s="1"/>
@@ -23650,7 +23722,7 @@
       <c r="AB726" s="1"/>
       <c r="AC726" s="1"/>
     </row>
-    <row r="727" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="727" spans="1:29" ht="13.2">
       <c r="A727" s="1"/>
       <c r="B727" s="1"/>
       <c r="C727" s="1"/>
@@ -23681,7 +23753,7 @@
       <c r="AB727" s="1"/>
       <c r="AC727" s="1"/>
     </row>
-    <row r="728" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="728" spans="1:29" ht="13.2">
       <c r="A728" s="1"/>
       <c r="B728" s="1"/>
       <c r="C728" s="1"/>
@@ -23712,7 +23784,7 @@
       <c r="AB728" s="1"/>
       <c r="AC728" s="1"/>
     </row>
-    <row r="729" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="729" spans="1:29" ht="13.2">
       <c r="A729" s="1"/>
       <c r="B729" s="1"/>
       <c r="C729" s="1"/>
@@ -23743,7 +23815,7 @@
       <c r="AB729" s="1"/>
       <c r="AC729" s="1"/>
     </row>
-    <row r="730" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="730" spans="1:29" ht="13.2">
       <c r="A730" s="1"/>
       <c r="B730" s="1"/>
       <c r="C730" s="1"/>
@@ -23774,7 +23846,7 @@
       <c r="AB730" s="1"/>
       <c r="AC730" s="1"/>
     </row>
-    <row r="731" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="731" spans="1:29" ht="13.2">
       <c r="A731" s="1"/>
       <c r="B731" s="1"/>
       <c r="C731" s="1"/>
@@ -23805,7 +23877,7 @@
       <c r="AB731" s="1"/>
       <c r="AC731" s="1"/>
     </row>
-    <row r="732" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="732" spans="1:29" ht="13.2">
       <c r="A732" s="1"/>
       <c r="B732" s="1"/>
       <c r="C732" s="1"/>
@@ -23836,7 +23908,7 @@
       <c r="AB732" s="1"/>
       <c r="AC732" s="1"/>
     </row>
-    <row r="733" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="733" spans="1:29" ht="13.2">
       <c r="A733" s="1"/>
       <c r="B733" s="1"/>
       <c r="C733" s="1"/>
@@ -23867,7 +23939,7 @@
       <c r="AB733" s="1"/>
       <c r="AC733" s="1"/>
     </row>
-    <row r="734" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="734" spans="1:29" ht="13.2">
       <c r="A734" s="1"/>
       <c r="B734" s="1"/>
       <c r="C734" s="1"/>
@@ -23898,7 +23970,7 @@
       <c r="AB734" s="1"/>
       <c r="AC734" s="1"/>
     </row>
-    <row r="735" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="735" spans="1:29" ht="13.2">
       <c r="A735" s="1"/>
       <c r="B735" s="1"/>
       <c r="C735" s="1"/>
@@ -23929,7 +24001,7 @@
       <c r="AB735" s="1"/>
       <c r="AC735" s="1"/>
     </row>
-    <row r="736" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="736" spans="1:29" ht="13.2">
       <c r="A736" s="1"/>
       <c r="B736" s="1"/>
       <c r="C736" s="1"/>
@@ -23960,7 +24032,7 @@
       <c r="AB736" s="1"/>
       <c r="AC736" s="1"/>
     </row>
-    <row r="737" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="737" spans="1:29" ht="13.2">
       <c r="A737" s="1"/>
       <c r="B737" s="1"/>
       <c r="C737" s="1"/>
@@ -23991,7 +24063,7 @@
       <c r="AB737" s="1"/>
       <c r="AC737" s="1"/>
     </row>
-    <row r="738" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="738" spans="1:29" ht="13.2">
       <c r="A738" s="1"/>
       <c r="B738" s="1"/>
       <c r="C738" s="1"/>
@@ -24022,7 +24094,7 @@
       <c r="AB738" s="1"/>
       <c r="AC738" s="1"/>
     </row>
-    <row r="739" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="739" spans="1:29" ht="13.2">
       <c r="A739" s="1"/>
       <c r="B739" s="1"/>
       <c r="C739" s="1"/>
@@ -24053,7 +24125,7 @@
       <c r="AB739" s="1"/>
       <c r="AC739" s="1"/>
     </row>
-    <row r="740" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="740" spans="1:29" ht="13.2">
       <c r="A740" s="1"/>
       <c r="B740" s="1"/>
       <c r="C740" s="1"/>
@@ -24084,7 +24156,7 @@
       <c r="AB740" s="1"/>
       <c r="AC740" s="1"/>
     </row>
-    <row r="741" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="741" spans="1:29" ht="13.2">
       <c r="A741" s="1"/>
       <c r="B741" s="1"/>
       <c r="C741" s="1"/>
@@ -24115,7 +24187,7 @@
       <c r="AB741" s="1"/>
       <c r="AC741" s="1"/>
     </row>
-    <row r="742" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="742" spans="1:29" ht="13.2">
       <c r="A742" s="1"/>
       <c r="B742" s="1"/>
       <c r="C742" s="1"/>
@@ -24146,7 +24218,7 @@
       <c r="AB742" s="1"/>
       <c r="AC742" s="1"/>
     </row>
-    <row r="743" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="743" spans="1:29" ht="13.2">
       <c r="A743" s="1"/>
       <c r="B743" s="1"/>
       <c r="C743" s="1"/>
@@ -24177,7 +24249,7 @@
       <c r="AB743" s="1"/>
       <c r="AC743" s="1"/>
     </row>
-    <row r="744" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="744" spans="1:29" ht="13.2">
       <c r="A744" s="1"/>
       <c r="B744" s="1"/>
       <c r="C744" s="1"/>
@@ -24208,7 +24280,7 @@
       <c r="AB744" s="1"/>
       <c r="AC744" s="1"/>
     </row>
-    <row r="745" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="745" spans="1:29" ht="13.2">
       <c r="A745" s="1"/>
       <c r="B745" s="1"/>
       <c r="C745" s="1"/>
@@ -24239,7 +24311,7 @@
       <c r="AB745" s="1"/>
       <c r="AC745" s="1"/>
     </row>
-    <row r="746" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="746" spans="1:29" ht="13.2">
       <c r="A746" s="1"/>
       <c r="B746" s="1"/>
       <c r="C746" s="1"/>
@@ -24270,7 +24342,7 @@
       <c r="AB746" s="1"/>
       <c r="AC746" s="1"/>
     </row>
-    <row r="747" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="747" spans="1:29" ht="13.2">
       <c r="A747" s="1"/>
       <c r="B747" s="1"/>
       <c r="C747" s="1"/>
@@ -24301,7 +24373,7 @@
       <c r="AB747" s="1"/>
       <c r="AC747" s="1"/>
     </row>
-    <row r="748" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="748" spans="1:29" ht="13.2">
       <c r="A748" s="1"/>
       <c r="B748" s="1"/>
       <c r="C748" s="1"/>
@@ -24332,7 +24404,7 @@
       <c r="AB748" s="1"/>
       <c r="AC748" s="1"/>
     </row>
-    <row r="749" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="749" spans="1:29" ht="13.2">
       <c r="A749" s="1"/>
       <c r="B749" s="1"/>
       <c r="C749" s="1"/>
@@ -24363,7 +24435,7 @@
       <c r="AB749" s="1"/>
       <c r="AC749" s="1"/>
     </row>
-    <row r="750" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="750" spans="1:29" ht="13.2">
       <c r="A750" s="1"/>
       <c r="B750" s="1"/>
       <c r="C750" s="1"/>
@@ -24394,7 +24466,7 @@
       <c r="AB750" s="1"/>
       <c r="AC750" s="1"/>
     </row>
-    <row r="751" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="751" spans="1:29" ht="13.2">
       <c r="A751" s="1"/>
       <c r="B751" s="1"/>
       <c r="C751" s="1"/>
@@ -24425,7 +24497,7 @@
       <c r="AB751" s="1"/>
       <c r="AC751" s="1"/>
     </row>
-    <row r="752" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="752" spans="1:29" ht="13.2">
       <c r="A752" s="1"/>
       <c r="B752" s="1"/>
       <c r="C752" s="1"/>
@@ -24456,7 +24528,7 @@
       <c r="AB752" s="1"/>
       <c r="AC752" s="1"/>
     </row>
-    <row r="753" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="753" spans="1:29" ht="13.2">
       <c r="A753" s="1"/>
       <c r="B753" s="1"/>
       <c r="C753" s="1"/>
@@ -24487,7 +24559,7 @@
       <c r="AB753" s="1"/>
       <c r="AC753" s="1"/>
     </row>
-    <row r="754" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="754" spans="1:29" ht="13.2">
       <c r="A754" s="1"/>
       <c r="B754" s="1"/>
       <c r="C754" s="1"/>
@@ -24518,7 +24590,7 @@
       <c r="AB754" s="1"/>
       <c r="AC754" s="1"/>
     </row>
-    <row r="755" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="755" spans="1:29" ht="13.2">
       <c r="A755" s="1"/>
       <c r="B755" s="1"/>
       <c r="C755" s="1"/>
@@ -24549,7 +24621,7 @@
       <c r="AB755" s="1"/>
       <c r="AC755" s="1"/>
     </row>
-    <row r="756" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="756" spans="1:29" ht="13.2">
       <c r="A756" s="1"/>
       <c r="B756" s="1"/>
       <c r="C756" s="1"/>
@@ -24580,7 +24652,7 @@
       <c r="AB756" s="1"/>
       <c r="AC756" s="1"/>
     </row>
-    <row r="757" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="757" spans="1:29" ht="13.2">
       <c r="A757" s="1"/>
       <c r="B757" s="1"/>
       <c r="C757" s="1"/>
@@ -24611,7 +24683,7 @@
       <c r="AB757" s="1"/>
       <c r="AC757" s="1"/>
     </row>
-    <row r="758" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="758" spans="1:29" ht="13.2">
       <c r="A758" s="1"/>
       <c r="B758" s="1"/>
       <c r="C758" s="1"/>
@@ -24642,7 +24714,7 @@
       <c r="AB758" s="1"/>
       <c r="AC758" s="1"/>
     </row>
-    <row r="759" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="759" spans="1:29" ht="13.2">
       <c r="A759" s="1"/>
       <c r="B759" s="1"/>
       <c r="C759" s="1"/>
@@ -24673,7 +24745,7 @@
       <c r="AB759" s="1"/>
       <c r="AC759" s="1"/>
     </row>
-    <row r="760" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="760" spans="1:29" ht="13.2">
       <c r="A760" s="1"/>
       <c r="B760" s="1"/>
       <c r="C760" s="1"/>
@@ -24704,7 +24776,7 @@
       <c r="AB760" s="1"/>
       <c r="AC760" s="1"/>
     </row>
-    <row r="761" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="761" spans="1:29" ht="13.2">
       <c r="A761" s="1"/>
       <c r="B761" s="1"/>
       <c r="C761" s="1"/>
@@ -24735,7 +24807,7 @@
       <c r="AB761" s="1"/>
       <c r="AC761" s="1"/>
     </row>
-    <row r="762" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="762" spans="1:29" ht="13.2">
       <c r="A762" s="1"/>
       <c r="B762" s="1"/>
       <c r="C762" s="1"/>
@@ -24766,7 +24838,7 @@
       <c r="AB762" s="1"/>
       <c r="AC762" s="1"/>
     </row>
-    <row r="763" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="763" spans="1:29" ht="13.2">
       <c r="A763" s="1"/>
       <c r="B763" s="1"/>
       <c r="C763" s="1"/>
@@ -24797,7 +24869,7 @@
       <c r="AB763" s="1"/>
       <c r="AC763" s="1"/>
     </row>
-    <row r="764" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="764" spans="1:29" ht="13.2">
       <c r="A764" s="1"/>
       <c r="B764" s="1"/>
       <c r="C764" s="1"/>
@@ -24828,7 +24900,7 @@
       <c r="AB764" s="1"/>
       <c r="AC764" s="1"/>
     </row>
-    <row r="765" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="765" spans="1:29" ht="13.2">
       <c r="A765" s="1"/>
       <c r="B765" s="1"/>
       <c r="C765" s="1"/>
@@ -24859,7 +24931,7 @@
       <c r="AB765" s="1"/>
       <c r="AC765" s="1"/>
     </row>
-    <row r="766" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="766" spans="1:29" ht="13.2">
       <c r="A766" s="1"/>
       <c r="B766" s="1"/>
       <c r="C766" s="1"/>
@@ -24890,7 +24962,7 @@
       <c r="AB766" s="1"/>
       <c r="AC766" s="1"/>
     </row>
-    <row r="767" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="767" spans="1:29" ht="13.2">
       <c r="A767" s="1"/>
       <c r="B767" s="1"/>
       <c r="C767" s="1"/>
@@ -24921,7 +24993,7 @@
       <c r="AB767" s="1"/>
       <c r="AC767" s="1"/>
     </row>
-    <row r="768" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="768" spans="1:29" ht="13.2">
       <c r="A768" s="1"/>
       <c r="B768" s="1"/>
       <c r="C768" s="1"/>
@@ -24952,7 +25024,7 @@
       <c r="AB768" s="1"/>
       <c r="AC768" s="1"/>
     </row>
-    <row r="769" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="769" spans="1:29" ht="13.2">
       <c r="A769" s="1"/>
       <c r="B769" s="1"/>
       <c r="C769" s="1"/>
@@ -24983,7 +25055,7 @@
       <c r="AB769" s="1"/>
       <c r="AC769" s="1"/>
     </row>
-    <row r="770" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="770" spans="1:29" ht="13.2">
       <c r="A770" s="1"/>
       <c r="B770" s="1"/>
       <c r="C770" s="1"/>
@@ -25014,7 +25086,7 @@
       <c r="AB770" s="1"/>
       <c r="AC770" s="1"/>
     </row>
-    <row r="771" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="771" spans="1:29" ht="13.2">
       <c r="A771" s="1"/>
       <c r="B771" s="1"/>
       <c r="C771" s="1"/>
@@ -25045,7 +25117,7 @@
       <c r="AB771" s="1"/>
       <c r="AC771" s="1"/>
     </row>
-    <row r="772" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="772" spans="1:29" ht="13.2">
       <c r="A772" s="1"/>
       <c r="B772" s="1"/>
       <c r="C772" s="1"/>
@@ -25076,7 +25148,7 @@
       <c r="AB772" s="1"/>
       <c r="AC772" s="1"/>
     </row>
-    <row r="773" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="773" spans="1:29" ht="13.2">
       <c r="A773" s="1"/>
       <c r="B773" s="1"/>
       <c r="C773" s="1"/>
@@ -25107,7 +25179,7 @@
       <c r="AB773" s="1"/>
       <c r="AC773" s="1"/>
     </row>
-    <row r="774" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="774" spans="1:29" ht="13.2">
       <c r="A774" s="1"/>
       <c r="B774" s="1"/>
       <c r="C774" s="1"/>
@@ -25138,7 +25210,7 @@
       <c r="AB774" s="1"/>
       <c r="AC774" s="1"/>
     </row>
-    <row r="775" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="775" spans="1:29" ht="13.2">
       <c r="A775" s="1"/>
       <c r="B775" s="1"/>
       <c r="C775" s="1"/>
@@ -25169,7 +25241,7 @@
       <c r="AB775" s="1"/>
       <c r="AC775" s="1"/>
     </row>
-    <row r="776" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="776" spans="1:29" ht="13.2">
       <c r="A776" s="1"/>
       <c r="B776" s="1"/>
       <c r="C776" s="1"/>
@@ -25200,7 +25272,7 @@
       <c r="AB776" s="1"/>
       <c r="AC776" s="1"/>
     </row>
-    <row r="777" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="777" spans="1:29" ht="13.2">
       <c r="A777" s="1"/>
       <c r="B777" s="1"/>
       <c r="C777" s="1"/>
@@ -25231,7 +25303,7 @@
       <c r="AB777" s="1"/>
       <c r="AC777" s="1"/>
     </row>
-    <row r="778" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="778" spans="1:29" ht="13.2">
       <c r="A778" s="1"/>
       <c r="B778" s="1"/>
       <c r="C778" s="1"/>
@@ -25262,7 +25334,7 @@
       <c r="AB778" s="1"/>
       <c r="AC778" s="1"/>
     </row>
-    <row r="779" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="779" spans="1:29" ht="13.2">
       <c r="A779" s="1"/>
       <c r="B779" s="1"/>
       <c r="C779" s="1"/>
@@ -25293,7 +25365,7 @@
       <c r="AB779" s="1"/>
       <c r="AC779" s="1"/>
     </row>
-    <row r="780" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="780" spans="1:29" ht="13.2">
       <c r="A780" s="1"/>
       <c r="B780" s="1"/>
       <c r="C780" s="1"/>
@@ -25324,7 +25396,7 @@
       <c r="AB780" s="1"/>
       <c r="AC780" s="1"/>
     </row>
-    <row r="781" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="781" spans="1:29" ht="13.2">
       <c r="A781" s="1"/>
       <c r="B781" s="1"/>
       <c r="C781" s="1"/>
@@ -25355,7 +25427,7 @@
       <c r="AB781" s="1"/>
       <c r="AC781" s="1"/>
     </row>
-    <row r="782" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="782" spans="1:29" ht="13.2">
       <c r="A782" s="1"/>
       <c r="B782" s="1"/>
       <c r="C782" s="1"/>
@@ -25386,7 +25458,7 @@
       <c r="AB782" s="1"/>
       <c r="AC782" s="1"/>
     </row>
-    <row r="783" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="783" spans="1:29" ht="13.2">
       <c r="A783" s="1"/>
       <c r="B783" s="1"/>
       <c r="C783" s="1"/>
@@ -25417,7 +25489,7 @@
       <c r="AB783" s="1"/>
       <c r="AC783" s="1"/>
     </row>
-    <row r="784" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="784" spans="1:29" ht="13.2">
       <c r="A784" s="1"/>
       <c r="B784" s="1"/>
       <c r="C784" s="1"/>
@@ -25448,7 +25520,7 @@
       <c r="AB784" s="1"/>
       <c r="AC784" s="1"/>
     </row>
-    <row r="785" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="785" spans="1:29" ht="13.2">
       <c r="A785" s="1"/>
       <c r="B785" s="1"/>
       <c r="C785" s="1"/>
@@ -25479,7 +25551,7 @@
       <c r="AB785" s="1"/>
       <c r="AC785" s="1"/>
     </row>
-    <row r="786" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="786" spans="1:29" ht="13.2">
       <c r="A786" s="1"/>
       <c r="B786" s="1"/>
       <c r="C786" s="1"/>
@@ -25510,7 +25582,7 @@
       <c r="AB786" s="1"/>
       <c r="AC786" s="1"/>
     </row>
-    <row r="787" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="787" spans="1:29" ht="13.2">
       <c r="A787" s="1"/>
       <c r="B787" s="1"/>
       <c r="C787" s="1"/>
@@ -25541,7 +25613,7 @@
       <c r="AB787" s="1"/>
       <c r="AC787" s="1"/>
     </row>
-    <row r="788" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="788" spans="1:29" ht="13.2">
       <c r="A788" s="1"/>
       <c r="B788" s="1"/>
       <c r="C788" s="1"/>
@@ -25572,7 +25644,7 @@
       <c r="AB788" s="1"/>
       <c r="AC788" s="1"/>
     </row>
-    <row r="789" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="789" spans="1:29" ht="13.2">
       <c r="A789" s="1"/>
       <c r="B789" s="1"/>
       <c r="C789" s="1"/>
@@ -25603,7 +25675,7 @@
       <c r="AB789" s="1"/>
       <c r="AC789" s="1"/>
     </row>
-    <row r="790" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="790" spans="1:29" ht="13.2">
       <c r="A790" s="1"/>
       <c r="B790" s="1"/>
       <c r="C790" s="1"/>
@@ -25634,7 +25706,7 @@
       <c r="AB790" s="1"/>
       <c r="AC790" s="1"/>
     </row>
-    <row r="791" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="791" spans="1:29" ht="13.2">
       <c r="A791" s="1"/>
       <c r="B791" s="1"/>
       <c r="C791" s="1"/>
@@ -25665,7 +25737,7 @@
       <c r="AB791" s="1"/>
       <c r="AC791" s="1"/>
     </row>
-    <row r="792" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="792" spans="1:29" ht="13.2">
       <c r="A792" s="1"/>
       <c r="B792" s="1"/>
       <c r="C792" s="1"/>
@@ -25696,7 +25768,7 @@
       <c r="AB792" s="1"/>
       <c r="AC792" s="1"/>
     </row>
-    <row r="793" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="793" spans="1:29" ht="13.2">
       <c r="A793" s="1"/>
       <c r="B793" s="1"/>
       <c r="C793" s="1"/>
@@ -25727,7 +25799,7 @@
       <c r="AB793" s="1"/>
       <c r="AC793" s="1"/>
     </row>
-    <row r="794" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="794" spans="1:29" ht="13.2">
       <c r="A794" s="1"/>
       <c r="B794" s="1"/>
       <c r="C794" s="1"/>
@@ -25758,7 +25830,7 @@
       <c r="AB794" s="1"/>
       <c r="AC794" s="1"/>
     </row>
-    <row r="795" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="795" spans="1:29" ht="13.2">
       <c r="A795" s="1"/>
       <c r="B795" s="1"/>
       <c r="C795" s="1"/>
@@ -25789,7 +25861,7 @@
       <c r="AB795" s="1"/>
       <c r="AC795" s="1"/>
     </row>
-    <row r="796" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="796" spans="1:29" ht="13.2">
       <c r="A796" s="1"/>
       <c r="B796" s="1"/>
       <c r="C796" s="1"/>
@@ -25820,7 +25892,7 @@
       <c r="AB796" s="1"/>
       <c r="AC796" s="1"/>
     </row>
-    <row r="797" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="797" spans="1:29" ht="13.2">
       <c r="A797" s="1"/>
       <c r="B797" s="1"/>
       <c r="C797" s="1"/>
@@ -25851,7 +25923,7 @@
       <c r="AB797" s="1"/>
       <c r="AC797" s="1"/>
     </row>
-    <row r="798" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="798" spans="1:29" ht="13.2">
       <c r="A798" s="1"/>
       <c r="B798" s="1"/>
       <c r="C798" s="1"/>
@@ -25882,7 +25954,7 @@
       <c r="AB798" s="1"/>
       <c r="AC798" s="1"/>
     </row>
-    <row r="799" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="799" spans="1:29" ht="13.2">
       <c r="A799" s="1"/>
       <c r="B799" s="1"/>
       <c r="C799" s="1"/>
@@ -25913,7 +25985,7 @@
       <c r="AB799" s="1"/>
       <c r="AC799" s="1"/>
     </row>
-    <row r="800" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="800" spans="1:29" ht="13.2">
       <c r="A800" s="1"/>
       <c r="B800" s="1"/>
       <c r="C800" s="1"/>
@@ -25944,7 +26016,7 @@
       <c r="AB800" s="1"/>
       <c r="AC800" s="1"/>
     </row>
-    <row r="801" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="801" spans="1:29" ht="13.2">
       <c r="A801" s="1"/>
       <c r="B801" s="1"/>
       <c r="C801" s="1"/>
@@ -25975,7 +26047,7 @@
       <c r="AB801" s="1"/>
       <c r="AC801" s="1"/>
     </row>
-    <row r="802" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="802" spans="1:29" ht="13.2">
       <c r="A802" s="1"/>
       <c r="B802" s="1"/>
       <c r="C802" s="1"/>
@@ -26006,7 +26078,7 @@
       <c r="AB802" s="1"/>
       <c r="AC802" s="1"/>
     </row>
-    <row r="803" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="803" spans="1:29" ht="13.2">
       <c r="A803" s="1"/>
       <c r="B803" s="1"/>
       <c r="C803" s="1"/>
@@ -26037,7 +26109,7 @@
       <c r="AB803" s="1"/>
       <c r="AC803" s="1"/>
     </row>
-    <row r="804" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="804" spans="1:29" ht="13.2">
       <c r="A804" s="1"/>
       <c r="B804" s="1"/>
       <c r="C804" s="1"/>
@@ -26068,7 +26140,7 @@
       <c r="AB804" s="1"/>
       <c r="AC804" s="1"/>
     </row>
-    <row r="805" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="805" spans="1:29" ht="13.2">
       <c r="A805" s="1"/>
       <c r="B805" s="1"/>
       <c r="C805" s="1"/>
@@ -26099,7 +26171,7 @@
       <c r="AB805" s="1"/>
       <c r="AC805" s="1"/>
     </row>
-    <row r="806" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="806" spans="1:29" ht="13.2">
       <c r="A806" s="1"/>
       <c r="B806" s="1"/>
       <c r="C806" s="1"/>
@@ -26130,7 +26202,7 @@
       <c r="AB806" s="1"/>
       <c r="AC806" s="1"/>
     </row>
-    <row r="807" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="807" spans="1:29" ht="13.2">
       <c r="A807" s="1"/>
       <c r="B807" s="1"/>
       <c r="C807" s="1"/>
@@ -26161,7 +26233,7 @@
       <c r="AB807" s="1"/>
       <c r="AC807" s="1"/>
     </row>
-    <row r="808" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="808" spans="1:29" ht="13.2">
       <c r="A808" s="1"/>
       <c r="B808" s="1"/>
       <c r="C808" s="1"/>
@@ -26192,7 +26264,7 @@
       <c r="AB808" s="1"/>
       <c r="AC808" s="1"/>
     </row>
-    <row r="809" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="809" spans="1:29" ht="13.2">
       <c r="A809" s="1"/>
       <c r="B809" s="1"/>
       <c r="C809" s="1"/>
@@ -26223,7 +26295,7 @@
       <c r="AB809" s="1"/>
       <c r="AC809" s="1"/>
     </row>
-    <row r="810" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="810" spans="1:29" ht="13.2">
       <c r="A810" s="1"/>
       <c r="B810" s="1"/>
       <c r="C810" s="1"/>
@@ -26254,7 +26326,7 @@
       <c r="AB810" s="1"/>
       <c r="AC810" s="1"/>
     </row>
-    <row r="811" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="811" spans="1:29" ht="13.2">
       <c r="A811" s="1"/>
       <c r="B811" s="1"/>
       <c r="C811" s="1"/>
@@ -26285,7 +26357,7 @@
       <c r="AB811" s="1"/>
       <c r="AC811" s="1"/>
     </row>
-    <row r="812" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="812" spans="1:29" ht="13.2">
       <c r="A812" s="1"/>
       <c r="B812" s="1"/>
       <c r="C812" s="1"/>
@@ -26316,7 +26388,7 @@
       <c r="AB812" s="1"/>
       <c r="AC812" s="1"/>
     </row>
-    <row r="813" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="813" spans="1:29" ht="13.2">
       <c r="A813" s="1"/>
       <c r="B813" s="1"/>
       <c r="C813" s="1"/>
@@ -26347,7 +26419,7 @@
       <c r="AB813" s="1"/>
       <c r="AC813" s="1"/>
     </row>
-    <row r="814" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="814" spans="1:29" ht="13.2">
       <c r="A814" s="1"/>
       <c r="B814" s="1"/>
       <c r="C814" s="1"/>
@@ -26378,7 +26450,7 @@
       <c r="AB814" s="1"/>
       <c r="AC814" s="1"/>
     </row>
-    <row r="815" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="815" spans="1:29" ht="13.2">
       <c r="A815" s="1"/>
       <c r="B815" s="1"/>
       <c r="C815" s="1"/>
@@ -26409,7 +26481,7 @@
       <c r="AB815" s="1"/>
       <c r="AC815" s="1"/>
     </row>
-    <row r="816" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="816" spans="1:29" ht="13.2">
       <c r="A816" s="1"/>
       <c r="B816" s="1"/>
       <c r="C816" s="1"/>
@@ -26440,7 +26512,7 @@
       <c r="AB816" s="1"/>
       <c r="AC816" s="1"/>
     </row>
-    <row r="817" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="817" spans="1:29" ht="13.2">
       <c r="A817" s="1"/>
       <c r="B817" s="1"/>
       <c r="C817" s="1"/>
@@ -26471,7 +26543,7 @@
       <c r="AB817" s="1"/>
       <c r="AC817" s="1"/>
     </row>
-    <row r="818" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="818" spans="1:29" ht="13.2">
       <c r="A818" s="1"/>
       <c r="B818" s="1"/>
       <c r="C818" s="1"/>
@@ -26502,7 +26574,7 @@
       <c r="AB818" s="1"/>
       <c r="AC818" s="1"/>
     </row>
-    <row r="819" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="819" spans="1:29" ht="13.2">
       <c r="A819" s="1"/>
       <c r="B819" s="1"/>
       <c r="C819" s="1"/>
@@ -26533,7 +26605,7 @@
       <c r="AB819" s="1"/>
       <c r="AC819" s="1"/>
     </row>
-    <row r="820" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="820" spans="1:29" ht="13.2">
       <c r="A820" s="1"/>
       <c r="B820" s="1"/>
       <c r="C820" s="1"/>
@@ -26564,7 +26636,7 @@
       <c r="AB820" s="1"/>
       <c r="AC820" s="1"/>
     </row>
-    <row r="821" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="821" spans="1:29" ht="13.2">
       <c r="A821" s="1"/>
       <c r="B821" s="1"/>
       <c r="C821" s="1"/>
@@ -26595,7 +26667,7 @@
       <c r="AB821" s="1"/>
       <c r="AC821" s="1"/>
     </row>
-    <row r="822" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="822" spans="1:29" ht="13.2">
       <c r="A822" s="1"/>
       <c r="B822" s="1"/>
       <c r="C822" s="1"/>
@@ -26626,7 +26698,7 @@
       <c r="AB822" s="1"/>
       <c r="AC822" s="1"/>
     </row>
-    <row r="823" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="823" spans="1:29" ht="13.2">
       <c r="A823" s="1"/>
       <c r="B823" s="1"/>
       <c r="C823" s="1"/>
@@ -26657,7 +26729,7 @@
       <c r="AB823" s="1"/>
       <c r="AC823" s="1"/>
     </row>
-    <row r="824" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="824" spans="1:29" ht="13.2">
       <c r="A824" s="1"/>
       <c r="B824" s="1"/>
       <c r="C824" s="1"/>
@@ -26688,7 +26760,7 @@
       <c r="AB824" s="1"/>
       <c r="AC824" s="1"/>
     </row>
-    <row r="825" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="825" spans="1:29" ht="13.2">
       <c r="A825" s="1"/>
       <c r="B825" s="1"/>
       <c r="C825" s="1"/>
@@ -26719,7 +26791,7 @@
       <c r="AB825" s="1"/>
       <c r="AC825" s="1"/>
     </row>
-    <row r="826" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="826" spans="1:29" ht="13.2">
       <c r="A826" s="1"/>
       <c r="B826" s="1"/>
       <c r="C826" s="1"/>
@@ -26750,7 +26822,7 @@
       <c r="AB826" s="1"/>
       <c r="AC826" s="1"/>
     </row>
-    <row r="827" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="827" spans="1:29" ht="13.2">
       <c r="A827" s="1"/>
       <c r="B827" s="1"/>
       <c r="C827" s="1"/>
@@ -26781,7 +26853,7 @@
       <c r="AB827" s="1"/>
       <c r="AC827" s="1"/>
     </row>
-    <row r="828" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="828" spans="1:29" ht="13.2">
       <c r="A828" s="1"/>
       <c r="B828" s="1"/>
       <c r="C828" s="1"/>
@@ -26812,7 +26884,7 @@
       <c r="AB828" s="1"/>
       <c r="AC828" s="1"/>
     </row>
-    <row r="829" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="829" spans="1:29" ht="13.2">
       <c r="A829" s="1"/>
       <c r="B829" s="1"/>
       <c r="C829" s="1"/>
@@ -26843,7 +26915,7 @@
       <c r="AB829" s="1"/>
       <c r="AC829" s="1"/>
     </row>
-    <row r="830" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="830" spans="1:29" ht="13.2">
       <c r="A830" s="1"/>
       <c r="B830" s="1"/>
       <c r="C830" s="1"/>
@@ -26874,7 +26946,7 @@
       <c r="AB830" s="1"/>
       <c r="AC830" s="1"/>
     </row>
-    <row r="831" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="831" spans="1:29" ht="13.2">
       <c r="A831" s="1"/>
       <c r="B831" s="1"/>
       <c r="C831" s="1"/>
@@ -26905,7 +26977,7 @@
       <c r="AB831" s="1"/>
       <c r="AC831" s="1"/>
     </row>
-    <row r="832" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="832" spans="1:29" ht="13.2">
       <c r="A832" s="1"/>
       <c r="B832" s="1"/>
       <c r="C832" s="1"/>
@@ -26936,7 +27008,7 @@
       <c r="AB832" s="1"/>
       <c r="AC832" s="1"/>
     </row>
-    <row r="833" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="833" spans="1:29" ht="13.2">
       <c r="A833" s="1"/>
       <c r="B833" s="1"/>
       <c r="C833" s="1"/>
@@ -26967,7 +27039,7 @@
       <c r="AB833" s="1"/>
       <c r="AC833" s="1"/>
     </row>
-    <row r="834" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="834" spans="1:29" ht="13.2">
       <c r="A834" s="1"/>
       <c r="B834" s="1"/>
       <c r="C834" s="1"/>
@@ -26998,7 +27070,7 @@
       <c r="AB834" s="1"/>
       <c r="AC834" s="1"/>
     </row>
-    <row r="835" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="835" spans="1:29" ht="13.2">
       <c r="A835" s="1"/>
       <c r="B835" s="1"/>
       <c r="C835" s="1"/>
@@ -27029,7 +27101,7 @@
       <c r="AB835" s="1"/>
       <c r="AC835" s="1"/>
     </row>
-    <row r="836" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="836" spans="1:29" ht="13.2">
       <c r="A836" s="1"/>
       <c r="B836" s="1"/>
       <c r="C836" s="1"/>
@@ -27060,7 +27132,7 @@
       <c r="AB836" s="1"/>
       <c r="AC836" s="1"/>
     </row>
-    <row r="837" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="837" spans="1:29" ht="13.2">
       <c r="A837" s="1"/>
       <c r="B837" s="1"/>
       <c r="C837" s="1"/>
@@ -27091,7 +27163,7 @@
       <c r="AB837" s="1"/>
       <c r="AC837" s="1"/>
     </row>
-    <row r="838" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="838" spans="1:29" ht="13.2">
       <c r="A838" s="1"/>
       <c r="B838" s="1"/>
       <c r="C838" s="1"/>
@@ -27122,7 +27194,7 @@
       <c r="AB838" s="1"/>
       <c r="AC838" s="1"/>
     </row>
-    <row r="839" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="839" spans="1:29" ht="13.2">
       <c r="A839" s="1"/>
       <c r="B839" s="1"/>
       <c r="C839" s="1"/>
@@ -27153,7 +27225,7 @@
       <c r="AB839" s="1"/>
       <c r="AC839" s="1"/>
     </row>
-    <row r="840" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="840" spans="1:29" ht="13.2">
       <c r="A840" s="1"/>
       <c r="B840" s="1"/>
       <c r="C840" s="1"/>
@@ -27184,7 +27256,7 @@
       <c r="AB840" s="1"/>
       <c r="AC840" s="1"/>
     </row>
-    <row r="841" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="841" spans="1:29" ht="13.2">
       <c r="A841" s="1"/>
       <c r="B841" s="1"/>
       <c r="C841" s="1"/>
@@ -27215,7 +27287,7 @@
       <c r="AB841" s="1"/>
       <c r="AC841" s="1"/>
     </row>
-    <row r="842" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="842" spans="1:29" ht="13.2">
       <c r="A842" s="1"/>
       <c r="B842" s="1"/>
       <c r="C842" s="1"/>
@@ -27246,7 +27318,7 @@
       <c r="AB842" s="1"/>
       <c r="AC842" s="1"/>
     </row>
-    <row r="843" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="843" spans="1:29" ht="13.2">
       <c r="A843" s="1"/>
       <c r="B843" s="1"/>
       <c r="C843" s="1"/>
@@ -27277,7 +27349,7 @@
       <c r="AB843" s="1"/>
       <c r="AC843" s="1"/>
     </row>
-    <row r="844" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="844" spans="1:29" ht="13.2">
       <c r="A844" s="1"/>
       <c r="B844" s="1"/>
       <c r="C844" s="1"/>
@@ -27308,7 +27380,7 @@
       <c r="AB844" s="1"/>
       <c r="AC844" s="1"/>
     </row>
-    <row r="845" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="845" spans="1:29" ht="13.2">
       <c r="A845" s="1"/>
       <c r="B845" s="1"/>
       <c r="C845" s="1"/>
@@ -27339,7 +27411,7 @@
       <c r="AB845" s="1"/>
       <c r="AC845" s="1"/>
     </row>
-    <row r="846" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="846" spans="1:29" ht="13.2">
       <c r="A846" s="1"/>
       <c r="B846" s="1"/>
       <c r="C846" s="1"/>
@@ -27370,7 +27442,7 @@
       <c r="AB846" s="1"/>
       <c r="AC846" s="1"/>
     </row>
-    <row r="847" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="847" spans="1:29" ht="13.2">
       <c r="A847" s="1"/>
       <c r="B847" s="1"/>
       <c r="C847" s="1"/>
@@ -27401,7 +27473,7 @@
       <c r="AB847" s="1"/>
       <c r="AC847" s="1"/>
     </row>
-    <row r="848" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="848" spans="1:29" ht="13.2">
       <c r="A848" s="1"/>
       <c r="B848" s="1"/>
       <c r="C848" s="1"/>
@@ -27432,7 +27504,7 @@
       <c r="AB848" s="1"/>
       <c r="AC848" s="1"/>
     </row>
-    <row r="849" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="849" spans="1:29" ht="13.2">
       <c r="A849" s="1"/>
       <c r="B849" s="1"/>
       <c r="C849" s="1"/>
@@ -27463,7 +27535,7 @@
       <c r="AB849" s="1"/>
       <c r="AC849" s="1"/>
     </row>
-    <row r="850" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="850" spans="1:29" ht="13.2">
       <c r="A850" s="1"/>
       <c r="B850" s="1"/>
       <c r="C850" s="1"/>
@@ -27494,7 +27566,7 @@
       <c r="AB850" s="1"/>
       <c r="AC850" s="1"/>
     </row>
-    <row r="851" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="851" spans="1:29" ht="13.2">
       <c r="A851" s="1"/>
       <c r="B851" s="1"/>
       <c r="C851" s="1"/>
@@ -27525,7 +27597,7 @@
       <c r="AB851" s="1"/>
       <c r="AC851" s="1"/>
     </row>
-    <row r="852" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="852" spans="1:29" ht="13.2">
       <c r="A852" s="1"/>
       <c r="B852" s="1"/>
       <c r="C852" s="1"/>
@@ -27556,7 +27628,7 @@
       <c r="AB852" s="1"/>
       <c r="AC852" s="1"/>
     </row>
-    <row r="853" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="853" spans="1:29" ht="13.2">
       <c r="A853" s="1"/>
       <c r="B853" s="1"/>
       <c r="C853" s="1"/>
@@ -27587,7 +27659,7 @@
       <c r="AB853" s="1"/>
       <c r="AC853" s="1"/>
     </row>
-    <row r="854" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="854" spans="1:29" ht="13.2">
       <c r="A854" s="1"/>
       <c r="B854" s="1"/>
       <c r="C854" s="1"/>
@@ -27618,7 +27690,7 @@
       <c r="AB854" s="1"/>
       <c r="AC854" s="1"/>
     </row>
-    <row r="855" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="855" spans="1:29" ht="13.2">
       <c r="A855" s="1"/>
       <c r="B855" s="1"/>
       <c r="C855" s="1"/>
@@ -27649,7 +27721,7 @@
       <c r="AB855" s="1"/>
       <c r="AC855" s="1"/>
     </row>
-    <row r="856" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="856" spans="1:29" ht="13.2">
       <c r="A856" s="1"/>
       <c r="B856" s="1"/>
       <c r="C856" s="1"/>
@@ -27680,7 +27752,7 @@
       <c r="AB856" s="1"/>
       <c r="AC856" s="1"/>
     </row>
-    <row r="857" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="857" spans="1:29" ht="13.2">
       <c r="A857" s="1"/>
       <c r="B857" s="1"/>
       <c r="C857" s="1"/>
@@ -27711,7 +27783,7 @@
       <c r="AB857" s="1"/>
       <c r="AC857" s="1"/>
     </row>
-    <row r="858" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="858" spans="1:29" ht="13.2">
       <c r="A858" s="1"/>
       <c r="B858" s="1"/>
       <c r="C858" s="1"/>
@@ -27742,7 +27814,7 @@
       <c r="AB858" s="1"/>
       <c r="AC858" s="1"/>
     </row>
-    <row r="859" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="859" spans="1:29" ht="13.2">
       <c r="A859" s="1"/>
       <c r="B859" s="1"/>
       <c r="C859" s="1"/>
@@ -27773,7 +27845,7 @@
       <c r="AB859" s="1"/>
       <c r="AC859" s="1"/>
     </row>
-    <row r="860" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="860" spans="1:29" ht="13.2">
       <c r="A860" s="1"/>
       <c r="B860" s="1"/>
       <c r="C860" s="1"/>
@@ -27804,7 +27876,7 @@
       <c r="AB860" s="1"/>
       <c r="AC860" s="1"/>
     </row>
-    <row r="861" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="861" spans="1:29" ht="13.2">
       <c r="A861" s="1"/>
       <c r="B861" s="1"/>
       <c r="C861" s="1"/>
@@ -27835,7 +27907,7 @@
       <c r="AB861" s="1"/>
       <c r="AC861" s="1"/>
     </row>
-    <row r="862" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="862" spans="1:29" ht="13.2">
       <c r="A862" s="1"/>
       <c r="B862" s="1"/>
       <c r="C862" s="1"/>
@@ -27866,7 +27938,7 @@
       <c r="AB862" s="1"/>
       <c r="AC862" s="1"/>
     </row>
-    <row r="863" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="863" spans="1:29" ht="13.2">
       <c r="A863" s="1"/>
       <c r="B863" s="1"/>
       <c r="C863" s="1"/>
@@ -27897,7 +27969,7 @@
       <c r="AB863" s="1"/>
       <c r="AC863" s="1"/>
     </row>
-    <row r="864" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="864" spans="1:29" ht="13.2">
       <c r="A864" s="1"/>
       <c r="B864" s="1"/>
       <c r="C864" s="1"/>
@@ -27928,7 +28000,7 @@
       <c r="AB864" s="1"/>
       <c r="AC864" s="1"/>
     </row>
-    <row r="865" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="865" spans="1:29" ht="13.2">
       <c r="A865" s="1"/>
       <c r="B865" s="1"/>
       <c r="C865" s="1"/>
@@ -27959,7 +28031,7 @@
       <c r="AB865" s="1"/>
       <c r="AC865" s="1"/>
     </row>
-    <row r="866" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="866" spans="1:29" ht="13.2">
       <c r="A866" s="1"/>
       <c r="B866" s="1"/>
       <c r="C866" s="1"/>
@@ -27990,7 +28062,7 @@
       <c r="AB866" s="1"/>
       <c r="AC866" s="1"/>
     </row>
-    <row r="867" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="867" spans="1:29" ht="13.2">
       <c r="A867" s="1"/>
       <c r="B867" s="1"/>
       <c r="C867" s="1"/>
@@ -28021,7 +28093,7 @@
       <c r="AB867" s="1"/>
       <c r="AC867" s="1"/>
     </row>
-    <row r="868" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="868" spans="1:29" ht="13.2">
       <c r="A868" s="1"/>
       <c r="B868" s="1"/>
       <c r="C868" s="1"/>
@@ -28052,7 +28124,7 @@
       <c r="AB868" s="1"/>
       <c r="AC868" s="1"/>
     </row>
-    <row r="869" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="869" spans="1:29" ht="13.2">
       <c r="A869" s="1"/>
       <c r="B869" s="1"/>
       <c r="C869" s="1"/>
@@ -28083,7 +28155,7 @@
       <c r="AB869" s="1"/>
       <c r="AC869" s="1"/>
     </row>
-    <row r="870" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="870" spans="1:29" ht="13.2">
       <c r="A870" s="1"/>
       <c r="B870" s="1"/>
       <c r="C870" s="1"/>
@@ -28114,7 +28186,7 @@
       <c r="AB870" s="1"/>
       <c r="AC870" s="1"/>
     </row>
-    <row r="871" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="871" spans="1:29" ht="13.2">
       <c r="A871" s="1"/>
       <c r="B871" s="1"/>
       <c r="C871" s="1"/>
@@ -28145,7 +28217,7 @@
       <c r="AB871" s="1"/>
       <c r="AC871" s="1"/>
     </row>
-    <row r="872" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="872" spans="1:29" ht="13.2">
       <c r="A872" s="1"/>
       <c r="B872" s="1"/>
       <c r="C872" s="1"/>
@@ -28176,7 +28248,7 @@
       <c r="AB872" s="1"/>
       <c r="AC872" s="1"/>
     </row>
-    <row r="873" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="873" spans="1:29" ht="13.2">
       <c r="A873" s="1"/>
       <c r="B873" s="1"/>
       <c r="C873" s="1"/>
@@ -28207,7 +28279,7 @@
       <c r="AB873" s="1"/>
       <c r="AC873" s="1"/>
     </row>
-    <row r="874" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="874" spans="1:29" ht="13.2">
       <c r="A874" s="1"/>
       <c r="B874" s="1"/>
       <c r="C874" s="1"/>
@@ -28238,7 +28310,7 @@
       <c r="AB874" s="1"/>
       <c r="AC874" s="1"/>
     </row>
-    <row r="875" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="875" spans="1:29" ht="13.2">
       <c r="A875" s="1"/>
       <c r="B875" s="1"/>
       <c r="C875" s="1"/>
@@ -28269,7 +28341,7 @@
       <c r="AB875" s="1"/>
       <c r="AC875" s="1"/>
     </row>
-    <row r="876" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="876" spans="1:29" ht="13.2">
       <c r="A876" s="1"/>
       <c r="B876" s="1"/>
       <c r="C876" s="1"/>
@@ -28300,7 +28372,7 @@
       <c r="AB876" s="1"/>
       <c r="AC876" s="1"/>
     </row>
-    <row r="877" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="877" spans="1:29" ht="13.2">
       <c r="A877" s="1"/>
       <c r="B877" s="1"/>
       <c r="C877" s="1"/>
@@ -28331,7 +28403,7 @@
       <c r="AB877" s="1"/>
       <c r="AC877" s="1"/>
     </row>
-    <row r="878" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="878" spans="1:29" ht="13.2">
       <c r="A878" s="1"/>
       <c r="B878" s="1"/>
       <c r="C878" s="1"/>
@@ -28362,7 +28434,7 @@
       <c r="AB878" s="1"/>
       <c r="AC878" s="1"/>
     </row>
-    <row r="879" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="879" spans="1:29" ht="13.2">
       <c r="A879" s="1"/>
       <c r="B879" s="1"/>
       <c r="C879" s="1"/>
@@ -28393,7 +28465,7 @@
       <c r="AB879" s="1"/>
       <c r="AC879" s="1"/>
     </row>
-    <row r="880" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="880" spans="1:29" ht="13.2">
       <c r="A880" s="1"/>
       <c r="B880" s="1"/>
       <c r="C880" s="1"/>
@@ -28424,7 +28496,7 @@
       <c r="AB880" s="1"/>
       <c r="AC880" s="1"/>
     </row>
-    <row r="881" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="881" spans="1:29" ht="13.2">
       <c r="A881" s="1"/>
       <c r="B881" s="1"/>
       <c r="C881" s="1"/>
@@ -28455,7 +28527,7 @@
       <c r="AB881" s="1"/>
       <c r="AC881" s="1"/>
     </row>
-    <row r="882" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="882" spans="1:29" ht="13.2">
       <c r="A882" s="1"/>
       <c r="B882" s="1"/>
       <c r="C882" s="1"/>
@@ -28486,7 +28558,7 @@
       <c r="AB882" s="1"/>
       <c r="AC882" s="1"/>
     </row>
-    <row r="883" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="883" spans="1:29" ht="13.2">
       <c r="A883" s="1"/>
       <c r="B883" s="1"/>
       <c r="C883" s="1"/>
@@ -28517,7 +28589,7 @@
       <c r="AB883" s="1"/>
       <c r="AC883" s="1"/>
     </row>
-    <row r="884" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="884" spans="1:29" ht="13.2">
       <c r="A884" s="1"/>
       <c r="B884" s="1"/>
       <c r="C884" s="1"/>
@@ -28548,7 +28620,7 @@
       <c r="AB884" s="1"/>
       <c r="AC884" s="1"/>
     </row>
-    <row r="885" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="885" spans="1:29" ht="13.2">
       <c r="A885" s="1"/>
       <c r="B885" s="1"/>
       <c r="C885" s="1"/>
@@ -28579,7 +28651,7 @@
       <c r="AB885" s="1"/>
       <c r="AC885" s="1"/>
     </row>
-    <row r="886" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="886" spans="1:29" ht="13.2">
       <c r="A886" s="1"/>
       <c r="B886" s="1"/>
       <c r="C886" s="1"/>
@@ -28610,7 +28682,7 @@
       <c r="AB886" s="1"/>
       <c r="AC886" s="1"/>
     </row>
-    <row r="887" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="887" spans="1:29" ht="13.2">
       <c r="A887" s="1"/>
       <c r="B887" s="1"/>
       <c r="C887" s="1"/>
@@ -28641,7 +28713,7 @@
       <c r="AB887" s="1"/>
       <c r="AC887" s="1"/>
     </row>
-    <row r="888" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="888" spans="1:29" ht="13.2">
       <c r="A888" s="1"/>
       <c r="B888" s="1"/>
       <c r="C888" s="1"/>
@@ -28672,7 +28744,7 @@
       <c r="AB888" s="1"/>
       <c r="AC888" s="1"/>
     </row>
-    <row r="889" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="889" spans="1:29" ht="13.2">
       <c r="A889" s="1"/>
       <c r="B889" s="1"/>
       <c r="C889" s="1"/>
@@ -28703,7 +28775,7 @@
       <c r="AB889" s="1"/>
       <c r="AC889" s="1"/>
     </row>
-    <row r="890" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="890" spans="1:29" ht="13.2">
       <c r="A890" s="1"/>
       <c r="B890" s="1"/>
       <c r="C890" s="1"/>
@@ -28734,7 +28806,7 @@
       <c r="AB890" s="1"/>
       <c r="AC890" s="1"/>
     </row>
-    <row r="891" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="891" spans="1:29" ht="13.2">
       <c r="A891" s="1"/>
       <c r="B891" s="1"/>
       <c r="C891" s="1"/>
@@ -28765,7 +28837,7 @@
       <c r="AB891" s="1"/>
       <c r="AC891" s="1"/>
     </row>
-    <row r="892" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="892" spans="1:29" ht="13.2">
       <c r="A892" s="1"/>
       <c r="B892" s="1"/>
       <c r="C892" s="1"/>
@@ -28796,7 +28868,7 @@
       <c r="AB892" s="1"/>
       <c r="AC892" s="1"/>
     </row>
-    <row r="893" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="893" spans="1:29" ht="13.2">
       <c r="A893" s="1"/>
       <c r="B893" s="1"/>
       <c r="C893" s="1"/>
@@ -28827,7 +28899,7 @@
       <c r="AB893" s="1"/>
       <c r="AC893" s="1"/>
     </row>
-    <row r="894" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="894" spans="1:29" ht="13.2">
       <c r="A894" s="1"/>
       <c r="B894" s="1"/>
       <c r="C894" s="1"/>
@@ -28858,7 +28930,7 @@
       <c r="AB894" s="1"/>
       <c r="AC894" s="1"/>
     </row>
-    <row r="895" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="895" spans="1:29" ht="13.2">
       <c r="A895" s="1"/>
       <c r="B895" s="1"/>
       <c r="C895" s="1"/>
@@ -28889,7 +28961,7 @@
       <c r="AB895" s="1"/>
       <c r="AC895" s="1"/>
     </row>
-    <row r="896" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="896" spans="1:29" ht="13.2">
       <c r="A896" s="1"/>
       <c r="B896" s="1"/>
       <c r="C896" s="1"/>
@@ -28920,7 +28992,7 @@
       <c r="AB896" s="1"/>
       <c r="AC896" s="1"/>
     </row>
-    <row r="897" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="897" spans="1:29" ht="13.2">
       <c r="A897" s="1"/>
       <c r="B897" s="1"/>
       <c r="C897" s="1"/>
@@ -28951,7 +29023,7 @@
       <c r="AB897" s="1"/>
       <c r="AC897" s="1"/>
     </row>
-    <row r="898" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="898" spans="1:29" ht="13.2">
       <c r="A898" s="1"/>
       <c r="B898" s="1"/>
       <c r="C898" s="1"/>
@@ -28982,7 +29054,7 @@
       <c r="AB898" s="1"/>
       <c r="AC898" s="1"/>
     </row>
-    <row r="899" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="899" spans="1:29" ht="13.2">
       <c r="A899" s="1"/>
       <c r="B899" s="1"/>
       <c r="C899" s="1"/>
@@ -29013,7 +29085,7 @@
       <c r="AB899" s="1"/>
       <c r="AC899" s="1"/>
     </row>
-    <row r="900" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="900" spans="1:29" ht="13.2">
       <c r="A900" s="1"/>
       <c r="B900" s="1"/>
       <c r="C900" s="1"/>
@@ -29044,7 +29116,7 @@
       <c r="AB900" s="1"/>
       <c r="AC900" s="1"/>
     </row>
-    <row r="901" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="901" spans="1:29" ht="13.2">
       <c r="A901" s="1"/>
       <c r="B901" s="1"/>
       <c r="C901" s="1"/>
@@ -29075,7 +29147,7 @@
       <c r="AB901" s="1"/>
       <c r="AC901" s="1"/>
     </row>
-    <row r="902" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="902" spans="1:29" ht="13.2">
       <c r="A902" s="1"/>
       <c r="B902" s="1"/>
       <c r="C902" s="1"/>
@@ -29106,7 +29178,7 @@
       <c r="AB902" s="1"/>
       <c r="AC902" s="1"/>
     </row>
-    <row r="903" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="903" spans="1:29" ht="13.2">
       <c r="A903" s="1"/>
       <c r="B903" s="1"/>
       <c r="C903" s="1"/>
@@ -29137,7 +29209,7 @@
       <c r="AB903" s="1"/>
       <c r="AC903" s="1"/>
     </row>
-    <row r="904" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="904" spans="1:29" ht="13.2">
       <c r="A904" s="1"/>
       <c r="B904" s="1"/>
       <c r="C904" s="1"/>
@@ -29168,7 +29240,7 @@
       <c r="AB904" s="1"/>
       <c r="AC904" s="1"/>
     </row>
-    <row r="905" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="905" spans="1:29" ht="13.2">
       <c r="A905" s="1"/>
       <c r="B905" s="1"/>
       <c r="C905" s="1"/>
@@ -29199,7 +29271,7 @@
       <c r="AB905" s="1"/>
       <c r="AC905" s="1"/>
     </row>
-    <row r="906" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="906" spans="1:29" ht="13.2">
       <c r="A906" s="1"/>
       <c r="B906" s="1"/>
       <c r="C906" s="1"/>
@@ -29230,7 +29302,7 @@
       <c r="AB906" s="1"/>
       <c r="AC906" s="1"/>
     </row>
-    <row r="907" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="907" spans="1:29" ht="13.2">
       <c r="A907" s="1"/>
       <c r="B907" s="1"/>
       <c r="C907" s="1"/>
@@ -29261,7 +29333,7 @@
       <c r="AB907" s="1"/>
       <c r="AC907" s="1"/>
     </row>
-    <row r="908" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="908" spans="1:29" ht="13.2">
       <c r="A908" s="1"/>
       <c r="B908" s="1"/>
       <c r="C908" s="1"/>
@@ -29292,7 +29364,7 @@
       <c r="AB908" s="1"/>
       <c r="AC908" s="1"/>
     </row>
-    <row r="909" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="909" spans="1:29" ht="13.2">
       <c r="A909" s="1"/>
       <c r="B909" s="1"/>
       <c r="C909" s="1"/>
@@ -29323,7 +29395,7 @@
       <c r="AB909" s="1"/>
       <c r="AC909" s="1"/>
     </row>
-    <row r="910" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="910" spans="1:29" ht="13.2">
       <c r="A910" s="1"/>
       <c r="B910" s="1"/>
       <c r="C910" s="1"/>
@@ -29354,7 +29426,7 @@
       <c r="AB910" s="1"/>
       <c r="AC910" s="1"/>
     </row>
-    <row r="911" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="911" spans="1:29" ht="13.2">
       <c r="A911" s="1"/>
       <c r="B911" s="1"/>
       <c r="C911" s="1"/>
@@ -29385,7 +29457,7 @@
       <c r="AB911" s="1"/>
       <c r="AC911" s="1"/>
     </row>
-    <row r="912" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="912" spans="1:29" ht="13.2">
       <c r="A912" s="1"/>
       <c r="B912" s="1"/>
       <c r="C912" s="1"/>
@@ -29416,7 +29488,7 @@
       <c r="AB912" s="1"/>
       <c r="AC912" s="1"/>
     </row>
-    <row r="913" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="913" spans="1:29" ht="13.2">
       <c r="A913" s="1"/>
       <c r="B913" s="1"/>
       <c r="C913" s="1"/>
@@ -29447,7 +29519,7 @@
       <c r="AB913" s="1"/>
       <c r="AC913" s="1"/>
     </row>
-    <row r="914" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="914" spans="1:29" ht="13.2">
       <c r="A914" s="1"/>
       <c r="B914" s="1"/>
       <c r="C914" s="1"/>
@@ -29478,7 +29550,7 @@
       <c r="AB914" s="1"/>
       <c r="AC914" s="1"/>
     </row>
-    <row r="915" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="915" spans="1:29" ht="13.2">
       <c r="A915" s="1"/>
       <c r="B915" s="1"/>
       <c r="C915" s="1"/>
@@ -29509,7 +29581,7 @@
       <c r="AB915" s="1"/>
       <c r="AC915" s="1"/>
     </row>
-    <row r="916" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="916" spans="1:29" ht="13.2">
       <c r="A916" s="1"/>
       <c r="B916" s="1"/>
       <c r="C916" s="1"/>
@@ -29540,7 +29612,7 @@
       <c r="AB916" s="1"/>
       <c r="AC916" s="1"/>
     </row>
-    <row r="917" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="917" spans="1:29" ht="13.2">
       <c r="A917" s="1"/>
       <c r="B917" s="1"/>
       <c r="C917" s="1"/>
@@ -29571,7 +29643,7 @@
       <c r="AB917" s="1"/>
       <c r="AC917" s="1"/>
     </row>
-    <row r="918" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="918" spans="1:29" ht="13.2">
       <c r="A918" s="1"/>
       <c r="B918" s="1"/>
       <c r="C918" s="1"/>
@@ -29602,7 +29674,7 @@
       <c r="AB918" s="1"/>
       <c r="AC918" s="1"/>
     </row>
-    <row r="919" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="919" spans="1:29" ht="13.2">
       <c r="A919" s="1"/>
       <c r="B919" s="1"/>
       <c r="C919" s="1"/>
@@ -29633,7 +29705,7 @@
       <c r="AB919" s="1"/>
       <c r="AC919" s="1"/>
     </row>
-    <row r="920" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="920" spans="1:29" ht="13.2">
       <c r="A920" s="1"/>
       <c r="B920" s="1"/>
       <c r="C920" s="1"/>
@@ -29664,7 +29736,7 @@
       <c r="AB920" s="1"/>
       <c r="AC920" s="1"/>
     </row>
-    <row r="921" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="921" spans="1:29" ht="13.2">
       <c r="A921" s="1"/>
       <c r="B921" s="1"/>
       <c r="C921" s="1"/>
@@ -29695,7 +29767,7 @@
       <c r="AB921" s="1"/>
       <c r="AC921" s="1"/>
     </row>
-    <row r="922" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="922" spans="1:29" ht="13.2">
       <c r="A922" s="1"/>
       <c r="B922" s="1"/>
       <c r="C922" s="1"/>
@@ -29726,7 +29798,7 @@
       <c r="AB922" s="1"/>
       <c r="AC922" s="1"/>
     </row>
-    <row r="923" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="923" spans="1:29" ht="13.2">
       <c r="A923" s="1"/>
       <c r="B923" s="1"/>
       <c r="C923" s="1"/>
@@ -29757,7 +29829,7 @@
       <c r="AB923" s="1"/>
       <c r="AC923" s="1"/>
     </row>
-    <row r="924" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="924" spans="1:29" ht="13.2">
       <c r="A924" s="1"/>
       <c r="B924" s="1"/>
       <c r="C924" s="1"/>
@@ -29788,7 +29860,7 @@
       <c r="AB924" s="1"/>
       <c r="AC924" s="1"/>
     </row>
-    <row r="925" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="925" spans="1:29" ht="13.2">
       <c r="A925" s="1"/>
       <c r="B925" s="1"/>
       <c r="C925" s="1"/>
@@ -29819,7 +29891,7 @@
       <c r="AB925" s="1"/>
       <c r="AC925" s="1"/>
     </row>
-    <row r="926" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="926" spans="1:29" ht="13.2">
       <c r="A926" s="1"/>
       <c r="B926" s="1"/>
       <c r="C926" s="1"/>
@@ -29850,7 +29922,7 @@
       <c r="AB926" s="1"/>
       <c r="AC926" s="1"/>
     </row>
-    <row r="927" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="927" spans="1:29" ht="13.2">
       <c r="A927" s="1"/>
       <c r="B927" s="1"/>
       <c r="C927" s="1"/>
@@ -29881,7 +29953,7 @@
       <c r="AB927" s="1"/>
       <c r="AC927" s="1"/>
     </row>
-    <row r="928" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="928" spans="1:29" ht="13.2">
       <c r="A928" s="1"/>
       <c r="B928" s="1"/>
       <c r="C928" s="1"/>
@@ -29912,7 +29984,7 @@
       <c r="AB928" s="1"/>
       <c r="AC928" s="1"/>
     </row>
-    <row r="929" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="929" spans="1:29" ht="13.2">
       <c r="A929" s="1"/>
       <c r="B929" s="1"/>
       <c r="C929" s="1"/>
@@ -29943,7 +30015,7 @@
       <c r="AB929" s="1"/>
       <c r="AC929" s="1"/>
     </row>
-    <row r="930" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="930" spans="1:29" ht="13.2">
       <c r="A930" s="1"/>
       <c r="B930" s="1"/>
       <c r="C930" s="1"/>
@@ -29974,7 +30046,7 @@
       <c r="AB930" s="1"/>
       <c r="AC930" s="1"/>
     </row>
-    <row r="931" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="931" spans="1:29" ht="13.2">
       <c r="A931" s="1"/>
       <c r="B931" s="1"/>
       <c r="C931" s="1"/>
@@ -30005,7 +30077,7 @@
       <c r="AB931" s="1"/>
       <c r="AC931" s="1"/>
     </row>
-    <row r="932" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="932" spans="1:29" ht="13.2">
       <c r="A932" s="1"/>
       <c r="B932" s="1"/>
       <c r="C932" s="1"/>
@@ -30036,7 +30108,7 @@
       <c r="AB932" s="1"/>
       <c r="AC932" s="1"/>
     </row>
-    <row r="933" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="933" spans="1:29" ht="13.2">
       <c r="A933" s="1"/>
       <c r="B933" s="1"/>
       <c r="C933" s="1"/>
@@ -30067,7 +30139,7 @@
       <c r="AB933" s="1"/>
       <c r="AC933" s="1"/>
     </row>
-    <row r="934" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="934" spans="1:29" ht="13.2">
       <c r="A934" s="1"/>
       <c r="B934" s="1"/>
       <c r="C934" s="1"/>
@@ -30098,7 +30170,7 @@
       <c r="AB934" s="1"/>
       <c r="AC934" s="1"/>
     </row>
-    <row r="935" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="935" spans="1:29" ht="13.2">
       <c r="A935" s="1"/>
       <c r="B935" s="1"/>
       <c r="C935" s="1"/>
@@ -30129,7 +30201,7 @@
       <c r="AB935" s="1"/>
       <c r="AC935" s="1"/>
     </row>
-    <row r="936" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="936" spans="1:29" ht="13.2">
       <c r="A936" s="1"/>
       <c r="B936" s="1"/>
       <c r="C936" s="1"/>
@@ -30160,7 +30232,7 @@
       <c r="AB936" s="1"/>
       <c r="AC936" s="1"/>
     </row>
-    <row r="937" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="937" spans="1:29" ht="13.2">
       <c r="A937" s="1"/>
       <c r="B937" s="1"/>
       <c r="C937" s="1"/>
@@ -30191,7 +30263,7 @@
       <c r="AB937" s="1"/>
       <c r="AC937" s="1"/>
     </row>
-    <row r="938" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="938" spans="1:29" ht="13.2">
       <c r="A938" s="1"/>
       <c r="B938" s="1"/>
       <c r="C938" s="1"/>
@@ -30222,7 +30294,7 @@
       <c r="AB938" s="1"/>
       <c r="AC938" s="1"/>
     </row>
-    <row r="939" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="939" spans="1:29" ht="13.2">
       <c r="A939" s="1"/>
       <c r="B939" s="1"/>
       <c r="C939" s="1"/>
@@ -30253,7 +30325,7 @@
       <c r="AB939" s="1"/>
       <c r="AC939" s="1"/>
     </row>
-    <row r="940" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="940" spans="1:29" ht="13.2">
       <c r="A940" s="1"/>
       <c r="B940" s="1"/>
       <c r="C940" s="1"/>
@@ -30284,7 +30356,7 @@
       <c r="AB940" s="1"/>
       <c r="AC940" s="1"/>
     </row>
-    <row r="941" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="941" spans="1:29" ht="13.2">
       <c r="A941" s="1"/>
       <c r="B941" s="1"/>
       <c r="C941" s="1"/>
@@ -30315,7 +30387,7 @@
       <c r="AB941" s="1"/>
       <c r="AC941" s="1"/>
     </row>
-    <row r="942" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="942" spans="1:29" ht="13.2">
       <c r="A942" s="1"/>
       <c r="B942" s="1"/>
       <c r="C942" s="1"/>
@@ -30346,7 +30418,7 @@
       <c r="AB942" s="1"/>
       <c r="AC942" s="1"/>
     </row>
-    <row r="943" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="943" spans="1:29" ht="13.2">
       <c r="A943" s="1"/>
       <c r="B943" s="1"/>
       <c r="C943" s="1"/>
@@ -30377,7 +30449,7 @@
       <c r="AB943" s="1"/>
       <c r="AC943" s="1"/>
     </row>
-    <row r="944" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="944" spans="1:29" ht="13.2">
       <c r="A944" s="1"/>
       <c r="B944" s="1"/>
       <c r="C944" s="1"/>
@@ -30408,7 +30480,7 @@
       <c r="AB944" s="1"/>
       <c r="AC944" s="1"/>
     </row>
-    <row r="945" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="945" spans="1:29" ht="13.2">
       <c r="A945" s="1"/>
       <c r="B945" s="1"/>
       <c r="C945" s="1"/>
@@ -30439,7 +30511,7 @@
       <c r="AB945" s="1"/>
       <c r="AC945" s="1"/>
     </row>
-    <row r="946" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="946" spans="1:29" ht="13.2">
       <c r="A946" s="1"/>
       <c r="B946" s="1"/>
       <c r="C946" s="1"/>
@@ -30470,7 +30542,7 @@
       <c r="AB946" s="1"/>
       <c r="AC946" s="1"/>
     </row>
-    <row r="947" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="947" spans="1:29" ht="13.2">
       <c r="A947" s="1"/>
       <c r="B947" s="1"/>
       <c r="C947" s="1"/>
@@ -30501,7 +30573,7 @@
       <c r="AB947" s="1"/>
       <c r="AC947" s="1"/>
     </row>
-    <row r="948" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="948" spans="1:29" ht="13.2">
       <c r="A948" s="1"/>
       <c r="B948" s="1"/>
       <c r="C948" s="1"/>
@@ -30532,7 +30604,7 @@
       <c r="AB948" s="1"/>
       <c r="AC948" s="1"/>
     </row>
-    <row r="949" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="949" spans="1:29" ht="13.2">
       <c r="A949" s="1"/>
       <c r="B949" s="1"/>
       <c r="C949" s="1"/>
@@ -30563,7 +30635,7 @@
       <c r="AB949" s="1"/>
       <c r="AC949" s="1"/>
     </row>
-    <row r="950" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="950" spans="1:29" ht="13.2">
       <c r="A950" s="1"/>
       <c r="B950" s="1"/>
       <c r="C950" s="1"/>
@@ -30594,7 +30666,7 @@
       <c r="AB950" s="1"/>
       <c r="AC950" s="1"/>
     </row>
-    <row r="951" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="951" spans="1:29" ht="13.2">
       <c r="A951" s="1"/>
       <c r="B951" s="1"/>
       <c r="C951" s="1"/>
@@ -30625,7 +30697,7 @@
       <c r="AB951" s="1"/>
       <c r="AC951" s="1"/>
     </row>
-    <row r="952" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="952" spans="1:29" ht="13.2">
       <c r="A952" s="1"/>
       <c r="B952" s="1"/>
       <c r="C952" s="1"/>
@@ -30656,7 +30728,7 @@
       <c r="AB952" s="1"/>
       <c r="AC952" s="1"/>
     </row>
-    <row r="953" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="953" spans="1:29" ht="13.2">
       <c r="A953" s="1"/>
       <c r="B953" s="1"/>
       <c r="C953" s="1"/>
@@ -30687,7 +30759,7 @@
       <c r="AB953" s="1"/>
       <c r="AC953" s="1"/>
     </row>
-    <row r="954" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="954" spans="1:29" ht="13.2">
       <c r="A954" s="1"/>
       <c r="B954" s="1"/>
       <c r="C954" s="1"/>
@@ -30718,7 +30790,7 @@
       <c r="AB954" s="1"/>
       <c r="AC954" s="1"/>
     </row>
-    <row r="955" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="955" spans="1:29" ht="13.2">
       <c r="A955" s="1"/>
       <c r="B955" s="1"/>
       <c r="C955" s="1"/>
@@ -30749,7 +30821,7 @@
       <c r="AB955" s="1"/>
       <c r="AC955" s="1"/>
     </row>
-    <row r="956" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="956" spans="1:29" ht="13.2">
       <c r="A956" s="1"/>
       <c r="B956" s="1"/>
       <c r="C956" s="1"/>
@@ -30780,7 +30852,7 @@
       <c r="AB956" s="1"/>
       <c r="AC956" s="1"/>
     </row>
-    <row r="957" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="957" spans="1:29" ht="13.2">
       <c r="A957" s="1"/>
       <c r="B957" s="1"/>
       <c r="C957" s="1"/>
@@ -30811,7 +30883,7 @@
       <c r="AB957" s="1"/>
       <c r="AC957" s="1"/>
     </row>
-    <row r="958" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="958" spans="1:29" ht="13.2">
       <c r="A958" s="1"/>
       <c r="B958" s="1"/>
       <c r="C958" s="1"/>
@@ -30842,7 +30914,7 @@
       <c r="AB958" s="1"/>
       <c r="AC958" s="1"/>
     </row>
-    <row r="959" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="959" spans="1:29" ht="13.2">
       <c r="A959" s="1"/>
       <c r="B959" s="1"/>
       <c r="C959" s="1"/>
@@ -30873,7 +30945,7 @@
       <c r="AB959" s="1"/>
       <c r="AC959" s="1"/>
     </row>
-    <row r="960" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="960" spans="1:29" ht="13.2">
       <c r="A960" s="1"/>
       <c r="B960" s="1"/>
       <c r="C960" s="1"/>
@@ -30904,7 +30976,7 @@
       <c r="AB960" s="1"/>
       <c r="AC960" s="1"/>
     </row>
-    <row r="961" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="961" spans="1:29" ht="13.2">
       <c r="A961" s="1"/>
       <c r="B961" s="1"/>
       <c r="C961" s="1"/>
@@ -30935,7 +31007,7 @@
       <c r="AB961" s="1"/>
       <c r="AC961" s="1"/>
     </row>
-    <row r="962" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="962" spans="1:29" ht="13.2">
       <c r="A962" s="1"/>
       <c r="B962" s="1"/>
       <c r="C962" s="1"/>
@@ -30966,7 +31038,7 @@
       <c r="AB962" s="1"/>
       <c r="AC962" s="1"/>
     </row>
-    <row r="963" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="963" spans="1:29" ht="13.2">
       <c r="A963" s="1"/>
       <c r="B963" s="1"/>
       <c r="C963" s="1"/>
@@ -30997,7 +31069,7 @@
       <c r="AB963" s="1"/>
       <c r="AC963" s="1"/>
     </row>
-    <row r="964" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="964" spans="1:29" ht="13.2">
       <c r="A964" s="1"/>
       <c r="B964" s="1"/>
       <c r="C964" s="1"/>
@@ -31028,7 +31100,7 @@
       <c r="AB964" s="1"/>
       <c r="AC964" s="1"/>
     </row>
-    <row r="965" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="965" spans="1:29" ht="13.2">
       <c r="A965" s="1"/>
       <c r="B965" s="1"/>
       <c r="C965" s="1"/>
@@ -31059,7 +31131,7 @@
       <c r="AB965" s="1"/>
       <c r="AC965" s="1"/>
     </row>
-    <row r="966" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="966" spans="1:29" ht="13.2">
       <c r="A966" s="1"/>
       <c r="B966" s="1"/>
       <c r="C966" s="1"/>
@@ -31090,7 +31162,7 @@
       <c r="AB966" s="1"/>
       <c r="AC966" s="1"/>
     </row>
-    <row r="967" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="967" spans="1:29" ht="13.2">
       <c r="A967" s="1"/>
       <c r="B967" s="1"/>
       <c r="C967" s="1"/>
@@ -31121,7 +31193,7 @@
       <c r="AB967" s="1"/>
       <c r="AC967" s="1"/>
     </row>
-    <row r="968" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="968" spans="1:29" ht="13.2">
       <c r="A968" s="1"/>
       <c r="B968" s="1"/>
       <c r="C968" s="1"/>
@@ -31152,7 +31224,7 @@
       <c r="AB968" s="1"/>
       <c r="AC968" s="1"/>
     </row>
-    <row r="969" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="969" spans="1:29" ht="13.2">
       <c r="A969" s="1"/>
       <c r="B969" s="1"/>
       <c r="C969" s="1"/>
@@ -31183,7 +31255,7 @@
       <c r="AB969" s="1"/>
       <c r="AC969" s="1"/>
     </row>
-    <row r="970" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="970" spans="1:29" ht="13.2">
       <c r="A970" s="1"/>
       <c r="B970" s="1"/>
       <c r="C970" s="1"/>
@@ -31214,7 +31286,7 @@
       <c r="AB970" s="1"/>
       <c r="AC970" s="1"/>
     </row>
-    <row r="971" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="971" spans="1:29" ht="13.2">
       <c r="A971" s="1"/>
       <c r="B971" s="1"/>
       <c r="C971" s="1"/>
@@ -31245,7 +31317,7 @@
       <c r="AB971" s="1"/>
       <c r="AC971" s="1"/>
     </row>
-    <row r="972" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="972" spans="1:29" ht="13.2">
       <c r="A972" s="1"/>
       <c r="B972" s="1"/>
       <c r="C972" s="1"/>
@@ -31276,7 +31348,7 @@
       <c r="AB972" s="1"/>
       <c r="AC972" s="1"/>
     </row>
-    <row r="973" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="973" spans="1:29" ht="13.2">
       <c r="A973" s="1"/>
       <c r="B973" s="1"/>
       <c r="C973" s="1"/>
@@ -31307,7 +31379,7 @@
       <c r="AB973" s="1"/>
       <c r="AC973" s="1"/>
     </row>
-    <row r="974" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="974" spans="1:29" ht="13.2">
       <c r="A974" s="1"/>
       <c r="B974" s="1"/>
       <c r="C974" s="1"/>
@@ -31338,7 +31410,7 @@
       <c r="AB974" s="1"/>
       <c r="AC974" s="1"/>
     </row>
-    <row r="975" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="975" spans="1:29" ht="13.2">
       <c r="A975" s="1"/>
       <c r="B975" s="1"/>
       <c r="C975" s="1"/>
@@ -31369,7 +31441,7 @@
       <c r="AB975" s="1"/>
       <c r="AC975" s="1"/>
     </row>
-    <row r="976" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="976" spans="1:29" ht="13.2">
       <c r="A976" s="1"/>
       <c r="B976" s="1"/>
       <c r="C976" s="1"/>
@@ -31400,7 +31472,7 @@
       <c r="AB976" s="1"/>
       <c r="AC976" s="1"/>
     </row>
-    <row r="977" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="977" spans="1:29" ht="13.2">
       <c r="A977" s="1"/>
       <c r="B977" s="1"/>
       <c r="C977" s="1"/>
@@ -31431,7 +31503,7 @@
       <c r="AB977" s="1"/>
       <c r="AC977" s="1"/>
     </row>
-    <row r="978" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="978" spans="1:29" ht="13.2">
       <c r="A978" s="1"/>
       <c r="B978" s="1"/>
       <c r="C978" s="1"/>
@@ -31462,7 +31534,7 @@
       <c r="AB978" s="1"/>
       <c r="AC978" s="1"/>
     </row>
-    <row r="979" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="979" spans="1:29" ht="13.2">
       <c r="A979" s="1"/>
       <c r="B979" s="1"/>
       <c r="C979" s="1"/>
@@ -31493,7 +31565,7 @@
       <c r="AB979" s="1"/>
       <c r="AC979" s="1"/>
     </row>
-    <row r="980" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="980" spans="1:29" ht="13.2">
       <c r="A980" s="1"/>
       <c r="B980" s="1"/>
       <c r="C980" s="1"/>
@@ -31524,7 +31596,7 @@
       <c r="AB980" s="1"/>
       <c r="AC980" s="1"/>
     </row>
-    <row r="981" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="981" spans="1:29" ht="13.2">
       <c r="A981" s="1"/>
       <c r="B981" s="1"/>
       <c r="C981" s="1"/>
@@ -31555,7 +31627,7 @@
       <c r="AB981" s="1"/>
       <c r="AC981" s="1"/>
     </row>
-    <row r="982" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="982" spans="1:29" ht="13.2">
       <c r="A982" s="1"/>
       <c r="B982" s="1"/>
       <c r="C982" s="1"/>
@@ -31586,7 +31658,7 @@
       <c r="AB982" s="1"/>
       <c r="AC982" s="1"/>
     </row>
-    <row r="983" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="983" spans="1:29" ht="13.2">
       <c r="A983" s="1"/>
       <c r="B983" s="1"/>
       <c r="C983" s="1"/>
@@ -31617,7 +31689,7 @@
       <c r="AB983" s="1"/>
       <c r="AC983" s="1"/>
     </row>
-    <row r="984" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="984" spans="1:29" ht="13.2">
       <c r="A984" s="1"/>
       <c r="B984" s="1"/>
       <c r="C984" s="1"/>
@@ -31648,7 +31720,7 @@
       <c r="AB984" s="1"/>
       <c r="AC984" s="1"/>
     </row>
-    <row r="985" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="985" spans="1:29" ht="13.2">
       <c r="A985" s="1"/>
       <c r="B985" s="1"/>
       <c r="C985" s="1"/>
@@ -31679,7 +31751,7 @@
       <c r="AB985" s="1"/>
       <c r="AC985" s="1"/>
     </row>
-    <row r="986" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="986" spans="1:29" ht="13.2">
       <c r="A986" s="1"/>
       <c r="B986" s="1"/>
       <c r="C986" s="1"/>
@@ -31710,7 +31782,7 @@
       <c r="AB986" s="1"/>
       <c r="AC986" s="1"/>
     </row>
-    <row r="987" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="987" spans="1:29" ht="13.2">
       <c r="A987" s="1"/>
       <c r="B987" s="1"/>
       <c r="C987" s="1"/>
@@ -31741,7 +31813,7 @@
       <c r="AB987" s="1"/>
       <c r="AC987" s="1"/>
     </row>
-    <row r="988" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="988" spans="1:29" ht="13.2">
       <c r="A988" s="1"/>
       <c r="B988" s="1"/>
       <c r="C988" s="1"/>
@@ -31772,7 +31844,7 @@
       <c r="AB988" s="1"/>
       <c r="AC988" s="1"/>
     </row>
-    <row r="989" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="989" spans="1:29" ht="13.2">
       <c r="A989" s="1"/>
       <c r="B989" s="1"/>
       <c r="C989" s="1"/>
@@ -31803,7 +31875,7 @@
       <c r="AB989" s="1"/>
       <c r="AC989" s="1"/>
     </row>
-    <row r="990" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="990" spans="1:29" ht="13.2">
       <c r="A990" s="1"/>
       <c r="B990" s="1"/>
       <c r="C990" s="1"/>
@@ -31834,7 +31906,7 @@
       <c r="AB990" s="1"/>
       <c r="AC990" s="1"/>
     </row>
-    <row r="991" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="991" spans="1:29" ht="13.2">
       <c r="A991" s="1"/>
       <c r="B991" s="1"/>
       <c r="C991" s="1"/>
@@ -31865,7 +31937,7 @@
       <c r="AB991" s="1"/>
       <c r="AC991" s="1"/>
     </row>
-    <row r="992" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="992" spans="1:29" ht="13.2">
       <c r="A992" s="1"/>
       <c r="B992" s="1"/>
       <c r="C992" s="1"/>
@@ -31896,7 +31968,7 @@
       <c r="AB992" s="1"/>
       <c r="AC992" s="1"/>
     </row>
-    <row r="993" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="993" spans="1:29" ht="13.2">
       <c r="A993" s="1"/>
       <c r="B993" s="1"/>
       <c r="C993" s="1"/>
@@ -31927,7 +31999,7 @@
       <c r="AB993" s="1"/>
       <c r="AC993" s="1"/>
     </row>
-    <row r="994" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="994" spans="1:29" ht="13.2">
       <c r="A994" s="1"/>
       <c r="B994" s="1"/>
       <c r="C994" s="1"/>
@@ -31958,7 +32030,7 @@
       <c r="AB994" s="1"/>
       <c r="AC994" s="1"/>
     </row>
-    <row r="995" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="995" spans="1:29" ht="13.2">
       <c r="A995" s="1"/>
       <c r="B995" s="1"/>
       <c r="C995" s="1"/>
@@ -31989,7 +32061,7 @@
       <c r="AB995" s="1"/>
       <c r="AC995" s="1"/>
     </row>
-    <row r="996" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="996" spans="1:29" ht="13.2">
       <c r="A996" s="1"/>
       <c r="B996" s="1"/>
       <c r="C996" s="1"/>
@@ -32020,7 +32092,7 @@
       <c r="AB996" s="1"/>
       <c r="AC996" s="1"/>
     </row>
-    <row r="997" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="997" spans="1:29" ht="13.2">
       <c r="A997" s="1"/>
       <c r="B997" s="1"/>
       <c r="C997" s="1"/>
@@ -32051,7 +32123,7 @@
       <c r="AB997" s="1"/>
       <c r="AC997" s="1"/>
     </row>
-    <row r="998" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="998" spans="1:29" ht="13.2">
       <c r="A998" s="1"/>
       <c r="B998" s="1"/>
       <c r="C998" s="1"/>
@@ -32082,7 +32154,7 @@
       <c r="AB998" s="1"/>
       <c r="AC998" s="1"/>
     </row>
-    <row r="999" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="999" spans="1:29" ht="13.2">
       <c r="A999" s="1"/>
       <c r="B999" s="1"/>
       <c r="C999" s="1"/>
@@ -32113,7 +32185,7 @@
       <c r="AB999" s="1"/>
       <c r="AC999" s="1"/>
     </row>
-    <row r="1000" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="1000" spans="1:29" ht="13.2">
       <c r="A1000" s="1"/>
       <c r="B1000" s="1"/>
       <c r="C1000" s="1"/>
@@ -32144,7 +32216,7 @@
       <c r="AB1000" s="1"/>
       <c r="AC1000" s="1"/>
     </row>
-    <row r="1001" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="1001" spans="1:29" ht="13.2">
       <c r="A1001" s="1"/>
       <c r="B1001" s="1"/>
       <c r="C1001" s="1"/>

--- a/LubanConfig/DataTables/Datas/#ArtifactParam.xlsx
+++ b/LubanConfig/DataTables/Datas/#ArtifactParam.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\monster-ball\LubanConfig\DataTables\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\601\monster-ball\LubanConfig\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7C2736F-42ED-444C-ADB1-E8D23982F7B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A7D1785-4DBF-484B-9B9A-508140F72185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ArtifactParam" sheetId="1" r:id="rId1"/>
@@ -241,7 +241,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="88">
   <si>
     <t>##var</t>
   </si>
@@ -309,6 +309,9 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>Pheonixfeather</t>
+  </si>
+  <si>
     <t>Invester</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -344,6 +347,9 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>Splitfire</t>
+  </si>
+  <si>
     <t>Splitball</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -356,6 +362,9 @@
   </si>
   <si>
     <t>Increase the size of the fire trail left by the fireball by 30%</t>
+  </si>
+  <si>
+    <t>FireCoal</t>
   </si>
   <si>
     <t>Increase fireball's firetrail uptime by 30% when triggered.</t>
@@ -553,55 +562,12 @@
     <t>LightingReq</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
-  <si>
-    <t>EverlastingCoal</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>PheonixFeather</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ExtraFuel</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>HologramProjector</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SplitFire</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>EmailNotification</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>EyeOfFrost</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>LightningRod</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>StormCaller</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>BountifulSupply</t>
-  </si>
-  <si>
-    <t>BottledThunder</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -665,18 +631,12 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -691,7 +651,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -711,15 +671,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -936,19 +890,18 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AC1001"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="17.33203125" customWidth="1"/>
-    <col min="5" max="5" width="18.6640625" customWidth="1"/>
-    <col min="6" max="6" width="71.88671875" customWidth="1"/>
-    <col min="7" max="7" width="20.109375" customWidth="1"/>
-    <col min="8" max="8" width="15.33203125" customWidth="1"/>
-    <col min="10" max="10" width="14.33203125" customWidth="1"/>
-    <col min="13" max="13" width="18" customWidth="1"/>
+    <col min="4" max="4" width="17.28515625" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" customWidth="1"/>
+    <col min="6" max="6" width="71.85546875" customWidth="1"/>
+    <col min="7" max="7" width="20.140625" customWidth="1"/>
+    <col min="8" max="8" width="15.28515625" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="15.75" customHeight="1">
+    <row r="1" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -959,7 +912,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>2</v>
@@ -1004,7 +957,7 @@
       <c r="AB1" s="1"/>
       <c r="AC1" s="1"/>
     </row>
-    <row r="2" spans="1:29" ht="15.75" customHeight="1">
+    <row r="2" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -1012,7 +965,7 @@
         <v>13</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>6</v>
@@ -1027,19 +980,19 @@
         <v>11</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>11</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>11</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M2" s="2" t="s">
         <v>11</v>
@@ -1060,7 +1013,7 @@
       <c r="AB2" s="1"/>
       <c r="AC2" s="1"/>
     </row>
-    <row r="3" spans="1:29" ht="15.75" customHeight="1">
+    <row r="3" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -1092,7 +1045,7 @@
       <c r="AB3" s="1"/>
       <c r="AC3" s="1"/>
     </row>
-    <row r="4" spans="1:29" ht="15.75" customHeight="1">
+    <row r="4" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -1124,25 +1077,25 @@
       <c r="AB4" s="1"/>
       <c r="AC4" s="1"/>
     </row>
-    <row r="5" spans="1:29" ht="15.75" customHeight="1">
+    <row r="5" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>0</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>9</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H5" s="1">
         <v>1.3</v>
@@ -1151,8 +1104,8 @@
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
-      <c r="M5" s="7" t="s">
-        <v>86</v>
+      <c r="M5" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="O5" s="1"/>
       <c r="P5" s="1"/>
@@ -1170,33 +1123,33 @@
       <c r="AB5" s="1"/>
       <c r="AC5" s="1"/>
     </row>
-    <row r="6" spans="1:29" ht="15.75" customHeight="1">
+    <row r="6" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6" s="1">
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>9</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="H6" s="5">
         <v>1.3</v>
       </c>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
-      <c r="M6" s="7" t="s">
-        <v>85</v>
+      <c r="M6" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
@@ -1214,34 +1167,31 @@
       <c r="AB6" s="1"/>
       <c r="AC6" s="1"/>
     </row>
-    <row r="7" spans="1:29" ht="30" customHeight="1">
+    <row r="7" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
       <c r="B7" s="1">
         <v>2</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>9</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="H7" s="5">
         <v>1.3</v>
       </c>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
-      <c r="M7" s="7" t="s">
-        <v>87</v>
-      </c>
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
@@ -1258,40 +1208,37 @@
       <c r="AB7" s="1"/>
       <c r="AC7" s="1"/>
     </row>
-    <row r="8" spans="1:29" ht="15.75" customHeight="1">
+    <row r="8" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
       <c r="B8" s="1">
         <v>3</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H8" s="1">
         <v>1.5</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J8" s="5">
         <v>0.7</v>
       </c>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
-      <c r="M8" s="7" t="s">
-        <v>88</v>
-      </c>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
@@ -1308,34 +1255,31 @@
       <c r="AB8" s="1"/>
       <c r="AC8" s="1"/>
     </row>
-    <row r="9" spans="1:29" ht="15.75" customHeight="1">
+    <row r="9" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
       <c r="B9" s="1">
         <v>4</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H9" s="1">
         <v>1.3</v>
       </c>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
-      <c r="M9" s="7" t="s">
-        <v>94</v>
-      </c>
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
@@ -1352,25 +1296,25 @@
       <c r="AB9" s="1"/>
       <c r="AC9" s="1"/>
     </row>
-    <row r="10" spans="1:29" ht="15.75" customHeight="1">
+    <row r="10" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
       <c r="B10" s="1">
         <v>5</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H10" s="1">
         <v>0.7</v>
@@ -1379,8 +1323,8 @@
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
-      <c r="M10" s="7" t="s">
-        <v>89</v>
+      <c r="M10" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
@@ -1398,25 +1342,25 @@
       <c r="AB10" s="1"/>
       <c r="AC10" s="1"/>
     </row>
-    <row r="11" spans="1:29" ht="15.75" customHeight="1">
+    <row r="11" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
       <c r="B11" s="1">
         <v>6</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H11" s="1">
         <v>1.3</v>
@@ -1425,9 +1369,7 @@
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
-      <c r="M11" s="7" t="s">
-        <v>90</v>
-      </c>
+      <c r="M11" s="1"/>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
@@ -1445,25 +1387,25 @@
       <c r="AB11" s="1"/>
       <c r="AC11" s="1"/>
     </row>
-    <row r="12" spans="1:29" ht="15.75" customHeight="1">
+    <row r="12" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
       <c r="B12" s="1">
         <v>7</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="H12" s="1">
         <v>1.3</v>
@@ -1472,9 +1414,7 @@
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
-      <c r="M12" s="7" t="s">
-        <v>91</v>
-      </c>
+      <c r="M12" s="1"/>
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
@@ -1492,37 +1432,34 @@
       <c r="AB12" s="1"/>
       <c r="AC12" s="1"/>
     </row>
-    <row r="13" spans="1:29" ht="15.75" customHeight="1">
+    <row r="13" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
       <c r="B13" s="1">
         <v>8</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H13" s="1">
         <v>1.3</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J13" s="5">
         <v>1.5</v>
-      </c>
-      <c r="M13" s="8" t="s">
-        <v>70</v>
       </c>
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
@@ -1541,37 +1478,34 @@
       <c r="AB13" s="1"/>
       <c r="AC13" s="1"/>
     </row>
-    <row r="14" spans="1:29" ht="28.5" customHeight="1">
+    <row r="14" spans="1:29" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
       <c r="B14" s="1">
         <v>9</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="H14" s="1">
         <v>1.3</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J14" s="5">
         <v>1.4</v>
-      </c>
-      <c r="M14" s="7" t="s">
-        <v>92</v>
       </c>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
@@ -1590,37 +1524,34 @@
       <c r="AB14" s="1"/>
       <c r="AC14" s="1"/>
     </row>
-    <row r="15" spans="1:29" ht="32.25" customHeight="1">
+    <row r="15" spans="1:29" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
       <c r="B15" s="1">
         <v>10</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="H15" s="1">
         <v>0.6</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J15" s="5">
         <v>0.5</v>
-      </c>
-      <c r="M15" s="7" t="s">
-        <v>93</v>
       </c>
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
@@ -1639,37 +1570,34 @@
       <c r="AB15" s="1"/>
       <c r="AC15" s="1"/>
     </row>
-    <row r="16" spans="1:29" ht="15.75" customHeight="1">
+    <row r="16" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1"/>
       <c r="B16" s="1">
         <v>11</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H16" s="1">
         <v>0.7</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="J16" s="5">
         <v>0.7</v>
-      </c>
-      <c r="M16" s="7" t="s">
-        <v>95</v>
       </c>
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
@@ -1688,23 +1616,23 @@
       <c r="AB16" s="1"/>
       <c r="AC16" s="1"/>
     </row>
-    <row r="17" spans="1:29" ht="15.75" customHeight="1">
+    <row r="17" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1"/>
       <c r="B17" s="1">
         <v>12</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H17" s="1">
         <v>200</v>
@@ -1713,8 +1641,8 @@
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
-      <c r="M17" s="8" t="s">
-        <v>19</v>
+      <c r="M17" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
@@ -1733,37 +1661,37 @@
       <c r="AB17" s="1"/>
       <c r="AC17" s="1"/>
     </row>
-    <row r="18" spans="1:29" ht="15.75" customHeight="1">
+    <row r="18" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1"/>
       <c r="B18" s="1">
         <v>13</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H18" s="1">
         <v>50</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J18" s="1">
         <v>30</v>
       </c>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
-      <c r="M18" s="8" t="s">
-        <v>22</v>
+      <c r="M18" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
@@ -1782,23 +1710,23 @@
       <c r="AB18" s="1"/>
       <c r="AC18" s="1"/>
     </row>
-    <row r="19" spans="1:29" ht="35.25" customHeight="1">
+    <row r="19" spans="1:29" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1"/>
       <c r="B19" s="1">
         <v>14</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H19" s="1">
         <v>100</v>
@@ -1807,8 +1735,8 @@
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
-      <c r="M19" s="7" t="s">
-        <v>26</v>
+      <c r="M19" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
@@ -1827,7 +1755,7 @@
       <c r="AB19" s="1"/>
       <c r="AC19" s="1"/>
     </row>
-    <row r="20" spans="1:29" ht="15.75" customHeight="1">
+    <row r="20" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="N20" s="1"/>
@@ -1847,7 +1775,7 @@
       <c r="AB20" s="1"/>
       <c r="AC20" s="1"/>
     </row>
-    <row r="21" spans="1:29" ht="15.75" customHeight="1">
+    <row r="21" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="N21" s="1"/>
@@ -1867,7 +1795,7 @@
       <c r="AB21" s="1"/>
       <c r="AC21" s="1"/>
     </row>
-    <row r="22" spans="1:29" ht="15.75" customHeight="1">
+    <row r="22" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -1898,7 +1826,7 @@
       <c r="AB22" s="1"/>
       <c r="AC22" s="1"/>
     </row>
-    <row r="23" spans="1:29" ht="15.75" customHeight="1">
+    <row r="23" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -1929,7 +1857,7 @@
       <c r="AB23" s="1"/>
       <c r="AC23" s="1"/>
     </row>
-    <row r="24" spans="1:29" ht="15.75" customHeight="1">
+    <row r="24" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -1960,7 +1888,7 @@
       <c r="AB24" s="1"/>
       <c r="AC24" s="1"/>
     </row>
-    <row r="25" spans="1:29" ht="15.75" customHeight="1">
+    <row r="25" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -1991,7 +1919,7 @@
       <c r="AB25" s="1"/>
       <c r="AC25" s="1"/>
     </row>
-    <row r="26" spans="1:29" ht="15.75" customHeight="1">
+    <row r="26" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -2022,7 +1950,7 @@
       <c r="AB26" s="1"/>
       <c r="AC26" s="1"/>
     </row>
-    <row r="27" spans="1:29" ht="15.75" customHeight="1">
+    <row r="27" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -2053,7 +1981,7 @@
       <c r="AB27" s="1"/>
       <c r="AC27" s="1"/>
     </row>
-    <row r="28" spans="1:29" ht="15.75" customHeight="1">
+    <row r="28" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -2084,7 +2012,7 @@
       <c r="AB28" s="1"/>
       <c r="AC28" s="1"/>
     </row>
-    <row r="29" spans="1:29" ht="15.75" customHeight="1">
+    <row r="29" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -2115,7 +2043,7 @@
       <c r="AB29" s="1"/>
       <c r="AC29" s="1"/>
     </row>
-    <row r="30" spans="1:29" ht="15.75" customHeight="1">
+    <row r="30" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -2146,7 +2074,7 @@
       <c r="AB30" s="1"/>
       <c r="AC30" s="1"/>
     </row>
-    <row r="31" spans="1:29" ht="15.75" customHeight="1">
+    <row r="31" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -2177,7 +2105,7 @@
       <c r="AB31" s="1"/>
       <c r="AC31" s="1"/>
     </row>
-    <row r="32" spans="1:29" ht="15.75" customHeight="1">
+    <row r="32" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -2208,7 +2136,7 @@
       <c r="AB32" s="1"/>
       <c r="AC32" s="1"/>
     </row>
-    <row r="33" spans="1:29" ht="15.75" customHeight="1">
+    <row r="33" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -2239,7 +2167,7 @@
       <c r="AB33" s="1"/>
       <c r="AC33" s="1"/>
     </row>
-    <row r="34" spans="1:29" ht="15.75" customHeight="1">
+    <row r="34" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -2270,7 +2198,7 @@
       <c r="AB34" s="1"/>
       <c r="AC34" s="1"/>
     </row>
-    <row r="35" spans="1:29" ht="15.75" customHeight="1">
+    <row r="35" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -2301,7 +2229,7 @@
       <c r="AB35" s="1"/>
       <c r="AC35" s="1"/>
     </row>
-    <row r="36" spans="1:29" ht="15.75" customHeight="1">
+    <row r="36" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -2332,7 +2260,7 @@
       <c r="AB36" s="1"/>
       <c r="AC36" s="1"/>
     </row>
-    <row r="37" spans="1:29" ht="15.75" customHeight="1">
+    <row r="37" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -2363,7 +2291,7 @@
       <c r="AB37" s="1"/>
       <c r="AC37" s="1"/>
     </row>
-    <row r="38" spans="1:29" ht="15.75" customHeight="1">
+    <row r="38" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -2394,7 +2322,7 @@
       <c r="AB38" s="1"/>
       <c r="AC38" s="1"/>
     </row>
-    <row r="39" spans="1:29" ht="15.75" customHeight="1">
+    <row r="39" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -2425,7 +2353,7 @@
       <c r="AB39" s="1"/>
       <c r="AC39" s="1"/>
     </row>
-    <row r="40" spans="1:29" ht="15.75" customHeight="1">
+    <row r="40" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -2456,7 +2384,7 @@
       <c r="AB40" s="1"/>
       <c r="AC40" s="1"/>
     </row>
-    <row r="41" spans="1:29" ht="15.75" customHeight="1">
+    <row r="41" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -2487,7 +2415,7 @@
       <c r="AB41" s="1"/>
       <c r="AC41" s="1"/>
     </row>
-    <row r="42" spans="1:29" ht="15.75" customHeight="1">
+    <row r="42" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -2518,7 +2446,7 @@
       <c r="AB42" s="1"/>
       <c r="AC42" s="1"/>
     </row>
-    <row r="43" spans="1:29" ht="15.75" customHeight="1">
+    <row r="43" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -2549,7 +2477,7 @@
       <c r="AB43" s="1"/>
       <c r="AC43" s="1"/>
     </row>
-    <row r="44" spans="1:29" ht="15.75" customHeight="1">
+    <row r="44" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -2580,7 +2508,7 @@
       <c r="AB44" s="1"/>
       <c r="AC44" s="1"/>
     </row>
-    <row r="45" spans="1:29" ht="15.75" customHeight="1">
+    <row r="45" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -2611,7 +2539,7 @@
       <c r="AB45" s="1"/>
       <c r="AC45" s="1"/>
     </row>
-    <row r="46" spans="1:29" ht="15.75" customHeight="1">
+    <row r="46" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -2642,7 +2570,7 @@
       <c r="AB46" s="1"/>
       <c r="AC46" s="1"/>
     </row>
-    <row r="47" spans="1:29" ht="15.75" customHeight="1">
+    <row r="47" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -2673,7 +2601,7 @@
       <c r="AB47" s="1"/>
       <c r="AC47" s="1"/>
     </row>
-    <row r="48" spans="1:29" ht="15.75" customHeight="1">
+    <row r="48" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -2704,7 +2632,7 @@
       <c r="AB48" s="1"/>
       <c r="AC48" s="1"/>
     </row>
-    <row r="49" spans="1:29" ht="15.75" customHeight="1">
+    <row r="49" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -2735,7 +2663,7 @@
       <c r="AB49" s="1"/>
       <c r="AC49" s="1"/>
     </row>
-    <row r="50" spans="1:29" ht="15.75" customHeight="1">
+    <row r="50" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -2766,7 +2694,7 @@
       <c r="AB50" s="1"/>
       <c r="AC50" s="1"/>
     </row>
-    <row r="51" spans="1:29" ht="15.75" customHeight="1">
+    <row r="51" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -2797,7 +2725,7 @@
       <c r="AB51" s="1"/>
       <c r="AC51" s="1"/>
     </row>
-    <row r="52" spans="1:29" ht="15.75" customHeight="1">
+    <row r="52" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -2828,7 +2756,7 @@
       <c r="AB52" s="1"/>
       <c r="AC52" s="1"/>
     </row>
-    <row r="53" spans="1:29" ht="15.75" customHeight="1">
+    <row r="53" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -2859,7 +2787,7 @@
       <c r="AB53" s="1"/>
       <c r="AC53" s="1"/>
     </row>
-    <row r="54" spans="1:29" ht="15.75" customHeight="1">
+    <row r="54" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -2890,7 +2818,7 @@
       <c r="AB54" s="1"/>
       <c r="AC54" s="1"/>
     </row>
-    <row r="55" spans="1:29" ht="15.75" customHeight="1">
+    <row r="55" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -2921,7 +2849,7 @@
       <c r="AB55" s="1"/>
       <c r="AC55" s="1"/>
     </row>
-    <row r="56" spans="1:29" ht="15.75" customHeight="1">
+    <row r="56" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -2952,7 +2880,7 @@
       <c r="AB56" s="1"/>
       <c r="AC56" s="1"/>
     </row>
-    <row r="57" spans="1:29" ht="15.75" customHeight="1">
+    <row r="57" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -2983,7 +2911,7 @@
       <c r="AB57" s="1"/>
       <c r="AC57" s="1"/>
     </row>
-    <row r="58" spans="1:29" ht="15.75" customHeight="1">
+    <row r="58" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -3014,7 +2942,7 @@
       <c r="AB58" s="1"/>
       <c r="AC58" s="1"/>
     </row>
-    <row r="59" spans="1:29" ht="15.75" customHeight="1">
+    <row r="59" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -3045,7 +2973,7 @@
       <c r="AB59" s="1"/>
       <c r="AC59" s="1"/>
     </row>
-    <row r="60" spans="1:29" ht="15.75" customHeight="1">
+    <row r="60" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -3076,7 +3004,7 @@
       <c r="AB60" s="1"/>
       <c r="AC60" s="1"/>
     </row>
-    <row r="61" spans="1:29" ht="15.75" customHeight="1">
+    <row r="61" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -3107,7 +3035,7 @@
       <c r="AB61" s="1"/>
       <c r="AC61" s="1"/>
     </row>
-    <row r="62" spans="1:29" ht="15.75" customHeight="1">
+    <row r="62" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -3138,7 +3066,7 @@
       <c r="AB62" s="1"/>
       <c r="AC62" s="1"/>
     </row>
-    <row r="63" spans="1:29" ht="15.75" customHeight="1">
+    <row r="63" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -3169,7 +3097,7 @@
       <c r="AB63" s="1"/>
       <c r="AC63" s="1"/>
     </row>
-    <row r="64" spans="1:29" ht="13.2">
+    <row r="64" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -3200,7 +3128,7 @@
       <c r="AB64" s="1"/>
       <c r="AC64" s="1"/>
     </row>
-    <row r="65" spans="1:29" ht="13.2">
+    <row r="65" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -3231,7 +3159,7 @@
       <c r="AB65" s="1"/>
       <c r="AC65" s="1"/>
     </row>
-    <row r="66" spans="1:29" ht="13.2">
+    <row r="66" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -3262,7 +3190,7 @@
       <c r="AB66" s="1"/>
       <c r="AC66" s="1"/>
     </row>
-    <row r="67" spans="1:29" ht="13.2">
+    <row r="67" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -3293,7 +3221,7 @@
       <c r="AB67" s="1"/>
       <c r="AC67" s="1"/>
     </row>
-    <row r="68" spans="1:29" ht="13.2">
+    <row r="68" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -3324,7 +3252,7 @@
       <c r="AB68" s="1"/>
       <c r="AC68" s="1"/>
     </row>
-    <row r="69" spans="1:29" ht="13.2">
+    <row r="69" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -3355,7 +3283,7 @@
       <c r="AB69" s="1"/>
       <c r="AC69" s="1"/>
     </row>
-    <row r="70" spans="1:29" ht="13.2">
+    <row r="70" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -3386,7 +3314,7 @@
       <c r="AB70" s="1"/>
       <c r="AC70" s="1"/>
     </row>
-    <row r="71" spans="1:29" ht="13.2">
+    <row r="71" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -3417,7 +3345,7 @@
       <c r="AB71" s="1"/>
       <c r="AC71" s="1"/>
     </row>
-    <row r="72" spans="1:29" ht="13.2">
+    <row r="72" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -3448,7 +3376,7 @@
       <c r="AB72" s="1"/>
       <c r="AC72" s="1"/>
     </row>
-    <row r="73" spans="1:29" ht="13.2">
+    <row r="73" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -3479,7 +3407,7 @@
       <c r="AB73" s="1"/>
       <c r="AC73" s="1"/>
     </row>
-    <row r="74" spans="1:29" ht="13.2">
+    <row r="74" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -3510,7 +3438,7 @@
       <c r="AB74" s="1"/>
       <c r="AC74" s="1"/>
     </row>
-    <row r="75" spans="1:29" ht="13.2">
+    <row r="75" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -3541,7 +3469,7 @@
       <c r="AB75" s="1"/>
       <c r="AC75" s="1"/>
     </row>
-    <row r="76" spans="1:29" ht="13.2">
+    <row r="76" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -3572,7 +3500,7 @@
       <c r="AB76" s="1"/>
       <c r="AC76" s="1"/>
     </row>
-    <row r="77" spans="1:29" ht="13.2">
+    <row r="77" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -3603,7 +3531,7 @@
       <c r="AB77" s="1"/>
       <c r="AC77" s="1"/>
     </row>
-    <row r="78" spans="1:29" ht="13.2">
+    <row r="78" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -3634,7 +3562,7 @@
       <c r="AB78" s="1"/>
       <c r="AC78" s="1"/>
     </row>
-    <row r="79" spans="1:29" ht="13.2">
+    <row r="79" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -3665,7 +3593,7 @@
       <c r="AB79" s="1"/>
       <c r="AC79" s="1"/>
     </row>
-    <row r="80" spans="1:29" ht="13.2">
+    <row r="80" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -3696,7 +3624,7 @@
       <c r="AB80" s="1"/>
       <c r="AC80" s="1"/>
     </row>
-    <row r="81" spans="1:29" ht="13.2">
+    <row r="81" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -3727,7 +3655,7 @@
       <c r="AB81" s="1"/>
       <c r="AC81" s="1"/>
     </row>
-    <row r="82" spans="1:29" ht="13.2">
+    <row r="82" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -3758,7 +3686,7 @@
       <c r="AB82" s="1"/>
       <c r="AC82" s="1"/>
     </row>
-    <row r="83" spans="1:29" ht="13.2">
+    <row r="83" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -3789,7 +3717,7 @@
       <c r="AB83" s="1"/>
       <c r="AC83" s="1"/>
     </row>
-    <row r="84" spans="1:29" ht="13.2">
+    <row r="84" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -3820,7 +3748,7 @@
       <c r="AB84" s="1"/>
       <c r="AC84" s="1"/>
     </row>
-    <row r="85" spans="1:29" ht="13.2">
+    <row r="85" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -3851,7 +3779,7 @@
       <c r="AB85" s="1"/>
       <c r="AC85" s="1"/>
     </row>
-    <row r="86" spans="1:29" ht="13.2">
+    <row r="86" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -3882,7 +3810,7 @@
       <c r="AB86" s="1"/>
       <c r="AC86" s="1"/>
     </row>
-    <row r="87" spans="1:29" ht="13.2">
+    <row r="87" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -3913,7 +3841,7 @@
       <c r="AB87" s="1"/>
       <c r="AC87" s="1"/>
     </row>
-    <row r="88" spans="1:29" ht="13.2">
+    <row r="88" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -3944,7 +3872,7 @@
       <c r="AB88" s="1"/>
       <c r="AC88" s="1"/>
     </row>
-    <row r="89" spans="1:29" ht="13.2">
+    <row r="89" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -3975,7 +3903,7 @@
       <c r="AB89" s="1"/>
       <c r="AC89" s="1"/>
     </row>
-    <row r="90" spans="1:29" ht="13.2">
+    <row r="90" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -4006,7 +3934,7 @@
       <c r="AB90" s="1"/>
       <c r="AC90" s="1"/>
     </row>
-    <row r="91" spans="1:29" ht="13.2">
+    <row r="91" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -4037,7 +3965,7 @@
       <c r="AB91" s="1"/>
       <c r="AC91" s="1"/>
     </row>
-    <row r="92" spans="1:29" ht="13.2">
+    <row r="92" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -4068,7 +3996,7 @@
       <c r="AB92" s="1"/>
       <c r="AC92" s="1"/>
     </row>
-    <row r="93" spans="1:29" ht="13.2">
+    <row r="93" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -4099,7 +4027,7 @@
       <c r="AB93" s="1"/>
       <c r="AC93" s="1"/>
     </row>
-    <row r="94" spans="1:29" ht="13.2">
+    <row r="94" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -4130,7 +4058,7 @@
       <c r="AB94" s="1"/>
       <c r="AC94" s="1"/>
     </row>
-    <row r="95" spans="1:29" ht="13.2">
+    <row r="95" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -4161,7 +4089,7 @@
       <c r="AB95" s="1"/>
       <c r="AC95" s="1"/>
     </row>
-    <row r="96" spans="1:29" ht="13.2">
+    <row r="96" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -4192,7 +4120,7 @@
       <c r="AB96" s="1"/>
       <c r="AC96" s="1"/>
     </row>
-    <row r="97" spans="1:29" ht="13.2">
+    <row r="97" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -4223,7 +4151,7 @@
       <c r="AB97" s="1"/>
       <c r="AC97" s="1"/>
     </row>
-    <row r="98" spans="1:29" ht="13.2">
+    <row r="98" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -4254,7 +4182,7 @@
       <c r="AB98" s="1"/>
       <c r="AC98" s="1"/>
     </row>
-    <row r="99" spans="1:29" ht="13.2">
+    <row r="99" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -4285,7 +4213,7 @@
       <c r="AB99" s="1"/>
       <c r="AC99" s="1"/>
     </row>
-    <row r="100" spans="1:29" ht="13.2">
+    <row r="100" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -4316,7 +4244,7 @@
       <c r="AB100" s="1"/>
       <c r="AC100" s="1"/>
     </row>
-    <row r="101" spans="1:29" ht="13.2">
+    <row r="101" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -4347,7 +4275,7 @@
       <c r="AB101" s="1"/>
       <c r="AC101" s="1"/>
     </row>
-    <row r="102" spans="1:29" ht="13.2">
+    <row r="102" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -4378,7 +4306,7 @@
       <c r="AB102" s="1"/>
       <c r="AC102" s="1"/>
     </row>
-    <row r="103" spans="1:29" ht="13.2">
+    <row r="103" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -4409,7 +4337,7 @@
       <c r="AB103" s="1"/>
       <c r="AC103" s="1"/>
     </row>
-    <row r="104" spans="1:29" ht="13.2">
+    <row r="104" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -4440,7 +4368,7 @@
       <c r="AB104" s="1"/>
       <c r="AC104" s="1"/>
     </row>
-    <row r="105" spans="1:29" ht="13.2">
+    <row r="105" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -4471,7 +4399,7 @@
       <c r="AB105" s="1"/>
       <c r="AC105" s="1"/>
     </row>
-    <row r="106" spans="1:29" ht="13.2">
+    <row r="106" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -4502,7 +4430,7 @@
       <c r="AB106" s="1"/>
       <c r="AC106" s="1"/>
     </row>
-    <row r="107" spans="1:29" ht="13.2">
+    <row r="107" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -4533,7 +4461,7 @@
       <c r="AB107" s="1"/>
       <c r="AC107" s="1"/>
     </row>
-    <row r="108" spans="1:29" ht="13.2">
+    <row r="108" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -4564,7 +4492,7 @@
       <c r="AB108" s="1"/>
       <c r="AC108" s="1"/>
     </row>
-    <row r="109" spans="1:29" ht="13.2">
+    <row r="109" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -4595,7 +4523,7 @@
       <c r="AB109" s="1"/>
       <c r="AC109" s="1"/>
     </row>
-    <row r="110" spans="1:29" ht="13.2">
+    <row r="110" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -4626,7 +4554,7 @@
       <c r="AB110" s="1"/>
       <c r="AC110" s="1"/>
     </row>
-    <row r="111" spans="1:29" ht="13.2">
+    <row r="111" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -4657,7 +4585,7 @@
       <c r="AB111" s="1"/>
       <c r="AC111" s="1"/>
     </row>
-    <row r="112" spans="1:29" ht="13.2">
+    <row r="112" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -4688,7 +4616,7 @@
       <c r="AB112" s="1"/>
       <c r="AC112" s="1"/>
     </row>
-    <row r="113" spans="1:29" ht="13.2">
+    <row r="113" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -4719,7 +4647,7 @@
       <c r="AB113" s="1"/>
       <c r="AC113" s="1"/>
     </row>
-    <row r="114" spans="1:29" ht="13.2">
+    <row r="114" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -4750,7 +4678,7 @@
       <c r="AB114" s="1"/>
       <c r="AC114" s="1"/>
     </row>
-    <row r="115" spans="1:29" ht="13.2">
+    <row r="115" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -4781,7 +4709,7 @@
       <c r="AB115" s="1"/>
       <c r="AC115" s="1"/>
     </row>
-    <row r="116" spans="1:29" ht="13.2">
+    <row r="116" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -4812,7 +4740,7 @@
       <c r="AB116" s="1"/>
       <c r="AC116" s="1"/>
     </row>
-    <row r="117" spans="1:29" ht="13.2">
+    <row r="117" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -4843,7 +4771,7 @@
       <c r="AB117" s="1"/>
       <c r="AC117" s="1"/>
     </row>
-    <row r="118" spans="1:29" ht="13.2">
+    <row r="118" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -4874,7 +4802,7 @@
       <c r="AB118" s="1"/>
       <c r="AC118" s="1"/>
     </row>
-    <row r="119" spans="1:29" ht="13.2">
+    <row r="119" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -4905,7 +4833,7 @@
       <c r="AB119" s="1"/>
       <c r="AC119" s="1"/>
     </row>
-    <row r="120" spans="1:29" ht="13.2">
+    <row r="120" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -4936,7 +4864,7 @@
       <c r="AB120" s="1"/>
       <c r="AC120" s="1"/>
     </row>
-    <row r="121" spans="1:29" ht="13.2">
+    <row r="121" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -4967,7 +4895,7 @@
       <c r="AB121" s="1"/>
       <c r="AC121" s="1"/>
     </row>
-    <row r="122" spans="1:29" ht="13.2">
+    <row r="122" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -4998,7 +4926,7 @@
       <c r="AB122" s="1"/>
       <c r="AC122" s="1"/>
     </row>
-    <row r="123" spans="1:29" ht="13.2">
+    <row r="123" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -5029,7 +4957,7 @@
       <c r="AB123" s="1"/>
       <c r="AC123" s="1"/>
     </row>
-    <row r="124" spans="1:29" ht="13.2">
+    <row r="124" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -5060,7 +4988,7 @@
       <c r="AB124" s="1"/>
       <c r="AC124" s="1"/>
     </row>
-    <row r="125" spans="1:29" ht="13.2">
+    <row r="125" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -5091,7 +5019,7 @@
       <c r="AB125" s="1"/>
       <c r="AC125" s="1"/>
     </row>
-    <row r="126" spans="1:29" ht="13.2">
+    <row r="126" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -5122,7 +5050,7 @@
       <c r="AB126" s="1"/>
       <c r="AC126" s="1"/>
     </row>
-    <row r="127" spans="1:29" ht="13.2">
+    <row r="127" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -5153,7 +5081,7 @@
       <c r="AB127" s="1"/>
       <c r="AC127" s="1"/>
     </row>
-    <row r="128" spans="1:29" ht="13.2">
+    <row r="128" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -5184,7 +5112,7 @@
       <c r="AB128" s="1"/>
       <c r="AC128" s="1"/>
     </row>
-    <row r="129" spans="1:29" ht="13.2">
+    <row r="129" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -5215,7 +5143,7 @@
       <c r="AB129" s="1"/>
       <c r="AC129" s="1"/>
     </row>
-    <row r="130" spans="1:29" ht="13.2">
+    <row r="130" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -5246,7 +5174,7 @@
       <c r="AB130" s="1"/>
       <c r="AC130" s="1"/>
     </row>
-    <row r="131" spans="1:29" ht="13.2">
+    <row r="131" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -5277,7 +5205,7 @@
       <c r="AB131" s="1"/>
       <c r="AC131" s="1"/>
     </row>
-    <row r="132" spans="1:29" ht="13.2">
+    <row r="132" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -5308,7 +5236,7 @@
       <c r="AB132" s="1"/>
       <c r="AC132" s="1"/>
     </row>
-    <row r="133" spans="1:29" ht="13.2">
+    <row r="133" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -5339,7 +5267,7 @@
       <c r="AB133" s="1"/>
       <c r="AC133" s="1"/>
     </row>
-    <row r="134" spans="1:29" ht="13.2">
+    <row r="134" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -5370,7 +5298,7 @@
       <c r="AB134" s="1"/>
       <c r="AC134" s="1"/>
     </row>
-    <row r="135" spans="1:29" ht="13.2">
+    <row r="135" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -5401,7 +5329,7 @@
       <c r="AB135" s="1"/>
       <c r="AC135" s="1"/>
     </row>
-    <row r="136" spans="1:29" ht="13.2">
+    <row r="136" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -5432,7 +5360,7 @@
       <c r="AB136" s="1"/>
       <c r="AC136" s="1"/>
     </row>
-    <row r="137" spans="1:29" ht="13.2">
+    <row r="137" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -5463,7 +5391,7 @@
       <c r="AB137" s="1"/>
       <c r="AC137" s="1"/>
     </row>
-    <row r="138" spans="1:29" ht="13.2">
+    <row r="138" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -5494,7 +5422,7 @@
       <c r="AB138" s="1"/>
       <c r="AC138" s="1"/>
     </row>
-    <row r="139" spans="1:29" ht="13.2">
+    <row r="139" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -5525,7 +5453,7 @@
       <c r="AB139" s="1"/>
       <c r="AC139" s="1"/>
     </row>
-    <row r="140" spans="1:29" ht="13.2">
+    <row r="140" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -5556,7 +5484,7 @@
       <c r="AB140" s="1"/>
       <c r="AC140" s="1"/>
     </row>
-    <row r="141" spans="1:29" ht="13.2">
+    <row r="141" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -5587,7 +5515,7 @@
       <c r="AB141" s="1"/>
       <c r="AC141" s="1"/>
     </row>
-    <row r="142" spans="1:29" ht="13.2">
+    <row r="142" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -5618,7 +5546,7 @@
       <c r="AB142" s="1"/>
       <c r="AC142" s="1"/>
     </row>
-    <row r="143" spans="1:29" ht="13.2">
+    <row r="143" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -5649,7 +5577,7 @@
       <c r="AB143" s="1"/>
       <c r="AC143" s="1"/>
     </row>
-    <row r="144" spans="1:29" ht="13.2">
+    <row r="144" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -5680,7 +5608,7 @@
       <c r="AB144" s="1"/>
       <c r="AC144" s="1"/>
     </row>
-    <row r="145" spans="1:29" ht="13.2">
+    <row r="145" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -5711,7 +5639,7 @@
       <c r="AB145" s="1"/>
       <c r="AC145" s="1"/>
     </row>
-    <row r="146" spans="1:29" ht="13.2">
+    <row r="146" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -5742,7 +5670,7 @@
       <c r="AB146" s="1"/>
       <c r="AC146" s="1"/>
     </row>
-    <row r="147" spans="1:29" ht="13.2">
+    <row r="147" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -5773,7 +5701,7 @@
       <c r="AB147" s="1"/>
       <c r="AC147" s="1"/>
     </row>
-    <row r="148" spans="1:29" ht="13.2">
+    <row r="148" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -5804,7 +5732,7 @@
       <c r="AB148" s="1"/>
       <c r="AC148" s="1"/>
     </row>
-    <row r="149" spans="1:29" ht="13.2">
+    <row r="149" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -5835,7 +5763,7 @@
       <c r="AB149" s="1"/>
       <c r="AC149" s="1"/>
     </row>
-    <row r="150" spans="1:29" ht="13.2">
+    <row r="150" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -5866,7 +5794,7 @@
       <c r="AB150" s="1"/>
       <c r="AC150" s="1"/>
     </row>
-    <row r="151" spans="1:29" ht="13.2">
+    <row r="151" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -5897,7 +5825,7 @@
       <c r="AB151" s="1"/>
       <c r="AC151" s="1"/>
     </row>
-    <row r="152" spans="1:29" ht="13.2">
+    <row r="152" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -5928,7 +5856,7 @@
       <c r="AB152" s="1"/>
       <c r="AC152" s="1"/>
     </row>
-    <row r="153" spans="1:29" ht="13.2">
+    <row r="153" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -5959,7 +5887,7 @@
       <c r="AB153" s="1"/>
       <c r="AC153" s="1"/>
     </row>
-    <row r="154" spans="1:29" ht="13.2">
+    <row r="154" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -5990,7 +5918,7 @@
       <c r="AB154" s="1"/>
       <c r="AC154" s="1"/>
     </row>
-    <row r="155" spans="1:29" ht="13.2">
+    <row r="155" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -6021,7 +5949,7 @@
       <c r="AB155" s="1"/>
       <c r="AC155" s="1"/>
     </row>
-    <row r="156" spans="1:29" ht="13.2">
+    <row r="156" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -6052,7 +5980,7 @@
       <c r="AB156" s="1"/>
       <c r="AC156" s="1"/>
     </row>
-    <row r="157" spans="1:29" ht="13.2">
+    <row r="157" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -6083,7 +6011,7 @@
       <c r="AB157" s="1"/>
       <c r="AC157" s="1"/>
     </row>
-    <row r="158" spans="1:29" ht="13.2">
+    <row r="158" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -6114,7 +6042,7 @@
       <c r="AB158" s="1"/>
       <c r="AC158" s="1"/>
     </row>
-    <row r="159" spans="1:29" ht="13.2">
+    <row r="159" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -6145,7 +6073,7 @@
       <c r="AB159" s="1"/>
       <c r="AC159" s="1"/>
     </row>
-    <row r="160" spans="1:29" ht="13.2">
+    <row r="160" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -6176,7 +6104,7 @@
       <c r="AB160" s="1"/>
       <c r="AC160" s="1"/>
     </row>
-    <row r="161" spans="1:29" ht="13.2">
+    <row r="161" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -6207,7 +6135,7 @@
       <c r="AB161" s="1"/>
       <c r="AC161" s="1"/>
     </row>
-    <row r="162" spans="1:29" ht="13.2">
+    <row r="162" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -6238,7 +6166,7 @@
       <c r="AB162" s="1"/>
       <c r="AC162" s="1"/>
     </row>
-    <row r="163" spans="1:29" ht="13.2">
+    <row r="163" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -6269,7 +6197,7 @@
       <c r="AB163" s="1"/>
       <c r="AC163" s="1"/>
     </row>
-    <row r="164" spans="1:29" ht="13.2">
+    <row r="164" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -6300,7 +6228,7 @@
       <c r="AB164" s="1"/>
       <c r="AC164" s="1"/>
     </row>
-    <row r="165" spans="1:29" ht="13.2">
+    <row r="165" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -6331,7 +6259,7 @@
       <c r="AB165" s="1"/>
       <c r="AC165" s="1"/>
     </row>
-    <row r="166" spans="1:29" ht="13.2">
+    <row r="166" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -6362,7 +6290,7 @@
       <c r="AB166" s="1"/>
       <c r="AC166" s="1"/>
     </row>
-    <row r="167" spans="1:29" ht="13.2">
+    <row r="167" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -6393,7 +6321,7 @@
       <c r="AB167" s="1"/>
       <c r="AC167" s="1"/>
     </row>
-    <row r="168" spans="1:29" ht="13.2">
+    <row r="168" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -6424,7 +6352,7 @@
       <c r="AB168" s="1"/>
       <c r="AC168" s="1"/>
     </row>
-    <row r="169" spans="1:29" ht="13.2">
+    <row r="169" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -6455,7 +6383,7 @@
       <c r="AB169" s="1"/>
       <c r="AC169" s="1"/>
     </row>
-    <row r="170" spans="1:29" ht="13.2">
+    <row r="170" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -6486,7 +6414,7 @@
       <c r="AB170" s="1"/>
       <c r="AC170" s="1"/>
     </row>
-    <row r="171" spans="1:29" ht="13.2">
+    <row r="171" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -6517,7 +6445,7 @@
       <c r="AB171" s="1"/>
       <c r="AC171" s="1"/>
     </row>
-    <row r="172" spans="1:29" ht="13.2">
+    <row r="172" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -6548,7 +6476,7 @@
       <c r="AB172" s="1"/>
       <c r="AC172" s="1"/>
     </row>
-    <row r="173" spans="1:29" ht="13.2">
+    <row r="173" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -6579,7 +6507,7 @@
       <c r="AB173" s="1"/>
       <c r="AC173" s="1"/>
     </row>
-    <row r="174" spans="1:29" ht="13.2">
+    <row r="174" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -6610,7 +6538,7 @@
       <c r="AB174" s="1"/>
       <c r="AC174" s="1"/>
     </row>
-    <row r="175" spans="1:29" ht="13.2">
+    <row r="175" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -6641,7 +6569,7 @@
       <c r="AB175" s="1"/>
       <c r="AC175" s="1"/>
     </row>
-    <row r="176" spans="1:29" ht="13.2">
+    <row r="176" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -6672,7 +6600,7 @@
       <c r="AB176" s="1"/>
       <c r="AC176" s="1"/>
     </row>
-    <row r="177" spans="1:29" ht="13.2">
+    <row r="177" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -6703,7 +6631,7 @@
       <c r="AB177" s="1"/>
       <c r="AC177" s="1"/>
     </row>
-    <row r="178" spans="1:29" ht="13.2">
+    <row r="178" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -6734,7 +6662,7 @@
       <c r="AB178" s="1"/>
       <c r="AC178" s="1"/>
     </row>
-    <row r="179" spans="1:29" ht="13.2">
+    <row r="179" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -6765,7 +6693,7 @@
       <c r="AB179" s="1"/>
       <c r="AC179" s="1"/>
     </row>
-    <row r="180" spans="1:29" ht="13.2">
+    <row r="180" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -6796,7 +6724,7 @@
       <c r="AB180" s="1"/>
       <c r="AC180" s="1"/>
     </row>
-    <row r="181" spans="1:29" ht="13.2">
+    <row r="181" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -6827,7 +6755,7 @@
       <c r="AB181" s="1"/>
       <c r="AC181" s="1"/>
     </row>
-    <row r="182" spans="1:29" ht="13.2">
+    <row r="182" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -6858,7 +6786,7 @@
       <c r="AB182" s="1"/>
       <c r="AC182" s="1"/>
     </row>
-    <row r="183" spans="1:29" ht="13.2">
+    <row r="183" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -6889,7 +6817,7 @@
       <c r="AB183" s="1"/>
       <c r="AC183" s="1"/>
     </row>
-    <row r="184" spans="1:29" ht="13.2">
+    <row r="184" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -6920,7 +6848,7 @@
       <c r="AB184" s="1"/>
       <c r="AC184" s="1"/>
     </row>
-    <row r="185" spans="1:29" ht="13.2">
+    <row r="185" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -6951,7 +6879,7 @@
       <c r="AB185" s="1"/>
       <c r="AC185" s="1"/>
     </row>
-    <row r="186" spans="1:29" ht="13.2">
+    <row r="186" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -6982,7 +6910,7 @@
       <c r="AB186" s="1"/>
       <c r="AC186" s="1"/>
     </row>
-    <row r="187" spans="1:29" ht="13.2">
+    <row r="187" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -7013,7 +6941,7 @@
       <c r="AB187" s="1"/>
       <c r="AC187" s="1"/>
     </row>
-    <row r="188" spans="1:29" ht="13.2">
+    <row r="188" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -7044,7 +6972,7 @@
       <c r="AB188" s="1"/>
       <c r="AC188" s="1"/>
     </row>
-    <row r="189" spans="1:29" ht="13.2">
+    <row r="189" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -7075,7 +7003,7 @@
       <c r="AB189" s="1"/>
       <c r="AC189" s="1"/>
     </row>
-    <row r="190" spans="1:29" ht="13.2">
+    <row r="190" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -7106,7 +7034,7 @@
       <c r="AB190" s="1"/>
       <c r="AC190" s="1"/>
     </row>
-    <row r="191" spans="1:29" ht="13.2">
+    <row r="191" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -7137,7 +7065,7 @@
       <c r="AB191" s="1"/>
       <c r="AC191" s="1"/>
     </row>
-    <row r="192" spans="1:29" ht="13.2">
+    <row r="192" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -7168,7 +7096,7 @@
       <c r="AB192" s="1"/>
       <c r="AC192" s="1"/>
     </row>
-    <row r="193" spans="1:29" ht="13.2">
+    <row r="193" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -7199,7 +7127,7 @@
       <c r="AB193" s="1"/>
       <c r="AC193" s="1"/>
     </row>
-    <row r="194" spans="1:29" ht="13.2">
+    <row r="194" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -7230,7 +7158,7 @@
       <c r="AB194" s="1"/>
       <c r="AC194" s="1"/>
     </row>
-    <row r="195" spans="1:29" ht="13.2">
+    <row r="195" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -7261,7 +7189,7 @@
       <c r="AB195" s="1"/>
       <c r="AC195" s="1"/>
     </row>
-    <row r="196" spans="1:29" ht="13.2">
+    <row r="196" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
@@ -7292,7 +7220,7 @@
       <c r="AB196" s="1"/>
       <c r="AC196" s="1"/>
     </row>
-    <row r="197" spans="1:29" ht="13.2">
+    <row r="197" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
@@ -7323,7 +7251,7 @@
       <c r="AB197" s="1"/>
       <c r="AC197" s="1"/>
     </row>
-    <row r="198" spans="1:29" ht="13.2">
+    <row r="198" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
@@ -7354,7 +7282,7 @@
       <c r="AB198" s="1"/>
       <c r="AC198" s="1"/>
     </row>
-    <row r="199" spans="1:29" ht="13.2">
+    <row r="199" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
@@ -7385,7 +7313,7 @@
       <c r="AB199" s="1"/>
       <c r="AC199" s="1"/>
     </row>
-    <row r="200" spans="1:29" ht="13.2">
+    <row r="200" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
@@ -7416,7 +7344,7 @@
       <c r="AB200" s="1"/>
       <c r="AC200" s="1"/>
     </row>
-    <row r="201" spans="1:29" ht="13.2">
+    <row r="201" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
@@ -7447,7 +7375,7 @@
       <c r="AB201" s="1"/>
       <c r="AC201" s="1"/>
     </row>
-    <row r="202" spans="1:29" ht="13.2">
+    <row r="202" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
@@ -7478,7 +7406,7 @@
       <c r="AB202" s="1"/>
       <c r="AC202" s="1"/>
     </row>
-    <row r="203" spans="1:29" ht="13.2">
+    <row r="203" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
@@ -7509,7 +7437,7 @@
       <c r="AB203" s="1"/>
       <c r="AC203" s="1"/>
     </row>
-    <row r="204" spans="1:29" ht="13.2">
+    <row r="204" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
@@ -7540,7 +7468,7 @@
       <c r="AB204" s="1"/>
       <c r="AC204" s="1"/>
     </row>
-    <row r="205" spans="1:29" ht="13.2">
+    <row r="205" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
@@ -7571,7 +7499,7 @@
       <c r="AB205" s="1"/>
       <c r="AC205" s="1"/>
     </row>
-    <row r="206" spans="1:29" ht="13.2">
+    <row r="206" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
@@ -7602,7 +7530,7 @@
       <c r="AB206" s="1"/>
       <c r="AC206" s="1"/>
     </row>
-    <row r="207" spans="1:29" ht="13.2">
+    <row r="207" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
@@ -7633,7 +7561,7 @@
       <c r="AB207" s="1"/>
       <c r="AC207" s="1"/>
     </row>
-    <row r="208" spans="1:29" ht="13.2">
+    <row r="208" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
@@ -7664,7 +7592,7 @@
       <c r="AB208" s="1"/>
       <c r="AC208" s="1"/>
     </row>
-    <row r="209" spans="1:29" ht="13.2">
+    <row r="209" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
@@ -7695,7 +7623,7 @@
       <c r="AB209" s="1"/>
       <c r="AC209" s="1"/>
     </row>
-    <row r="210" spans="1:29" ht="13.2">
+    <row r="210" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
@@ -7726,7 +7654,7 @@
       <c r="AB210" s="1"/>
       <c r="AC210" s="1"/>
     </row>
-    <row r="211" spans="1:29" ht="13.2">
+    <row r="211" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
@@ -7757,7 +7685,7 @@
       <c r="AB211" s="1"/>
       <c r="AC211" s="1"/>
     </row>
-    <row r="212" spans="1:29" ht="13.2">
+    <row r="212" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
@@ -7788,7 +7716,7 @@
       <c r="AB212" s="1"/>
       <c r="AC212" s="1"/>
     </row>
-    <row r="213" spans="1:29" ht="13.2">
+    <row r="213" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
@@ -7819,7 +7747,7 @@
       <c r="AB213" s="1"/>
       <c r="AC213" s="1"/>
     </row>
-    <row r="214" spans="1:29" ht="13.2">
+    <row r="214" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
@@ -7850,7 +7778,7 @@
       <c r="AB214" s="1"/>
       <c r="AC214" s="1"/>
     </row>
-    <row r="215" spans="1:29" ht="13.2">
+    <row r="215" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
@@ -7881,7 +7809,7 @@
       <c r="AB215" s="1"/>
       <c r="AC215" s="1"/>
     </row>
-    <row r="216" spans="1:29" ht="13.2">
+    <row r="216" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
@@ -7912,7 +7840,7 @@
       <c r="AB216" s="1"/>
       <c r="AC216" s="1"/>
     </row>
-    <row r="217" spans="1:29" ht="13.2">
+    <row r="217" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
@@ -7943,7 +7871,7 @@
       <c r="AB217" s="1"/>
       <c r="AC217" s="1"/>
     </row>
-    <row r="218" spans="1:29" ht="13.2">
+    <row r="218" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
@@ -7974,7 +7902,7 @@
       <c r="AB218" s="1"/>
       <c r="AC218" s="1"/>
     </row>
-    <row r="219" spans="1:29" ht="13.2">
+    <row r="219" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
@@ -8005,7 +7933,7 @@
       <c r="AB219" s="1"/>
       <c r="AC219" s="1"/>
     </row>
-    <row r="220" spans="1:29" ht="13.2">
+    <row r="220" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
@@ -8036,7 +7964,7 @@
       <c r="AB220" s="1"/>
       <c r="AC220" s="1"/>
     </row>
-    <row r="221" spans="1:29" ht="13.2">
+    <row r="221" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="C221" s="1"/>
@@ -8067,7 +7995,7 @@
       <c r="AB221" s="1"/>
       <c r="AC221" s="1"/>
     </row>
-    <row r="222" spans="1:29" ht="13.2">
+    <row r="222" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
       <c r="C222" s="1"/>
@@ -8098,7 +8026,7 @@
       <c r="AB222" s="1"/>
       <c r="AC222" s="1"/>
     </row>
-    <row r="223" spans="1:29" ht="13.2">
+    <row r="223" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="C223" s="1"/>
@@ -8129,7 +8057,7 @@
       <c r="AB223" s="1"/>
       <c r="AC223" s="1"/>
     </row>
-    <row r="224" spans="1:29" ht="13.2">
+    <row r="224" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
       <c r="C224" s="1"/>
@@ -8160,7 +8088,7 @@
       <c r="AB224" s="1"/>
       <c r="AC224" s="1"/>
     </row>
-    <row r="225" spans="1:29" ht="13.2">
+    <row r="225" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
@@ -8191,7 +8119,7 @@
       <c r="AB225" s="1"/>
       <c r="AC225" s="1"/>
     </row>
-    <row r="226" spans="1:29" ht="13.2">
+    <row r="226" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
@@ -8222,7 +8150,7 @@
       <c r="AB226" s="1"/>
       <c r="AC226" s="1"/>
     </row>
-    <row r="227" spans="1:29" ht="13.2">
+    <row r="227" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A227" s="1"/>
       <c r="B227" s="1"/>
       <c r="C227" s="1"/>
@@ -8253,7 +8181,7 @@
       <c r="AB227" s="1"/>
       <c r="AC227" s="1"/>
     </row>
-    <row r="228" spans="1:29" ht="13.2">
+    <row r="228" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
@@ -8284,7 +8212,7 @@
       <c r="AB228" s="1"/>
       <c r="AC228" s="1"/>
     </row>
-    <row r="229" spans="1:29" ht="13.2">
+    <row r="229" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A229" s="1"/>
       <c r="B229" s="1"/>
       <c r="C229" s="1"/>
@@ -8315,7 +8243,7 @@
       <c r="AB229" s="1"/>
       <c r="AC229" s="1"/>
     </row>
-    <row r="230" spans="1:29" ht="13.2">
+    <row r="230" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A230" s="1"/>
       <c r="B230" s="1"/>
       <c r="C230" s="1"/>
@@ -8346,7 +8274,7 @@
       <c r="AB230" s="1"/>
       <c r="AC230" s="1"/>
     </row>
-    <row r="231" spans="1:29" ht="13.2">
+    <row r="231" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A231" s="1"/>
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
@@ -8377,7 +8305,7 @@
       <c r="AB231" s="1"/>
       <c r="AC231" s="1"/>
     </row>
-    <row r="232" spans="1:29" ht="13.2">
+    <row r="232" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A232" s="1"/>
       <c r="B232" s="1"/>
       <c r="C232" s="1"/>
@@ -8408,7 +8336,7 @@
       <c r="AB232" s="1"/>
       <c r="AC232" s="1"/>
     </row>
-    <row r="233" spans="1:29" ht="13.2">
+    <row r="233" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A233" s="1"/>
       <c r="B233" s="1"/>
       <c r="C233" s="1"/>
@@ -8439,7 +8367,7 @@
       <c r="AB233" s="1"/>
       <c r="AC233" s="1"/>
     </row>
-    <row r="234" spans="1:29" ht="13.2">
+    <row r="234" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A234" s="1"/>
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
@@ -8470,7 +8398,7 @@
       <c r="AB234" s="1"/>
       <c r="AC234" s="1"/>
     </row>
-    <row r="235" spans="1:29" ht="13.2">
+    <row r="235" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A235" s="1"/>
       <c r="B235" s="1"/>
       <c r="C235" s="1"/>
@@ -8501,7 +8429,7 @@
       <c r="AB235" s="1"/>
       <c r="AC235" s="1"/>
     </row>
-    <row r="236" spans="1:29" ht="13.2">
+    <row r="236" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
@@ -8532,7 +8460,7 @@
       <c r="AB236" s="1"/>
       <c r="AC236" s="1"/>
     </row>
-    <row r="237" spans="1:29" ht="13.2">
+    <row r="237" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A237" s="1"/>
       <c r="B237" s="1"/>
       <c r="C237" s="1"/>
@@ -8563,7 +8491,7 @@
       <c r="AB237" s="1"/>
       <c r="AC237" s="1"/>
     </row>
-    <row r="238" spans="1:29" ht="13.2">
+    <row r="238" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A238" s="1"/>
       <c r="B238" s="1"/>
       <c r="C238" s="1"/>
@@ -8594,7 +8522,7 @@
       <c r="AB238" s="1"/>
       <c r="AC238" s="1"/>
     </row>
-    <row r="239" spans="1:29" ht="13.2">
+    <row r="239" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A239" s="1"/>
       <c r="B239" s="1"/>
       <c r="C239" s="1"/>
@@ -8625,7 +8553,7 @@
       <c r="AB239" s="1"/>
       <c r="AC239" s="1"/>
     </row>
-    <row r="240" spans="1:29" ht="13.2">
+    <row r="240" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
@@ -8656,7 +8584,7 @@
       <c r="AB240" s="1"/>
       <c r="AC240" s="1"/>
     </row>
-    <row r="241" spans="1:29" ht="13.2">
+    <row r="241" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A241" s="1"/>
       <c r="B241" s="1"/>
       <c r="C241" s="1"/>
@@ -8687,7 +8615,7 @@
       <c r="AB241" s="1"/>
       <c r="AC241" s="1"/>
     </row>
-    <row r="242" spans="1:29" ht="13.2">
+    <row r="242" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A242" s="1"/>
       <c r="B242" s="1"/>
       <c r="C242" s="1"/>
@@ -8718,7 +8646,7 @@
       <c r="AB242" s="1"/>
       <c r="AC242" s="1"/>
     </row>
-    <row r="243" spans="1:29" ht="13.2">
+    <row r="243" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A243" s="1"/>
       <c r="B243" s="1"/>
       <c r="C243" s="1"/>
@@ -8749,7 +8677,7 @@
       <c r="AB243" s="1"/>
       <c r="AC243" s="1"/>
     </row>
-    <row r="244" spans="1:29" ht="13.2">
+    <row r="244" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A244" s="1"/>
       <c r="B244" s="1"/>
       <c r="C244" s="1"/>
@@ -8780,7 +8708,7 @@
       <c r="AB244" s="1"/>
       <c r="AC244" s="1"/>
     </row>
-    <row r="245" spans="1:29" ht="13.2">
+    <row r="245" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="1"/>
@@ -8811,7 +8739,7 @@
       <c r="AB245" s="1"/>
       <c r="AC245" s="1"/>
     </row>
-    <row r="246" spans="1:29" ht="13.2">
+    <row r="246" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A246" s="1"/>
       <c r="B246" s="1"/>
       <c r="C246" s="1"/>
@@ -8842,7 +8770,7 @@
       <c r="AB246" s="1"/>
       <c r="AC246" s="1"/>
     </row>
-    <row r="247" spans="1:29" ht="13.2">
+    <row r="247" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A247" s="1"/>
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
@@ -8873,7 +8801,7 @@
       <c r="AB247" s="1"/>
       <c r="AC247" s="1"/>
     </row>
-    <row r="248" spans="1:29" ht="13.2">
+    <row r="248" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A248" s="1"/>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
@@ -8904,7 +8832,7 @@
       <c r="AB248" s="1"/>
       <c r="AC248" s="1"/>
     </row>
-    <row r="249" spans="1:29" ht="13.2">
+    <row r="249" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A249" s="1"/>
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
@@ -8935,7 +8863,7 @@
       <c r="AB249" s="1"/>
       <c r="AC249" s="1"/>
     </row>
-    <row r="250" spans="1:29" ht="13.2">
+    <row r="250" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A250" s="1"/>
       <c r="B250" s="1"/>
       <c r="C250" s="1"/>
@@ -8966,7 +8894,7 @@
       <c r="AB250" s="1"/>
       <c r="AC250" s="1"/>
     </row>
-    <row r="251" spans="1:29" ht="13.2">
+    <row r="251" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A251" s="1"/>
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
@@ -8997,7 +8925,7 @@
       <c r="AB251" s="1"/>
       <c r="AC251" s="1"/>
     </row>
-    <row r="252" spans="1:29" ht="13.2">
+    <row r="252" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A252" s="1"/>
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
@@ -9028,7 +8956,7 @@
       <c r="AB252" s="1"/>
       <c r="AC252" s="1"/>
     </row>
-    <row r="253" spans="1:29" ht="13.2">
+    <row r="253" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A253" s="1"/>
       <c r="B253" s="1"/>
       <c r="C253" s="1"/>
@@ -9059,7 +8987,7 @@
       <c r="AB253" s="1"/>
       <c r="AC253" s="1"/>
     </row>
-    <row r="254" spans="1:29" ht="13.2">
+    <row r="254" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A254" s="1"/>
       <c r="B254" s="1"/>
       <c r="C254" s="1"/>
@@ -9090,7 +9018,7 @@
       <c r="AB254" s="1"/>
       <c r="AC254" s="1"/>
     </row>
-    <row r="255" spans="1:29" ht="13.2">
+    <row r="255" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A255" s="1"/>
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
@@ -9121,7 +9049,7 @@
       <c r="AB255" s="1"/>
       <c r="AC255" s="1"/>
     </row>
-    <row r="256" spans="1:29" ht="13.2">
+    <row r="256" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A256" s="1"/>
       <c r="B256" s="1"/>
       <c r="C256" s="1"/>
@@ -9152,7 +9080,7 @@
       <c r="AB256" s="1"/>
       <c r="AC256" s="1"/>
     </row>
-    <row r="257" spans="1:29" ht="13.2">
+    <row r="257" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A257" s="1"/>
       <c r="B257" s="1"/>
       <c r="C257" s="1"/>
@@ -9183,7 +9111,7 @@
       <c r="AB257" s="1"/>
       <c r="AC257" s="1"/>
     </row>
-    <row r="258" spans="1:29" ht="13.2">
+    <row r="258" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A258" s="1"/>
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
@@ -9214,7 +9142,7 @@
       <c r="AB258" s="1"/>
       <c r="AC258" s="1"/>
     </row>
-    <row r="259" spans="1:29" ht="13.2">
+    <row r="259" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A259" s="1"/>
       <c r="B259" s="1"/>
       <c r="C259" s="1"/>
@@ -9245,7 +9173,7 @@
       <c r="AB259" s="1"/>
       <c r="AC259" s="1"/>
     </row>
-    <row r="260" spans="1:29" ht="13.2">
+    <row r="260" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A260" s="1"/>
       <c r="B260" s="1"/>
       <c r="C260" s="1"/>
@@ -9276,7 +9204,7 @@
       <c r="AB260" s="1"/>
       <c r="AC260" s="1"/>
     </row>
-    <row r="261" spans="1:29" ht="13.2">
+    <row r="261" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A261" s="1"/>
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
@@ -9307,7 +9235,7 @@
       <c r="AB261" s="1"/>
       <c r="AC261" s="1"/>
     </row>
-    <row r="262" spans="1:29" ht="13.2">
+    <row r="262" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A262" s="1"/>
       <c r="B262" s="1"/>
       <c r="C262" s="1"/>
@@ -9338,7 +9266,7 @@
       <c r="AB262" s="1"/>
       <c r="AC262" s="1"/>
     </row>
-    <row r="263" spans="1:29" ht="13.2">
+    <row r="263" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A263" s="1"/>
       <c r="B263" s="1"/>
       <c r="C263" s="1"/>
@@ -9369,7 +9297,7 @@
       <c r="AB263" s="1"/>
       <c r="AC263" s="1"/>
     </row>
-    <row r="264" spans="1:29" ht="13.2">
+    <row r="264" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A264" s="1"/>
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
@@ -9400,7 +9328,7 @@
       <c r="AB264" s="1"/>
       <c r="AC264" s="1"/>
     </row>
-    <row r="265" spans="1:29" ht="13.2">
+    <row r="265" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A265" s="1"/>
       <c r="B265" s="1"/>
       <c r="C265" s="1"/>
@@ -9431,7 +9359,7 @@
       <c r="AB265" s="1"/>
       <c r="AC265" s="1"/>
     </row>
-    <row r="266" spans="1:29" ht="13.2">
+    <row r="266" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A266" s="1"/>
       <c r="B266" s="1"/>
       <c r="C266" s="1"/>
@@ -9462,7 +9390,7 @@
       <c r="AB266" s="1"/>
       <c r="AC266" s="1"/>
     </row>
-    <row r="267" spans="1:29" ht="13.2">
+    <row r="267" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A267" s="1"/>
       <c r="B267" s="1"/>
       <c r="C267" s="1"/>
@@ -9493,7 +9421,7 @@
       <c r="AB267" s="1"/>
       <c r="AC267" s="1"/>
     </row>
-    <row r="268" spans="1:29" ht="13.2">
+    <row r="268" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A268" s="1"/>
       <c r="B268" s="1"/>
       <c r="C268" s="1"/>
@@ -9524,7 +9452,7 @@
       <c r="AB268" s="1"/>
       <c r="AC268" s="1"/>
     </row>
-    <row r="269" spans="1:29" ht="13.2">
+    <row r="269" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A269" s="1"/>
       <c r="B269" s="1"/>
       <c r="C269" s="1"/>
@@ -9555,7 +9483,7 @@
       <c r="AB269" s="1"/>
       <c r="AC269" s="1"/>
     </row>
-    <row r="270" spans="1:29" ht="13.2">
+    <row r="270" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A270" s="1"/>
       <c r="B270" s="1"/>
       <c r="C270" s="1"/>
@@ -9586,7 +9514,7 @@
       <c r="AB270" s="1"/>
       <c r="AC270" s="1"/>
     </row>
-    <row r="271" spans="1:29" ht="13.2">
+    <row r="271" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A271" s="1"/>
       <c r="B271" s="1"/>
       <c r="C271" s="1"/>
@@ -9617,7 +9545,7 @@
       <c r="AB271" s="1"/>
       <c r="AC271" s="1"/>
     </row>
-    <row r="272" spans="1:29" ht="13.2">
+    <row r="272" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
@@ -9648,7 +9576,7 @@
       <c r="AB272" s="1"/>
       <c r="AC272" s="1"/>
     </row>
-    <row r="273" spans="1:29" ht="13.2">
+    <row r="273" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A273" s="1"/>
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
@@ -9679,7 +9607,7 @@
       <c r="AB273" s="1"/>
       <c r="AC273" s="1"/>
     </row>
-    <row r="274" spans="1:29" ht="13.2">
+    <row r="274" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A274" s="1"/>
       <c r="B274" s="1"/>
       <c r="C274" s="1"/>
@@ -9710,7 +9638,7 @@
       <c r="AB274" s="1"/>
       <c r="AC274" s="1"/>
     </row>
-    <row r="275" spans="1:29" ht="13.2">
+    <row r="275" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A275" s="1"/>
       <c r="B275" s="1"/>
       <c r="C275" s="1"/>
@@ -9741,7 +9669,7 @@
       <c r="AB275" s="1"/>
       <c r="AC275" s="1"/>
     </row>
-    <row r="276" spans="1:29" ht="13.2">
+    <row r="276" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A276" s="1"/>
       <c r="B276" s="1"/>
       <c r="C276" s="1"/>
@@ -9772,7 +9700,7 @@
       <c r="AB276" s="1"/>
       <c r="AC276" s="1"/>
     </row>
-    <row r="277" spans="1:29" ht="13.2">
+    <row r="277" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A277" s="1"/>
       <c r="B277" s="1"/>
       <c r="C277" s="1"/>
@@ -9803,7 +9731,7 @@
       <c r="AB277" s="1"/>
       <c r="AC277" s="1"/>
     </row>
-    <row r="278" spans="1:29" ht="13.2">
+    <row r="278" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A278" s="1"/>
       <c r="B278" s="1"/>
       <c r="C278" s="1"/>
@@ -9834,7 +9762,7 @@
       <c r="AB278" s="1"/>
       <c r="AC278" s="1"/>
     </row>
-    <row r="279" spans="1:29" ht="13.2">
+    <row r="279" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A279" s="1"/>
       <c r="B279" s="1"/>
       <c r="C279" s="1"/>
@@ -9865,7 +9793,7 @@
       <c r="AB279" s="1"/>
       <c r="AC279" s="1"/>
     </row>
-    <row r="280" spans="1:29" ht="13.2">
+    <row r="280" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A280" s="1"/>
       <c r="B280" s="1"/>
       <c r="C280" s="1"/>
@@ -9896,7 +9824,7 @@
       <c r="AB280" s="1"/>
       <c r="AC280" s="1"/>
     </row>
-    <row r="281" spans="1:29" ht="13.2">
+    <row r="281" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A281" s="1"/>
       <c r="B281" s="1"/>
       <c r="C281" s="1"/>
@@ -9927,7 +9855,7 @@
       <c r="AB281" s="1"/>
       <c r="AC281" s="1"/>
     </row>
-    <row r="282" spans="1:29" ht="13.2">
+    <row r="282" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A282" s="1"/>
       <c r="B282" s="1"/>
       <c r="C282" s="1"/>
@@ -9958,7 +9886,7 @@
       <c r="AB282" s="1"/>
       <c r="AC282" s="1"/>
     </row>
-    <row r="283" spans="1:29" ht="13.2">
+    <row r="283" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A283" s="1"/>
       <c r="B283" s="1"/>
       <c r="C283" s="1"/>
@@ -9989,7 +9917,7 @@
       <c r="AB283" s="1"/>
       <c r="AC283" s="1"/>
     </row>
-    <row r="284" spans="1:29" ht="13.2">
+    <row r="284" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A284" s="1"/>
       <c r="B284" s="1"/>
       <c r="C284" s="1"/>
@@ -10020,7 +9948,7 @@
       <c r="AB284" s="1"/>
       <c r="AC284" s="1"/>
     </row>
-    <row r="285" spans="1:29" ht="13.2">
+    <row r="285" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A285" s="1"/>
       <c r="B285" s="1"/>
       <c r="C285" s="1"/>
@@ -10051,7 +9979,7 @@
       <c r="AB285" s="1"/>
       <c r="AC285" s="1"/>
     </row>
-    <row r="286" spans="1:29" ht="13.2">
+    <row r="286" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A286" s="1"/>
       <c r="B286" s="1"/>
       <c r="C286" s="1"/>
@@ -10082,7 +10010,7 @@
       <c r="AB286" s="1"/>
       <c r="AC286" s="1"/>
     </row>
-    <row r="287" spans="1:29" ht="13.2">
+    <row r="287" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
@@ -10113,7 +10041,7 @@
       <c r="AB287" s="1"/>
       <c r="AC287" s="1"/>
     </row>
-    <row r="288" spans="1:29" ht="13.2">
+    <row r="288" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A288" s="1"/>
       <c r="B288" s="1"/>
       <c r="C288" s="1"/>
@@ -10144,7 +10072,7 @@
       <c r="AB288" s="1"/>
       <c r="AC288" s="1"/>
     </row>
-    <row r="289" spans="1:29" ht="13.2">
+    <row r="289" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A289" s="1"/>
       <c r="B289" s="1"/>
       <c r="C289" s="1"/>
@@ -10175,7 +10103,7 @@
       <c r="AB289" s="1"/>
       <c r="AC289" s="1"/>
     </row>
-    <row r="290" spans="1:29" ht="13.2">
+    <row r="290" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A290" s="1"/>
       <c r="B290" s="1"/>
       <c r="C290" s="1"/>
@@ -10206,7 +10134,7 @@
       <c r="AB290" s="1"/>
       <c r="AC290" s="1"/>
     </row>
-    <row r="291" spans="1:29" ht="13.2">
+    <row r="291" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A291" s="1"/>
       <c r="B291" s="1"/>
       <c r="C291" s="1"/>
@@ -10237,7 +10165,7 @@
       <c r="AB291" s="1"/>
       <c r="AC291" s="1"/>
     </row>
-    <row r="292" spans="1:29" ht="13.2">
+    <row r="292" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A292" s="1"/>
       <c r="B292" s="1"/>
       <c r="C292" s="1"/>
@@ -10268,7 +10196,7 @@
       <c r="AB292" s="1"/>
       <c r="AC292" s="1"/>
     </row>
-    <row r="293" spans="1:29" ht="13.2">
+    <row r="293" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A293" s="1"/>
       <c r="B293" s="1"/>
       <c r="C293" s="1"/>
@@ -10299,7 +10227,7 @@
       <c r="AB293" s="1"/>
       <c r="AC293" s="1"/>
     </row>
-    <row r="294" spans="1:29" ht="13.2">
+    <row r="294" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A294" s="1"/>
       <c r="B294" s="1"/>
       <c r="C294" s="1"/>
@@ -10330,7 +10258,7 @@
       <c r="AB294" s="1"/>
       <c r="AC294" s="1"/>
     </row>
-    <row r="295" spans="1:29" ht="13.2">
+    <row r="295" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A295" s="1"/>
       <c r="B295" s="1"/>
       <c r="C295" s="1"/>
@@ -10361,7 +10289,7 @@
       <c r="AB295" s="1"/>
       <c r="AC295" s="1"/>
     </row>
-    <row r="296" spans="1:29" ht="13.2">
+    <row r="296" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A296" s="1"/>
       <c r="B296" s="1"/>
       <c r="C296" s="1"/>
@@ -10392,7 +10320,7 @@
       <c r="AB296" s="1"/>
       <c r="AC296" s="1"/>
     </row>
-    <row r="297" spans="1:29" ht="13.2">
+    <row r="297" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A297" s="1"/>
       <c r="B297" s="1"/>
       <c r="C297" s="1"/>
@@ -10423,7 +10351,7 @@
       <c r="AB297" s="1"/>
       <c r="AC297" s="1"/>
     </row>
-    <row r="298" spans="1:29" ht="13.2">
+    <row r="298" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A298" s="1"/>
       <c r="B298" s="1"/>
       <c r="C298" s="1"/>
@@ -10454,7 +10382,7 @@
       <c r="AB298" s="1"/>
       <c r="AC298" s="1"/>
     </row>
-    <row r="299" spans="1:29" ht="13.2">
+    <row r="299" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A299" s="1"/>
       <c r="B299" s="1"/>
       <c r="C299" s="1"/>
@@ -10485,7 +10413,7 @@
       <c r="AB299" s="1"/>
       <c r="AC299" s="1"/>
     </row>
-    <row r="300" spans="1:29" ht="13.2">
+    <row r="300" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A300" s="1"/>
       <c r="B300" s="1"/>
       <c r="C300" s="1"/>
@@ -10516,7 +10444,7 @@
       <c r="AB300" s="1"/>
       <c r="AC300" s="1"/>
     </row>
-    <row r="301" spans="1:29" ht="13.2">
+    <row r="301" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A301" s="1"/>
       <c r="B301" s="1"/>
       <c r="C301" s="1"/>
@@ -10547,7 +10475,7 @@
       <c r="AB301" s="1"/>
       <c r="AC301" s="1"/>
     </row>
-    <row r="302" spans="1:29" ht="13.2">
+    <row r="302" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A302" s="1"/>
       <c r="B302" s="1"/>
       <c r="C302" s="1"/>
@@ -10578,7 +10506,7 @@
       <c r="AB302" s="1"/>
       <c r="AC302" s="1"/>
     </row>
-    <row r="303" spans="1:29" ht="13.2">
+    <row r="303" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A303" s="1"/>
       <c r="B303" s="1"/>
       <c r="C303" s="1"/>
@@ -10609,7 +10537,7 @@
       <c r="AB303" s="1"/>
       <c r="AC303" s="1"/>
     </row>
-    <row r="304" spans="1:29" ht="13.2">
+    <row r="304" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A304" s="1"/>
       <c r="B304" s="1"/>
       <c r="C304" s="1"/>
@@ -10640,7 +10568,7 @@
       <c r="AB304" s="1"/>
       <c r="AC304" s="1"/>
     </row>
-    <row r="305" spans="1:29" ht="13.2">
+    <row r="305" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A305" s="1"/>
       <c r="B305" s="1"/>
       <c r="C305" s="1"/>
@@ -10671,7 +10599,7 @@
       <c r="AB305" s="1"/>
       <c r="AC305" s="1"/>
     </row>
-    <row r="306" spans="1:29" ht="13.2">
+    <row r="306" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A306" s="1"/>
       <c r="B306" s="1"/>
       <c r="C306" s="1"/>
@@ -10702,7 +10630,7 @@
       <c r="AB306" s="1"/>
       <c r="AC306" s="1"/>
     </row>
-    <row r="307" spans="1:29" ht="13.2">
+    <row r="307" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A307" s="1"/>
       <c r="B307" s="1"/>
       <c r="C307" s="1"/>
@@ -10733,7 +10661,7 @@
       <c r="AB307" s="1"/>
       <c r="AC307" s="1"/>
     </row>
-    <row r="308" spans="1:29" ht="13.2">
+    <row r="308" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A308" s="1"/>
       <c r="B308" s="1"/>
       <c r="C308" s="1"/>
@@ -10764,7 +10692,7 @@
       <c r="AB308" s="1"/>
       <c r="AC308" s="1"/>
     </row>
-    <row r="309" spans="1:29" ht="13.2">
+    <row r="309" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A309" s="1"/>
       <c r="B309" s="1"/>
       <c r="C309" s="1"/>
@@ -10795,7 +10723,7 @@
       <c r="AB309" s="1"/>
       <c r="AC309" s="1"/>
     </row>
-    <row r="310" spans="1:29" ht="13.2">
+    <row r="310" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A310" s="1"/>
       <c r="B310" s="1"/>
       <c r="C310" s="1"/>
@@ -10826,7 +10754,7 @@
       <c r="AB310" s="1"/>
       <c r="AC310" s="1"/>
     </row>
-    <row r="311" spans="1:29" ht="13.2">
+    <row r="311" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A311" s="1"/>
       <c r="B311" s="1"/>
       <c r="C311" s="1"/>
@@ -10857,7 +10785,7 @@
       <c r="AB311" s="1"/>
       <c r="AC311" s="1"/>
     </row>
-    <row r="312" spans="1:29" ht="13.2">
+    <row r="312" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A312" s="1"/>
       <c r="B312" s="1"/>
       <c r="C312" s="1"/>
@@ -10888,7 +10816,7 @@
       <c r="AB312" s="1"/>
       <c r="AC312" s="1"/>
     </row>
-    <row r="313" spans="1:29" ht="13.2">
+    <row r="313" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A313" s="1"/>
       <c r="B313" s="1"/>
       <c r="C313" s="1"/>
@@ -10919,7 +10847,7 @@
       <c r="AB313" s="1"/>
       <c r="AC313" s="1"/>
     </row>
-    <row r="314" spans="1:29" ht="13.2">
+    <row r="314" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A314" s="1"/>
       <c r="B314" s="1"/>
       <c r="C314" s="1"/>
@@ -10950,7 +10878,7 @@
       <c r="AB314" s="1"/>
       <c r="AC314" s="1"/>
     </row>
-    <row r="315" spans="1:29" ht="13.2">
+    <row r="315" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A315" s="1"/>
       <c r="B315" s="1"/>
       <c r="C315" s="1"/>
@@ -10981,7 +10909,7 @@
       <c r="AB315" s="1"/>
       <c r="AC315" s="1"/>
     </row>
-    <row r="316" spans="1:29" ht="13.2">
+    <row r="316" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A316" s="1"/>
       <c r="B316" s="1"/>
       <c r="C316" s="1"/>
@@ -11012,7 +10940,7 @@
       <c r="AB316" s="1"/>
       <c r="AC316" s="1"/>
     </row>
-    <row r="317" spans="1:29" ht="13.2">
+    <row r="317" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A317" s="1"/>
       <c r="B317" s="1"/>
       <c r="C317" s="1"/>
@@ -11043,7 +10971,7 @@
       <c r="AB317" s="1"/>
       <c r="AC317" s="1"/>
     </row>
-    <row r="318" spans="1:29" ht="13.2">
+    <row r="318" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A318" s="1"/>
       <c r="B318" s="1"/>
       <c r="C318" s="1"/>
@@ -11074,7 +11002,7 @@
       <c r="AB318" s="1"/>
       <c r="AC318" s="1"/>
     </row>
-    <row r="319" spans="1:29" ht="13.2">
+    <row r="319" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A319" s="1"/>
       <c r="B319" s="1"/>
       <c r="C319" s="1"/>
@@ -11105,7 +11033,7 @@
       <c r="AB319" s="1"/>
       <c r="AC319" s="1"/>
     </row>
-    <row r="320" spans="1:29" ht="13.2">
+    <row r="320" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A320" s="1"/>
       <c r="B320" s="1"/>
       <c r="C320" s="1"/>
@@ -11136,7 +11064,7 @@
       <c r="AB320" s="1"/>
       <c r="AC320" s="1"/>
     </row>
-    <row r="321" spans="1:29" ht="13.2">
+    <row r="321" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A321" s="1"/>
       <c r="B321" s="1"/>
       <c r="C321" s="1"/>
@@ -11167,7 +11095,7 @@
       <c r="AB321" s="1"/>
       <c r="AC321" s="1"/>
     </row>
-    <row r="322" spans="1:29" ht="13.2">
+    <row r="322" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A322" s="1"/>
       <c r="B322" s="1"/>
       <c r="C322" s="1"/>
@@ -11198,7 +11126,7 @@
       <c r="AB322" s="1"/>
       <c r="AC322" s="1"/>
     </row>
-    <row r="323" spans="1:29" ht="13.2">
+    <row r="323" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A323" s="1"/>
       <c r="B323" s="1"/>
       <c r="C323" s="1"/>
@@ -11229,7 +11157,7 @@
       <c r="AB323" s="1"/>
       <c r="AC323" s="1"/>
     </row>
-    <row r="324" spans="1:29" ht="13.2">
+    <row r="324" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A324" s="1"/>
       <c r="B324" s="1"/>
       <c r="C324" s="1"/>
@@ -11260,7 +11188,7 @@
       <c r="AB324" s="1"/>
       <c r="AC324" s="1"/>
     </row>
-    <row r="325" spans="1:29" ht="13.2">
+    <row r="325" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A325" s="1"/>
       <c r="B325" s="1"/>
       <c r="C325" s="1"/>
@@ -11291,7 +11219,7 @@
       <c r="AB325" s="1"/>
       <c r="AC325" s="1"/>
     </row>
-    <row r="326" spans="1:29" ht="13.2">
+    <row r="326" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A326" s="1"/>
       <c r="B326" s="1"/>
       <c r="C326" s="1"/>
@@ -11322,7 +11250,7 @@
       <c r="AB326" s="1"/>
       <c r="AC326" s="1"/>
     </row>
-    <row r="327" spans="1:29" ht="13.2">
+    <row r="327" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A327" s="1"/>
       <c r="B327" s="1"/>
       <c r="C327" s="1"/>
@@ -11353,7 +11281,7 @@
       <c r="AB327" s="1"/>
       <c r="AC327" s="1"/>
     </row>
-    <row r="328" spans="1:29" ht="13.2">
+    <row r="328" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A328" s="1"/>
       <c r="B328" s="1"/>
       <c r="C328" s="1"/>
@@ -11384,7 +11312,7 @@
       <c r="AB328" s="1"/>
       <c r="AC328" s="1"/>
     </row>
-    <row r="329" spans="1:29" ht="13.2">
+    <row r="329" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A329" s="1"/>
       <c r="B329" s="1"/>
       <c r="C329" s="1"/>
@@ -11415,7 +11343,7 @@
       <c r="AB329" s="1"/>
       <c r="AC329" s="1"/>
     </row>
-    <row r="330" spans="1:29" ht="13.2">
+    <row r="330" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A330" s="1"/>
       <c r="B330" s="1"/>
       <c r="C330" s="1"/>
@@ -11446,7 +11374,7 @@
       <c r="AB330" s="1"/>
       <c r="AC330" s="1"/>
     </row>
-    <row r="331" spans="1:29" ht="13.2">
+    <row r="331" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A331" s="1"/>
       <c r="B331" s="1"/>
       <c r="C331" s="1"/>
@@ -11477,7 +11405,7 @@
       <c r="AB331" s="1"/>
       <c r="AC331" s="1"/>
     </row>
-    <row r="332" spans="1:29" ht="13.2">
+    <row r="332" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A332" s="1"/>
       <c r="B332" s="1"/>
       <c r="C332" s="1"/>
@@ -11508,7 +11436,7 @@
       <c r="AB332" s="1"/>
       <c r="AC332" s="1"/>
     </row>
-    <row r="333" spans="1:29" ht="13.2">
+    <row r="333" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A333" s="1"/>
       <c r="B333" s="1"/>
       <c r="C333" s="1"/>
@@ -11539,7 +11467,7 @@
       <c r="AB333" s="1"/>
       <c r="AC333" s="1"/>
     </row>
-    <row r="334" spans="1:29" ht="13.2">
+    <row r="334" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A334" s="1"/>
       <c r="B334" s="1"/>
       <c r="C334" s="1"/>
@@ -11570,7 +11498,7 @@
       <c r="AB334" s="1"/>
       <c r="AC334" s="1"/>
     </row>
-    <row r="335" spans="1:29" ht="13.2">
+    <row r="335" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A335" s="1"/>
       <c r="B335" s="1"/>
       <c r="C335" s="1"/>
@@ -11601,7 +11529,7 @@
       <c r="AB335" s="1"/>
       <c r="AC335" s="1"/>
     </row>
-    <row r="336" spans="1:29" ht="13.2">
+    <row r="336" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A336" s="1"/>
       <c r="B336" s="1"/>
       <c r="C336" s="1"/>
@@ -11632,7 +11560,7 @@
       <c r="AB336" s="1"/>
       <c r="AC336" s="1"/>
     </row>
-    <row r="337" spans="1:29" ht="13.2">
+    <row r="337" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A337" s="1"/>
       <c r="B337" s="1"/>
       <c r="C337" s="1"/>
@@ -11663,7 +11591,7 @@
       <c r="AB337" s="1"/>
       <c r="AC337" s="1"/>
     </row>
-    <row r="338" spans="1:29" ht="13.2">
+    <row r="338" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A338" s="1"/>
       <c r="B338" s="1"/>
       <c r="C338" s="1"/>
@@ -11694,7 +11622,7 @@
       <c r="AB338" s="1"/>
       <c r="AC338" s="1"/>
     </row>
-    <row r="339" spans="1:29" ht="13.2">
+    <row r="339" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A339" s="1"/>
       <c r="B339" s="1"/>
       <c r="C339" s="1"/>
@@ -11725,7 +11653,7 @@
       <c r="AB339" s="1"/>
       <c r="AC339" s="1"/>
     </row>
-    <row r="340" spans="1:29" ht="13.2">
+    <row r="340" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A340" s="1"/>
       <c r="B340" s="1"/>
       <c r="C340" s="1"/>
@@ -11756,7 +11684,7 @@
       <c r="AB340" s="1"/>
       <c r="AC340" s="1"/>
     </row>
-    <row r="341" spans="1:29" ht="13.2">
+    <row r="341" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A341" s="1"/>
       <c r="B341" s="1"/>
       <c r="C341" s="1"/>
@@ -11787,7 +11715,7 @@
       <c r="AB341" s="1"/>
       <c r="AC341" s="1"/>
     </row>
-    <row r="342" spans="1:29" ht="13.2">
+    <row r="342" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A342" s="1"/>
       <c r="B342" s="1"/>
       <c r="C342" s="1"/>
@@ -11818,7 +11746,7 @@
       <c r="AB342" s="1"/>
       <c r="AC342" s="1"/>
     </row>
-    <row r="343" spans="1:29" ht="13.2">
+    <row r="343" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A343" s="1"/>
       <c r="B343" s="1"/>
       <c r="C343" s="1"/>
@@ -11849,7 +11777,7 @@
       <c r="AB343" s="1"/>
       <c r="AC343" s="1"/>
     </row>
-    <row r="344" spans="1:29" ht="13.2">
+    <row r="344" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A344" s="1"/>
       <c r="B344" s="1"/>
       <c r="C344" s="1"/>
@@ -11880,7 +11808,7 @@
       <c r="AB344" s="1"/>
       <c r="AC344" s="1"/>
     </row>
-    <row r="345" spans="1:29" ht="13.2">
+    <row r="345" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A345" s="1"/>
       <c r="B345" s="1"/>
       <c r="C345" s="1"/>
@@ -11911,7 +11839,7 @@
       <c r="AB345" s="1"/>
       <c r="AC345" s="1"/>
     </row>
-    <row r="346" spans="1:29" ht="13.2">
+    <row r="346" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A346" s="1"/>
       <c r="B346" s="1"/>
       <c r="C346" s="1"/>
@@ -11942,7 +11870,7 @@
       <c r="AB346" s="1"/>
       <c r="AC346" s="1"/>
     </row>
-    <row r="347" spans="1:29" ht="13.2">
+    <row r="347" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A347" s="1"/>
       <c r="B347" s="1"/>
       <c r="C347" s="1"/>
@@ -11973,7 +11901,7 @@
       <c r="AB347" s="1"/>
       <c r="AC347" s="1"/>
     </row>
-    <row r="348" spans="1:29" ht="13.2">
+    <row r="348" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A348" s="1"/>
       <c r="B348" s="1"/>
       <c r="C348" s="1"/>
@@ -12004,7 +11932,7 @@
       <c r="AB348" s="1"/>
       <c r="AC348" s="1"/>
     </row>
-    <row r="349" spans="1:29" ht="13.2">
+    <row r="349" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A349" s="1"/>
       <c r="B349" s="1"/>
       <c r="C349" s="1"/>
@@ -12035,7 +11963,7 @@
       <c r="AB349" s="1"/>
       <c r="AC349" s="1"/>
     </row>
-    <row r="350" spans="1:29" ht="13.2">
+    <row r="350" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A350" s="1"/>
       <c r="B350" s="1"/>
       <c r="C350" s="1"/>
@@ -12066,7 +11994,7 @@
       <c r="AB350" s="1"/>
       <c r="AC350" s="1"/>
     </row>
-    <row r="351" spans="1:29" ht="13.2">
+    <row r="351" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A351" s="1"/>
       <c r="B351" s="1"/>
       <c r="C351" s="1"/>
@@ -12097,7 +12025,7 @@
       <c r="AB351" s="1"/>
       <c r="AC351" s="1"/>
     </row>
-    <row r="352" spans="1:29" ht="13.2">
+    <row r="352" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A352" s="1"/>
       <c r="B352" s="1"/>
       <c r="C352" s="1"/>
@@ -12128,7 +12056,7 @@
       <c r="AB352" s="1"/>
       <c r="AC352" s="1"/>
     </row>
-    <row r="353" spans="1:29" ht="13.2">
+    <row r="353" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A353" s="1"/>
       <c r="B353" s="1"/>
       <c r="C353" s="1"/>
@@ -12159,7 +12087,7 @@
       <c r="AB353" s="1"/>
       <c r="AC353" s="1"/>
     </row>
-    <row r="354" spans="1:29" ht="13.2">
+    <row r="354" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A354" s="1"/>
       <c r="B354" s="1"/>
       <c r="C354" s="1"/>
@@ -12190,7 +12118,7 @@
       <c r="AB354" s="1"/>
       <c r="AC354" s="1"/>
     </row>
-    <row r="355" spans="1:29" ht="13.2">
+    <row r="355" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A355" s="1"/>
       <c r="B355" s="1"/>
       <c r="C355" s="1"/>
@@ -12221,7 +12149,7 @@
       <c r="AB355" s="1"/>
       <c r="AC355" s="1"/>
     </row>
-    <row r="356" spans="1:29" ht="13.2">
+    <row r="356" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A356" s="1"/>
       <c r="B356" s="1"/>
       <c r="C356" s="1"/>
@@ -12252,7 +12180,7 @@
       <c r="AB356" s="1"/>
       <c r="AC356" s="1"/>
     </row>
-    <row r="357" spans="1:29" ht="13.2">
+    <row r="357" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A357" s="1"/>
       <c r="B357" s="1"/>
       <c r="C357" s="1"/>
@@ -12283,7 +12211,7 @@
       <c r="AB357" s="1"/>
       <c r="AC357" s="1"/>
     </row>
-    <row r="358" spans="1:29" ht="13.2">
+    <row r="358" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A358" s="1"/>
       <c r="B358" s="1"/>
       <c r="C358" s="1"/>
@@ -12314,7 +12242,7 @@
       <c r="AB358" s="1"/>
       <c r="AC358" s="1"/>
     </row>
-    <row r="359" spans="1:29" ht="13.2">
+    <row r="359" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A359" s="1"/>
       <c r="B359" s="1"/>
       <c r="C359" s="1"/>
@@ -12345,7 +12273,7 @@
       <c r="AB359" s="1"/>
       <c r="AC359" s="1"/>
     </row>
-    <row r="360" spans="1:29" ht="13.2">
+    <row r="360" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A360" s="1"/>
       <c r="B360" s="1"/>
       <c r="C360" s="1"/>
@@ -12376,7 +12304,7 @@
       <c r="AB360" s="1"/>
       <c r="AC360" s="1"/>
     </row>
-    <row r="361" spans="1:29" ht="13.2">
+    <row r="361" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A361" s="1"/>
       <c r="B361" s="1"/>
       <c r="C361" s="1"/>
@@ -12407,7 +12335,7 @@
       <c r="AB361" s="1"/>
       <c r="AC361" s="1"/>
     </row>
-    <row r="362" spans="1:29" ht="13.2">
+    <row r="362" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A362" s="1"/>
       <c r="B362" s="1"/>
       <c r="C362" s="1"/>
@@ -12438,7 +12366,7 @@
       <c r="AB362" s="1"/>
       <c r="AC362" s="1"/>
     </row>
-    <row r="363" spans="1:29" ht="13.2">
+    <row r="363" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A363" s="1"/>
       <c r="B363" s="1"/>
       <c r="C363" s="1"/>
@@ -12469,7 +12397,7 @@
       <c r="AB363" s="1"/>
       <c r="AC363" s="1"/>
     </row>
-    <row r="364" spans="1:29" ht="13.2">
+    <row r="364" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A364" s="1"/>
       <c r="B364" s="1"/>
       <c r="C364" s="1"/>
@@ -12500,7 +12428,7 @@
       <c r="AB364" s="1"/>
       <c r="AC364" s="1"/>
     </row>
-    <row r="365" spans="1:29" ht="13.2">
+    <row r="365" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A365" s="1"/>
       <c r="B365" s="1"/>
       <c r="C365" s="1"/>
@@ -12531,7 +12459,7 @@
       <c r="AB365" s="1"/>
       <c r="AC365" s="1"/>
     </row>
-    <row r="366" spans="1:29" ht="13.2">
+    <row r="366" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A366" s="1"/>
       <c r="B366" s="1"/>
       <c r="C366" s="1"/>
@@ -12562,7 +12490,7 @@
       <c r="AB366" s="1"/>
       <c r="AC366" s="1"/>
     </row>
-    <row r="367" spans="1:29" ht="13.2">
+    <row r="367" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A367" s="1"/>
       <c r="B367" s="1"/>
       <c r="C367" s="1"/>
@@ -12593,7 +12521,7 @@
       <c r="AB367" s="1"/>
       <c r="AC367" s="1"/>
     </row>
-    <row r="368" spans="1:29" ht="13.2">
+    <row r="368" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A368" s="1"/>
       <c r="B368" s="1"/>
       <c r="C368" s="1"/>
@@ -12624,7 +12552,7 @@
       <c r="AB368" s="1"/>
       <c r="AC368" s="1"/>
     </row>
-    <row r="369" spans="1:29" ht="13.2">
+    <row r="369" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A369" s="1"/>
       <c r="B369" s="1"/>
       <c r="C369" s="1"/>
@@ -12655,7 +12583,7 @@
       <c r="AB369" s="1"/>
       <c r="AC369" s="1"/>
     </row>
-    <row r="370" spans="1:29" ht="13.2">
+    <row r="370" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A370" s="1"/>
       <c r="B370" s="1"/>
       <c r="C370" s="1"/>
@@ -12686,7 +12614,7 @@
       <c r="AB370" s="1"/>
       <c r="AC370" s="1"/>
     </row>
-    <row r="371" spans="1:29" ht="13.2">
+    <row r="371" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A371" s="1"/>
       <c r="B371" s="1"/>
       <c r="C371" s="1"/>
@@ -12717,7 +12645,7 @@
       <c r="AB371" s="1"/>
       <c r="AC371" s="1"/>
     </row>
-    <row r="372" spans="1:29" ht="13.2">
+    <row r="372" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A372" s="1"/>
       <c r="B372" s="1"/>
       <c r="C372" s="1"/>
@@ -12748,7 +12676,7 @@
       <c r="AB372" s="1"/>
       <c r="AC372" s="1"/>
     </row>
-    <row r="373" spans="1:29" ht="13.2">
+    <row r="373" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A373" s="1"/>
       <c r="B373" s="1"/>
       <c r="C373" s="1"/>
@@ -12779,7 +12707,7 @@
       <c r="AB373" s="1"/>
       <c r="AC373" s="1"/>
     </row>
-    <row r="374" spans="1:29" ht="13.2">
+    <row r="374" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A374" s="1"/>
       <c r="B374" s="1"/>
       <c r="C374" s="1"/>
@@ -12810,7 +12738,7 @@
       <c r="AB374" s="1"/>
       <c r="AC374" s="1"/>
     </row>
-    <row r="375" spans="1:29" ht="13.2">
+    <row r="375" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A375" s="1"/>
       <c r="B375" s="1"/>
       <c r="C375" s="1"/>
@@ -12841,7 +12769,7 @@
       <c r="AB375" s="1"/>
       <c r="AC375" s="1"/>
     </row>
-    <row r="376" spans="1:29" ht="13.2">
+    <row r="376" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A376" s="1"/>
       <c r="B376" s="1"/>
       <c r="C376" s="1"/>
@@ -12872,7 +12800,7 @@
       <c r="AB376" s="1"/>
       <c r="AC376" s="1"/>
     </row>
-    <row r="377" spans="1:29" ht="13.2">
+    <row r="377" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A377" s="1"/>
       <c r="B377" s="1"/>
       <c r="C377" s="1"/>
@@ -12903,7 +12831,7 @@
       <c r="AB377" s="1"/>
       <c r="AC377" s="1"/>
     </row>
-    <row r="378" spans="1:29" ht="13.2">
+    <row r="378" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A378" s="1"/>
       <c r="B378" s="1"/>
       <c r="C378" s="1"/>
@@ -12934,7 +12862,7 @@
       <c r="AB378" s="1"/>
       <c r="AC378" s="1"/>
     </row>
-    <row r="379" spans="1:29" ht="13.2">
+    <row r="379" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A379" s="1"/>
       <c r="B379" s="1"/>
       <c r="C379" s="1"/>
@@ -12965,7 +12893,7 @@
       <c r="AB379" s="1"/>
       <c r="AC379" s="1"/>
     </row>
-    <row r="380" spans="1:29" ht="13.2">
+    <row r="380" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A380" s="1"/>
       <c r="B380" s="1"/>
       <c r="C380" s="1"/>
@@ -12996,7 +12924,7 @@
       <c r="AB380" s="1"/>
       <c r="AC380" s="1"/>
     </row>
-    <row r="381" spans="1:29" ht="13.2">
+    <row r="381" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A381" s="1"/>
       <c r="B381" s="1"/>
       <c r="C381" s="1"/>
@@ -13027,7 +12955,7 @@
       <c r="AB381" s="1"/>
       <c r="AC381" s="1"/>
     </row>
-    <row r="382" spans="1:29" ht="13.2">
+    <row r="382" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A382" s="1"/>
       <c r="B382" s="1"/>
       <c r="C382" s="1"/>
@@ -13058,7 +12986,7 @@
       <c r="AB382" s="1"/>
       <c r="AC382" s="1"/>
     </row>
-    <row r="383" spans="1:29" ht="13.2">
+    <row r="383" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A383" s="1"/>
       <c r="B383" s="1"/>
       <c r="C383" s="1"/>
@@ -13089,7 +13017,7 @@
       <c r="AB383" s="1"/>
       <c r="AC383" s="1"/>
     </row>
-    <row r="384" spans="1:29" ht="13.2">
+    <row r="384" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A384" s="1"/>
       <c r="B384" s="1"/>
       <c r="C384" s="1"/>
@@ -13120,7 +13048,7 @@
       <c r="AB384" s="1"/>
       <c r="AC384" s="1"/>
     </row>
-    <row r="385" spans="1:29" ht="13.2">
+    <row r="385" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A385" s="1"/>
       <c r="B385" s="1"/>
       <c r="C385" s="1"/>
@@ -13151,7 +13079,7 @@
       <c r="AB385" s="1"/>
       <c r="AC385" s="1"/>
     </row>
-    <row r="386" spans="1:29" ht="13.2">
+    <row r="386" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A386" s="1"/>
       <c r="B386" s="1"/>
       <c r="C386" s="1"/>
@@ -13182,7 +13110,7 @@
       <c r="AB386" s="1"/>
       <c r="AC386" s="1"/>
     </row>
-    <row r="387" spans="1:29" ht="13.2">
+    <row r="387" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A387" s="1"/>
       <c r="B387" s="1"/>
       <c r="C387" s="1"/>
@@ -13213,7 +13141,7 @@
       <c r="AB387" s="1"/>
       <c r="AC387" s="1"/>
     </row>
-    <row r="388" spans="1:29" ht="13.2">
+    <row r="388" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A388" s="1"/>
       <c r="B388" s="1"/>
       <c r="C388" s="1"/>
@@ -13244,7 +13172,7 @@
       <c r="AB388" s="1"/>
       <c r="AC388" s="1"/>
     </row>
-    <row r="389" spans="1:29" ht="13.2">
+    <row r="389" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A389" s="1"/>
       <c r="B389" s="1"/>
       <c r="C389" s="1"/>
@@ -13275,7 +13203,7 @@
       <c r="AB389" s="1"/>
       <c r="AC389" s="1"/>
     </row>
-    <row r="390" spans="1:29" ht="13.2">
+    <row r="390" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A390" s="1"/>
       <c r="B390" s="1"/>
       <c r="C390" s="1"/>
@@ -13306,7 +13234,7 @@
       <c r="AB390" s="1"/>
       <c r="AC390" s="1"/>
     </row>
-    <row r="391" spans="1:29" ht="13.2">
+    <row r="391" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A391" s="1"/>
       <c r="B391" s="1"/>
       <c r="C391" s="1"/>
@@ -13337,7 +13265,7 @@
       <c r="AB391" s="1"/>
       <c r="AC391" s="1"/>
     </row>
-    <row r="392" spans="1:29" ht="13.2">
+    <row r="392" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A392" s="1"/>
       <c r="B392" s="1"/>
       <c r="C392" s="1"/>
@@ -13368,7 +13296,7 @@
       <c r="AB392" s="1"/>
       <c r="AC392" s="1"/>
     </row>
-    <row r="393" spans="1:29" ht="13.2">
+    <row r="393" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A393" s="1"/>
       <c r="B393" s="1"/>
       <c r="C393" s="1"/>
@@ -13399,7 +13327,7 @@
       <c r="AB393" s="1"/>
       <c r="AC393" s="1"/>
     </row>
-    <row r="394" spans="1:29" ht="13.2">
+    <row r="394" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A394" s="1"/>
       <c r="B394" s="1"/>
       <c r="C394" s="1"/>
@@ -13430,7 +13358,7 @@
       <c r="AB394" s="1"/>
       <c r="AC394" s="1"/>
     </row>
-    <row r="395" spans="1:29" ht="13.2">
+    <row r="395" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A395" s="1"/>
       <c r="B395" s="1"/>
       <c r="C395" s="1"/>
@@ -13461,7 +13389,7 @@
       <c r="AB395" s="1"/>
       <c r="AC395" s="1"/>
     </row>
-    <row r="396" spans="1:29" ht="13.2">
+    <row r="396" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A396" s="1"/>
       <c r="B396" s="1"/>
       <c r="C396" s="1"/>
@@ -13492,7 +13420,7 @@
       <c r="AB396" s="1"/>
       <c r="AC396" s="1"/>
     </row>
-    <row r="397" spans="1:29" ht="13.2">
+    <row r="397" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A397" s="1"/>
       <c r="B397" s="1"/>
       <c r="C397" s="1"/>
@@ -13523,7 +13451,7 @@
       <c r="AB397" s="1"/>
       <c r="AC397" s="1"/>
     </row>
-    <row r="398" spans="1:29" ht="13.2">
+    <row r="398" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A398" s="1"/>
       <c r="B398" s="1"/>
       <c r="C398" s="1"/>
@@ -13554,7 +13482,7 @@
       <c r="AB398" s="1"/>
       <c r="AC398" s="1"/>
     </row>
-    <row r="399" spans="1:29" ht="13.2">
+    <row r="399" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A399" s="1"/>
       <c r="B399" s="1"/>
       <c r="C399" s="1"/>
@@ -13585,7 +13513,7 @@
       <c r="AB399" s="1"/>
       <c r="AC399" s="1"/>
     </row>
-    <row r="400" spans="1:29" ht="13.2">
+    <row r="400" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A400" s="1"/>
       <c r="B400" s="1"/>
       <c r="C400" s="1"/>
@@ -13616,7 +13544,7 @@
       <c r="AB400" s="1"/>
       <c r="AC400" s="1"/>
     </row>
-    <row r="401" spans="1:29" ht="13.2">
+    <row r="401" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A401" s="1"/>
       <c r="B401" s="1"/>
       <c r="C401" s="1"/>
@@ -13647,7 +13575,7 @@
       <c r="AB401" s="1"/>
       <c r="AC401" s="1"/>
     </row>
-    <row r="402" spans="1:29" ht="13.2">
+    <row r="402" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A402" s="1"/>
       <c r="B402" s="1"/>
       <c r="C402" s="1"/>
@@ -13678,7 +13606,7 @@
       <c r="AB402" s="1"/>
       <c r="AC402" s="1"/>
     </row>
-    <row r="403" spans="1:29" ht="13.2">
+    <row r="403" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A403" s="1"/>
       <c r="B403" s="1"/>
       <c r="C403" s="1"/>
@@ -13709,7 +13637,7 @@
       <c r="AB403" s="1"/>
       <c r="AC403" s="1"/>
     </row>
-    <row r="404" spans="1:29" ht="13.2">
+    <row r="404" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A404" s="1"/>
       <c r="B404" s="1"/>
       <c r="C404" s="1"/>
@@ -13740,7 +13668,7 @@
       <c r="AB404" s="1"/>
       <c r="AC404" s="1"/>
     </row>
-    <row r="405" spans="1:29" ht="13.2">
+    <row r="405" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A405" s="1"/>
       <c r="B405" s="1"/>
       <c r="C405" s="1"/>
@@ -13771,7 +13699,7 @@
       <c r="AB405" s="1"/>
       <c r="AC405" s="1"/>
     </row>
-    <row r="406" spans="1:29" ht="13.2">
+    <row r="406" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A406" s="1"/>
       <c r="B406" s="1"/>
       <c r="C406" s="1"/>
@@ -13802,7 +13730,7 @@
       <c r="AB406" s="1"/>
       <c r="AC406" s="1"/>
     </row>
-    <row r="407" spans="1:29" ht="13.2">
+    <row r="407" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A407" s="1"/>
       <c r="B407" s="1"/>
       <c r="C407" s="1"/>
@@ -13833,7 +13761,7 @@
       <c r="AB407" s="1"/>
       <c r="AC407" s="1"/>
     </row>
-    <row r="408" spans="1:29" ht="13.2">
+    <row r="408" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A408" s="1"/>
       <c r="B408" s="1"/>
       <c r="C408" s="1"/>
@@ -13864,7 +13792,7 @@
       <c r="AB408" s="1"/>
       <c r="AC408" s="1"/>
     </row>
-    <row r="409" spans="1:29" ht="13.2">
+    <row r="409" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A409" s="1"/>
       <c r="B409" s="1"/>
       <c r="C409" s="1"/>
@@ -13895,7 +13823,7 @@
       <c r="AB409" s="1"/>
       <c r="AC409" s="1"/>
     </row>
-    <row r="410" spans="1:29" ht="13.2">
+    <row r="410" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A410" s="1"/>
       <c r="B410" s="1"/>
       <c r="C410" s="1"/>
@@ -13926,7 +13854,7 @@
       <c r="AB410" s="1"/>
       <c r="AC410" s="1"/>
     </row>
-    <row r="411" spans="1:29" ht="13.2">
+    <row r="411" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A411" s="1"/>
       <c r="B411" s="1"/>
       <c r="C411" s="1"/>
@@ -13957,7 +13885,7 @@
       <c r="AB411" s="1"/>
       <c r="AC411" s="1"/>
     </row>
-    <row r="412" spans="1:29" ht="13.2">
+    <row r="412" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A412" s="1"/>
       <c r="B412" s="1"/>
       <c r="C412" s="1"/>
@@ -13988,7 +13916,7 @@
       <c r="AB412" s="1"/>
       <c r="AC412" s="1"/>
     </row>
-    <row r="413" spans="1:29" ht="13.2">
+    <row r="413" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A413" s="1"/>
       <c r="B413" s="1"/>
       <c r="C413" s="1"/>
@@ -14019,7 +13947,7 @@
       <c r="AB413" s="1"/>
       <c r="AC413" s="1"/>
     </row>
-    <row r="414" spans="1:29" ht="13.2">
+    <row r="414" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A414" s="1"/>
       <c r="B414" s="1"/>
       <c r="C414" s="1"/>
@@ -14050,7 +13978,7 @@
       <c r="AB414" s="1"/>
       <c r="AC414" s="1"/>
     </row>
-    <row r="415" spans="1:29" ht="13.2">
+    <row r="415" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A415" s="1"/>
       <c r="B415" s="1"/>
       <c r="C415" s="1"/>
@@ -14081,7 +14009,7 @@
       <c r="AB415" s="1"/>
       <c r="AC415" s="1"/>
     </row>
-    <row r="416" spans="1:29" ht="13.2">
+    <row r="416" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A416" s="1"/>
       <c r="B416" s="1"/>
       <c r="C416" s="1"/>
@@ -14112,7 +14040,7 @@
       <c r="AB416" s="1"/>
       <c r="AC416" s="1"/>
     </row>
-    <row r="417" spans="1:29" ht="13.2">
+    <row r="417" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A417" s="1"/>
       <c r="B417" s="1"/>
       <c r="C417" s="1"/>
@@ -14143,7 +14071,7 @@
       <c r="AB417" s="1"/>
       <c r="AC417" s="1"/>
     </row>
-    <row r="418" spans="1:29" ht="13.2">
+    <row r="418" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A418" s="1"/>
       <c r="B418" s="1"/>
       <c r="C418" s="1"/>
@@ -14174,7 +14102,7 @@
       <c r="AB418" s="1"/>
       <c r="AC418" s="1"/>
     </row>
-    <row r="419" spans="1:29" ht="13.2">
+    <row r="419" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A419" s="1"/>
       <c r="B419" s="1"/>
       <c r="C419" s="1"/>
@@ -14205,7 +14133,7 @@
       <c r="AB419" s="1"/>
       <c r="AC419" s="1"/>
     </row>
-    <row r="420" spans="1:29" ht="13.2">
+    <row r="420" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A420" s="1"/>
       <c r="B420" s="1"/>
       <c r="C420" s="1"/>
@@ -14236,7 +14164,7 @@
       <c r="AB420" s="1"/>
       <c r="AC420" s="1"/>
     </row>
-    <row r="421" spans="1:29" ht="13.2">
+    <row r="421" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A421" s="1"/>
       <c r="B421" s="1"/>
       <c r="C421" s="1"/>
@@ -14267,7 +14195,7 @@
       <c r="AB421" s="1"/>
       <c r="AC421" s="1"/>
     </row>
-    <row r="422" spans="1:29" ht="13.2">
+    <row r="422" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A422" s="1"/>
       <c r="B422" s="1"/>
       <c r="C422" s="1"/>
@@ -14298,7 +14226,7 @@
       <c r="AB422" s="1"/>
       <c r="AC422" s="1"/>
     </row>
-    <row r="423" spans="1:29" ht="13.2">
+    <row r="423" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A423" s="1"/>
       <c r="B423" s="1"/>
       <c r="C423" s="1"/>
@@ -14329,7 +14257,7 @@
       <c r="AB423" s="1"/>
       <c r="AC423" s="1"/>
     </row>
-    <row r="424" spans="1:29" ht="13.2">
+    <row r="424" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A424" s="1"/>
       <c r="B424" s="1"/>
       <c r="C424" s="1"/>
@@ -14360,7 +14288,7 @@
       <c r="AB424" s="1"/>
       <c r="AC424" s="1"/>
     </row>
-    <row r="425" spans="1:29" ht="13.2">
+    <row r="425" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A425" s="1"/>
       <c r="B425" s="1"/>
       <c r="C425" s="1"/>
@@ -14391,7 +14319,7 @@
       <c r="AB425" s="1"/>
       <c r="AC425" s="1"/>
     </row>
-    <row r="426" spans="1:29" ht="13.2">
+    <row r="426" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A426" s="1"/>
       <c r="B426" s="1"/>
       <c r="C426" s="1"/>
@@ -14422,7 +14350,7 @@
       <c r="AB426" s="1"/>
       <c r="AC426" s="1"/>
     </row>
-    <row r="427" spans="1:29" ht="13.2">
+    <row r="427" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A427" s="1"/>
       <c r="B427" s="1"/>
       <c r="C427" s="1"/>
@@ -14453,7 +14381,7 @@
       <c r="AB427" s="1"/>
       <c r="AC427" s="1"/>
     </row>
-    <row r="428" spans="1:29" ht="13.2">
+    <row r="428" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A428" s="1"/>
       <c r="B428" s="1"/>
       <c r="C428" s="1"/>
@@ -14484,7 +14412,7 @@
       <c r="AB428" s="1"/>
       <c r="AC428" s="1"/>
     </row>
-    <row r="429" spans="1:29" ht="13.2">
+    <row r="429" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A429" s="1"/>
       <c r="B429" s="1"/>
       <c r="C429" s="1"/>
@@ -14515,7 +14443,7 @@
       <c r="AB429" s="1"/>
       <c r="AC429" s="1"/>
     </row>
-    <row r="430" spans="1:29" ht="13.2">
+    <row r="430" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A430" s="1"/>
       <c r="B430" s="1"/>
       <c r="C430" s="1"/>
@@ -14546,7 +14474,7 @@
       <c r="AB430" s="1"/>
       <c r="AC430" s="1"/>
     </row>
-    <row r="431" spans="1:29" ht="13.2">
+    <row r="431" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A431" s="1"/>
       <c r="B431" s="1"/>
       <c r="C431" s="1"/>
@@ -14577,7 +14505,7 @@
       <c r="AB431" s="1"/>
       <c r="AC431" s="1"/>
     </row>
-    <row r="432" spans="1:29" ht="13.2">
+    <row r="432" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A432" s="1"/>
       <c r="B432" s="1"/>
       <c r="C432" s="1"/>
@@ -14608,7 +14536,7 @@
       <c r="AB432" s="1"/>
       <c r="AC432" s="1"/>
     </row>
-    <row r="433" spans="1:29" ht="13.2">
+    <row r="433" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A433" s="1"/>
       <c r="B433" s="1"/>
       <c r="C433" s="1"/>
@@ -14639,7 +14567,7 @@
       <c r="AB433" s="1"/>
       <c r="AC433" s="1"/>
     </row>
-    <row r="434" spans="1:29" ht="13.2">
+    <row r="434" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A434" s="1"/>
       <c r="B434" s="1"/>
       <c r="C434" s="1"/>
@@ -14670,7 +14598,7 @@
       <c r="AB434" s="1"/>
       <c r="AC434" s="1"/>
     </row>
-    <row r="435" spans="1:29" ht="13.2">
+    <row r="435" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A435" s="1"/>
       <c r="B435" s="1"/>
       <c r="C435" s="1"/>
@@ -14701,7 +14629,7 @@
       <c r="AB435" s="1"/>
       <c r="AC435" s="1"/>
     </row>
-    <row r="436" spans="1:29" ht="13.2">
+    <row r="436" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A436" s="1"/>
       <c r="B436" s="1"/>
       <c r="C436" s="1"/>
@@ -14732,7 +14660,7 @@
       <c r="AB436" s="1"/>
       <c r="AC436" s="1"/>
     </row>
-    <row r="437" spans="1:29" ht="13.2">
+    <row r="437" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A437" s="1"/>
       <c r="B437" s="1"/>
       <c r="C437" s="1"/>
@@ -14763,7 +14691,7 @@
       <c r="AB437" s="1"/>
       <c r="AC437" s="1"/>
     </row>
-    <row r="438" spans="1:29" ht="13.2">
+    <row r="438" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A438" s="1"/>
       <c r="B438" s="1"/>
       <c r="C438" s="1"/>
@@ -14794,7 +14722,7 @@
       <c r="AB438" s="1"/>
       <c r="AC438" s="1"/>
     </row>
-    <row r="439" spans="1:29" ht="13.2">
+    <row r="439" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A439" s="1"/>
       <c r="B439" s="1"/>
       <c r="C439" s="1"/>
@@ -14825,7 +14753,7 @@
       <c r="AB439" s="1"/>
       <c r="AC439" s="1"/>
     </row>
-    <row r="440" spans="1:29" ht="13.2">
+    <row r="440" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A440" s="1"/>
       <c r="B440" s="1"/>
       <c r="C440" s="1"/>
@@ -14856,7 +14784,7 @@
       <c r="AB440" s="1"/>
       <c r="AC440" s="1"/>
     </row>
-    <row r="441" spans="1:29" ht="13.2">
+    <row r="441" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A441" s="1"/>
       <c r="B441" s="1"/>
       <c r="C441" s="1"/>
@@ -14887,7 +14815,7 @@
       <c r="AB441" s="1"/>
       <c r="AC441" s="1"/>
     </row>
-    <row r="442" spans="1:29" ht="13.2">
+    <row r="442" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A442" s="1"/>
       <c r="B442" s="1"/>
       <c r="C442" s="1"/>
@@ -14918,7 +14846,7 @@
       <c r="AB442" s="1"/>
       <c r="AC442" s="1"/>
     </row>
-    <row r="443" spans="1:29" ht="13.2">
+    <row r="443" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A443" s="1"/>
       <c r="B443" s="1"/>
       <c r="C443" s="1"/>
@@ -14949,7 +14877,7 @@
       <c r="AB443" s="1"/>
       <c r="AC443" s="1"/>
     </row>
-    <row r="444" spans="1:29" ht="13.2">
+    <row r="444" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A444" s="1"/>
       <c r="B444" s="1"/>
       <c r="C444" s="1"/>
@@ -14980,7 +14908,7 @@
       <c r="AB444" s="1"/>
       <c r="AC444" s="1"/>
     </row>
-    <row r="445" spans="1:29" ht="13.2">
+    <row r="445" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A445" s="1"/>
       <c r="B445" s="1"/>
       <c r="C445" s="1"/>
@@ -15011,7 +14939,7 @@
       <c r="AB445" s="1"/>
       <c r="AC445" s="1"/>
     </row>
-    <row r="446" spans="1:29" ht="13.2">
+    <row r="446" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A446" s="1"/>
       <c r="B446" s="1"/>
       <c r="C446" s="1"/>
@@ -15042,7 +14970,7 @@
       <c r="AB446" s="1"/>
       <c r="AC446" s="1"/>
     </row>
-    <row r="447" spans="1:29" ht="13.2">
+    <row r="447" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A447" s="1"/>
       <c r="B447" s="1"/>
       <c r="C447" s="1"/>
@@ -15073,7 +15001,7 @@
       <c r="AB447" s="1"/>
       <c r="AC447" s="1"/>
     </row>
-    <row r="448" spans="1:29" ht="13.2">
+    <row r="448" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A448" s="1"/>
       <c r="B448" s="1"/>
       <c r="C448" s="1"/>
@@ -15104,7 +15032,7 @@
       <c r="AB448" s="1"/>
       <c r="AC448" s="1"/>
     </row>
-    <row r="449" spans="1:29" ht="13.2">
+    <row r="449" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A449" s="1"/>
       <c r="B449" s="1"/>
       <c r="C449" s="1"/>
@@ -15135,7 +15063,7 @@
       <c r="AB449" s="1"/>
       <c r="AC449" s="1"/>
     </row>
-    <row r="450" spans="1:29" ht="13.2">
+    <row r="450" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A450" s="1"/>
       <c r="B450" s="1"/>
       <c r="C450" s="1"/>
@@ -15166,7 +15094,7 @@
       <c r="AB450" s="1"/>
       <c r="AC450" s="1"/>
     </row>
-    <row r="451" spans="1:29" ht="13.2">
+    <row r="451" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A451" s="1"/>
       <c r="B451" s="1"/>
       <c r="C451" s="1"/>
@@ -15197,7 +15125,7 @@
       <c r="AB451" s="1"/>
       <c r="AC451" s="1"/>
     </row>
-    <row r="452" spans="1:29" ht="13.2">
+    <row r="452" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A452" s="1"/>
       <c r="B452" s="1"/>
       <c r="C452" s="1"/>
@@ -15228,7 +15156,7 @@
       <c r="AB452" s="1"/>
       <c r="AC452" s="1"/>
     </row>
-    <row r="453" spans="1:29" ht="13.2">
+    <row r="453" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A453" s="1"/>
       <c r="B453" s="1"/>
       <c r="C453" s="1"/>
@@ -15259,7 +15187,7 @@
       <c r="AB453" s="1"/>
       <c r="AC453" s="1"/>
     </row>
-    <row r="454" spans="1:29" ht="13.2">
+    <row r="454" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A454" s="1"/>
       <c r="B454" s="1"/>
       <c r="C454" s="1"/>
@@ -15290,7 +15218,7 @@
       <c r="AB454" s="1"/>
       <c r="AC454" s="1"/>
     </row>
-    <row r="455" spans="1:29" ht="13.2">
+    <row r="455" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A455" s="1"/>
       <c r="B455" s="1"/>
       <c r="C455" s="1"/>
@@ -15321,7 +15249,7 @@
       <c r="AB455" s="1"/>
       <c r="AC455" s="1"/>
     </row>
-    <row r="456" spans="1:29" ht="13.2">
+    <row r="456" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A456" s="1"/>
       <c r="B456" s="1"/>
       <c r="C456" s="1"/>
@@ -15352,7 +15280,7 @@
       <c r="AB456" s="1"/>
       <c r="AC456" s="1"/>
     </row>
-    <row r="457" spans="1:29" ht="13.2">
+    <row r="457" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A457" s="1"/>
       <c r="B457" s="1"/>
       <c r="C457" s="1"/>
@@ -15383,7 +15311,7 @@
       <c r="AB457" s="1"/>
       <c r="AC457" s="1"/>
     </row>
-    <row r="458" spans="1:29" ht="13.2">
+    <row r="458" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A458" s="1"/>
       <c r="B458" s="1"/>
       <c r="C458" s="1"/>
@@ -15414,7 +15342,7 @@
       <c r="AB458" s="1"/>
       <c r="AC458" s="1"/>
     </row>
-    <row r="459" spans="1:29" ht="13.2">
+    <row r="459" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A459" s="1"/>
       <c r="B459" s="1"/>
       <c r="C459" s="1"/>
@@ -15445,7 +15373,7 @@
       <c r="AB459" s="1"/>
       <c r="AC459" s="1"/>
     </row>
-    <row r="460" spans="1:29" ht="13.2">
+    <row r="460" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A460" s="1"/>
       <c r="B460" s="1"/>
       <c r="C460" s="1"/>
@@ -15476,7 +15404,7 @@
       <c r="AB460" s="1"/>
       <c r="AC460" s="1"/>
     </row>
-    <row r="461" spans="1:29" ht="13.2">
+    <row r="461" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A461" s="1"/>
       <c r="B461" s="1"/>
       <c r="C461" s="1"/>
@@ -15507,7 +15435,7 @@
       <c r="AB461" s="1"/>
       <c r="AC461" s="1"/>
     </row>
-    <row r="462" spans="1:29" ht="13.2">
+    <row r="462" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A462" s="1"/>
       <c r="B462" s="1"/>
       <c r="C462" s="1"/>
@@ -15538,7 +15466,7 @@
       <c r="AB462" s="1"/>
       <c r="AC462" s="1"/>
     </row>
-    <row r="463" spans="1:29" ht="13.2">
+    <row r="463" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A463" s="1"/>
       <c r="B463" s="1"/>
       <c r="C463" s="1"/>
@@ -15569,7 +15497,7 @@
       <c r="AB463" s="1"/>
       <c r="AC463" s="1"/>
     </row>
-    <row r="464" spans="1:29" ht="13.2">
+    <row r="464" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A464" s="1"/>
       <c r="B464" s="1"/>
       <c r="C464" s="1"/>
@@ -15600,7 +15528,7 @@
       <c r="AB464" s="1"/>
       <c r="AC464" s="1"/>
     </row>
-    <row r="465" spans="1:29" ht="13.2">
+    <row r="465" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A465" s="1"/>
       <c r="B465" s="1"/>
       <c r="C465" s="1"/>
@@ -15631,7 +15559,7 @@
       <c r="AB465" s="1"/>
       <c r="AC465" s="1"/>
     </row>
-    <row r="466" spans="1:29" ht="13.2">
+    <row r="466" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A466" s="1"/>
       <c r="B466" s="1"/>
       <c r="C466" s="1"/>
@@ -15662,7 +15590,7 @@
       <c r="AB466" s="1"/>
       <c r="AC466" s="1"/>
     </row>
-    <row r="467" spans="1:29" ht="13.2">
+    <row r="467" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A467" s="1"/>
       <c r="B467" s="1"/>
       <c r="C467" s="1"/>
@@ -15693,7 +15621,7 @@
       <c r="AB467" s="1"/>
       <c r="AC467" s="1"/>
     </row>
-    <row r="468" spans="1:29" ht="13.2">
+    <row r="468" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A468" s="1"/>
       <c r="B468" s="1"/>
       <c r="C468" s="1"/>
@@ -15724,7 +15652,7 @@
       <c r="AB468" s="1"/>
       <c r="AC468" s="1"/>
     </row>
-    <row r="469" spans="1:29" ht="13.2">
+    <row r="469" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A469" s="1"/>
       <c r="B469" s="1"/>
       <c r="C469" s="1"/>
@@ -15755,7 +15683,7 @@
       <c r="AB469" s="1"/>
       <c r="AC469" s="1"/>
     </row>
-    <row r="470" spans="1:29" ht="13.2">
+    <row r="470" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A470" s="1"/>
       <c r="B470" s="1"/>
       <c r="C470" s="1"/>
@@ -15786,7 +15714,7 @@
       <c r="AB470" s="1"/>
       <c r="AC470" s="1"/>
     </row>
-    <row r="471" spans="1:29" ht="13.2">
+    <row r="471" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A471" s="1"/>
       <c r="B471" s="1"/>
       <c r="C471" s="1"/>
@@ -15817,7 +15745,7 @@
       <c r="AB471" s="1"/>
       <c r="AC471" s="1"/>
     </row>
-    <row r="472" spans="1:29" ht="13.2">
+    <row r="472" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A472" s="1"/>
       <c r="B472" s="1"/>
       <c r="C472" s="1"/>
@@ -15848,7 +15776,7 @@
       <c r="AB472" s="1"/>
       <c r="AC472" s="1"/>
     </row>
-    <row r="473" spans="1:29" ht="13.2">
+    <row r="473" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A473" s="1"/>
       <c r="B473" s="1"/>
       <c r="C473" s="1"/>
@@ -15879,7 +15807,7 @@
       <c r="AB473" s="1"/>
       <c r="AC473" s="1"/>
     </row>
-    <row r="474" spans="1:29" ht="13.2">
+    <row r="474" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A474" s="1"/>
       <c r="B474" s="1"/>
       <c r="C474" s="1"/>
@@ -15910,7 +15838,7 @@
       <c r="AB474" s="1"/>
       <c r="AC474" s="1"/>
     </row>
-    <row r="475" spans="1:29" ht="13.2">
+    <row r="475" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A475" s="1"/>
       <c r="B475" s="1"/>
       <c r="C475" s="1"/>
@@ -15941,7 +15869,7 @@
       <c r="AB475" s="1"/>
       <c r="AC475" s="1"/>
     </row>
-    <row r="476" spans="1:29" ht="13.2">
+    <row r="476" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A476" s="1"/>
       <c r="B476" s="1"/>
       <c r="C476" s="1"/>
@@ -15972,7 +15900,7 @@
       <c r="AB476" s="1"/>
       <c r="AC476" s="1"/>
     </row>
-    <row r="477" spans="1:29" ht="13.2">
+    <row r="477" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A477" s="1"/>
       <c r="B477" s="1"/>
       <c r="C477" s="1"/>
@@ -16003,7 +15931,7 @@
       <c r="AB477" s="1"/>
       <c r="AC477" s="1"/>
     </row>
-    <row r="478" spans="1:29" ht="13.2">
+    <row r="478" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A478" s="1"/>
       <c r="B478" s="1"/>
       <c r="C478" s="1"/>
@@ -16034,7 +15962,7 @@
       <c r="AB478" s="1"/>
       <c r="AC478" s="1"/>
     </row>
-    <row r="479" spans="1:29" ht="13.2">
+    <row r="479" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A479" s="1"/>
       <c r="B479" s="1"/>
       <c r="C479" s="1"/>
@@ -16065,7 +15993,7 @@
       <c r="AB479" s="1"/>
       <c r="AC479" s="1"/>
     </row>
-    <row r="480" spans="1:29" ht="13.2">
+    <row r="480" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A480" s="1"/>
       <c r="B480" s="1"/>
       <c r="C480" s="1"/>
@@ -16096,7 +16024,7 @@
       <c r="AB480" s="1"/>
       <c r="AC480" s="1"/>
     </row>
-    <row r="481" spans="1:29" ht="13.2">
+    <row r="481" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A481" s="1"/>
       <c r="B481" s="1"/>
       <c r="C481" s="1"/>
@@ -16127,7 +16055,7 @@
       <c r="AB481" s="1"/>
       <c r="AC481" s="1"/>
     </row>
-    <row r="482" spans="1:29" ht="13.2">
+    <row r="482" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A482" s="1"/>
       <c r="B482" s="1"/>
       <c r="C482" s="1"/>
@@ -16158,7 +16086,7 @@
       <c r="AB482" s="1"/>
       <c r="AC482" s="1"/>
     </row>
-    <row r="483" spans="1:29" ht="13.2">
+    <row r="483" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A483" s="1"/>
       <c r="B483" s="1"/>
       <c r="C483" s="1"/>
@@ -16189,7 +16117,7 @@
       <c r="AB483" s="1"/>
       <c r="AC483" s="1"/>
     </row>
-    <row r="484" spans="1:29" ht="13.2">
+    <row r="484" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A484" s="1"/>
       <c r="B484" s="1"/>
       <c r="C484" s="1"/>
@@ -16220,7 +16148,7 @@
       <c r="AB484" s="1"/>
       <c r="AC484" s="1"/>
     </row>
-    <row r="485" spans="1:29" ht="13.2">
+    <row r="485" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A485" s="1"/>
       <c r="B485" s="1"/>
       <c r="C485" s="1"/>
@@ -16251,7 +16179,7 @@
       <c r="AB485" s="1"/>
       <c r="AC485" s="1"/>
     </row>
-    <row r="486" spans="1:29" ht="13.2">
+    <row r="486" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A486" s="1"/>
       <c r="B486" s="1"/>
       <c r="C486" s="1"/>
@@ -16282,7 +16210,7 @@
       <c r="AB486" s="1"/>
       <c r="AC486" s="1"/>
     </row>
-    <row r="487" spans="1:29" ht="13.2">
+    <row r="487" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A487" s="1"/>
       <c r="B487" s="1"/>
       <c r="C487" s="1"/>
@@ -16313,7 +16241,7 @@
       <c r="AB487" s="1"/>
       <c r="AC487" s="1"/>
     </row>
-    <row r="488" spans="1:29" ht="13.2">
+    <row r="488" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A488" s="1"/>
       <c r="B488" s="1"/>
       <c r="C488" s="1"/>
@@ -16344,7 +16272,7 @@
       <c r="AB488" s="1"/>
       <c r="AC488" s="1"/>
     </row>
-    <row r="489" spans="1:29" ht="13.2">
+    <row r="489" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A489" s="1"/>
       <c r="B489" s="1"/>
       <c r="C489" s="1"/>
@@ -16375,7 +16303,7 @@
       <c r="AB489" s="1"/>
       <c r="AC489" s="1"/>
     </row>
-    <row r="490" spans="1:29" ht="13.2">
+    <row r="490" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A490" s="1"/>
       <c r="B490" s="1"/>
       <c r="C490" s="1"/>
@@ -16406,7 +16334,7 @@
       <c r="AB490" s="1"/>
       <c r="AC490" s="1"/>
     </row>
-    <row r="491" spans="1:29" ht="13.2">
+    <row r="491" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A491" s="1"/>
       <c r="B491" s="1"/>
       <c r="C491" s="1"/>
@@ -16437,7 +16365,7 @@
       <c r="AB491" s="1"/>
       <c r="AC491" s="1"/>
     </row>
-    <row r="492" spans="1:29" ht="13.2">
+    <row r="492" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A492" s="1"/>
       <c r="B492" s="1"/>
       <c r="C492" s="1"/>
@@ -16468,7 +16396,7 @@
       <c r="AB492" s="1"/>
       <c r="AC492" s="1"/>
     </row>
-    <row r="493" spans="1:29" ht="13.2">
+    <row r="493" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A493" s="1"/>
       <c r="B493" s="1"/>
       <c r="C493" s="1"/>
@@ -16499,7 +16427,7 @@
       <c r="AB493" s="1"/>
       <c r="AC493" s="1"/>
     </row>
-    <row r="494" spans="1:29" ht="13.2">
+    <row r="494" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A494" s="1"/>
       <c r="B494" s="1"/>
       <c r="C494" s="1"/>
@@ -16530,7 +16458,7 @@
       <c r="AB494" s="1"/>
       <c r="AC494" s="1"/>
     </row>
-    <row r="495" spans="1:29" ht="13.2">
+    <row r="495" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A495" s="1"/>
       <c r="B495" s="1"/>
       <c r="C495" s="1"/>
@@ -16561,7 +16489,7 @@
       <c r="AB495" s="1"/>
       <c r="AC495" s="1"/>
     </row>
-    <row r="496" spans="1:29" ht="13.2">
+    <row r="496" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A496" s="1"/>
       <c r="B496" s="1"/>
       <c r="C496" s="1"/>
@@ -16592,7 +16520,7 @@
       <c r="AB496" s="1"/>
       <c r="AC496" s="1"/>
     </row>
-    <row r="497" spans="1:29" ht="13.2">
+    <row r="497" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A497" s="1"/>
       <c r="B497" s="1"/>
       <c r="C497" s="1"/>
@@ -16623,7 +16551,7 @@
       <c r="AB497" s="1"/>
       <c r="AC497" s="1"/>
     </row>
-    <row r="498" spans="1:29" ht="13.2">
+    <row r="498" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A498" s="1"/>
       <c r="B498" s="1"/>
       <c r="C498" s="1"/>
@@ -16654,7 +16582,7 @@
       <c r="AB498" s="1"/>
       <c r="AC498" s="1"/>
     </row>
-    <row r="499" spans="1:29" ht="13.2">
+    <row r="499" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A499" s="1"/>
       <c r="B499" s="1"/>
       <c r="C499" s="1"/>
@@ -16685,7 +16613,7 @@
       <c r="AB499" s="1"/>
       <c r="AC499" s="1"/>
     </row>
-    <row r="500" spans="1:29" ht="13.2">
+    <row r="500" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A500" s="1"/>
       <c r="B500" s="1"/>
       <c r="C500" s="1"/>
@@ -16716,7 +16644,7 @@
       <c r="AB500" s="1"/>
       <c r="AC500" s="1"/>
     </row>
-    <row r="501" spans="1:29" ht="13.2">
+    <row r="501" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A501" s="1"/>
       <c r="B501" s="1"/>
       <c r="C501" s="1"/>
@@ -16747,7 +16675,7 @@
       <c r="AB501" s="1"/>
       <c r="AC501" s="1"/>
     </row>
-    <row r="502" spans="1:29" ht="13.2">
+    <row r="502" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A502" s="1"/>
       <c r="B502" s="1"/>
       <c r="C502" s="1"/>
@@ -16778,7 +16706,7 @@
       <c r="AB502" s="1"/>
       <c r="AC502" s="1"/>
     </row>
-    <row r="503" spans="1:29" ht="13.2">
+    <row r="503" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A503" s="1"/>
       <c r="B503" s="1"/>
       <c r="C503" s="1"/>
@@ -16809,7 +16737,7 @@
       <c r="AB503" s="1"/>
       <c r="AC503" s="1"/>
     </row>
-    <row r="504" spans="1:29" ht="13.2">
+    <row r="504" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A504" s="1"/>
       <c r="B504" s="1"/>
       <c r="C504" s="1"/>
@@ -16840,7 +16768,7 @@
       <c r="AB504" s="1"/>
       <c r="AC504" s="1"/>
     </row>
-    <row r="505" spans="1:29" ht="13.2">
+    <row r="505" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A505" s="1"/>
       <c r="B505" s="1"/>
       <c r="C505" s="1"/>
@@ -16871,7 +16799,7 @@
       <c r="AB505" s="1"/>
       <c r="AC505" s="1"/>
     </row>
-    <row r="506" spans="1:29" ht="13.2">
+    <row r="506" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A506" s="1"/>
       <c r="B506" s="1"/>
       <c r="C506" s="1"/>
@@ -16902,7 +16830,7 @@
       <c r="AB506" s="1"/>
       <c r="AC506" s="1"/>
     </row>
-    <row r="507" spans="1:29" ht="13.2">
+    <row r="507" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A507" s="1"/>
       <c r="B507" s="1"/>
       <c r="C507" s="1"/>
@@ -16933,7 +16861,7 @@
       <c r="AB507" s="1"/>
       <c r="AC507" s="1"/>
     </row>
-    <row r="508" spans="1:29" ht="13.2">
+    <row r="508" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A508" s="1"/>
       <c r="B508" s="1"/>
       <c r="C508" s="1"/>
@@ -16964,7 +16892,7 @@
       <c r="AB508" s="1"/>
       <c r="AC508" s="1"/>
     </row>
-    <row r="509" spans="1:29" ht="13.2">
+    <row r="509" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A509" s="1"/>
       <c r="B509" s="1"/>
       <c r="C509" s="1"/>
@@ -16995,7 +16923,7 @@
       <c r="AB509" s="1"/>
       <c r="AC509" s="1"/>
     </row>
-    <row r="510" spans="1:29" ht="13.2">
+    <row r="510" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A510" s="1"/>
       <c r="B510" s="1"/>
       <c r="C510" s="1"/>
@@ -17026,7 +16954,7 @@
       <c r="AB510" s="1"/>
       <c r="AC510" s="1"/>
     </row>
-    <row r="511" spans="1:29" ht="13.2">
+    <row r="511" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A511" s="1"/>
       <c r="B511" s="1"/>
       <c r="C511" s="1"/>
@@ -17057,7 +16985,7 @@
       <c r="AB511" s="1"/>
       <c r="AC511" s="1"/>
     </row>
-    <row r="512" spans="1:29" ht="13.2">
+    <row r="512" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A512" s="1"/>
       <c r="B512" s="1"/>
       <c r="C512" s="1"/>
@@ -17088,7 +17016,7 @@
       <c r="AB512" s="1"/>
       <c r="AC512" s="1"/>
     </row>
-    <row r="513" spans="1:29" ht="13.2">
+    <row r="513" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A513" s="1"/>
       <c r="B513" s="1"/>
       <c r="C513" s="1"/>
@@ -17119,7 +17047,7 @@
       <c r="AB513" s="1"/>
       <c r="AC513" s="1"/>
     </row>
-    <row r="514" spans="1:29" ht="13.2">
+    <row r="514" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A514" s="1"/>
       <c r="B514" s="1"/>
       <c r="C514" s="1"/>
@@ -17150,7 +17078,7 @@
       <c r="AB514" s="1"/>
       <c r="AC514" s="1"/>
     </row>
-    <row r="515" spans="1:29" ht="13.2">
+    <row r="515" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A515" s="1"/>
       <c r="B515" s="1"/>
       <c r="C515" s="1"/>
@@ -17181,7 +17109,7 @@
       <c r="AB515" s="1"/>
       <c r="AC515" s="1"/>
     </row>
-    <row r="516" spans="1:29" ht="13.2">
+    <row r="516" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A516" s="1"/>
       <c r="B516" s="1"/>
       <c r="C516" s="1"/>
@@ -17212,7 +17140,7 @@
       <c r="AB516" s="1"/>
       <c r="AC516" s="1"/>
     </row>
-    <row r="517" spans="1:29" ht="13.2">
+    <row r="517" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A517" s="1"/>
       <c r="B517" s="1"/>
       <c r="C517" s="1"/>
@@ -17243,7 +17171,7 @@
       <c r="AB517" s="1"/>
       <c r="AC517" s="1"/>
     </row>
-    <row r="518" spans="1:29" ht="13.2">
+    <row r="518" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A518" s="1"/>
       <c r="B518" s="1"/>
       <c r="C518" s="1"/>
@@ -17274,7 +17202,7 @@
       <c r="AB518" s="1"/>
       <c r="AC518" s="1"/>
     </row>
-    <row r="519" spans="1:29" ht="13.2">
+    <row r="519" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A519" s="1"/>
       <c r="B519" s="1"/>
       <c r="C519" s="1"/>
@@ -17305,7 +17233,7 @@
       <c r="AB519" s="1"/>
       <c r="AC519" s="1"/>
     </row>
-    <row r="520" spans="1:29" ht="13.2">
+    <row r="520" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A520" s="1"/>
       <c r="B520" s="1"/>
       <c r="C520" s="1"/>
@@ -17336,7 +17264,7 @@
       <c r="AB520" s="1"/>
       <c r="AC520" s="1"/>
     </row>
-    <row r="521" spans="1:29" ht="13.2">
+    <row r="521" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A521" s="1"/>
       <c r="B521" s="1"/>
       <c r="C521" s="1"/>
@@ -17367,7 +17295,7 @@
       <c r="AB521" s="1"/>
       <c r="AC521" s="1"/>
     </row>
-    <row r="522" spans="1:29" ht="13.2">
+    <row r="522" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A522" s="1"/>
       <c r="B522" s="1"/>
       <c r="C522" s="1"/>
@@ -17398,7 +17326,7 @@
       <c r="AB522" s="1"/>
       <c r="AC522" s="1"/>
     </row>
-    <row r="523" spans="1:29" ht="13.2">
+    <row r="523" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A523" s="1"/>
       <c r="B523" s="1"/>
       <c r="C523" s="1"/>
@@ -17429,7 +17357,7 @@
       <c r="AB523" s="1"/>
       <c r="AC523" s="1"/>
     </row>
-    <row r="524" spans="1:29" ht="13.2">
+    <row r="524" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A524" s="1"/>
       <c r="B524" s="1"/>
       <c r="C524" s="1"/>
@@ -17460,7 +17388,7 @@
       <c r="AB524" s="1"/>
       <c r="AC524" s="1"/>
     </row>
-    <row r="525" spans="1:29" ht="13.2">
+    <row r="525" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A525" s="1"/>
       <c r="B525" s="1"/>
       <c r="C525" s="1"/>
@@ -17491,7 +17419,7 @@
       <c r="AB525" s="1"/>
       <c r="AC525" s="1"/>
     </row>
-    <row r="526" spans="1:29" ht="13.2">
+    <row r="526" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A526" s="1"/>
       <c r="B526" s="1"/>
       <c r="C526" s="1"/>
@@ -17522,7 +17450,7 @@
       <c r="AB526" s="1"/>
       <c r="AC526" s="1"/>
     </row>
-    <row r="527" spans="1:29" ht="13.2">
+    <row r="527" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A527" s="1"/>
       <c r="B527" s="1"/>
       <c r="C527" s="1"/>
@@ -17553,7 +17481,7 @@
       <c r="AB527" s="1"/>
       <c r="AC527" s="1"/>
     </row>
-    <row r="528" spans="1:29" ht="13.2">
+    <row r="528" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A528" s="1"/>
       <c r="B528" s="1"/>
       <c r="C528" s="1"/>
@@ -17584,7 +17512,7 @@
       <c r="AB528" s="1"/>
       <c r="AC528" s="1"/>
     </row>
-    <row r="529" spans="1:29" ht="13.2">
+    <row r="529" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A529" s="1"/>
       <c r="B529" s="1"/>
       <c r="C529" s="1"/>
@@ -17615,7 +17543,7 @@
       <c r="AB529" s="1"/>
       <c r="AC529" s="1"/>
     </row>
-    <row r="530" spans="1:29" ht="13.2">
+    <row r="530" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A530" s="1"/>
       <c r="B530" s="1"/>
       <c r="C530" s="1"/>
@@ -17646,7 +17574,7 @@
       <c r="AB530" s="1"/>
       <c r="AC530" s="1"/>
     </row>
-    <row r="531" spans="1:29" ht="13.2">
+    <row r="531" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A531" s="1"/>
       <c r="B531" s="1"/>
       <c r="C531" s="1"/>
@@ -17677,7 +17605,7 @@
       <c r="AB531" s="1"/>
       <c r="AC531" s="1"/>
     </row>
-    <row r="532" spans="1:29" ht="13.2">
+    <row r="532" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A532" s="1"/>
       <c r="B532" s="1"/>
       <c r="C532" s="1"/>
@@ -17708,7 +17636,7 @@
       <c r="AB532" s="1"/>
       <c r="AC532" s="1"/>
     </row>
-    <row r="533" spans="1:29" ht="13.2">
+    <row r="533" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A533" s="1"/>
       <c r="B533" s="1"/>
       <c r="C533" s="1"/>
@@ -17739,7 +17667,7 @@
       <c r="AB533" s="1"/>
       <c r="AC533" s="1"/>
     </row>
-    <row r="534" spans="1:29" ht="13.2">
+    <row r="534" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A534" s="1"/>
       <c r="B534" s="1"/>
       <c r="C534" s="1"/>
@@ -17770,7 +17698,7 @@
       <c r="AB534" s="1"/>
       <c r="AC534" s="1"/>
     </row>
-    <row r="535" spans="1:29" ht="13.2">
+    <row r="535" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A535" s="1"/>
       <c r="B535" s="1"/>
       <c r="C535" s="1"/>
@@ -17801,7 +17729,7 @@
       <c r="AB535" s="1"/>
       <c r="AC535" s="1"/>
     </row>
-    <row r="536" spans="1:29" ht="13.2">
+    <row r="536" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A536" s="1"/>
       <c r="B536" s="1"/>
       <c r="C536" s="1"/>
@@ -17832,7 +17760,7 @@
       <c r="AB536" s="1"/>
       <c r="AC536" s="1"/>
     </row>
-    <row r="537" spans="1:29" ht="13.2">
+    <row r="537" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A537" s="1"/>
       <c r="B537" s="1"/>
       <c r="C537" s="1"/>
@@ -17863,7 +17791,7 @@
       <c r="AB537" s="1"/>
       <c r="AC537" s="1"/>
     </row>
-    <row r="538" spans="1:29" ht="13.2">
+    <row r="538" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A538" s="1"/>
       <c r="B538" s="1"/>
       <c r="C538" s="1"/>
@@ -17894,7 +17822,7 @@
       <c r="AB538" s="1"/>
       <c r="AC538" s="1"/>
     </row>
-    <row r="539" spans="1:29" ht="13.2">
+    <row r="539" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A539" s="1"/>
       <c r="B539" s="1"/>
       <c r="C539" s="1"/>
@@ -17925,7 +17853,7 @@
       <c r="AB539" s="1"/>
       <c r="AC539" s="1"/>
     </row>
-    <row r="540" spans="1:29" ht="13.2">
+    <row r="540" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A540" s="1"/>
       <c r="B540" s="1"/>
       <c r="C540" s="1"/>
@@ -17956,7 +17884,7 @@
       <c r="AB540" s="1"/>
       <c r="AC540" s="1"/>
     </row>
-    <row r="541" spans="1:29" ht="13.2">
+    <row r="541" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A541" s="1"/>
       <c r="B541" s="1"/>
       <c r="C541" s="1"/>
@@ -17987,7 +17915,7 @@
       <c r="AB541" s="1"/>
       <c r="AC541" s="1"/>
     </row>
-    <row r="542" spans="1:29" ht="13.2">
+    <row r="542" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A542" s="1"/>
       <c r="B542" s="1"/>
       <c r="C542" s="1"/>
@@ -18018,7 +17946,7 @@
       <c r="AB542" s="1"/>
       <c r="AC542" s="1"/>
     </row>
-    <row r="543" spans="1:29" ht="13.2">
+    <row r="543" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A543" s="1"/>
       <c r="B543" s="1"/>
       <c r="C543" s="1"/>
@@ -18049,7 +17977,7 @@
       <c r="AB543" s="1"/>
       <c r="AC543" s="1"/>
     </row>
-    <row r="544" spans="1:29" ht="13.2">
+    <row r="544" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A544" s="1"/>
       <c r="B544" s="1"/>
       <c r="C544" s="1"/>
@@ -18080,7 +18008,7 @@
       <c r="AB544" s="1"/>
       <c r="AC544" s="1"/>
     </row>
-    <row r="545" spans="1:29" ht="13.2">
+    <row r="545" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A545" s="1"/>
       <c r="B545" s="1"/>
       <c r="C545" s="1"/>
@@ -18111,7 +18039,7 @@
       <c r="AB545" s="1"/>
       <c r="AC545" s="1"/>
     </row>
-    <row r="546" spans="1:29" ht="13.2">
+    <row r="546" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A546" s="1"/>
       <c r="B546" s="1"/>
       <c r="C546" s="1"/>
@@ -18142,7 +18070,7 @@
       <c r="AB546" s="1"/>
       <c r="AC546" s="1"/>
     </row>
-    <row r="547" spans="1:29" ht="13.2">
+    <row r="547" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A547" s="1"/>
       <c r="B547" s="1"/>
       <c r="C547" s="1"/>
@@ -18173,7 +18101,7 @@
       <c r="AB547" s="1"/>
       <c r="AC547" s="1"/>
     </row>
-    <row r="548" spans="1:29" ht="13.2">
+    <row r="548" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A548" s="1"/>
       <c r="B548" s="1"/>
       <c r="C548" s="1"/>
@@ -18204,7 +18132,7 @@
       <c r="AB548" s="1"/>
       <c r="AC548" s="1"/>
     </row>
-    <row r="549" spans="1:29" ht="13.2">
+    <row r="549" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A549" s="1"/>
       <c r="B549" s="1"/>
       <c r="C549" s="1"/>
@@ -18235,7 +18163,7 @@
       <c r="AB549" s="1"/>
       <c r="AC549" s="1"/>
     </row>
-    <row r="550" spans="1:29" ht="13.2">
+    <row r="550" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A550" s="1"/>
       <c r="B550" s="1"/>
       <c r="C550" s="1"/>
@@ -18266,7 +18194,7 @@
       <c r="AB550" s="1"/>
       <c r="AC550" s="1"/>
     </row>
-    <row r="551" spans="1:29" ht="13.2">
+    <row r="551" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A551" s="1"/>
       <c r="B551" s="1"/>
       <c r="C551" s="1"/>
@@ -18297,7 +18225,7 @@
       <c r="AB551" s="1"/>
       <c r="AC551" s="1"/>
     </row>
-    <row r="552" spans="1:29" ht="13.2">
+    <row r="552" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A552" s="1"/>
       <c r="B552" s="1"/>
       <c r="C552" s="1"/>
@@ -18328,7 +18256,7 @@
       <c r="AB552" s="1"/>
       <c r="AC552" s="1"/>
     </row>
-    <row r="553" spans="1:29" ht="13.2">
+    <row r="553" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A553" s="1"/>
       <c r="B553" s="1"/>
       <c r="C553" s="1"/>
@@ -18359,7 +18287,7 @@
       <c r="AB553" s="1"/>
       <c r="AC553" s="1"/>
     </row>
-    <row r="554" spans="1:29" ht="13.2">
+    <row r="554" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A554" s="1"/>
       <c r="B554" s="1"/>
       <c r="C554" s="1"/>
@@ -18390,7 +18318,7 @@
       <c r="AB554" s="1"/>
       <c r="AC554" s="1"/>
     </row>
-    <row r="555" spans="1:29" ht="13.2">
+    <row r="555" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A555" s="1"/>
       <c r="B555" s="1"/>
       <c r="C555" s="1"/>
@@ -18421,7 +18349,7 @@
       <c r="AB555" s="1"/>
       <c r="AC555" s="1"/>
     </row>
-    <row r="556" spans="1:29" ht="13.2">
+    <row r="556" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A556" s="1"/>
       <c r="B556" s="1"/>
       <c r="C556" s="1"/>
@@ -18452,7 +18380,7 @@
       <c r="AB556" s="1"/>
       <c r="AC556" s="1"/>
     </row>
-    <row r="557" spans="1:29" ht="13.2">
+    <row r="557" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A557" s="1"/>
       <c r="B557" s="1"/>
       <c r="C557" s="1"/>
@@ -18483,7 +18411,7 @@
       <c r="AB557" s="1"/>
       <c r="AC557" s="1"/>
     </row>
-    <row r="558" spans="1:29" ht="13.2">
+    <row r="558" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A558" s="1"/>
       <c r="B558" s="1"/>
       <c r="C558" s="1"/>
@@ -18514,7 +18442,7 @@
       <c r="AB558" s="1"/>
       <c r="AC558" s="1"/>
     </row>
-    <row r="559" spans="1:29" ht="13.2">
+    <row r="559" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A559" s="1"/>
       <c r="B559" s="1"/>
       <c r="C559" s="1"/>
@@ -18545,7 +18473,7 @@
       <c r="AB559" s="1"/>
       <c r="AC559" s="1"/>
     </row>
-    <row r="560" spans="1:29" ht="13.2">
+    <row r="560" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A560" s="1"/>
       <c r="B560" s="1"/>
       <c r="C560" s="1"/>
@@ -18576,7 +18504,7 @@
       <c r="AB560" s="1"/>
       <c r="AC560" s="1"/>
     </row>
-    <row r="561" spans="1:29" ht="13.2">
+    <row r="561" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A561" s="1"/>
       <c r="B561" s="1"/>
       <c r="C561" s="1"/>
@@ -18607,7 +18535,7 @@
       <c r="AB561" s="1"/>
       <c r="AC561" s="1"/>
     </row>
-    <row r="562" spans="1:29" ht="13.2">
+    <row r="562" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A562" s="1"/>
       <c r="B562" s="1"/>
       <c r="C562" s="1"/>
@@ -18638,7 +18566,7 @@
       <c r="AB562" s="1"/>
       <c r="AC562" s="1"/>
     </row>
-    <row r="563" spans="1:29" ht="13.2">
+    <row r="563" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A563" s="1"/>
       <c r="B563" s="1"/>
       <c r="C563" s="1"/>
@@ -18669,7 +18597,7 @@
       <c r="AB563" s="1"/>
       <c r="AC563" s="1"/>
     </row>
-    <row r="564" spans="1:29" ht="13.2">
+    <row r="564" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A564" s="1"/>
       <c r="B564" s="1"/>
       <c r="C564" s="1"/>
@@ -18700,7 +18628,7 @@
       <c r="AB564" s="1"/>
       <c r="AC564" s="1"/>
     </row>
-    <row r="565" spans="1:29" ht="13.2">
+    <row r="565" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A565" s="1"/>
       <c r="B565" s="1"/>
       <c r="C565" s="1"/>
@@ -18731,7 +18659,7 @@
       <c r="AB565" s="1"/>
       <c r="AC565" s="1"/>
     </row>
-    <row r="566" spans="1:29" ht="13.2">
+    <row r="566" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A566" s="1"/>
       <c r="B566" s="1"/>
       <c r="C566" s="1"/>
@@ -18762,7 +18690,7 @@
       <c r="AB566" s="1"/>
       <c r="AC566" s="1"/>
     </row>
-    <row r="567" spans="1:29" ht="13.2">
+    <row r="567" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A567" s="1"/>
       <c r="B567" s="1"/>
       <c r="C567" s="1"/>
@@ -18793,7 +18721,7 @@
       <c r="AB567" s="1"/>
       <c r="AC567" s="1"/>
     </row>
-    <row r="568" spans="1:29" ht="13.2">
+    <row r="568" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A568" s="1"/>
       <c r="B568" s="1"/>
       <c r="C568" s="1"/>
@@ -18824,7 +18752,7 @@
       <c r="AB568" s="1"/>
       <c r="AC568" s="1"/>
     </row>
-    <row r="569" spans="1:29" ht="13.2">
+    <row r="569" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A569" s="1"/>
       <c r="B569" s="1"/>
       <c r="C569" s="1"/>
@@ -18855,7 +18783,7 @@
       <c r="AB569" s="1"/>
       <c r="AC569" s="1"/>
     </row>
-    <row r="570" spans="1:29" ht="13.2">
+    <row r="570" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A570" s="1"/>
       <c r="B570" s="1"/>
       <c r="C570" s="1"/>
@@ -18886,7 +18814,7 @@
       <c r="AB570" s="1"/>
       <c r="AC570" s="1"/>
     </row>
-    <row r="571" spans="1:29" ht="13.2">
+    <row r="571" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A571" s="1"/>
       <c r="B571" s="1"/>
       <c r="C571" s="1"/>
@@ -18917,7 +18845,7 @@
       <c r="AB571" s="1"/>
       <c r="AC571" s="1"/>
     </row>
-    <row r="572" spans="1:29" ht="13.2">
+    <row r="572" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A572" s="1"/>
       <c r="B572" s="1"/>
       <c r="C572" s="1"/>
@@ -18948,7 +18876,7 @@
       <c r="AB572" s="1"/>
       <c r="AC572" s="1"/>
     </row>
-    <row r="573" spans="1:29" ht="13.2">
+    <row r="573" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A573" s="1"/>
       <c r="B573" s="1"/>
       <c r="C573" s="1"/>
@@ -18979,7 +18907,7 @@
       <c r="AB573" s="1"/>
       <c r="AC573" s="1"/>
     </row>
-    <row r="574" spans="1:29" ht="13.2">
+    <row r="574" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A574" s="1"/>
       <c r="B574" s="1"/>
       <c r="C574" s="1"/>
@@ -19010,7 +18938,7 @@
       <c r="AB574" s="1"/>
       <c r="AC574" s="1"/>
     </row>
-    <row r="575" spans="1:29" ht="13.2">
+    <row r="575" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A575" s="1"/>
       <c r="B575" s="1"/>
       <c r="C575" s="1"/>
@@ -19041,7 +18969,7 @@
       <c r="AB575" s="1"/>
       <c r="AC575" s="1"/>
     </row>
-    <row r="576" spans="1:29" ht="13.2">
+    <row r="576" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A576" s="1"/>
       <c r="B576" s="1"/>
       <c r="C576" s="1"/>
@@ -19072,7 +19000,7 @@
       <c r="AB576" s="1"/>
       <c r="AC576" s="1"/>
     </row>
-    <row r="577" spans="1:29" ht="13.2">
+    <row r="577" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A577" s="1"/>
       <c r="B577" s="1"/>
       <c r="C577" s="1"/>
@@ -19103,7 +19031,7 @@
       <c r="AB577" s="1"/>
       <c r="AC577" s="1"/>
     </row>
-    <row r="578" spans="1:29" ht="13.2">
+    <row r="578" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A578" s="1"/>
       <c r="B578" s="1"/>
       <c r="C578" s="1"/>
@@ -19134,7 +19062,7 @@
       <c r="AB578" s="1"/>
       <c r="AC578" s="1"/>
     </row>
-    <row r="579" spans="1:29" ht="13.2">
+    <row r="579" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A579" s="1"/>
       <c r="B579" s="1"/>
       <c r="C579" s="1"/>
@@ -19165,7 +19093,7 @@
       <c r="AB579" s="1"/>
       <c r="AC579" s="1"/>
     </row>
-    <row r="580" spans="1:29" ht="13.2">
+    <row r="580" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A580" s="1"/>
       <c r="B580" s="1"/>
       <c r="C580" s="1"/>
@@ -19196,7 +19124,7 @@
       <c r="AB580" s="1"/>
       <c r="AC580" s="1"/>
     </row>
-    <row r="581" spans="1:29" ht="13.2">
+    <row r="581" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A581" s="1"/>
       <c r="B581" s="1"/>
       <c r="C581" s="1"/>
@@ -19227,7 +19155,7 @@
       <c r="AB581" s="1"/>
       <c r="AC581" s="1"/>
     </row>
-    <row r="582" spans="1:29" ht="13.2">
+    <row r="582" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A582" s="1"/>
       <c r="B582" s="1"/>
       <c r="C582" s="1"/>
@@ -19258,7 +19186,7 @@
       <c r="AB582" s="1"/>
       <c r="AC582" s="1"/>
     </row>
-    <row r="583" spans="1:29" ht="13.2">
+    <row r="583" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A583" s="1"/>
       <c r="B583" s="1"/>
       <c r="C583" s="1"/>
@@ -19289,7 +19217,7 @@
       <c r="AB583" s="1"/>
       <c r="AC583" s="1"/>
     </row>
-    <row r="584" spans="1:29" ht="13.2">
+    <row r="584" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A584" s="1"/>
       <c r="B584" s="1"/>
       <c r="C584" s="1"/>
@@ -19320,7 +19248,7 @@
       <c r="AB584" s="1"/>
       <c r="AC584" s="1"/>
     </row>
-    <row r="585" spans="1:29" ht="13.2">
+    <row r="585" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A585" s="1"/>
       <c r="B585" s="1"/>
       <c r="C585" s="1"/>
@@ -19351,7 +19279,7 @@
       <c r="AB585" s="1"/>
       <c r="AC585" s="1"/>
     </row>
-    <row r="586" spans="1:29" ht="13.2">
+    <row r="586" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A586" s="1"/>
       <c r="B586" s="1"/>
       <c r="C586" s="1"/>
@@ -19382,7 +19310,7 @@
       <c r="AB586" s="1"/>
       <c r="AC586" s="1"/>
     </row>
-    <row r="587" spans="1:29" ht="13.2">
+    <row r="587" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A587" s="1"/>
       <c r="B587" s="1"/>
       <c r="C587" s="1"/>
@@ -19413,7 +19341,7 @@
       <c r="AB587" s="1"/>
       <c r="AC587" s="1"/>
     </row>
-    <row r="588" spans="1:29" ht="13.2">
+    <row r="588" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A588" s="1"/>
       <c r="B588" s="1"/>
       <c r="C588" s="1"/>
@@ -19444,7 +19372,7 @@
       <c r="AB588" s="1"/>
       <c r="AC588" s="1"/>
     </row>
-    <row r="589" spans="1:29" ht="13.2">
+    <row r="589" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A589" s="1"/>
       <c r="B589" s="1"/>
       <c r="C589" s="1"/>
@@ -19475,7 +19403,7 @@
       <c r="AB589" s="1"/>
       <c r="AC589" s="1"/>
     </row>
-    <row r="590" spans="1:29" ht="13.2">
+    <row r="590" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A590" s="1"/>
       <c r="B590" s="1"/>
       <c r="C590" s="1"/>
@@ -19506,7 +19434,7 @@
       <c r="AB590" s="1"/>
       <c r="AC590" s="1"/>
     </row>
-    <row r="591" spans="1:29" ht="13.2">
+    <row r="591" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A591" s="1"/>
       <c r="B591" s="1"/>
       <c r="C591" s="1"/>
@@ -19537,7 +19465,7 @@
       <c r="AB591" s="1"/>
       <c r="AC591" s="1"/>
     </row>
-    <row r="592" spans="1:29" ht="13.2">
+    <row r="592" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A592" s="1"/>
       <c r="B592" s="1"/>
       <c r="C592" s="1"/>
@@ -19568,7 +19496,7 @@
       <c r="AB592" s="1"/>
       <c r="AC592" s="1"/>
     </row>
-    <row r="593" spans="1:29" ht="13.2">
+    <row r="593" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A593" s="1"/>
       <c r="B593" s="1"/>
       <c r="C593" s="1"/>
@@ -19599,7 +19527,7 @@
       <c r="AB593" s="1"/>
       <c r="AC593" s="1"/>
     </row>
-    <row r="594" spans="1:29" ht="13.2">
+    <row r="594" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A594" s="1"/>
       <c r="B594" s="1"/>
       <c r="C594" s="1"/>
@@ -19630,7 +19558,7 @@
       <c r="AB594" s="1"/>
       <c r="AC594" s="1"/>
     </row>
-    <row r="595" spans="1:29" ht="13.2">
+    <row r="595" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A595" s="1"/>
       <c r="B595" s="1"/>
       <c r="C595" s="1"/>
@@ -19661,7 +19589,7 @@
       <c r="AB595" s="1"/>
       <c r="AC595" s="1"/>
     </row>
-    <row r="596" spans="1:29" ht="13.2">
+    <row r="596" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A596" s="1"/>
       <c r="B596" s="1"/>
       <c r="C596" s="1"/>
@@ -19692,7 +19620,7 @@
       <c r="AB596" s="1"/>
       <c r="AC596" s="1"/>
     </row>
-    <row r="597" spans="1:29" ht="13.2">
+    <row r="597" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A597" s="1"/>
       <c r="B597" s="1"/>
       <c r="C597" s="1"/>
@@ -19723,7 +19651,7 @@
       <c r="AB597" s="1"/>
       <c r="AC597" s="1"/>
     </row>
-    <row r="598" spans="1:29" ht="13.2">
+    <row r="598" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A598" s="1"/>
       <c r="B598" s="1"/>
       <c r="C598" s="1"/>
@@ -19754,7 +19682,7 @@
       <c r="AB598" s="1"/>
       <c r="AC598" s="1"/>
     </row>
-    <row r="599" spans="1:29" ht="13.2">
+    <row r="599" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A599" s="1"/>
       <c r="B599" s="1"/>
       <c r="C599" s="1"/>
@@ -19785,7 +19713,7 @@
       <c r="AB599" s="1"/>
       <c r="AC599" s="1"/>
     </row>
-    <row r="600" spans="1:29" ht="13.2">
+    <row r="600" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A600" s="1"/>
       <c r="B600" s="1"/>
       <c r="C600" s="1"/>
@@ -19816,7 +19744,7 @@
       <c r="AB600" s="1"/>
       <c r="AC600" s="1"/>
     </row>
-    <row r="601" spans="1:29" ht="13.2">
+    <row r="601" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A601" s="1"/>
       <c r="B601" s="1"/>
       <c r="C601" s="1"/>
@@ -19847,7 +19775,7 @@
       <c r="AB601" s="1"/>
       <c r="AC601" s="1"/>
     </row>
-    <row r="602" spans="1:29" ht="13.2">
+    <row r="602" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A602" s="1"/>
       <c r="B602" s="1"/>
       <c r="C602" s="1"/>
@@ -19878,7 +19806,7 @@
       <c r="AB602" s="1"/>
       <c r="AC602" s="1"/>
     </row>
-    <row r="603" spans="1:29" ht="13.2">
+    <row r="603" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A603" s="1"/>
       <c r="B603" s="1"/>
       <c r="C603" s="1"/>
@@ -19909,7 +19837,7 @@
       <c r="AB603" s="1"/>
       <c r="AC603" s="1"/>
     </row>
-    <row r="604" spans="1:29" ht="13.2">
+    <row r="604" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A604" s="1"/>
       <c r="B604" s="1"/>
       <c r="C604" s="1"/>
@@ -19940,7 +19868,7 @@
       <c r="AB604" s="1"/>
       <c r="AC604" s="1"/>
     </row>
-    <row r="605" spans="1:29" ht="13.2">
+    <row r="605" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A605" s="1"/>
       <c r="B605" s="1"/>
       <c r="C605" s="1"/>
@@ -19971,7 +19899,7 @@
       <c r="AB605" s="1"/>
       <c r="AC605" s="1"/>
     </row>
-    <row r="606" spans="1:29" ht="13.2">
+    <row r="606" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A606" s="1"/>
       <c r="B606" s="1"/>
       <c r="C606" s="1"/>
@@ -20002,7 +19930,7 @@
       <c r="AB606" s="1"/>
       <c r="AC606" s="1"/>
     </row>
-    <row r="607" spans="1:29" ht="13.2">
+    <row r="607" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A607" s="1"/>
       <c r="B607" s="1"/>
       <c r="C607" s="1"/>
@@ -20033,7 +19961,7 @@
       <c r="AB607" s="1"/>
       <c r="AC607" s="1"/>
     </row>
-    <row r="608" spans="1:29" ht="13.2">
+    <row r="608" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A608" s="1"/>
       <c r="B608" s="1"/>
       <c r="C608" s="1"/>
@@ -20064,7 +19992,7 @@
       <c r="AB608" s="1"/>
       <c r="AC608" s="1"/>
     </row>
-    <row r="609" spans="1:29" ht="13.2">
+    <row r="609" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A609" s="1"/>
       <c r="B609" s="1"/>
       <c r="C609" s="1"/>
@@ -20095,7 +20023,7 @@
       <c r="AB609" s="1"/>
       <c r="AC609" s="1"/>
     </row>
-    <row r="610" spans="1:29" ht="13.2">
+    <row r="610" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A610" s="1"/>
       <c r="B610" s="1"/>
       <c r="C610" s="1"/>
@@ -20126,7 +20054,7 @@
       <c r="AB610" s="1"/>
       <c r="AC610" s="1"/>
     </row>
-    <row r="611" spans="1:29" ht="13.2">
+    <row r="611" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A611" s="1"/>
       <c r="B611" s="1"/>
       <c r="C611" s="1"/>
@@ -20157,7 +20085,7 @@
       <c r="AB611" s="1"/>
       <c r="AC611" s="1"/>
     </row>
-    <row r="612" spans="1:29" ht="13.2">
+    <row r="612" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A612" s="1"/>
       <c r="B612" s="1"/>
       <c r="C612" s="1"/>
@@ -20188,7 +20116,7 @@
       <c r="AB612" s="1"/>
       <c r="AC612" s="1"/>
     </row>
-    <row r="613" spans="1:29" ht="13.2">
+    <row r="613" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A613" s="1"/>
       <c r="B613" s="1"/>
       <c r="C613" s="1"/>
@@ -20219,7 +20147,7 @@
       <c r="AB613" s="1"/>
       <c r="AC613" s="1"/>
     </row>
-    <row r="614" spans="1:29" ht="13.2">
+    <row r="614" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A614" s="1"/>
       <c r="B614" s="1"/>
       <c r="C614" s="1"/>
@@ -20250,7 +20178,7 @@
       <c r="AB614" s="1"/>
       <c r="AC614" s="1"/>
     </row>
-    <row r="615" spans="1:29" ht="13.2">
+    <row r="615" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A615" s="1"/>
       <c r="B615" s="1"/>
       <c r="C615" s="1"/>
@@ -20281,7 +20209,7 @@
       <c r="AB615" s="1"/>
       <c r="AC615" s="1"/>
     </row>
-    <row r="616" spans="1:29" ht="13.2">
+    <row r="616" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A616" s="1"/>
       <c r="B616" s="1"/>
       <c r="C616" s="1"/>
@@ -20312,7 +20240,7 @@
       <c r="AB616" s="1"/>
       <c r="AC616" s="1"/>
     </row>
-    <row r="617" spans="1:29" ht="13.2">
+    <row r="617" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A617" s="1"/>
       <c r="B617" s="1"/>
       <c r="C617" s="1"/>
@@ -20343,7 +20271,7 @@
       <c r="AB617" s="1"/>
       <c r="AC617" s="1"/>
     </row>
-    <row r="618" spans="1:29" ht="13.2">
+    <row r="618" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A618" s="1"/>
       <c r="B618" s="1"/>
       <c r="C618" s="1"/>
@@ -20374,7 +20302,7 @@
       <c r="AB618" s="1"/>
       <c r="AC618" s="1"/>
     </row>
-    <row r="619" spans="1:29" ht="13.2">
+    <row r="619" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A619" s="1"/>
       <c r="B619" s="1"/>
       <c r="C619" s="1"/>
@@ -20405,7 +20333,7 @@
       <c r="AB619" s="1"/>
       <c r="AC619" s="1"/>
     </row>
-    <row r="620" spans="1:29" ht="13.2">
+    <row r="620" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A620" s="1"/>
       <c r="B620" s="1"/>
       <c r="C620" s="1"/>
@@ -20436,7 +20364,7 @@
       <c r="AB620" s="1"/>
       <c r="AC620" s="1"/>
     </row>
-    <row r="621" spans="1:29" ht="13.2">
+    <row r="621" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A621" s="1"/>
       <c r="B621" s="1"/>
       <c r="C621" s="1"/>
@@ -20467,7 +20395,7 @@
       <c r="AB621" s="1"/>
       <c r="AC621" s="1"/>
     </row>
-    <row r="622" spans="1:29" ht="13.2">
+    <row r="622" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A622" s="1"/>
       <c r="B622" s="1"/>
       <c r="C622" s="1"/>
@@ -20498,7 +20426,7 @@
       <c r="AB622" s="1"/>
       <c r="AC622" s="1"/>
     </row>
-    <row r="623" spans="1:29" ht="13.2">
+    <row r="623" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A623" s="1"/>
       <c r="B623" s="1"/>
       <c r="C623" s="1"/>
@@ -20529,7 +20457,7 @@
       <c r="AB623" s="1"/>
       <c r="AC623" s="1"/>
     </row>
-    <row r="624" spans="1:29" ht="13.2">
+    <row r="624" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A624" s="1"/>
       <c r="B624" s="1"/>
       <c r="C624" s="1"/>
@@ -20560,7 +20488,7 @@
       <c r="AB624" s="1"/>
       <c r="AC624" s="1"/>
     </row>
-    <row r="625" spans="1:29" ht="13.2">
+    <row r="625" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A625" s="1"/>
       <c r="B625" s="1"/>
       <c r="C625" s="1"/>
@@ -20591,7 +20519,7 @@
       <c r="AB625" s="1"/>
       <c r="AC625" s="1"/>
     </row>
-    <row r="626" spans="1:29" ht="13.2">
+    <row r="626" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A626" s="1"/>
       <c r="B626" s="1"/>
       <c r="C626" s="1"/>
@@ -20622,7 +20550,7 @@
       <c r="AB626" s="1"/>
       <c r="AC626" s="1"/>
     </row>
-    <row r="627" spans="1:29" ht="13.2">
+    <row r="627" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A627" s="1"/>
       <c r="B627" s="1"/>
       <c r="C627" s="1"/>
@@ -20653,7 +20581,7 @@
       <c r="AB627" s="1"/>
       <c r="AC627" s="1"/>
     </row>
-    <row r="628" spans="1:29" ht="13.2">
+    <row r="628" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A628" s="1"/>
       <c r="B628" s="1"/>
       <c r="C628" s="1"/>
@@ -20684,7 +20612,7 @@
       <c r="AB628" s="1"/>
       <c r="AC628" s="1"/>
     </row>
-    <row r="629" spans="1:29" ht="13.2">
+    <row r="629" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A629" s="1"/>
       <c r="B629" s="1"/>
       <c r="C629" s="1"/>
@@ -20715,7 +20643,7 @@
       <c r="AB629" s="1"/>
       <c r="AC629" s="1"/>
     </row>
-    <row r="630" spans="1:29" ht="13.2">
+    <row r="630" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A630" s="1"/>
       <c r="B630" s="1"/>
       <c r="C630" s="1"/>
@@ -20746,7 +20674,7 @@
       <c r="AB630" s="1"/>
       <c r="AC630" s="1"/>
     </row>
-    <row r="631" spans="1:29" ht="13.2">
+    <row r="631" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A631" s="1"/>
       <c r="B631" s="1"/>
       <c r="C631" s="1"/>
@@ -20777,7 +20705,7 @@
       <c r="AB631" s="1"/>
       <c r="AC631" s="1"/>
     </row>
-    <row r="632" spans="1:29" ht="13.2">
+    <row r="632" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A632" s="1"/>
       <c r="B632" s="1"/>
       <c r="C632" s="1"/>
@@ -20808,7 +20736,7 @@
       <c r="AB632" s="1"/>
       <c r="AC632" s="1"/>
     </row>
-    <row r="633" spans="1:29" ht="13.2">
+    <row r="633" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A633" s="1"/>
       <c r="B633" s="1"/>
       <c r="C633" s="1"/>
@@ -20839,7 +20767,7 @@
       <c r="AB633" s="1"/>
       <c r="AC633" s="1"/>
     </row>
-    <row r="634" spans="1:29" ht="13.2">
+    <row r="634" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A634" s="1"/>
       <c r="B634" s="1"/>
       <c r="C634" s="1"/>
@@ -20870,7 +20798,7 @@
       <c r="AB634" s="1"/>
       <c r="AC634" s="1"/>
     </row>
-    <row r="635" spans="1:29" ht="13.2">
+    <row r="635" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A635" s="1"/>
       <c r="B635" s="1"/>
       <c r="C635" s="1"/>
@@ -20901,7 +20829,7 @@
       <c r="AB635" s="1"/>
       <c r="AC635" s="1"/>
     </row>
-    <row r="636" spans="1:29" ht="13.2">
+    <row r="636" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A636" s="1"/>
       <c r="B636" s="1"/>
       <c r="C636" s="1"/>
@@ -20932,7 +20860,7 @@
       <c r="AB636" s="1"/>
       <c r="AC636" s="1"/>
     </row>
-    <row r="637" spans="1:29" ht="13.2">
+    <row r="637" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A637" s="1"/>
       <c r="B637" s="1"/>
       <c r="C637" s="1"/>
@@ -20963,7 +20891,7 @@
       <c r="AB637" s="1"/>
       <c r="AC637" s="1"/>
     </row>
-    <row r="638" spans="1:29" ht="13.2">
+    <row r="638" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A638" s="1"/>
       <c r="B638" s="1"/>
       <c r="C638" s="1"/>
@@ -20994,7 +20922,7 @@
       <c r="AB638" s="1"/>
       <c r="AC638" s="1"/>
     </row>
-    <row r="639" spans="1:29" ht="13.2">
+    <row r="639" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A639" s="1"/>
       <c r="B639" s="1"/>
       <c r="C639" s="1"/>
@@ -21025,7 +20953,7 @@
       <c r="AB639" s="1"/>
       <c r="AC639" s="1"/>
     </row>
-    <row r="640" spans="1:29" ht="13.2">
+    <row r="640" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A640" s="1"/>
       <c r="B640" s="1"/>
       <c r="C640" s="1"/>
@@ -21056,7 +20984,7 @@
       <c r="AB640" s="1"/>
       <c r="AC640" s="1"/>
     </row>
-    <row r="641" spans="1:29" ht="13.2">
+    <row r="641" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A641" s="1"/>
       <c r="B641" s="1"/>
       <c r="C641" s="1"/>
@@ -21087,7 +21015,7 @@
       <c r="AB641" s="1"/>
       <c r="AC641" s="1"/>
     </row>
-    <row r="642" spans="1:29" ht="13.2">
+    <row r="642" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A642" s="1"/>
       <c r="B642" s="1"/>
       <c r="C642" s="1"/>
@@ -21118,7 +21046,7 @@
       <c r="AB642" s="1"/>
       <c r="AC642" s="1"/>
     </row>
-    <row r="643" spans="1:29" ht="13.2">
+    <row r="643" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A643" s="1"/>
       <c r="B643" s="1"/>
       <c r="C643" s="1"/>
@@ -21149,7 +21077,7 @@
       <c r="AB643" s="1"/>
       <c r="AC643" s="1"/>
     </row>
-    <row r="644" spans="1:29" ht="13.2">
+    <row r="644" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A644" s="1"/>
       <c r="B644" s="1"/>
       <c r="C644" s="1"/>
@@ -21180,7 +21108,7 @@
       <c r="AB644" s="1"/>
       <c r="AC644" s="1"/>
     </row>
-    <row r="645" spans="1:29" ht="13.2">
+    <row r="645" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A645" s="1"/>
       <c r="B645" s="1"/>
       <c r="C645" s="1"/>
@@ -21211,7 +21139,7 @@
       <c r="AB645" s="1"/>
       <c r="AC645" s="1"/>
     </row>
-    <row r="646" spans="1:29" ht="13.2">
+    <row r="646" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A646" s="1"/>
       <c r="B646" s="1"/>
       <c r="C646" s="1"/>
@@ -21242,7 +21170,7 @@
       <c r="AB646" s="1"/>
       <c r="AC646" s="1"/>
     </row>
-    <row r="647" spans="1:29" ht="13.2">
+    <row r="647" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A647" s="1"/>
       <c r="B647" s="1"/>
       <c r="C647" s="1"/>
@@ -21273,7 +21201,7 @@
       <c r="AB647" s="1"/>
       <c r="AC647" s="1"/>
     </row>
-    <row r="648" spans="1:29" ht="13.2">
+    <row r="648" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A648" s="1"/>
       <c r="B648" s="1"/>
       <c r="C648" s="1"/>
@@ -21304,7 +21232,7 @@
       <c r="AB648" s="1"/>
       <c r="AC648" s="1"/>
     </row>
-    <row r="649" spans="1:29" ht="13.2">
+    <row r="649" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A649" s="1"/>
       <c r="B649" s="1"/>
       <c r="C649" s="1"/>
@@ -21335,7 +21263,7 @@
       <c r="AB649" s="1"/>
       <c r="AC649" s="1"/>
     </row>
-    <row r="650" spans="1:29" ht="13.2">
+    <row r="650" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A650" s="1"/>
       <c r="B650" s="1"/>
       <c r="C650" s="1"/>
@@ -21366,7 +21294,7 @@
       <c r="AB650" s="1"/>
       <c r="AC650" s="1"/>
     </row>
-    <row r="651" spans="1:29" ht="13.2">
+    <row r="651" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A651" s="1"/>
       <c r="B651" s="1"/>
       <c r="C651" s="1"/>
@@ -21397,7 +21325,7 @@
       <c r="AB651" s="1"/>
       <c r="AC651" s="1"/>
     </row>
-    <row r="652" spans="1:29" ht="13.2">
+    <row r="652" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A652" s="1"/>
       <c r="B652" s="1"/>
       <c r="C652" s="1"/>
@@ -21428,7 +21356,7 @@
       <c r="AB652" s="1"/>
       <c r="AC652" s="1"/>
     </row>
-    <row r="653" spans="1:29" ht="13.2">
+    <row r="653" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A653" s="1"/>
       <c r="B653" s="1"/>
       <c r="C653" s="1"/>
@@ -21459,7 +21387,7 @@
       <c r="AB653" s="1"/>
       <c r="AC653" s="1"/>
     </row>
-    <row r="654" spans="1:29" ht="13.2">
+    <row r="654" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A654" s="1"/>
       <c r="B654" s="1"/>
       <c r="C654" s="1"/>
@@ -21490,7 +21418,7 @@
       <c r="AB654" s="1"/>
       <c r="AC654" s="1"/>
     </row>
-    <row r="655" spans="1:29" ht="13.2">
+    <row r="655" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A655" s="1"/>
       <c r="B655" s="1"/>
       <c r="C655" s="1"/>
@@ -21521,7 +21449,7 @@
       <c r="AB655" s="1"/>
       <c r="AC655" s="1"/>
     </row>
-    <row r="656" spans="1:29" ht="13.2">
+    <row r="656" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A656" s="1"/>
       <c r="B656" s="1"/>
       <c r="C656" s="1"/>
@@ -21552,7 +21480,7 @@
       <c r="AB656" s="1"/>
       <c r="AC656" s="1"/>
     </row>
-    <row r="657" spans="1:29" ht="13.2">
+    <row r="657" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A657" s="1"/>
       <c r="B657" s="1"/>
       <c r="C657" s="1"/>
@@ -21583,7 +21511,7 @@
       <c r="AB657" s="1"/>
       <c r="AC657" s="1"/>
     </row>
-    <row r="658" spans="1:29" ht="13.2">
+    <row r="658" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A658" s="1"/>
       <c r="B658" s="1"/>
       <c r="C658" s="1"/>
@@ -21614,7 +21542,7 @@
       <c r="AB658" s="1"/>
       <c r="AC658" s="1"/>
     </row>
-    <row r="659" spans="1:29" ht="13.2">
+    <row r="659" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A659" s="1"/>
       <c r="B659" s="1"/>
       <c r="C659" s="1"/>
@@ -21645,7 +21573,7 @@
       <c r="AB659" s="1"/>
       <c r="AC659" s="1"/>
     </row>
-    <row r="660" spans="1:29" ht="13.2">
+    <row r="660" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A660" s="1"/>
       <c r="B660" s="1"/>
       <c r="C660" s="1"/>
@@ -21676,7 +21604,7 @@
       <c r="AB660" s="1"/>
       <c r="AC660" s="1"/>
     </row>
-    <row r="661" spans="1:29" ht="13.2">
+    <row r="661" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A661" s="1"/>
       <c r="B661" s="1"/>
       <c r="C661" s="1"/>
@@ -21707,7 +21635,7 @@
       <c r="AB661" s="1"/>
       <c r="AC661" s="1"/>
     </row>
-    <row r="662" spans="1:29" ht="13.2">
+    <row r="662" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A662" s="1"/>
       <c r="B662" s="1"/>
       <c r="C662" s="1"/>
@@ -21738,7 +21666,7 @@
       <c r="AB662" s="1"/>
       <c r="AC662" s="1"/>
     </row>
-    <row r="663" spans="1:29" ht="13.2">
+    <row r="663" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A663" s="1"/>
       <c r="B663" s="1"/>
       <c r="C663" s="1"/>
@@ -21769,7 +21697,7 @@
       <c r="AB663" s="1"/>
       <c r="AC663" s="1"/>
     </row>
-    <row r="664" spans="1:29" ht="13.2">
+    <row r="664" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A664" s="1"/>
       <c r="B664" s="1"/>
       <c r="C664" s="1"/>
@@ -21800,7 +21728,7 @@
       <c r="AB664" s="1"/>
       <c r="AC664" s="1"/>
     </row>
-    <row r="665" spans="1:29" ht="13.2">
+    <row r="665" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A665" s="1"/>
       <c r="B665" s="1"/>
       <c r="C665" s="1"/>
@@ -21831,7 +21759,7 @@
       <c r="AB665" s="1"/>
       <c r="AC665" s="1"/>
     </row>
-    <row r="666" spans="1:29" ht="13.2">
+    <row r="666" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A666" s="1"/>
       <c r="B666" s="1"/>
       <c r="C666" s="1"/>
@@ -21862,7 +21790,7 @@
       <c r="AB666" s="1"/>
       <c r="AC666" s="1"/>
     </row>
-    <row r="667" spans="1:29" ht="13.2">
+    <row r="667" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A667" s="1"/>
       <c r="B667" s="1"/>
       <c r="C667" s="1"/>
@@ -21893,7 +21821,7 @@
       <c r="AB667" s="1"/>
       <c r="AC667" s="1"/>
     </row>
-    <row r="668" spans="1:29" ht="13.2">
+    <row r="668" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A668" s="1"/>
       <c r="B668" s="1"/>
       <c r="C668" s="1"/>
@@ -21924,7 +21852,7 @@
       <c r="AB668" s="1"/>
       <c r="AC668" s="1"/>
     </row>
-    <row r="669" spans="1:29" ht="13.2">
+    <row r="669" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A669" s="1"/>
       <c r="B669" s="1"/>
       <c r="C669" s="1"/>
@@ -21955,7 +21883,7 @@
       <c r="AB669" s="1"/>
       <c r="AC669" s="1"/>
     </row>
-    <row r="670" spans="1:29" ht="13.2">
+    <row r="670" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A670" s="1"/>
       <c r="B670" s="1"/>
       <c r="C670" s="1"/>
@@ -21986,7 +21914,7 @@
       <c r="AB670" s="1"/>
       <c r="AC670" s="1"/>
     </row>
-    <row r="671" spans="1:29" ht="13.2">
+    <row r="671" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A671" s="1"/>
       <c r="B671" s="1"/>
       <c r="C671" s="1"/>
@@ -22017,7 +21945,7 @@
       <c r="AB671" s="1"/>
       <c r="AC671" s="1"/>
     </row>
-    <row r="672" spans="1:29" ht="13.2">
+    <row r="672" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A672" s="1"/>
       <c r="B672" s="1"/>
       <c r="C672" s="1"/>
@@ -22048,7 +21976,7 @@
       <c r="AB672" s="1"/>
       <c r="AC672" s="1"/>
     </row>
-    <row r="673" spans="1:29" ht="13.2">
+    <row r="673" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A673" s="1"/>
       <c r="B673" s="1"/>
       <c r="C673" s="1"/>
@@ -22079,7 +22007,7 @@
       <c r="AB673" s="1"/>
       <c r="AC673" s="1"/>
     </row>
-    <row r="674" spans="1:29" ht="13.2">
+    <row r="674" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A674" s="1"/>
       <c r="B674" s="1"/>
       <c r="C674" s="1"/>
@@ -22110,7 +22038,7 @@
       <c r="AB674" s="1"/>
       <c r="AC674" s="1"/>
     </row>
-    <row r="675" spans="1:29" ht="13.2">
+    <row r="675" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A675" s="1"/>
       <c r="B675" s="1"/>
       <c r="C675" s="1"/>
@@ -22141,7 +22069,7 @@
       <c r="AB675" s="1"/>
       <c r="AC675" s="1"/>
     </row>
-    <row r="676" spans="1:29" ht="13.2">
+    <row r="676" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A676" s="1"/>
       <c r="B676" s="1"/>
       <c r="C676" s="1"/>
@@ -22172,7 +22100,7 @@
       <c r="AB676" s="1"/>
       <c r="AC676" s="1"/>
     </row>
-    <row r="677" spans="1:29" ht="13.2">
+    <row r="677" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A677" s="1"/>
       <c r="B677" s="1"/>
       <c r="C677" s="1"/>
@@ -22203,7 +22131,7 @@
       <c r="AB677" s="1"/>
       <c r="AC677" s="1"/>
     </row>
-    <row r="678" spans="1:29" ht="13.2">
+    <row r="678" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A678" s="1"/>
       <c r="B678" s="1"/>
       <c r="C678" s="1"/>
@@ -22234,7 +22162,7 @@
       <c r="AB678" s="1"/>
       <c r="AC678" s="1"/>
     </row>
-    <row r="679" spans="1:29" ht="13.2">
+    <row r="679" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A679" s="1"/>
       <c r="B679" s="1"/>
       <c r="C679" s="1"/>
@@ -22265,7 +22193,7 @@
       <c r="AB679" s="1"/>
       <c r="AC679" s="1"/>
     </row>
-    <row r="680" spans="1:29" ht="13.2">
+    <row r="680" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A680" s="1"/>
       <c r="B680" s="1"/>
       <c r="C680" s="1"/>
@@ -22296,7 +22224,7 @@
       <c r="AB680" s="1"/>
       <c r="AC680" s="1"/>
     </row>
-    <row r="681" spans="1:29" ht="13.2">
+    <row r="681" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A681" s="1"/>
       <c r="B681" s="1"/>
       <c r="C681" s="1"/>
@@ -22327,7 +22255,7 @@
       <c r="AB681" s="1"/>
       <c r="AC681" s="1"/>
     </row>
-    <row r="682" spans="1:29" ht="13.2">
+    <row r="682" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A682" s="1"/>
       <c r="B682" s="1"/>
       <c r="C682" s="1"/>
@@ -22358,7 +22286,7 @@
       <c r="AB682" s="1"/>
       <c r="AC682" s="1"/>
     </row>
-    <row r="683" spans="1:29" ht="13.2">
+    <row r="683" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A683" s="1"/>
       <c r="B683" s="1"/>
       <c r="C683" s="1"/>
@@ -22389,7 +22317,7 @@
       <c r="AB683" s="1"/>
       <c r="AC683" s="1"/>
     </row>
-    <row r="684" spans="1:29" ht="13.2">
+    <row r="684" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A684" s="1"/>
       <c r="B684" s="1"/>
       <c r="C684" s="1"/>
@@ -22420,7 +22348,7 @@
       <c r="AB684" s="1"/>
       <c r="AC684" s="1"/>
     </row>
-    <row r="685" spans="1:29" ht="13.2">
+    <row r="685" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A685" s="1"/>
       <c r="B685" s="1"/>
       <c r="C685" s="1"/>
@@ -22451,7 +22379,7 @@
       <c r="AB685" s="1"/>
       <c r="AC685" s="1"/>
     </row>
-    <row r="686" spans="1:29" ht="13.2">
+    <row r="686" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A686" s="1"/>
       <c r="B686" s="1"/>
       <c r="C686" s="1"/>
@@ -22482,7 +22410,7 @@
       <c r="AB686" s="1"/>
       <c r="AC686" s="1"/>
     </row>
-    <row r="687" spans="1:29" ht="13.2">
+    <row r="687" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A687" s="1"/>
       <c r="B687" s="1"/>
       <c r="C687" s="1"/>
@@ -22513,7 +22441,7 @@
       <c r="AB687" s="1"/>
       <c r="AC687" s="1"/>
     </row>
-    <row r="688" spans="1:29" ht="13.2">
+    <row r="688" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A688" s="1"/>
       <c r="B688" s="1"/>
       <c r="C688" s="1"/>
@@ -22544,7 +22472,7 @@
       <c r="AB688" s="1"/>
       <c r="AC688" s="1"/>
     </row>
-    <row r="689" spans="1:29" ht="13.2">
+    <row r="689" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A689" s="1"/>
       <c r="B689" s="1"/>
       <c r="C689" s="1"/>
@@ -22575,7 +22503,7 @@
       <c r="AB689" s="1"/>
       <c r="AC689" s="1"/>
     </row>
-    <row r="690" spans="1:29" ht="13.2">
+    <row r="690" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A690" s="1"/>
       <c r="B690" s="1"/>
       <c r="C690" s="1"/>
@@ -22606,7 +22534,7 @@
       <c r="AB690" s="1"/>
       <c r="AC690" s="1"/>
     </row>
-    <row r="691" spans="1:29" ht="13.2">
+    <row r="691" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A691" s="1"/>
       <c r="B691" s="1"/>
       <c r="C691" s="1"/>
@@ -22637,7 +22565,7 @@
       <c r="AB691" s="1"/>
       <c r="AC691" s="1"/>
     </row>
-    <row r="692" spans="1:29" ht="13.2">
+    <row r="692" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A692" s="1"/>
       <c r="B692" s="1"/>
       <c r="C692" s="1"/>
@@ -22668,7 +22596,7 @@
       <c r="AB692" s="1"/>
       <c r="AC692" s="1"/>
     </row>
-    <row r="693" spans="1:29" ht="13.2">
+    <row r="693" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A693" s="1"/>
       <c r="B693" s="1"/>
       <c r="C693" s="1"/>
@@ -22699,7 +22627,7 @@
       <c r="AB693" s="1"/>
       <c r="AC693" s="1"/>
     </row>
-    <row r="694" spans="1:29" ht="13.2">
+    <row r="694" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A694" s="1"/>
       <c r="B694" s="1"/>
       <c r="C694" s="1"/>
@@ -22730,7 +22658,7 @@
       <c r="AB694" s="1"/>
       <c r="AC694" s="1"/>
     </row>
-    <row r="695" spans="1:29" ht="13.2">
+    <row r="695" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A695" s="1"/>
       <c r="B695" s="1"/>
       <c r="C695" s="1"/>
@@ -22761,7 +22689,7 @@
       <c r="AB695" s="1"/>
       <c r="AC695" s="1"/>
     </row>
-    <row r="696" spans="1:29" ht="13.2">
+    <row r="696" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A696" s="1"/>
       <c r="B696" s="1"/>
       <c r="C696" s="1"/>
@@ -22792,7 +22720,7 @@
       <c r="AB696" s="1"/>
       <c r="AC696" s="1"/>
     </row>
-    <row r="697" spans="1:29" ht="13.2">
+    <row r="697" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A697" s="1"/>
       <c r="B697" s="1"/>
       <c r="C697" s="1"/>
@@ -22823,7 +22751,7 @@
       <c r="AB697" s="1"/>
       <c r="AC697" s="1"/>
     </row>
-    <row r="698" spans="1:29" ht="13.2">
+    <row r="698" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A698" s="1"/>
       <c r="B698" s="1"/>
       <c r="C698" s="1"/>
@@ -22854,7 +22782,7 @@
       <c r="AB698" s="1"/>
       <c r="AC698" s="1"/>
     </row>
-    <row r="699" spans="1:29" ht="13.2">
+    <row r="699" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A699" s="1"/>
       <c r="B699" s="1"/>
       <c r="C699" s="1"/>
@@ -22885,7 +22813,7 @@
       <c r="AB699" s="1"/>
       <c r="AC699" s="1"/>
     </row>
-    <row r="700" spans="1:29" ht="13.2">
+    <row r="700" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A700" s="1"/>
       <c r="B700" s="1"/>
       <c r="C700" s="1"/>
@@ -22916,7 +22844,7 @@
       <c r="AB700" s="1"/>
       <c r="AC700" s="1"/>
     </row>
-    <row r="701" spans="1:29" ht="13.2">
+    <row r="701" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A701" s="1"/>
       <c r="B701" s="1"/>
       <c r="C701" s="1"/>
@@ -22947,7 +22875,7 @@
       <c r="AB701" s="1"/>
       <c r="AC701" s="1"/>
     </row>
-    <row r="702" spans="1:29" ht="13.2">
+    <row r="702" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A702" s="1"/>
       <c r="B702" s="1"/>
       <c r="C702" s="1"/>
@@ -22978,7 +22906,7 @@
       <c r="AB702" s="1"/>
       <c r="AC702" s="1"/>
     </row>
-    <row r="703" spans="1:29" ht="13.2">
+    <row r="703" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A703" s="1"/>
       <c r="B703" s="1"/>
       <c r="C703" s="1"/>
@@ -23009,7 +22937,7 @@
       <c r="AB703" s="1"/>
       <c r="AC703" s="1"/>
     </row>
-    <row r="704" spans="1:29" ht="13.2">
+    <row r="704" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A704" s="1"/>
       <c r="B704" s="1"/>
       <c r="C704" s="1"/>
@@ -23040,7 +22968,7 @@
       <c r="AB704" s="1"/>
       <c r="AC704" s="1"/>
     </row>
-    <row r="705" spans="1:29" ht="13.2">
+    <row r="705" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A705" s="1"/>
       <c r="B705" s="1"/>
       <c r="C705" s="1"/>
@@ -23071,7 +22999,7 @@
       <c r="AB705" s="1"/>
       <c r="AC705" s="1"/>
     </row>
-    <row r="706" spans="1:29" ht="13.2">
+    <row r="706" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A706" s="1"/>
       <c r="B706" s="1"/>
       <c r="C706" s="1"/>
@@ -23102,7 +23030,7 @@
       <c r="AB706" s="1"/>
       <c r="AC706" s="1"/>
     </row>
-    <row r="707" spans="1:29" ht="13.2">
+    <row r="707" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A707" s="1"/>
       <c r="B707" s="1"/>
       <c r="C707" s="1"/>
@@ -23133,7 +23061,7 @@
       <c r="AB707" s="1"/>
       <c r="AC707" s="1"/>
     </row>
-    <row r="708" spans="1:29" ht="13.2">
+    <row r="708" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A708" s="1"/>
       <c r="B708" s="1"/>
       <c r="C708" s="1"/>
@@ -23164,7 +23092,7 @@
       <c r="AB708" s="1"/>
       <c r="AC708" s="1"/>
     </row>
-    <row r="709" spans="1:29" ht="13.2">
+    <row r="709" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A709" s="1"/>
       <c r="B709" s="1"/>
       <c r="C709" s="1"/>
@@ -23195,7 +23123,7 @@
       <c r="AB709" s="1"/>
       <c r="AC709" s="1"/>
     </row>
-    <row r="710" spans="1:29" ht="13.2">
+    <row r="710" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A710" s="1"/>
       <c r="B710" s="1"/>
       <c r="C710" s="1"/>
@@ -23226,7 +23154,7 @@
       <c r="AB710" s="1"/>
       <c r="AC710" s="1"/>
     </row>
-    <row r="711" spans="1:29" ht="13.2">
+    <row r="711" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A711" s="1"/>
       <c r="B711" s="1"/>
       <c r="C711" s="1"/>
@@ -23257,7 +23185,7 @@
       <c r="AB711" s="1"/>
       <c r="AC711" s="1"/>
     </row>
-    <row r="712" spans="1:29" ht="13.2">
+    <row r="712" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A712" s="1"/>
       <c r="B712" s="1"/>
       <c r="C712" s="1"/>
@@ -23288,7 +23216,7 @@
       <c r="AB712" s="1"/>
       <c r="AC712" s="1"/>
     </row>
-    <row r="713" spans="1:29" ht="13.2">
+    <row r="713" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A713" s="1"/>
       <c r="B713" s="1"/>
       <c r="C713" s="1"/>
@@ -23319,7 +23247,7 @@
       <c r="AB713" s="1"/>
       <c r="AC713" s="1"/>
     </row>
-    <row r="714" spans="1:29" ht="13.2">
+    <row r="714" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A714" s="1"/>
       <c r="B714" s="1"/>
       <c r="C714" s="1"/>
@@ -23350,7 +23278,7 @@
       <c r="AB714" s="1"/>
       <c r="AC714" s="1"/>
     </row>
-    <row r="715" spans="1:29" ht="13.2">
+    <row r="715" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A715" s="1"/>
       <c r="B715" s="1"/>
       <c r="C715" s="1"/>
@@ -23381,7 +23309,7 @@
       <c r="AB715" s="1"/>
       <c r="AC715" s="1"/>
     </row>
-    <row r="716" spans="1:29" ht="13.2">
+    <row r="716" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A716" s="1"/>
       <c r="B716" s="1"/>
       <c r="C716" s="1"/>
@@ -23412,7 +23340,7 @@
       <c r="AB716" s="1"/>
       <c r="AC716" s="1"/>
     </row>
-    <row r="717" spans="1:29" ht="13.2">
+    <row r="717" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A717" s="1"/>
       <c r="B717" s="1"/>
       <c r="C717" s="1"/>
@@ -23443,7 +23371,7 @@
       <c r="AB717" s="1"/>
       <c r="AC717" s="1"/>
     </row>
-    <row r="718" spans="1:29" ht="13.2">
+    <row r="718" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A718" s="1"/>
       <c r="B718" s="1"/>
       <c r="C718" s="1"/>
@@ -23474,7 +23402,7 @@
       <c r="AB718" s="1"/>
       <c r="AC718" s="1"/>
     </row>
-    <row r="719" spans="1:29" ht="13.2">
+    <row r="719" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A719" s="1"/>
       <c r="B719" s="1"/>
       <c r="C719" s="1"/>
@@ -23505,7 +23433,7 @@
       <c r="AB719" s="1"/>
       <c r="AC719" s="1"/>
     </row>
-    <row r="720" spans="1:29" ht="13.2">
+    <row r="720" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A720" s="1"/>
       <c r="B720" s="1"/>
       <c r="C720" s="1"/>
@@ -23536,7 +23464,7 @@
       <c r="AB720" s="1"/>
       <c r="AC720" s="1"/>
     </row>
-    <row r="721" spans="1:29" ht="13.2">
+    <row r="721" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A721" s="1"/>
       <c r="B721" s="1"/>
       <c r="C721" s="1"/>
@@ -23567,7 +23495,7 @@
       <c r="AB721" s="1"/>
       <c r="AC721" s="1"/>
     </row>
-    <row r="722" spans="1:29" ht="13.2">
+    <row r="722" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A722" s="1"/>
       <c r="B722" s="1"/>
       <c r="C722" s="1"/>
@@ -23598,7 +23526,7 @@
       <c r="AB722" s="1"/>
       <c r="AC722" s="1"/>
     </row>
-    <row r="723" spans="1:29" ht="13.2">
+    <row r="723" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A723" s="1"/>
       <c r="B723" s="1"/>
       <c r="C723" s="1"/>
@@ -23629,7 +23557,7 @@
       <c r="AB723" s="1"/>
       <c r="AC723" s="1"/>
     </row>
-    <row r="724" spans="1:29" ht="13.2">
+    <row r="724" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A724" s="1"/>
       <c r="B724" s="1"/>
       <c r="C724" s="1"/>
@@ -23660,7 +23588,7 @@
       <c r="AB724" s="1"/>
       <c r="AC724" s="1"/>
     </row>
-    <row r="725" spans="1:29" ht="13.2">
+    <row r="725" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A725" s="1"/>
       <c r="B725" s="1"/>
       <c r="C725" s="1"/>
@@ -23691,7 +23619,7 @@
       <c r="AB725" s="1"/>
       <c r="AC725" s="1"/>
     </row>
-    <row r="726" spans="1:29" ht="13.2">
+    <row r="726" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A726" s="1"/>
       <c r="B726" s="1"/>
       <c r="C726" s="1"/>
@@ -23722,7 +23650,7 @@
       <c r="AB726" s="1"/>
       <c r="AC726" s="1"/>
     </row>
-    <row r="727" spans="1:29" ht="13.2">
+    <row r="727" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A727" s="1"/>
       <c r="B727" s="1"/>
       <c r="C727" s="1"/>
@@ -23753,7 +23681,7 @@
       <c r="AB727" s="1"/>
       <c r="AC727" s="1"/>
     </row>
-    <row r="728" spans="1:29" ht="13.2">
+    <row r="728" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A728" s="1"/>
       <c r="B728" s="1"/>
       <c r="C728" s="1"/>
@@ -23784,7 +23712,7 @@
       <c r="AB728" s="1"/>
       <c r="AC728" s="1"/>
     </row>
-    <row r="729" spans="1:29" ht="13.2">
+    <row r="729" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A729" s="1"/>
       <c r="B729" s="1"/>
       <c r="C729" s="1"/>
@@ -23815,7 +23743,7 @@
       <c r="AB729" s="1"/>
       <c r="AC729" s="1"/>
     </row>
-    <row r="730" spans="1:29" ht="13.2">
+    <row r="730" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A730" s="1"/>
       <c r="B730" s="1"/>
       <c r="C730" s="1"/>
@@ -23846,7 +23774,7 @@
       <c r="AB730" s="1"/>
       <c r="AC730" s="1"/>
     </row>
-    <row r="731" spans="1:29" ht="13.2">
+    <row r="731" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A731" s="1"/>
       <c r="B731" s="1"/>
       <c r="C731" s="1"/>
@@ -23877,7 +23805,7 @@
       <c r="AB731" s="1"/>
       <c r="AC731" s="1"/>
     </row>
-    <row r="732" spans="1:29" ht="13.2">
+    <row r="732" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A732" s="1"/>
       <c r="B732" s="1"/>
       <c r="C732" s="1"/>
@@ -23908,7 +23836,7 @@
       <c r="AB732" s="1"/>
       <c r="AC732" s="1"/>
     </row>
-    <row r="733" spans="1:29" ht="13.2">
+    <row r="733" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A733" s="1"/>
       <c r="B733" s="1"/>
       <c r="C733" s="1"/>
@@ -23939,7 +23867,7 @@
       <c r="AB733" s="1"/>
       <c r="AC733" s="1"/>
     </row>
-    <row r="734" spans="1:29" ht="13.2">
+    <row r="734" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A734" s="1"/>
       <c r="B734" s="1"/>
       <c r="C734" s="1"/>
@@ -23970,7 +23898,7 @@
       <c r="AB734" s="1"/>
       <c r="AC734" s="1"/>
     </row>
-    <row r="735" spans="1:29" ht="13.2">
+    <row r="735" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A735" s="1"/>
       <c r="B735" s="1"/>
       <c r="C735" s="1"/>
@@ -24001,7 +23929,7 @@
       <c r="AB735" s="1"/>
       <c r="AC735" s="1"/>
     </row>
-    <row r="736" spans="1:29" ht="13.2">
+    <row r="736" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A736" s="1"/>
       <c r="B736" s="1"/>
       <c r="C736" s="1"/>
@@ -24032,7 +23960,7 @@
       <c r="AB736" s="1"/>
       <c r="AC736" s="1"/>
     </row>
-    <row r="737" spans="1:29" ht="13.2">
+    <row r="737" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A737" s="1"/>
       <c r="B737" s="1"/>
       <c r="C737" s="1"/>
@@ -24063,7 +23991,7 @@
       <c r="AB737" s="1"/>
       <c r="AC737" s="1"/>
     </row>
-    <row r="738" spans="1:29" ht="13.2">
+    <row r="738" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A738" s="1"/>
       <c r="B738" s="1"/>
       <c r="C738" s="1"/>
@@ -24094,7 +24022,7 @@
       <c r="AB738" s="1"/>
       <c r="AC738" s="1"/>
     </row>
-    <row r="739" spans="1:29" ht="13.2">
+    <row r="739" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A739" s="1"/>
       <c r="B739" s="1"/>
       <c r="C739" s="1"/>
@@ -24125,7 +24053,7 @@
       <c r="AB739" s="1"/>
       <c r="AC739" s="1"/>
     </row>
-    <row r="740" spans="1:29" ht="13.2">
+    <row r="740" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A740" s="1"/>
       <c r="B740" s="1"/>
       <c r="C740" s="1"/>
@@ -24156,7 +24084,7 @@
       <c r="AB740" s="1"/>
       <c r="AC740" s="1"/>
     </row>
-    <row r="741" spans="1:29" ht="13.2">
+    <row r="741" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A741" s="1"/>
       <c r="B741" s="1"/>
       <c r="C741" s="1"/>
@@ -24187,7 +24115,7 @@
       <c r="AB741" s="1"/>
       <c r="AC741" s="1"/>
     </row>
-    <row r="742" spans="1:29" ht="13.2">
+    <row r="742" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A742" s="1"/>
       <c r="B742" s="1"/>
       <c r="C742" s="1"/>
@@ -24218,7 +24146,7 @@
       <c r="AB742" s="1"/>
       <c r="AC742" s="1"/>
     </row>
-    <row r="743" spans="1:29" ht="13.2">
+    <row r="743" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A743" s="1"/>
       <c r="B743" s="1"/>
       <c r="C743" s="1"/>
@@ -24249,7 +24177,7 @@
       <c r="AB743" s="1"/>
       <c r="AC743" s="1"/>
     </row>
-    <row r="744" spans="1:29" ht="13.2">
+    <row r="744" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A744" s="1"/>
       <c r="B744" s="1"/>
       <c r="C744" s="1"/>
@@ -24280,7 +24208,7 @@
       <c r="AB744" s="1"/>
       <c r="AC744" s="1"/>
     </row>
-    <row r="745" spans="1:29" ht="13.2">
+    <row r="745" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A745" s="1"/>
       <c r="B745" s="1"/>
       <c r="C745" s="1"/>
@@ -24311,7 +24239,7 @@
       <c r="AB745" s="1"/>
       <c r="AC745" s="1"/>
     </row>
-    <row r="746" spans="1:29" ht="13.2">
+    <row r="746" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A746" s="1"/>
       <c r="B746" s="1"/>
       <c r="C746" s="1"/>
@@ -24342,7 +24270,7 @@
       <c r="AB746" s="1"/>
       <c r="AC746" s="1"/>
     </row>
-    <row r="747" spans="1:29" ht="13.2">
+    <row r="747" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A747" s="1"/>
       <c r="B747" s="1"/>
       <c r="C747" s="1"/>
@@ -24373,7 +24301,7 @@
       <c r="AB747" s="1"/>
       <c r="AC747" s="1"/>
     </row>
-    <row r="748" spans="1:29" ht="13.2">
+    <row r="748" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A748" s="1"/>
       <c r="B748" s="1"/>
       <c r="C748" s="1"/>
@@ -24404,7 +24332,7 @@
       <c r="AB748" s="1"/>
       <c r="AC748" s="1"/>
     </row>
-    <row r="749" spans="1:29" ht="13.2">
+    <row r="749" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A749" s="1"/>
       <c r="B749" s="1"/>
       <c r="C749" s="1"/>
@@ -24435,7 +24363,7 @@
       <c r="AB749" s="1"/>
       <c r="AC749" s="1"/>
     </row>
-    <row r="750" spans="1:29" ht="13.2">
+    <row r="750" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A750" s="1"/>
       <c r="B750" s="1"/>
       <c r="C750" s="1"/>
@@ -24466,7 +24394,7 @@
       <c r="AB750" s="1"/>
       <c r="AC750" s="1"/>
     </row>
-    <row r="751" spans="1:29" ht="13.2">
+    <row r="751" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A751" s="1"/>
       <c r="B751" s="1"/>
       <c r="C751" s="1"/>
@@ -24497,7 +24425,7 @@
       <c r="AB751" s="1"/>
       <c r="AC751" s="1"/>
     </row>
-    <row r="752" spans="1:29" ht="13.2">
+    <row r="752" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A752" s="1"/>
       <c r="B752" s="1"/>
       <c r="C752" s="1"/>
@@ -24528,7 +24456,7 @@
       <c r="AB752" s="1"/>
       <c r="AC752" s="1"/>
     </row>
-    <row r="753" spans="1:29" ht="13.2">
+    <row r="753" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A753" s="1"/>
       <c r="B753" s="1"/>
       <c r="C753" s="1"/>
@@ -24559,7 +24487,7 @@
       <c r="AB753" s="1"/>
       <c r="AC753" s="1"/>
     </row>
-    <row r="754" spans="1:29" ht="13.2">
+    <row r="754" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A754" s="1"/>
       <c r="B754" s="1"/>
       <c r="C754" s="1"/>
@@ -24590,7 +24518,7 @@
       <c r="AB754" s="1"/>
       <c r="AC754" s="1"/>
     </row>
-    <row r="755" spans="1:29" ht="13.2">
+    <row r="755" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A755" s="1"/>
       <c r="B755" s="1"/>
       <c r="C755" s="1"/>
@@ -24621,7 +24549,7 @@
       <c r="AB755" s="1"/>
       <c r="AC755" s="1"/>
     </row>
-    <row r="756" spans="1:29" ht="13.2">
+    <row r="756" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A756" s="1"/>
       <c r="B756" s="1"/>
       <c r="C756" s="1"/>
@@ -24652,7 +24580,7 @@
       <c r="AB756" s="1"/>
       <c r="AC756" s="1"/>
     </row>
-    <row r="757" spans="1:29" ht="13.2">
+    <row r="757" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A757" s="1"/>
       <c r="B757" s="1"/>
       <c r="C757" s="1"/>
@@ -24683,7 +24611,7 @@
       <c r="AB757" s="1"/>
       <c r="AC757" s="1"/>
     </row>
-    <row r="758" spans="1:29" ht="13.2">
+    <row r="758" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A758" s="1"/>
       <c r="B758" s="1"/>
       <c r="C758" s="1"/>
@@ -24714,7 +24642,7 @@
       <c r="AB758" s="1"/>
       <c r="AC758" s="1"/>
     </row>
-    <row r="759" spans="1:29" ht="13.2">
+    <row r="759" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A759" s="1"/>
       <c r="B759" s="1"/>
       <c r="C759" s="1"/>
@@ -24745,7 +24673,7 @@
       <c r="AB759" s="1"/>
       <c r="AC759" s="1"/>
     </row>
-    <row r="760" spans="1:29" ht="13.2">
+    <row r="760" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A760" s="1"/>
       <c r="B760" s="1"/>
       <c r="C760" s="1"/>
@@ -24776,7 +24704,7 @@
       <c r="AB760" s="1"/>
       <c r="AC760" s="1"/>
     </row>
-    <row r="761" spans="1:29" ht="13.2">
+    <row r="761" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A761" s="1"/>
       <c r="B761" s="1"/>
       <c r="C761" s="1"/>
@@ -24807,7 +24735,7 @@
       <c r="AB761" s="1"/>
       <c r="AC761" s="1"/>
     </row>
-    <row r="762" spans="1:29" ht="13.2">
+    <row r="762" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A762" s="1"/>
       <c r="B762" s="1"/>
       <c r="C762" s="1"/>
@@ -24838,7 +24766,7 @@
       <c r="AB762" s="1"/>
       <c r="AC762" s="1"/>
     </row>
-    <row r="763" spans="1:29" ht="13.2">
+    <row r="763" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A763" s="1"/>
       <c r="B763" s="1"/>
       <c r="C763" s="1"/>
@@ -24869,7 +24797,7 @@
       <c r="AB763" s="1"/>
       <c r="AC763" s="1"/>
     </row>
-    <row r="764" spans="1:29" ht="13.2">
+    <row r="764" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A764" s="1"/>
       <c r="B764" s="1"/>
       <c r="C764" s="1"/>
@@ -24900,7 +24828,7 @@
       <c r="AB764" s="1"/>
       <c r="AC764" s="1"/>
     </row>
-    <row r="765" spans="1:29" ht="13.2">
+    <row r="765" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A765" s="1"/>
       <c r="B765" s="1"/>
       <c r="C765" s="1"/>
@@ -24931,7 +24859,7 @@
       <c r="AB765" s="1"/>
       <c r="AC765" s="1"/>
     </row>
-    <row r="766" spans="1:29" ht="13.2">
+    <row r="766" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A766" s="1"/>
       <c r="B766" s="1"/>
       <c r="C766" s="1"/>
@@ -24962,7 +24890,7 @@
       <c r="AB766" s="1"/>
       <c r="AC766" s="1"/>
     </row>
-    <row r="767" spans="1:29" ht="13.2">
+    <row r="767" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A767" s="1"/>
       <c r="B767" s="1"/>
       <c r="C767" s="1"/>
@@ -24993,7 +24921,7 @@
       <c r="AB767" s="1"/>
       <c r="AC767" s="1"/>
     </row>
-    <row r="768" spans="1:29" ht="13.2">
+    <row r="768" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A768" s="1"/>
       <c r="B768" s="1"/>
       <c r="C768" s="1"/>
@@ -25024,7 +24952,7 @@
       <c r="AB768" s="1"/>
       <c r="AC768" s="1"/>
     </row>
-    <row r="769" spans="1:29" ht="13.2">
+    <row r="769" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A769" s="1"/>
       <c r="B769" s="1"/>
       <c r="C769" s="1"/>
@@ -25055,7 +24983,7 @@
       <c r="AB769" s="1"/>
       <c r="AC769" s="1"/>
     </row>
-    <row r="770" spans="1:29" ht="13.2">
+    <row r="770" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A770" s="1"/>
       <c r="B770" s="1"/>
       <c r="C770" s="1"/>
@@ -25086,7 +25014,7 @@
       <c r="AB770" s="1"/>
       <c r="AC770" s="1"/>
     </row>
-    <row r="771" spans="1:29" ht="13.2">
+    <row r="771" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A771" s="1"/>
       <c r="B771" s="1"/>
       <c r="C771" s="1"/>
@@ -25117,7 +25045,7 @@
       <c r="AB771" s="1"/>
       <c r="AC771" s="1"/>
     </row>
-    <row r="772" spans="1:29" ht="13.2">
+    <row r="772" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A772" s="1"/>
       <c r="B772" s="1"/>
       <c r="C772" s="1"/>
@@ -25148,7 +25076,7 @@
       <c r="AB772" s="1"/>
       <c r="AC772" s="1"/>
     </row>
-    <row r="773" spans="1:29" ht="13.2">
+    <row r="773" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A773" s="1"/>
       <c r="B773" s="1"/>
       <c r="C773" s="1"/>
@@ -25179,7 +25107,7 @@
       <c r="AB773" s="1"/>
       <c r="AC773" s="1"/>
     </row>
-    <row r="774" spans="1:29" ht="13.2">
+    <row r="774" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A774" s="1"/>
       <c r="B774" s="1"/>
       <c r="C774" s="1"/>
@@ -25210,7 +25138,7 @@
       <c r="AB774" s="1"/>
       <c r="AC774" s="1"/>
     </row>
-    <row r="775" spans="1:29" ht="13.2">
+    <row r="775" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A775" s="1"/>
       <c r="B775" s="1"/>
       <c r="C775" s="1"/>
@@ -25241,7 +25169,7 @@
       <c r="AB775" s="1"/>
       <c r="AC775" s="1"/>
     </row>
-    <row r="776" spans="1:29" ht="13.2">
+    <row r="776" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A776" s="1"/>
       <c r="B776" s="1"/>
       <c r="C776" s="1"/>
@@ -25272,7 +25200,7 @@
       <c r="AB776" s="1"/>
       <c r="AC776" s="1"/>
     </row>
-    <row r="777" spans="1:29" ht="13.2">
+    <row r="777" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A777" s="1"/>
       <c r="B777" s="1"/>
       <c r="C777" s="1"/>
@@ -25303,7 +25231,7 @@
       <c r="AB777" s="1"/>
       <c r="AC777" s="1"/>
     </row>
-    <row r="778" spans="1:29" ht="13.2">
+    <row r="778" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A778" s="1"/>
       <c r="B778" s="1"/>
       <c r="C778" s="1"/>
@@ -25334,7 +25262,7 @@
       <c r="AB778" s="1"/>
       <c r="AC778" s="1"/>
     </row>
-    <row r="779" spans="1:29" ht="13.2">
+    <row r="779" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A779" s="1"/>
       <c r="B779" s="1"/>
       <c r="C779" s="1"/>
@@ -25365,7 +25293,7 @@
       <c r="AB779" s="1"/>
       <c r="AC779" s="1"/>
     </row>
-    <row r="780" spans="1:29" ht="13.2">
+    <row r="780" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A780" s="1"/>
       <c r="B780" s="1"/>
       <c r="C780" s="1"/>
@@ -25396,7 +25324,7 @@
       <c r="AB780" s="1"/>
       <c r="AC780" s="1"/>
     </row>
-    <row r="781" spans="1:29" ht="13.2">
+    <row r="781" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A781" s="1"/>
       <c r="B781" s="1"/>
       <c r="C781" s="1"/>
@@ -25427,7 +25355,7 @@
       <c r="AB781" s="1"/>
       <c r="AC781" s="1"/>
     </row>
-    <row r="782" spans="1:29" ht="13.2">
+    <row r="782" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A782" s="1"/>
       <c r="B782" s="1"/>
       <c r="C782" s="1"/>
@@ -25458,7 +25386,7 @@
       <c r="AB782" s="1"/>
       <c r="AC782" s="1"/>
     </row>
-    <row r="783" spans="1:29" ht="13.2">
+    <row r="783" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A783" s="1"/>
       <c r="B783" s="1"/>
       <c r="C783" s="1"/>
@@ -25489,7 +25417,7 @@
       <c r="AB783" s="1"/>
       <c r="AC783" s="1"/>
     </row>
-    <row r="784" spans="1:29" ht="13.2">
+    <row r="784" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A784" s="1"/>
       <c r="B784" s="1"/>
       <c r="C784" s="1"/>
@@ -25520,7 +25448,7 @@
       <c r="AB784" s="1"/>
       <c r="AC784" s="1"/>
     </row>
-    <row r="785" spans="1:29" ht="13.2">
+    <row r="785" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A785" s="1"/>
       <c r="B785" s="1"/>
       <c r="C785" s="1"/>
@@ -25551,7 +25479,7 @@
       <c r="AB785" s="1"/>
       <c r="AC785" s="1"/>
     </row>
-    <row r="786" spans="1:29" ht="13.2">
+    <row r="786" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A786" s="1"/>
       <c r="B786" s="1"/>
       <c r="C786" s="1"/>
@@ -25582,7 +25510,7 @@
       <c r="AB786" s="1"/>
       <c r="AC786" s="1"/>
     </row>
-    <row r="787" spans="1:29" ht="13.2">
+    <row r="787" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A787" s="1"/>
       <c r="B787" s="1"/>
       <c r="C787" s="1"/>
@@ -25613,7 +25541,7 @@
       <c r="AB787" s="1"/>
       <c r="AC787" s="1"/>
     </row>
-    <row r="788" spans="1:29" ht="13.2">
+    <row r="788" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A788" s="1"/>
       <c r="B788" s="1"/>
       <c r="C788" s="1"/>
@@ -25644,7 +25572,7 @@
       <c r="AB788" s="1"/>
       <c r="AC788" s="1"/>
     </row>
-    <row r="789" spans="1:29" ht="13.2">
+    <row r="789" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A789" s="1"/>
       <c r="B789" s="1"/>
       <c r="C789" s="1"/>
@@ -25675,7 +25603,7 @@
       <c r="AB789" s="1"/>
       <c r="AC789" s="1"/>
     </row>
-    <row r="790" spans="1:29" ht="13.2">
+    <row r="790" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A790" s="1"/>
       <c r="B790" s="1"/>
       <c r="C790" s="1"/>
@@ -25706,7 +25634,7 @@
       <c r="AB790" s="1"/>
       <c r="AC790" s="1"/>
     </row>
-    <row r="791" spans="1:29" ht="13.2">
+    <row r="791" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A791" s="1"/>
       <c r="B791" s="1"/>
       <c r="C791" s="1"/>
@@ -25737,7 +25665,7 @@
       <c r="AB791" s="1"/>
       <c r="AC791" s="1"/>
     </row>
-    <row r="792" spans="1:29" ht="13.2">
+    <row r="792" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A792" s="1"/>
       <c r="B792" s="1"/>
       <c r="C792" s="1"/>
@@ -25768,7 +25696,7 @@
       <c r="AB792" s="1"/>
       <c r="AC792" s="1"/>
     </row>
-    <row r="793" spans="1:29" ht="13.2">
+    <row r="793" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A793" s="1"/>
       <c r="B793" s="1"/>
       <c r="C793" s="1"/>
@@ -25799,7 +25727,7 @@
       <c r="AB793" s="1"/>
       <c r="AC793" s="1"/>
     </row>
-    <row r="794" spans="1:29" ht="13.2">
+    <row r="794" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A794" s="1"/>
       <c r="B794" s="1"/>
       <c r="C794" s="1"/>
@@ -25830,7 +25758,7 @@
       <c r="AB794" s="1"/>
       <c r="AC794" s="1"/>
     </row>
-    <row r="795" spans="1:29" ht="13.2">
+    <row r="795" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A795" s="1"/>
       <c r="B795" s="1"/>
       <c r="C795" s="1"/>
@@ -25861,7 +25789,7 @@
       <c r="AB795" s="1"/>
       <c r="AC795" s="1"/>
     </row>
-    <row r="796" spans="1:29" ht="13.2">
+    <row r="796" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A796" s="1"/>
       <c r="B796" s="1"/>
       <c r="C796" s="1"/>
@@ -25892,7 +25820,7 @@
       <c r="AB796" s="1"/>
       <c r="AC796" s="1"/>
     </row>
-    <row r="797" spans="1:29" ht="13.2">
+    <row r="797" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A797" s="1"/>
       <c r="B797" s="1"/>
       <c r="C797" s="1"/>
@@ -25923,7 +25851,7 @@
       <c r="AB797" s="1"/>
       <c r="AC797" s="1"/>
     </row>
-    <row r="798" spans="1:29" ht="13.2">
+    <row r="798" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A798" s="1"/>
       <c r="B798" s="1"/>
       <c r="C798" s="1"/>
@@ -25954,7 +25882,7 @@
       <c r="AB798" s="1"/>
       <c r="AC798" s="1"/>
     </row>
-    <row r="799" spans="1:29" ht="13.2">
+    <row r="799" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A799" s="1"/>
       <c r="B799" s="1"/>
       <c r="C799" s="1"/>
@@ -25985,7 +25913,7 @@
       <c r="AB799" s="1"/>
       <c r="AC799" s="1"/>
     </row>
-    <row r="800" spans="1:29" ht="13.2">
+    <row r="800" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A800" s="1"/>
       <c r="B800" s="1"/>
       <c r="C800" s="1"/>
@@ -26016,7 +25944,7 @@
       <c r="AB800" s="1"/>
       <c r="AC800" s="1"/>
     </row>
-    <row r="801" spans="1:29" ht="13.2">
+    <row r="801" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A801" s="1"/>
       <c r="B801" s="1"/>
       <c r="C801" s="1"/>
@@ -26047,7 +25975,7 @@
       <c r="AB801" s="1"/>
       <c r="AC801" s="1"/>
     </row>
-    <row r="802" spans="1:29" ht="13.2">
+    <row r="802" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A802" s="1"/>
       <c r="B802" s="1"/>
       <c r="C802" s="1"/>
@@ -26078,7 +26006,7 @@
       <c r="AB802" s="1"/>
       <c r="AC802" s="1"/>
     </row>
-    <row r="803" spans="1:29" ht="13.2">
+    <row r="803" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A803" s="1"/>
       <c r="B803" s="1"/>
       <c r="C803" s="1"/>
@@ -26109,7 +26037,7 @@
       <c r="AB803" s="1"/>
       <c r="AC803" s="1"/>
     </row>
-    <row r="804" spans="1:29" ht="13.2">
+    <row r="804" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A804" s="1"/>
       <c r="B804" s="1"/>
       <c r="C804" s="1"/>
@@ -26140,7 +26068,7 @@
       <c r="AB804" s="1"/>
       <c r="AC804" s="1"/>
     </row>
-    <row r="805" spans="1:29" ht="13.2">
+    <row r="805" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A805" s="1"/>
       <c r="B805" s="1"/>
       <c r="C805" s="1"/>
@@ -26171,7 +26099,7 @@
       <c r="AB805" s="1"/>
       <c r="AC805" s="1"/>
     </row>
-    <row r="806" spans="1:29" ht="13.2">
+    <row r="806" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A806" s="1"/>
       <c r="B806" s="1"/>
       <c r="C806" s="1"/>
@@ -26202,7 +26130,7 @@
       <c r="AB806" s="1"/>
       <c r="AC806" s="1"/>
     </row>
-    <row r="807" spans="1:29" ht="13.2">
+    <row r="807" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A807" s="1"/>
       <c r="B807" s="1"/>
       <c r="C807" s="1"/>
@@ -26233,7 +26161,7 @@
       <c r="AB807" s="1"/>
       <c r="AC807" s="1"/>
     </row>
-    <row r="808" spans="1:29" ht="13.2">
+    <row r="808" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A808" s="1"/>
       <c r="B808" s="1"/>
       <c r="C808" s="1"/>
@@ -26264,7 +26192,7 @@
       <c r="AB808" s="1"/>
       <c r="AC808" s="1"/>
     </row>
-    <row r="809" spans="1:29" ht="13.2">
+    <row r="809" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A809" s="1"/>
       <c r="B809" s="1"/>
       <c r="C809" s="1"/>
@@ -26295,7 +26223,7 @@
       <c r="AB809" s="1"/>
       <c r="AC809" s="1"/>
     </row>
-    <row r="810" spans="1:29" ht="13.2">
+    <row r="810" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A810" s="1"/>
       <c r="B810" s="1"/>
       <c r="C810" s="1"/>
@@ -26326,7 +26254,7 @@
       <c r="AB810" s="1"/>
       <c r="AC810" s="1"/>
     </row>
-    <row r="811" spans="1:29" ht="13.2">
+    <row r="811" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A811" s="1"/>
       <c r="B811" s="1"/>
       <c r="C811" s="1"/>
@@ -26357,7 +26285,7 @@
       <c r="AB811" s="1"/>
       <c r="AC811" s="1"/>
     </row>
-    <row r="812" spans="1:29" ht="13.2">
+    <row r="812" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A812" s="1"/>
       <c r="B812" s="1"/>
       <c r="C812" s="1"/>
@@ -26388,7 +26316,7 @@
       <c r="AB812" s="1"/>
       <c r="AC812" s="1"/>
     </row>
-    <row r="813" spans="1:29" ht="13.2">
+    <row r="813" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A813" s="1"/>
       <c r="B813" s="1"/>
       <c r="C813" s="1"/>
@@ -26419,7 +26347,7 @@
       <c r="AB813" s="1"/>
       <c r="AC813" s="1"/>
     </row>
-    <row r="814" spans="1:29" ht="13.2">
+    <row r="814" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A814" s="1"/>
       <c r="B814" s="1"/>
       <c r="C814" s="1"/>
@@ -26450,7 +26378,7 @@
       <c r="AB814" s="1"/>
       <c r="AC814" s="1"/>
     </row>
-    <row r="815" spans="1:29" ht="13.2">
+    <row r="815" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A815" s="1"/>
       <c r="B815" s="1"/>
       <c r="C815" s="1"/>
@@ -26481,7 +26409,7 @@
       <c r="AB815" s="1"/>
       <c r="AC815" s="1"/>
     </row>
-    <row r="816" spans="1:29" ht="13.2">
+    <row r="816" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A816" s="1"/>
       <c r="B816" s="1"/>
       <c r="C816" s="1"/>
@@ -26512,7 +26440,7 @@
       <c r="AB816" s="1"/>
       <c r="AC816" s="1"/>
     </row>
-    <row r="817" spans="1:29" ht="13.2">
+    <row r="817" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A817" s="1"/>
       <c r="B817" s="1"/>
       <c r="C817" s="1"/>
@@ -26543,7 +26471,7 @@
       <c r="AB817" s="1"/>
       <c r="AC817" s="1"/>
     </row>
-    <row r="818" spans="1:29" ht="13.2">
+    <row r="818" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A818" s="1"/>
       <c r="B818" s="1"/>
       <c r="C818" s="1"/>
@@ -26574,7 +26502,7 @@
       <c r="AB818" s="1"/>
       <c r="AC818" s="1"/>
     </row>
-    <row r="819" spans="1:29" ht="13.2">
+    <row r="819" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A819" s="1"/>
       <c r="B819" s="1"/>
       <c r="C819" s="1"/>
@@ -26605,7 +26533,7 @@
       <c r="AB819" s="1"/>
       <c r="AC819" s="1"/>
     </row>
-    <row r="820" spans="1:29" ht="13.2">
+    <row r="820" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A820" s="1"/>
       <c r="B820" s="1"/>
       <c r="C820" s="1"/>
@@ -26636,7 +26564,7 @@
       <c r="AB820" s="1"/>
       <c r="AC820" s="1"/>
     </row>
-    <row r="821" spans="1:29" ht="13.2">
+    <row r="821" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A821" s="1"/>
       <c r="B821" s="1"/>
       <c r="C821" s="1"/>
@@ -26667,7 +26595,7 @@
       <c r="AB821" s="1"/>
       <c r="AC821" s="1"/>
     </row>
-    <row r="822" spans="1:29" ht="13.2">
+    <row r="822" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A822" s="1"/>
       <c r="B822" s="1"/>
       <c r="C822" s="1"/>
@@ -26698,7 +26626,7 @@
       <c r="AB822" s="1"/>
       <c r="AC822" s="1"/>
     </row>
-    <row r="823" spans="1:29" ht="13.2">
+    <row r="823" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A823" s="1"/>
       <c r="B823" s="1"/>
       <c r="C823" s="1"/>
@@ -26729,7 +26657,7 @@
       <c r="AB823" s="1"/>
       <c r="AC823" s="1"/>
     </row>
-    <row r="824" spans="1:29" ht="13.2">
+    <row r="824" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A824" s="1"/>
       <c r="B824" s="1"/>
       <c r="C824" s="1"/>
@@ -26760,7 +26688,7 @@
       <c r="AB824" s="1"/>
       <c r="AC824" s="1"/>
     </row>
-    <row r="825" spans="1:29" ht="13.2">
+    <row r="825" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A825" s="1"/>
       <c r="B825" s="1"/>
       <c r="C825" s="1"/>
@@ -26791,7 +26719,7 @@
       <c r="AB825" s="1"/>
       <c r="AC825" s="1"/>
     </row>
-    <row r="826" spans="1:29" ht="13.2">
+    <row r="826" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A826" s="1"/>
       <c r="B826" s="1"/>
       <c r="C826" s="1"/>
@@ -26822,7 +26750,7 @@
       <c r="AB826" s="1"/>
       <c r="AC826" s="1"/>
     </row>
-    <row r="827" spans="1:29" ht="13.2">
+    <row r="827" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A827" s="1"/>
       <c r="B827" s="1"/>
       <c r="C827" s="1"/>
@@ -26853,7 +26781,7 @@
       <c r="AB827" s="1"/>
       <c r="AC827" s="1"/>
     </row>
-    <row r="828" spans="1:29" ht="13.2">
+    <row r="828" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A828" s="1"/>
       <c r="B828" s="1"/>
       <c r="C828" s="1"/>
@@ -26884,7 +26812,7 @@
       <c r="AB828" s="1"/>
       <c r="AC828" s="1"/>
     </row>
-    <row r="829" spans="1:29" ht="13.2">
+    <row r="829" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A829" s="1"/>
       <c r="B829" s="1"/>
       <c r="C829" s="1"/>
@@ -26915,7 +26843,7 @@
       <c r="AB829" s="1"/>
       <c r="AC829" s="1"/>
     </row>
-    <row r="830" spans="1:29" ht="13.2">
+    <row r="830" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A830" s="1"/>
       <c r="B830" s="1"/>
       <c r="C830" s="1"/>
@@ -26946,7 +26874,7 @@
       <c r="AB830" s="1"/>
       <c r="AC830" s="1"/>
     </row>
-    <row r="831" spans="1:29" ht="13.2">
+    <row r="831" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A831" s="1"/>
       <c r="B831" s="1"/>
       <c r="C831" s="1"/>
@@ -26977,7 +26905,7 @@
       <c r="AB831" s="1"/>
       <c r="AC831" s="1"/>
     </row>
-    <row r="832" spans="1:29" ht="13.2">
+    <row r="832" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A832" s="1"/>
       <c r="B832" s="1"/>
       <c r="C832" s="1"/>
@@ -27008,7 +26936,7 @@
       <c r="AB832" s="1"/>
       <c r="AC832" s="1"/>
     </row>
-    <row r="833" spans="1:29" ht="13.2">
+    <row r="833" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A833" s="1"/>
       <c r="B833" s="1"/>
       <c r="C833" s="1"/>
@@ -27039,7 +26967,7 @@
       <c r="AB833" s="1"/>
       <c r="AC833" s="1"/>
     </row>
-    <row r="834" spans="1:29" ht="13.2">
+    <row r="834" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A834" s="1"/>
       <c r="B834" s="1"/>
       <c r="C834" s="1"/>
@@ -27070,7 +26998,7 @@
       <c r="AB834" s="1"/>
       <c r="AC834" s="1"/>
     </row>
-    <row r="835" spans="1:29" ht="13.2">
+    <row r="835" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A835" s="1"/>
       <c r="B835" s="1"/>
       <c r="C835" s="1"/>
@@ -27101,7 +27029,7 @@
       <c r="AB835" s="1"/>
       <c r="AC835" s="1"/>
     </row>
-    <row r="836" spans="1:29" ht="13.2">
+    <row r="836" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A836" s="1"/>
       <c r="B836" s="1"/>
       <c r="C836" s="1"/>
@@ -27132,7 +27060,7 @@
       <c r="AB836" s="1"/>
       <c r="AC836" s="1"/>
     </row>
-    <row r="837" spans="1:29" ht="13.2">
+    <row r="837" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A837" s="1"/>
       <c r="B837" s="1"/>
       <c r="C837" s="1"/>
@@ -27163,7 +27091,7 @@
       <c r="AB837" s="1"/>
       <c r="AC837" s="1"/>
     </row>
-    <row r="838" spans="1:29" ht="13.2">
+    <row r="838" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A838" s="1"/>
       <c r="B838" s="1"/>
       <c r="C838" s="1"/>
@@ -27194,7 +27122,7 @@
       <c r="AB838" s="1"/>
       <c r="AC838" s="1"/>
     </row>
-    <row r="839" spans="1:29" ht="13.2">
+    <row r="839" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A839" s="1"/>
       <c r="B839" s="1"/>
       <c r="C839" s="1"/>
@@ -27225,7 +27153,7 @@
       <c r="AB839" s="1"/>
       <c r="AC839" s="1"/>
     </row>
-    <row r="840" spans="1:29" ht="13.2">
+    <row r="840" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A840" s="1"/>
       <c r="B840" s="1"/>
       <c r="C840" s="1"/>
@@ -27256,7 +27184,7 @@
       <c r="AB840" s="1"/>
       <c r="AC840" s="1"/>
     </row>
-    <row r="841" spans="1:29" ht="13.2">
+    <row r="841" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A841" s="1"/>
       <c r="B841" s="1"/>
       <c r="C841" s="1"/>
@@ -27287,7 +27215,7 @@
       <c r="AB841" s="1"/>
       <c r="AC841" s="1"/>
     </row>
-    <row r="842" spans="1:29" ht="13.2">
+    <row r="842" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A842" s="1"/>
       <c r="B842" s="1"/>
       <c r="C842" s="1"/>
@@ -27318,7 +27246,7 @@
       <c r="AB842" s="1"/>
       <c r="AC842" s="1"/>
     </row>
-    <row r="843" spans="1:29" ht="13.2">
+    <row r="843" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A843" s="1"/>
       <c r="B843" s="1"/>
       <c r="C843" s="1"/>
@@ -27349,7 +27277,7 @@
       <c r="AB843" s="1"/>
       <c r="AC843" s="1"/>
     </row>
-    <row r="844" spans="1:29" ht="13.2">
+    <row r="844" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A844" s="1"/>
       <c r="B844" s="1"/>
       <c r="C844" s="1"/>
@@ -27380,7 +27308,7 @@
       <c r="AB844" s="1"/>
       <c r="AC844" s="1"/>
     </row>
-    <row r="845" spans="1:29" ht="13.2">
+    <row r="845" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A845" s="1"/>
       <c r="B845" s="1"/>
       <c r="C845" s="1"/>
@@ -27411,7 +27339,7 @@
       <c r="AB845" s="1"/>
       <c r="AC845" s="1"/>
     </row>
-    <row r="846" spans="1:29" ht="13.2">
+    <row r="846" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A846" s="1"/>
       <c r="B846" s="1"/>
       <c r="C846" s="1"/>
@@ -27442,7 +27370,7 @@
       <c r="AB846" s="1"/>
       <c r="AC846" s="1"/>
     </row>
-    <row r="847" spans="1:29" ht="13.2">
+    <row r="847" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A847" s="1"/>
       <c r="B847" s="1"/>
       <c r="C847" s="1"/>
@@ -27473,7 +27401,7 @@
       <c r="AB847" s="1"/>
       <c r="AC847" s="1"/>
     </row>
-    <row r="848" spans="1:29" ht="13.2">
+    <row r="848" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A848" s="1"/>
       <c r="B848" s="1"/>
       <c r="C848" s="1"/>
@@ -27504,7 +27432,7 @@
       <c r="AB848" s="1"/>
       <c r="AC848" s="1"/>
     </row>
-    <row r="849" spans="1:29" ht="13.2">
+    <row r="849" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A849" s="1"/>
       <c r="B849" s="1"/>
       <c r="C849" s="1"/>
@@ -27535,7 +27463,7 @@
       <c r="AB849" s="1"/>
       <c r="AC849" s="1"/>
     </row>
-    <row r="850" spans="1:29" ht="13.2">
+    <row r="850" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A850" s="1"/>
       <c r="B850" s="1"/>
       <c r="C850" s="1"/>
@@ -27566,7 +27494,7 @@
       <c r="AB850" s="1"/>
       <c r="AC850" s="1"/>
     </row>
-    <row r="851" spans="1:29" ht="13.2">
+    <row r="851" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A851" s="1"/>
       <c r="B851" s="1"/>
       <c r="C851" s="1"/>
@@ -27597,7 +27525,7 @@
       <c r="AB851" s="1"/>
       <c r="AC851" s="1"/>
     </row>
-    <row r="852" spans="1:29" ht="13.2">
+    <row r="852" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A852" s="1"/>
       <c r="B852" s="1"/>
       <c r="C852" s="1"/>
@@ -27628,7 +27556,7 @@
       <c r="AB852" s="1"/>
       <c r="AC852" s="1"/>
     </row>
-    <row r="853" spans="1:29" ht="13.2">
+    <row r="853" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A853" s="1"/>
       <c r="B853" s="1"/>
       <c r="C853" s="1"/>
@@ -27659,7 +27587,7 @@
       <c r="AB853" s="1"/>
       <c r="AC853" s="1"/>
     </row>
-    <row r="854" spans="1:29" ht="13.2">
+    <row r="854" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A854" s="1"/>
       <c r="B854" s="1"/>
       <c r="C854" s="1"/>
@@ -27690,7 +27618,7 @@
       <c r="AB854" s="1"/>
       <c r="AC854" s="1"/>
     </row>
-    <row r="855" spans="1:29" ht="13.2">
+    <row r="855" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A855" s="1"/>
       <c r="B855" s="1"/>
       <c r="C855" s="1"/>
@@ -27721,7 +27649,7 @@
       <c r="AB855" s="1"/>
       <c r="AC855" s="1"/>
     </row>
-    <row r="856" spans="1:29" ht="13.2">
+    <row r="856" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A856" s="1"/>
       <c r="B856" s="1"/>
       <c r="C856" s="1"/>
@@ -27752,7 +27680,7 @@
       <c r="AB856" s="1"/>
       <c r="AC856" s="1"/>
     </row>
-    <row r="857" spans="1:29" ht="13.2">
+    <row r="857" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A857" s="1"/>
       <c r="B857" s="1"/>
       <c r="C857" s="1"/>
@@ -27783,7 +27711,7 @@
       <c r="AB857" s="1"/>
       <c r="AC857" s="1"/>
     </row>
-    <row r="858" spans="1:29" ht="13.2">
+    <row r="858" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A858" s="1"/>
       <c r="B858" s="1"/>
       <c r="C858" s="1"/>
@@ -27814,7 +27742,7 @@
       <c r="AB858" s="1"/>
       <c r="AC858" s="1"/>
     </row>
-    <row r="859" spans="1:29" ht="13.2">
+    <row r="859" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A859" s="1"/>
       <c r="B859" s="1"/>
       <c r="C859" s="1"/>
@@ -27845,7 +27773,7 @@
       <c r="AB859" s="1"/>
       <c r="AC859" s="1"/>
     </row>
-    <row r="860" spans="1:29" ht="13.2">
+    <row r="860" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A860" s="1"/>
       <c r="B860" s="1"/>
       <c r="C860" s="1"/>
@@ -27876,7 +27804,7 @@
       <c r="AB860" s="1"/>
       <c r="AC860" s="1"/>
     </row>
-    <row r="861" spans="1:29" ht="13.2">
+    <row r="861" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A861" s="1"/>
       <c r="B861" s="1"/>
       <c r="C861" s="1"/>
@@ -27907,7 +27835,7 @@
       <c r="AB861" s="1"/>
       <c r="AC861" s="1"/>
     </row>
-    <row r="862" spans="1:29" ht="13.2">
+    <row r="862" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A862" s="1"/>
       <c r="B862" s="1"/>
       <c r="C862" s="1"/>
@@ -27938,7 +27866,7 @@
       <c r="AB862" s="1"/>
       <c r="AC862" s="1"/>
     </row>
-    <row r="863" spans="1:29" ht="13.2">
+    <row r="863" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A863" s="1"/>
       <c r="B863" s="1"/>
       <c r="C863" s="1"/>
@@ -27969,7 +27897,7 @@
       <c r="AB863" s="1"/>
       <c r="AC863" s="1"/>
     </row>
-    <row r="864" spans="1:29" ht="13.2">
+    <row r="864" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A864" s="1"/>
       <c r="B864" s="1"/>
       <c r="C864" s="1"/>
@@ -28000,7 +27928,7 @@
       <c r="AB864" s="1"/>
       <c r="AC864" s="1"/>
     </row>
-    <row r="865" spans="1:29" ht="13.2">
+    <row r="865" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A865" s="1"/>
       <c r="B865" s="1"/>
       <c r="C865" s="1"/>
@@ -28031,7 +27959,7 @@
       <c r="AB865" s="1"/>
       <c r="AC865" s="1"/>
     </row>
-    <row r="866" spans="1:29" ht="13.2">
+    <row r="866" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A866" s="1"/>
       <c r="B866" s="1"/>
       <c r="C866" s="1"/>
@@ -28062,7 +27990,7 @@
       <c r="AB866" s="1"/>
       <c r="AC866" s="1"/>
     </row>
-    <row r="867" spans="1:29" ht="13.2">
+    <row r="867" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A867" s="1"/>
       <c r="B867" s="1"/>
       <c r="C867" s="1"/>
@@ -28093,7 +28021,7 @@
       <c r="AB867" s="1"/>
       <c r="AC867" s="1"/>
     </row>
-    <row r="868" spans="1:29" ht="13.2">
+    <row r="868" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A868" s="1"/>
       <c r="B868" s="1"/>
       <c r="C868" s="1"/>
@@ -28124,7 +28052,7 @@
       <c r="AB868" s="1"/>
       <c r="AC868" s="1"/>
     </row>
-    <row r="869" spans="1:29" ht="13.2">
+    <row r="869" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A869" s="1"/>
       <c r="B869" s="1"/>
       <c r="C869" s="1"/>
@@ -28155,7 +28083,7 @@
       <c r="AB869" s="1"/>
       <c r="AC869" s="1"/>
     </row>
-    <row r="870" spans="1:29" ht="13.2">
+    <row r="870" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A870" s="1"/>
       <c r="B870" s="1"/>
       <c r="C870" s="1"/>
@@ -28186,7 +28114,7 @@
       <c r="AB870" s="1"/>
       <c r="AC870" s="1"/>
     </row>
-    <row r="871" spans="1:29" ht="13.2">
+    <row r="871" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A871" s="1"/>
       <c r="B871" s="1"/>
       <c r="C871" s="1"/>
@@ -28217,7 +28145,7 @@
       <c r="AB871" s="1"/>
       <c r="AC871" s="1"/>
     </row>
-    <row r="872" spans="1:29" ht="13.2">
+    <row r="872" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A872" s="1"/>
       <c r="B872" s="1"/>
       <c r="C872" s="1"/>
@@ -28248,7 +28176,7 @@
       <c r="AB872" s="1"/>
       <c r="AC872" s="1"/>
     </row>
-    <row r="873" spans="1:29" ht="13.2">
+    <row r="873" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A873" s="1"/>
       <c r="B873" s="1"/>
       <c r="C873" s="1"/>
@@ -28279,7 +28207,7 @@
       <c r="AB873" s="1"/>
       <c r="AC873" s="1"/>
     </row>
-    <row r="874" spans="1:29" ht="13.2">
+    <row r="874" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A874" s="1"/>
       <c r="B874" s="1"/>
       <c r="C874" s="1"/>
@@ -28310,7 +28238,7 @@
       <c r="AB874" s="1"/>
       <c r="AC874" s="1"/>
     </row>
-    <row r="875" spans="1:29" ht="13.2">
+    <row r="875" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A875" s="1"/>
       <c r="B875" s="1"/>
       <c r="C875" s="1"/>
@@ -28341,7 +28269,7 @@
       <c r="AB875" s="1"/>
       <c r="AC875" s="1"/>
     </row>
-    <row r="876" spans="1:29" ht="13.2">
+    <row r="876" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A876" s="1"/>
       <c r="B876" s="1"/>
       <c r="C876" s="1"/>
@@ -28372,7 +28300,7 @@
       <c r="AB876" s="1"/>
       <c r="AC876" s="1"/>
     </row>
-    <row r="877" spans="1:29" ht="13.2">
+    <row r="877" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A877" s="1"/>
       <c r="B877" s="1"/>
       <c r="C877" s="1"/>
@@ -28403,7 +28331,7 @@
       <c r="AB877" s="1"/>
       <c r="AC877" s="1"/>
     </row>
-    <row r="878" spans="1:29" ht="13.2">
+    <row r="878" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A878" s="1"/>
       <c r="B878" s="1"/>
       <c r="C878" s="1"/>
@@ -28434,7 +28362,7 @@
       <c r="AB878" s="1"/>
       <c r="AC878" s="1"/>
     </row>
-    <row r="879" spans="1:29" ht="13.2">
+    <row r="879" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A879" s="1"/>
       <c r="B879" s="1"/>
       <c r="C879" s="1"/>
@@ -28465,7 +28393,7 @@
       <c r="AB879" s="1"/>
       <c r="AC879" s="1"/>
     </row>
-    <row r="880" spans="1:29" ht="13.2">
+    <row r="880" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A880" s="1"/>
       <c r="B880" s="1"/>
       <c r="C880" s="1"/>
@@ -28496,7 +28424,7 @@
       <c r="AB880" s="1"/>
       <c r="AC880" s="1"/>
     </row>
-    <row r="881" spans="1:29" ht="13.2">
+    <row r="881" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A881" s="1"/>
       <c r="B881" s="1"/>
       <c r="C881" s="1"/>
@@ -28527,7 +28455,7 @@
       <c r="AB881" s="1"/>
       <c r="AC881" s="1"/>
     </row>
-    <row r="882" spans="1:29" ht="13.2">
+    <row r="882" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A882" s="1"/>
       <c r="B882" s="1"/>
       <c r="C882" s="1"/>
@@ -28558,7 +28486,7 @@
       <c r="AB882" s="1"/>
       <c r="AC882" s="1"/>
     </row>
-    <row r="883" spans="1:29" ht="13.2">
+    <row r="883" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A883" s="1"/>
       <c r="B883" s="1"/>
       <c r="C883" s="1"/>
@@ -28589,7 +28517,7 @@
       <c r="AB883" s="1"/>
       <c r="AC883" s="1"/>
     </row>
-    <row r="884" spans="1:29" ht="13.2">
+    <row r="884" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A884" s="1"/>
       <c r="B884" s="1"/>
       <c r="C884" s="1"/>
@@ -28620,7 +28548,7 @@
       <c r="AB884" s="1"/>
       <c r="AC884" s="1"/>
     </row>
-    <row r="885" spans="1:29" ht="13.2">
+    <row r="885" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A885" s="1"/>
       <c r="B885" s="1"/>
       <c r="C885" s="1"/>
@@ -28651,7 +28579,7 @@
       <c r="AB885" s="1"/>
       <c r="AC885" s="1"/>
     </row>
-    <row r="886" spans="1:29" ht="13.2">
+    <row r="886" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A886" s="1"/>
       <c r="B886" s="1"/>
       <c r="C886" s="1"/>
@@ -28682,7 +28610,7 @@
       <c r="AB886" s="1"/>
       <c r="AC886" s="1"/>
     </row>
-    <row r="887" spans="1:29" ht="13.2">
+    <row r="887" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A887" s="1"/>
       <c r="B887" s="1"/>
       <c r="C887" s="1"/>
@@ -28713,7 +28641,7 @@
       <c r="AB887" s="1"/>
       <c r="AC887" s="1"/>
     </row>
-    <row r="888" spans="1:29" ht="13.2">
+    <row r="888" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A888" s="1"/>
       <c r="B888" s="1"/>
       <c r="C888" s="1"/>
@@ -28744,7 +28672,7 @@
       <c r="AB888" s="1"/>
       <c r="AC888" s="1"/>
     </row>
-    <row r="889" spans="1:29" ht="13.2">
+    <row r="889" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A889" s="1"/>
       <c r="B889" s="1"/>
       <c r="C889" s="1"/>
@@ -28775,7 +28703,7 @@
       <c r="AB889" s="1"/>
       <c r="AC889" s="1"/>
     </row>
-    <row r="890" spans="1:29" ht="13.2">
+    <row r="890" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A890" s="1"/>
       <c r="B890" s="1"/>
       <c r="C890" s="1"/>
@@ -28806,7 +28734,7 @@
       <c r="AB890" s="1"/>
       <c r="AC890" s="1"/>
     </row>
-    <row r="891" spans="1:29" ht="13.2">
+    <row r="891" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A891" s="1"/>
       <c r="B891" s="1"/>
       <c r="C891" s="1"/>
@@ -28837,7 +28765,7 @@
       <c r="AB891" s="1"/>
       <c r="AC891" s="1"/>
     </row>
-    <row r="892" spans="1:29" ht="13.2">
+    <row r="892" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A892" s="1"/>
       <c r="B892" s="1"/>
       <c r="C892" s="1"/>
@@ -28868,7 +28796,7 @@
       <c r="AB892" s="1"/>
       <c r="AC892" s="1"/>
     </row>
-    <row r="893" spans="1:29" ht="13.2">
+    <row r="893" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A893" s="1"/>
       <c r="B893" s="1"/>
       <c r="C893" s="1"/>
@@ -28899,7 +28827,7 @@
       <c r="AB893" s="1"/>
       <c r="AC893" s="1"/>
     </row>
-    <row r="894" spans="1:29" ht="13.2">
+    <row r="894" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A894" s="1"/>
       <c r="B894" s="1"/>
       <c r="C894" s="1"/>
@@ -28930,7 +28858,7 @@
       <c r="AB894" s="1"/>
       <c r="AC894" s="1"/>
     </row>
-    <row r="895" spans="1:29" ht="13.2">
+    <row r="895" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A895" s="1"/>
       <c r="B895" s="1"/>
       <c r="C895" s="1"/>
@@ -28961,7 +28889,7 @@
       <c r="AB895" s="1"/>
       <c r="AC895" s="1"/>
     </row>
-    <row r="896" spans="1:29" ht="13.2">
+    <row r="896" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A896" s="1"/>
       <c r="B896" s="1"/>
       <c r="C896" s="1"/>
@@ -28992,7 +28920,7 @@
       <c r="AB896" s="1"/>
       <c r="AC896" s="1"/>
     </row>
-    <row r="897" spans="1:29" ht="13.2">
+    <row r="897" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A897" s="1"/>
       <c r="B897" s="1"/>
       <c r="C897" s="1"/>
@@ -29023,7 +28951,7 @@
       <c r="AB897" s="1"/>
       <c r="AC897" s="1"/>
     </row>
-    <row r="898" spans="1:29" ht="13.2">
+    <row r="898" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A898" s="1"/>
       <c r="B898" s="1"/>
       <c r="C898" s="1"/>
@@ -29054,7 +28982,7 @@
       <c r="AB898" s="1"/>
       <c r="AC898" s="1"/>
     </row>
-    <row r="899" spans="1:29" ht="13.2">
+    <row r="899" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A899" s="1"/>
       <c r="B899" s="1"/>
       <c r="C899" s="1"/>
@@ -29085,7 +29013,7 @@
       <c r="AB899" s="1"/>
       <c r="AC899" s="1"/>
     </row>
-    <row r="900" spans="1:29" ht="13.2">
+    <row r="900" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A900" s="1"/>
       <c r="B900" s="1"/>
       <c r="C900" s="1"/>
@@ -29116,7 +29044,7 @@
       <c r="AB900" s="1"/>
       <c r="AC900" s="1"/>
     </row>
-    <row r="901" spans="1:29" ht="13.2">
+    <row r="901" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A901" s="1"/>
       <c r="B901" s="1"/>
       <c r="C901" s="1"/>
@@ -29147,7 +29075,7 @@
       <c r="AB901" s="1"/>
       <c r="AC901" s="1"/>
     </row>
-    <row r="902" spans="1:29" ht="13.2">
+    <row r="902" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A902" s="1"/>
       <c r="B902" s="1"/>
       <c r="C902" s="1"/>
@@ -29178,7 +29106,7 @@
       <c r="AB902" s="1"/>
       <c r="AC902" s="1"/>
     </row>
-    <row r="903" spans="1:29" ht="13.2">
+    <row r="903" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A903" s="1"/>
       <c r="B903" s="1"/>
       <c r="C903" s="1"/>
@@ -29209,7 +29137,7 @@
       <c r="AB903" s="1"/>
       <c r="AC903" s="1"/>
     </row>
-    <row r="904" spans="1:29" ht="13.2">
+    <row r="904" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A904" s="1"/>
       <c r="B904" s="1"/>
       <c r="C904" s="1"/>
@@ -29240,7 +29168,7 @@
       <c r="AB904" s="1"/>
       <c r="AC904" s="1"/>
     </row>
-    <row r="905" spans="1:29" ht="13.2">
+    <row r="905" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A905" s="1"/>
       <c r="B905" s="1"/>
       <c r="C905" s="1"/>
@@ -29271,7 +29199,7 @@
       <c r="AB905" s="1"/>
       <c r="AC905" s="1"/>
     </row>
-    <row r="906" spans="1:29" ht="13.2">
+    <row r="906" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A906" s="1"/>
       <c r="B906" s="1"/>
       <c r="C906" s="1"/>
@@ -29302,7 +29230,7 @@
       <c r="AB906" s="1"/>
       <c r="AC906" s="1"/>
     </row>
-    <row r="907" spans="1:29" ht="13.2">
+    <row r="907" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A907" s="1"/>
       <c r="B907" s="1"/>
       <c r="C907" s="1"/>
@@ -29333,7 +29261,7 @@
       <c r="AB907" s="1"/>
       <c r="AC907" s="1"/>
     </row>
-    <row r="908" spans="1:29" ht="13.2">
+    <row r="908" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A908" s="1"/>
       <c r="B908" s="1"/>
       <c r="C908" s="1"/>
@@ -29364,7 +29292,7 @@
       <c r="AB908" s="1"/>
       <c r="AC908" s="1"/>
     </row>
-    <row r="909" spans="1:29" ht="13.2">
+    <row r="909" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A909" s="1"/>
       <c r="B909" s="1"/>
       <c r="C909" s="1"/>
@@ -29395,7 +29323,7 @@
       <c r="AB909" s="1"/>
       <c r="AC909" s="1"/>
     </row>
-    <row r="910" spans="1:29" ht="13.2">
+    <row r="910" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A910" s="1"/>
       <c r="B910" s="1"/>
       <c r="C910" s="1"/>
@@ -29426,7 +29354,7 @@
       <c r="AB910" s="1"/>
       <c r="AC910" s="1"/>
     </row>
-    <row r="911" spans="1:29" ht="13.2">
+    <row r="911" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A911" s="1"/>
       <c r="B911" s="1"/>
       <c r="C911" s="1"/>
@@ -29457,7 +29385,7 @@
       <c r="AB911" s="1"/>
       <c r="AC911" s="1"/>
     </row>
-    <row r="912" spans="1:29" ht="13.2">
+    <row r="912" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A912" s="1"/>
       <c r="B912" s="1"/>
       <c r="C912" s="1"/>
@@ -29488,7 +29416,7 @@
       <c r="AB912" s="1"/>
       <c r="AC912" s="1"/>
     </row>
-    <row r="913" spans="1:29" ht="13.2">
+    <row r="913" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A913" s="1"/>
       <c r="B913" s="1"/>
       <c r="C913" s="1"/>
@@ -29519,7 +29447,7 @@
       <c r="AB913" s="1"/>
       <c r="AC913" s="1"/>
     </row>
-    <row r="914" spans="1:29" ht="13.2">
+    <row r="914" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A914" s="1"/>
       <c r="B914" s="1"/>
       <c r="C914" s="1"/>
@@ -29550,7 +29478,7 @@
       <c r="AB914" s="1"/>
       <c r="AC914" s="1"/>
     </row>
-    <row r="915" spans="1:29" ht="13.2">
+    <row r="915" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A915" s="1"/>
       <c r="B915" s="1"/>
       <c r="C915" s="1"/>
@@ -29581,7 +29509,7 @@
       <c r="AB915" s="1"/>
       <c r="AC915" s="1"/>
     </row>
-    <row r="916" spans="1:29" ht="13.2">
+    <row r="916" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A916" s="1"/>
       <c r="B916" s="1"/>
       <c r="C916" s="1"/>
@@ -29612,7 +29540,7 @@
       <c r="AB916" s="1"/>
       <c r="AC916" s="1"/>
     </row>
-    <row r="917" spans="1:29" ht="13.2">
+    <row r="917" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A917" s="1"/>
       <c r="B917" s="1"/>
       <c r="C917" s="1"/>
@@ -29643,7 +29571,7 @@
       <c r="AB917" s="1"/>
       <c r="AC917" s="1"/>
     </row>
-    <row r="918" spans="1:29" ht="13.2">
+    <row r="918" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A918" s="1"/>
       <c r="B918" s="1"/>
       <c r="C918" s="1"/>
@@ -29674,7 +29602,7 @@
       <c r="AB918" s="1"/>
       <c r="AC918" s="1"/>
     </row>
-    <row r="919" spans="1:29" ht="13.2">
+    <row r="919" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A919" s="1"/>
       <c r="B919" s="1"/>
       <c r="C919" s="1"/>
@@ -29705,7 +29633,7 @@
       <c r="AB919" s="1"/>
       <c r="AC919" s="1"/>
     </row>
-    <row r="920" spans="1:29" ht="13.2">
+    <row r="920" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A920" s="1"/>
       <c r="B920" s="1"/>
       <c r="C920" s="1"/>
@@ -29736,7 +29664,7 @@
       <c r="AB920" s="1"/>
       <c r="AC920" s="1"/>
     </row>
-    <row r="921" spans="1:29" ht="13.2">
+    <row r="921" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A921" s="1"/>
       <c r="B921" s="1"/>
       <c r="C921" s="1"/>
@@ -29767,7 +29695,7 @@
       <c r="AB921" s="1"/>
       <c r="AC921" s="1"/>
     </row>
-    <row r="922" spans="1:29" ht="13.2">
+    <row r="922" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A922" s="1"/>
       <c r="B922" s="1"/>
       <c r="C922" s="1"/>
@@ -29798,7 +29726,7 @@
       <c r="AB922" s="1"/>
       <c r="AC922" s="1"/>
     </row>
-    <row r="923" spans="1:29" ht="13.2">
+    <row r="923" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A923" s="1"/>
       <c r="B923" s="1"/>
       <c r="C923" s="1"/>
@@ -29829,7 +29757,7 @@
       <c r="AB923" s="1"/>
       <c r="AC923" s="1"/>
     </row>
-    <row r="924" spans="1:29" ht="13.2">
+    <row r="924" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A924" s="1"/>
       <c r="B924" s="1"/>
       <c r="C924" s="1"/>
@@ -29860,7 +29788,7 @@
       <c r="AB924" s="1"/>
       <c r="AC924" s="1"/>
     </row>
-    <row r="925" spans="1:29" ht="13.2">
+    <row r="925" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A925" s="1"/>
       <c r="B925" s="1"/>
       <c r="C925" s="1"/>
@@ -29891,7 +29819,7 @@
       <c r="AB925" s="1"/>
       <c r="AC925" s="1"/>
     </row>
-    <row r="926" spans="1:29" ht="13.2">
+    <row r="926" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A926" s="1"/>
       <c r="B926" s="1"/>
       <c r="C926" s="1"/>
@@ -29922,7 +29850,7 @@
       <c r="AB926" s="1"/>
       <c r="AC926" s="1"/>
     </row>
-    <row r="927" spans="1:29" ht="13.2">
+    <row r="927" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A927" s="1"/>
       <c r="B927" s="1"/>
       <c r="C927" s="1"/>
@@ -29953,7 +29881,7 @@
       <c r="AB927" s="1"/>
       <c r="AC927" s="1"/>
     </row>
-    <row r="928" spans="1:29" ht="13.2">
+    <row r="928" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A928" s="1"/>
       <c r="B928" s="1"/>
       <c r="C928" s="1"/>
@@ -29984,7 +29912,7 @@
       <c r="AB928" s="1"/>
       <c r="AC928" s="1"/>
     </row>
-    <row r="929" spans="1:29" ht="13.2">
+    <row r="929" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A929" s="1"/>
       <c r="B929" s="1"/>
       <c r="C929" s="1"/>
@@ -30015,7 +29943,7 @@
       <c r="AB929" s="1"/>
       <c r="AC929" s="1"/>
     </row>
-    <row r="930" spans="1:29" ht="13.2">
+    <row r="930" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A930" s="1"/>
       <c r="B930" s="1"/>
       <c r="C930" s="1"/>
@@ -30046,7 +29974,7 @@
       <c r="AB930" s="1"/>
       <c r="AC930" s="1"/>
     </row>
-    <row r="931" spans="1:29" ht="13.2">
+    <row r="931" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A931" s="1"/>
       <c r="B931" s="1"/>
       <c r="C931" s="1"/>
@@ -30077,7 +30005,7 @@
       <c r="AB931" s="1"/>
       <c r="AC931" s="1"/>
     </row>
-    <row r="932" spans="1:29" ht="13.2">
+    <row r="932" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A932" s="1"/>
       <c r="B932" s="1"/>
       <c r="C932" s="1"/>
@@ -30108,7 +30036,7 @@
       <c r="AB932" s="1"/>
       <c r="AC932" s="1"/>
     </row>
-    <row r="933" spans="1:29" ht="13.2">
+    <row r="933" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A933" s="1"/>
       <c r="B933" s="1"/>
       <c r="C933" s="1"/>
@@ -30139,7 +30067,7 @@
       <c r="AB933" s="1"/>
       <c r="AC933" s="1"/>
     </row>
-    <row r="934" spans="1:29" ht="13.2">
+    <row r="934" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A934" s="1"/>
       <c r="B934" s="1"/>
       <c r="C934" s="1"/>
@@ -30170,7 +30098,7 @@
       <c r="AB934" s="1"/>
       <c r="AC934" s="1"/>
     </row>
-    <row r="935" spans="1:29" ht="13.2">
+    <row r="935" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A935" s="1"/>
       <c r="B935" s="1"/>
       <c r="C935" s="1"/>
@@ -30201,7 +30129,7 @@
       <c r="AB935" s="1"/>
       <c r="AC935" s="1"/>
     </row>
-    <row r="936" spans="1:29" ht="13.2">
+    <row r="936" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A936" s="1"/>
       <c r="B936" s="1"/>
       <c r="C936" s="1"/>
@@ -30232,7 +30160,7 @@
       <c r="AB936" s="1"/>
       <c r="AC936" s="1"/>
     </row>
-    <row r="937" spans="1:29" ht="13.2">
+    <row r="937" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A937" s="1"/>
       <c r="B937" s="1"/>
       <c r="C937" s="1"/>
@@ -30263,7 +30191,7 @@
       <c r="AB937" s="1"/>
       <c r="AC937" s="1"/>
     </row>
-    <row r="938" spans="1:29" ht="13.2">
+    <row r="938" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A938" s="1"/>
       <c r="B938" s="1"/>
       <c r="C938" s="1"/>
@@ -30294,7 +30222,7 @@
       <c r="AB938" s="1"/>
       <c r="AC938" s="1"/>
     </row>
-    <row r="939" spans="1:29" ht="13.2">
+    <row r="939" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A939" s="1"/>
       <c r="B939" s="1"/>
       <c r="C939" s="1"/>
@@ -30325,7 +30253,7 @@
       <c r="AB939" s="1"/>
       <c r="AC939" s="1"/>
     </row>
-    <row r="940" spans="1:29" ht="13.2">
+    <row r="940" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A940" s="1"/>
       <c r="B940" s="1"/>
       <c r="C940" s="1"/>
@@ -30356,7 +30284,7 @@
       <c r="AB940" s="1"/>
       <c r="AC940" s="1"/>
     </row>
-    <row r="941" spans="1:29" ht="13.2">
+    <row r="941" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A941" s="1"/>
       <c r="B941" s="1"/>
       <c r="C941" s="1"/>
@@ -30387,7 +30315,7 @@
       <c r="AB941" s="1"/>
       <c r="AC941" s="1"/>
     </row>
-    <row r="942" spans="1:29" ht="13.2">
+    <row r="942" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A942" s="1"/>
       <c r="B942" s="1"/>
       <c r="C942" s="1"/>
@@ -30418,7 +30346,7 @@
       <c r="AB942" s="1"/>
       <c r="AC942" s="1"/>
     </row>
-    <row r="943" spans="1:29" ht="13.2">
+    <row r="943" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A943" s="1"/>
       <c r="B943" s="1"/>
       <c r="C943" s="1"/>
@@ -30449,7 +30377,7 @@
       <c r="AB943" s="1"/>
       <c r="AC943" s="1"/>
     </row>
-    <row r="944" spans="1:29" ht="13.2">
+    <row r="944" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A944" s="1"/>
       <c r="B944" s="1"/>
       <c r="C944" s="1"/>
@@ -30480,7 +30408,7 @@
       <c r="AB944" s="1"/>
       <c r="AC944" s="1"/>
     </row>
-    <row r="945" spans="1:29" ht="13.2">
+    <row r="945" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A945" s="1"/>
       <c r="B945" s="1"/>
       <c r="C945" s="1"/>
@@ -30511,7 +30439,7 @@
       <c r="AB945" s="1"/>
       <c r="AC945" s="1"/>
     </row>
-    <row r="946" spans="1:29" ht="13.2">
+    <row r="946" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A946" s="1"/>
       <c r="B946" s="1"/>
       <c r="C946" s="1"/>
@@ -30542,7 +30470,7 @@
       <c r="AB946" s="1"/>
       <c r="AC946" s="1"/>
     </row>
-    <row r="947" spans="1:29" ht="13.2">
+    <row r="947" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A947" s="1"/>
       <c r="B947" s="1"/>
       <c r="C947" s="1"/>
@@ -30573,7 +30501,7 @@
       <c r="AB947" s="1"/>
       <c r="AC947" s="1"/>
     </row>
-    <row r="948" spans="1:29" ht="13.2">
+    <row r="948" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A948" s="1"/>
       <c r="B948" s="1"/>
       <c r="C948" s="1"/>
@@ -30604,7 +30532,7 @@
       <c r="AB948" s="1"/>
       <c r="AC948" s="1"/>
     </row>
-    <row r="949" spans="1:29" ht="13.2">
+    <row r="949" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A949" s="1"/>
       <c r="B949" s="1"/>
       <c r="C949" s="1"/>
@@ -30635,7 +30563,7 @@
       <c r="AB949" s="1"/>
       <c r="AC949" s="1"/>
     </row>
-    <row r="950" spans="1:29" ht="13.2">
+    <row r="950" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A950" s="1"/>
       <c r="B950" s="1"/>
       <c r="C950" s="1"/>
@@ -30666,7 +30594,7 @@
       <c r="AB950" s="1"/>
       <c r="AC950" s="1"/>
     </row>
-    <row r="951" spans="1:29" ht="13.2">
+    <row r="951" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A951" s="1"/>
       <c r="B951" s="1"/>
       <c r="C951" s="1"/>
@@ -30697,7 +30625,7 @@
       <c r="AB951" s="1"/>
       <c r="AC951" s="1"/>
     </row>
-    <row r="952" spans="1:29" ht="13.2">
+    <row r="952" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A952" s="1"/>
       <c r="B952" s="1"/>
       <c r="C952" s="1"/>
@@ -30728,7 +30656,7 @@
       <c r="AB952" s="1"/>
       <c r="AC952" s="1"/>
     </row>
-    <row r="953" spans="1:29" ht="13.2">
+    <row r="953" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A953" s="1"/>
       <c r="B953" s="1"/>
       <c r="C953" s="1"/>
@@ -30759,7 +30687,7 @@
       <c r="AB953" s="1"/>
       <c r="AC953" s="1"/>
     </row>
-    <row r="954" spans="1:29" ht="13.2">
+    <row r="954" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A954" s="1"/>
       <c r="B954" s="1"/>
       <c r="C954" s="1"/>
@@ -30790,7 +30718,7 @@
       <c r="AB954" s="1"/>
       <c r="AC954" s="1"/>
     </row>
-    <row r="955" spans="1:29" ht="13.2">
+    <row r="955" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A955" s="1"/>
       <c r="B955" s="1"/>
       <c r="C955" s="1"/>
@@ -30821,7 +30749,7 @@
       <c r="AB955" s="1"/>
       <c r="AC955" s="1"/>
     </row>
-    <row r="956" spans="1:29" ht="13.2">
+    <row r="956" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A956" s="1"/>
       <c r="B956" s="1"/>
       <c r="C956" s="1"/>
@@ -30852,7 +30780,7 @@
       <c r="AB956" s="1"/>
       <c r="AC956" s="1"/>
     </row>
-    <row r="957" spans="1:29" ht="13.2">
+    <row r="957" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A957" s="1"/>
       <c r="B957" s="1"/>
       <c r="C957" s="1"/>
@@ -30883,7 +30811,7 @@
       <c r="AB957" s="1"/>
       <c r="AC957" s="1"/>
     </row>
-    <row r="958" spans="1:29" ht="13.2">
+    <row r="958" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A958" s="1"/>
       <c r="B958" s="1"/>
       <c r="C958" s="1"/>
@@ -30914,7 +30842,7 @@
       <c r="AB958" s="1"/>
       <c r="AC958" s="1"/>
     </row>
-    <row r="959" spans="1:29" ht="13.2">
+    <row r="959" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A959" s="1"/>
       <c r="B959" s="1"/>
       <c r="C959" s="1"/>
@@ -30945,7 +30873,7 @@
       <c r="AB959" s="1"/>
       <c r="AC959" s="1"/>
     </row>
-    <row r="960" spans="1:29" ht="13.2">
+    <row r="960" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A960" s="1"/>
       <c r="B960" s="1"/>
       <c r="C960" s="1"/>
@@ -30976,7 +30904,7 @@
       <c r="AB960" s="1"/>
       <c r="AC960" s="1"/>
     </row>
-    <row r="961" spans="1:29" ht="13.2">
+    <row r="961" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A961" s="1"/>
       <c r="B961" s="1"/>
       <c r="C961" s="1"/>
@@ -31007,7 +30935,7 @@
       <c r="AB961" s="1"/>
       <c r="AC961" s="1"/>
     </row>
-    <row r="962" spans="1:29" ht="13.2">
+    <row r="962" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A962" s="1"/>
       <c r="B962" s="1"/>
       <c r="C962" s="1"/>
@@ -31038,7 +30966,7 @@
       <c r="AB962" s="1"/>
       <c r="AC962" s="1"/>
     </row>
-    <row r="963" spans="1:29" ht="13.2">
+    <row r="963" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A963" s="1"/>
       <c r="B963" s="1"/>
       <c r="C963" s="1"/>
@@ -31069,7 +30997,7 @@
       <c r="AB963" s="1"/>
       <c r="AC963" s="1"/>
     </row>
-    <row r="964" spans="1:29" ht="13.2">
+    <row r="964" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A964" s="1"/>
       <c r="B964" s="1"/>
       <c r="C964" s="1"/>
@@ -31100,7 +31028,7 @@
       <c r="AB964" s="1"/>
       <c r="AC964" s="1"/>
     </row>
-    <row r="965" spans="1:29" ht="13.2">
+    <row r="965" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A965" s="1"/>
       <c r="B965" s="1"/>
       <c r="C965" s="1"/>
@@ -31131,7 +31059,7 @@
       <c r="AB965" s="1"/>
       <c r="AC965" s="1"/>
     </row>
-    <row r="966" spans="1:29" ht="13.2">
+    <row r="966" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A966" s="1"/>
       <c r="B966" s="1"/>
       <c r="C966" s="1"/>
@@ -31162,7 +31090,7 @@
       <c r="AB966" s="1"/>
       <c r="AC966" s="1"/>
     </row>
-    <row r="967" spans="1:29" ht="13.2">
+    <row r="967" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A967" s="1"/>
       <c r="B967" s="1"/>
       <c r="C967" s="1"/>
@@ -31193,7 +31121,7 @@
       <c r="AB967" s="1"/>
       <c r="AC967" s="1"/>
     </row>
-    <row r="968" spans="1:29" ht="13.2">
+    <row r="968" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A968" s="1"/>
       <c r="B968" s="1"/>
       <c r="C968" s="1"/>
@@ -31224,7 +31152,7 @@
       <c r="AB968" s="1"/>
       <c r="AC968" s="1"/>
     </row>
-    <row r="969" spans="1:29" ht="13.2">
+    <row r="969" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A969" s="1"/>
       <c r="B969" s="1"/>
       <c r="C969" s="1"/>
@@ -31255,7 +31183,7 @@
       <c r="AB969" s="1"/>
       <c r="AC969" s="1"/>
     </row>
-    <row r="970" spans="1:29" ht="13.2">
+    <row r="970" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A970" s="1"/>
       <c r="B970" s="1"/>
       <c r="C970" s="1"/>
@@ -31286,7 +31214,7 @@
       <c r="AB970" s="1"/>
       <c r="AC970" s="1"/>
     </row>
-    <row r="971" spans="1:29" ht="13.2">
+    <row r="971" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A971" s="1"/>
       <c r="B971" s="1"/>
       <c r="C971" s="1"/>
@@ -31317,7 +31245,7 @@
       <c r="AB971" s="1"/>
       <c r="AC971" s="1"/>
     </row>
-    <row r="972" spans="1:29" ht="13.2">
+    <row r="972" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A972" s="1"/>
       <c r="B972" s="1"/>
       <c r="C972" s="1"/>
@@ -31348,7 +31276,7 @@
       <c r="AB972" s="1"/>
       <c r="AC972" s="1"/>
     </row>
-    <row r="973" spans="1:29" ht="13.2">
+    <row r="973" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A973" s="1"/>
       <c r="B973" s="1"/>
       <c r="C973" s="1"/>
@@ -31379,7 +31307,7 @@
       <c r="AB973" s="1"/>
       <c r="AC973" s="1"/>
     </row>
-    <row r="974" spans="1:29" ht="13.2">
+    <row r="974" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A974" s="1"/>
       <c r="B974" s="1"/>
       <c r="C974" s="1"/>
@@ -31410,7 +31338,7 @@
       <c r="AB974" s="1"/>
       <c r="AC974" s="1"/>
     </row>
-    <row r="975" spans="1:29" ht="13.2">
+    <row r="975" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A975" s="1"/>
       <c r="B975" s="1"/>
       <c r="C975" s="1"/>
@@ -31441,7 +31369,7 @@
       <c r="AB975" s="1"/>
       <c r="AC975" s="1"/>
     </row>
-    <row r="976" spans="1:29" ht="13.2">
+    <row r="976" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A976" s="1"/>
       <c r="B976" s="1"/>
       <c r="C976" s="1"/>
@@ -31472,7 +31400,7 @@
       <c r="AB976" s="1"/>
       <c r="AC976" s="1"/>
     </row>
-    <row r="977" spans="1:29" ht="13.2">
+    <row r="977" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A977" s="1"/>
       <c r="B977" s="1"/>
       <c r="C977" s="1"/>
@@ -31503,7 +31431,7 @@
       <c r="AB977" s="1"/>
       <c r="AC977" s="1"/>
     </row>
-    <row r="978" spans="1:29" ht="13.2">
+    <row r="978" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A978" s="1"/>
       <c r="B978" s="1"/>
       <c r="C978" s="1"/>
@@ -31534,7 +31462,7 @@
       <c r="AB978" s="1"/>
       <c r="AC978" s="1"/>
     </row>
-    <row r="979" spans="1:29" ht="13.2">
+    <row r="979" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A979" s="1"/>
       <c r="B979" s="1"/>
       <c r="C979" s="1"/>
@@ -31565,7 +31493,7 @@
       <c r="AB979" s="1"/>
       <c r="AC979" s="1"/>
     </row>
-    <row r="980" spans="1:29" ht="13.2">
+    <row r="980" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A980" s="1"/>
       <c r="B980" s="1"/>
       <c r="C980" s="1"/>
@@ -31596,7 +31524,7 @@
       <c r="AB980" s="1"/>
       <c r="AC980" s="1"/>
     </row>
-    <row r="981" spans="1:29" ht="13.2">
+    <row r="981" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A981" s="1"/>
       <c r="B981" s="1"/>
       <c r="C981" s="1"/>
@@ -31627,7 +31555,7 @@
       <c r="AB981" s="1"/>
       <c r="AC981" s="1"/>
     </row>
-    <row r="982" spans="1:29" ht="13.2">
+    <row r="982" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A982" s="1"/>
       <c r="B982" s="1"/>
       <c r="C982" s="1"/>
@@ -31658,7 +31586,7 @@
       <c r="AB982" s="1"/>
       <c r="AC982" s="1"/>
     </row>
-    <row r="983" spans="1:29" ht="13.2">
+    <row r="983" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A983" s="1"/>
       <c r="B983" s="1"/>
       <c r="C983" s="1"/>
@@ -31689,7 +31617,7 @@
       <c r="AB983" s="1"/>
       <c r="AC983" s="1"/>
     </row>
-    <row r="984" spans="1:29" ht="13.2">
+    <row r="984" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A984" s="1"/>
       <c r="B984" s="1"/>
       <c r="C984" s="1"/>
@@ -31720,7 +31648,7 @@
       <c r="AB984" s="1"/>
       <c r="AC984" s="1"/>
     </row>
-    <row r="985" spans="1:29" ht="13.2">
+    <row r="985" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A985" s="1"/>
       <c r="B985" s="1"/>
       <c r="C985" s="1"/>
@@ -31751,7 +31679,7 @@
       <c r="AB985" s="1"/>
       <c r="AC985" s="1"/>
     </row>
-    <row r="986" spans="1:29" ht="13.2">
+    <row r="986" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A986" s="1"/>
       <c r="B986" s="1"/>
       <c r="C986" s="1"/>
@@ -31782,7 +31710,7 @@
       <c r="AB986" s="1"/>
       <c r="AC986" s="1"/>
     </row>
-    <row r="987" spans="1:29" ht="13.2">
+    <row r="987" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A987" s="1"/>
       <c r="B987" s="1"/>
       <c r="C987" s="1"/>
@@ -31813,7 +31741,7 @@
       <c r="AB987" s="1"/>
       <c r="AC987" s="1"/>
     </row>
-    <row r="988" spans="1:29" ht="13.2">
+    <row r="988" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A988" s="1"/>
       <c r="B988" s="1"/>
       <c r="C988" s="1"/>
@@ -31844,7 +31772,7 @@
       <c r="AB988" s="1"/>
       <c r="AC988" s="1"/>
     </row>
-    <row r="989" spans="1:29" ht="13.2">
+    <row r="989" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A989" s="1"/>
       <c r="B989" s="1"/>
       <c r="C989" s="1"/>
@@ -31875,7 +31803,7 @@
       <c r="AB989" s="1"/>
       <c r="AC989" s="1"/>
     </row>
-    <row r="990" spans="1:29" ht="13.2">
+    <row r="990" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A990" s="1"/>
       <c r="B990" s="1"/>
       <c r="C990" s="1"/>
@@ -31906,7 +31834,7 @@
       <c r="AB990" s="1"/>
       <c r="AC990" s="1"/>
     </row>
-    <row r="991" spans="1:29" ht="13.2">
+    <row r="991" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A991" s="1"/>
       <c r="B991" s="1"/>
       <c r="C991" s="1"/>
@@ -31937,7 +31865,7 @@
       <c r="AB991" s="1"/>
       <c r="AC991" s="1"/>
     </row>
-    <row r="992" spans="1:29" ht="13.2">
+    <row r="992" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A992" s="1"/>
       <c r="B992" s="1"/>
       <c r="C992" s="1"/>
@@ -31968,7 +31896,7 @@
       <c r="AB992" s="1"/>
       <c r="AC992" s="1"/>
     </row>
-    <row r="993" spans="1:29" ht="13.2">
+    <row r="993" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A993" s="1"/>
       <c r="B993" s="1"/>
       <c r="C993" s="1"/>
@@ -31999,7 +31927,7 @@
       <c r="AB993" s="1"/>
       <c r="AC993" s="1"/>
     </row>
-    <row r="994" spans="1:29" ht="13.2">
+    <row r="994" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A994" s="1"/>
       <c r="B994" s="1"/>
       <c r="C994" s="1"/>
@@ -32030,7 +31958,7 @@
       <c r="AB994" s="1"/>
       <c r="AC994" s="1"/>
     </row>
-    <row r="995" spans="1:29" ht="13.2">
+    <row r="995" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A995" s="1"/>
       <c r="B995" s="1"/>
       <c r="C995" s="1"/>
@@ -32061,7 +31989,7 @@
       <c r="AB995" s="1"/>
       <c r="AC995" s="1"/>
     </row>
-    <row r="996" spans="1:29" ht="13.2">
+    <row r="996" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A996" s="1"/>
       <c r="B996" s="1"/>
       <c r="C996" s="1"/>
@@ -32092,7 +32020,7 @@
       <c r="AB996" s="1"/>
       <c r="AC996" s="1"/>
     </row>
-    <row r="997" spans="1:29" ht="13.2">
+    <row r="997" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A997" s="1"/>
       <c r="B997" s="1"/>
       <c r="C997" s="1"/>
@@ -32123,7 +32051,7 @@
       <c r="AB997" s="1"/>
       <c r="AC997" s="1"/>
     </row>
-    <row r="998" spans="1:29" ht="13.2">
+    <row r="998" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A998" s="1"/>
       <c r="B998" s="1"/>
       <c r="C998" s="1"/>
@@ -32154,7 +32082,7 @@
       <c r="AB998" s="1"/>
       <c r="AC998" s="1"/>
     </row>
-    <row r="999" spans="1:29" ht="13.2">
+    <row r="999" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A999" s="1"/>
       <c r="B999" s="1"/>
       <c r="C999" s="1"/>
@@ -32185,7 +32113,7 @@
       <c r="AB999" s="1"/>
       <c r="AC999" s="1"/>
     </row>
-    <row r="1000" spans="1:29" ht="13.2">
+    <row r="1000" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1000" s="1"/>
       <c r="B1000" s="1"/>
       <c r="C1000" s="1"/>
@@ -32216,7 +32144,7 @@
       <c r="AB1000" s="1"/>
       <c r="AC1000" s="1"/>
     </row>
-    <row r="1001" spans="1:29" ht="13.2">
+    <row r="1001" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1001" s="1"/>
       <c r="B1001" s="1"/>
       <c r="C1001" s="1"/>

--- a/LubanConfig/DataTables/Datas/#ArtifactParam.xlsx
+++ b/LubanConfig/DataTables/Datas/#ArtifactParam.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\monster-ball\LubanConfig\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7C2736F-42ED-444C-ADB1-E8D23982F7B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08D0D25D-1E47-46AF-8165-54A7570F7906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -241,7 +241,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="120">
   <si>
     <t>##var</t>
   </si>
@@ -313,19 +313,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Increase player's starting gold by {0}.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Gold</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Headhunter</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Increase damage dealt towards monster by {0}%, but receive {1}% less point from all sources.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -338,10 +330,6 @@
   </si>
   <si>
     <t>Stargate</t>
-  </si>
-  <si>
-    <t>Increase points granted by using the teleporter by {0}%.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Splitball</t>
@@ -596,6 +584,110 @@
     <t>BottledThunder</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>Increase damage dealt towards monster by 30%, but receive 15% reduced point from all sources.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Increase player's starting gold by 200.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HadronCollider</t>
+  </si>
+  <si>
+    <t>Increase points granted by using the teleporter by 30%.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Increase points granted by using the bumper by 45%.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>WhirlingFate</t>
+  </si>
+  <si>
+    <t>SpinnerPoint</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BumperPoint</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TeleportPoint</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MonsterDamage</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>StartingGold</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SwitchPoint</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Increase points granted by using the drop switch by 25%.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Increase points granted by using the spinner by 35%.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PreciseMissile</t>
+  </si>
+  <si>
+    <t>DamagerPoint</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Increase points granted by using the damagers by 10%.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BigGameHunter</t>
+  </si>
+  <si>
+    <t>Big Game Hunter</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Precise Missile</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Clanky Lever</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Whirling Fate</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hadron Collider</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ClankyLever</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GoldIncrease</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Increase all monster's gold drop by 30%, but increase all ball prices by 10%.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GoldDrop</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -691,7 +783,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -701,9 +793,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -716,6 +805,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -959,7 +1054,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>2</v>
@@ -1012,7 +1107,7 @@
         <v>13</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>6</v>
@@ -1027,19 +1122,19 @@
         <v>11</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>11</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>11</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="M2" s="2" t="s">
         <v>11</v>
@@ -1130,19 +1225,19 @@
         <v>0</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>9</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H5" s="1">
         <v>1.3</v>
@@ -1151,8 +1246,8 @@
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
-      <c r="M5" s="7" t="s">
-        <v>86</v>
+      <c r="M5" s="6" t="s">
+        <v>83</v>
       </c>
       <c r="O5" s="1"/>
       <c r="P5" s="1"/>
@@ -1176,27 +1271,27 @@
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>9</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6" s="4">
         <v>1.3</v>
       </c>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
-      <c r="M6" s="7" t="s">
-        <v>85</v>
+      <c r="M6" s="6" t="s">
+        <v>82</v>
       </c>
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
@@ -1220,27 +1315,27 @@
         <v>2</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>9</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="4">
         <v>1.3</v>
       </c>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
-      <c r="M7" s="7" t="s">
-        <v>87</v>
+      <c r="M7" s="6" t="s">
+        <v>84</v>
       </c>
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
@@ -1264,33 +1359,33 @@
         <v>3</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="H8" s="1">
         <v>1.5</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
-      <c r="J8" s="5">
+      <c r="J8" s="4">
         <v>0.7</v>
       </c>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
-      <c r="M8" s="7" t="s">
-        <v>88</v>
+      <c r="M8" s="6" t="s">
+        <v>85</v>
       </c>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
@@ -1314,27 +1409,27 @@
         <v>4</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="G9" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="H9" s="1">
         <v>1.3</v>
       </c>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
-      <c r="M9" s="7" t="s">
-        <v>94</v>
+      <c r="M9" s="6" t="s">
+        <v>91</v>
       </c>
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
@@ -1358,19 +1453,19 @@
         <v>5</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H10" s="1">
         <v>0.7</v>
@@ -1379,8 +1474,8 @@
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
-      <c r="M10" s="7" t="s">
-        <v>89</v>
+      <c r="M10" s="6" t="s">
+        <v>86</v>
       </c>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
@@ -1404,19 +1499,19 @@
         <v>6</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H11" s="1">
         <v>1.3</v>
@@ -1425,8 +1520,8 @@
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
-      <c r="M11" s="7" t="s">
-        <v>90</v>
+      <c r="M11" s="6" t="s">
+        <v>87</v>
       </c>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
@@ -1451,19 +1546,19 @@
         <v>7</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H12" s="1">
         <v>1.3</v>
@@ -1472,8 +1567,8 @@
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
-      <c r="M12" s="7" t="s">
-        <v>91</v>
+      <c r="M12" s="6" t="s">
+        <v>88</v>
       </c>
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
@@ -1498,31 +1593,31 @@
         <v>8</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="H13" s="1">
         <v>1.3</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
-      <c r="J13" s="5">
+      <c r="J13" s="4">
         <v>1.5</v>
       </c>
-      <c r="M13" s="8" t="s">
-        <v>70</v>
+      <c r="M13" s="7" t="s">
+        <v>67</v>
       </c>
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
@@ -1547,31 +1642,31 @@
         <v>9</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
-      <c r="F14" s="6" t="s">
-        <v>45</v>
+      <c r="F14" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H14" s="1">
         <v>1.3</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
-      <c r="J14" s="5">
+      <c r="J14" s="4">
         <v>1.4</v>
       </c>
-      <c r="M14" s="7" t="s">
-        <v>92</v>
+      <c r="M14" s="6" t="s">
+        <v>89</v>
       </c>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
@@ -1596,31 +1691,31 @@
         <v>10</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
-      <c r="F15" s="6" t="s">
-        <v>46</v>
+      <c r="F15" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H15" s="1">
         <v>0.6</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
-      <c r="J15" s="5">
+      <c r="J15" s="4">
         <v>0.5</v>
       </c>
-      <c r="M15" s="7" t="s">
-        <v>93</v>
+      <c r="M15" s="6" t="s">
+        <v>90</v>
       </c>
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
@@ -1645,31 +1740,31 @@
         <v>11</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="H16" s="1">
         <v>0.7</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
-      <c r="J16" s="5">
+      <c r="J16" s="4">
         <v>0.7</v>
       </c>
-      <c r="M16" s="7" t="s">
-        <v>95</v>
+      <c r="M16" s="6" t="s">
+        <v>92</v>
       </c>
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
@@ -1693,18 +1788,18 @@
       <c r="B17" s="1">
         <v>12</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>19</v>
+      <c r="C17" s="1" t="s">
+        <v>103</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E17" s="1"/>
-      <c r="F17" s="2" t="s">
-        <v>20</v>
+      <c r="F17" s="1" t="s">
+        <v>94</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H17" s="1">
         <v>200</v>
@@ -1713,7 +1808,7 @@
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
-      <c r="M17" s="8" t="s">
+      <c r="M17" s="7" t="s">
         <v>19</v>
       </c>
       <c r="N17" s="1"/>
@@ -1733,37 +1828,37 @@
       <c r="AB17" s="1"/>
       <c r="AC17" s="1"/>
     </row>
-    <row r="18" spans="1:29" ht="15.75" customHeight="1">
+    <row r="18" spans="1:29" ht="39.6" customHeight="1">
       <c r="A18" s="1"/>
       <c r="B18" s="1">
         <v>13</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E18" s="1"/>
+      <c r="F18" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>22</v>
+      <c r="H18" s="1">
+        <v>1.3</v>
       </c>
-      <c r="E18" s="1"/>
-      <c r="F18" s="4" t="s">
+      <c r="I18" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G18" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H18" s="1">
-        <v>50</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="J18" s="1">
-        <v>30</v>
+        <v>0.85</v>
       </c>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
-      <c r="M18" s="8" t="s">
-        <v>22</v>
+      <c r="M18" s="7" t="s">
+        <v>21</v>
       </c>
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
@@ -1787,28 +1882,28 @@
       <c r="B19" s="1">
         <v>14</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>26</v>
+      <c r="C19" s="8" t="s">
+        <v>101</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E19" s="1"/>
-      <c r="F19" s="2" t="s">
-        <v>27</v>
+      <c r="F19" s="1" t="s">
+        <v>96</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H19" s="1">
-        <v>100</v>
+        <v>1.3</v>
       </c>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
-      <c r="M19" s="7" t="s">
-        <v>26</v>
+      <c r="M19" s="6" t="s">
+        <v>24</v>
       </c>
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
@@ -1829,7 +1924,27 @@
     </row>
     <row r="20" spans="1:29" ht="15.75" customHeight="1">
       <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
+      <c r="B20" s="1">
+        <v>15</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H20" s="1">
+        <v>1.45</v>
+      </c>
+      <c r="M20" s="4" t="s">
+        <v>95</v>
+      </c>
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
       <c r="P20" s="1"/>
@@ -1849,7 +1964,27 @@
     </row>
     <row r="21" spans="1:29" ht="15.75" customHeight="1">
       <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
+      <c r="B21" s="1">
+        <v>16</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H21" s="1">
+        <v>1.35</v>
+      </c>
+      <c r="M21" s="4" t="s">
+        <v>98</v>
+      </c>
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
       <c r="P21" s="1"/>
@@ -1869,18 +2004,32 @@
     </row>
     <row r="22" spans="1:29" ht="15.75" customHeight="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
+      <c r="B22" s="1">
+        <v>17</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>113</v>
+      </c>
       <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
+      <c r="F22" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H22" s="1">
+        <v>1.25</v>
+      </c>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
-      <c r="M22" s="1"/>
+      <c r="M22" s="1" t="s">
+        <v>116</v>
+      </c>
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
       <c r="P22" s="1"/>
@@ -1900,18 +2049,32 @@
     </row>
     <row r="23" spans="1:29" ht="15.75" customHeight="1">
       <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
+      <c r="B23" s="1">
+        <v>18</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>112</v>
+      </c>
       <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
+      <c r="F23" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H23" s="1">
+        <v>1.1000000000000001</v>
+      </c>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
-      <c r="M23" s="1"/>
+      <c r="M23" s="1" t="s">
+        <v>107</v>
+      </c>
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
@@ -1931,18 +2094,36 @@
     </row>
     <row r="24" spans="1:29" ht="15.75" customHeight="1">
       <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
+      <c r="B24" s="1">
+        <v>19</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>111</v>
+      </c>
       <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
+      <c r="F24" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H24" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="J24" s="1">
+        <v>1.1000000000000001</v>
+      </c>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
+      <c r="M24" s="1" t="s">
+        <v>110</v>
+      </c>
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>

--- a/LubanConfig/DataTables/Datas/#ArtifactParam.xlsx
+++ b/LubanConfig/DataTables/Datas/#ArtifactParam.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\monster-ball\LubanConfig\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08D0D25D-1E47-46AF-8165-54A7570F7906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6434687F-EEE3-4720-9462-FC233894840C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -241,7 +241,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="154">
   <si>
     <t>##var</t>
   </si>
@@ -688,6 +688,139 @@
     <t>GoldDrop</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>CubelinsLens</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AgileProfessor</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AlienPizza</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CthulusTentacle</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>EyeofBoundary</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CorruptedDisc</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HotelBroom</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cubelin's Lens</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Agile Professor</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Alien's Pizza</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cthulu's Tentacle</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Eye of Boundary</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Corrupted Disc</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Broom from a hotel</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Increase all ball's size by 20%, but increase their price by 10%.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Increase all ball's speed by 50%, but receive 30% less points from all sources.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gain 150 additional gold everytime you enter the shop.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Increase all ball's critical strike damage by 200%, but reduce 50% of their critical strike chance.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>You now enters the realm of the dead.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Everytime you gain gold, it would be randomly multiplied between 150% or 50% of its original value.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Spawn 1 additional monster in all milestones.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MonsterSpawn</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GoldChange</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DeathZone</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BallCritChange</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ExtraGold</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BallSpeed</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BallSize</t>
+  </si>
+  <si>
+    <t>BallSizeChange</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BallSpeedChange</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BallCritDmg</t>
+  </si>
+  <si>
+    <t>BallCritChance</t>
+  </si>
+  <si>
+    <t>MonsterSpawnSCount</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.5-0.5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -2143,18 +2276,36 @@
     </row>
     <row r="25" spans="1:29" ht="15.75" customHeight="1">
       <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
+      <c r="B25" s="1">
+        <v>20</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>127</v>
+      </c>
       <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-      <c r="J25" s="1"/>
+      <c r="F25" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="H25" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="J25" s="1">
+        <v>1.1000000000000001</v>
+      </c>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
-      <c r="M25" s="1"/>
+      <c r="M25" s="1" t="s">
+        <v>120</v>
+      </c>
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
       <c r="P25" s="1"/>
@@ -2174,18 +2325,36 @@
     </row>
     <row r="26" spans="1:29" ht="15.75" customHeight="1">
       <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
+      <c r="B26" s="1">
+        <v>21</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
+      <c r="F26" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="H26" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J26" s="1">
+        <v>0.7</v>
+      </c>
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
-      <c r="M26" s="1"/>
+      <c r="M26" s="1" t="s">
+        <v>121</v>
+      </c>
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
@@ -2205,18 +2374,32 @@
     </row>
     <row r="27" spans="1:29" ht="15.75" customHeight="1">
       <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
+      <c r="B27" s="1">
+        <v>22</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>129</v>
+      </c>
       <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
+      <c r="F27" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="1">
+        <v>150</v>
+      </c>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
-      <c r="M27" s="1"/>
+      <c r="M27" s="1" t="s">
+        <v>122</v>
+      </c>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
@@ -2236,18 +2419,36 @@
     </row>
     <row r="28" spans="1:29" ht="15.75" customHeight="1">
       <c r="A28" s="1"/>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
+      <c r="B28" s="1">
+        <v>23</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>130</v>
+      </c>
       <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
+      <c r="F28" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="H28" s="1">
+        <v>2</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="J28" s="1">
+        <v>0.5</v>
+      </c>
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
-      <c r="M28" s="1"/>
+      <c r="M28" s="1" t="s">
+        <v>123</v>
+      </c>
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
       <c r="P28" s="1"/>
@@ -2267,18 +2468,28 @@
     </row>
     <row r="29" spans="1:29" ht="15.75" customHeight="1">
       <c r="A29" s="1"/>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
+      <c r="B29" s="1">
+        <v>24</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>131</v>
+      </c>
       <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
+      <c r="F29" s="1" t="s">
+        <v>138</v>
+      </c>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
-      <c r="M29" s="1"/>
+      <c r="M29" s="1" t="s">
+        <v>124</v>
+      </c>
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
       <c r="P29" s="1"/>
@@ -2298,18 +2509,32 @@
     </row>
     <row r="30" spans="1:29" ht="15.75" customHeight="1">
       <c r="A30" s="1"/>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
+      <c r="B30" s="1">
+        <v>25</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>132</v>
+      </c>
       <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
+      <c r="F30" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>153</v>
+      </c>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
-      <c r="M30" s="1"/>
+      <c r="M30" s="1" t="s">
+        <v>125</v>
+      </c>
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
       <c r="P30" s="1"/>
@@ -2329,18 +2554,32 @@
     </row>
     <row r="31" spans="1:29" ht="15.75" customHeight="1">
       <c r="A31" s="1"/>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
+      <c r="B31" s="1">
+        <v>26</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>133</v>
+      </c>
       <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
+      <c r="F31" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="H31" s="1">
+        <v>1</v>
+      </c>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
-      <c r="M31" s="1"/>
+      <c r="M31" s="1" t="s">
+        <v>126</v>
+      </c>
       <c r="N31" s="1"/>
       <c r="O31" s="1"/>
       <c r="P31" s="1"/>

--- a/LubanConfig/DataTables/Datas/#ArtifactParam.xlsx
+++ b/LubanConfig/DataTables/Datas/#ArtifactParam.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\monster-ball\LubanConfig\DataTables\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\601\monster-ball\LubanConfig\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6434687F-EEE3-4720-9462-FC233894840C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A3D0C7F-D28E-4AFD-A6D7-FECC85B0C8C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ArtifactParam" sheetId="1" r:id="rId1"/>
@@ -241,7 +241,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="153">
   <si>
     <t>##var</t>
   </si>
@@ -808,17 +808,15 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>BallCritDmg</t>
-  </si>
-  <si>
-    <t>BallCritChance</t>
-  </si>
-  <si>
     <t>MonsterSpawnSCount</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>1.5-0.5</t>
+    <t>BallCritDmg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BallCritChance</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -826,7 +824,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -947,7 +945,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1164,19 +1162,19 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AC1001"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="17.33203125" customWidth="1"/>
-    <col min="5" max="5" width="18.6640625" customWidth="1"/>
-    <col min="6" max="6" width="71.88671875" customWidth="1"/>
-    <col min="7" max="7" width="20.109375" customWidth="1"/>
-    <col min="8" max="8" width="15.33203125" customWidth="1"/>
-    <col min="10" max="10" width="14.33203125" customWidth="1"/>
+    <col min="4" max="4" width="17.28515625" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" customWidth="1"/>
+    <col min="6" max="6" width="71.85546875" customWidth="1"/>
+    <col min="7" max="7" width="20.140625" customWidth="1"/>
+    <col min="8" max="8" width="15.28515625" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" customWidth="1"/>
     <col min="13" max="13" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="15.75" customHeight="1">
+    <row r="1" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1232,7 +1230,7 @@
       <c r="AB1" s="1"/>
       <c r="AC1" s="1"/>
     </row>
-    <row r="2" spans="1:29" ht="15.75" customHeight="1">
+    <row r="2" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -1288,7 +1286,7 @@
       <c r="AB2" s="1"/>
       <c r="AC2" s="1"/>
     </row>
-    <row r="3" spans="1:29" ht="15.75" customHeight="1">
+    <row r="3" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -1320,7 +1318,7 @@
       <c r="AB3" s="1"/>
       <c r="AC3" s="1"/>
     </row>
-    <row r="4" spans="1:29" ht="15.75" customHeight="1">
+    <row r="4" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -1352,7 +1350,7 @@
       <c r="AB4" s="1"/>
       <c r="AC4" s="1"/>
     </row>
-    <row r="5" spans="1:29" ht="15.75" customHeight="1">
+    <row r="5" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>0</v>
@@ -1398,7 +1396,7 @@
       <c r="AB5" s="1"/>
       <c r="AC5" s="1"/>
     </row>
-    <row r="6" spans="1:29" ht="15.75" customHeight="1">
+    <row r="6" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6" s="1">
         <v>1</v>
@@ -1442,7 +1440,7 @@
       <c r="AB6" s="1"/>
       <c r="AC6" s="1"/>
     </row>
-    <row r="7" spans="1:29" ht="30" customHeight="1">
+    <row r="7" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
       <c r="B7" s="1">
         <v>2</v>
@@ -1486,7 +1484,7 @@
       <c r="AB7" s="1"/>
       <c r="AC7" s="1"/>
     </row>
-    <row r="8" spans="1:29" ht="15.75" customHeight="1">
+    <row r="8" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
       <c r="B8" s="1">
         <v>3</v>
@@ -1536,7 +1534,7 @@
       <c r="AB8" s="1"/>
       <c r="AC8" s="1"/>
     </row>
-    <row r="9" spans="1:29" ht="15.75" customHeight="1">
+    <row r="9" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
       <c r="B9" s="1">
         <v>4</v>
@@ -1580,7 +1578,7 @@
       <c r="AB9" s="1"/>
       <c r="AC9" s="1"/>
     </row>
-    <row r="10" spans="1:29" ht="15.75" customHeight="1">
+    <row r="10" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
       <c r="B10" s="1">
         <v>5</v>
@@ -1626,7 +1624,7 @@
       <c r="AB10" s="1"/>
       <c r="AC10" s="1"/>
     </row>
-    <row r="11" spans="1:29" ht="15.75" customHeight="1">
+    <row r="11" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
       <c r="B11" s="1">
         <v>6</v>
@@ -1673,7 +1671,7 @@
       <c r="AB11" s="1"/>
       <c r="AC11" s="1"/>
     </row>
-    <row r="12" spans="1:29" ht="15.75" customHeight="1">
+    <row r="12" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
       <c r="B12" s="1">
         <v>7</v>
@@ -1720,7 +1718,7 @@
       <c r="AB12" s="1"/>
       <c r="AC12" s="1"/>
     </row>
-    <row r="13" spans="1:29" ht="15.75" customHeight="1">
+    <row r="13" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
       <c r="B13" s="1">
         <v>8</v>
@@ -1769,7 +1767,7 @@
       <c r="AB13" s="1"/>
       <c r="AC13" s="1"/>
     </row>
-    <row r="14" spans="1:29" ht="28.5" customHeight="1">
+    <row r="14" spans="1:29" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
       <c r="B14" s="1">
         <v>9</v>
@@ -1818,7 +1816,7 @@
       <c r="AB14" s="1"/>
       <c r="AC14" s="1"/>
     </row>
-    <row r="15" spans="1:29" ht="32.25" customHeight="1">
+    <row r="15" spans="1:29" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
       <c r="B15" s="1">
         <v>10</v>
@@ -1867,7 +1865,7 @@
       <c r="AB15" s="1"/>
       <c r="AC15" s="1"/>
     </row>
-    <row r="16" spans="1:29" ht="15.75" customHeight="1">
+    <row r="16" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1"/>
       <c r="B16" s="1">
         <v>11</v>
@@ -1916,7 +1914,7 @@
       <c r="AB16" s="1"/>
       <c r="AC16" s="1"/>
     </row>
-    <row r="17" spans="1:29" ht="15.75" customHeight="1">
+    <row r="17" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1"/>
       <c r="B17" s="1">
         <v>12</v>
@@ -1961,7 +1959,7 @@
       <c r="AB17" s="1"/>
       <c r="AC17" s="1"/>
     </row>
-    <row r="18" spans="1:29" ht="39.6" customHeight="1">
+    <row r="18" spans="1:29" ht="39.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1"/>
       <c r="B18" s="1">
         <v>13</v>
@@ -2010,7 +2008,7 @@
       <c r="AB18" s="1"/>
       <c r="AC18" s="1"/>
     </row>
-    <row r="19" spans="1:29" ht="35.25" customHeight="1">
+    <row r="19" spans="1:29" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1"/>
       <c r="B19" s="1">
         <v>14</v>
@@ -2055,7 +2053,7 @@
       <c r="AB19" s="1"/>
       <c r="AC19" s="1"/>
     </row>
-    <row r="20" spans="1:29" ht="15.75" customHeight="1">
+    <row r="20" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1"/>
       <c r="B20" s="1">
         <v>15</v>
@@ -2095,7 +2093,7 @@
       <c r="AB20" s="1"/>
       <c r="AC20" s="1"/>
     </row>
-    <row r="21" spans="1:29" ht="15.75" customHeight="1">
+    <row r="21" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1"/>
       <c r="B21" s="1">
         <v>16</v>
@@ -2135,7 +2133,7 @@
       <c r="AB21" s="1"/>
       <c r="AC21" s="1"/>
     </row>
-    <row r="22" spans="1:29" ht="15.75" customHeight="1">
+    <row r="22" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1"/>
       <c r="B22" s="1">
         <v>17</v>
@@ -2180,7 +2178,7 @@
       <c r="AB22" s="1"/>
       <c r="AC22" s="1"/>
     </row>
-    <row r="23" spans="1:29" ht="15.75" customHeight="1">
+    <row r="23" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1"/>
       <c r="B23" s="1">
         <v>18</v>
@@ -2225,7 +2223,7 @@
       <c r="AB23" s="1"/>
       <c r="AC23" s="1"/>
     </row>
-    <row r="24" spans="1:29" ht="15.75" customHeight="1">
+    <row r="24" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1"/>
       <c r="B24" s="1">
         <v>19</v>
@@ -2274,7 +2272,7 @@
       <c r="AB24" s="1"/>
       <c r="AC24" s="1"/>
     </row>
-    <row r="25" spans="1:29" ht="15.75" customHeight="1">
+    <row r="25" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
       <c r="B25" s="1">
         <v>20</v>
@@ -2323,7 +2321,7 @@
       <c r="AB25" s="1"/>
       <c r="AC25" s="1"/>
     </row>
-    <row r="26" spans="1:29" ht="15.75" customHeight="1">
+    <row r="26" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1"/>
       <c r="B26" s="1">
         <v>21</v>
@@ -2372,7 +2370,7 @@
       <c r="AB26" s="1"/>
       <c r="AC26" s="1"/>
     </row>
-    <row r="27" spans="1:29" ht="15.75" customHeight="1">
+    <row r="27" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1"/>
       <c r="B27" s="1">
         <v>22</v>
@@ -2417,7 +2415,7 @@
       <c r="AB27" s="1"/>
       <c r="AC27" s="1"/>
     </row>
-    <row r="28" spans="1:29" ht="15.75" customHeight="1">
+    <row r="28" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1"/>
       <c r="B28" s="1">
         <v>23</v>
@@ -2433,13 +2431,13 @@
         <v>137</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H28" s="1">
         <v>2</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J28" s="1">
         <v>0.5</v>
@@ -2466,7 +2464,7 @@
       <c r="AB28" s="1"/>
       <c r="AC28" s="1"/>
     </row>
-    <row r="29" spans="1:29" ht="15.75" customHeight="1">
+    <row r="29" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1"/>
       <c r="B29" s="1">
         <v>24</v>
@@ -2507,7 +2505,7 @@
       <c r="AB29" s="1"/>
       <c r="AC29" s="1"/>
     </row>
-    <row r="30" spans="1:29" ht="15.75" customHeight="1">
+    <row r="30" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1"/>
       <c r="B30" s="1">
         <v>25</v>
@@ -2525,11 +2523,13 @@
       <c r="G30" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H30" s="1" t="s">
-        <v>153</v>
+      <c r="H30" s="1">
+        <v>0.5</v>
       </c>
       <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
+      <c r="J30" s="1">
+        <v>1.5</v>
+      </c>
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1" t="s">
@@ -2552,7 +2552,7 @@
       <c r="AB30" s="1"/>
       <c r="AC30" s="1"/>
     </row>
-    <row r="31" spans="1:29" ht="15.75" customHeight="1">
+    <row r="31" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
       <c r="B31" s="1">
         <v>26</v>
@@ -2568,7 +2568,7 @@
         <v>140</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H31" s="1">
         <v>1</v>
@@ -2597,7 +2597,7 @@
       <c r="AB31" s="1"/>
       <c r="AC31" s="1"/>
     </row>
-    <row r="32" spans="1:29" ht="15.75" customHeight="1">
+    <row r="32" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -2628,7 +2628,7 @@
       <c r="AB32" s="1"/>
       <c r="AC32" s="1"/>
     </row>
-    <row r="33" spans="1:29" ht="15.75" customHeight="1">
+    <row r="33" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -2659,7 +2659,7 @@
       <c r="AB33" s="1"/>
       <c r="AC33" s="1"/>
     </row>
-    <row r="34" spans="1:29" ht="15.75" customHeight="1">
+    <row r="34" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -2690,7 +2690,7 @@
       <c r="AB34" s="1"/>
       <c r="AC34" s="1"/>
     </row>
-    <row r="35" spans="1:29" ht="15.75" customHeight="1">
+    <row r="35" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -2721,7 +2721,7 @@
       <c r="AB35" s="1"/>
       <c r="AC35" s="1"/>
     </row>
-    <row r="36" spans="1:29" ht="15.75" customHeight="1">
+    <row r="36" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -2752,7 +2752,7 @@
       <c r="AB36" s="1"/>
       <c r="AC36" s="1"/>
     </row>
-    <row r="37" spans="1:29" ht="15.75" customHeight="1">
+    <row r="37" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -2783,7 +2783,7 @@
       <c r="AB37" s="1"/>
       <c r="AC37" s="1"/>
     </row>
-    <row r="38" spans="1:29" ht="15.75" customHeight="1">
+    <row r="38" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -2814,7 +2814,7 @@
       <c r="AB38" s="1"/>
       <c r="AC38" s="1"/>
     </row>
-    <row r="39" spans="1:29" ht="15.75" customHeight="1">
+    <row r="39" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -2845,7 +2845,7 @@
       <c r="AB39" s="1"/>
       <c r="AC39" s="1"/>
     </row>
-    <row r="40" spans="1:29" ht="15.75" customHeight="1">
+    <row r="40" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -2876,7 +2876,7 @@
       <c r="AB40" s="1"/>
       <c r="AC40" s="1"/>
     </row>
-    <row r="41" spans="1:29" ht="15.75" customHeight="1">
+    <row r="41" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -2907,7 +2907,7 @@
       <c r="AB41" s="1"/>
       <c r="AC41" s="1"/>
     </row>
-    <row r="42" spans="1:29" ht="15.75" customHeight="1">
+    <row r="42" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -2938,7 +2938,7 @@
       <c r="AB42" s="1"/>
       <c r="AC42" s="1"/>
     </row>
-    <row r="43" spans="1:29" ht="15.75" customHeight="1">
+    <row r="43" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -2969,7 +2969,7 @@
       <c r="AB43" s="1"/>
       <c r="AC43" s="1"/>
     </row>
-    <row r="44" spans="1:29" ht="15.75" customHeight="1">
+    <row r="44" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -3000,7 +3000,7 @@
       <c r="AB44" s="1"/>
       <c r="AC44" s="1"/>
     </row>
-    <row r="45" spans="1:29" ht="15.75" customHeight="1">
+    <row r="45" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -3031,7 +3031,7 @@
       <c r="AB45" s="1"/>
       <c r="AC45" s="1"/>
     </row>
-    <row r="46" spans="1:29" ht="15.75" customHeight="1">
+    <row r="46" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -3062,7 +3062,7 @@
       <c r="AB46" s="1"/>
       <c r="AC46" s="1"/>
     </row>
-    <row r="47" spans="1:29" ht="15.75" customHeight="1">
+    <row r="47" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -3093,7 +3093,7 @@
       <c r="AB47" s="1"/>
       <c r="AC47" s="1"/>
     </row>
-    <row r="48" spans="1:29" ht="15.75" customHeight="1">
+    <row r="48" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -3124,7 +3124,7 @@
       <c r="AB48" s="1"/>
       <c r="AC48" s="1"/>
     </row>
-    <row r="49" spans="1:29" ht="15.75" customHeight="1">
+    <row r="49" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -3155,7 +3155,7 @@
       <c r="AB49" s="1"/>
       <c r="AC49" s="1"/>
     </row>
-    <row r="50" spans="1:29" ht="15.75" customHeight="1">
+    <row r="50" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -3186,7 +3186,7 @@
       <c r="AB50" s="1"/>
       <c r="AC50" s="1"/>
     </row>
-    <row r="51" spans="1:29" ht="15.75" customHeight="1">
+    <row r="51" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -3217,7 +3217,7 @@
       <c r="AB51" s="1"/>
       <c r="AC51" s="1"/>
     </row>
-    <row r="52" spans="1:29" ht="15.75" customHeight="1">
+    <row r="52" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -3248,7 +3248,7 @@
       <c r="AB52" s="1"/>
       <c r="AC52" s="1"/>
     </row>
-    <row r="53" spans="1:29" ht="15.75" customHeight="1">
+    <row r="53" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -3279,7 +3279,7 @@
       <c r="AB53" s="1"/>
       <c r="AC53" s="1"/>
     </row>
-    <row r="54" spans="1:29" ht="15.75" customHeight="1">
+    <row r="54" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -3310,7 +3310,7 @@
       <c r="AB54" s="1"/>
       <c r="AC54" s="1"/>
     </row>
-    <row r="55" spans="1:29" ht="15.75" customHeight="1">
+    <row r="55" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -3341,7 +3341,7 @@
       <c r="AB55" s="1"/>
       <c r="AC55" s="1"/>
     </row>
-    <row r="56" spans="1:29" ht="15.75" customHeight="1">
+    <row r="56" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -3372,7 +3372,7 @@
       <c r="AB56" s="1"/>
       <c r="AC56" s="1"/>
     </row>
-    <row r="57" spans="1:29" ht="15.75" customHeight="1">
+    <row r="57" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -3403,7 +3403,7 @@
       <c r="AB57" s="1"/>
       <c r="AC57" s="1"/>
     </row>
-    <row r="58" spans="1:29" ht="15.75" customHeight="1">
+    <row r="58" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -3434,7 +3434,7 @@
       <c r="AB58" s="1"/>
       <c r="AC58" s="1"/>
     </row>
-    <row r="59" spans="1:29" ht="15.75" customHeight="1">
+    <row r="59" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -3465,7 +3465,7 @@
       <c r="AB59" s="1"/>
       <c r="AC59" s="1"/>
     </row>
-    <row r="60" spans="1:29" ht="15.75" customHeight="1">
+    <row r="60" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -3496,7 +3496,7 @@
       <c r="AB60" s="1"/>
       <c r="AC60" s="1"/>
     </row>
-    <row r="61" spans="1:29" ht="15.75" customHeight="1">
+    <row r="61" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -3527,7 +3527,7 @@
       <c r="AB61" s="1"/>
       <c r="AC61" s="1"/>
     </row>
-    <row r="62" spans="1:29" ht="15.75" customHeight="1">
+    <row r="62" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -3558,7 +3558,7 @@
       <c r="AB62" s="1"/>
       <c r="AC62" s="1"/>
     </row>
-    <row r="63" spans="1:29" ht="15.75" customHeight="1">
+    <row r="63" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -3589,7 +3589,7 @@
       <c r="AB63" s="1"/>
       <c r="AC63" s="1"/>
     </row>
-    <row r="64" spans="1:29" ht="13.2">
+    <row r="64" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -3620,7 +3620,7 @@
       <c r="AB64" s="1"/>
       <c r="AC64" s="1"/>
     </row>
-    <row r="65" spans="1:29" ht="13.2">
+    <row r="65" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -3651,7 +3651,7 @@
       <c r="AB65" s="1"/>
       <c r="AC65" s="1"/>
     </row>
-    <row r="66" spans="1:29" ht="13.2">
+    <row r="66" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -3682,7 +3682,7 @@
       <c r="AB66" s="1"/>
       <c r="AC66" s="1"/>
     </row>
-    <row r="67" spans="1:29" ht="13.2">
+    <row r="67" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -3713,7 +3713,7 @@
       <c r="AB67" s="1"/>
       <c r="AC67" s="1"/>
     </row>
-    <row r="68" spans="1:29" ht="13.2">
+    <row r="68" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -3744,7 +3744,7 @@
       <c r="AB68" s="1"/>
       <c r="AC68" s="1"/>
     </row>
-    <row r="69" spans="1:29" ht="13.2">
+    <row r="69" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -3775,7 +3775,7 @@
       <c r="AB69" s="1"/>
       <c r="AC69" s="1"/>
     </row>
-    <row r="70" spans="1:29" ht="13.2">
+    <row r="70" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -3806,7 +3806,7 @@
       <c r="AB70" s="1"/>
       <c r="AC70" s="1"/>
     </row>
-    <row r="71" spans="1:29" ht="13.2">
+    <row r="71" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -3837,7 +3837,7 @@
       <c r="AB71" s="1"/>
       <c r="AC71" s="1"/>
     </row>
-    <row r="72" spans="1:29" ht="13.2">
+    <row r="72" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -3868,7 +3868,7 @@
       <c r="AB72" s="1"/>
       <c r="AC72" s="1"/>
     </row>
-    <row r="73" spans="1:29" ht="13.2">
+    <row r="73" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -3899,7 +3899,7 @@
       <c r="AB73" s="1"/>
       <c r="AC73" s="1"/>
     </row>
-    <row r="74" spans="1:29" ht="13.2">
+    <row r="74" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -3930,7 +3930,7 @@
       <c r="AB74" s="1"/>
       <c r="AC74" s="1"/>
     </row>
-    <row r="75" spans="1:29" ht="13.2">
+    <row r="75" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -3961,7 +3961,7 @@
       <c r="AB75" s="1"/>
       <c r="AC75" s="1"/>
     </row>
-    <row r="76" spans="1:29" ht="13.2">
+    <row r="76" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -3992,7 +3992,7 @@
       <c r="AB76" s="1"/>
       <c r="AC76" s="1"/>
     </row>
-    <row r="77" spans="1:29" ht="13.2">
+    <row r="77" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -4023,7 +4023,7 @@
       <c r="AB77" s="1"/>
       <c r="AC77" s="1"/>
     </row>
-    <row r="78" spans="1:29" ht="13.2">
+    <row r="78" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -4054,7 +4054,7 @@
       <c r="AB78" s="1"/>
       <c r="AC78" s="1"/>
     </row>
-    <row r="79" spans="1:29" ht="13.2">
+    <row r="79" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -4085,7 +4085,7 @@
       <c r="AB79" s="1"/>
       <c r="AC79" s="1"/>
     </row>
-    <row r="80" spans="1:29" ht="13.2">
+    <row r="80" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -4116,7 +4116,7 @@
       <c r="AB80" s="1"/>
       <c r="AC80" s="1"/>
     </row>
-    <row r="81" spans="1:29" ht="13.2">
+    <row r="81" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -4147,7 +4147,7 @@
       <c r="AB81" s="1"/>
       <c r="AC81" s="1"/>
     </row>
-    <row r="82" spans="1:29" ht="13.2">
+    <row r="82" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -4178,7 +4178,7 @@
       <c r="AB82" s="1"/>
       <c r="AC82" s="1"/>
     </row>
-    <row r="83" spans="1:29" ht="13.2">
+    <row r="83" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -4209,7 +4209,7 @@
       <c r="AB83" s="1"/>
       <c r="AC83" s="1"/>
     </row>
-    <row r="84" spans="1:29" ht="13.2">
+    <row r="84" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -4240,7 +4240,7 @@
       <c r="AB84" s="1"/>
       <c r="AC84" s="1"/>
     </row>
-    <row r="85" spans="1:29" ht="13.2">
+    <row r="85" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -4271,7 +4271,7 @@
       <c r="AB85" s="1"/>
       <c r="AC85" s="1"/>
     </row>
-    <row r="86" spans="1:29" ht="13.2">
+    <row r="86" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -4302,7 +4302,7 @@
       <c r="AB86" s="1"/>
       <c r="AC86" s="1"/>
     </row>
-    <row r="87" spans="1:29" ht="13.2">
+    <row r="87" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -4333,7 +4333,7 @@
       <c r="AB87" s="1"/>
       <c r="AC87" s="1"/>
     </row>
-    <row r="88" spans="1:29" ht="13.2">
+    <row r="88" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -4364,7 +4364,7 @@
       <c r="AB88" s="1"/>
       <c r="AC88" s="1"/>
     </row>
-    <row r="89" spans="1:29" ht="13.2">
+    <row r="89" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -4395,7 +4395,7 @@
       <c r="AB89" s="1"/>
       <c r="AC89" s="1"/>
     </row>
-    <row r="90" spans="1:29" ht="13.2">
+    <row r="90" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -4426,7 +4426,7 @@
       <c r="AB90" s="1"/>
       <c r="AC90" s="1"/>
     </row>
-    <row r="91" spans="1:29" ht="13.2">
+    <row r="91" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -4457,7 +4457,7 @@
       <c r="AB91" s="1"/>
       <c r="AC91" s="1"/>
     </row>
-    <row r="92" spans="1:29" ht="13.2">
+    <row r="92" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -4488,7 +4488,7 @@
       <c r="AB92" s="1"/>
       <c r="AC92" s="1"/>
     </row>
-    <row r="93" spans="1:29" ht="13.2">
+    <row r="93" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -4519,7 +4519,7 @@
       <c r="AB93" s="1"/>
       <c r="AC93" s="1"/>
     </row>
-    <row r="94" spans="1:29" ht="13.2">
+    <row r="94" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -4550,7 +4550,7 @@
       <c r="AB94" s="1"/>
       <c r="AC94" s="1"/>
     </row>
-    <row r="95" spans="1:29" ht="13.2">
+    <row r="95" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -4581,7 +4581,7 @@
       <c r="AB95" s="1"/>
       <c r="AC95" s="1"/>
     </row>
-    <row r="96" spans="1:29" ht="13.2">
+    <row r="96" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -4612,7 +4612,7 @@
       <c r="AB96" s="1"/>
       <c r="AC96" s="1"/>
     </row>
-    <row r="97" spans="1:29" ht="13.2">
+    <row r="97" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -4643,7 +4643,7 @@
       <c r="AB97" s="1"/>
       <c r="AC97" s="1"/>
     </row>
-    <row r="98" spans="1:29" ht="13.2">
+    <row r="98" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -4674,7 +4674,7 @@
       <c r="AB98" s="1"/>
       <c r="AC98" s="1"/>
     </row>
-    <row r="99" spans="1:29" ht="13.2">
+    <row r="99" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -4705,7 +4705,7 @@
       <c r="AB99" s="1"/>
       <c r="AC99" s="1"/>
     </row>
-    <row r="100" spans="1:29" ht="13.2">
+    <row r="100" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -4736,7 +4736,7 @@
       <c r="AB100" s="1"/>
       <c r="AC100" s="1"/>
     </row>
-    <row r="101" spans="1:29" ht="13.2">
+    <row r="101" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -4767,7 +4767,7 @@
       <c r="AB101" s="1"/>
       <c r="AC101" s="1"/>
     </row>
-    <row r="102" spans="1:29" ht="13.2">
+    <row r="102" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -4798,7 +4798,7 @@
       <c r="AB102" s="1"/>
       <c r="AC102" s="1"/>
     </row>
-    <row r="103" spans="1:29" ht="13.2">
+    <row r="103" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -4829,7 +4829,7 @@
       <c r="AB103" s="1"/>
       <c r="AC103" s="1"/>
     </row>
-    <row r="104" spans="1:29" ht="13.2">
+    <row r="104" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -4860,7 +4860,7 @@
       <c r="AB104" s="1"/>
       <c r="AC104" s="1"/>
     </row>
-    <row r="105" spans="1:29" ht="13.2">
+    <row r="105" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -4891,7 +4891,7 @@
       <c r="AB105" s="1"/>
       <c r="AC105" s="1"/>
     </row>
-    <row r="106" spans="1:29" ht="13.2">
+    <row r="106" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -4922,7 +4922,7 @@
       <c r="AB106" s="1"/>
       <c r="AC106" s="1"/>
     </row>
-    <row r="107" spans="1:29" ht="13.2">
+    <row r="107" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -4953,7 +4953,7 @@
       <c r="AB107" s="1"/>
       <c r="AC107" s="1"/>
     </row>
-    <row r="108" spans="1:29" ht="13.2">
+    <row r="108" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -4984,7 +4984,7 @@
       <c r="AB108" s="1"/>
       <c r="AC108" s="1"/>
     </row>
-    <row r="109" spans="1:29" ht="13.2">
+    <row r="109" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -5015,7 +5015,7 @@
       <c r="AB109" s="1"/>
       <c r="AC109" s="1"/>
     </row>
-    <row r="110" spans="1:29" ht="13.2">
+    <row r="110" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -5046,7 +5046,7 @@
       <c r="AB110" s="1"/>
       <c r="AC110" s="1"/>
     </row>
-    <row r="111" spans="1:29" ht="13.2">
+    <row r="111" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -5077,7 +5077,7 @@
       <c r="AB111" s="1"/>
       <c r="AC111" s="1"/>
     </row>
-    <row r="112" spans="1:29" ht="13.2">
+    <row r="112" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -5108,7 +5108,7 @@
       <c r="AB112" s="1"/>
       <c r="AC112" s="1"/>
     </row>
-    <row r="113" spans="1:29" ht="13.2">
+    <row r="113" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -5139,7 +5139,7 @@
       <c r="AB113" s="1"/>
       <c r="AC113" s="1"/>
     </row>
-    <row r="114" spans="1:29" ht="13.2">
+    <row r="114" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -5170,7 +5170,7 @@
       <c r="AB114" s="1"/>
       <c r="AC114" s="1"/>
     </row>
-    <row r="115" spans="1:29" ht="13.2">
+    <row r="115" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -5201,7 +5201,7 @@
       <c r="AB115" s="1"/>
       <c r="AC115" s="1"/>
     </row>
-    <row r="116" spans="1:29" ht="13.2">
+    <row r="116" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -5232,7 +5232,7 @@
       <c r="AB116" s="1"/>
       <c r="AC116" s="1"/>
     </row>
-    <row r="117" spans="1:29" ht="13.2">
+    <row r="117" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -5263,7 +5263,7 @@
       <c r="AB117" s="1"/>
       <c r="AC117" s="1"/>
     </row>
-    <row r="118" spans="1:29" ht="13.2">
+    <row r="118" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -5294,7 +5294,7 @@
       <c r="AB118" s="1"/>
       <c r="AC118" s="1"/>
     </row>
-    <row r="119" spans="1:29" ht="13.2">
+    <row r="119" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -5325,7 +5325,7 @@
       <c r="AB119" s="1"/>
       <c r="AC119" s="1"/>
     </row>
-    <row r="120" spans="1:29" ht="13.2">
+    <row r="120" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -5356,7 +5356,7 @@
       <c r="AB120" s="1"/>
       <c r="AC120" s="1"/>
     </row>
-    <row r="121" spans="1:29" ht="13.2">
+    <row r="121" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -5387,7 +5387,7 @@
       <c r="AB121" s="1"/>
       <c r="AC121" s="1"/>
     </row>
-    <row r="122" spans="1:29" ht="13.2">
+    <row r="122" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -5418,7 +5418,7 @@
       <c r="AB122" s="1"/>
       <c r="AC122" s="1"/>
     </row>
-    <row r="123" spans="1:29" ht="13.2">
+    <row r="123" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -5449,7 +5449,7 @@
       <c r="AB123" s="1"/>
       <c r="AC123" s="1"/>
     </row>
-    <row r="124" spans="1:29" ht="13.2">
+    <row r="124" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -5480,7 +5480,7 @@
       <c r="AB124" s="1"/>
       <c r="AC124" s="1"/>
     </row>
-    <row r="125" spans="1:29" ht="13.2">
+    <row r="125" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -5511,7 +5511,7 @@
       <c r="AB125" s="1"/>
       <c r="AC125" s="1"/>
     </row>
-    <row r="126" spans="1:29" ht="13.2">
+    <row r="126" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -5542,7 +5542,7 @@
       <c r="AB126" s="1"/>
       <c r="AC126" s="1"/>
     </row>
-    <row r="127" spans="1:29" ht="13.2">
+    <row r="127" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -5573,7 +5573,7 @@
       <c r="AB127" s="1"/>
       <c r="AC127" s="1"/>
     </row>
-    <row r="128" spans="1:29" ht="13.2">
+    <row r="128" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -5604,7 +5604,7 @@
       <c r="AB128" s="1"/>
       <c r="AC128" s="1"/>
     </row>
-    <row r="129" spans="1:29" ht="13.2">
+    <row r="129" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -5635,7 +5635,7 @@
       <c r="AB129" s="1"/>
       <c r="AC129" s="1"/>
     </row>
-    <row r="130" spans="1:29" ht="13.2">
+    <row r="130" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -5666,7 +5666,7 @@
       <c r="AB130" s="1"/>
       <c r="AC130" s="1"/>
     </row>
-    <row r="131" spans="1:29" ht="13.2">
+    <row r="131" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -5697,7 +5697,7 @@
       <c r="AB131" s="1"/>
       <c r="AC131" s="1"/>
     </row>
-    <row r="132" spans="1:29" ht="13.2">
+    <row r="132" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -5728,7 +5728,7 @@
       <c r="AB132" s="1"/>
       <c r="AC132" s="1"/>
     </row>
-    <row r="133" spans="1:29" ht="13.2">
+    <row r="133" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -5759,7 +5759,7 @@
       <c r="AB133" s="1"/>
       <c r="AC133" s="1"/>
     </row>
-    <row r="134" spans="1:29" ht="13.2">
+    <row r="134" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -5790,7 +5790,7 @@
       <c r="AB134" s="1"/>
       <c r="AC134" s="1"/>
     </row>
-    <row r="135" spans="1:29" ht="13.2">
+    <row r="135" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -5821,7 +5821,7 @@
       <c r="AB135" s="1"/>
       <c r="AC135" s="1"/>
     </row>
-    <row r="136" spans="1:29" ht="13.2">
+    <row r="136" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -5852,7 +5852,7 @@
       <c r="AB136" s="1"/>
       <c r="AC136" s="1"/>
     </row>
-    <row r="137" spans="1:29" ht="13.2">
+    <row r="137" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -5883,7 +5883,7 @@
       <c r="AB137" s="1"/>
       <c r="AC137" s="1"/>
     </row>
-    <row r="138" spans="1:29" ht="13.2">
+    <row r="138" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -5914,7 +5914,7 @@
       <c r="AB138" s="1"/>
       <c r="AC138" s="1"/>
     </row>
-    <row r="139" spans="1:29" ht="13.2">
+    <row r="139" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -5945,7 +5945,7 @@
       <c r="AB139" s="1"/>
       <c r="AC139" s="1"/>
     </row>
-    <row r="140" spans="1:29" ht="13.2">
+    <row r="140" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -5976,7 +5976,7 @@
       <c r="AB140" s="1"/>
       <c r="AC140" s="1"/>
     </row>
-    <row r="141" spans="1:29" ht="13.2">
+    <row r="141" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -6007,7 +6007,7 @@
       <c r="AB141" s="1"/>
       <c r="AC141" s="1"/>
     </row>
-    <row r="142" spans="1:29" ht="13.2">
+    <row r="142" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -6038,7 +6038,7 @@
       <c r="AB142" s="1"/>
       <c r="AC142" s="1"/>
     </row>
-    <row r="143" spans="1:29" ht="13.2">
+    <row r="143" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -6069,7 +6069,7 @@
       <c r="AB143" s="1"/>
       <c r="AC143" s="1"/>
     </row>
-    <row r="144" spans="1:29" ht="13.2">
+    <row r="144" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -6100,7 +6100,7 @@
       <c r="AB144" s="1"/>
       <c r="AC144" s="1"/>
     </row>
-    <row r="145" spans="1:29" ht="13.2">
+    <row r="145" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -6131,7 +6131,7 @@
       <c r="AB145" s="1"/>
       <c r="AC145" s="1"/>
     </row>
-    <row r="146" spans="1:29" ht="13.2">
+    <row r="146" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -6162,7 +6162,7 @@
       <c r="AB146" s="1"/>
       <c r="AC146" s="1"/>
     </row>
-    <row r="147" spans="1:29" ht="13.2">
+    <row r="147" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -6193,7 +6193,7 @@
       <c r="AB147" s="1"/>
       <c r="AC147" s="1"/>
     </row>
-    <row r="148" spans="1:29" ht="13.2">
+    <row r="148" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -6224,7 +6224,7 @@
       <c r="AB148" s="1"/>
       <c r="AC148" s="1"/>
     </row>
-    <row r="149" spans="1:29" ht="13.2">
+    <row r="149" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -6255,7 +6255,7 @@
       <c r="AB149" s="1"/>
       <c r="AC149" s="1"/>
     </row>
-    <row r="150" spans="1:29" ht="13.2">
+    <row r="150" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -6286,7 +6286,7 @@
       <c r="AB150" s="1"/>
       <c r="AC150" s="1"/>
     </row>
-    <row r="151" spans="1:29" ht="13.2">
+    <row r="151" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -6317,7 +6317,7 @@
       <c r="AB151" s="1"/>
       <c r="AC151" s="1"/>
     </row>
-    <row r="152" spans="1:29" ht="13.2">
+    <row r="152" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -6348,7 +6348,7 @@
       <c r="AB152" s="1"/>
       <c r="AC152" s="1"/>
     </row>
-    <row r="153" spans="1:29" ht="13.2">
+    <row r="153" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -6379,7 +6379,7 @@
       <c r="AB153" s="1"/>
       <c r="AC153" s="1"/>
     </row>
-    <row r="154" spans="1:29" ht="13.2">
+    <row r="154" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -6410,7 +6410,7 @@
       <c r="AB154" s="1"/>
       <c r="AC154" s="1"/>
     </row>
-    <row r="155" spans="1:29" ht="13.2">
+    <row r="155" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -6441,7 +6441,7 @@
       <c r="AB155" s="1"/>
       <c r="AC155" s="1"/>
     </row>
-    <row r="156" spans="1:29" ht="13.2">
+    <row r="156" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -6472,7 +6472,7 @@
       <c r="AB156" s="1"/>
       <c r="AC156" s="1"/>
     </row>
-    <row r="157" spans="1:29" ht="13.2">
+    <row r="157" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -6503,7 +6503,7 @@
       <c r="AB157" s="1"/>
       <c r="AC157" s="1"/>
     </row>
-    <row r="158" spans="1:29" ht="13.2">
+    <row r="158" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -6534,7 +6534,7 @@
       <c r="AB158" s="1"/>
       <c r="AC158" s="1"/>
     </row>
-    <row r="159" spans="1:29" ht="13.2">
+    <row r="159" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -6565,7 +6565,7 @@
       <c r="AB159" s="1"/>
       <c r="AC159" s="1"/>
     </row>
-    <row r="160" spans="1:29" ht="13.2">
+    <row r="160" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -6596,7 +6596,7 @@
       <c r="AB160" s="1"/>
       <c r="AC160" s="1"/>
     </row>
-    <row r="161" spans="1:29" ht="13.2">
+    <row r="161" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -6627,7 +6627,7 @@
       <c r="AB161" s="1"/>
       <c r="AC161" s="1"/>
     </row>
-    <row r="162" spans="1:29" ht="13.2">
+    <row r="162" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -6658,7 +6658,7 @@
       <c r="AB162" s="1"/>
       <c r="AC162" s="1"/>
     </row>
-    <row r="163" spans="1:29" ht="13.2">
+    <row r="163" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -6689,7 +6689,7 @@
       <c r="AB163" s="1"/>
       <c r="AC163" s="1"/>
     </row>
-    <row r="164" spans="1:29" ht="13.2">
+    <row r="164" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -6720,7 +6720,7 @@
       <c r="AB164" s="1"/>
       <c r="AC164" s="1"/>
     </row>
-    <row r="165" spans="1:29" ht="13.2">
+    <row r="165" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -6751,7 +6751,7 @@
       <c r="AB165" s="1"/>
       <c r="AC165" s="1"/>
     </row>
-    <row r="166" spans="1:29" ht="13.2">
+    <row r="166" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -6782,7 +6782,7 @@
       <c r="AB166" s="1"/>
       <c r="AC166" s="1"/>
     </row>
-    <row r="167" spans="1:29" ht="13.2">
+    <row r="167" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -6813,7 +6813,7 @@
       <c r="AB167" s="1"/>
       <c r="AC167" s="1"/>
     </row>
-    <row r="168" spans="1:29" ht="13.2">
+    <row r="168" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -6844,7 +6844,7 @@
       <c r="AB168" s="1"/>
       <c r="AC168" s="1"/>
     </row>
-    <row r="169" spans="1:29" ht="13.2">
+    <row r="169" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -6875,7 +6875,7 @@
       <c r="AB169" s="1"/>
       <c r="AC169" s="1"/>
     </row>
-    <row r="170" spans="1:29" ht="13.2">
+    <row r="170" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -6906,7 +6906,7 @@
       <c r="AB170" s="1"/>
       <c r="AC170" s="1"/>
     </row>
-    <row r="171" spans="1:29" ht="13.2">
+    <row r="171" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -6937,7 +6937,7 @@
       <c r="AB171" s="1"/>
       <c r="AC171" s="1"/>
     </row>
-    <row r="172" spans="1:29" ht="13.2">
+    <row r="172" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -6968,7 +6968,7 @@
       <c r="AB172" s="1"/>
       <c r="AC172" s="1"/>
     </row>
-    <row r="173" spans="1:29" ht="13.2">
+    <row r="173" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -6999,7 +6999,7 @@
       <c r="AB173" s="1"/>
       <c r="AC173" s="1"/>
     </row>
-    <row r="174" spans="1:29" ht="13.2">
+    <row r="174" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -7030,7 +7030,7 @@
       <c r="AB174" s="1"/>
       <c r="AC174" s="1"/>
     </row>
-    <row r="175" spans="1:29" ht="13.2">
+    <row r="175" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -7061,7 +7061,7 @@
       <c r="AB175" s="1"/>
       <c r="AC175" s="1"/>
     </row>
-    <row r="176" spans="1:29" ht="13.2">
+    <row r="176" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -7092,7 +7092,7 @@
       <c r="AB176" s="1"/>
       <c r="AC176" s="1"/>
     </row>
-    <row r="177" spans="1:29" ht="13.2">
+    <row r="177" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -7123,7 +7123,7 @@
       <c r="AB177" s="1"/>
       <c r="AC177" s="1"/>
     </row>
-    <row r="178" spans="1:29" ht="13.2">
+    <row r="178" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -7154,7 +7154,7 @@
       <c r="AB178" s="1"/>
       <c r="AC178" s="1"/>
     </row>
-    <row r="179" spans="1:29" ht="13.2">
+    <row r="179" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -7185,7 +7185,7 @@
       <c r="AB179" s="1"/>
       <c r="AC179" s="1"/>
     </row>
-    <row r="180" spans="1:29" ht="13.2">
+    <row r="180" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -7216,7 +7216,7 @@
       <c r="AB180" s="1"/>
       <c r="AC180" s="1"/>
     </row>
-    <row r="181" spans="1:29" ht="13.2">
+    <row r="181" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -7247,7 +7247,7 @@
       <c r="AB181" s="1"/>
       <c r="AC181" s="1"/>
     </row>
-    <row r="182" spans="1:29" ht="13.2">
+    <row r="182" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -7278,7 +7278,7 @@
       <c r="AB182" s="1"/>
       <c r="AC182" s="1"/>
     </row>
-    <row r="183" spans="1:29" ht="13.2">
+    <row r="183" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -7309,7 +7309,7 @@
       <c r="AB183" s="1"/>
       <c r="AC183" s="1"/>
     </row>
-    <row r="184" spans="1:29" ht="13.2">
+    <row r="184" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -7340,7 +7340,7 @@
       <c r="AB184" s="1"/>
       <c r="AC184" s="1"/>
     </row>
-    <row r="185" spans="1:29" ht="13.2">
+    <row r="185" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -7371,7 +7371,7 @@
       <c r="AB185" s="1"/>
       <c r="AC185" s="1"/>
     </row>
-    <row r="186" spans="1:29" ht="13.2">
+    <row r="186" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -7402,7 +7402,7 @@
       <c r="AB186" s="1"/>
       <c r="AC186" s="1"/>
     </row>
-    <row r="187" spans="1:29" ht="13.2">
+    <row r="187" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -7433,7 +7433,7 @@
       <c r="AB187" s="1"/>
       <c r="AC187" s="1"/>
     </row>
-    <row r="188" spans="1:29" ht="13.2">
+    <row r="188" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -7464,7 +7464,7 @@
       <c r="AB188" s="1"/>
       <c r="AC188" s="1"/>
     </row>
-    <row r="189" spans="1:29" ht="13.2">
+    <row r="189" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -7495,7 +7495,7 @@
       <c r="AB189" s="1"/>
       <c r="AC189" s="1"/>
     </row>
-    <row r="190" spans="1:29" ht="13.2">
+    <row r="190" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -7526,7 +7526,7 @@
       <c r="AB190" s="1"/>
       <c r="AC190" s="1"/>
     </row>
-    <row r="191" spans="1:29" ht="13.2">
+    <row r="191" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -7557,7 +7557,7 @@
       <c r="AB191" s="1"/>
       <c r="AC191" s="1"/>
     </row>
-    <row r="192" spans="1:29" ht="13.2">
+    <row r="192" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -7588,7 +7588,7 @@
       <c r="AB192" s="1"/>
       <c r="AC192" s="1"/>
     </row>
-    <row r="193" spans="1:29" ht="13.2">
+    <row r="193" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -7619,7 +7619,7 @@
       <c r="AB193" s="1"/>
       <c r="AC193" s="1"/>
     </row>
-    <row r="194" spans="1:29" ht="13.2">
+    <row r="194" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -7650,7 +7650,7 @@
       <c r="AB194" s="1"/>
       <c r="AC194" s="1"/>
     </row>
-    <row r="195" spans="1:29" ht="13.2">
+    <row r="195" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -7681,7 +7681,7 @@
       <c r="AB195" s="1"/>
       <c r="AC195" s="1"/>
     </row>
-    <row r="196" spans="1:29" ht="13.2">
+    <row r="196" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
@@ -7712,7 +7712,7 @@
       <c r="AB196" s="1"/>
       <c r="AC196" s="1"/>
     </row>
-    <row r="197" spans="1:29" ht="13.2">
+    <row r="197" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
@@ -7743,7 +7743,7 @@
       <c r="AB197" s="1"/>
       <c r="AC197" s="1"/>
     </row>
-    <row r="198" spans="1:29" ht="13.2">
+    <row r="198" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
@@ -7774,7 +7774,7 @@
       <c r="AB198" s="1"/>
       <c r="AC198" s="1"/>
     </row>
-    <row r="199" spans="1:29" ht="13.2">
+    <row r="199" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
@@ -7805,7 +7805,7 @@
       <c r="AB199" s="1"/>
       <c r="AC199" s="1"/>
     </row>
-    <row r="200" spans="1:29" ht="13.2">
+    <row r="200" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
@@ -7836,7 +7836,7 @@
       <c r="AB200" s="1"/>
       <c r="AC200" s="1"/>
     </row>
-    <row r="201" spans="1:29" ht="13.2">
+    <row r="201" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
@@ -7867,7 +7867,7 @@
       <c r="AB201" s="1"/>
       <c r="AC201" s="1"/>
     </row>
-    <row r="202" spans="1:29" ht="13.2">
+    <row r="202" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
@@ -7898,7 +7898,7 @@
       <c r="AB202" s="1"/>
       <c r="AC202" s="1"/>
     </row>
-    <row r="203" spans="1:29" ht="13.2">
+    <row r="203" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
@@ -7929,7 +7929,7 @@
       <c r="AB203" s="1"/>
       <c r="AC203" s="1"/>
     </row>
-    <row r="204" spans="1:29" ht="13.2">
+    <row r="204" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
@@ -7960,7 +7960,7 @@
       <c r="AB204" s="1"/>
       <c r="AC204" s="1"/>
     </row>
-    <row r="205" spans="1:29" ht="13.2">
+    <row r="205" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
@@ -7991,7 +7991,7 @@
       <c r="AB205" s="1"/>
       <c r="AC205" s="1"/>
     </row>
-    <row r="206" spans="1:29" ht="13.2">
+    <row r="206" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
@@ -8022,7 +8022,7 @@
       <c r="AB206" s="1"/>
       <c r="AC206" s="1"/>
     </row>
-    <row r="207" spans="1:29" ht="13.2">
+    <row r="207" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
@@ -8053,7 +8053,7 @@
       <c r="AB207" s="1"/>
       <c r="AC207" s="1"/>
     </row>
-    <row r="208" spans="1:29" ht="13.2">
+    <row r="208" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
@@ -8084,7 +8084,7 @@
       <c r="AB208" s="1"/>
       <c r="AC208" s="1"/>
     </row>
-    <row r="209" spans="1:29" ht="13.2">
+    <row r="209" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
@@ -8115,7 +8115,7 @@
       <c r="AB209" s="1"/>
       <c r="AC209" s="1"/>
     </row>
-    <row r="210" spans="1:29" ht="13.2">
+    <row r="210" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
@@ -8146,7 +8146,7 @@
       <c r="AB210" s="1"/>
       <c r="AC210" s="1"/>
     </row>
-    <row r="211" spans="1:29" ht="13.2">
+    <row r="211" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
@@ -8177,7 +8177,7 @@
       <c r="AB211" s="1"/>
       <c r="AC211" s="1"/>
     </row>
-    <row r="212" spans="1:29" ht="13.2">
+    <row r="212" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
@@ -8208,7 +8208,7 @@
       <c r="AB212" s="1"/>
       <c r="AC212" s="1"/>
     </row>
-    <row r="213" spans="1:29" ht="13.2">
+    <row r="213" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
@@ -8239,7 +8239,7 @@
       <c r="AB213" s="1"/>
       <c r="AC213" s="1"/>
     </row>
-    <row r="214" spans="1:29" ht="13.2">
+    <row r="214" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
@@ -8270,7 +8270,7 @@
       <c r="AB214" s="1"/>
       <c r="AC214" s="1"/>
     </row>
-    <row r="215" spans="1:29" ht="13.2">
+    <row r="215" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
@@ -8301,7 +8301,7 @@
       <c r="AB215" s="1"/>
       <c r="AC215" s="1"/>
     </row>
-    <row r="216" spans="1:29" ht="13.2">
+    <row r="216" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
@@ -8332,7 +8332,7 @@
       <c r="AB216" s="1"/>
       <c r="AC216" s="1"/>
     </row>
-    <row r="217" spans="1:29" ht="13.2">
+    <row r="217" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
@@ -8363,7 +8363,7 @@
       <c r="AB217" s="1"/>
       <c r="AC217" s="1"/>
     </row>
-    <row r="218" spans="1:29" ht="13.2">
+    <row r="218" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
@@ -8394,7 +8394,7 @@
       <c r="AB218" s="1"/>
       <c r="AC218" s="1"/>
     </row>
-    <row r="219" spans="1:29" ht="13.2">
+    <row r="219" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
@@ -8425,7 +8425,7 @@
       <c r="AB219" s="1"/>
       <c r="AC219" s="1"/>
     </row>
-    <row r="220" spans="1:29" ht="13.2">
+    <row r="220" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
@@ -8456,7 +8456,7 @@
       <c r="AB220" s="1"/>
       <c r="AC220" s="1"/>
     </row>
-    <row r="221" spans="1:29" ht="13.2">
+    <row r="221" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="C221" s="1"/>
@@ -8487,7 +8487,7 @@
       <c r="AB221" s="1"/>
       <c r="AC221" s="1"/>
     </row>
-    <row r="222" spans="1:29" ht="13.2">
+    <row r="222" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
       <c r="C222" s="1"/>
@@ -8518,7 +8518,7 @@
       <c r="AB222" s="1"/>
       <c r="AC222" s="1"/>
     </row>
-    <row r="223" spans="1:29" ht="13.2">
+    <row r="223" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="C223" s="1"/>
@@ -8549,7 +8549,7 @@
       <c r="AB223" s="1"/>
       <c r="AC223" s="1"/>
     </row>
-    <row r="224" spans="1:29" ht="13.2">
+    <row r="224" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
       <c r="C224" s="1"/>
@@ -8580,7 +8580,7 @@
       <c r="AB224" s="1"/>
       <c r="AC224" s="1"/>
     </row>
-    <row r="225" spans="1:29" ht="13.2">
+    <row r="225" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
@@ -8611,7 +8611,7 @@
       <c r="AB225" s="1"/>
       <c r="AC225" s="1"/>
     </row>
-    <row r="226" spans="1:29" ht="13.2">
+    <row r="226" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
@@ -8642,7 +8642,7 @@
       <c r="AB226" s="1"/>
       <c r="AC226" s="1"/>
     </row>
-    <row r="227" spans="1:29" ht="13.2">
+    <row r="227" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A227" s="1"/>
       <c r="B227" s="1"/>
       <c r="C227" s="1"/>
@@ -8673,7 +8673,7 @@
       <c r="AB227" s="1"/>
       <c r="AC227" s="1"/>
     </row>
-    <row r="228" spans="1:29" ht="13.2">
+    <row r="228" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
@@ -8704,7 +8704,7 @@
       <c r="AB228" s="1"/>
       <c r="AC228" s="1"/>
     </row>
-    <row r="229" spans="1:29" ht="13.2">
+    <row r="229" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A229" s="1"/>
       <c r="B229" s="1"/>
       <c r="C229" s="1"/>
@@ -8735,7 +8735,7 @@
       <c r="AB229" s="1"/>
       <c r="AC229" s="1"/>
     </row>
-    <row r="230" spans="1:29" ht="13.2">
+    <row r="230" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A230" s="1"/>
       <c r="B230" s="1"/>
       <c r="C230" s="1"/>
@@ -8766,7 +8766,7 @@
       <c r="AB230" s="1"/>
       <c r="AC230" s="1"/>
     </row>
-    <row r="231" spans="1:29" ht="13.2">
+    <row r="231" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A231" s="1"/>
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
@@ -8797,7 +8797,7 @@
       <c r="AB231" s="1"/>
       <c r="AC231" s="1"/>
     </row>
-    <row r="232" spans="1:29" ht="13.2">
+    <row r="232" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A232" s="1"/>
       <c r="B232" s="1"/>
       <c r="C232" s="1"/>
@@ -8828,7 +8828,7 @@
       <c r="AB232" s="1"/>
       <c r="AC232" s="1"/>
     </row>
-    <row r="233" spans="1:29" ht="13.2">
+    <row r="233" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A233" s="1"/>
       <c r="B233" s="1"/>
       <c r="C233" s="1"/>
@@ -8859,7 +8859,7 @@
       <c r="AB233" s="1"/>
       <c r="AC233" s="1"/>
     </row>
-    <row r="234" spans="1:29" ht="13.2">
+    <row r="234" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A234" s="1"/>
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
@@ -8890,7 +8890,7 @@
       <c r="AB234" s="1"/>
       <c r="AC234" s="1"/>
     </row>
-    <row r="235" spans="1:29" ht="13.2">
+    <row r="235" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A235" s="1"/>
       <c r="B235" s="1"/>
       <c r="C235" s="1"/>
@@ -8921,7 +8921,7 @@
       <c r="AB235" s="1"/>
       <c r="AC235" s="1"/>
     </row>
-    <row r="236" spans="1:29" ht="13.2">
+    <row r="236" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
@@ -8952,7 +8952,7 @@
       <c r="AB236" s="1"/>
       <c r="AC236" s="1"/>
     </row>
-    <row r="237" spans="1:29" ht="13.2">
+    <row r="237" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A237" s="1"/>
       <c r="B237" s="1"/>
       <c r="C237" s="1"/>
@@ -8983,7 +8983,7 @@
       <c r="AB237" s="1"/>
       <c r="AC237" s="1"/>
     </row>
-    <row r="238" spans="1:29" ht="13.2">
+    <row r="238" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A238" s="1"/>
       <c r="B238" s="1"/>
       <c r="C238" s="1"/>
@@ -9014,7 +9014,7 @@
       <c r="AB238" s="1"/>
       <c r="AC238" s="1"/>
     </row>
-    <row r="239" spans="1:29" ht="13.2">
+    <row r="239" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A239" s="1"/>
       <c r="B239" s="1"/>
       <c r="C239" s="1"/>
@@ -9045,7 +9045,7 @@
       <c r="AB239" s="1"/>
       <c r="AC239" s="1"/>
     </row>
-    <row r="240" spans="1:29" ht="13.2">
+    <row r="240" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
@@ -9076,7 +9076,7 @@
       <c r="AB240" s="1"/>
       <c r="AC240" s="1"/>
     </row>
-    <row r="241" spans="1:29" ht="13.2">
+    <row r="241" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A241" s="1"/>
       <c r="B241" s="1"/>
       <c r="C241" s="1"/>
@@ -9107,7 +9107,7 @@
       <c r="AB241" s="1"/>
       <c r="AC241" s="1"/>
     </row>
-    <row r="242" spans="1:29" ht="13.2">
+    <row r="242" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A242" s="1"/>
       <c r="B242" s="1"/>
       <c r="C242" s="1"/>
@@ -9138,7 +9138,7 @@
       <c r="AB242" s="1"/>
       <c r="AC242" s="1"/>
     </row>
-    <row r="243" spans="1:29" ht="13.2">
+    <row r="243" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A243" s="1"/>
       <c r="B243" s="1"/>
       <c r="C243" s="1"/>
@@ -9169,7 +9169,7 @@
       <c r="AB243" s="1"/>
       <c r="AC243" s="1"/>
     </row>
-    <row r="244" spans="1:29" ht="13.2">
+    <row r="244" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A244" s="1"/>
       <c r="B244" s="1"/>
       <c r="C244" s="1"/>
@@ -9200,7 +9200,7 @@
       <c r="AB244" s="1"/>
       <c r="AC244" s="1"/>
     </row>
-    <row r="245" spans="1:29" ht="13.2">
+    <row r="245" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="1"/>
@@ -9231,7 +9231,7 @@
       <c r="AB245" s="1"/>
       <c r="AC245" s="1"/>
     </row>
-    <row r="246" spans="1:29" ht="13.2">
+    <row r="246" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A246" s="1"/>
       <c r="B246" s="1"/>
       <c r="C246" s="1"/>
@@ -9262,7 +9262,7 @@
       <c r="AB246" s="1"/>
       <c r="AC246" s="1"/>
     </row>
-    <row r="247" spans="1:29" ht="13.2">
+    <row r="247" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A247" s="1"/>
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
@@ -9293,7 +9293,7 @@
       <c r="AB247" s="1"/>
       <c r="AC247" s="1"/>
     </row>
-    <row r="248" spans="1:29" ht="13.2">
+    <row r="248" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A248" s="1"/>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
@@ -9324,7 +9324,7 @@
       <c r="AB248" s="1"/>
       <c r="AC248" s="1"/>
     </row>
-    <row r="249" spans="1:29" ht="13.2">
+    <row r="249" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A249" s="1"/>
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
@@ -9355,7 +9355,7 @@
       <c r="AB249" s="1"/>
       <c r="AC249" s="1"/>
     </row>
-    <row r="250" spans="1:29" ht="13.2">
+    <row r="250" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A250" s="1"/>
       <c r="B250" s="1"/>
       <c r="C250" s="1"/>
@@ -9386,7 +9386,7 @@
       <c r="AB250" s="1"/>
       <c r="AC250" s="1"/>
     </row>
-    <row r="251" spans="1:29" ht="13.2">
+    <row r="251" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A251" s="1"/>
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
@@ -9417,7 +9417,7 @@
       <c r="AB251" s="1"/>
       <c r="AC251" s="1"/>
     </row>
-    <row r="252" spans="1:29" ht="13.2">
+    <row r="252" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A252" s="1"/>
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
@@ -9448,7 +9448,7 @@
       <c r="AB252" s="1"/>
       <c r="AC252" s="1"/>
     </row>
-    <row r="253" spans="1:29" ht="13.2">
+    <row r="253" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A253" s="1"/>
       <c r="B253" s="1"/>
       <c r="C253" s="1"/>
@@ -9479,7 +9479,7 @@
       <c r="AB253" s="1"/>
       <c r="AC253" s="1"/>
     </row>
-    <row r="254" spans="1:29" ht="13.2">
+    <row r="254" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A254" s="1"/>
       <c r="B254" s="1"/>
       <c r="C254" s="1"/>
@@ -9510,7 +9510,7 @@
       <c r="AB254" s="1"/>
       <c r="AC254" s="1"/>
     </row>
-    <row r="255" spans="1:29" ht="13.2">
+    <row r="255" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A255" s="1"/>
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
@@ -9541,7 +9541,7 @@
       <c r="AB255" s="1"/>
       <c r="AC255" s="1"/>
     </row>
-    <row r="256" spans="1:29" ht="13.2">
+    <row r="256" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A256" s="1"/>
       <c r="B256" s="1"/>
       <c r="C256" s="1"/>
@@ -9572,7 +9572,7 @@
       <c r="AB256" s="1"/>
       <c r="AC256" s="1"/>
     </row>
-    <row r="257" spans="1:29" ht="13.2">
+    <row r="257" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A257" s="1"/>
       <c r="B257" s="1"/>
       <c r="C257" s="1"/>
@@ -9603,7 +9603,7 @@
       <c r="AB257" s="1"/>
       <c r="AC257" s="1"/>
     </row>
-    <row r="258" spans="1:29" ht="13.2">
+    <row r="258" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A258" s="1"/>
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
@@ -9634,7 +9634,7 @@
       <c r="AB258" s="1"/>
       <c r="AC258" s="1"/>
     </row>
-    <row r="259" spans="1:29" ht="13.2">
+    <row r="259" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A259" s="1"/>
       <c r="B259" s="1"/>
       <c r="C259" s="1"/>
@@ -9665,7 +9665,7 @@
       <c r="AB259" s="1"/>
       <c r="AC259" s="1"/>
     </row>
-    <row r="260" spans="1:29" ht="13.2">
+    <row r="260" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A260" s="1"/>
       <c r="B260" s="1"/>
       <c r="C260" s="1"/>
@@ -9696,7 +9696,7 @@
       <c r="AB260" s="1"/>
       <c r="AC260" s="1"/>
     </row>
-    <row r="261" spans="1:29" ht="13.2">
+    <row r="261" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A261" s="1"/>
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
@@ -9727,7 +9727,7 @@
       <c r="AB261" s="1"/>
       <c r="AC261" s="1"/>
     </row>
-    <row r="262" spans="1:29" ht="13.2">
+    <row r="262" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A262" s="1"/>
       <c r="B262" s="1"/>
       <c r="C262" s="1"/>
@@ -9758,7 +9758,7 @@
       <c r="AB262" s="1"/>
       <c r="AC262" s="1"/>
     </row>
-    <row r="263" spans="1:29" ht="13.2">
+    <row r="263" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A263" s="1"/>
       <c r="B263" s="1"/>
       <c r="C263" s="1"/>
@@ -9789,7 +9789,7 @@
       <c r="AB263" s="1"/>
       <c r="AC263" s="1"/>
     </row>
-    <row r="264" spans="1:29" ht="13.2">
+    <row r="264" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A264" s="1"/>
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
@@ -9820,7 +9820,7 @@
       <c r="AB264" s="1"/>
       <c r="AC264" s="1"/>
     </row>
-    <row r="265" spans="1:29" ht="13.2">
+    <row r="265" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A265" s="1"/>
       <c r="B265" s="1"/>
       <c r="C265" s="1"/>
@@ -9851,7 +9851,7 @@
       <c r="AB265" s="1"/>
       <c r="AC265" s="1"/>
     </row>
-    <row r="266" spans="1:29" ht="13.2">
+    <row r="266" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A266" s="1"/>
       <c r="B266" s="1"/>
       <c r="C266" s="1"/>
@@ -9882,7 +9882,7 @@
       <c r="AB266" s="1"/>
       <c r="AC266" s="1"/>
     </row>
-    <row r="267" spans="1:29" ht="13.2">
+    <row r="267" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A267" s="1"/>
       <c r="B267" s="1"/>
       <c r="C267" s="1"/>
@@ -9913,7 +9913,7 @@
       <c r="AB267" s="1"/>
       <c r="AC267" s="1"/>
     </row>
-    <row r="268" spans="1:29" ht="13.2">
+    <row r="268" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A268" s="1"/>
       <c r="B268" s="1"/>
       <c r="C268" s="1"/>
@@ -9944,7 +9944,7 @@
       <c r="AB268" s="1"/>
       <c r="AC268" s="1"/>
     </row>
-    <row r="269" spans="1:29" ht="13.2">
+    <row r="269" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A269" s="1"/>
       <c r="B269" s="1"/>
       <c r="C269" s="1"/>
@@ -9975,7 +9975,7 @@
       <c r="AB269" s="1"/>
       <c r="AC269" s="1"/>
     </row>
-    <row r="270" spans="1:29" ht="13.2">
+    <row r="270" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A270" s="1"/>
       <c r="B270" s="1"/>
       <c r="C270" s="1"/>
@@ -10006,7 +10006,7 @@
       <c r="AB270" s="1"/>
       <c r="AC270" s="1"/>
     </row>
-    <row r="271" spans="1:29" ht="13.2">
+    <row r="271" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A271" s="1"/>
       <c r="B271" s="1"/>
       <c r="C271" s="1"/>
@@ -10037,7 +10037,7 @@
       <c r="AB271" s="1"/>
       <c r="AC271" s="1"/>
     </row>
-    <row r="272" spans="1:29" ht="13.2">
+    <row r="272" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
@@ -10068,7 +10068,7 @@
       <c r="AB272" s="1"/>
       <c r="AC272" s="1"/>
     </row>
-    <row r="273" spans="1:29" ht="13.2">
+    <row r="273" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A273" s="1"/>
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
@@ -10099,7 +10099,7 @@
       <c r="AB273" s="1"/>
       <c r="AC273" s="1"/>
     </row>
-    <row r="274" spans="1:29" ht="13.2">
+    <row r="274" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A274" s="1"/>
       <c r="B274" s="1"/>
       <c r="C274" s="1"/>
@@ -10130,7 +10130,7 @@
       <c r="AB274" s="1"/>
       <c r="AC274" s="1"/>
     </row>
-    <row r="275" spans="1:29" ht="13.2">
+    <row r="275" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A275" s="1"/>
       <c r="B275" s="1"/>
       <c r="C275" s="1"/>
@@ -10161,7 +10161,7 @@
       <c r="AB275" s="1"/>
       <c r="AC275" s="1"/>
     </row>
-    <row r="276" spans="1:29" ht="13.2">
+    <row r="276" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A276" s="1"/>
       <c r="B276" s="1"/>
       <c r="C276" s="1"/>
@@ -10192,7 +10192,7 @@
       <c r="AB276" s="1"/>
       <c r="AC276" s="1"/>
     </row>
-    <row r="277" spans="1:29" ht="13.2">
+    <row r="277" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A277" s="1"/>
       <c r="B277" s="1"/>
       <c r="C277" s="1"/>
@@ -10223,7 +10223,7 @@
       <c r="AB277" s="1"/>
       <c r="AC277" s="1"/>
     </row>
-    <row r="278" spans="1:29" ht="13.2">
+    <row r="278" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A278" s="1"/>
       <c r="B278" s="1"/>
       <c r="C278" s="1"/>
@@ -10254,7 +10254,7 @@
       <c r="AB278" s="1"/>
       <c r="AC278" s="1"/>
     </row>
-    <row r="279" spans="1:29" ht="13.2">
+    <row r="279" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A279" s="1"/>
       <c r="B279" s="1"/>
       <c r="C279" s="1"/>
@@ -10285,7 +10285,7 @@
       <c r="AB279" s="1"/>
       <c r="AC279" s="1"/>
     </row>
-    <row r="280" spans="1:29" ht="13.2">
+    <row r="280" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A280" s="1"/>
       <c r="B280" s="1"/>
       <c r="C280" s="1"/>
@@ -10316,7 +10316,7 @@
       <c r="AB280" s="1"/>
       <c r="AC280" s="1"/>
     </row>
-    <row r="281" spans="1:29" ht="13.2">
+    <row r="281" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A281" s="1"/>
       <c r="B281" s="1"/>
       <c r="C281" s="1"/>
@@ -10347,7 +10347,7 @@
       <c r="AB281" s="1"/>
       <c r="AC281" s="1"/>
     </row>
-    <row r="282" spans="1:29" ht="13.2">
+    <row r="282" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A282" s="1"/>
       <c r="B282" s="1"/>
       <c r="C282" s="1"/>
@@ -10378,7 +10378,7 @@
       <c r="AB282" s="1"/>
       <c r="AC282" s="1"/>
     </row>
-    <row r="283" spans="1:29" ht="13.2">
+    <row r="283" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A283" s="1"/>
       <c r="B283" s="1"/>
       <c r="C283" s="1"/>
@@ -10409,7 +10409,7 @@
       <c r="AB283" s="1"/>
       <c r="AC283" s="1"/>
     </row>
-    <row r="284" spans="1:29" ht="13.2">
+    <row r="284" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A284" s="1"/>
       <c r="B284" s="1"/>
       <c r="C284" s="1"/>
@@ -10440,7 +10440,7 @@
       <c r="AB284" s="1"/>
       <c r="AC284" s="1"/>
     </row>
-    <row r="285" spans="1:29" ht="13.2">
+    <row r="285" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A285" s="1"/>
       <c r="B285" s="1"/>
       <c r="C285" s="1"/>
@@ -10471,7 +10471,7 @@
       <c r="AB285" s="1"/>
       <c r="AC285" s="1"/>
     </row>
-    <row r="286" spans="1:29" ht="13.2">
+    <row r="286" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A286" s="1"/>
       <c r="B286" s="1"/>
       <c r="C286" s="1"/>
@@ -10502,7 +10502,7 @@
       <c r="AB286" s="1"/>
       <c r="AC286" s="1"/>
     </row>
-    <row r="287" spans="1:29" ht="13.2">
+    <row r="287" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
@@ -10533,7 +10533,7 @@
       <c r="AB287" s="1"/>
       <c r="AC287" s="1"/>
     </row>
-    <row r="288" spans="1:29" ht="13.2">
+    <row r="288" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A288" s="1"/>
       <c r="B288" s="1"/>
       <c r="C288" s="1"/>
@@ -10564,7 +10564,7 @@
       <c r="AB288" s="1"/>
       <c r="AC288" s="1"/>
     </row>
-    <row r="289" spans="1:29" ht="13.2">
+    <row r="289" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A289" s="1"/>
       <c r="B289" s="1"/>
       <c r="C289" s="1"/>
@@ -10595,7 +10595,7 @@
       <c r="AB289" s="1"/>
       <c r="AC289" s="1"/>
     </row>
-    <row r="290" spans="1:29" ht="13.2">
+    <row r="290" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A290" s="1"/>
       <c r="B290" s="1"/>
       <c r="C290" s="1"/>
@@ -10626,7 +10626,7 @@
       <c r="AB290" s="1"/>
       <c r="AC290" s="1"/>
     </row>
-    <row r="291" spans="1:29" ht="13.2">
+    <row r="291" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A291" s="1"/>
       <c r="B291" s="1"/>
       <c r="C291" s="1"/>
@@ -10657,7 +10657,7 @@
       <c r="AB291" s="1"/>
       <c r="AC291" s="1"/>
     </row>
-    <row r="292" spans="1:29" ht="13.2">
+    <row r="292" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A292" s="1"/>
       <c r="B292" s="1"/>
       <c r="C292" s="1"/>
@@ -10688,7 +10688,7 @@
       <c r="AB292" s="1"/>
       <c r="AC292" s="1"/>
     </row>
-    <row r="293" spans="1:29" ht="13.2">
+    <row r="293" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A293" s="1"/>
       <c r="B293" s="1"/>
       <c r="C293" s="1"/>
@@ -10719,7 +10719,7 @@
       <c r="AB293" s="1"/>
       <c r="AC293" s="1"/>
     </row>
-    <row r="294" spans="1:29" ht="13.2">
+    <row r="294" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A294" s="1"/>
       <c r="B294" s="1"/>
       <c r="C294" s="1"/>
@@ -10750,7 +10750,7 @@
       <c r="AB294" s="1"/>
       <c r="AC294" s="1"/>
     </row>
-    <row r="295" spans="1:29" ht="13.2">
+    <row r="295" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A295" s="1"/>
       <c r="B295" s="1"/>
       <c r="C295" s="1"/>
@@ -10781,7 +10781,7 @@
       <c r="AB295" s="1"/>
       <c r="AC295" s="1"/>
     </row>
-    <row r="296" spans="1:29" ht="13.2">
+    <row r="296" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A296" s="1"/>
       <c r="B296" s="1"/>
       <c r="C296" s="1"/>
@@ -10812,7 +10812,7 @@
       <c r="AB296" s="1"/>
       <c r="AC296" s="1"/>
     </row>
-    <row r="297" spans="1:29" ht="13.2">
+    <row r="297" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A297" s="1"/>
       <c r="B297" s="1"/>
       <c r="C297" s="1"/>
@@ -10843,7 +10843,7 @@
       <c r="AB297" s="1"/>
       <c r="AC297" s="1"/>
     </row>
-    <row r="298" spans="1:29" ht="13.2">
+    <row r="298" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A298" s="1"/>
       <c r="B298" s="1"/>
       <c r="C298" s="1"/>
@@ -10874,7 +10874,7 @@
       <c r="AB298" s="1"/>
       <c r="AC298" s="1"/>
     </row>
-    <row r="299" spans="1:29" ht="13.2">
+    <row r="299" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A299" s="1"/>
       <c r="B299" s="1"/>
       <c r="C299" s="1"/>
@@ -10905,7 +10905,7 @@
       <c r="AB299" s="1"/>
       <c r="AC299" s="1"/>
     </row>
-    <row r="300" spans="1:29" ht="13.2">
+    <row r="300" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A300" s="1"/>
       <c r="B300" s="1"/>
       <c r="C300" s="1"/>
@@ -10936,7 +10936,7 @@
       <c r="AB300" s="1"/>
       <c r="AC300" s="1"/>
     </row>
-    <row r="301" spans="1:29" ht="13.2">
+    <row r="301" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A301" s="1"/>
       <c r="B301" s="1"/>
       <c r="C301" s="1"/>
@@ -10967,7 +10967,7 @@
       <c r="AB301" s="1"/>
       <c r="AC301" s="1"/>
     </row>
-    <row r="302" spans="1:29" ht="13.2">
+    <row r="302" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A302" s="1"/>
       <c r="B302" s="1"/>
       <c r="C302" s="1"/>
@@ -10998,7 +10998,7 @@
       <c r="AB302" s="1"/>
       <c r="AC302" s="1"/>
     </row>
-    <row r="303" spans="1:29" ht="13.2">
+    <row r="303" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A303" s="1"/>
       <c r="B303" s="1"/>
       <c r="C303" s="1"/>
@@ -11029,7 +11029,7 @@
       <c r="AB303" s="1"/>
       <c r="AC303" s="1"/>
     </row>
-    <row r="304" spans="1:29" ht="13.2">
+    <row r="304" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A304" s="1"/>
       <c r="B304" s="1"/>
       <c r="C304" s="1"/>
@@ -11060,7 +11060,7 @@
       <c r="AB304" s="1"/>
       <c r="AC304" s="1"/>
     </row>
-    <row r="305" spans="1:29" ht="13.2">
+    <row r="305" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A305" s="1"/>
       <c r="B305" s="1"/>
       <c r="C305" s="1"/>
@@ -11091,7 +11091,7 @@
       <c r="AB305" s="1"/>
       <c r="AC305" s="1"/>
     </row>
-    <row r="306" spans="1:29" ht="13.2">
+    <row r="306" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A306" s="1"/>
       <c r="B306" s="1"/>
       <c r="C306" s="1"/>
@@ -11122,7 +11122,7 @@
       <c r="AB306" s="1"/>
       <c r="AC306" s="1"/>
     </row>
-    <row r="307" spans="1:29" ht="13.2">
+    <row r="307" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A307" s="1"/>
       <c r="B307" s="1"/>
       <c r="C307" s="1"/>
@@ -11153,7 +11153,7 @@
       <c r="AB307" s="1"/>
       <c r="AC307" s="1"/>
     </row>
-    <row r="308" spans="1:29" ht="13.2">
+    <row r="308" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A308" s="1"/>
       <c r="B308" s="1"/>
       <c r="C308" s="1"/>
@@ -11184,7 +11184,7 @@
       <c r="AB308" s="1"/>
       <c r="AC308" s="1"/>
     </row>
-    <row r="309" spans="1:29" ht="13.2">
+    <row r="309" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A309" s="1"/>
       <c r="B309" s="1"/>
       <c r="C309" s="1"/>
@@ -11215,7 +11215,7 @@
       <c r="AB309" s="1"/>
       <c r="AC309" s="1"/>
     </row>
-    <row r="310" spans="1:29" ht="13.2">
+    <row r="310" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A310" s="1"/>
       <c r="B310" s="1"/>
       <c r="C310" s="1"/>
@@ -11246,7 +11246,7 @@
       <c r="AB310" s="1"/>
       <c r="AC310" s="1"/>
     </row>
-    <row r="311" spans="1:29" ht="13.2">
+    <row r="311" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A311" s="1"/>
       <c r="B311" s="1"/>
       <c r="C311" s="1"/>
@@ -11277,7 +11277,7 @@
       <c r="AB311" s="1"/>
       <c r="AC311" s="1"/>
     </row>
-    <row r="312" spans="1:29" ht="13.2">
+    <row r="312" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A312" s="1"/>
       <c r="B312" s="1"/>
       <c r="C312" s="1"/>
@@ -11308,7 +11308,7 @@
       <c r="AB312" s="1"/>
       <c r="AC312" s="1"/>
     </row>
-    <row r="313" spans="1:29" ht="13.2">
+    <row r="313" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A313" s="1"/>
       <c r="B313" s="1"/>
       <c r="C313" s="1"/>
@@ -11339,7 +11339,7 @@
       <c r="AB313" s="1"/>
       <c r="AC313" s="1"/>
     </row>
-    <row r="314" spans="1:29" ht="13.2">
+    <row r="314" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A314" s="1"/>
       <c r="B314" s="1"/>
       <c r="C314" s="1"/>
@@ -11370,7 +11370,7 @@
       <c r="AB314" s="1"/>
       <c r="AC314" s="1"/>
     </row>
-    <row r="315" spans="1:29" ht="13.2">
+    <row r="315" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A315" s="1"/>
       <c r="B315" s="1"/>
       <c r="C315" s="1"/>
@@ -11401,7 +11401,7 @@
       <c r="AB315" s="1"/>
       <c r="AC315" s="1"/>
     </row>
-    <row r="316" spans="1:29" ht="13.2">
+    <row r="316" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A316" s="1"/>
       <c r="B316" s="1"/>
       <c r="C316" s="1"/>
@@ -11432,7 +11432,7 @@
       <c r="AB316" s="1"/>
       <c r="AC316" s="1"/>
     </row>
-    <row r="317" spans="1:29" ht="13.2">
+    <row r="317" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A317" s="1"/>
       <c r="B317" s="1"/>
       <c r="C317" s="1"/>
@@ -11463,7 +11463,7 @@
       <c r="AB317" s="1"/>
       <c r="AC317" s="1"/>
     </row>
-    <row r="318" spans="1:29" ht="13.2">
+    <row r="318" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A318" s="1"/>
       <c r="B318" s="1"/>
       <c r="C318" s="1"/>
@@ -11494,7 +11494,7 @@
       <c r="AB318" s="1"/>
       <c r="AC318" s="1"/>
     </row>
-    <row r="319" spans="1:29" ht="13.2">
+    <row r="319" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A319" s="1"/>
       <c r="B319" s="1"/>
       <c r="C319" s="1"/>
@@ -11525,7 +11525,7 @@
       <c r="AB319" s="1"/>
       <c r="AC319" s="1"/>
     </row>
-    <row r="320" spans="1:29" ht="13.2">
+    <row r="320" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A320" s="1"/>
       <c r="B320" s="1"/>
       <c r="C320" s="1"/>
@@ -11556,7 +11556,7 @@
       <c r="AB320" s="1"/>
       <c r="AC320" s="1"/>
     </row>
-    <row r="321" spans="1:29" ht="13.2">
+    <row r="321" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A321" s="1"/>
       <c r="B321" s="1"/>
       <c r="C321" s="1"/>
@@ -11587,7 +11587,7 @@
       <c r="AB321" s="1"/>
       <c r="AC321" s="1"/>
     </row>
-    <row r="322" spans="1:29" ht="13.2">
+    <row r="322" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A322" s="1"/>
       <c r="B322" s="1"/>
       <c r="C322" s="1"/>
@@ -11618,7 +11618,7 @@
       <c r="AB322" s="1"/>
       <c r="AC322" s="1"/>
     </row>
-    <row r="323" spans="1:29" ht="13.2">
+    <row r="323" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A323" s="1"/>
       <c r="B323" s="1"/>
       <c r="C323" s="1"/>
@@ -11649,7 +11649,7 @@
       <c r="AB323" s="1"/>
       <c r="AC323" s="1"/>
     </row>
-    <row r="324" spans="1:29" ht="13.2">
+    <row r="324" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A324" s="1"/>
       <c r="B324" s="1"/>
       <c r="C324" s="1"/>
@@ -11680,7 +11680,7 @@
       <c r="AB324" s="1"/>
       <c r="AC324" s="1"/>
     </row>
-    <row r="325" spans="1:29" ht="13.2">
+    <row r="325" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A325" s="1"/>
       <c r="B325" s="1"/>
       <c r="C325" s="1"/>
@@ -11711,7 +11711,7 @@
       <c r="AB325" s="1"/>
       <c r="AC325" s="1"/>
     </row>
-    <row r="326" spans="1:29" ht="13.2">
+    <row r="326" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A326" s="1"/>
       <c r="B326" s="1"/>
       <c r="C326" s="1"/>
@@ -11742,7 +11742,7 @@
       <c r="AB326" s="1"/>
       <c r="AC326" s="1"/>
     </row>
-    <row r="327" spans="1:29" ht="13.2">
+    <row r="327" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A327" s="1"/>
       <c r="B327" s="1"/>
       <c r="C327" s="1"/>
@@ -11773,7 +11773,7 @@
       <c r="AB327" s="1"/>
       <c r="AC327" s="1"/>
     </row>
-    <row r="328" spans="1:29" ht="13.2">
+    <row r="328" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A328" s="1"/>
       <c r="B328" s="1"/>
       <c r="C328" s="1"/>
@@ -11804,7 +11804,7 @@
       <c r="AB328" s="1"/>
       <c r="AC328" s="1"/>
     </row>
-    <row r="329" spans="1:29" ht="13.2">
+    <row r="329" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A329" s="1"/>
       <c r="B329" s="1"/>
       <c r="C329" s="1"/>
@@ -11835,7 +11835,7 @@
       <c r="AB329" s="1"/>
       <c r="AC329" s="1"/>
     </row>
-    <row r="330" spans="1:29" ht="13.2">
+    <row r="330" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A330" s="1"/>
       <c r="B330" s="1"/>
       <c r="C330" s="1"/>
@@ -11866,7 +11866,7 @@
       <c r="AB330" s="1"/>
       <c r="AC330" s="1"/>
     </row>
-    <row r="331" spans="1:29" ht="13.2">
+    <row r="331" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A331" s="1"/>
       <c r="B331" s="1"/>
       <c r="C331" s="1"/>
@@ -11897,7 +11897,7 @@
       <c r="AB331" s="1"/>
       <c r="AC331" s="1"/>
     </row>
-    <row r="332" spans="1:29" ht="13.2">
+    <row r="332" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A332" s="1"/>
       <c r="B332" s="1"/>
       <c r="C332" s="1"/>
@@ -11928,7 +11928,7 @@
       <c r="AB332" s="1"/>
       <c r="AC332" s="1"/>
     </row>
-    <row r="333" spans="1:29" ht="13.2">
+    <row r="333" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A333" s="1"/>
       <c r="B333" s="1"/>
       <c r="C333" s="1"/>
@@ -11959,7 +11959,7 @@
       <c r="AB333" s="1"/>
       <c r="AC333" s="1"/>
     </row>
-    <row r="334" spans="1:29" ht="13.2">
+    <row r="334" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A334" s="1"/>
       <c r="B334" s="1"/>
       <c r="C334" s="1"/>
@@ -11990,7 +11990,7 @@
       <c r="AB334" s="1"/>
       <c r="AC334" s="1"/>
     </row>
-    <row r="335" spans="1:29" ht="13.2">
+    <row r="335" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A335" s="1"/>
       <c r="B335" s="1"/>
       <c r="C335" s="1"/>
@@ -12021,7 +12021,7 @@
       <c r="AB335" s="1"/>
       <c r="AC335" s="1"/>
     </row>
-    <row r="336" spans="1:29" ht="13.2">
+    <row r="336" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A336" s="1"/>
       <c r="B336" s="1"/>
       <c r="C336" s="1"/>
@@ -12052,7 +12052,7 @@
       <c r="AB336" s="1"/>
       <c r="AC336" s="1"/>
     </row>
-    <row r="337" spans="1:29" ht="13.2">
+    <row r="337" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A337" s="1"/>
       <c r="B337" s="1"/>
       <c r="C337" s="1"/>
@@ -12083,7 +12083,7 @@
       <c r="AB337" s="1"/>
       <c r="AC337" s="1"/>
     </row>
-    <row r="338" spans="1:29" ht="13.2">
+    <row r="338" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A338" s="1"/>
       <c r="B338" s="1"/>
       <c r="C338" s="1"/>
@@ -12114,7 +12114,7 @@
       <c r="AB338" s="1"/>
       <c r="AC338" s="1"/>
     </row>
-    <row r="339" spans="1:29" ht="13.2">
+    <row r="339" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A339" s="1"/>
       <c r="B339" s="1"/>
       <c r="C339" s="1"/>
@@ -12145,7 +12145,7 @@
       <c r="AB339" s="1"/>
       <c r="AC339" s="1"/>
     </row>
-    <row r="340" spans="1:29" ht="13.2">
+    <row r="340" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A340" s="1"/>
       <c r="B340" s="1"/>
       <c r="C340" s="1"/>
@@ -12176,7 +12176,7 @@
       <c r="AB340" s="1"/>
       <c r="AC340" s="1"/>
     </row>
-    <row r="341" spans="1:29" ht="13.2">
+    <row r="341" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A341" s="1"/>
       <c r="B341" s="1"/>
       <c r="C341" s="1"/>
@@ -12207,7 +12207,7 @@
       <c r="AB341" s="1"/>
       <c r="AC341" s="1"/>
     </row>
-    <row r="342" spans="1:29" ht="13.2">
+    <row r="342" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A342" s="1"/>
       <c r="B342" s="1"/>
       <c r="C342" s="1"/>
@@ -12238,7 +12238,7 @@
       <c r="AB342" s="1"/>
       <c r="AC342" s="1"/>
     </row>
-    <row r="343" spans="1:29" ht="13.2">
+    <row r="343" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A343" s="1"/>
       <c r="B343" s="1"/>
       <c r="C343" s="1"/>
@@ -12269,7 +12269,7 @@
       <c r="AB343" s="1"/>
       <c r="AC343" s="1"/>
     </row>
-    <row r="344" spans="1:29" ht="13.2">
+    <row r="344" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A344" s="1"/>
       <c r="B344" s="1"/>
       <c r="C344" s="1"/>
@@ -12300,7 +12300,7 @@
       <c r="AB344" s="1"/>
       <c r="AC344" s="1"/>
     </row>
-    <row r="345" spans="1:29" ht="13.2">
+    <row r="345" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A345" s="1"/>
       <c r="B345" s="1"/>
       <c r="C345" s="1"/>
@@ -12331,7 +12331,7 @@
       <c r="AB345" s="1"/>
       <c r="AC345" s="1"/>
     </row>
-    <row r="346" spans="1:29" ht="13.2">
+    <row r="346" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A346" s="1"/>
       <c r="B346" s="1"/>
       <c r="C346" s="1"/>
@@ -12362,7 +12362,7 @@
       <c r="AB346" s="1"/>
       <c r="AC346" s="1"/>
     </row>
-    <row r="347" spans="1:29" ht="13.2">
+    <row r="347" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A347" s="1"/>
       <c r="B347" s="1"/>
       <c r="C347" s="1"/>
@@ -12393,7 +12393,7 @@
       <c r="AB347" s="1"/>
       <c r="AC347" s="1"/>
     </row>
-    <row r="348" spans="1:29" ht="13.2">
+    <row r="348" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A348" s="1"/>
       <c r="B348" s="1"/>
       <c r="C348" s="1"/>
@@ -12424,7 +12424,7 @@
       <c r="AB348" s="1"/>
       <c r="AC348" s="1"/>
     </row>
-    <row r="349" spans="1:29" ht="13.2">
+    <row r="349" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A349" s="1"/>
       <c r="B349" s="1"/>
       <c r="C349" s="1"/>
@@ -12455,7 +12455,7 @@
       <c r="AB349" s="1"/>
       <c r="AC349" s="1"/>
     </row>
-    <row r="350" spans="1:29" ht="13.2">
+    <row r="350" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A350" s="1"/>
       <c r="B350" s="1"/>
       <c r="C350" s="1"/>
@@ -12486,7 +12486,7 @@
       <c r="AB350" s="1"/>
       <c r="AC350" s="1"/>
     </row>
-    <row r="351" spans="1:29" ht="13.2">
+    <row r="351" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A351" s="1"/>
       <c r="B351" s="1"/>
       <c r="C351" s="1"/>
@@ -12517,7 +12517,7 @@
       <c r="AB351" s="1"/>
       <c r="AC351" s="1"/>
     </row>
-    <row r="352" spans="1:29" ht="13.2">
+    <row r="352" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A352" s="1"/>
       <c r="B352" s="1"/>
       <c r="C352" s="1"/>
@@ -12548,7 +12548,7 @@
       <c r="AB352" s="1"/>
       <c r="AC352" s="1"/>
     </row>
-    <row r="353" spans="1:29" ht="13.2">
+    <row r="353" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A353" s="1"/>
       <c r="B353" s="1"/>
       <c r="C353" s="1"/>
@@ -12579,7 +12579,7 @@
       <c r="AB353" s="1"/>
       <c r="AC353" s="1"/>
     </row>
-    <row r="354" spans="1:29" ht="13.2">
+    <row r="354" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A354" s="1"/>
       <c r="B354" s="1"/>
       <c r="C354" s="1"/>
@@ -12610,7 +12610,7 @@
       <c r="AB354" s="1"/>
       <c r="AC354" s="1"/>
     </row>
-    <row r="355" spans="1:29" ht="13.2">
+    <row r="355" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A355" s="1"/>
       <c r="B355" s="1"/>
       <c r="C355" s="1"/>
@@ -12641,7 +12641,7 @@
       <c r="AB355" s="1"/>
       <c r="AC355" s="1"/>
     </row>
-    <row r="356" spans="1:29" ht="13.2">
+    <row r="356" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A356" s="1"/>
       <c r="B356" s="1"/>
       <c r="C356" s="1"/>
@@ -12672,7 +12672,7 @@
       <c r="AB356" s="1"/>
       <c r="AC356" s="1"/>
     </row>
-    <row r="357" spans="1:29" ht="13.2">
+    <row r="357" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A357" s="1"/>
       <c r="B357" s="1"/>
       <c r="C357" s="1"/>
@@ -12703,7 +12703,7 @@
       <c r="AB357" s="1"/>
       <c r="AC357" s="1"/>
     </row>
-    <row r="358" spans="1:29" ht="13.2">
+    <row r="358" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A358" s="1"/>
       <c r="B358" s="1"/>
       <c r="C358" s="1"/>
@@ -12734,7 +12734,7 @@
       <c r="AB358" s="1"/>
       <c r="AC358" s="1"/>
     </row>
-    <row r="359" spans="1:29" ht="13.2">
+    <row r="359" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A359" s="1"/>
       <c r="B359" s="1"/>
       <c r="C359" s="1"/>
@@ -12765,7 +12765,7 @@
       <c r="AB359" s="1"/>
       <c r="AC359" s="1"/>
     </row>
-    <row r="360" spans="1:29" ht="13.2">
+    <row r="360" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A360" s="1"/>
       <c r="B360" s="1"/>
       <c r="C360" s="1"/>
@@ -12796,7 +12796,7 @@
       <c r="AB360" s="1"/>
       <c r="AC360" s="1"/>
     </row>
-    <row r="361" spans="1:29" ht="13.2">
+    <row r="361" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A361" s="1"/>
       <c r="B361" s="1"/>
       <c r="C361" s="1"/>
@@ -12827,7 +12827,7 @@
       <c r="AB361" s="1"/>
       <c r="AC361" s="1"/>
     </row>
-    <row r="362" spans="1:29" ht="13.2">
+    <row r="362" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A362" s="1"/>
       <c r="B362" s="1"/>
       <c r="C362" s="1"/>
@@ -12858,7 +12858,7 @@
       <c r="AB362" s="1"/>
       <c r="AC362" s="1"/>
     </row>
-    <row r="363" spans="1:29" ht="13.2">
+    <row r="363" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A363" s="1"/>
       <c r="B363" s="1"/>
       <c r="C363" s="1"/>
@@ -12889,7 +12889,7 @@
       <c r="AB363" s="1"/>
       <c r="AC363" s="1"/>
     </row>
-    <row r="364" spans="1:29" ht="13.2">
+    <row r="364" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A364" s="1"/>
       <c r="B364" s="1"/>
       <c r="C364" s="1"/>
@@ -12920,7 +12920,7 @@
       <c r="AB364" s="1"/>
       <c r="AC364" s="1"/>
     </row>
-    <row r="365" spans="1:29" ht="13.2">
+    <row r="365" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A365" s="1"/>
       <c r="B365" s="1"/>
       <c r="C365" s="1"/>
@@ -12951,7 +12951,7 @@
       <c r="AB365" s="1"/>
       <c r="AC365" s="1"/>
     </row>
-    <row r="366" spans="1:29" ht="13.2">
+    <row r="366" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A366" s="1"/>
       <c r="B366" s="1"/>
       <c r="C366" s="1"/>
@@ -12982,7 +12982,7 @@
       <c r="AB366" s="1"/>
       <c r="AC366" s="1"/>
     </row>
-    <row r="367" spans="1:29" ht="13.2">
+    <row r="367" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A367" s="1"/>
       <c r="B367" s="1"/>
       <c r="C367" s="1"/>
@@ -13013,7 +13013,7 @@
       <c r="AB367" s="1"/>
       <c r="AC367" s="1"/>
     </row>
-    <row r="368" spans="1:29" ht="13.2">
+    <row r="368" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A368" s="1"/>
       <c r="B368" s="1"/>
       <c r="C368" s="1"/>
@@ -13044,7 +13044,7 @@
       <c r="AB368" s="1"/>
       <c r="AC368" s="1"/>
     </row>
-    <row r="369" spans="1:29" ht="13.2">
+    <row r="369" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A369" s="1"/>
       <c r="B369" s="1"/>
       <c r="C369" s="1"/>
@@ -13075,7 +13075,7 @@
       <c r="AB369" s="1"/>
       <c r="AC369" s="1"/>
     </row>
-    <row r="370" spans="1:29" ht="13.2">
+    <row r="370" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A370" s="1"/>
       <c r="B370" s="1"/>
       <c r="C370" s="1"/>
@@ -13106,7 +13106,7 @@
       <c r="AB370" s="1"/>
       <c r="AC370" s="1"/>
     </row>
-    <row r="371" spans="1:29" ht="13.2">
+    <row r="371" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A371" s="1"/>
       <c r="B371" s="1"/>
       <c r="C371" s="1"/>
@@ -13137,7 +13137,7 @@
       <c r="AB371" s="1"/>
       <c r="AC371" s="1"/>
     </row>
-    <row r="372" spans="1:29" ht="13.2">
+    <row r="372" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A372" s="1"/>
       <c r="B372" s="1"/>
       <c r="C372" s="1"/>
@@ -13168,7 +13168,7 @@
       <c r="AB372" s="1"/>
       <c r="AC372" s="1"/>
     </row>
-    <row r="373" spans="1:29" ht="13.2">
+    <row r="373" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A373" s="1"/>
       <c r="B373" s="1"/>
       <c r="C373" s="1"/>
@@ -13199,7 +13199,7 @@
       <c r="AB373" s="1"/>
       <c r="AC373" s="1"/>
     </row>
-    <row r="374" spans="1:29" ht="13.2">
+    <row r="374" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A374" s="1"/>
       <c r="B374" s="1"/>
       <c r="C374" s="1"/>
@@ -13230,7 +13230,7 @@
       <c r="AB374" s="1"/>
       <c r="AC374" s="1"/>
     </row>
-    <row r="375" spans="1:29" ht="13.2">
+    <row r="375" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A375" s="1"/>
       <c r="B375" s="1"/>
       <c r="C375" s="1"/>
@@ -13261,7 +13261,7 @@
       <c r="AB375" s="1"/>
       <c r="AC375" s="1"/>
     </row>
-    <row r="376" spans="1:29" ht="13.2">
+    <row r="376" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A376" s="1"/>
       <c r="B376" s="1"/>
       <c r="C376" s="1"/>
@@ -13292,7 +13292,7 @@
       <c r="AB376" s="1"/>
       <c r="AC376" s="1"/>
     </row>
-    <row r="377" spans="1:29" ht="13.2">
+    <row r="377" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A377" s="1"/>
       <c r="B377" s="1"/>
       <c r="C377" s="1"/>
@@ -13323,7 +13323,7 @@
       <c r="AB377" s="1"/>
       <c r="AC377" s="1"/>
     </row>
-    <row r="378" spans="1:29" ht="13.2">
+    <row r="378" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A378" s="1"/>
       <c r="B378" s="1"/>
       <c r="C378" s="1"/>
@@ -13354,7 +13354,7 @@
       <c r="AB378" s="1"/>
       <c r="AC378" s="1"/>
     </row>
-    <row r="379" spans="1:29" ht="13.2">
+    <row r="379" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A379" s="1"/>
       <c r="B379" s="1"/>
       <c r="C379" s="1"/>
@@ -13385,7 +13385,7 @@
       <c r="AB379" s="1"/>
       <c r="AC379" s="1"/>
     </row>
-    <row r="380" spans="1:29" ht="13.2">
+    <row r="380" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A380" s="1"/>
       <c r="B380" s="1"/>
       <c r="C380" s="1"/>
@@ -13416,7 +13416,7 @@
       <c r="AB380" s="1"/>
       <c r="AC380" s="1"/>
     </row>
-    <row r="381" spans="1:29" ht="13.2">
+    <row r="381" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A381" s="1"/>
       <c r="B381" s="1"/>
       <c r="C381" s="1"/>
@@ -13447,7 +13447,7 @@
       <c r="AB381" s="1"/>
       <c r="AC381" s="1"/>
     </row>
-    <row r="382" spans="1:29" ht="13.2">
+    <row r="382" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A382" s="1"/>
       <c r="B382" s="1"/>
       <c r="C382" s="1"/>
@@ -13478,7 +13478,7 @@
       <c r="AB382" s="1"/>
       <c r="AC382" s="1"/>
     </row>
-    <row r="383" spans="1:29" ht="13.2">
+    <row r="383" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A383" s="1"/>
       <c r="B383" s="1"/>
       <c r="C383" s="1"/>
@@ -13509,7 +13509,7 @@
       <c r="AB383" s="1"/>
       <c r="AC383" s="1"/>
     </row>
-    <row r="384" spans="1:29" ht="13.2">
+    <row r="384" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A384" s="1"/>
       <c r="B384" s="1"/>
       <c r="C384" s="1"/>
@@ -13540,7 +13540,7 @@
       <c r="AB384" s="1"/>
       <c r="AC384" s="1"/>
     </row>
-    <row r="385" spans="1:29" ht="13.2">
+    <row r="385" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A385" s="1"/>
       <c r="B385" s="1"/>
       <c r="C385" s="1"/>
@@ -13571,7 +13571,7 @@
       <c r="AB385" s="1"/>
       <c r="AC385" s="1"/>
     </row>
-    <row r="386" spans="1:29" ht="13.2">
+    <row r="386" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A386" s="1"/>
       <c r="B386" s="1"/>
       <c r="C386" s="1"/>
@@ -13602,7 +13602,7 @@
       <c r="AB386" s="1"/>
       <c r="AC386" s="1"/>
     </row>
-    <row r="387" spans="1:29" ht="13.2">
+    <row r="387" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A387" s="1"/>
       <c r="B387" s="1"/>
       <c r="C387" s="1"/>
@@ -13633,7 +13633,7 @@
       <c r="AB387" s="1"/>
       <c r="AC387" s="1"/>
     </row>
-    <row r="388" spans="1:29" ht="13.2">
+    <row r="388" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A388" s="1"/>
       <c r="B388" s="1"/>
       <c r="C388" s="1"/>
@@ -13664,7 +13664,7 @@
       <c r="AB388" s="1"/>
       <c r="AC388" s="1"/>
     </row>
-    <row r="389" spans="1:29" ht="13.2">
+    <row r="389" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A389" s="1"/>
       <c r="B389" s="1"/>
       <c r="C389" s="1"/>
@@ -13695,7 +13695,7 @@
       <c r="AB389" s="1"/>
       <c r="AC389" s="1"/>
     </row>
-    <row r="390" spans="1:29" ht="13.2">
+    <row r="390" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A390" s="1"/>
       <c r="B390" s="1"/>
       <c r="C390" s="1"/>
@@ -13726,7 +13726,7 @@
       <c r="AB390" s="1"/>
       <c r="AC390" s="1"/>
     </row>
-    <row r="391" spans="1:29" ht="13.2">
+    <row r="391" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A391" s="1"/>
       <c r="B391" s="1"/>
       <c r="C391" s="1"/>
@@ -13757,7 +13757,7 @@
       <c r="AB391" s="1"/>
       <c r="AC391" s="1"/>
     </row>
-    <row r="392" spans="1:29" ht="13.2">
+    <row r="392" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A392" s="1"/>
       <c r="B392" s="1"/>
       <c r="C392" s="1"/>
@@ -13788,7 +13788,7 @@
       <c r="AB392" s="1"/>
       <c r="AC392" s="1"/>
     </row>
-    <row r="393" spans="1:29" ht="13.2">
+    <row r="393" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A393" s="1"/>
       <c r="B393" s="1"/>
       <c r="C393" s="1"/>
@@ -13819,7 +13819,7 @@
       <c r="AB393" s="1"/>
       <c r="AC393" s="1"/>
     </row>
-    <row r="394" spans="1:29" ht="13.2">
+    <row r="394" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A394" s="1"/>
       <c r="B394" s="1"/>
       <c r="C394" s="1"/>
@@ -13850,7 +13850,7 @@
       <c r="AB394" s="1"/>
       <c r="AC394" s="1"/>
     </row>
-    <row r="395" spans="1:29" ht="13.2">
+    <row r="395" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A395" s="1"/>
       <c r="B395" s="1"/>
       <c r="C395" s="1"/>
@@ -13881,7 +13881,7 @@
       <c r="AB395" s="1"/>
       <c r="AC395" s="1"/>
     </row>
-    <row r="396" spans="1:29" ht="13.2">
+    <row r="396" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A396" s="1"/>
       <c r="B396" s="1"/>
       <c r="C396" s="1"/>
@@ -13912,7 +13912,7 @@
       <c r="AB396" s="1"/>
       <c r="AC396" s="1"/>
     </row>
-    <row r="397" spans="1:29" ht="13.2">
+    <row r="397" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A397" s="1"/>
       <c r="B397" s="1"/>
       <c r="C397" s="1"/>
@@ -13943,7 +13943,7 @@
       <c r="AB397" s="1"/>
       <c r="AC397" s="1"/>
     </row>
-    <row r="398" spans="1:29" ht="13.2">
+    <row r="398" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A398" s="1"/>
       <c r="B398" s="1"/>
       <c r="C398" s="1"/>
@@ -13974,7 +13974,7 @@
       <c r="AB398" s="1"/>
       <c r="AC398" s="1"/>
     </row>
-    <row r="399" spans="1:29" ht="13.2">
+    <row r="399" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A399" s="1"/>
       <c r="B399" s="1"/>
       <c r="C399" s="1"/>
@@ -14005,7 +14005,7 @@
       <c r="AB399" s="1"/>
       <c r="AC399" s="1"/>
     </row>
-    <row r="400" spans="1:29" ht="13.2">
+    <row r="400" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A400" s="1"/>
       <c r="B400" s="1"/>
       <c r="C400" s="1"/>
@@ -14036,7 +14036,7 @@
       <c r="AB400" s="1"/>
       <c r="AC400" s="1"/>
     </row>
-    <row r="401" spans="1:29" ht="13.2">
+    <row r="401" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A401" s="1"/>
       <c r="B401" s="1"/>
       <c r="C401" s="1"/>
@@ -14067,7 +14067,7 @@
       <c r="AB401" s="1"/>
       <c r="AC401" s="1"/>
     </row>
-    <row r="402" spans="1:29" ht="13.2">
+    <row r="402" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A402" s="1"/>
       <c r="B402" s="1"/>
       <c r="C402" s="1"/>
@@ -14098,7 +14098,7 @@
       <c r="AB402" s="1"/>
       <c r="AC402" s="1"/>
     </row>
-    <row r="403" spans="1:29" ht="13.2">
+    <row r="403" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A403" s="1"/>
       <c r="B403" s="1"/>
       <c r="C403" s="1"/>
@@ -14129,7 +14129,7 @@
       <c r="AB403" s="1"/>
       <c r="AC403" s="1"/>
     </row>
-    <row r="404" spans="1:29" ht="13.2">
+    <row r="404" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A404" s="1"/>
       <c r="B404" s="1"/>
       <c r="C404" s="1"/>
@@ -14160,7 +14160,7 @@
       <c r="AB404" s="1"/>
       <c r="AC404" s="1"/>
     </row>
-    <row r="405" spans="1:29" ht="13.2">
+    <row r="405" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A405" s="1"/>
       <c r="B405" s="1"/>
       <c r="C405" s="1"/>
@@ -14191,7 +14191,7 @@
       <c r="AB405" s="1"/>
       <c r="AC405" s="1"/>
     </row>
-    <row r="406" spans="1:29" ht="13.2">
+    <row r="406" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A406" s="1"/>
       <c r="B406" s="1"/>
       <c r="C406" s="1"/>
@@ -14222,7 +14222,7 @@
       <c r="AB406" s="1"/>
       <c r="AC406" s="1"/>
     </row>
-    <row r="407" spans="1:29" ht="13.2">
+    <row r="407" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A407" s="1"/>
       <c r="B407" s="1"/>
       <c r="C407" s="1"/>
@@ -14253,7 +14253,7 @@
       <c r="AB407" s="1"/>
       <c r="AC407" s="1"/>
     </row>
-    <row r="408" spans="1:29" ht="13.2">
+    <row r="408" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A408" s="1"/>
       <c r="B408" s="1"/>
       <c r="C408" s="1"/>
@@ -14284,7 +14284,7 @@
       <c r="AB408" s="1"/>
       <c r="AC408" s="1"/>
     </row>
-    <row r="409" spans="1:29" ht="13.2">
+    <row r="409" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A409" s="1"/>
       <c r="B409" s="1"/>
       <c r="C409" s="1"/>
@@ -14315,7 +14315,7 @@
       <c r="AB409" s="1"/>
       <c r="AC409" s="1"/>
     </row>
-    <row r="410" spans="1:29" ht="13.2">
+    <row r="410" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A410" s="1"/>
       <c r="B410" s="1"/>
       <c r="C410" s="1"/>
@@ -14346,7 +14346,7 @@
       <c r="AB410" s="1"/>
       <c r="AC410" s="1"/>
     </row>
-    <row r="411" spans="1:29" ht="13.2">
+    <row r="411" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A411" s="1"/>
       <c r="B411" s="1"/>
       <c r="C411" s="1"/>
@@ -14377,7 +14377,7 @@
       <c r="AB411" s="1"/>
       <c r="AC411" s="1"/>
     </row>
-    <row r="412" spans="1:29" ht="13.2">
+    <row r="412" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A412" s="1"/>
       <c r="B412" s="1"/>
       <c r="C412" s="1"/>
@@ -14408,7 +14408,7 @@
       <c r="AB412" s="1"/>
       <c r="AC412" s="1"/>
     </row>
-    <row r="413" spans="1:29" ht="13.2">
+    <row r="413" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A413" s="1"/>
       <c r="B413" s="1"/>
       <c r="C413" s="1"/>
@@ -14439,7 +14439,7 @@
       <c r="AB413" s="1"/>
       <c r="AC413" s="1"/>
     </row>
-    <row r="414" spans="1:29" ht="13.2">
+    <row r="414" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A414" s="1"/>
       <c r="B414" s="1"/>
       <c r="C414" s="1"/>
@@ -14470,7 +14470,7 @@
       <c r="AB414" s="1"/>
       <c r="AC414" s="1"/>
     </row>
-    <row r="415" spans="1:29" ht="13.2">
+    <row r="415" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A415" s="1"/>
       <c r="B415" s="1"/>
       <c r="C415" s="1"/>
@@ -14501,7 +14501,7 @@
       <c r="AB415" s="1"/>
       <c r="AC415" s="1"/>
     </row>
-    <row r="416" spans="1:29" ht="13.2">
+    <row r="416" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A416" s="1"/>
       <c r="B416" s="1"/>
       <c r="C416" s="1"/>
@@ -14532,7 +14532,7 @@
       <c r="AB416" s="1"/>
       <c r="AC416" s="1"/>
     </row>
-    <row r="417" spans="1:29" ht="13.2">
+    <row r="417" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A417" s="1"/>
       <c r="B417" s="1"/>
       <c r="C417" s="1"/>
@@ -14563,7 +14563,7 @@
       <c r="AB417" s="1"/>
       <c r="AC417" s="1"/>
     </row>
-    <row r="418" spans="1:29" ht="13.2">
+    <row r="418" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A418" s="1"/>
       <c r="B418" s="1"/>
       <c r="C418" s="1"/>
@@ -14594,7 +14594,7 @@
       <c r="AB418" s="1"/>
       <c r="AC418" s="1"/>
     </row>
-    <row r="419" spans="1:29" ht="13.2">
+    <row r="419" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A419" s="1"/>
       <c r="B419" s="1"/>
       <c r="C419" s="1"/>
@@ -14625,7 +14625,7 @@
       <c r="AB419" s="1"/>
       <c r="AC419" s="1"/>
     </row>
-    <row r="420" spans="1:29" ht="13.2">
+    <row r="420" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A420" s="1"/>
       <c r="B420" s="1"/>
       <c r="C420" s="1"/>
@@ -14656,7 +14656,7 @@
       <c r="AB420" s="1"/>
       <c r="AC420" s="1"/>
     </row>
-    <row r="421" spans="1:29" ht="13.2">
+    <row r="421" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A421" s="1"/>
       <c r="B421" s="1"/>
       <c r="C421" s="1"/>
@@ -14687,7 +14687,7 @@
       <c r="AB421" s="1"/>
       <c r="AC421" s="1"/>
     </row>
-    <row r="422" spans="1:29" ht="13.2">
+    <row r="422" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A422" s="1"/>
       <c r="B422" s="1"/>
       <c r="C422" s="1"/>
@@ -14718,7 +14718,7 @@
       <c r="AB422" s="1"/>
       <c r="AC422" s="1"/>
     </row>
-    <row r="423" spans="1:29" ht="13.2">
+    <row r="423" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A423" s="1"/>
       <c r="B423" s="1"/>
       <c r="C423" s="1"/>
@@ -14749,7 +14749,7 @@
       <c r="AB423" s="1"/>
       <c r="AC423" s="1"/>
     </row>
-    <row r="424" spans="1:29" ht="13.2">
+    <row r="424" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A424" s="1"/>
       <c r="B424" s="1"/>
       <c r="C424" s="1"/>
@@ -14780,7 +14780,7 @@
       <c r="AB424" s="1"/>
       <c r="AC424" s="1"/>
     </row>
-    <row r="425" spans="1:29" ht="13.2">
+    <row r="425" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A425" s="1"/>
       <c r="B425" s="1"/>
       <c r="C425" s="1"/>
@@ -14811,7 +14811,7 @@
       <c r="AB425" s="1"/>
       <c r="AC425" s="1"/>
     </row>
-    <row r="426" spans="1:29" ht="13.2">
+    <row r="426" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A426" s="1"/>
       <c r="B426" s="1"/>
       <c r="C426" s="1"/>
@@ -14842,7 +14842,7 @@
       <c r="AB426" s="1"/>
       <c r="AC426" s="1"/>
     </row>
-    <row r="427" spans="1:29" ht="13.2">
+    <row r="427" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A427" s="1"/>
       <c r="B427" s="1"/>
       <c r="C427" s="1"/>
@@ -14873,7 +14873,7 @@
       <c r="AB427" s="1"/>
       <c r="AC427" s="1"/>
     </row>
-    <row r="428" spans="1:29" ht="13.2">
+    <row r="428" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A428" s="1"/>
       <c r="B428" s="1"/>
       <c r="C428" s="1"/>
@@ -14904,7 +14904,7 @@
       <c r="AB428" s="1"/>
       <c r="AC428" s="1"/>
     </row>
-    <row r="429" spans="1:29" ht="13.2">
+    <row r="429" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A429" s="1"/>
       <c r="B429" s="1"/>
       <c r="C429" s="1"/>
@@ -14935,7 +14935,7 @@
       <c r="AB429" s="1"/>
       <c r="AC429" s="1"/>
     </row>
-    <row r="430" spans="1:29" ht="13.2">
+    <row r="430" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A430" s="1"/>
       <c r="B430" s="1"/>
       <c r="C430" s="1"/>
@@ -14966,7 +14966,7 @@
       <c r="AB430" s="1"/>
       <c r="AC430" s="1"/>
     </row>
-    <row r="431" spans="1:29" ht="13.2">
+    <row r="431" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A431" s="1"/>
       <c r="B431" s="1"/>
       <c r="C431" s="1"/>
@@ -14997,7 +14997,7 @@
       <c r="AB431" s="1"/>
       <c r="AC431" s="1"/>
     </row>
-    <row r="432" spans="1:29" ht="13.2">
+    <row r="432" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A432" s="1"/>
       <c r="B432" s="1"/>
       <c r="C432" s="1"/>
@@ -15028,7 +15028,7 @@
       <c r="AB432" s="1"/>
       <c r="AC432" s="1"/>
     </row>
-    <row r="433" spans="1:29" ht="13.2">
+    <row r="433" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A433" s="1"/>
       <c r="B433" s="1"/>
       <c r="C433" s="1"/>
@@ -15059,7 +15059,7 @@
       <c r="AB433" s="1"/>
       <c r="AC433" s="1"/>
     </row>
-    <row r="434" spans="1:29" ht="13.2">
+    <row r="434" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A434" s="1"/>
       <c r="B434" s="1"/>
       <c r="C434" s="1"/>
@@ -15090,7 +15090,7 @@
       <c r="AB434" s="1"/>
       <c r="AC434" s="1"/>
     </row>
-    <row r="435" spans="1:29" ht="13.2">
+    <row r="435" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A435" s="1"/>
       <c r="B435" s="1"/>
       <c r="C435" s="1"/>
@@ -15121,7 +15121,7 @@
       <c r="AB435" s="1"/>
       <c r="AC435" s="1"/>
     </row>
-    <row r="436" spans="1:29" ht="13.2">
+    <row r="436" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A436" s="1"/>
       <c r="B436" s="1"/>
       <c r="C436" s="1"/>
@@ -15152,7 +15152,7 @@
       <c r="AB436" s="1"/>
       <c r="AC436" s="1"/>
     </row>
-    <row r="437" spans="1:29" ht="13.2">
+    <row r="437" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A437" s="1"/>
       <c r="B437" s="1"/>
       <c r="C437" s="1"/>
@@ -15183,7 +15183,7 @@
       <c r="AB437" s="1"/>
       <c r="AC437" s="1"/>
     </row>
-    <row r="438" spans="1:29" ht="13.2">
+    <row r="438" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A438" s="1"/>
       <c r="B438" s="1"/>
       <c r="C438" s="1"/>
@@ -15214,7 +15214,7 @@
       <c r="AB438" s="1"/>
       <c r="AC438" s="1"/>
     </row>
-    <row r="439" spans="1:29" ht="13.2">
+    <row r="439" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A439" s="1"/>
       <c r="B439" s="1"/>
       <c r="C439" s="1"/>
@@ -15245,7 +15245,7 @@
       <c r="AB439" s="1"/>
       <c r="AC439" s="1"/>
     </row>
-    <row r="440" spans="1:29" ht="13.2">
+    <row r="440" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A440" s="1"/>
       <c r="B440" s="1"/>
       <c r="C440" s="1"/>
@@ -15276,7 +15276,7 @@
       <c r="AB440" s="1"/>
       <c r="AC440" s="1"/>
     </row>
-    <row r="441" spans="1:29" ht="13.2">
+    <row r="441" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A441" s="1"/>
       <c r="B441" s="1"/>
       <c r="C441" s="1"/>
@@ -15307,7 +15307,7 @@
       <c r="AB441" s="1"/>
       <c r="AC441" s="1"/>
     </row>
-    <row r="442" spans="1:29" ht="13.2">
+    <row r="442" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A442" s="1"/>
       <c r="B442" s="1"/>
       <c r="C442" s="1"/>
@@ -15338,7 +15338,7 @@
       <c r="AB442" s="1"/>
       <c r="AC442" s="1"/>
     </row>
-    <row r="443" spans="1:29" ht="13.2">
+    <row r="443" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A443" s="1"/>
       <c r="B443" s="1"/>
       <c r="C443" s="1"/>
@@ -15369,7 +15369,7 @@
       <c r="AB443" s="1"/>
       <c r="AC443" s="1"/>
     </row>
-    <row r="444" spans="1:29" ht="13.2">
+    <row r="444" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A444" s="1"/>
       <c r="B444" s="1"/>
       <c r="C444" s="1"/>
@@ -15400,7 +15400,7 @@
       <c r="AB444" s="1"/>
       <c r="AC444" s="1"/>
     </row>
-    <row r="445" spans="1:29" ht="13.2">
+    <row r="445" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A445" s="1"/>
       <c r="B445" s="1"/>
       <c r="C445" s="1"/>
@@ -15431,7 +15431,7 @@
       <c r="AB445" s="1"/>
       <c r="AC445" s="1"/>
     </row>
-    <row r="446" spans="1:29" ht="13.2">
+    <row r="446" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A446" s="1"/>
       <c r="B446" s="1"/>
       <c r="C446" s="1"/>
@@ -15462,7 +15462,7 @@
       <c r="AB446" s="1"/>
       <c r="AC446" s="1"/>
     </row>
-    <row r="447" spans="1:29" ht="13.2">
+    <row r="447" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A447" s="1"/>
       <c r="B447" s="1"/>
       <c r="C447" s="1"/>
@@ -15493,7 +15493,7 @@
       <c r="AB447" s="1"/>
       <c r="AC447" s="1"/>
     </row>
-    <row r="448" spans="1:29" ht="13.2">
+    <row r="448" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A448" s="1"/>
       <c r="B448" s="1"/>
       <c r="C448" s="1"/>
@@ -15524,7 +15524,7 @@
       <c r="AB448" s="1"/>
       <c r="AC448" s="1"/>
     </row>
-    <row r="449" spans="1:29" ht="13.2">
+    <row r="449" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A449" s="1"/>
       <c r="B449" s="1"/>
       <c r="C449" s="1"/>
@@ -15555,7 +15555,7 @@
       <c r="AB449" s="1"/>
       <c r="AC449" s="1"/>
     </row>
-    <row r="450" spans="1:29" ht="13.2">
+    <row r="450" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A450" s="1"/>
       <c r="B450" s="1"/>
       <c r="C450" s="1"/>
@@ -15586,7 +15586,7 @@
       <c r="AB450" s="1"/>
       <c r="AC450" s="1"/>
     </row>
-    <row r="451" spans="1:29" ht="13.2">
+    <row r="451" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A451" s="1"/>
       <c r="B451" s="1"/>
       <c r="C451" s="1"/>
@@ -15617,7 +15617,7 @@
       <c r="AB451" s="1"/>
       <c r="AC451" s="1"/>
     </row>
-    <row r="452" spans="1:29" ht="13.2">
+    <row r="452" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A452" s="1"/>
       <c r="B452" s="1"/>
       <c r="C452" s="1"/>
@@ -15648,7 +15648,7 @@
       <c r="AB452" s="1"/>
       <c r="AC452" s="1"/>
     </row>
-    <row r="453" spans="1:29" ht="13.2">
+    <row r="453" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A453" s="1"/>
       <c r="B453" s="1"/>
       <c r="C453" s="1"/>
@@ -15679,7 +15679,7 @@
       <c r="AB453" s="1"/>
       <c r="AC453" s="1"/>
     </row>
-    <row r="454" spans="1:29" ht="13.2">
+    <row r="454" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A454" s="1"/>
       <c r="B454" s="1"/>
       <c r="C454" s="1"/>
@@ -15710,7 +15710,7 @@
       <c r="AB454" s="1"/>
       <c r="AC454" s="1"/>
     </row>
-    <row r="455" spans="1:29" ht="13.2">
+    <row r="455" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A455" s="1"/>
       <c r="B455" s="1"/>
       <c r="C455" s="1"/>
@@ -15741,7 +15741,7 @@
       <c r="AB455" s="1"/>
       <c r="AC455" s="1"/>
     </row>
-    <row r="456" spans="1:29" ht="13.2">
+    <row r="456" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A456" s="1"/>
       <c r="B456" s="1"/>
       <c r="C456" s="1"/>
@@ -15772,7 +15772,7 @@
       <c r="AB456" s="1"/>
       <c r="AC456" s="1"/>
     </row>
-    <row r="457" spans="1:29" ht="13.2">
+    <row r="457" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A457" s="1"/>
       <c r="B457" s="1"/>
       <c r="C457" s="1"/>
@@ -15803,7 +15803,7 @@
       <c r="AB457" s="1"/>
       <c r="AC457" s="1"/>
     </row>
-    <row r="458" spans="1:29" ht="13.2">
+    <row r="458" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A458" s="1"/>
       <c r="B458" s="1"/>
       <c r="C458" s="1"/>
@@ -15834,7 +15834,7 @@
       <c r="AB458" s="1"/>
       <c r="AC458" s="1"/>
     </row>
-    <row r="459" spans="1:29" ht="13.2">
+    <row r="459" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A459" s="1"/>
       <c r="B459" s="1"/>
       <c r="C459" s="1"/>
@@ -15865,7 +15865,7 @@
       <c r="AB459" s="1"/>
       <c r="AC459" s="1"/>
     </row>
-    <row r="460" spans="1:29" ht="13.2">
+    <row r="460" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A460" s="1"/>
       <c r="B460" s="1"/>
       <c r="C460" s="1"/>
@@ -15896,7 +15896,7 @@
       <c r="AB460" s="1"/>
       <c r="AC460" s="1"/>
     </row>
-    <row r="461" spans="1:29" ht="13.2">
+    <row r="461" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A461" s="1"/>
       <c r="B461" s="1"/>
       <c r="C461" s="1"/>
@@ -15927,7 +15927,7 @@
       <c r="AB461" s="1"/>
       <c r="AC461" s="1"/>
     </row>
-    <row r="462" spans="1:29" ht="13.2">
+    <row r="462" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A462" s="1"/>
       <c r="B462" s="1"/>
       <c r="C462" s="1"/>
@@ -15958,7 +15958,7 @@
       <c r="AB462" s="1"/>
       <c r="AC462" s="1"/>
     </row>
-    <row r="463" spans="1:29" ht="13.2">
+    <row r="463" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A463" s="1"/>
       <c r="B463" s="1"/>
       <c r="C463" s="1"/>
@@ -15989,7 +15989,7 @@
       <c r="AB463" s="1"/>
       <c r="AC463" s="1"/>
     </row>
-    <row r="464" spans="1:29" ht="13.2">
+    <row r="464" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A464" s="1"/>
       <c r="B464" s="1"/>
       <c r="C464" s="1"/>
@@ -16020,7 +16020,7 @@
       <c r="AB464" s="1"/>
       <c r="AC464" s="1"/>
     </row>
-    <row r="465" spans="1:29" ht="13.2">
+    <row r="465" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A465" s="1"/>
       <c r="B465" s="1"/>
       <c r="C465" s="1"/>
@@ -16051,7 +16051,7 @@
       <c r="AB465" s="1"/>
       <c r="AC465" s="1"/>
     </row>
-    <row r="466" spans="1:29" ht="13.2">
+    <row r="466" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A466" s="1"/>
       <c r="B466" s="1"/>
       <c r="C466" s="1"/>
@@ -16082,7 +16082,7 @@
       <c r="AB466" s="1"/>
       <c r="AC466" s="1"/>
     </row>
-    <row r="467" spans="1:29" ht="13.2">
+    <row r="467" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A467" s="1"/>
       <c r="B467" s="1"/>
       <c r="C467" s="1"/>
@@ -16113,7 +16113,7 @@
       <c r="AB467" s="1"/>
       <c r="AC467" s="1"/>
     </row>
-    <row r="468" spans="1:29" ht="13.2">
+    <row r="468" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A468" s="1"/>
       <c r="B468" s="1"/>
       <c r="C468" s="1"/>
@@ -16144,7 +16144,7 @@
       <c r="AB468" s="1"/>
       <c r="AC468" s="1"/>
     </row>
-    <row r="469" spans="1:29" ht="13.2">
+    <row r="469" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A469" s="1"/>
       <c r="B469" s="1"/>
       <c r="C469" s="1"/>
@@ -16175,7 +16175,7 @@
       <c r="AB469" s="1"/>
       <c r="AC469" s="1"/>
     </row>
-    <row r="470" spans="1:29" ht="13.2">
+    <row r="470" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A470" s="1"/>
       <c r="B470" s="1"/>
       <c r="C470" s="1"/>
@@ -16206,7 +16206,7 @@
       <c r="AB470" s="1"/>
       <c r="AC470" s="1"/>
     </row>
-    <row r="471" spans="1:29" ht="13.2">
+    <row r="471" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A471" s="1"/>
       <c r="B471" s="1"/>
       <c r="C471" s="1"/>
@@ -16237,7 +16237,7 @@
       <c r="AB471" s="1"/>
       <c r="AC471" s="1"/>
     </row>
-    <row r="472" spans="1:29" ht="13.2">
+    <row r="472" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A472" s="1"/>
       <c r="B472" s="1"/>
       <c r="C472" s="1"/>
@@ -16268,7 +16268,7 @@
       <c r="AB472" s="1"/>
       <c r="AC472" s="1"/>
     </row>
-    <row r="473" spans="1:29" ht="13.2">
+    <row r="473" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A473" s="1"/>
       <c r="B473" s="1"/>
       <c r="C473" s="1"/>
@@ -16299,7 +16299,7 @@
       <c r="AB473" s="1"/>
       <c r="AC473" s="1"/>
     </row>
-    <row r="474" spans="1:29" ht="13.2">
+    <row r="474" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A474" s="1"/>
       <c r="B474" s="1"/>
       <c r="C474" s="1"/>
@@ -16330,7 +16330,7 @@
       <c r="AB474" s="1"/>
       <c r="AC474" s="1"/>
     </row>
-    <row r="475" spans="1:29" ht="13.2">
+    <row r="475" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A475" s="1"/>
       <c r="B475" s="1"/>
       <c r="C475" s="1"/>
@@ -16361,7 +16361,7 @@
       <c r="AB475" s="1"/>
       <c r="AC475" s="1"/>
     </row>
-    <row r="476" spans="1:29" ht="13.2">
+    <row r="476" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A476" s="1"/>
       <c r="B476" s="1"/>
       <c r="C476" s="1"/>
@@ -16392,7 +16392,7 @@
       <c r="AB476" s="1"/>
       <c r="AC476" s="1"/>
     </row>
-    <row r="477" spans="1:29" ht="13.2">
+    <row r="477" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A477" s="1"/>
       <c r="B477" s="1"/>
       <c r="C477" s="1"/>
@@ -16423,7 +16423,7 @@
       <c r="AB477" s="1"/>
       <c r="AC477" s="1"/>
     </row>
-    <row r="478" spans="1:29" ht="13.2">
+    <row r="478" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A478" s="1"/>
       <c r="B478" s="1"/>
       <c r="C478" s="1"/>
@@ -16454,7 +16454,7 @@
       <c r="AB478" s="1"/>
       <c r="AC478" s="1"/>
     </row>
-    <row r="479" spans="1:29" ht="13.2">
+    <row r="479" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A479" s="1"/>
       <c r="B479" s="1"/>
       <c r="C479" s="1"/>
@@ -16485,7 +16485,7 @@
       <c r="AB479" s="1"/>
       <c r="AC479" s="1"/>
     </row>
-    <row r="480" spans="1:29" ht="13.2">
+    <row r="480" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A480" s="1"/>
       <c r="B480" s="1"/>
       <c r="C480" s="1"/>
@@ -16516,7 +16516,7 @@
       <c r="AB480" s="1"/>
       <c r="AC480" s="1"/>
     </row>
-    <row r="481" spans="1:29" ht="13.2">
+    <row r="481" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A481" s="1"/>
       <c r="B481" s="1"/>
       <c r="C481" s="1"/>
@@ -16547,7 +16547,7 @@
       <c r="AB481" s="1"/>
       <c r="AC481" s="1"/>
     </row>
-    <row r="482" spans="1:29" ht="13.2">
+    <row r="482" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A482" s="1"/>
       <c r="B482" s="1"/>
       <c r="C482" s="1"/>
@@ -16578,7 +16578,7 @@
       <c r="AB482" s="1"/>
       <c r="AC482" s="1"/>
     </row>
-    <row r="483" spans="1:29" ht="13.2">
+    <row r="483" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A483" s="1"/>
       <c r="B483" s="1"/>
       <c r="C483" s="1"/>
@@ -16609,7 +16609,7 @@
       <c r="AB483" s="1"/>
       <c r="AC483" s="1"/>
     </row>
-    <row r="484" spans="1:29" ht="13.2">
+    <row r="484" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A484" s="1"/>
       <c r="B484" s="1"/>
       <c r="C484" s="1"/>
@@ -16640,7 +16640,7 @@
       <c r="AB484" s="1"/>
       <c r="AC484" s="1"/>
     </row>
-    <row r="485" spans="1:29" ht="13.2">
+    <row r="485" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A485" s="1"/>
       <c r="B485" s="1"/>
       <c r="C485" s="1"/>
@@ -16671,7 +16671,7 @@
       <c r="AB485" s="1"/>
       <c r="AC485" s="1"/>
     </row>
-    <row r="486" spans="1:29" ht="13.2">
+    <row r="486" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A486" s="1"/>
       <c r="B486" s="1"/>
       <c r="C486" s="1"/>
@@ -16702,7 +16702,7 @@
       <c r="AB486" s="1"/>
       <c r="AC486" s="1"/>
     </row>
-    <row r="487" spans="1:29" ht="13.2">
+    <row r="487" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A487" s="1"/>
       <c r="B487" s="1"/>
       <c r="C487" s="1"/>
@@ -16733,7 +16733,7 @@
       <c r="AB487" s="1"/>
       <c r="AC487" s="1"/>
     </row>
-    <row r="488" spans="1:29" ht="13.2">
+    <row r="488" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A488" s="1"/>
       <c r="B488" s="1"/>
       <c r="C488" s="1"/>
@@ -16764,7 +16764,7 @@
       <c r="AB488" s="1"/>
       <c r="AC488" s="1"/>
     </row>
-    <row r="489" spans="1:29" ht="13.2">
+    <row r="489" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A489" s="1"/>
       <c r="B489" s="1"/>
       <c r="C489" s="1"/>
@@ -16795,7 +16795,7 @@
       <c r="AB489" s="1"/>
       <c r="AC489" s="1"/>
     </row>
-    <row r="490" spans="1:29" ht="13.2">
+    <row r="490" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A490" s="1"/>
       <c r="B490" s="1"/>
       <c r="C490" s="1"/>
@@ -16826,7 +16826,7 @@
       <c r="AB490" s="1"/>
       <c r="AC490" s="1"/>
     </row>
-    <row r="491" spans="1:29" ht="13.2">
+    <row r="491" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A491" s="1"/>
       <c r="B491" s="1"/>
       <c r="C491" s="1"/>
@@ -16857,7 +16857,7 @@
       <c r="AB491" s="1"/>
       <c r="AC491" s="1"/>
     </row>
-    <row r="492" spans="1:29" ht="13.2">
+    <row r="492" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A492" s="1"/>
       <c r="B492" s="1"/>
       <c r="C492" s="1"/>
@@ -16888,7 +16888,7 @@
       <c r="AB492" s="1"/>
       <c r="AC492" s="1"/>
     </row>
-    <row r="493" spans="1:29" ht="13.2">
+    <row r="493" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A493" s="1"/>
       <c r="B493" s="1"/>
       <c r="C493" s="1"/>
@@ -16919,7 +16919,7 @@
       <c r="AB493" s="1"/>
       <c r="AC493" s="1"/>
     </row>
-    <row r="494" spans="1:29" ht="13.2">
+    <row r="494" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A494" s="1"/>
       <c r="B494" s="1"/>
       <c r="C494" s="1"/>
@@ -16950,7 +16950,7 @@
       <c r="AB494" s="1"/>
       <c r="AC494" s="1"/>
     </row>
-    <row r="495" spans="1:29" ht="13.2">
+    <row r="495" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A495" s="1"/>
       <c r="B495" s="1"/>
       <c r="C495" s="1"/>
@@ -16981,7 +16981,7 @@
       <c r="AB495" s="1"/>
       <c r="AC495" s="1"/>
     </row>
-    <row r="496" spans="1:29" ht="13.2">
+    <row r="496" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A496" s="1"/>
       <c r="B496" s="1"/>
       <c r="C496" s="1"/>
@@ -17012,7 +17012,7 @@
       <c r="AB496" s="1"/>
       <c r="AC496" s="1"/>
     </row>
-    <row r="497" spans="1:29" ht="13.2">
+    <row r="497" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A497" s="1"/>
       <c r="B497" s="1"/>
       <c r="C497" s="1"/>
@@ -17043,7 +17043,7 @@
       <c r="AB497" s="1"/>
       <c r="AC497" s="1"/>
     </row>
-    <row r="498" spans="1:29" ht="13.2">
+    <row r="498" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A498" s="1"/>
       <c r="B498" s="1"/>
       <c r="C498" s="1"/>
@@ -17074,7 +17074,7 @@
       <c r="AB498" s="1"/>
       <c r="AC498" s="1"/>
     </row>
-    <row r="499" spans="1:29" ht="13.2">
+    <row r="499" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A499" s="1"/>
       <c r="B499" s="1"/>
       <c r="C499" s="1"/>
@@ -17105,7 +17105,7 @@
       <c r="AB499" s="1"/>
       <c r="AC499" s="1"/>
     </row>
-    <row r="500" spans="1:29" ht="13.2">
+    <row r="500" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A500" s="1"/>
       <c r="B500" s="1"/>
       <c r="C500" s="1"/>
@@ -17136,7 +17136,7 @@
       <c r="AB500" s="1"/>
       <c r="AC500" s="1"/>
     </row>
-    <row r="501" spans="1:29" ht="13.2">
+    <row r="501" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A501" s="1"/>
       <c r="B501" s="1"/>
       <c r="C501" s="1"/>
@@ -17167,7 +17167,7 @@
       <c r="AB501" s="1"/>
       <c r="AC501" s="1"/>
     </row>
-    <row r="502" spans="1:29" ht="13.2">
+    <row r="502" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A502" s="1"/>
       <c r="B502" s="1"/>
       <c r="C502" s="1"/>
@@ -17198,7 +17198,7 @@
       <c r="AB502" s="1"/>
       <c r="AC502" s="1"/>
     </row>
-    <row r="503" spans="1:29" ht="13.2">
+    <row r="503" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A503" s="1"/>
       <c r="B503" s="1"/>
       <c r="C503" s="1"/>
@@ -17229,7 +17229,7 @@
       <c r="AB503" s="1"/>
       <c r="AC503" s="1"/>
     </row>
-    <row r="504" spans="1:29" ht="13.2">
+    <row r="504" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A504" s="1"/>
       <c r="B504" s="1"/>
       <c r="C504" s="1"/>
@@ -17260,7 +17260,7 @@
       <c r="AB504" s="1"/>
       <c r="AC504" s="1"/>
     </row>
-    <row r="505" spans="1:29" ht="13.2">
+    <row r="505" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A505" s="1"/>
       <c r="B505" s="1"/>
       <c r="C505" s="1"/>
@@ -17291,7 +17291,7 @@
       <c r="AB505" s="1"/>
       <c r="AC505" s="1"/>
     </row>
-    <row r="506" spans="1:29" ht="13.2">
+    <row r="506" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A506" s="1"/>
       <c r="B506" s="1"/>
       <c r="C506" s="1"/>
@@ -17322,7 +17322,7 @@
       <c r="AB506" s="1"/>
       <c r="AC506" s="1"/>
     </row>
-    <row r="507" spans="1:29" ht="13.2">
+    <row r="507" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A507" s="1"/>
       <c r="B507" s="1"/>
       <c r="C507" s="1"/>
@@ -17353,7 +17353,7 @@
       <c r="AB507" s="1"/>
       <c r="AC507" s="1"/>
     </row>
-    <row r="508" spans="1:29" ht="13.2">
+    <row r="508" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A508" s="1"/>
       <c r="B508" s="1"/>
       <c r="C508" s="1"/>
@@ -17384,7 +17384,7 @@
       <c r="AB508" s="1"/>
       <c r="AC508" s="1"/>
     </row>
-    <row r="509" spans="1:29" ht="13.2">
+    <row r="509" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A509" s="1"/>
       <c r="B509" s="1"/>
       <c r="C509" s="1"/>
@@ -17415,7 +17415,7 @@
       <c r="AB509" s="1"/>
       <c r="AC509" s="1"/>
     </row>
-    <row r="510" spans="1:29" ht="13.2">
+    <row r="510" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A510" s="1"/>
       <c r="B510" s="1"/>
       <c r="C510" s="1"/>
@@ -17446,7 +17446,7 @@
       <c r="AB510" s="1"/>
       <c r="AC510" s="1"/>
     </row>
-    <row r="511" spans="1:29" ht="13.2">
+    <row r="511" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A511" s="1"/>
       <c r="B511" s="1"/>
       <c r="C511" s="1"/>
@@ -17477,7 +17477,7 @@
       <c r="AB511" s="1"/>
       <c r="AC511" s="1"/>
     </row>
-    <row r="512" spans="1:29" ht="13.2">
+    <row r="512" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A512" s="1"/>
       <c r="B512" s="1"/>
       <c r="C512" s="1"/>
@@ -17508,7 +17508,7 @@
       <c r="AB512" s="1"/>
       <c r="AC512" s="1"/>
     </row>
-    <row r="513" spans="1:29" ht="13.2">
+    <row r="513" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A513" s="1"/>
       <c r="B513" s="1"/>
       <c r="C513" s="1"/>
@@ -17539,7 +17539,7 @@
       <c r="AB513" s="1"/>
       <c r="AC513" s="1"/>
     </row>
-    <row r="514" spans="1:29" ht="13.2">
+    <row r="514" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A514" s="1"/>
       <c r="B514" s="1"/>
       <c r="C514" s="1"/>
@@ -17570,7 +17570,7 @@
       <c r="AB514" s="1"/>
       <c r="AC514" s="1"/>
     </row>
-    <row r="515" spans="1:29" ht="13.2">
+    <row r="515" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A515" s="1"/>
       <c r="B515" s="1"/>
       <c r="C515" s="1"/>
@@ -17601,7 +17601,7 @@
       <c r="AB515" s="1"/>
       <c r="AC515" s="1"/>
     </row>
-    <row r="516" spans="1:29" ht="13.2">
+    <row r="516" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A516" s="1"/>
       <c r="B516" s="1"/>
       <c r="C516" s="1"/>
@@ -17632,7 +17632,7 @@
       <c r="AB516" s="1"/>
       <c r="AC516" s="1"/>
     </row>
-    <row r="517" spans="1:29" ht="13.2">
+    <row r="517" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A517" s="1"/>
       <c r="B517" s="1"/>
       <c r="C517" s="1"/>
@@ -17663,7 +17663,7 @@
       <c r="AB517" s="1"/>
       <c r="AC517" s="1"/>
     </row>
-    <row r="518" spans="1:29" ht="13.2">
+    <row r="518" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A518" s="1"/>
       <c r="B518" s="1"/>
       <c r="C518" s="1"/>
@@ -17694,7 +17694,7 @@
       <c r="AB518" s="1"/>
       <c r="AC518" s="1"/>
     </row>
-    <row r="519" spans="1:29" ht="13.2">
+    <row r="519" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A519" s="1"/>
       <c r="B519" s="1"/>
       <c r="C519" s="1"/>
@@ -17725,7 +17725,7 @@
       <c r="AB519" s="1"/>
       <c r="AC519" s="1"/>
     </row>
-    <row r="520" spans="1:29" ht="13.2">
+    <row r="520" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A520" s="1"/>
       <c r="B520" s="1"/>
       <c r="C520" s="1"/>
@@ -17756,7 +17756,7 @@
       <c r="AB520" s="1"/>
       <c r="AC520" s="1"/>
     </row>
-    <row r="521" spans="1:29" ht="13.2">
+    <row r="521" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A521" s="1"/>
       <c r="B521" s="1"/>
       <c r="C521" s="1"/>
@@ -17787,7 +17787,7 @@
       <c r="AB521" s="1"/>
       <c r="AC521" s="1"/>
     </row>
-    <row r="522" spans="1:29" ht="13.2">
+    <row r="522" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A522" s="1"/>
       <c r="B522" s="1"/>
       <c r="C522" s="1"/>
@@ -17818,7 +17818,7 @@
       <c r="AB522" s="1"/>
       <c r="AC522" s="1"/>
     </row>
-    <row r="523" spans="1:29" ht="13.2">
+    <row r="523" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A523" s="1"/>
       <c r="B523" s="1"/>
       <c r="C523" s="1"/>
@@ -17849,7 +17849,7 @@
       <c r="AB523" s="1"/>
       <c r="AC523" s="1"/>
     </row>
-    <row r="524" spans="1:29" ht="13.2">
+    <row r="524" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A524" s="1"/>
       <c r="B524" s="1"/>
       <c r="C524" s="1"/>
@@ -17880,7 +17880,7 @@
       <c r="AB524" s="1"/>
       <c r="AC524" s="1"/>
     </row>
-    <row r="525" spans="1:29" ht="13.2">
+    <row r="525" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A525" s="1"/>
       <c r="B525" s="1"/>
       <c r="C525" s="1"/>
@@ -17911,7 +17911,7 @@
       <c r="AB525" s="1"/>
       <c r="AC525" s="1"/>
     </row>
-    <row r="526" spans="1:29" ht="13.2">
+    <row r="526" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A526" s="1"/>
       <c r="B526" s="1"/>
       <c r="C526" s="1"/>
@@ -17942,7 +17942,7 @@
       <c r="AB526" s="1"/>
       <c r="AC526" s="1"/>
     </row>
-    <row r="527" spans="1:29" ht="13.2">
+    <row r="527" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A527" s="1"/>
       <c r="B527" s="1"/>
       <c r="C527" s="1"/>
@@ -17973,7 +17973,7 @@
       <c r="AB527" s="1"/>
       <c r="AC527" s="1"/>
     </row>
-    <row r="528" spans="1:29" ht="13.2">
+    <row r="528" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A528" s="1"/>
       <c r="B528" s="1"/>
       <c r="C528" s="1"/>
@@ -18004,7 +18004,7 @@
       <c r="AB528" s="1"/>
       <c r="AC528" s="1"/>
     </row>
-    <row r="529" spans="1:29" ht="13.2">
+    <row r="529" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A529" s="1"/>
       <c r="B529" s="1"/>
       <c r="C529" s="1"/>
@@ -18035,7 +18035,7 @@
       <c r="AB529" s="1"/>
       <c r="AC529" s="1"/>
     </row>
-    <row r="530" spans="1:29" ht="13.2">
+    <row r="530" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A530" s="1"/>
       <c r="B530" s="1"/>
       <c r="C530" s="1"/>
@@ -18066,7 +18066,7 @@
       <c r="AB530" s="1"/>
       <c r="AC530" s="1"/>
     </row>
-    <row r="531" spans="1:29" ht="13.2">
+    <row r="531" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A531" s="1"/>
       <c r="B531" s="1"/>
       <c r="C531" s="1"/>
@@ -18097,7 +18097,7 @@
       <c r="AB531" s="1"/>
       <c r="AC531" s="1"/>
     </row>
-    <row r="532" spans="1:29" ht="13.2">
+    <row r="532" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A532" s="1"/>
       <c r="B532" s="1"/>
       <c r="C532" s="1"/>
@@ -18128,7 +18128,7 @@
       <c r="AB532" s="1"/>
       <c r="AC532" s="1"/>
     </row>
-    <row r="533" spans="1:29" ht="13.2">
+    <row r="533" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A533" s="1"/>
       <c r="B533" s="1"/>
       <c r="C533" s="1"/>
@@ -18159,7 +18159,7 @@
       <c r="AB533" s="1"/>
       <c r="AC533" s="1"/>
     </row>
-    <row r="534" spans="1:29" ht="13.2">
+    <row r="534" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A534" s="1"/>
       <c r="B534" s="1"/>
       <c r="C534" s="1"/>
@@ -18190,7 +18190,7 @@
       <c r="AB534" s="1"/>
       <c r="AC534" s="1"/>
     </row>
-    <row r="535" spans="1:29" ht="13.2">
+    <row r="535" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A535" s="1"/>
       <c r="B535" s="1"/>
       <c r="C535" s="1"/>
@@ -18221,7 +18221,7 @@
       <c r="AB535" s="1"/>
       <c r="AC535" s="1"/>
     </row>
-    <row r="536" spans="1:29" ht="13.2">
+    <row r="536" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A536" s="1"/>
       <c r="B536" s="1"/>
       <c r="C536" s="1"/>
@@ -18252,7 +18252,7 @@
       <c r="AB536" s="1"/>
       <c r="AC536" s="1"/>
     </row>
-    <row r="537" spans="1:29" ht="13.2">
+    <row r="537" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A537" s="1"/>
       <c r="B537" s="1"/>
       <c r="C537" s="1"/>
@@ -18283,7 +18283,7 @@
       <c r="AB537" s="1"/>
       <c r="AC537" s="1"/>
     </row>
-    <row r="538" spans="1:29" ht="13.2">
+    <row r="538" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A538" s="1"/>
       <c r="B538" s="1"/>
       <c r="C538" s="1"/>
@@ -18314,7 +18314,7 @@
       <c r="AB538" s="1"/>
       <c r="AC538" s="1"/>
     </row>
-    <row r="539" spans="1:29" ht="13.2">
+    <row r="539" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A539" s="1"/>
       <c r="B539" s="1"/>
       <c r="C539" s="1"/>
@@ -18345,7 +18345,7 @@
       <c r="AB539" s="1"/>
       <c r="AC539" s="1"/>
     </row>
-    <row r="540" spans="1:29" ht="13.2">
+    <row r="540" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A540" s="1"/>
       <c r="B540" s="1"/>
       <c r="C540" s="1"/>
@@ -18376,7 +18376,7 @@
       <c r="AB540" s="1"/>
       <c r="AC540" s="1"/>
     </row>
-    <row r="541" spans="1:29" ht="13.2">
+    <row r="541" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A541" s="1"/>
       <c r="B541" s="1"/>
       <c r="C541" s="1"/>
@@ -18407,7 +18407,7 @@
       <c r="AB541" s="1"/>
       <c r="AC541" s="1"/>
     </row>
-    <row r="542" spans="1:29" ht="13.2">
+    <row r="542" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A542" s="1"/>
       <c r="B542" s="1"/>
       <c r="C542" s="1"/>
@@ -18438,7 +18438,7 @@
       <c r="AB542" s="1"/>
       <c r="AC542" s="1"/>
     </row>
-    <row r="543" spans="1:29" ht="13.2">
+    <row r="543" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A543" s="1"/>
       <c r="B543" s="1"/>
       <c r="C543" s="1"/>
@@ -18469,7 +18469,7 @@
       <c r="AB543" s="1"/>
       <c r="AC543" s="1"/>
     </row>
-    <row r="544" spans="1:29" ht="13.2">
+    <row r="544" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A544" s="1"/>
       <c r="B544" s="1"/>
       <c r="C544" s="1"/>
@@ -18500,7 +18500,7 @@
       <c r="AB544" s="1"/>
       <c r="AC544" s="1"/>
     </row>
-    <row r="545" spans="1:29" ht="13.2">
+    <row r="545" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A545" s="1"/>
       <c r="B545" s="1"/>
       <c r="C545" s="1"/>
@@ -18531,7 +18531,7 @@
       <c r="AB545" s="1"/>
       <c r="AC545" s="1"/>
     </row>
-    <row r="546" spans="1:29" ht="13.2">
+    <row r="546" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A546" s="1"/>
       <c r="B546" s="1"/>
       <c r="C546" s="1"/>
@@ -18562,7 +18562,7 @@
       <c r="AB546" s="1"/>
       <c r="AC546" s="1"/>
     </row>
-    <row r="547" spans="1:29" ht="13.2">
+    <row r="547" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A547" s="1"/>
       <c r="B547" s="1"/>
       <c r="C547" s="1"/>
@@ -18593,7 +18593,7 @@
       <c r="AB547" s="1"/>
       <c r="AC547" s="1"/>
     </row>
-    <row r="548" spans="1:29" ht="13.2">
+    <row r="548" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A548" s="1"/>
       <c r="B548" s="1"/>
       <c r="C548" s="1"/>
@@ -18624,7 +18624,7 @@
       <c r="AB548" s="1"/>
       <c r="AC548" s="1"/>
     </row>
-    <row r="549" spans="1:29" ht="13.2">
+    <row r="549" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A549" s="1"/>
       <c r="B549" s="1"/>
       <c r="C549" s="1"/>
@@ -18655,7 +18655,7 @@
       <c r="AB549" s="1"/>
       <c r="AC549" s="1"/>
     </row>
-    <row r="550" spans="1:29" ht="13.2">
+    <row r="550" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A550" s="1"/>
       <c r="B550" s="1"/>
       <c r="C550" s="1"/>
@@ -18686,7 +18686,7 @@
       <c r="AB550" s="1"/>
       <c r="AC550" s="1"/>
     </row>
-    <row r="551" spans="1:29" ht="13.2">
+    <row r="551" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A551" s="1"/>
       <c r="B551" s="1"/>
       <c r="C551" s="1"/>
@@ -18717,7 +18717,7 @@
       <c r="AB551" s="1"/>
       <c r="AC551" s="1"/>
     </row>
-    <row r="552" spans="1:29" ht="13.2">
+    <row r="552" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A552" s="1"/>
       <c r="B552" s="1"/>
       <c r="C552" s="1"/>
@@ -18748,7 +18748,7 @@
       <c r="AB552" s="1"/>
       <c r="AC552" s="1"/>
     </row>
-    <row r="553" spans="1:29" ht="13.2">
+    <row r="553" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A553" s="1"/>
       <c r="B553" s="1"/>
       <c r="C553" s="1"/>
@@ -18779,7 +18779,7 @@
       <c r="AB553" s="1"/>
       <c r="AC553" s="1"/>
     </row>
-    <row r="554" spans="1:29" ht="13.2">
+    <row r="554" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A554" s="1"/>
       <c r="B554" s="1"/>
       <c r="C554" s="1"/>
@@ -18810,7 +18810,7 @@
       <c r="AB554" s="1"/>
       <c r="AC554" s="1"/>
     </row>
-    <row r="555" spans="1:29" ht="13.2">
+    <row r="555" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A555" s="1"/>
       <c r="B555" s="1"/>
       <c r="C555" s="1"/>
@@ -18841,7 +18841,7 @@
       <c r="AB555" s="1"/>
       <c r="AC555" s="1"/>
     </row>
-    <row r="556" spans="1:29" ht="13.2">
+    <row r="556" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A556" s="1"/>
       <c r="B556" s="1"/>
       <c r="C556" s="1"/>
@@ -18872,7 +18872,7 @@
       <c r="AB556" s="1"/>
       <c r="AC556" s="1"/>
     </row>
-    <row r="557" spans="1:29" ht="13.2">
+    <row r="557" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A557" s="1"/>
       <c r="B557" s="1"/>
       <c r="C557" s="1"/>
@@ -18903,7 +18903,7 @@
       <c r="AB557" s="1"/>
       <c r="AC557" s="1"/>
     </row>
-    <row r="558" spans="1:29" ht="13.2">
+    <row r="558" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A558" s="1"/>
       <c r="B558" s="1"/>
       <c r="C558" s="1"/>
@@ -18934,7 +18934,7 @@
       <c r="AB558" s="1"/>
       <c r="AC558" s="1"/>
     </row>
-    <row r="559" spans="1:29" ht="13.2">
+    <row r="559" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A559" s="1"/>
       <c r="B559" s="1"/>
       <c r="C559" s="1"/>
@@ -18965,7 +18965,7 @@
       <c r="AB559" s="1"/>
       <c r="AC559" s="1"/>
     </row>
-    <row r="560" spans="1:29" ht="13.2">
+    <row r="560" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A560" s="1"/>
       <c r="B560" s="1"/>
       <c r="C560" s="1"/>
@@ -18996,7 +18996,7 @@
       <c r="AB560" s="1"/>
       <c r="AC560" s="1"/>
     </row>
-    <row r="561" spans="1:29" ht="13.2">
+    <row r="561" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A561" s="1"/>
       <c r="B561" s="1"/>
       <c r="C561" s="1"/>
@@ -19027,7 +19027,7 @@
       <c r="AB561" s="1"/>
       <c r="AC561" s="1"/>
     </row>
-    <row r="562" spans="1:29" ht="13.2">
+    <row r="562" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A562" s="1"/>
       <c r="B562" s="1"/>
       <c r="C562" s="1"/>
@@ -19058,7 +19058,7 @@
       <c r="AB562" s="1"/>
       <c r="AC562" s="1"/>
     </row>
-    <row r="563" spans="1:29" ht="13.2">
+    <row r="563" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A563" s="1"/>
       <c r="B563" s="1"/>
       <c r="C563" s="1"/>
@@ -19089,7 +19089,7 @@
       <c r="AB563" s="1"/>
       <c r="AC563" s="1"/>
     </row>
-    <row r="564" spans="1:29" ht="13.2">
+    <row r="564" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A564" s="1"/>
       <c r="B564" s="1"/>
       <c r="C564" s="1"/>
@@ -19120,7 +19120,7 @@
       <c r="AB564" s="1"/>
       <c r="AC564" s="1"/>
     </row>
-    <row r="565" spans="1:29" ht="13.2">
+    <row r="565" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A565" s="1"/>
       <c r="B565" s="1"/>
       <c r="C565" s="1"/>
@@ -19151,7 +19151,7 @@
       <c r="AB565" s="1"/>
       <c r="AC565" s="1"/>
     </row>
-    <row r="566" spans="1:29" ht="13.2">
+    <row r="566" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A566" s="1"/>
       <c r="B566" s="1"/>
       <c r="C566" s="1"/>
@@ -19182,7 +19182,7 @@
       <c r="AB566" s="1"/>
       <c r="AC566" s="1"/>
     </row>
-    <row r="567" spans="1:29" ht="13.2">
+    <row r="567" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A567" s="1"/>
       <c r="B567" s="1"/>
       <c r="C567" s="1"/>
@@ -19213,7 +19213,7 @@
       <c r="AB567" s="1"/>
       <c r="AC567" s="1"/>
     </row>
-    <row r="568" spans="1:29" ht="13.2">
+    <row r="568" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A568" s="1"/>
       <c r="B568" s="1"/>
       <c r="C568" s="1"/>
@@ -19244,7 +19244,7 @@
       <c r="AB568" s="1"/>
       <c r="AC568" s="1"/>
     </row>
-    <row r="569" spans="1:29" ht="13.2">
+    <row r="569" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A569" s="1"/>
       <c r="B569" s="1"/>
       <c r="C569" s="1"/>
@@ -19275,7 +19275,7 @@
       <c r="AB569" s="1"/>
       <c r="AC569" s="1"/>
     </row>
-    <row r="570" spans="1:29" ht="13.2">
+    <row r="570" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A570" s="1"/>
       <c r="B570" s="1"/>
       <c r="C570" s="1"/>
@@ -19306,7 +19306,7 @@
       <c r="AB570" s="1"/>
       <c r="AC570" s="1"/>
     </row>
-    <row r="571" spans="1:29" ht="13.2">
+    <row r="571" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A571" s="1"/>
       <c r="B571" s="1"/>
       <c r="C571" s="1"/>
@@ -19337,7 +19337,7 @@
       <c r="AB571" s="1"/>
       <c r="AC571" s="1"/>
     </row>
-    <row r="572" spans="1:29" ht="13.2">
+    <row r="572" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A572" s="1"/>
       <c r="B572" s="1"/>
       <c r="C572" s="1"/>
@@ -19368,7 +19368,7 @@
       <c r="AB572" s="1"/>
       <c r="AC572" s="1"/>
     </row>
-    <row r="573" spans="1:29" ht="13.2">
+    <row r="573" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A573" s="1"/>
       <c r="B573" s="1"/>
       <c r="C573" s="1"/>
@@ -19399,7 +19399,7 @@
       <c r="AB573" s="1"/>
       <c r="AC573" s="1"/>
     </row>
-    <row r="574" spans="1:29" ht="13.2">
+    <row r="574" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A574" s="1"/>
       <c r="B574" s="1"/>
       <c r="C574" s="1"/>
@@ -19430,7 +19430,7 @@
       <c r="AB574" s="1"/>
       <c r="AC574" s="1"/>
     </row>
-    <row r="575" spans="1:29" ht="13.2">
+    <row r="575" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A575" s="1"/>
       <c r="B575" s="1"/>
       <c r="C575" s="1"/>
@@ -19461,7 +19461,7 @@
       <c r="AB575" s="1"/>
       <c r="AC575" s="1"/>
     </row>
-    <row r="576" spans="1:29" ht="13.2">
+    <row r="576" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A576" s="1"/>
       <c r="B576" s="1"/>
       <c r="C576" s="1"/>
@@ -19492,7 +19492,7 @@
       <c r="AB576" s="1"/>
       <c r="AC576" s="1"/>
     </row>
-    <row r="577" spans="1:29" ht="13.2">
+    <row r="577" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A577" s="1"/>
       <c r="B577" s="1"/>
       <c r="C577" s="1"/>
@@ -19523,7 +19523,7 @@
       <c r="AB577" s="1"/>
       <c r="AC577" s="1"/>
     </row>
-    <row r="578" spans="1:29" ht="13.2">
+    <row r="578" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A578" s="1"/>
       <c r="B578" s="1"/>
       <c r="C578" s="1"/>
@@ -19554,7 +19554,7 @@
       <c r="AB578" s="1"/>
       <c r="AC578" s="1"/>
     </row>
-    <row r="579" spans="1:29" ht="13.2">
+    <row r="579" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A579" s="1"/>
       <c r="B579" s="1"/>
       <c r="C579" s="1"/>
@@ -19585,7 +19585,7 @@
       <c r="AB579" s="1"/>
       <c r="AC579" s="1"/>
     </row>
-    <row r="580" spans="1:29" ht="13.2">
+    <row r="580" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A580" s="1"/>
       <c r="B580" s="1"/>
       <c r="C580" s="1"/>
@@ -19616,7 +19616,7 @@
       <c r="AB580" s="1"/>
       <c r="AC580" s="1"/>
     </row>
-    <row r="581" spans="1:29" ht="13.2">
+    <row r="581" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A581" s="1"/>
       <c r="B581" s="1"/>
       <c r="C581" s="1"/>
@@ -19647,7 +19647,7 @@
       <c r="AB581" s="1"/>
       <c r="AC581" s="1"/>
     </row>
-    <row r="582" spans="1:29" ht="13.2">
+    <row r="582" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A582" s="1"/>
       <c r="B582" s="1"/>
       <c r="C582" s="1"/>
@@ -19678,7 +19678,7 @@
       <c r="AB582" s="1"/>
       <c r="AC582" s="1"/>
     </row>
-    <row r="583" spans="1:29" ht="13.2">
+    <row r="583" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A583" s="1"/>
       <c r="B583" s="1"/>
       <c r="C583" s="1"/>
@@ -19709,7 +19709,7 @@
       <c r="AB583" s="1"/>
       <c r="AC583" s="1"/>
     </row>
-    <row r="584" spans="1:29" ht="13.2">
+    <row r="584" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A584" s="1"/>
       <c r="B584" s="1"/>
       <c r="C584" s="1"/>
@@ -19740,7 +19740,7 @@
       <c r="AB584" s="1"/>
       <c r="AC584" s="1"/>
     </row>
-    <row r="585" spans="1:29" ht="13.2">
+    <row r="585" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A585" s="1"/>
       <c r="B585" s="1"/>
       <c r="C585" s="1"/>
@@ -19771,7 +19771,7 @@
       <c r="AB585" s="1"/>
       <c r="AC585" s="1"/>
     </row>
-    <row r="586" spans="1:29" ht="13.2">
+    <row r="586" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A586" s="1"/>
       <c r="B586" s="1"/>
       <c r="C586" s="1"/>
@@ -19802,7 +19802,7 @@
       <c r="AB586" s="1"/>
       <c r="AC586" s="1"/>
     </row>
-    <row r="587" spans="1:29" ht="13.2">
+    <row r="587" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A587" s="1"/>
       <c r="B587" s="1"/>
       <c r="C587" s="1"/>
@@ -19833,7 +19833,7 @@
       <c r="AB587" s="1"/>
       <c r="AC587" s="1"/>
     </row>
-    <row r="588" spans="1:29" ht="13.2">
+    <row r="588" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A588" s="1"/>
       <c r="B588" s="1"/>
       <c r="C588" s="1"/>
@@ -19864,7 +19864,7 @@
       <c r="AB588" s="1"/>
       <c r="AC588" s="1"/>
     </row>
-    <row r="589" spans="1:29" ht="13.2">
+    <row r="589" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A589" s="1"/>
       <c r="B589" s="1"/>
       <c r="C589" s="1"/>
@@ -19895,7 +19895,7 @@
       <c r="AB589" s="1"/>
       <c r="AC589" s="1"/>
     </row>
-    <row r="590" spans="1:29" ht="13.2">
+    <row r="590" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A590" s="1"/>
       <c r="B590" s="1"/>
       <c r="C590" s="1"/>
@@ -19926,7 +19926,7 @@
       <c r="AB590" s="1"/>
       <c r="AC590" s="1"/>
     </row>
-    <row r="591" spans="1:29" ht="13.2">
+    <row r="591" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A591" s="1"/>
       <c r="B591" s="1"/>
       <c r="C591" s="1"/>
@@ -19957,7 +19957,7 @@
       <c r="AB591" s="1"/>
       <c r="AC591" s="1"/>
     </row>
-    <row r="592" spans="1:29" ht="13.2">
+    <row r="592" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A592" s="1"/>
       <c r="B592" s="1"/>
       <c r="C592" s="1"/>
@@ -19988,7 +19988,7 @@
       <c r="AB592" s="1"/>
       <c r="AC592" s="1"/>
     </row>
-    <row r="593" spans="1:29" ht="13.2">
+    <row r="593" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A593" s="1"/>
       <c r="B593" s="1"/>
       <c r="C593" s="1"/>
@@ -20019,7 +20019,7 @@
       <c r="AB593" s="1"/>
       <c r="AC593" s="1"/>
     </row>
-    <row r="594" spans="1:29" ht="13.2">
+    <row r="594" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A594" s="1"/>
       <c r="B594" s="1"/>
       <c r="C594" s="1"/>
@@ -20050,7 +20050,7 @@
       <c r="AB594" s="1"/>
       <c r="AC594" s="1"/>
     </row>
-    <row r="595" spans="1:29" ht="13.2">
+    <row r="595" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A595" s="1"/>
       <c r="B595" s="1"/>
       <c r="C595" s="1"/>
@@ -20081,7 +20081,7 @@
       <c r="AB595" s="1"/>
       <c r="AC595" s="1"/>
     </row>
-    <row r="596" spans="1:29" ht="13.2">
+    <row r="596" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A596" s="1"/>
       <c r="B596" s="1"/>
       <c r="C596" s="1"/>
@@ -20112,7 +20112,7 @@
       <c r="AB596" s="1"/>
       <c r="AC596" s="1"/>
     </row>
-    <row r="597" spans="1:29" ht="13.2">
+    <row r="597" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A597" s="1"/>
       <c r="B597" s="1"/>
       <c r="C597" s="1"/>
@@ -20143,7 +20143,7 @@
       <c r="AB597" s="1"/>
       <c r="AC597" s="1"/>
     </row>
-    <row r="598" spans="1:29" ht="13.2">
+    <row r="598" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A598" s="1"/>
       <c r="B598" s="1"/>
       <c r="C598" s="1"/>
@@ -20174,7 +20174,7 @@
       <c r="AB598" s="1"/>
       <c r="AC598" s="1"/>
     </row>
-    <row r="599" spans="1:29" ht="13.2">
+    <row r="599" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A599" s="1"/>
       <c r="B599" s="1"/>
       <c r="C599" s="1"/>
@@ -20205,7 +20205,7 @@
       <c r="AB599" s="1"/>
       <c r="AC599" s="1"/>
     </row>
-    <row r="600" spans="1:29" ht="13.2">
+    <row r="600" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A600" s="1"/>
       <c r="B600" s="1"/>
       <c r="C600" s="1"/>
@@ -20236,7 +20236,7 @@
       <c r="AB600" s="1"/>
       <c r="AC600" s="1"/>
     </row>
-    <row r="601" spans="1:29" ht="13.2">
+    <row r="601" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A601" s="1"/>
       <c r="B601" s="1"/>
       <c r="C601" s="1"/>
@@ -20267,7 +20267,7 @@
       <c r="AB601" s="1"/>
       <c r="AC601" s="1"/>
     </row>
-    <row r="602" spans="1:29" ht="13.2">
+    <row r="602" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A602" s="1"/>
       <c r="B602" s="1"/>
       <c r="C602" s="1"/>
@@ -20298,7 +20298,7 @@
       <c r="AB602" s="1"/>
       <c r="AC602" s="1"/>
     </row>
-    <row r="603" spans="1:29" ht="13.2">
+    <row r="603" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A603" s="1"/>
       <c r="B603" s="1"/>
       <c r="C603" s="1"/>
@@ -20329,7 +20329,7 @@
       <c r="AB603" s="1"/>
       <c r="AC603" s="1"/>
     </row>
-    <row r="604" spans="1:29" ht="13.2">
+    <row r="604" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A604" s="1"/>
       <c r="B604" s="1"/>
       <c r="C604" s="1"/>
@@ -20360,7 +20360,7 @@
       <c r="AB604" s="1"/>
       <c r="AC604" s="1"/>
     </row>
-    <row r="605" spans="1:29" ht="13.2">
+    <row r="605" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A605" s="1"/>
       <c r="B605" s="1"/>
       <c r="C605" s="1"/>
@@ -20391,7 +20391,7 @@
       <c r="AB605" s="1"/>
       <c r="AC605" s="1"/>
     </row>
-    <row r="606" spans="1:29" ht="13.2">
+    <row r="606" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A606" s="1"/>
       <c r="B606" s="1"/>
       <c r="C606" s="1"/>
@@ -20422,7 +20422,7 @@
       <c r="AB606" s="1"/>
       <c r="AC606" s="1"/>
     </row>
-    <row r="607" spans="1:29" ht="13.2">
+    <row r="607" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A607" s="1"/>
       <c r="B607" s="1"/>
       <c r="C607" s="1"/>
@@ -20453,7 +20453,7 @@
       <c r="AB607" s="1"/>
       <c r="AC607" s="1"/>
     </row>
-    <row r="608" spans="1:29" ht="13.2">
+    <row r="608" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A608" s="1"/>
       <c r="B608" s="1"/>
       <c r="C608" s="1"/>
@@ -20484,7 +20484,7 @@
       <c r="AB608" s="1"/>
       <c r="AC608" s="1"/>
     </row>
-    <row r="609" spans="1:29" ht="13.2">
+    <row r="609" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A609" s="1"/>
       <c r="B609" s="1"/>
       <c r="C609" s="1"/>
@@ -20515,7 +20515,7 @@
       <c r="AB609" s="1"/>
       <c r="AC609" s="1"/>
     </row>
-    <row r="610" spans="1:29" ht="13.2">
+    <row r="610" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A610" s="1"/>
       <c r="B610" s="1"/>
       <c r="C610" s="1"/>
@@ -20546,7 +20546,7 @@
       <c r="AB610" s="1"/>
       <c r="AC610" s="1"/>
     </row>
-    <row r="611" spans="1:29" ht="13.2">
+    <row r="611" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A611" s="1"/>
       <c r="B611" s="1"/>
       <c r="C611" s="1"/>
@@ -20577,7 +20577,7 @@
       <c r="AB611" s="1"/>
       <c r="AC611" s="1"/>
     </row>
-    <row r="612" spans="1:29" ht="13.2">
+    <row r="612" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A612" s="1"/>
       <c r="B612" s="1"/>
       <c r="C612" s="1"/>
@@ -20608,7 +20608,7 @@
       <c r="AB612" s="1"/>
       <c r="AC612" s="1"/>
     </row>
-    <row r="613" spans="1:29" ht="13.2">
+    <row r="613" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A613" s="1"/>
       <c r="B613" s="1"/>
       <c r="C613" s="1"/>
@@ -20639,7 +20639,7 @@
       <c r="AB613" s="1"/>
       <c r="AC613" s="1"/>
     </row>
-    <row r="614" spans="1:29" ht="13.2">
+    <row r="614" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A614" s="1"/>
       <c r="B614" s="1"/>
       <c r="C614" s="1"/>
@@ -20670,7 +20670,7 @@
       <c r="AB614" s="1"/>
       <c r="AC614" s="1"/>
     </row>
-    <row r="615" spans="1:29" ht="13.2">
+    <row r="615" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A615" s="1"/>
       <c r="B615" s="1"/>
       <c r="C615" s="1"/>
@@ -20701,7 +20701,7 @@
       <c r="AB615" s="1"/>
       <c r="AC615" s="1"/>
     </row>
-    <row r="616" spans="1:29" ht="13.2">
+    <row r="616" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A616" s="1"/>
       <c r="B616" s="1"/>
       <c r="C616" s="1"/>
@@ -20732,7 +20732,7 @@
       <c r="AB616" s="1"/>
       <c r="AC616" s="1"/>
     </row>
-    <row r="617" spans="1:29" ht="13.2">
+    <row r="617" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A617" s="1"/>
       <c r="B617" s="1"/>
       <c r="C617" s="1"/>
@@ -20763,7 +20763,7 @@
       <c r="AB617" s="1"/>
       <c r="AC617" s="1"/>
     </row>
-    <row r="618" spans="1:29" ht="13.2">
+    <row r="618" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A618" s="1"/>
       <c r="B618" s="1"/>
       <c r="C618" s="1"/>
@@ -20794,7 +20794,7 @@
       <c r="AB618" s="1"/>
       <c r="AC618" s="1"/>
     </row>
-    <row r="619" spans="1:29" ht="13.2">
+    <row r="619" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A619" s="1"/>
       <c r="B619" s="1"/>
       <c r="C619" s="1"/>
@@ -20825,7 +20825,7 @@
       <c r="AB619" s="1"/>
       <c r="AC619" s="1"/>
     </row>
-    <row r="620" spans="1:29" ht="13.2">
+    <row r="620" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A620" s="1"/>
       <c r="B620" s="1"/>
       <c r="C620" s="1"/>
@@ -20856,7 +20856,7 @@
       <c r="AB620" s="1"/>
       <c r="AC620" s="1"/>
     </row>
-    <row r="621" spans="1:29" ht="13.2">
+    <row r="621" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A621" s="1"/>
       <c r="B621" s="1"/>
       <c r="C621" s="1"/>
@@ -20887,7 +20887,7 @@
       <c r="AB621" s="1"/>
       <c r="AC621" s="1"/>
     </row>
-    <row r="622" spans="1:29" ht="13.2">
+    <row r="622" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A622" s="1"/>
       <c r="B622" s="1"/>
       <c r="C622" s="1"/>
@@ -20918,7 +20918,7 @@
       <c r="AB622" s="1"/>
       <c r="AC622" s="1"/>
     </row>
-    <row r="623" spans="1:29" ht="13.2">
+    <row r="623" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A623" s="1"/>
       <c r="B623" s="1"/>
       <c r="C623" s="1"/>
@@ -20949,7 +20949,7 @@
       <c r="AB623" s="1"/>
       <c r="AC623" s="1"/>
     </row>
-    <row r="624" spans="1:29" ht="13.2">
+    <row r="624" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A624" s="1"/>
       <c r="B624" s="1"/>
       <c r="C624" s="1"/>
@@ -20980,7 +20980,7 @@
       <c r="AB624" s="1"/>
       <c r="AC624" s="1"/>
     </row>
-    <row r="625" spans="1:29" ht="13.2">
+    <row r="625" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A625" s="1"/>
       <c r="B625" s="1"/>
       <c r="C625" s="1"/>
@@ -21011,7 +21011,7 @@
       <c r="AB625" s="1"/>
       <c r="AC625" s="1"/>
     </row>
-    <row r="626" spans="1:29" ht="13.2">
+    <row r="626" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A626" s="1"/>
       <c r="B626" s="1"/>
       <c r="C626" s="1"/>
@@ -21042,7 +21042,7 @@
       <c r="AB626" s="1"/>
       <c r="AC626" s="1"/>
     </row>
-    <row r="627" spans="1:29" ht="13.2">
+    <row r="627" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A627" s="1"/>
       <c r="B627" s="1"/>
       <c r="C627" s="1"/>
@@ -21073,7 +21073,7 @@
       <c r="AB627" s="1"/>
       <c r="AC627" s="1"/>
     </row>
-    <row r="628" spans="1:29" ht="13.2">
+    <row r="628" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A628" s="1"/>
       <c r="B628" s="1"/>
       <c r="C628" s="1"/>
@@ -21104,7 +21104,7 @@
       <c r="AB628" s="1"/>
       <c r="AC628" s="1"/>
     </row>
-    <row r="629" spans="1:29" ht="13.2">
+    <row r="629" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A629" s="1"/>
       <c r="B629" s="1"/>
       <c r="C629" s="1"/>
@@ -21135,7 +21135,7 @@
       <c r="AB629" s="1"/>
       <c r="AC629" s="1"/>
     </row>
-    <row r="630" spans="1:29" ht="13.2">
+    <row r="630" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A630" s="1"/>
       <c r="B630" s="1"/>
       <c r="C630" s="1"/>
@@ -21166,7 +21166,7 @@
       <c r="AB630" s="1"/>
       <c r="AC630" s="1"/>
     </row>
-    <row r="631" spans="1:29" ht="13.2">
+    <row r="631" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A631" s="1"/>
       <c r="B631" s="1"/>
       <c r="C631" s="1"/>
@@ -21197,7 +21197,7 @@
       <c r="AB631" s="1"/>
       <c r="AC631" s="1"/>
     </row>
-    <row r="632" spans="1:29" ht="13.2">
+    <row r="632" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A632" s="1"/>
       <c r="B632" s="1"/>
       <c r="C632" s="1"/>
@@ -21228,7 +21228,7 @@
       <c r="AB632" s="1"/>
       <c r="AC632" s="1"/>
     </row>
-    <row r="633" spans="1:29" ht="13.2">
+    <row r="633" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A633" s="1"/>
       <c r="B633" s="1"/>
       <c r="C633" s="1"/>
@@ -21259,7 +21259,7 @@
       <c r="AB633" s="1"/>
       <c r="AC633" s="1"/>
     </row>
-    <row r="634" spans="1:29" ht="13.2">
+    <row r="634" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A634" s="1"/>
       <c r="B634" s="1"/>
       <c r="C634" s="1"/>
@@ -21290,7 +21290,7 @@
       <c r="AB634" s="1"/>
       <c r="AC634" s="1"/>
     </row>
-    <row r="635" spans="1:29" ht="13.2">
+    <row r="635" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A635" s="1"/>
       <c r="B635" s="1"/>
       <c r="C635" s="1"/>
@@ -21321,7 +21321,7 @@
       <c r="AB635" s="1"/>
       <c r="AC635" s="1"/>
     </row>
-    <row r="636" spans="1:29" ht="13.2">
+    <row r="636" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A636" s="1"/>
       <c r="B636" s="1"/>
       <c r="C636" s="1"/>
@@ -21352,7 +21352,7 @@
       <c r="AB636" s="1"/>
       <c r="AC636" s="1"/>
     </row>
-    <row r="637" spans="1:29" ht="13.2">
+    <row r="637" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A637" s="1"/>
       <c r="B637" s="1"/>
       <c r="C637" s="1"/>
@@ -21383,7 +21383,7 @@
       <c r="AB637" s="1"/>
       <c r="AC637" s="1"/>
     </row>
-    <row r="638" spans="1:29" ht="13.2">
+    <row r="638" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A638" s="1"/>
       <c r="B638" s="1"/>
       <c r="C638" s="1"/>
@@ -21414,7 +21414,7 @@
       <c r="AB638" s="1"/>
       <c r="AC638" s="1"/>
     </row>
-    <row r="639" spans="1:29" ht="13.2">
+    <row r="639" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A639" s="1"/>
       <c r="B639" s="1"/>
       <c r="C639" s="1"/>
@@ -21445,7 +21445,7 @@
       <c r="AB639" s="1"/>
       <c r="AC639" s="1"/>
     </row>
-    <row r="640" spans="1:29" ht="13.2">
+    <row r="640" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A640" s="1"/>
       <c r="B640" s="1"/>
       <c r="C640" s="1"/>
@@ -21476,7 +21476,7 @@
       <c r="AB640" s="1"/>
       <c r="AC640" s="1"/>
     </row>
-    <row r="641" spans="1:29" ht="13.2">
+    <row r="641" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A641" s="1"/>
       <c r="B641" s="1"/>
       <c r="C641" s="1"/>
@@ -21507,7 +21507,7 @@
       <c r="AB641" s="1"/>
       <c r="AC641" s="1"/>
     </row>
-    <row r="642" spans="1:29" ht="13.2">
+    <row r="642" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A642" s="1"/>
       <c r="B642" s="1"/>
       <c r="C642" s="1"/>
@@ -21538,7 +21538,7 @@
       <c r="AB642" s="1"/>
       <c r="AC642" s="1"/>
     </row>
-    <row r="643" spans="1:29" ht="13.2">
+    <row r="643" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A643" s="1"/>
       <c r="B643" s="1"/>
       <c r="C643" s="1"/>
@@ -21569,7 +21569,7 @@
       <c r="AB643" s="1"/>
       <c r="AC643" s="1"/>
     </row>
-    <row r="644" spans="1:29" ht="13.2">
+    <row r="644" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A644" s="1"/>
       <c r="B644" s="1"/>
       <c r="C644" s="1"/>
@@ -21600,7 +21600,7 @@
       <c r="AB644" s="1"/>
       <c r="AC644" s="1"/>
     </row>
-    <row r="645" spans="1:29" ht="13.2">
+    <row r="645" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A645" s="1"/>
       <c r="B645" s="1"/>
       <c r="C645" s="1"/>
@@ -21631,7 +21631,7 @@
       <c r="AB645" s="1"/>
       <c r="AC645" s="1"/>
     </row>
-    <row r="646" spans="1:29" ht="13.2">
+    <row r="646" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A646" s="1"/>
       <c r="B646" s="1"/>
       <c r="C646" s="1"/>
@@ -21662,7 +21662,7 @@
       <c r="AB646" s="1"/>
       <c r="AC646" s="1"/>
     </row>
-    <row r="647" spans="1:29" ht="13.2">
+    <row r="647" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A647" s="1"/>
       <c r="B647" s="1"/>
       <c r="C647" s="1"/>
@@ -21693,7 +21693,7 @@
       <c r="AB647" s="1"/>
       <c r="AC647" s="1"/>
     </row>
-    <row r="648" spans="1:29" ht="13.2">
+    <row r="648" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A648" s="1"/>
       <c r="B648" s="1"/>
       <c r="C648" s="1"/>
@@ -21724,7 +21724,7 @@
       <c r="AB648" s="1"/>
       <c r="AC648" s="1"/>
     </row>
-    <row r="649" spans="1:29" ht="13.2">
+    <row r="649" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A649" s="1"/>
       <c r="B649" s="1"/>
       <c r="C649" s="1"/>
@@ -21755,7 +21755,7 @@
       <c r="AB649" s="1"/>
       <c r="AC649" s="1"/>
     </row>
-    <row r="650" spans="1:29" ht="13.2">
+    <row r="650" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A650" s="1"/>
       <c r="B650" s="1"/>
       <c r="C650" s="1"/>
@@ -21786,7 +21786,7 @@
       <c r="AB650" s="1"/>
       <c r="AC650" s="1"/>
     </row>
-    <row r="651" spans="1:29" ht="13.2">
+    <row r="651" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A651" s="1"/>
       <c r="B651" s="1"/>
       <c r="C651" s="1"/>
@@ -21817,7 +21817,7 @@
       <c r="AB651" s="1"/>
       <c r="AC651" s="1"/>
     </row>
-    <row r="652" spans="1:29" ht="13.2">
+    <row r="652" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A652" s="1"/>
       <c r="B652" s="1"/>
       <c r="C652" s="1"/>
@@ -21848,7 +21848,7 @@
       <c r="AB652" s="1"/>
       <c r="AC652" s="1"/>
     </row>
-    <row r="653" spans="1:29" ht="13.2">
+    <row r="653" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A653" s="1"/>
       <c r="B653" s="1"/>
       <c r="C653" s="1"/>
@@ -21879,7 +21879,7 @@
       <c r="AB653" s="1"/>
       <c r="AC653" s="1"/>
     </row>
-    <row r="654" spans="1:29" ht="13.2">
+    <row r="654" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A654" s="1"/>
       <c r="B654" s="1"/>
       <c r="C654" s="1"/>
@@ -21910,7 +21910,7 @@
       <c r="AB654" s="1"/>
       <c r="AC654" s="1"/>
     </row>
-    <row r="655" spans="1:29" ht="13.2">
+    <row r="655" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A655" s="1"/>
       <c r="B655" s="1"/>
       <c r="C655" s="1"/>
@@ -21941,7 +21941,7 @@
       <c r="AB655" s="1"/>
       <c r="AC655" s="1"/>
     </row>
-    <row r="656" spans="1:29" ht="13.2">
+    <row r="656" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A656" s="1"/>
       <c r="B656" s="1"/>
       <c r="C656" s="1"/>
@@ -21972,7 +21972,7 @@
       <c r="AB656" s="1"/>
       <c r="AC656" s="1"/>
     </row>
-    <row r="657" spans="1:29" ht="13.2">
+    <row r="657" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A657" s="1"/>
       <c r="B657" s="1"/>
       <c r="C657" s="1"/>
@@ -22003,7 +22003,7 @@
       <c r="AB657" s="1"/>
       <c r="AC657" s="1"/>
     </row>
-    <row r="658" spans="1:29" ht="13.2">
+    <row r="658" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A658" s="1"/>
       <c r="B658" s="1"/>
       <c r="C658" s="1"/>
@@ -22034,7 +22034,7 @@
       <c r="AB658" s="1"/>
       <c r="AC658" s="1"/>
     </row>
-    <row r="659" spans="1:29" ht="13.2">
+    <row r="659" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A659" s="1"/>
       <c r="B659" s="1"/>
       <c r="C659" s="1"/>
@@ -22065,7 +22065,7 @@
       <c r="AB659" s="1"/>
       <c r="AC659" s="1"/>
     </row>
-    <row r="660" spans="1:29" ht="13.2">
+    <row r="660" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A660" s="1"/>
       <c r="B660" s="1"/>
       <c r="C660" s="1"/>
@@ -22096,7 +22096,7 @@
       <c r="AB660" s="1"/>
       <c r="AC660" s="1"/>
     </row>
-    <row r="661" spans="1:29" ht="13.2">
+    <row r="661" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A661" s="1"/>
       <c r="B661" s="1"/>
       <c r="C661" s="1"/>
@@ -22127,7 +22127,7 @@
       <c r="AB661" s="1"/>
       <c r="AC661" s="1"/>
     </row>
-    <row r="662" spans="1:29" ht="13.2">
+    <row r="662" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A662" s="1"/>
       <c r="B662" s="1"/>
       <c r="C662" s="1"/>
@@ -22158,7 +22158,7 @@
       <c r="AB662" s="1"/>
       <c r="AC662" s="1"/>
     </row>
-    <row r="663" spans="1:29" ht="13.2">
+    <row r="663" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A663" s="1"/>
       <c r="B663" s="1"/>
       <c r="C663" s="1"/>
@@ -22189,7 +22189,7 @@
       <c r="AB663" s="1"/>
       <c r="AC663" s="1"/>
     </row>
-    <row r="664" spans="1:29" ht="13.2">
+    <row r="664" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A664" s="1"/>
       <c r="B664" s="1"/>
       <c r="C664" s="1"/>
@@ -22220,7 +22220,7 @@
       <c r="AB664" s="1"/>
       <c r="AC664" s="1"/>
     </row>
-    <row r="665" spans="1:29" ht="13.2">
+    <row r="665" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A665" s="1"/>
       <c r="B665" s="1"/>
       <c r="C665" s="1"/>
@@ -22251,7 +22251,7 @@
       <c r="AB665" s="1"/>
       <c r="AC665" s="1"/>
     </row>
-    <row r="666" spans="1:29" ht="13.2">
+    <row r="666" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A666" s="1"/>
       <c r="B666" s="1"/>
       <c r="C666" s="1"/>
@@ -22282,7 +22282,7 @@
       <c r="AB666" s="1"/>
       <c r="AC666" s="1"/>
     </row>
-    <row r="667" spans="1:29" ht="13.2">
+    <row r="667" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A667" s="1"/>
       <c r="B667" s="1"/>
       <c r="C667" s="1"/>
@@ -22313,7 +22313,7 @@
       <c r="AB667" s="1"/>
       <c r="AC667" s="1"/>
     </row>
-    <row r="668" spans="1:29" ht="13.2">
+    <row r="668" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A668" s="1"/>
       <c r="B668" s="1"/>
       <c r="C668" s="1"/>
@@ -22344,7 +22344,7 @@
       <c r="AB668" s="1"/>
       <c r="AC668" s="1"/>
     </row>
-    <row r="669" spans="1:29" ht="13.2">
+    <row r="669" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A669" s="1"/>
       <c r="B669" s="1"/>
       <c r="C669" s="1"/>
@@ -22375,7 +22375,7 @@
       <c r="AB669" s="1"/>
       <c r="AC669" s="1"/>
     </row>
-    <row r="670" spans="1:29" ht="13.2">
+    <row r="670" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A670" s="1"/>
       <c r="B670" s="1"/>
       <c r="C670" s="1"/>
@@ -22406,7 +22406,7 @@
       <c r="AB670" s="1"/>
       <c r="AC670" s="1"/>
     </row>
-    <row r="671" spans="1:29" ht="13.2">
+    <row r="671" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A671" s="1"/>
       <c r="B671" s="1"/>
       <c r="C671" s="1"/>
@@ -22437,7 +22437,7 @@
       <c r="AB671" s="1"/>
       <c r="AC671" s="1"/>
     </row>
-    <row r="672" spans="1:29" ht="13.2">
+    <row r="672" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A672" s="1"/>
       <c r="B672" s="1"/>
       <c r="C672" s="1"/>
@@ -22468,7 +22468,7 @@
       <c r="AB672" s="1"/>
       <c r="AC672" s="1"/>
     </row>
-    <row r="673" spans="1:29" ht="13.2">
+    <row r="673" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A673" s="1"/>
       <c r="B673" s="1"/>
       <c r="C673" s="1"/>
@@ -22499,7 +22499,7 @@
       <c r="AB673" s="1"/>
       <c r="AC673" s="1"/>
     </row>
-    <row r="674" spans="1:29" ht="13.2">
+    <row r="674" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A674" s="1"/>
       <c r="B674" s="1"/>
       <c r="C674" s="1"/>
@@ -22530,7 +22530,7 @@
       <c r="AB674" s="1"/>
       <c r="AC674" s="1"/>
     </row>
-    <row r="675" spans="1:29" ht="13.2">
+    <row r="675" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A675" s="1"/>
       <c r="B675" s="1"/>
       <c r="C675" s="1"/>
@@ -22561,7 +22561,7 @@
       <c r="AB675" s="1"/>
       <c r="AC675" s="1"/>
     </row>
-    <row r="676" spans="1:29" ht="13.2">
+    <row r="676" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A676" s="1"/>
       <c r="B676" s="1"/>
       <c r="C676" s="1"/>
@@ -22592,7 +22592,7 @@
       <c r="AB676" s="1"/>
       <c r="AC676" s="1"/>
     </row>
-    <row r="677" spans="1:29" ht="13.2">
+    <row r="677" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A677" s="1"/>
       <c r="B677" s="1"/>
       <c r="C677" s="1"/>
@@ -22623,7 +22623,7 @@
       <c r="AB677" s="1"/>
       <c r="AC677" s="1"/>
     </row>
-    <row r="678" spans="1:29" ht="13.2">
+    <row r="678" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A678" s="1"/>
       <c r="B678" s="1"/>
       <c r="C678" s="1"/>
@@ -22654,7 +22654,7 @@
       <c r="AB678" s="1"/>
       <c r="AC678" s="1"/>
     </row>
-    <row r="679" spans="1:29" ht="13.2">
+    <row r="679" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A679" s="1"/>
       <c r="B679" s="1"/>
       <c r="C679" s="1"/>
@@ -22685,7 +22685,7 @@
       <c r="AB679" s="1"/>
       <c r="AC679" s="1"/>
     </row>
-    <row r="680" spans="1:29" ht="13.2">
+    <row r="680" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A680" s="1"/>
       <c r="B680" s="1"/>
       <c r="C680" s="1"/>
@@ -22716,7 +22716,7 @@
       <c r="AB680" s="1"/>
       <c r="AC680" s="1"/>
     </row>
-    <row r="681" spans="1:29" ht="13.2">
+    <row r="681" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A681" s="1"/>
       <c r="B681" s="1"/>
       <c r="C681" s="1"/>
@@ -22747,7 +22747,7 @@
       <c r="AB681" s="1"/>
       <c r="AC681" s="1"/>
     </row>
-    <row r="682" spans="1:29" ht="13.2">
+    <row r="682" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A682" s="1"/>
       <c r="B682" s="1"/>
       <c r="C682" s="1"/>
@@ -22778,7 +22778,7 @@
       <c r="AB682" s="1"/>
       <c r="AC682" s="1"/>
     </row>
-    <row r="683" spans="1:29" ht="13.2">
+    <row r="683" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A683" s="1"/>
       <c r="B683" s="1"/>
       <c r="C683" s="1"/>
@@ -22809,7 +22809,7 @@
       <c r="AB683" s="1"/>
       <c r="AC683" s="1"/>
     </row>
-    <row r="684" spans="1:29" ht="13.2">
+    <row r="684" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A684" s="1"/>
       <c r="B684" s="1"/>
       <c r="C684" s="1"/>
@@ -22840,7 +22840,7 @@
       <c r="AB684" s="1"/>
       <c r="AC684" s="1"/>
     </row>
-    <row r="685" spans="1:29" ht="13.2">
+    <row r="685" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A685" s="1"/>
       <c r="B685" s="1"/>
       <c r="C685" s="1"/>
@@ -22871,7 +22871,7 @@
       <c r="AB685" s="1"/>
       <c r="AC685" s="1"/>
     </row>
-    <row r="686" spans="1:29" ht="13.2">
+    <row r="686" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A686" s="1"/>
       <c r="B686" s="1"/>
       <c r="C686" s="1"/>
@@ -22902,7 +22902,7 @@
       <c r="AB686" s="1"/>
       <c r="AC686" s="1"/>
     </row>
-    <row r="687" spans="1:29" ht="13.2">
+    <row r="687" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A687" s="1"/>
       <c r="B687" s="1"/>
       <c r="C687" s="1"/>
@@ -22933,7 +22933,7 @@
       <c r="AB687" s="1"/>
       <c r="AC687" s="1"/>
     </row>
-    <row r="688" spans="1:29" ht="13.2">
+    <row r="688" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A688" s="1"/>
       <c r="B688" s="1"/>
       <c r="C688" s="1"/>
@@ -22964,7 +22964,7 @@
       <c r="AB688" s="1"/>
       <c r="AC688" s="1"/>
     </row>
-    <row r="689" spans="1:29" ht="13.2">
+    <row r="689" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A689" s="1"/>
       <c r="B689" s="1"/>
       <c r="C689" s="1"/>
@@ -22995,7 +22995,7 @@
       <c r="AB689" s="1"/>
       <c r="AC689" s="1"/>
     </row>
-    <row r="690" spans="1:29" ht="13.2">
+    <row r="690" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A690" s="1"/>
       <c r="B690" s="1"/>
       <c r="C690" s="1"/>
@@ -23026,7 +23026,7 @@
       <c r="AB690" s="1"/>
       <c r="AC690" s="1"/>
     </row>
-    <row r="691" spans="1:29" ht="13.2">
+    <row r="691" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A691" s="1"/>
       <c r="B691" s="1"/>
       <c r="C691" s="1"/>
@@ -23057,7 +23057,7 @@
       <c r="AB691" s="1"/>
       <c r="AC691" s="1"/>
     </row>
-    <row r="692" spans="1:29" ht="13.2">
+    <row r="692" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A692" s="1"/>
       <c r="B692" s="1"/>
       <c r="C692" s="1"/>
@@ -23088,7 +23088,7 @@
       <c r="AB692" s="1"/>
       <c r="AC692" s="1"/>
     </row>
-    <row r="693" spans="1:29" ht="13.2">
+    <row r="693" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A693" s="1"/>
       <c r="B693" s="1"/>
       <c r="C693" s="1"/>
@@ -23119,7 +23119,7 @@
       <c r="AB693" s="1"/>
       <c r="AC693" s="1"/>
     </row>
-    <row r="694" spans="1:29" ht="13.2">
+    <row r="694" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A694" s="1"/>
       <c r="B694" s="1"/>
       <c r="C694" s="1"/>
@@ -23150,7 +23150,7 @@
       <c r="AB694" s="1"/>
       <c r="AC694" s="1"/>
     </row>
-    <row r="695" spans="1:29" ht="13.2">
+    <row r="695" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A695" s="1"/>
       <c r="B695" s="1"/>
       <c r="C695" s="1"/>
@@ -23181,7 +23181,7 @@
       <c r="AB695" s="1"/>
       <c r="AC695" s="1"/>
     </row>
-    <row r="696" spans="1:29" ht="13.2">
+    <row r="696" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A696" s="1"/>
       <c r="B696" s="1"/>
       <c r="C696" s="1"/>
@@ -23212,7 +23212,7 @@
       <c r="AB696" s="1"/>
       <c r="AC696" s="1"/>
     </row>
-    <row r="697" spans="1:29" ht="13.2">
+    <row r="697" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A697" s="1"/>
       <c r="B697" s="1"/>
       <c r="C697" s="1"/>
@@ -23243,7 +23243,7 @@
       <c r="AB697" s="1"/>
       <c r="AC697" s="1"/>
     </row>
-    <row r="698" spans="1:29" ht="13.2">
+    <row r="698" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A698" s="1"/>
       <c r="B698" s="1"/>
       <c r="C698" s="1"/>
@@ -23274,7 +23274,7 @@
       <c r="AB698" s="1"/>
       <c r="AC698" s="1"/>
     </row>
-    <row r="699" spans="1:29" ht="13.2">
+    <row r="699" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A699" s="1"/>
       <c r="B699" s="1"/>
       <c r="C699" s="1"/>
@@ -23305,7 +23305,7 @@
       <c r="AB699" s="1"/>
       <c r="AC699" s="1"/>
     </row>
-    <row r="700" spans="1:29" ht="13.2">
+    <row r="700" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A700" s="1"/>
       <c r="B700" s="1"/>
       <c r="C700" s="1"/>
@@ -23336,7 +23336,7 @@
       <c r="AB700" s="1"/>
       <c r="AC700" s="1"/>
     </row>
-    <row r="701" spans="1:29" ht="13.2">
+    <row r="701" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A701" s="1"/>
       <c r="B701" s="1"/>
       <c r="C701" s="1"/>
@@ -23367,7 +23367,7 @@
       <c r="AB701" s="1"/>
       <c r="AC701" s="1"/>
     </row>
-    <row r="702" spans="1:29" ht="13.2">
+    <row r="702" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A702" s="1"/>
       <c r="B702" s="1"/>
       <c r="C702" s="1"/>
@@ -23398,7 +23398,7 @@
       <c r="AB702" s="1"/>
       <c r="AC702" s="1"/>
     </row>
-    <row r="703" spans="1:29" ht="13.2">
+    <row r="703" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A703" s="1"/>
       <c r="B703" s="1"/>
       <c r="C703" s="1"/>
@@ -23429,7 +23429,7 @@
       <c r="AB703" s="1"/>
       <c r="AC703" s="1"/>
     </row>
-    <row r="704" spans="1:29" ht="13.2">
+    <row r="704" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A704" s="1"/>
       <c r="B704" s="1"/>
       <c r="C704" s="1"/>
@@ -23460,7 +23460,7 @@
       <c r="AB704" s="1"/>
       <c r="AC704" s="1"/>
     </row>
-    <row r="705" spans="1:29" ht="13.2">
+    <row r="705" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A705" s="1"/>
       <c r="B705" s="1"/>
       <c r="C705" s="1"/>
@@ -23491,7 +23491,7 @@
       <c r="AB705" s="1"/>
       <c r="AC705" s="1"/>
     </row>
-    <row r="706" spans="1:29" ht="13.2">
+    <row r="706" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A706" s="1"/>
       <c r="B706" s="1"/>
       <c r="C706" s="1"/>
@@ -23522,7 +23522,7 @@
       <c r="AB706" s="1"/>
       <c r="AC706" s="1"/>
     </row>
-    <row r="707" spans="1:29" ht="13.2">
+    <row r="707" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A707" s="1"/>
       <c r="B707" s="1"/>
       <c r="C707" s="1"/>
@@ -23553,7 +23553,7 @@
       <c r="AB707" s="1"/>
       <c r="AC707" s="1"/>
     </row>
-    <row r="708" spans="1:29" ht="13.2">
+    <row r="708" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A708" s="1"/>
       <c r="B708" s="1"/>
       <c r="C708" s="1"/>
@@ -23584,7 +23584,7 @@
       <c r="AB708" s="1"/>
       <c r="AC708" s="1"/>
     </row>
-    <row r="709" spans="1:29" ht="13.2">
+    <row r="709" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A709" s="1"/>
       <c r="B709" s="1"/>
       <c r="C709" s="1"/>
@@ -23615,7 +23615,7 @@
       <c r="AB709" s="1"/>
       <c r="AC709" s="1"/>
     </row>
-    <row r="710" spans="1:29" ht="13.2">
+    <row r="710" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A710" s="1"/>
       <c r="B710" s="1"/>
       <c r="C710" s="1"/>
@@ -23646,7 +23646,7 @@
       <c r="AB710" s="1"/>
       <c r="AC710" s="1"/>
     </row>
-    <row r="711" spans="1:29" ht="13.2">
+    <row r="711" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A711" s="1"/>
       <c r="B711" s="1"/>
       <c r="C711" s="1"/>
@@ -23677,7 +23677,7 @@
       <c r="AB711" s="1"/>
       <c r="AC711" s="1"/>
     </row>
-    <row r="712" spans="1:29" ht="13.2">
+    <row r="712" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A712" s="1"/>
       <c r="B712" s="1"/>
       <c r="C712" s="1"/>
@@ -23708,7 +23708,7 @@
       <c r="AB712" s="1"/>
       <c r="AC712" s="1"/>
     </row>
-    <row r="713" spans="1:29" ht="13.2">
+    <row r="713" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A713" s="1"/>
       <c r="B713" s="1"/>
       <c r="C713" s="1"/>
@@ -23739,7 +23739,7 @@
       <c r="AB713" s="1"/>
       <c r="AC713" s="1"/>
     </row>
-    <row r="714" spans="1:29" ht="13.2">
+    <row r="714" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A714" s="1"/>
       <c r="B714" s="1"/>
       <c r="C714" s="1"/>
@@ -23770,7 +23770,7 @@
       <c r="AB714" s="1"/>
       <c r="AC714" s="1"/>
     </row>
-    <row r="715" spans="1:29" ht="13.2">
+    <row r="715" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A715" s="1"/>
       <c r="B715" s="1"/>
       <c r="C715" s="1"/>
@@ -23801,7 +23801,7 @@
       <c r="AB715" s="1"/>
       <c r="AC715" s="1"/>
     </row>
-    <row r="716" spans="1:29" ht="13.2">
+    <row r="716" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A716" s="1"/>
       <c r="B716" s="1"/>
       <c r="C716" s="1"/>
@@ -23832,7 +23832,7 @@
       <c r="AB716" s="1"/>
       <c r="AC716" s="1"/>
     </row>
-    <row r="717" spans="1:29" ht="13.2">
+    <row r="717" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A717" s="1"/>
       <c r="B717" s="1"/>
       <c r="C717" s="1"/>
@@ -23863,7 +23863,7 @@
       <c r="AB717" s="1"/>
       <c r="AC717" s="1"/>
     </row>
-    <row r="718" spans="1:29" ht="13.2">
+    <row r="718" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A718" s="1"/>
       <c r="B718" s="1"/>
       <c r="C718" s="1"/>
@@ -23894,7 +23894,7 @@
       <c r="AB718" s="1"/>
       <c r="AC718" s="1"/>
     </row>
-    <row r="719" spans="1:29" ht="13.2">
+    <row r="719" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A719" s="1"/>
       <c r="B719" s="1"/>
       <c r="C719" s="1"/>
@@ -23925,7 +23925,7 @@
       <c r="AB719" s="1"/>
       <c r="AC719" s="1"/>
     </row>
-    <row r="720" spans="1:29" ht="13.2">
+    <row r="720" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A720" s="1"/>
       <c r="B720" s="1"/>
       <c r="C720" s="1"/>
@@ -23956,7 +23956,7 @@
       <c r="AB720" s="1"/>
       <c r="AC720" s="1"/>
     </row>
-    <row r="721" spans="1:29" ht="13.2">
+    <row r="721" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A721" s="1"/>
       <c r="B721" s="1"/>
       <c r="C721" s="1"/>
@@ -23987,7 +23987,7 @@
       <c r="AB721" s="1"/>
       <c r="AC721" s="1"/>
     </row>
-    <row r="722" spans="1:29" ht="13.2">
+    <row r="722" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A722" s="1"/>
       <c r="B722" s="1"/>
       <c r="C722" s="1"/>
@@ -24018,7 +24018,7 @@
       <c r="AB722" s="1"/>
       <c r="AC722" s="1"/>
     </row>
-    <row r="723" spans="1:29" ht="13.2">
+    <row r="723" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A723" s="1"/>
       <c r="B723" s="1"/>
       <c r="C723" s="1"/>
@@ -24049,7 +24049,7 @@
       <c r="AB723" s="1"/>
       <c r="AC723" s="1"/>
     </row>
-    <row r="724" spans="1:29" ht="13.2">
+    <row r="724" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A724" s="1"/>
       <c r="B724" s="1"/>
       <c r="C724" s="1"/>
@@ -24080,7 +24080,7 @@
       <c r="AB724" s="1"/>
       <c r="AC724" s="1"/>
     </row>
-    <row r="725" spans="1:29" ht="13.2">
+    <row r="725" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A725" s="1"/>
       <c r="B725" s="1"/>
       <c r="C725" s="1"/>
@@ -24111,7 +24111,7 @@
       <c r="AB725" s="1"/>
       <c r="AC725" s="1"/>
     </row>
-    <row r="726" spans="1:29" ht="13.2">
+    <row r="726" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A726" s="1"/>
       <c r="B726" s="1"/>
       <c r="C726" s="1"/>
@@ -24142,7 +24142,7 @@
       <c r="AB726" s="1"/>
       <c r="AC726" s="1"/>
     </row>
-    <row r="727" spans="1:29" ht="13.2">
+    <row r="727" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A727" s="1"/>
       <c r="B727" s="1"/>
       <c r="C727" s="1"/>
@@ -24173,7 +24173,7 @@
       <c r="AB727" s="1"/>
       <c r="AC727" s="1"/>
     </row>
-    <row r="728" spans="1:29" ht="13.2">
+    <row r="728" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A728" s="1"/>
       <c r="B728" s="1"/>
       <c r="C728" s="1"/>
@@ -24204,7 +24204,7 @@
       <c r="AB728" s="1"/>
       <c r="AC728" s="1"/>
     </row>
-    <row r="729" spans="1:29" ht="13.2">
+    <row r="729" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A729" s="1"/>
       <c r="B729" s="1"/>
       <c r="C729" s="1"/>
@@ -24235,7 +24235,7 @@
       <c r="AB729" s="1"/>
       <c r="AC729" s="1"/>
     </row>
-    <row r="730" spans="1:29" ht="13.2">
+    <row r="730" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A730" s="1"/>
       <c r="B730" s="1"/>
       <c r="C730" s="1"/>
@@ -24266,7 +24266,7 @@
       <c r="AB730" s="1"/>
       <c r="AC730" s="1"/>
     </row>
-    <row r="731" spans="1:29" ht="13.2">
+    <row r="731" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A731" s="1"/>
       <c r="B731" s="1"/>
       <c r="C731" s="1"/>
@@ -24297,7 +24297,7 @@
       <c r="AB731" s="1"/>
       <c r="AC731" s="1"/>
     </row>
-    <row r="732" spans="1:29" ht="13.2">
+    <row r="732" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A732" s="1"/>
       <c r="B732" s="1"/>
       <c r="C732" s="1"/>
@@ -24328,7 +24328,7 @@
       <c r="AB732" s="1"/>
       <c r="AC732" s="1"/>
     </row>
-    <row r="733" spans="1:29" ht="13.2">
+    <row r="733" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A733" s="1"/>
       <c r="B733" s="1"/>
       <c r="C733" s="1"/>
@@ -24359,7 +24359,7 @@
       <c r="AB733" s="1"/>
       <c r="AC733" s="1"/>
     </row>
-    <row r="734" spans="1:29" ht="13.2">
+    <row r="734" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A734" s="1"/>
       <c r="B734" s="1"/>
       <c r="C734" s="1"/>
@@ -24390,7 +24390,7 @@
       <c r="AB734" s="1"/>
       <c r="AC734" s="1"/>
     </row>
-    <row r="735" spans="1:29" ht="13.2">
+    <row r="735" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A735" s="1"/>
       <c r="B735" s="1"/>
       <c r="C735" s="1"/>
@@ -24421,7 +24421,7 @@
       <c r="AB735" s="1"/>
       <c r="AC735" s="1"/>
     </row>
-    <row r="736" spans="1:29" ht="13.2">
+    <row r="736" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A736" s="1"/>
       <c r="B736" s="1"/>
       <c r="C736" s="1"/>
@@ -24452,7 +24452,7 @@
       <c r="AB736" s="1"/>
       <c r="AC736" s="1"/>
     </row>
-    <row r="737" spans="1:29" ht="13.2">
+    <row r="737" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A737" s="1"/>
       <c r="B737" s="1"/>
       <c r="C737" s="1"/>
@@ -24483,7 +24483,7 @@
       <c r="AB737" s="1"/>
       <c r="AC737" s="1"/>
     </row>
-    <row r="738" spans="1:29" ht="13.2">
+    <row r="738" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A738" s="1"/>
       <c r="B738" s="1"/>
       <c r="C738" s="1"/>
@@ -24514,7 +24514,7 @@
       <c r="AB738" s="1"/>
       <c r="AC738" s="1"/>
     </row>
-    <row r="739" spans="1:29" ht="13.2">
+    <row r="739" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A739" s="1"/>
       <c r="B739" s="1"/>
       <c r="C739" s="1"/>
@@ -24545,7 +24545,7 @@
       <c r="AB739" s="1"/>
       <c r="AC739" s="1"/>
     </row>
-    <row r="740" spans="1:29" ht="13.2">
+    <row r="740" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A740" s="1"/>
       <c r="B740" s="1"/>
       <c r="C740" s="1"/>
@@ -24576,7 +24576,7 @@
       <c r="AB740" s="1"/>
       <c r="AC740" s="1"/>
     </row>
-    <row r="741" spans="1:29" ht="13.2">
+    <row r="741" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A741" s="1"/>
       <c r="B741" s="1"/>
       <c r="C741" s="1"/>
@@ -24607,7 +24607,7 @@
       <c r="AB741" s="1"/>
       <c r="AC741" s="1"/>
     </row>
-    <row r="742" spans="1:29" ht="13.2">
+    <row r="742" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A742" s="1"/>
       <c r="B742" s="1"/>
       <c r="C742" s="1"/>
@@ -24638,7 +24638,7 @@
       <c r="AB742" s="1"/>
       <c r="AC742" s="1"/>
     </row>
-    <row r="743" spans="1:29" ht="13.2">
+    <row r="743" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A743" s="1"/>
       <c r="B743" s="1"/>
       <c r="C743" s="1"/>
@@ -24669,7 +24669,7 @@
       <c r="AB743" s="1"/>
       <c r="AC743" s="1"/>
     </row>
-    <row r="744" spans="1:29" ht="13.2">
+    <row r="744" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A744" s="1"/>
       <c r="B744" s="1"/>
       <c r="C744" s="1"/>
@@ -24700,7 +24700,7 @@
       <c r="AB744" s="1"/>
       <c r="AC744" s="1"/>
     </row>
-    <row r="745" spans="1:29" ht="13.2">
+    <row r="745" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A745" s="1"/>
       <c r="B745" s="1"/>
       <c r="C745" s="1"/>
@@ -24731,7 +24731,7 @@
       <c r="AB745" s="1"/>
       <c r="AC745" s="1"/>
     </row>
-    <row r="746" spans="1:29" ht="13.2">
+    <row r="746" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A746" s="1"/>
       <c r="B746" s="1"/>
       <c r="C746" s="1"/>
@@ -24762,7 +24762,7 @@
       <c r="AB746" s="1"/>
       <c r="AC746" s="1"/>
     </row>
-    <row r="747" spans="1:29" ht="13.2">
+    <row r="747" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A747" s="1"/>
       <c r="B747" s="1"/>
       <c r="C747" s="1"/>
@@ -24793,7 +24793,7 @@
       <c r="AB747" s="1"/>
       <c r="AC747" s="1"/>
     </row>
-    <row r="748" spans="1:29" ht="13.2">
+    <row r="748" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A748" s="1"/>
       <c r="B748" s="1"/>
       <c r="C748" s="1"/>
@@ -24824,7 +24824,7 @@
       <c r="AB748" s="1"/>
       <c r="AC748" s="1"/>
     </row>
-    <row r="749" spans="1:29" ht="13.2">
+    <row r="749" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A749" s="1"/>
       <c r="B749" s="1"/>
       <c r="C749" s="1"/>
@@ -24855,7 +24855,7 @@
       <c r="AB749" s="1"/>
       <c r="AC749" s="1"/>
     </row>
-    <row r="750" spans="1:29" ht="13.2">
+    <row r="750" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A750" s="1"/>
       <c r="B750" s="1"/>
       <c r="C750" s="1"/>
@@ -24886,7 +24886,7 @@
       <c r="AB750" s="1"/>
       <c r="AC750" s="1"/>
     </row>
-    <row r="751" spans="1:29" ht="13.2">
+    <row r="751" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A751" s="1"/>
       <c r="B751" s="1"/>
       <c r="C751" s="1"/>
@@ -24917,7 +24917,7 @@
       <c r="AB751" s="1"/>
       <c r="AC751" s="1"/>
     </row>
-    <row r="752" spans="1:29" ht="13.2">
+    <row r="752" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A752" s="1"/>
       <c r="B752" s="1"/>
       <c r="C752" s="1"/>
@@ -24948,7 +24948,7 @@
       <c r="AB752" s="1"/>
       <c r="AC752" s="1"/>
     </row>
-    <row r="753" spans="1:29" ht="13.2">
+    <row r="753" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A753" s="1"/>
       <c r="B753" s="1"/>
       <c r="C753" s="1"/>
@@ -24979,7 +24979,7 @@
       <c r="AB753" s="1"/>
       <c r="AC753" s="1"/>
     </row>
-    <row r="754" spans="1:29" ht="13.2">
+    <row r="754" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A754" s="1"/>
       <c r="B754" s="1"/>
       <c r="C754" s="1"/>
@@ -25010,7 +25010,7 @@
       <c r="AB754" s="1"/>
       <c r="AC754" s="1"/>
     </row>
-    <row r="755" spans="1:29" ht="13.2">
+    <row r="755" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A755" s="1"/>
       <c r="B755" s="1"/>
       <c r="C755" s="1"/>
@@ -25041,7 +25041,7 @@
       <c r="AB755" s="1"/>
       <c r="AC755" s="1"/>
     </row>
-    <row r="756" spans="1:29" ht="13.2">
+    <row r="756" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A756" s="1"/>
       <c r="B756" s="1"/>
       <c r="C756" s="1"/>
@@ -25072,7 +25072,7 @@
       <c r="AB756" s="1"/>
       <c r="AC756" s="1"/>
     </row>
-    <row r="757" spans="1:29" ht="13.2">
+    <row r="757" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A757" s="1"/>
       <c r="B757" s="1"/>
       <c r="C757" s="1"/>
@@ -25103,7 +25103,7 @@
       <c r="AB757" s="1"/>
       <c r="AC757" s="1"/>
     </row>
-    <row r="758" spans="1:29" ht="13.2">
+    <row r="758" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A758" s="1"/>
       <c r="B758" s="1"/>
       <c r="C758" s="1"/>
@@ -25134,7 +25134,7 @@
       <c r="AB758" s="1"/>
       <c r="AC758" s="1"/>
     </row>
-    <row r="759" spans="1:29" ht="13.2">
+    <row r="759" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A759" s="1"/>
       <c r="B759" s="1"/>
       <c r="C759" s="1"/>
@@ -25165,7 +25165,7 @@
       <c r="AB759" s="1"/>
       <c r="AC759" s="1"/>
     </row>
-    <row r="760" spans="1:29" ht="13.2">
+    <row r="760" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A760" s="1"/>
       <c r="B760" s="1"/>
       <c r="C760" s="1"/>
@@ -25196,7 +25196,7 @@
       <c r="AB760" s="1"/>
       <c r="AC760" s="1"/>
     </row>
-    <row r="761" spans="1:29" ht="13.2">
+    <row r="761" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A761" s="1"/>
       <c r="B761" s="1"/>
       <c r="C761" s="1"/>
@@ -25227,7 +25227,7 @@
       <c r="AB761" s="1"/>
       <c r="AC761" s="1"/>
     </row>
-    <row r="762" spans="1:29" ht="13.2">
+    <row r="762" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A762" s="1"/>
       <c r="B762" s="1"/>
       <c r="C762" s="1"/>
@@ -25258,7 +25258,7 @@
       <c r="AB762" s="1"/>
       <c r="AC762" s="1"/>
     </row>
-    <row r="763" spans="1:29" ht="13.2">
+    <row r="763" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A763" s="1"/>
       <c r="B763" s="1"/>
       <c r="C763" s="1"/>
@@ -25289,7 +25289,7 @@
       <c r="AB763" s="1"/>
       <c r="AC763" s="1"/>
     </row>
-    <row r="764" spans="1:29" ht="13.2">
+    <row r="764" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A764" s="1"/>
       <c r="B764" s="1"/>
       <c r="C764" s="1"/>
@@ -25320,7 +25320,7 @@
       <c r="AB764" s="1"/>
       <c r="AC764" s="1"/>
     </row>
-    <row r="765" spans="1:29" ht="13.2">
+    <row r="765" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A765" s="1"/>
       <c r="B765" s="1"/>
       <c r="C765" s="1"/>
@@ -25351,7 +25351,7 @@
       <c r="AB765" s="1"/>
       <c r="AC765" s="1"/>
     </row>
-    <row r="766" spans="1:29" ht="13.2">
+    <row r="766" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A766" s="1"/>
       <c r="B766" s="1"/>
       <c r="C766" s="1"/>
@@ -25382,7 +25382,7 @@
       <c r="AB766" s="1"/>
       <c r="AC766" s="1"/>
     </row>
-    <row r="767" spans="1:29" ht="13.2">
+    <row r="767" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A767" s="1"/>
       <c r="B767" s="1"/>
       <c r="C767" s="1"/>
@@ -25413,7 +25413,7 @@
       <c r="AB767" s="1"/>
       <c r="AC767" s="1"/>
     </row>
-    <row r="768" spans="1:29" ht="13.2">
+    <row r="768" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A768" s="1"/>
       <c r="B768" s="1"/>
       <c r="C768" s="1"/>
@@ -25444,7 +25444,7 @@
       <c r="AB768" s="1"/>
       <c r="AC768" s="1"/>
     </row>
-    <row r="769" spans="1:29" ht="13.2">
+    <row r="769" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A769" s="1"/>
       <c r="B769" s="1"/>
       <c r="C769" s="1"/>
@@ -25475,7 +25475,7 @@
       <c r="AB769" s="1"/>
       <c r="AC769" s="1"/>
     </row>
-    <row r="770" spans="1:29" ht="13.2">
+    <row r="770" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A770" s="1"/>
       <c r="B770" s="1"/>
       <c r="C770" s="1"/>
@@ -25506,7 +25506,7 @@
       <c r="AB770" s="1"/>
       <c r="AC770" s="1"/>
     </row>
-    <row r="771" spans="1:29" ht="13.2">
+    <row r="771" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A771" s="1"/>
       <c r="B771" s="1"/>
       <c r="C771" s="1"/>
@@ -25537,7 +25537,7 @@
       <c r="AB771" s="1"/>
       <c r="AC771" s="1"/>
     </row>
-    <row r="772" spans="1:29" ht="13.2">
+    <row r="772" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A772" s="1"/>
       <c r="B772" s="1"/>
       <c r="C772" s="1"/>
@@ -25568,7 +25568,7 @@
       <c r="AB772" s="1"/>
       <c r="AC772" s="1"/>
     </row>
-    <row r="773" spans="1:29" ht="13.2">
+    <row r="773" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A773" s="1"/>
       <c r="B773" s="1"/>
       <c r="C773" s="1"/>
@@ -25599,7 +25599,7 @@
       <c r="AB773" s="1"/>
       <c r="AC773" s="1"/>
     </row>
-    <row r="774" spans="1:29" ht="13.2">
+    <row r="774" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A774" s="1"/>
       <c r="B774" s="1"/>
       <c r="C774" s="1"/>
@@ -25630,7 +25630,7 @@
       <c r="AB774" s="1"/>
       <c r="AC774" s="1"/>
     </row>
-    <row r="775" spans="1:29" ht="13.2">
+    <row r="775" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A775" s="1"/>
       <c r="B775" s="1"/>
       <c r="C775" s="1"/>
@@ -25661,7 +25661,7 @@
       <c r="AB775" s="1"/>
       <c r="AC775" s="1"/>
     </row>
-    <row r="776" spans="1:29" ht="13.2">
+    <row r="776" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A776" s="1"/>
       <c r="B776" s="1"/>
       <c r="C776" s="1"/>
@@ -25692,7 +25692,7 @@
       <c r="AB776" s="1"/>
       <c r="AC776" s="1"/>
     </row>
-    <row r="777" spans="1:29" ht="13.2">
+    <row r="777" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A777" s="1"/>
       <c r="B777" s="1"/>
       <c r="C777" s="1"/>
@@ -25723,7 +25723,7 @@
       <c r="AB777" s="1"/>
       <c r="AC777" s="1"/>
     </row>
-    <row r="778" spans="1:29" ht="13.2">
+    <row r="778" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A778" s="1"/>
       <c r="B778" s="1"/>
       <c r="C778" s="1"/>
@@ -25754,7 +25754,7 @@
       <c r="AB778" s="1"/>
       <c r="AC778" s="1"/>
     </row>
-    <row r="779" spans="1:29" ht="13.2">
+    <row r="779" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A779" s="1"/>
       <c r="B779" s="1"/>
       <c r="C779" s="1"/>
@@ -25785,7 +25785,7 @@
       <c r="AB779" s="1"/>
       <c r="AC779" s="1"/>
     </row>
-    <row r="780" spans="1:29" ht="13.2">
+    <row r="780" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A780" s="1"/>
       <c r="B780" s="1"/>
       <c r="C780" s="1"/>
@@ -25816,7 +25816,7 @@
       <c r="AB780" s="1"/>
       <c r="AC780" s="1"/>
     </row>
-    <row r="781" spans="1:29" ht="13.2">
+    <row r="781" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A781" s="1"/>
       <c r="B781" s="1"/>
       <c r="C781" s="1"/>
@@ -25847,7 +25847,7 @@
       <c r="AB781" s="1"/>
       <c r="AC781" s="1"/>
     </row>
-    <row r="782" spans="1:29" ht="13.2">
+    <row r="782" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A782" s="1"/>
       <c r="B782" s="1"/>
       <c r="C782" s="1"/>
@@ -25878,7 +25878,7 @@
       <c r="AB782" s="1"/>
       <c r="AC782" s="1"/>
     </row>
-    <row r="783" spans="1:29" ht="13.2">
+    <row r="783" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A783" s="1"/>
       <c r="B783" s="1"/>
       <c r="C783" s="1"/>
@@ -25909,7 +25909,7 @@
       <c r="AB783" s="1"/>
       <c r="AC783" s="1"/>
     </row>
-    <row r="784" spans="1:29" ht="13.2">
+    <row r="784" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A784" s="1"/>
       <c r="B784" s="1"/>
       <c r="C784" s="1"/>
@@ -25940,7 +25940,7 @@
       <c r="AB784" s="1"/>
       <c r="AC784" s="1"/>
     </row>
-    <row r="785" spans="1:29" ht="13.2">
+    <row r="785" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A785" s="1"/>
       <c r="B785" s="1"/>
       <c r="C785" s="1"/>
@@ -25971,7 +25971,7 @@
       <c r="AB785" s="1"/>
       <c r="AC785" s="1"/>
     </row>
-    <row r="786" spans="1:29" ht="13.2">
+    <row r="786" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A786" s="1"/>
       <c r="B786" s="1"/>
       <c r="C786" s="1"/>
@@ -26002,7 +26002,7 @@
       <c r="AB786" s="1"/>
       <c r="AC786" s="1"/>
     </row>
-    <row r="787" spans="1:29" ht="13.2">
+    <row r="787" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A787" s="1"/>
       <c r="B787" s="1"/>
       <c r="C787" s="1"/>
@@ -26033,7 +26033,7 @@
       <c r="AB787" s="1"/>
       <c r="AC787" s="1"/>
     </row>
-    <row r="788" spans="1:29" ht="13.2">
+    <row r="788" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A788" s="1"/>
       <c r="B788" s="1"/>
       <c r="C788" s="1"/>
@@ -26064,7 +26064,7 @@
       <c r="AB788" s="1"/>
       <c r="AC788" s="1"/>
     </row>
-    <row r="789" spans="1:29" ht="13.2">
+    <row r="789" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A789" s="1"/>
       <c r="B789" s="1"/>
       <c r="C789" s="1"/>
@@ -26095,7 +26095,7 @@
       <c r="AB789" s="1"/>
       <c r="AC789" s="1"/>
     </row>
-    <row r="790" spans="1:29" ht="13.2">
+    <row r="790" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A790" s="1"/>
       <c r="B790" s="1"/>
       <c r="C790" s="1"/>
@@ -26126,7 +26126,7 @@
       <c r="AB790" s="1"/>
       <c r="AC790" s="1"/>
     </row>
-    <row r="791" spans="1:29" ht="13.2">
+    <row r="791" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A791" s="1"/>
       <c r="B791" s="1"/>
       <c r="C791" s="1"/>
@@ -26157,7 +26157,7 @@
       <c r="AB791" s="1"/>
       <c r="AC791" s="1"/>
     </row>
-    <row r="792" spans="1:29" ht="13.2">
+    <row r="792" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A792" s="1"/>
       <c r="B792" s="1"/>
       <c r="C792" s="1"/>
@@ -26188,7 +26188,7 @@
       <c r="AB792" s="1"/>
       <c r="AC792" s="1"/>
     </row>
-    <row r="793" spans="1:29" ht="13.2">
+    <row r="793" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A793" s="1"/>
       <c r="B793" s="1"/>
       <c r="C793" s="1"/>
@@ -26219,7 +26219,7 @@
       <c r="AB793" s="1"/>
       <c r="AC793" s="1"/>
     </row>
-    <row r="794" spans="1:29" ht="13.2">
+    <row r="794" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A794" s="1"/>
       <c r="B794" s="1"/>
       <c r="C794" s="1"/>
@@ -26250,7 +26250,7 @@
       <c r="AB794" s="1"/>
       <c r="AC794" s="1"/>
     </row>
-    <row r="795" spans="1:29" ht="13.2">
+    <row r="795" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A795" s="1"/>
       <c r="B795" s="1"/>
       <c r="C795" s="1"/>
@@ -26281,7 +26281,7 @@
       <c r="AB795" s="1"/>
       <c r="AC795" s="1"/>
     </row>
-    <row r="796" spans="1:29" ht="13.2">
+    <row r="796" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A796" s="1"/>
       <c r="B796" s="1"/>
       <c r="C796" s="1"/>
@@ -26312,7 +26312,7 @@
       <c r="AB796" s="1"/>
       <c r="AC796" s="1"/>
     </row>
-    <row r="797" spans="1:29" ht="13.2">
+    <row r="797" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A797" s="1"/>
       <c r="B797" s="1"/>
       <c r="C797" s="1"/>
@@ -26343,7 +26343,7 @@
       <c r="AB797" s="1"/>
       <c r="AC797" s="1"/>
     </row>
-    <row r="798" spans="1:29" ht="13.2">
+    <row r="798" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A798" s="1"/>
       <c r="B798" s="1"/>
       <c r="C798" s="1"/>
@@ -26374,7 +26374,7 @@
       <c r="AB798" s="1"/>
       <c r="AC798" s="1"/>
     </row>
-    <row r="799" spans="1:29" ht="13.2">
+    <row r="799" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A799" s="1"/>
       <c r="B799" s="1"/>
       <c r="C799" s="1"/>
@@ -26405,7 +26405,7 @@
       <c r="AB799" s="1"/>
       <c r="AC799" s="1"/>
     </row>
-    <row r="800" spans="1:29" ht="13.2">
+    <row r="800" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A800" s="1"/>
       <c r="B800" s="1"/>
       <c r="C800" s="1"/>
@@ -26436,7 +26436,7 @@
       <c r="AB800" s="1"/>
       <c r="AC800" s="1"/>
     </row>
-    <row r="801" spans="1:29" ht="13.2">
+    <row r="801" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A801" s="1"/>
       <c r="B801" s="1"/>
       <c r="C801" s="1"/>
@@ -26467,7 +26467,7 @@
       <c r="AB801" s="1"/>
       <c r="AC801" s="1"/>
     </row>
-    <row r="802" spans="1:29" ht="13.2">
+    <row r="802" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A802" s="1"/>
       <c r="B802" s="1"/>
       <c r="C802" s="1"/>
@@ -26498,7 +26498,7 @@
       <c r="AB802" s="1"/>
       <c r="AC802" s="1"/>
     </row>
-    <row r="803" spans="1:29" ht="13.2">
+    <row r="803" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A803" s="1"/>
       <c r="B803" s="1"/>
       <c r="C803" s="1"/>
@@ -26529,7 +26529,7 @@
       <c r="AB803" s="1"/>
       <c r="AC803" s="1"/>
     </row>
-    <row r="804" spans="1:29" ht="13.2">
+    <row r="804" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A804" s="1"/>
       <c r="B804" s="1"/>
       <c r="C804" s="1"/>
@@ -26560,7 +26560,7 @@
       <c r="AB804" s="1"/>
       <c r="AC804" s="1"/>
     </row>
-    <row r="805" spans="1:29" ht="13.2">
+    <row r="805" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A805" s="1"/>
       <c r="B805" s="1"/>
       <c r="C805" s="1"/>
@@ -26591,7 +26591,7 @@
       <c r="AB805" s="1"/>
       <c r="AC805" s="1"/>
     </row>
-    <row r="806" spans="1:29" ht="13.2">
+    <row r="806" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A806" s="1"/>
       <c r="B806" s="1"/>
       <c r="C806" s="1"/>
@@ -26622,7 +26622,7 @@
       <c r="AB806" s="1"/>
       <c r="AC806" s="1"/>
     </row>
-    <row r="807" spans="1:29" ht="13.2">
+    <row r="807" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A807" s="1"/>
       <c r="B807" s="1"/>
       <c r="C807" s="1"/>
@@ -26653,7 +26653,7 @@
       <c r="AB807" s="1"/>
       <c r="AC807" s="1"/>
     </row>
-    <row r="808" spans="1:29" ht="13.2">
+    <row r="808" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A808" s="1"/>
       <c r="B808" s="1"/>
       <c r="C808" s="1"/>
@@ -26684,7 +26684,7 @@
       <c r="AB808" s="1"/>
       <c r="AC808" s="1"/>
     </row>
-    <row r="809" spans="1:29" ht="13.2">
+    <row r="809" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A809" s="1"/>
       <c r="B809" s="1"/>
       <c r="C809" s="1"/>
@@ -26715,7 +26715,7 @@
       <c r="AB809" s="1"/>
       <c r="AC809" s="1"/>
     </row>
-    <row r="810" spans="1:29" ht="13.2">
+    <row r="810" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A810" s="1"/>
       <c r="B810" s="1"/>
       <c r="C810" s="1"/>
@@ -26746,7 +26746,7 @@
       <c r="AB810" s="1"/>
       <c r="AC810" s="1"/>
     </row>
-    <row r="811" spans="1:29" ht="13.2">
+    <row r="811" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A811" s="1"/>
       <c r="B811" s="1"/>
       <c r="C811" s="1"/>
@@ -26777,7 +26777,7 @@
       <c r="AB811" s="1"/>
       <c r="AC811" s="1"/>
     </row>
-    <row r="812" spans="1:29" ht="13.2">
+    <row r="812" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A812" s="1"/>
       <c r="B812" s="1"/>
       <c r="C812" s="1"/>
@@ -26808,7 +26808,7 @@
       <c r="AB812" s="1"/>
       <c r="AC812" s="1"/>
     </row>
-    <row r="813" spans="1:29" ht="13.2">
+    <row r="813" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A813" s="1"/>
       <c r="B813" s="1"/>
       <c r="C813" s="1"/>
@@ -26839,7 +26839,7 @@
       <c r="AB813" s="1"/>
       <c r="AC813" s="1"/>
     </row>
-    <row r="814" spans="1:29" ht="13.2">
+    <row r="814" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A814" s="1"/>
       <c r="B814" s="1"/>
       <c r="C814" s="1"/>
@@ -26870,7 +26870,7 @@
       <c r="AB814" s="1"/>
       <c r="AC814" s="1"/>
     </row>
-    <row r="815" spans="1:29" ht="13.2">
+    <row r="815" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A815" s="1"/>
       <c r="B815" s="1"/>
       <c r="C815" s="1"/>
@@ -26901,7 +26901,7 @@
       <c r="AB815" s="1"/>
       <c r="AC815" s="1"/>
     </row>
-    <row r="816" spans="1:29" ht="13.2">
+    <row r="816" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A816" s="1"/>
       <c r="B816" s="1"/>
       <c r="C816" s="1"/>
@@ -26932,7 +26932,7 @@
       <c r="AB816" s="1"/>
       <c r="AC816" s="1"/>
     </row>
-    <row r="817" spans="1:29" ht="13.2">
+    <row r="817" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A817" s="1"/>
       <c r="B817" s="1"/>
       <c r="C817" s="1"/>
@@ -26963,7 +26963,7 @@
       <c r="AB817" s="1"/>
       <c r="AC817" s="1"/>
     </row>
-    <row r="818" spans="1:29" ht="13.2">
+    <row r="818" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A818" s="1"/>
       <c r="B818" s="1"/>
       <c r="C818" s="1"/>
@@ -26994,7 +26994,7 @@
       <c r="AB818" s="1"/>
       <c r="AC818" s="1"/>
     </row>
-    <row r="819" spans="1:29" ht="13.2">
+    <row r="819" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A819" s="1"/>
       <c r="B819" s="1"/>
       <c r="C819" s="1"/>
@@ -27025,7 +27025,7 @@
       <c r="AB819" s="1"/>
       <c r="AC819" s="1"/>
     </row>
-    <row r="820" spans="1:29" ht="13.2">
+    <row r="820" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A820" s="1"/>
       <c r="B820" s="1"/>
       <c r="C820" s="1"/>
@@ -27056,7 +27056,7 @@
       <c r="AB820" s="1"/>
       <c r="AC820" s="1"/>
     </row>
-    <row r="821" spans="1:29" ht="13.2">
+    <row r="821" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A821" s="1"/>
       <c r="B821" s="1"/>
       <c r="C821" s="1"/>
@@ -27087,7 +27087,7 @@
       <c r="AB821" s="1"/>
       <c r="AC821" s="1"/>
     </row>
-    <row r="822" spans="1:29" ht="13.2">
+    <row r="822" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A822" s="1"/>
       <c r="B822" s="1"/>
       <c r="C822" s="1"/>
@@ -27118,7 +27118,7 @@
       <c r="AB822" s="1"/>
       <c r="AC822" s="1"/>
     </row>
-    <row r="823" spans="1:29" ht="13.2">
+    <row r="823" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A823" s="1"/>
       <c r="B823" s="1"/>
       <c r="C823" s="1"/>
@@ -27149,7 +27149,7 @@
       <c r="AB823" s="1"/>
       <c r="AC823" s="1"/>
     </row>
-    <row r="824" spans="1:29" ht="13.2">
+    <row r="824" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A824" s="1"/>
       <c r="B824" s="1"/>
       <c r="C824" s="1"/>
@@ -27180,7 +27180,7 @@
       <c r="AB824" s="1"/>
       <c r="AC824" s="1"/>
     </row>
-    <row r="825" spans="1:29" ht="13.2">
+    <row r="825" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A825" s="1"/>
       <c r="B825" s="1"/>
       <c r="C825" s="1"/>
@@ -27211,7 +27211,7 @@
       <c r="AB825" s="1"/>
       <c r="AC825" s="1"/>
     </row>
-    <row r="826" spans="1:29" ht="13.2">
+    <row r="826" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A826" s="1"/>
       <c r="B826" s="1"/>
       <c r="C826" s="1"/>
@@ -27242,7 +27242,7 @@
       <c r="AB826" s="1"/>
       <c r="AC826" s="1"/>
     </row>
-    <row r="827" spans="1:29" ht="13.2">
+    <row r="827" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A827" s="1"/>
       <c r="B827" s="1"/>
       <c r="C827" s="1"/>
@@ -27273,7 +27273,7 @@
       <c r="AB827" s="1"/>
       <c r="AC827" s="1"/>
     </row>
-    <row r="828" spans="1:29" ht="13.2">
+    <row r="828" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A828" s="1"/>
       <c r="B828" s="1"/>
       <c r="C828" s="1"/>
@@ -27304,7 +27304,7 @@
       <c r="AB828" s="1"/>
       <c r="AC828" s="1"/>
     </row>
-    <row r="829" spans="1:29" ht="13.2">
+    <row r="829" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A829" s="1"/>
       <c r="B829" s="1"/>
       <c r="C829" s="1"/>
@@ -27335,7 +27335,7 @@
       <c r="AB829" s="1"/>
       <c r="AC829" s="1"/>
     </row>
-    <row r="830" spans="1:29" ht="13.2">
+    <row r="830" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A830" s="1"/>
       <c r="B830" s="1"/>
       <c r="C830" s="1"/>
@@ -27366,7 +27366,7 @@
       <c r="AB830" s="1"/>
       <c r="AC830" s="1"/>
     </row>
-    <row r="831" spans="1:29" ht="13.2">
+    <row r="831" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A831" s="1"/>
       <c r="B831" s="1"/>
       <c r="C831" s="1"/>
@@ -27397,7 +27397,7 @@
       <c r="AB831" s="1"/>
       <c r="AC831" s="1"/>
     </row>
-    <row r="832" spans="1:29" ht="13.2">
+    <row r="832" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A832" s="1"/>
       <c r="B832" s="1"/>
       <c r="C832" s="1"/>
@@ -27428,7 +27428,7 @@
       <c r="AB832" s="1"/>
       <c r="AC832" s="1"/>
     </row>
-    <row r="833" spans="1:29" ht="13.2">
+    <row r="833" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A833" s="1"/>
       <c r="B833" s="1"/>
       <c r="C833" s="1"/>
@@ -27459,7 +27459,7 @@
       <c r="AB833" s="1"/>
       <c r="AC833" s="1"/>
     </row>
-    <row r="834" spans="1:29" ht="13.2">
+    <row r="834" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A834" s="1"/>
       <c r="B834" s="1"/>
       <c r="C834" s="1"/>
@@ -27490,7 +27490,7 @@
       <c r="AB834" s="1"/>
       <c r="AC834" s="1"/>
     </row>
-    <row r="835" spans="1:29" ht="13.2">
+    <row r="835" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A835" s="1"/>
       <c r="B835" s="1"/>
       <c r="C835" s="1"/>
@@ -27521,7 +27521,7 @@
       <c r="AB835" s="1"/>
       <c r="AC835" s="1"/>
     </row>
-    <row r="836" spans="1:29" ht="13.2">
+    <row r="836" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A836" s="1"/>
       <c r="B836" s="1"/>
       <c r="C836" s="1"/>
@@ -27552,7 +27552,7 @@
       <c r="AB836" s="1"/>
       <c r="AC836" s="1"/>
     </row>
-    <row r="837" spans="1:29" ht="13.2">
+    <row r="837" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A837" s="1"/>
       <c r="B837" s="1"/>
       <c r="C837" s="1"/>
@@ -27583,7 +27583,7 @@
       <c r="AB837" s="1"/>
       <c r="AC837" s="1"/>
     </row>
-    <row r="838" spans="1:29" ht="13.2">
+    <row r="838" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A838" s="1"/>
       <c r="B838" s="1"/>
       <c r="C838" s="1"/>
@@ -27614,7 +27614,7 @@
       <c r="AB838" s="1"/>
       <c r="AC838" s="1"/>
     </row>
-    <row r="839" spans="1:29" ht="13.2">
+    <row r="839" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A839" s="1"/>
       <c r="B839" s="1"/>
       <c r="C839" s="1"/>
@@ -27645,7 +27645,7 @@
       <c r="AB839" s="1"/>
       <c r="AC839" s="1"/>
     </row>
-    <row r="840" spans="1:29" ht="13.2">
+    <row r="840" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A840" s="1"/>
       <c r="B840" s="1"/>
       <c r="C840" s="1"/>
@@ -27676,7 +27676,7 @@
       <c r="AB840" s="1"/>
       <c r="AC840" s="1"/>
     </row>
-    <row r="841" spans="1:29" ht="13.2">
+    <row r="841" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A841" s="1"/>
       <c r="B841" s="1"/>
       <c r="C841" s="1"/>
@@ -27707,7 +27707,7 @@
       <c r="AB841" s="1"/>
       <c r="AC841" s="1"/>
     </row>
-    <row r="842" spans="1:29" ht="13.2">
+    <row r="842" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A842" s="1"/>
       <c r="B842" s="1"/>
       <c r="C842" s="1"/>
@@ -27738,7 +27738,7 @@
       <c r="AB842" s="1"/>
       <c r="AC842" s="1"/>
     </row>
-    <row r="843" spans="1:29" ht="13.2">
+    <row r="843" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A843" s="1"/>
       <c r="B843" s="1"/>
       <c r="C843" s="1"/>
@@ -27769,7 +27769,7 @@
       <c r="AB843" s="1"/>
       <c r="AC843" s="1"/>
     </row>
-    <row r="844" spans="1:29" ht="13.2">
+    <row r="844" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A844" s="1"/>
       <c r="B844" s="1"/>
       <c r="C844" s="1"/>
@@ -27800,7 +27800,7 @@
       <c r="AB844" s="1"/>
       <c r="AC844" s="1"/>
     </row>
-    <row r="845" spans="1:29" ht="13.2">
+    <row r="845" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A845" s="1"/>
       <c r="B845" s="1"/>
       <c r="C845" s="1"/>
@@ -27831,7 +27831,7 @@
       <c r="AB845" s="1"/>
       <c r="AC845" s="1"/>
     </row>
-    <row r="846" spans="1:29" ht="13.2">
+    <row r="846" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A846" s="1"/>
       <c r="B846" s="1"/>
       <c r="C846" s="1"/>
@@ -27862,7 +27862,7 @@
       <c r="AB846" s="1"/>
       <c r="AC846" s="1"/>
     </row>
-    <row r="847" spans="1:29" ht="13.2">
+    <row r="847" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A847" s="1"/>
       <c r="B847" s="1"/>
       <c r="C847" s="1"/>
@@ -27893,7 +27893,7 @@
       <c r="AB847" s="1"/>
       <c r="AC847" s="1"/>
     </row>
-    <row r="848" spans="1:29" ht="13.2">
+    <row r="848" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A848" s="1"/>
       <c r="B848" s="1"/>
       <c r="C848" s="1"/>
@@ -27924,7 +27924,7 @@
       <c r="AB848" s="1"/>
       <c r="AC848" s="1"/>
     </row>
-    <row r="849" spans="1:29" ht="13.2">
+    <row r="849" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A849" s="1"/>
       <c r="B849" s="1"/>
       <c r="C849" s="1"/>
@@ -27955,7 +27955,7 @@
       <c r="AB849" s="1"/>
       <c r="AC849" s="1"/>
     </row>
-    <row r="850" spans="1:29" ht="13.2">
+    <row r="850" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A850" s="1"/>
       <c r="B850" s="1"/>
       <c r="C850" s="1"/>
@@ -27986,7 +27986,7 @@
       <c r="AB850" s="1"/>
       <c r="AC850" s="1"/>
     </row>
-    <row r="851" spans="1:29" ht="13.2">
+    <row r="851" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A851" s="1"/>
       <c r="B851" s="1"/>
       <c r="C851" s="1"/>
@@ -28017,7 +28017,7 @@
       <c r="AB851" s="1"/>
       <c r="AC851" s="1"/>
     </row>
-    <row r="852" spans="1:29" ht="13.2">
+    <row r="852" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A852" s="1"/>
       <c r="B852" s="1"/>
       <c r="C852" s="1"/>
@@ -28048,7 +28048,7 @@
       <c r="AB852" s="1"/>
       <c r="AC852" s="1"/>
     </row>
-    <row r="853" spans="1:29" ht="13.2">
+    <row r="853" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A853" s="1"/>
       <c r="B853" s="1"/>
       <c r="C853" s="1"/>
@@ -28079,7 +28079,7 @@
       <c r="AB853" s="1"/>
       <c r="AC853" s="1"/>
     </row>
-    <row r="854" spans="1:29" ht="13.2">
+    <row r="854" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A854" s="1"/>
       <c r="B854" s="1"/>
       <c r="C854" s="1"/>
@@ -28110,7 +28110,7 @@
       <c r="AB854" s="1"/>
       <c r="AC854" s="1"/>
     </row>
-    <row r="855" spans="1:29" ht="13.2">
+    <row r="855" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A855" s="1"/>
       <c r="B855" s="1"/>
       <c r="C855" s="1"/>
@@ -28141,7 +28141,7 @@
       <c r="AB855" s="1"/>
       <c r="AC855" s="1"/>
     </row>
-    <row r="856" spans="1:29" ht="13.2">
+    <row r="856" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A856" s="1"/>
       <c r="B856" s="1"/>
       <c r="C856" s="1"/>
@@ -28172,7 +28172,7 @@
       <c r="AB856" s="1"/>
       <c r="AC856" s="1"/>
     </row>
-    <row r="857" spans="1:29" ht="13.2">
+    <row r="857" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A857" s="1"/>
       <c r="B857" s="1"/>
       <c r="C857" s="1"/>
@@ -28203,7 +28203,7 @@
       <c r="AB857" s="1"/>
       <c r="AC857" s="1"/>
     </row>
-    <row r="858" spans="1:29" ht="13.2">
+    <row r="858" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A858" s="1"/>
       <c r="B858" s="1"/>
       <c r="C858" s="1"/>
@@ -28234,7 +28234,7 @@
       <c r="AB858" s="1"/>
       <c r="AC858" s="1"/>
     </row>
-    <row r="859" spans="1:29" ht="13.2">
+    <row r="859" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A859" s="1"/>
       <c r="B859" s="1"/>
       <c r="C859" s="1"/>
@@ -28265,7 +28265,7 @@
       <c r="AB859" s="1"/>
       <c r="AC859" s="1"/>
     </row>
-    <row r="860" spans="1:29" ht="13.2">
+    <row r="860" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A860" s="1"/>
       <c r="B860" s="1"/>
       <c r="C860" s="1"/>
@@ -28296,7 +28296,7 @@
       <c r="AB860" s="1"/>
       <c r="AC860" s="1"/>
     </row>
-    <row r="861" spans="1:29" ht="13.2">
+    <row r="861" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A861" s="1"/>
       <c r="B861" s="1"/>
       <c r="C861" s="1"/>
@@ -28327,7 +28327,7 @@
       <c r="AB861" s="1"/>
       <c r="AC861" s="1"/>
     </row>
-    <row r="862" spans="1:29" ht="13.2">
+    <row r="862" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A862" s="1"/>
       <c r="B862" s="1"/>
       <c r="C862" s="1"/>
@@ -28358,7 +28358,7 @@
       <c r="AB862" s="1"/>
       <c r="AC862" s="1"/>
     </row>
-    <row r="863" spans="1:29" ht="13.2">
+    <row r="863" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A863" s="1"/>
       <c r="B863" s="1"/>
       <c r="C863" s="1"/>
@@ -28389,7 +28389,7 @@
       <c r="AB863" s="1"/>
       <c r="AC863" s="1"/>
     </row>
-    <row r="864" spans="1:29" ht="13.2">
+    <row r="864" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A864" s="1"/>
       <c r="B864" s="1"/>
       <c r="C864" s="1"/>
@@ -28420,7 +28420,7 @@
       <c r="AB864" s="1"/>
       <c r="AC864" s="1"/>
     </row>
-    <row r="865" spans="1:29" ht="13.2">
+    <row r="865" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A865" s="1"/>
       <c r="B865" s="1"/>
       <c r="C865" s="1"/>
@@ -28451,7 +28451,7 @@
       <c r="AB865" s="1"/>
       <c r="AC865" s="1"/>
     </row>
-    <row r="866" spans="1:29" ht="13.2">
+    <row r="866" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A866" s="1"/>
       <c r="B866" s="1"/>
       <c r="C866" s="1"/>
@@ -28482,7 +28482,7 @@
       <c r="AB866" s="1"/>
       <c r="AC866" s="1"/>
     </row>
-    <row r="867" spans="1:29" ht="13.2">
+    <row r="867" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A867" s="1"/>
       <c r="B867" s="1"/>
       <c r="C867" s="1"/>
@@ -28513,7 +28513,7 @@
       <c r="AB867" s="1"/>
       <c r="AC867" s="1"/>
     </row>
-    <row r="868" spans="1:29" ht="13.2">
+    <row r="868" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A868" s="1"/>
       <c r="B868" s="1"/>
       <c r="C868" s="1"/>
@@ -28544,7 +28544,7 @@
       <c r="AB868" s="1"/>
       <c r="AC868" s="1"/>
     </row>
-    <row r="869" spans="1:29" ht="13.2">
+    <row r="869" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A869" s="1"/>
       <c r="B869" s="1"/>
       <c r="C869" s="1"/>
@@ -28575,7 +28575,7 @@
       <c r="AB869" s="1"/>
       <c r="AC869" s="1"/>
     </row>
-    <row r="870" spans="1:29" ht="13.2">
+    <row r="870" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A870" s="1"/>
       <c r="B870" s="1"/>
       <c r="C870" s="1"/>
@@ -28606,7 +28606,7 @@
       <c r="AB870" s="1"/>
       <c r="AC870" s="1"/>
     </row>
-    <row r="871" spans="1:29" ht="13.2">
+    <row r="871" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A871" s="1"/>
       <c r="B871" s="1"/>
       <c r="C871" s="1"/>
@@ -28637,7 +28637,7 @@
       <c r="AB871" s="1"/>
       <c r="AC871" s="1"/>
     </row>
-    <row r="872" spans="1:29" ht="13.2">
+    <row r="872" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A872" s="1"/>
       <c r="B872" s="1"/>
       <c r="C872" s="1"/>
@@ -28668,7 +28668,7 @@
       <c r="AB872" s="1"/>
       <c r="AC872" s="1"/>
     </row>
-    <row r="873" spans="1:29" ht="13.2">
+    <row r="873" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A873" s="1"/>
       <c r="B873" s="1"/>
       <c r="C873" s="1"/>
@@ -28699,7 +28699,7 @@
       <c r="AB873" s="1"/>
       <c r="AC873" s="1"/>
     </row>
-    <row r="874" spans="1:29" ht="13.2">
+    <row r="874" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A874" s="1"/>
       <c r="B874" s="1"/>
       <c r="C874" s="1"/>
@@ -28730,7 +28730,7 @@
       <c r="AB874" s="1"/>
       <c r="AC874" s="1"/>
     </row>
-    <row r="875" spans="1:29" ht="13.2">
+    <row r="875" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A875" s="1"/>
       <c r="B875" s="1"/>
       <c r="C875" s="1"/>
@@ -28761,7 +28761,7 @@
       <c r="AB875" s="1"/>
       <c r="AC875" s="1"/>
     </row>
-    <row r="876" spans="1:29" ht="13.2">
+    <row r="876" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A876" s="1"/>
       <c r="B876" s="1"/>
       <c r="C876" s="1"/>
@@ -28792,7 +28792,7 @@
       <c r="AB876" s="1"/>
       <c r="AC876" s="1"/>
     </row>
-    <row r="877" spans="1:29" ht="13.2">
+    <row r="877" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A877" s="1"/>
       <c r="B877" s="1"/>
       <c r="C877" s="1"/>
@@ -28823,7 +28823,7 @@
       <c r="AB877" s="1"/>
       <c r="AC877" s="1"/>
     </row>
-    <row r="878" spans="1:29" ht="13.2">
+    <row r="878" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A878" s="1"/>
       <c r="B878" s="1"/>
       <c r="C878" s="1"/>
@@ -28854,7 +28854,7 @@
       <c r="AB878" s="1"/>
       <c r="AC878" s="1"/>
     </row>
-    <row r="879" spans="1:29" ht="13.2">
+    <row r="879" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A879" s="1"/>
       <c r="B879" s="1"/>
       <c r="C879" s="1"/>
@@ -28885,7 +28885,7 @@
       <c r="AB879" s="1"/>
       <c r="AC879" s="1"/>
     </row>
-    <row r="880" spans="1:29" ht="13.2">
+    <row r="880" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A880" s="1"/>
       <c r="B880" s="1"/>
       <c r="C880" s="1"/>
@@ -28916,7 +28916,7 @@
       <c r="AB880" s="1"/>
       <c r="AC880" s="1"/>
     </row>
-    <row r="881" spans="1:29" ht="13.2">
+    <row r="881" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A881" s="1"/>
       <c r="B881" s="1"/>
       <c r="C881" s="1"/>
@@ -28947,7 +28947,7 @@
       <c r="AB881" s="1"/>
       <c r="AC881" s="1"/>
     </row>
-    <row r="882" spans="1:29" ht="13.2">
+    <row r="882" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A882" s="1"/>
       <c r="B882" s="1"/>
       <c r="C882" s="1"/>
@@ -28978,7 +28978,7 @@
       <c r="AB882" s="1"/>
       <c r="AC882" s="1"/>
     </row>
-    <row r="883" spans="1:29" ht="13.2">
+    <row r="883" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A883" s="1"/>
       <c r="B883" s="1"/>
       <c r="C883" s="1"/>
@@ -29009,7 +29009,7 @@
       <c r="AB883" s="1"/>
       <c r="AC883" s="1"/>
     </row>
-    <row r="884" spans="1:29" ht="13.2">
+    <row r="884" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A884" s="1"/>
       <c r="B884" s="1"/>
       <c r="C884" s="1"/>
@@ -29040,7 +29040,7 @@
       <c r="AB884" s="1"/>
       <c r="AC884" s="1"/>
     </row>
-    <row r="885" spans="1:29" ht="13.2">
+    <row r="885" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A885" s="1"/>
       <c r="B885" s="1"/>
       <c r="C885" s="1"/>
@@ -29071,7 +29071,7 @@
       <c r="AB885" s="1"/>
       <c r="AC885" s="1"/>
     </row>
-    <row r="886" spans="1:29" ht="13.2">
+    <row r="886" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A886" s="1"/>
       <c r="B886" s="1"/>
       <c r="C886" s="1"/>
@@ -29102,7 +29102,7 @@
       <c r="AB886" s="1"/>
       <c r="AC886" s="1"/>
     </row>
-    <row r="887" spans="1:29" ht="13.2">
+    <row r="887" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A887" s="1"/>
       <c r="B887" s="1"/>
       <c r="C887" s="1"/>
@@ -29133,7 +29133,7 @@
       <c r="AB887" s="1"/>
       <c r="AC887" s="1"/>
     </row>
-    <row r="888" spans="1:29" ht="13.2">
+    <row r="888" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A888" s="1"/>
       <c r="B888" s="1"/>
       <c r="C888" s="1"/>
@@ -29164,7 +29164,7 @@
       <c r="AB888" s="1"/>
       <c r="AC888" s="1"/>
     </row>
-    <row r="889" spans="1:29" ht="13.2">
+    <row r="889" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A889" s="1"/>
       <c r="B889" s="1"/>
       <c r="C889" s="1"/>
@@ -29195,7 +29195,7 @@
       <c r="AB889" s="1"/>
       <c r="AC889" s="1"/>
     </row>
-    <row r="890" spans="1:29" ht="13.2">
+    <row r="890" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A890" s="1"/>
       <c r="B890" s="1"/>
       <c r="C890" s="1"/>
@@ -29226,7 +29226,7 @@
       <c r="AB890" s="1"/>
       <c r="AC890" s="1"/>
     </row>
-    <row r="891" spans="1:29" ht="13.2">
+    <row r="891" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A891" s="1"/>
       <c r="B891" s="1"/>
       <c r="C891" s="1"/>
@@ -29257,7 +29257,7 @@
       <c r="AB891" s="1"/>
       <c r="AC891" s="1"/>
     </row>
-    <row r="892" spans="1:29" ht="13.2">
+    <row r="892" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A892" s="1"/>
       <c r="B892" s="1"/>
       <c r="C892" s="1"/>
@@ -29288,7 +29288,7 @@
       <c r="AB892" s="1"/>
       <c r="AC892" s="1"/>
     </row>
-    <row r="893" spans="1:29" ht="13.2">
+    <row r="893" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A893" s="1"/>
       <c r="B893" s="1"/>
       <c r="C893" s="1"/>
@@ -29319,7 +29319,7 @@
       <c r="AB893" s="1"/>
       <c r="AC893" s="1"/>
     </row>
-    <row r="894" spans="1:29" ht="13.2">
+    <row r="894" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A894" s="1"/>
       <c r="B894" s="1"/>
       <c r="C894" s="1"/>
@@ -29350,7 +29350,7 @@
       <c r="AB894" s="1"/>
       <c r="AC894" s="1"/>
     </row>
-    <row r="895" spans="1:29" ht="13.2">
+    <row r="895" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A895" s="1"/>
       <c r="B895" s="1"/>
       <c r="C895" s="1"/>
@@ -29381,7 +29381,7 @@
       <c r="AB895" s="1"/>
       <c r="AC895" s="1"/>
     </row>
-    <row r="896" spans="1:29" ht="13.2">
+    <row r="896" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A896" s="1"/>
       <c r="B896" s="1"/>
       <c r="C896" s="1"/>
@@ -29412,7 +29412,7 @@
       <c r="AB896" s="1"/>
       <c r="AC896" s="1"/>
     </row>
-    <row r="897" spans="1:29" ht="13.2">
+    <row r="897" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A897" s="1"/>
       <c r="B897" s="1"/>
       <c r="C897" s="1"/>
@@ -29443,7 +29443,7 @@
       <c r="AB897" s="1"/>
       <c r="AC897" s="1"/>
     </row>
-    <row r="898" spans="1:29" ht="13.2">
+    <row r="898" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A898" s="1"/>
       <c r="B898" s="1"/>
       <c r="C898" s="1"/>
@@ -29474,7 +29474,7 @@
       <c r="AB898" s="1"/>
       <c r="AC898" s="1"/>
     </row>
-    <row r="899" spans="1:29" ht="13.2">
+    <row r="899" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A899" s="1"/>
       <c r="B899" s="1"/>
       <c r="C899" s="1"/>
@@ -29505,7 +29505,7 @@
       <c r="AB899" s="1"/>
       <c r="AC899" s="1"/>
     </row>
-    <row r="900" spans="1:29" ht="13.2">
+    <row r="900" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A900" s="1"/>
       <c r="B900" s="1"/>
       <c r="C900" s="1"/>
@@ -29536,7 +29536,7 @@
       <c r="AB900" s="1"/>
       <c r="AC900" s="1"/>
     </row>
-    <row r="901" spans="1:29" ht="13.2">
+    <row r="901" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A901" s="1"/>
       <c r="B901" s="1"/>
       <c r="C901" s="1"/>
@@ -29567,7 +29567,7 @@
       <c r="AB901" s="1"/>
       <c r="AC901" s="1"/>
     </row>
-    <row r="902" spans="1:29" ht="13.2">
+    <row r="902" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A902" s="1"/>
       <c r="B902" s="1"/>
       <c r="C902" s="1"/>
@@ -29598,7 +29598,7 @@
       <c r="AB902" s="1"/>
       <c r="AC902" s="1"/>
     </row>
-    <row r="903" spans="1:29" ht="13.2">
+    <row r="903" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A903" s="1"/>
       <c r="B903" s="1"/>
       <c r="C903" s="1"/>
@@ -29629,7 +29629,7 @@
       <c r="AB903" s="1"/>
       <c r="AC903" s="1"/>
     </row>
-    <row r="904" spans="1:29" ht="13.2">
+    <row r="904" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A904" s="1"/>
       <c r="B904" s="1"/>
       <c r="C904" s="1"/>
@@ -29660,7 +29660,7 @@
       <c r="AB904" s="1"/>
       <c r="AC904" s="1"/>
     </row>
-    <row r="905" spans="1:29" ht="13.2">
+    <row r="905" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A905" s="1"/>
       <c r="B905" s="1"/>
       <c r="C905" s="1"/>
@@ -29691,7 +29691,7 @@
       <c r="AB905" s="1"/>
       <c r="AC905" s="1"/>
     </row>
-    <row r="906" spans="1:29" ht="13.2">
+    <row r="906" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A906" s="1"/>
       <c r="B906" s="1"/>
       <c r="C906" s="1"/>
@@ -29722,7 +29722,7 @@
       <c r="AB906" s="1"/>
       <c r="AC906" s="1"/>
     </row>
-    <row r="907" spans="1:29" ht="13.2">
+    <row r="907" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A907" s="1"/>
       <c r="B907" s="1"/>
       <c r="C907" s="1"/>
@@ -29753,7 +29753,7 @@
       <c r="AB907" s="1"/>
       <c r="AC907" s="1"/>
     </row>
-    <row r="908" spans="1:29" ht="13.2">
+    <row r="908" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A908" s="1"/>
       <c r="B908" s="1"/>
       <c r="C908" s="1"/>
@@ -29784,7 +29784,7 @@
       <c r="AB908" s="1"/>
       <c r="AC908" s="1"/>
     </row>
-    <row r="909" spans="1:29" ht="13.2">
+    <row r="909" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A909" s="1"/>
       <c r="B909" s="1"/>
       <c r="C909" s="1"/>
@@ -29815,7 +29815,7 @@
       <c r="AB909" s="1"/>
       <c r="AC909" s="1"/>
     </row>
-    <row r="910" spans="1:29" ht="13.2">
+    <row r="910" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A910" s="1"/>
       <c r="B910" s="1"/>
       <c r="C910" s="1"/>
@@ -29846,7 +29846,7 @@
       <c r="AB910" s="1"/>
       <c r="AC910" s="1"/>
     </row>
-    <row r="911" spans="1:29" ht="13.2">
+    <row r="911" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A911" s="1"/>
       <c r="B911" s="1"/>
       <c r="C911" s="1"/>
@@ -29877,7 +29877,7 @@
       <c r="AB911" s="1"/>
       <c r="AC911" s="1"/>
     </row>
-    <row r="912" spans="1:29" ht="13.2">
+    <row r="912" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A912" s="1"/>
       <c r="B912" s="1"/>
       <c r="C912" s="1"/>
@@ -29908,7 +29908,7 @@
       <c r="AB912" s="1"/>
       <c r="AC912" s="1"/>
     </row>
-    <row r="913" spans="1:29" ht="13.2">
+    <row r="913" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A913" s="1"/>
       <c r="B913" s="1"/>
       <c r="C913" s="1"/>
@@ -29939,7 +29939,7 @@
       <c r="AB913" s="1"/>
       <c r="AC913" s="1"/>
     </row>
-    <row r="914" spans="1:29" ht="13.2">
+    <row r="914" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A914" s="1"/>
       <c r="B914" s="1"/>
       <c r="C914" s="1"/>
@@ -29970,7 +29970,7 @@
       <c r="AB914" s="1"/>
       <c r="AC914" s="1"/>
     </row>
-    <row r="915" spans="1:29" ht="13.2">
+    <row r="915" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A915" s="1"/>
       <c r="B915" s="1"/>
       <c r="C915" s="1"/>
@@ -30001,7 +30001,7 @@
       <c r="AB915" s="1"/>
       <c r="AC915" s="1"/>
     </row>
-    <row r="916" spans="1:29" ht="13.2">
+    <row r="916" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A916" s="1"/>
       <c r="B916" s="1"/>
       <c r="C916" s="1"/>
@@ -30032,7 +30032,7 @@
       <c r="AB916" s="1"/>
       <c r="AC916" s="1"/>
     </row>
-    <row r="917" spans="1:29" ht="13.2">
+    <row r="917" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A917" s="1"/>
       <c r="B917" s="1"/>
       <c r="C917" s="1"/>
@@ -30063,7 +30063,7 @@
       <c r="AB917" s="1"/>
       <c r="AC917" s="1"/>
     </row>
-    <row r="918" spans="1:29" ht="13.2">
+    <row r="918" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A918" s="1"/>
       <c r="B918" s="1"/>
       <c r="C918" s="1"/>
@@ -30094,7 +30094,7 @@
       <c r="AB918" s="1"/>
       <c r="AC918" s="1"/>
     </row>
-    <row r="919" spans="1:29" ht="13.2">
+    <row r="919" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A919" s="1"/>
       <c r="B919" s="1"/>
       <c r="C919" s="1"/>
@@ -30125,7 +30125,7 @@
       <c r="AB919" s="1"/>
       <c r="AC919" s="1"/>
     </row>
-    <row r="920" spans="1:29" ht="13.2">
+    <row r="920" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A920" s="1"/>
       <c r="B920" s="1"/>
       <c r="C920" s="1"/>
@@ -30156,7 +30156,7 @@
       <c r="AB920" s="1"/>
       <c r="AC920" s="1"/>
     </row>
-    <row r="921" spans="1:29" ht="13.2">
+    <row r="921" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A921" s="1"/>
       <c r="B921" s="1"/>
       <c r="C921" s="1"/>
@@ -30187,7 +30187,7 @@
       <c r="AB921" s="1"/>
       <c r="AC921" s="1"/>
     </row>
-    <row r="922" spans="1:29" ht="13.2">
+    <row r="922" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A922" s="1"/>
       <c r="B922" s="1"/>
       <c r="C922" s="1"/>
@@ -30218,7 +30218,7 @@
       <c r="AB922" s="1"/>
       <c r="AC922" s="1"/>
     </row>
-    <row r="923" spans="1:29" ht="13.2">
+    <row r="923" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A923" s="1"/>
       <c r="B923" s="1"/>
       <c r="C923" s="1"/>
@@ -30249,7 +30249,7 @@
       <c r="AB923" s="1"/>
       <c r="AC923" s="1"/>
     </row>
-    <row r="924" spans="1:29" ht="13.2">
+    <row r="924" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A924" s="1"/>
       <c r="B924" s="1"/>
       <c r="C924" s="1"/>
@@ -30280,7 +30280,7 @@
       <c r="AB924" s="1"/>
       <c r="AC924" s="1"/>
     </row>
-    <row r="925" spans="1:29" ht="13.2">
+    <row r="925" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A925" s="1"/>
       <c r="B925" s="1"/>
       <c r="C925" s="1"/>
@@ -30311,7 +30311,7 @@
       <c r="AB925" s="1"/>
       <c r="AC925" s="1"/>
     </row>
-    <row r="926" spans="1:29" ht="13.2">
+    <row r="926" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A926" s="1"/>
       <c r="B926" s="1"/>
       <c r="C926" s="1"/>
@@ -30342,7 +30342,7 @@
       <c r="AB926" s="1"/>
       <c r="AC926" s="1"/>
     </row>
-    <row r="927" spans="1:29" ht="13.2">
+    <row r="927" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A927" s="1"/>
       <c r="B927" s="1"/>
       <c r="C927" s="1"/>
@@ -30373,7 +30373,7 @@
       <c r="AB927" s="1"/>
       <c r="AC927" s="1"/>
     </row>
-    <row r="928" spans="1:29" ht="13.2">
+    <row r="928" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A928" s="1"/>
       <c r="B928" s="1"/>
       <c r="C928" s="1"/>
@@ -30404,7 +30404,7 @@
       <c r="AB928" s="1"/>
       <c r="AC928" s="1"/>
     </row>
-    <row r="929" spans="1:29" ht="13.2">
+    <row r="929" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A929" s="1"/>
       <c r="B929" s="1"/>
       <c r="C929" s="1"/>
@@ -30435,7 +30435,7 @@
       <c r="AB929" s="1"/>
       <c r="AC929" s="1"/>
     </row>
-    <row r="930" spans="1:29" ht="13.2">
+    <row r="930" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A930" s="1"/>
       <c r="B930" s="1"/>
       <c r="C930" s="1"/>
@@ -30466,7 +30466,7 @@
       <c r="AB930" s="1"/>
       <c r="AC930" s="1"/>
     </row>
-    <row r="931" spans="1:29" ht="13.2">
+    <row r="931" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A931" s="1"/>
       <c r="B931" s="1"/>
       <c r="C931" s="1"/>
@@ -30497,7 +30497,7 @@
       <c r="AB931" s="1"/>
       <c r="AC931" s="1"/>
     </row>
-    <row r="932" spans="1:29" ht="13.2">
+    <row r="932" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A932" s="1"/>
       <c r="B932" s="1"/>
       <c r="C932" s="1"/>
@@ -30528,7 +30528,7 @@
       <c r="AB932" s="1"/>
       <c r="AC932" s="1"/>
     </row>
-    <row r="933" spans="1:29" ht="13.2">
+    <row r="933" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A933" s="1"/>
       <c r="B933" s="1"/>
       <c r="C933" s="1"/>
@@ -30559,7 +30559,7 @@
       <c r="AB933" s="1"/>
       <c r="AC933" s="1"/>
     </row>
-    <row r="934" spans="1:29" ht="13.2">
+    <row r="934" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A934" s="1"/>
       <c r="B934" s="1"/>
       <c r="C934" s="1"/>
@@ -30590,7 +30590,7 @@
       <c r="AB934" s="1"/>
       <c r="AC934" s="1"/>
     </row>
-    <row r="935" spans="1:29" ht="13.2">
+    <row r="935" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A935" s="1"/>
       <c r="B935" s="1"/>
       <c r="C935" s="1"/>
@@ -30621,7 +30621,7 @@
       <c r="AB935" s="1"/>
       <c r="AC935" s="1"/>
     </row>
-    <row r="936" spans="1:29" ht="13.2">
+    <row r="936" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A936" s="1"/>
       <c r="B936" s="1"/>
       <c r="C936" s="1"/>
@@ -30652,7 +30652,7 @@
       <c r="AB936" s="1"/>
       <c r="AC936" s="1"/>
     </row>
-    <row r="937" spans="1:29" ht="13.2">
+    <row r="937" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A937" s="1"/>
       <c r="B937" s="1"/>
       <c r="C937" s="1"/>
@@ -30683,7 +30683,7 @@
       <c r="AB937" s="1"/>
       <c r="AC937" s="1"/>
     </row>
-    <row r="938" spans="1:29" ht="13.2">
+    <row r="938" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A938" s="1"/>
       <c r="B938" s="1"/>
       <c r="C938" s="1"/>
@@ -30714,7 +30714,7 @@
       <c r="AB938" s="1"/>
       <c r="AC938" s="1"/>
     </row>
-    <row r="939" spans="1:29" ht="13.2">
+    <row r="939" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A939" s="1"/>
       <c r="B939" s="1"/>
       <c r="C939" s="1"/>
@@ -30745,7 +30745,7 @@
       <c r="AB939" s="1"/>
       <c r="AC939" s="1"/>
     </row>
-    <row r="940" spans="1:29" ht="13.2">
+    <row r="940" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A940" s="1"/>
       <c r="B940" s="1"/>
       <c r="C940" s="1"/>
@@ -30776,7 +30776,7 @@
       <c r="AB940" s="1"/>
       <c r="AC940" s="1"/>
     </row>
-    <row r="941" spans="1:29" ht="13.2">
+    <row r="941" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A941" s="1"/>
       <c r="B941" s="1"/>
       <c r="C941" s="1"/>
@@ -30807,7 +30807,7 @@
       <c r="AB941" s="1"/>
       <c r="AC941" s="1"/>
     </row>
-    <row r="942" spans="1:29" ht="13.2">
+    <row r="942" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A942" s="1"/>
       <c r="B942" s="1"/>
       <c r="C942" s="1"/>
@@ -30838,7 +30838,7 @@
       <c r="AB942" s="1"/>
       <c r="AC942" s="1"/>
     </row>
-    <row r="943" spans="1:29" ht="13.2">
+    <row r="943" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A943" s="1"/>
       <c r="B943" s="1"/>
       <c r="C943" s="1"/>
@@ -30869,7 +30869,7 @@
       <c r="AB943" s="1"/>
       <c r="AC943" s="1"/>
     </row>
-    <row r="944" spans="1:29" ht="13.2">
+    <row r="944" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A944" s="1"/>
       <c r="B944" s="1"/>
       <c r="C944" s="1"/>
@@ -30900,7 +30900,7 @@
       <c r="AB944" s="1"/>
       <c r="AC944" s="1"/>
     </row>
-    <row r="945" spans="1:29" ht="13.2">
+    <row r="945" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A945" s="1"/>
       <c r="B945" s="1"/>
       <c r="C945" s="1"/>
@@ -30931,7 +30931,7 @@
       <c r="AB945" s="1"/>
       <c r="AC945" s="1"/>
     </row>
-    <row r="946" spans="1:29" ht="13.2">
+    <row r="946" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A946" s="1"/>
       <c r="B946" s="1"/>
       <c r="C946" s="1"/>
@@ -30962,7 +30962,7 @@
       <c r="AB946" s="1"/>
       <c r="AC946" s="1"/>
     </row>
-    <row r="947" spans="1:29" ht="13.2">
+    <row r="947" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A947" s="1"/>
       <c r="B947" s="1"/>
       <c r="C947" s="1"/>
@@ -30993,7 +30993,7 @@
       <c r="AB947" s="1"/>
       <c r="AC947" s="1"/>
     </row>
-    <row r="948" spans="1:29" ht="13.2">
+    <row r="948" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A948" s="1"/>
       <c r="B948" s="1"/>
       <c r="C948" s="1"/>
@@ -31024,7 +31024,7 @@
       <c r="AB948" s="1"/>
       <c r="AC948" s="1"/>
     </row>
-    <row r="949" spans="1:29" ht="13.2">
+    <row r="949" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A949" s="1"/>
       <c r="B949" s="1"/>
       <c r="C949" s="1"/>
@@ -31055,7 +31055,7 @@
       <c r="AB949" s="1"/>
       <c r="AC949" s="1"/>
     </row>
-    <row r="950" spans="1:29" ht="13.2">
+    <row r="950" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A950" s="1"/>
       <c r="B950" s="1"/>
       <c r="C950" s="1"/>
@@ -31086,7 +31086,7 @@
       <c r="AB950" s="1"/>
       <c r="AC950" s="1"/>
     </row>
-    <row r="951" spans="1:29" ht="13.2">
+    <row r="951" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A951" s="1"/>
       <c r="B951" s="1"/>
       <c r="C951" s="1"/>
@@ -31117,7 +31117,7 @@
       <c r="AB951" s="1"/>
       <c r="AC951" s="1"/>
     </row>
-    <row r="952" spans="1:29" ht="13.2">
+    <row r="952" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A952" s="1"/>
       <c r="B952" s="1"/>
       <c r="C952" s="1"/>
@@ -31148,7 +31148,7 @@
       <c r="AB952" s="1"/>
       <c r="AC952" s="1"/>
     </row>
-    <row r="953" spans="1:29" ht="13.2">
+    <row r="953" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A953" s="1"/>
       <c r="B953" s="1"/>
       <c r="C953" s="1"/>
@@ -31179,7 +31179,7 @@
       <c r="AB953" s="1"/>
       <c r="AC953" s="1"/>
     </row>
-    <row r="954" spans="1:29" ht="13.2">
+    <row r="954" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A954" s="1"/>
       <c r="B954" s="1"/>
       <c r="C954" s="1"/>
@@ -31210,7 +31210,7 @@
       <c r="AB954" s="1"/>
       <c r="AC954" s="1"/>
     </row>
-    <row r="955" spans="1:29" ht="13.2">
+    <row r="955" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A955" s="1"/>
       <c r="B955" s="1"/>
       <c r="C955" s="1"/>
@@ -31241,7 +31241,7 @@
       <c r="AB955" s="1"/>
       <c r="AC955" s="1"/>
     </row>
-    <row r="956" spans="1:29" ht="13.2">
+    <row r="956" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A956" s="1"/>
       <c r="B956" s="1"/>
       <c r="C956" s="1"/>
@@ -31272,7 +31272,7 @@
       <c r="AB956" s="1"/>
       <c r="AC956" s="1"/>
     </row>
-    <row r="957" spans="1:29" ht="13.2">
+    <row r="957" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A957" s="1"/>
       <c r="B957" s="1"/>
       <c r="C957" s="1"/>
@@ -31303,7 +31303,7 @@
       <c r="AB957" s="1"/>
       <c r="AC957" s="1"/>
     </row>
-    <row r="958" spans="1:29" ht="13.2">
+    <row r="958" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A958" s="1"/>
       <c r="B958" s="1"/>
       <c r="C958" s="1"/>
@@ -31334,7 +31334,7 @@
       <c r="AB958" s="1"/>
       <c r="AC958" s="1"/>
     </row>
-    <row r="959" spans="1:29" ht="13.2">
+    <row r="959" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A959" s="1"/>
       <c r="B959" s="1"/>
       <c r="C959" s="1"/>
@@ -31365,7 +31365,7 @@
       <c r="AB959" s="1"/>
       <c r="AC959" s="1"/>
     </row>
-    <row r="960" spans="1:29" ht="13.2">
+    <row r="960" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A960" s="1"/>
       <c r="B960" s="1"/>
       <c r="C960" s="1"/>
@@ -31396,7 +31396,7 @@
       <c r="AB960" s="1"/>
       <c r="AC960" s="1"/>
     </row>
-    <row r="961" spans="1:29" ht="13.2">
+    <row r="961" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A961" s="1"/>
       <c r="B961" s="1"/>
       <c r="C961" s="1"/>
@@ -31427,7 +31427,7 @@
       <c r="AB961" s="1"/>
       <c r="AC961" s="1"/>
     </row>
-    <row r="962" spans="1:29" ht="13.2">
+    <row r="962" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A962" s="1"/>
       <c r="B962" s="1"/>
       <c r="C962" s="1"/>
@@ -31458,7 +31458,7 @@
       <c r="AB962" s="1"/>
       <c r="AC962" s="1"/>
     </row>
-    <row r="963" spans="1:29" ht="13.2">
+    <row r="963" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A963" s="1"/>
       <c r="B963" s="1"/>
       <c r="C963" s="1"/>
@@ -31489,7 +31489,7 @@
       <c r="AB963" s="1"/>
       <c r="AC963" s="1"/>
     </row>
-    <row r="964" spans="1:29" ht="13.2">
+    <row r="964" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A964" s="1"/>
       <c r="B964" s="1"/>
       <c r="C964" s="1"/>
@@ -31520,7 +31520,7 @@
       <c r="AB964" s="1"/>
       <c r="AC964" s="1"/>
     </row>
-    <row r="965" spans="1:29" ht="13.2">
+    <row r="965" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A965" s="1"/>
       <c r="B965" s="1"/>
       <c r="C965" s="1"/>
@@ -31551,7 +31551,7 @@
       <c r="AB965" s="1"/>
       <c r="AC965" s="1"/>
     </row>
-    <row r="966" spans="1:29" ht="13.2">
+    <row r="966" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A966" s="1"/>
       <c r="B966" s="1"/>
       <c r="C966" s="1"/>
@@ -31582,7 +31582,7 @@
       <c r="AB966" s="1"/>
       <c r="AC966" s="1"/>
     </row>
-    <row r="967" spans="1:29" ht="13.2">
+    <row r="967" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A967" s="1"/>
       <c r="B967" s="1"/>
       <c r="C967" s="1"/>
@@ -31613,7 +31613,7 @@
       <c r="AB967" s="1"/>
       <c r="AC967" s="1"/>
     </row>
-    <row r="968" spans="1:29" ht="13.2">
+    <row r="968" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A968" s="1"/>
       <c r="B968" s="1"/>
       <c r="C968" s="1"/>
@@ -31644,7 +31644,7 @@
       <c r="AB968" s="1"/>
       <c r="AC968" s="1"/>
     </row>
-    <row r="969" spans="1:29" ht="13.2">
+    <row r="969" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A969" s="1"/>
       <c r="B969" s="1"/>
       <c r="C969" s="1"/>
@@ -31675,7 +31675,7 @@
       <c r="AB969" s="1"/>
       <c r="AC969" s="1"/>
     </row>
-    <row r="970" spans="1:29" ht="13.2">
+    <row r="970" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A970" s="1"/>
       <c r="B970" s="1"/>
       <c r="C970" s="1"/>
@@ -31706,7 +31706,7 @@
       <c r="AB970" s="1"/>
       <c r="AC970" s="1"/>
     </row>
-    <row r="971" spans="1:29" ht="13.2">
+    <row r="971" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A971" s="1"/>
       <c r="B971" s="1"/>
       <c r="C971" s="1"/>
@@ -31737,7 +31737,7 @@
       <c r="AB971" s="1"/>
       <c r="AC971" s="1"/>
     </row>
-    <row r="972" spans="1:29" ht="13.2">
+    <row r="972" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A972" s="1"/>
       <c r="B972" s="1"/>
       <c r="C972" s="1"/>
@@ -31768,7 +31768,7 @@
       <c r="AB972" s="1"/>
       <c r="AC972" s="1"/>
     </row>
-    <row r="973" spans="1:29" ht="13.2">
+    <row r="973" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A973" s="1"/>
       <c r="B973" s="1"/>
       <c r="C973" s="1"/>
@@ -31799,7 +31799,7 @@
       <c r="AB973" s="1"/>
       <c r="AC973" s="1"/>
     </row>
-    <row r="974" spans="1:29" ht="13.2">
+    <row r="974" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A974" s="1"/>
       <c r="B974" s="1"/>
       <c r="C974" s="1"/>
@@ -31830,7 +31830,7 @@
       <c r="AB974" s="1"/>
       <c r="AC974" s="1"/>
     </row>
-    <row r="975" spans="1:29" ht="13.2">
+    <row r="975" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A975" s="1"/>
       <c r="B975" s="1"/>
       <c r="C975" s="1"/>
@@ -31861,7 +31861,7 @@
       <c r="AB975" s="1"/>
       <c r="AC975" s="1"/>
     </row>
-    <row r="976" spans="1:29" ht="13.2">
+    <row r="976" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A976" s="1"/>
       <c r="B976" s="1"/>
       <c r="C976" s="1"/>
@@ -31892,7 +31892,7 @@
       <c r="AB976" s="1"/>
       <c r="AC976" s="1"/>
     </row>
-    <row r="977" spans="1:29" ht="13.2">
+    <row r="977" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A977" s="1"/>
       <c r="B977" s="1"/>
       <c r="C977" s="1"/>
@@ -31923,7 +31923,7 @@
       <c r="AB977" s="1"/>
       <c r="AC977" s="1"/>
     </row>
-    <row r="978" spans="1:29" ht="13.2">
+    <row r="978" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A978" s="1"/>
       <c r="B978" s="1"/>
       <c r="C978" s="1"/>
@@ -31954,7 +31954,7 @@
       <c r="AB978" s="1"/>
       <c r="AC978" s="1"/>
     </row>
-    <row r="979" spans="1:29" ht="13.2">
+    <row r="979" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A979" s="1"/>
       <c r="B979" s="1"/>
       <c r="C979" s="1"/>
@@ -31985,7 +31985,7 @@
       <c r="AB979" s="1"/>
       <c r="AC979" s="1"/>
     </row>
-    <row r="980" spans="1:29" ht="13.2">
+    <row r="980" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A980" s="1"/>
       <c r="B980" s="1"/>
       <c r="C980" s="1"/>
@@ -32016,7 +32016,7 @@
       <c r="AB980" s="1"/>
       <c r="AC980" s="1"/>
     </row>
-    <row r="981" spans="1:29" ht="13.2">
+    <row r="981" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A981" s="1"/>
       <c r="B981" s="1"/>
       <c r="C981" s="1"/>
@@ -32047,7 +32047,7 @@
       <c r="AB981" s="1"/>
       <c r="AC981" s="1"/>
     </row>
-    <row r="982" spans="1:29" ht="13.2">
+    <row r="982" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A982" s="1"/>
       <c r="B982" s="1"/>
       <c r="C982" s="1"/>
@@ -32078,7 +32078,7 @@
       <c r="AB982" s="1"/>
       <c r="AC982" s="1"/>
     </row>
-    <row r="983" spans="1:29" ht="13.2">
+    <row r="983" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A983" s="1"/>
       <c r="B983" s="1"/>
       <c r="C983" s="1"/>
@@ -32109,7 +32109,7 @@
       <c r="AB983" s="1"/>
       <c r="AC983" s="1"/>
     </row>
-    <row r="984" spans="1:29" ht="13.2">
+    <row r="984" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A984" s="1"/>
       <c r="B984" s="1"/>
       <c r="C984" s="1"/>
@@ -32140,7 +32140,7 @@
       <c r="AB984" s="1"/>
       <c r="AC984" s="1"/>
     </row>
-    <row r="985" spans="1:29" ht="13.2">
+    <row r="985" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A985" s="1"/>
       <c r="B985" s="1"/>
       <c r="C985" s="1"/>
@@ -32171,7 +32171,7 @@
       <c r="AB985" s="1"/>
       <c r="AC985" s="1"/>
     </row>
-    <row r="986" spans="1:29" ht="13.2">
+    <row r="986" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A986" s="1"/>
       <c r="B986" s="1"/>
       <c r="C986" s="1"/>
@@ -32202,7 +32202,7 @@
       <c r="AB986" s="1"/>
       <c r="AC986" s="1"/>
     </row>
-    <row r="987" spans="1:29" ht="13.2">
+    <row r="987" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A987" s="1"/>
       <c r="B987" s="1"/>
       <c r="C987" s="1"/>
@@ -32233,7 +32233,7 @@
       <c r="AB987" s="1"/>
       <c r="AC987" s="1"/>
     </row>
-    <row r="988" spans="1:29" ht="13.2">
+    <row r="988" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A988" s="1"/>
       <c r="B988" s="1"/>
       <c r="C988" s="1"/>
@@ -32264,7 +32264,7 @@
       <c r="AB988" s="1"/>
       <c r="AC988" s="1"/>
     </row>
-    <row r="989" spans="1:29" ht="13.2">
+    <row r="989" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A989" s="1"/>
       <c r="B989" s="1"/>
       <c r="C989" s="1"/>
@@ -32295,7 +32295,7 @@
       <c r="AB989" s="1"/>
       <c r="AC989" s="1"/>
     </row>
-    <row r="990" spans="1:29" ht="13.2">
+    <row r="990" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A990" s="1"/>
       <c r="B990" s="1"/>
       <c r="C990" s="1"/>
@@ -32326,7 +32326,7 @@
       <c r="AB990" s="1"/>
       <c r="AC990" s="1"/>
     </row>
-    <row r="991" spans="1:29" ht="13.2">
+    <row r="991" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A991" s="1"/>
       <c r="B991" s="1"/>
       <c r="C991" s="1"/>
@@ -32357,7 +32357,7 @@
       <c r="AB991" s="1"/>
       <c r="AC991" s="1"/>
     </row>
-    <row r="992" spans="1:29" ht="13.2">
+    <row r="992" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A992" s="1"/>
       <c r="B992" s="1"/>
       <c r="C992" s="1"/>
@@ -32388,7 +32388,7 @@
       <c r="AB992" s="1"/>
       <c r="AC992" s="1"/>
     </row>
-    <row r="993" spans="1:29" ht="13.2">
+    <row r="993" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A993" s="1"/>
       <c r="B993" s="1"/>
       <c r="C993" s="1"/>
@@ -32419,7 +32419,7 @@
       <c r="AB993" s="1"/>
       <c r="AC993" s="1"/>
     </row>
-    <row r="994" spans="1:29" ht="13.2">
+    <row r="994" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A994" s="1"/>
       <c r="B994" s="1"/>
       <c r="C994" s="1"/>
@@ -32450,7 +32450,7 @@
       <c r="AB994" s="1"/>
       <c r="AC994" s="1"/>
     </row>
-    <row r="995" spans="1:29" ht="13.2">
+    <row r="995" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A995" s="1"/>
       <c r="B995" s="1"/>
       <c r="C995" s="1"/>
@@ -32481,7 +32481,7 @@
       <c r="AB995" s="1"/>
       <c r="AC995" s="1"/>
     </row>
-    <row r="996" spans="1:29" ht="13.2">
+    <row r="996" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A996" s="1"/>
       <c r="B996" s="1"/>
       <c r="C996" s="1"/>
@@ -32512,7 +32512,7 @@
       <c r="AB996" s="1"/>
       <c r="AC996" s="1"/>
     </row>
-    <row r="997" spans="1:29" ht="13.2">
+    <row r="997" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A997" s="1"/>
       <c r="B997" s="1"/>
       <c r="C997" s="1"/>
@@ -32543,7 +32543,7 @@
       <c r="AB997" s="1"/>
       <c r="AC997" s="1"/>
     </row>
-    <row r="998" spans="1:29" ht="13.2">
+    <row r="998" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A998" s="1"/>
       <c r="B998" s="1"/>
       <c r="C998" s="1"/>
@@ -32574,7 +32574,7 @@
       <c r="AB998" s="1"/>
       <c r="AC998" s="1"/>
     </row>
-    <row r="999" spans="1:29" ht="13.2">
+    <row r="999" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A999" s="1"/>
       <c r="B999" s="1"/>
       <c r="C999" s="1"/>
@@ -32605,7 +32605,7 @@
       <c r="AB999" s="1"/>
       <c r="AC999" s="1"/>
     </row>
-    <row r="1000" spans="1:29" ht="13.2">
+    <row r="1000" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1000" s="1"/>
       <c r="B1000" s="1"/>
       <c r="C1000" s="1"/>
@@ -32636,7 +32636,7 @@
       <c r="AB1000" s="1"/>
       <c r="AC1000" s="1"/>
     </row>
-    <row r="1001" spans="1:29" ht="13.2">
+    <row r="1001" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1001" s="1"/>
       <c r="B1001" s="1"/>
       <c r="C1001" s="1"/>
